--- a/jogos_2026-08-08.xlsx
+++ b/jogos_2026-08-08.xlsx
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="G10">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="G11">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G25">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G27">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G35">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G37">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G42">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="G47">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G48">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="G49">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G50">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G59">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G63">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G65">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="G68">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G69">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G71">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G72">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="G75">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G81">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G82">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G100">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G101">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G102">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G111">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="G114">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G147">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G148">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G149">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G150">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G151">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G152">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G194">
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G195">

--- a/jogos_2026-08-08.xlsx
+++ b/jogos_2026-08-08.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU200"/>
+  <dimension ref="A1:AU206"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1729,27 +1729,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>06:15</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="G9">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-08-08 06:15:00</t>
+          <t>2026-08-08 06:00:00</t>
         </is>
       </c>
     </row>
@@ -1892,12 +1892,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G10">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-08-08 06:30:00</t>
+          <t>2026-08-08 06:15:00</t>
         </is>
       </c>
     </row>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="G11">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="G12">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2026-08-08 07:00:00</t>
+          <t>2026-08-08 06:30:00</t>
         </is>
       </c>
     </row>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tegevajaro Miyazaki</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G13">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Tegevajaro Miyazaki</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G14">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G15">
@@ -2875,22 +2875,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="G16">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G17">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shimizu S-Pulse</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Shimizu S-Pulse</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="G22">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="G23">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2026-08-08 07:15:00</t>
+          <t>2026-08-08 07:00:00</t>
         </is>
       </c>
     </row>
@@ -4174,27 +4174,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="G24">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>2026-08-08 07:30:00</t>
+          <t>2026-08-08 07:15:00</t>
         </is>
       </c>
     </row>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G27">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G29">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G31">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G32">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>2026-08-08 08:00:00</t>
+          <t>2026-08-08 07:30:00</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G33">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G34">
@@ -5972,22 +5972,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G35">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G38">
@@ -6624,22 +6624,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G39">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G40">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>2026-08-08 08:30:00</t>
+          <t>2026-08-08 08:00:00</t>
         </is>
       </c>
     </row>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G42">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G43">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>2026-08-08 08:35:00</t>
+          <t>2026-08-08 08:30:00</t>
         </is>
       </c>
     </row>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G44">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G45">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>2026-08-08 09:00:00</t>
+          <t>2026-08-08 08:35:00</t>
         </is>
       </c>
     </row>
@@ -7765,22 +7765,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G46">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G47">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="G48">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G49">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="G50">
@@ -8580,22 +8580,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G51">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G52">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G53">
@@ -9064,27 +9064,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="O54">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P54">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9215,7 +9215,7 @@
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>2026-08-08 09:30:00</t>
+          <t>2026-08-08 09:00:00</t>
         </is>
       </c>
     </row>
@@ -9227,12 +9227,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>2026-08-08 09:45:00</t>
+          <t>2026-08-08 09:30:00</t>
         </is>
       </c>
     </row>
@@ -9390,12 +9390,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G56">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>2026-08-08 10:00:00</t>
+          <t>2026-08-08 09:45:00</t>
         </is>
       </c>
     </row>
@@ -9558,22 +9558,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G57">
@@ -9721,7 +9721,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G59">
@@ -10047,7 +10047,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G60">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G61">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G62">
@@ -10531,27 +10531,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G63">
@@ -10682,7 +10682,7 @@
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>2026-08-08 10:30:00</t>
+          <t>2026-08-08 10:00:00</t>
         </is>
       </c>
     </row>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G64">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G65">
@@ -11025,7 +11025,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G66">
@@ -11183,27 +11183,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="G67">
@@ -11334,7 +11334,7 @@
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>2026-08-08 11:00:00</t>
+          <t>2026-08-08 10:30:00</t>
         </is>
       </c>
     </row>
@@ -11351,22 +11351,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G68">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="G69">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G70">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G71">
@@ -12003,7 +12003,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G72">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G73">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G74">
@@ -12655,7 +12655,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G76">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G77">
@@ -12981,22 +12981,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G78">
@@ -13144,22 +13144,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G79">
@@ -13307,22 +13307,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G80">
@@ -13470,22 +13470,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G81">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G82">
@@ -13796,7 +13796,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G83">
@@ -13959,22 +13959,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G84">
@@ -14122,22 +14122,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G85">
@@ -14280,12 +14280,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G86">
@@ -14431,7 +14431,7 @@
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>2026-08-08 11:30:00</t>
+          <t>2026-08-08 11:00:00</t>
         </is>
       </c>
     </row>
@@ -14443,27 +14443,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G87">
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>2026-08-08 11:30:00</t>
+          <t>2026-08-08 11:00:00</t>
         </is>
       </c>
     </row>
@@ -14611,22 +14611,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O88">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P88">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -14692,10 +14692,10 @@
         <v>0</v>
       </c>
       <c r="AA88">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB88">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC88">
         <v>0</v>
@@ -14774,7 +14774,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="G89">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q90">
         <v>0</v>
@@ -15018,10 +15018,10 @@
         <v>0</v>
       </c>
       <c r="AA90">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB90">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC90">
         <v>0</v>
@@ -15095,27 +15095,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G91">
@@ -15246,7 +15246,7 @@
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>2026-08-08 12:00:00</t>
+          <t>2026-08-08 11:30:00</t>
         </is>
       </c>
     </row>
@@ -15258,27 +15258,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G92">
@@ -15409,7 +15409,7 @@
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>2026-08-08 12:00:00</t>
+          <t>2026-08-08 11:30:00</t>
         </is>
       </c>
     </row>
@@ -15426,22 +15426,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G93">
@@ -15589,22 +15589,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G94">
@@ -15752,7 +15752,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G95">
@@ -15915,22 +15915,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G96">
@@ -16078,7 +16078,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G97">
@@ -16241,22 +16241,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O98">
-        <v>4.94</v>
+        <v>0</v>
       </c>
       <c r="P98">
-        <v>6.51</v>
+        <v>0</v>
       </c>
       <c r="Q98">
         <v>0</v>
@@ -16404,22 +16404,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G99">
@@ -16562,12 +16562,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O100">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="P100">
-        <v>0</v>
+        <v>6.51</v>
       </c>
       <c r="Q100">
         <v>0</v>
@@ -16713,7 +16713,7 @@
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>2026-08-08 12:30:00</t>
+          <t>2026-08-08 12:00:00</t>
         </is>
       </c>
     </row>
@@ -16725,12 +16725,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G101">
@@ -16876,7 +16876,7 @@
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>2026-08-08 12:30:00</t>
+          <t>2026-08-08 12:00:00</t>
         </is>
       </c>
     </row>
@@ -16888,27 +16888,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G102">
@@ -17039,7 +17039,7 @@
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>2026-08-08 12:30:00</t>
+          <t>2026-08-08 12:00:00</t>
         </is>
       </c>
     </row>
@@ -17056,7 +17056,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G103">
@@ -17219,7 +17219,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G104">
@@ -17382,22 +17382,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G105">
@@ -17545,7 +17545,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O106">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P106">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -17703,12 +17703,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G107">
@@ -17854,7 +17854,7 @@
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>2026-08-08 13:00:00</t>
+          <t>2026-08-08 12:30:00</t>
         </is>
       </c>
     </row>
@@ -17866,12 +17866,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G108">
@@ -18017,7 +18017,7 @@
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>2026-08-08 13:00:00</t>
+          <t>2026-08-08 12:30:00</t>
         </is>
       </c>
     </row>
@@ -18029,27 +18029,27 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O109">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P109">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q109">
         <v>0</v>
@@ -18180,7 +18180,7 @@
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>2026-08-08 13:00:00</t>
+          <t>2026-08-08 12:30:00</t>
         </is>
       </c>
     </row>
@@ -18197,7 +18197,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G110">
@@ -18360,22 +18360,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G111">
@@ -18523,7 +18523,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G112">
@@ -18686,22 +18686,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="G113">
@@ -18849,7 +18849,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G114">
@@ -19012,7 +19012,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G115">
@@ -19170,27 +19170,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O116">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P116">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="Q116">
         <v>0</v>
@@ -19321,7 +19321,7 @@
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>2026-08-08 13:15:00</t>
+          <t>2026-08-08 13:00:00</t>
         </is>
       </c>
     </row>
@@ -19333,27 +19333,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G117">
@@ -19484,7 +19484,7 @@
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>2026-08-08 13:30:00</t>
+          <t>2026-08-08 13:00:00</t>
         </is>
       </c>
     </row>
@@ -19496,12 +19496,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="G118">
@@ -19647,7 +19647,7 @@
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>2026-08-08 13:30:00</t>
+          <t>2026-08-08 13:00:00</t>
         </is>
       </c>
     </row>
@@ -19659,12 +19659,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G119">
@@ -19810,7 +19810,7 @@
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>2026-08-08 13:45:00</t>
+          <t>2026-08-08 13:00:00</t>
         </is>
       </c>
     </row>
@@ -19822,27 +19822,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,13 +19869,13 @@
         </is>
       </c>
       <c r="N120">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O120">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P120">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q120">
         <v>0</v>
@@ -19973,7 +19973,7 @@
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>2026-08-08 14:00:00</t>
+          <t>2026-08-08 13:15:00</t>
         </is>
       </c>
     </row>
@@ -19985,27 +19985,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G121">
@@ -20136,7 +20136,7 @@
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>2026-08-08 14:00:00</t>
+          <t>2026-08-08 13:30:00</t>
         </is>
       </c>
     </row>
@@ -20148,12 +20148,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G122">
@@ -20299,7 +20299,7 @@
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>2026-08-08 14:00:00</t>
+          <t>2026-08-08 13:30:00</t>
         </is>
       </c>
     </row>
@@ -20311,27 +20311,27 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G123">
@@ -20462,7 +20462,7 @@
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>2026-08-08 14:00:00</t>
+          <t>2026-08-08 13:30:00</t>
         </is>
       </c>
     </row>
@@ -20474,12 +20474,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,13 +20521,13 @@
         </is>
       </c>
       <c r="N124">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O124">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="P124">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="Q124">
         <v>0</v>
@@ -20560,10 +20560,10 @@
         <v>0</v>
       </c>
       <c r="AA124">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB124">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC124">
         <v>0</v>
@@ -20625,7 +20625,7 @@
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>2026-08-08 14:00:00</t>
+          <t>2026-08-08 13:45:00</t>
         </is>
       </c>
     </row>
@@ -20642,22 +20642,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G125">
@@ -20805,7 +20805,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G126">
@@ -20968,7 +20968,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G127">
@@ -21131,22 +21131,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G128">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,13 +21336,13 @@
         </is>
       </c>
       <c r="N129">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O129">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P129">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="Q129">
         <v>0</v>
@@ -21375,10 +21375,10 @@
         <v>0</v>
       </c>
       <c r="AA129">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB129">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC129">
         <v>0</v>
@@ -21452,12 +21452,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G130">
@@ -21603,7 +21603,7 @@
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>2026-08-08 14:30:00</t>
+          <t>2026-08-08 14:00:00</t>
         </is>
       </c>
     </row>
@@ -21615,12 +21615,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,13 +21662,13 @@
         </is>
       </c>
       <c r="N131">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="O131">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P131">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -21766,7 +21766,7 @@
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>2026-08-08 14:30:00</t>
+          <t>2026-08-08 14:00:00</t>
         </is>
       </c>
     </row>
@@ -21778,12 +21778,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G132">
@@ -21929,7 +21929,7 @@
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>2026-08-08 15:00:00</t>
+          <t>2026-08-08 14:00:00</t>
         </is>
       </c>
     </row>
@@ -21941,12 +21941,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G133">
@@ -22092,7 +22092,7 @@
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>2026-08-08 15:00:00</t>
+          <t>2026-08-08 14:00:00</t>
         </is>
       </c>
     </row>
@@ -22104,12 +22104,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G134">
@@ -22255,7 +22255,7 @@
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>2026-08-08 15:00:00</t>
+          <t>2026-08-08 14:30:00</t>
         </is>
       </c>
     </row>
@@ -22267,12 +22267,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,13 +22314,13 @@
         </is>
       </c>
       <c r="N135">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="O135">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P135">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q135">
         <v>0</v>
@@ -22418,7 +22418,7 @@
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>2026-08-08 15:00:00</t>
+          <t>2026-08-08 14:30:00</t>
         </is>
       </c>
     </row>
@@ -22430,12 +22430,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Podbeskidzie</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G136">
@@ -22581,7 +22581,7 @@
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>2026-08-08 15:15:00</t>
+          <t>2026-08-08 14:30:00</t>
         </is>
       </c>
     </row>
@@ -22593,12 +22593,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G137">
@@ -22744,7 +22744,7 @@
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>2026-08-08 15:15:00</t>
+          <t>2026-08-08 15:00:00</t>
         </is>
       </c>
     </row>
@@ -22756,12 +22756,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G138">
@@ -22907,7 +22907,7 @@
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>2026-08-08 15:15:00</t>
+          <t>2026-08-08 15:00:00</t>
         </is>
       </c>
     </row>
@@ -22919,12 +22919,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Dunav 2010</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G139">
@@ -23070,7 +23070,7 @@
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>2026-08-08 15:15:00</t>
+          <t>2026-08-08 15:00:00</t>
         </is>
       </c>
     </row>
@@ -23082,12 +23082,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G140">
@@ -23233,7 +23233,7 @@
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>2026-08-08 15:30:00</t>
+          <t>2026-08-08 15:00:00</t>
         </is>
       </c>
     </row>
@@ -23245,12 +23245,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Podbeskidzie</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G141">
@@ -23396,7 +23396,7 @@
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>2026-08-08 15:30:00</t>
+          <t>2026-08-08 15:15:00</t>
         </is>
       </c>
     </row>
@@ -23408,12 +23408,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G142">
@@ -23559,7 +23559,7 @@
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>2026-08-08 15:30:00</t>
+          <t>2026-08-08 15:15:00</t>
         </is>
       </c>
     </row>
@@ -23571,12 +23571,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Voluntari</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,13 +23618,13 @@
         </is>
       </c>
       <c r="N143">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="O143">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P143">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -23722,7 +23722,7 @@
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>2026-08-08 15:30:00</t>
+          <t>2026-08-08 15:15:00</t>
         </is>
       </c>
     </row>
@@ -23734,12 +23734,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Dunav 2010</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G144">
@@ -23885,7 +23885,7 @@
       </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>2026-08-08 15:45:00</t>
+          <t>2026-08-08 15:15:00</t>
         </is>
       </c>
     </row>
@@ -23897,12 +23897,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G145">
@@ -24048,7 +24048,7 @@
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>2026-08-08 15:45:00</t>
+          <t>2026-08-08 15:30:00</t>
         </is>
       </c>
     </row>
@@ -24060,12 +24060,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G146">
@@ -24211,7 +24211,7 @@
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>2026-08-08 15:45:00</t>
+          <t>2026-08-08 15:30:00</t>
         </is>
       </c>
     </row>
@@ -24223,12 +24223,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G147">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>2026-08-08 15:45:00</t>
+          <t>2026-08-08 15:30:00</t>
         </is>
       </c>
     </row>
@@ -24386,12 +24386,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Voluntari</t>
         </is>
       </c>
       <c r="G148">
@@ -24433,13 +24433,13 @@
         </is>
       </c>
       <c r="N148">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O148">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P148">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q148">
         <v>0</v>
@@ -24537,7 +24537,7 @@
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>2026-08-08 15:45:00</t>
+          <t>2026-08-08 15:30:00</t>
         </is>
       </c>
     </row>
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G149">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G150">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G151">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G152">
@@ -25206,7 +25206,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,13 +25248,13 @@
         </is>
       </c>
       <c r="N153">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="O153">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="P153">
-        <v>4.66</v>
+        <v>0</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -25287,10 +25287,10 @@
         <v>0</v>
       </c>
       <c r="AA153">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB153">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC153">
         <v>0</v>
@@ -25369,7 +25369,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="N154">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="O154">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="P154">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q154">
         <v>0</v>
@@ -25450,10 +25450,10 @@
         <v>0</v>
       </c>
       <c r="AA154">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB154">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC154">
         <v>0</v>
@@ -25527,27 +25527,27 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G155">
@@ -25678,7 +25678,7 @@
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>2026-08-08 16:00:00</t>
+          <t>2026-08-08 15:45:00</t>
         </is>
       </c>
     </row>
@@ -25690,12 +25690,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G156">
@@ -25841,7 +25841,7 @@
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>2026-08-08 16:00:00</t>
+          <t>2026-08-08 15:45:00</t>
         </is>
       </c>
     </row>
@@ -25853,12 +25853,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G157">
@@ -26004,7 +26004,7 @@
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>2026-08-08 16:00:00</t>
+          <t>2026-08-08 15:45:00</t>
         </is>
       </c>
     </row>
@@ -26016,27 +26016,27 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,13 +26063,13 @@
         </is>
       </c>
       <c r="N158">
-        <v>2.45</v>
+        <v>1.76</v>
       </c>
       <c r="O158">
-        <v>3.27</v>
+        <v>3.79</v>
       </c>
       <c r="P158">
-        <v>3.06</v>
+        <v>4.66</v>
       </c>
       <c r="Q158">
         <v>0</v>
@@ -26102,10 +26102,10 @@
         <v>0</v>
       </c>
       <c r="AA158">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AB158">
-        <v>1.66</v>
+        <v>1.88</v>
       </c>
       <c r="AC158">
         <v>0</v>
@@ -26167,7 +26167,7 @@
       </c>
       <c r="AU158" t="inlineStr">
         <is>
-          <t>2026-08-08 16:00:00</t>
+          <t>2026-08-08 15:45:00</t>
         </is>
       </c>
     </row>
@@ -26179,27 +26179,27 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,13 +26226,13 @@
         </is>
       </c>
       <c r="N159">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="O159">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="P159">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q159">
         <v>0</v>
@@ -26265,10 +26265,10 @@
         <v>0</v>
       </c>
       <c r="AA159">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB159">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC159">
         <v>0</v>
@@ -26330,7 +26330,7 @@
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>2026-08-08 16:00:00</t>
+          <t>2026-08-08 15:45:00</t>
         </is>
       </c>
     </row>
@@ -26347,7 +26347,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G160">
@@ -26510,7 +26510,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G161">
@@ -26673,7 +26673,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G162">
@@ -26836,7 +26836,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G163">
@@ -26878,13 +26878,13 @@
         </is>
       </c>
       <c r="N163">
-        <v>2.24</v>
+        <v>2.45</v>
       </c>
       <c r="O163">
-        <v>3.18</v>
+        <v>3.27</v>
       </c>
       <c r="P163">
-        <v>3.2</v>
+        <v>3.06</v>
       </c>
       <c r="Q163">
         <v>0</v>
@@ -26917,10 +26917,10 @@
         <v>0</v>
       </c>
       <c r="AA163">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AB163">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AC163">
         <v>0</v>
@@ -26994,27 +26994,27 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G164">
@@ -27041,13 +27041,13 @@
         </is>
       </c>
       <c r="N164">
-        <v>12.1</v>
+        <v>0</v>
       </c>
       <c r="O164">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="P164">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Q164">
         <v>0</v>
@@ -27086,10 +27086,10 @@
         <v>0</v>
       </c>
       <c r="AC164">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD164">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE164">
         <v>0</v>
@@ -27145,7 +27145,7 @@
       </c>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>2026-08-08 16:30:00</t>
+          <t>2026-08-08 16:00:00</t>
         </is>
       </c>
     </row>
@@ -27157,12 +27157,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G165">
@@ -27308,7 +27308,7 @@
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>2026-08-08 17:00:00</t>
+          <t>2026-08-08 16:00:00</t>
         </is>
       </c>
     </row>
@@ -27320,27 +27320,27 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G166">
@@ -27471,7 +27471,7 @@
       </c>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>2026-08-08 17:00:00</t>
+          <t>2026-08-08 16:00:00</t>
         </is>
       </c>
     </row>
@@ -27483,27 +27483,27 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G167">
@@ -27634,7 +27634,7 @@
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>2026-08-08 17:00:00</t>
+          <t>2026-08-08 16:00:00</t>
         </is>
       </c>
     </row>
@@ -27646,27 +27646,27 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G168">
@@ -27689,68 +27689,68 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N168">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O168">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="P168">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q168">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R168">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S168">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T168">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="U168">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="V168">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W168">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X168">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y168">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z168">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="AA168">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB168">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC168">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="AD168">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE168">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF168">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG168">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AH168" t="inlineStr">
         <is>
@@ -27763,10 +27763,10 @@
         </is>
       </c>
       <c r="AJ168">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK168">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL168">
         <v>0</v>
@@ -27797,7 +27797,7 @@
       </c>
       <c r="AU168" t="inlineStr">
         <is>
-          <t>2026-08-08 17:30:00</t>
+          <t>2026-08-08 16:00:00</t>
         </is>
       </c>
     </row>
@@ -27809,12 +27809,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G169">
@@ -27856,13 +27856,13 @@
         </is>
       </c>
       <c r="N169">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O169">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P169">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q169">
         <v>0</v>
@@ -27895,10 +27895,10 @@
         <v>0</v>
       </c>
       <c r="AA169">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB169">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC169">
         <v>0</v>
@@ -27960,7 +27960,7 @@
       </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>2026-08-08 18:00:00</t>
+          <t>2026-08-08 16:00:00</t>
         </is>
       </c>
     </row>
@@ -27972,27 +27972,27 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G170">
@@ -28019,13 +28019,13 @@
         </is>
       </c>
       <c r="N170">
-        <v>0</v>
+        <v>12.1</v>
       </c>
       <c r="O170">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="P170">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Q170">
         <v>0</v>
@@ -28064,10 +28064,10 @@
         <v>0</v>
       </c>
       <c r="AC170">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD170">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE170">
         <v>0</v>
@@ -28123,7 +28123,7 @@
       </c>
       <c r="AU170" t="inlineStr">
         <is>
-          <t>2026-08-08 18:15:00</t>
+          <t>2026-08-08 16:30:00</t>
         </is>
       </c>
     </row>
@@ -28135,12 +28135,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G171">
@@ -28286,7 +28286,7 @@
       </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>2026-08-08 18:30:00</t>
+          <t>2026-08-08 17:00:00</t>
         </is>
       </c>
     </row>
@@ -28298,12 +28298,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G172">
@@ -28345,13 +28345,13 @@
         </is>
       </c>
       <c r="N172">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="O172">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P172">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q172">
         <v>0</v>
@@ -28384,10 +28384,10 @@
         <v>0</v>
       </c>
       <c r="AA172">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB172">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC172">
         <v>0</v>
@@ -28449,7 +28449,7 @@
       </c>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>2026-08-08 18:30:00</t>
+          <t>2026-08-08 17:00:00</t>
         </is>
       </c>
     </row>
@@ -28461,12 +28461,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G173">
@@ -28612,7 +28612,7 @@
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>2026-08-08 18:30:00</t>
+          <t>2026-08-08 17:00:00</t>
         </is>
       </c>
     </row>
@@ -28624,12 +28624,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G174">
@@ -28667,68 +28667,68 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N174">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O174">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P174">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q174">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R174">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S174">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T174">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="U174">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V174">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W174">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X174">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y174">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z174">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="AA174">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB174">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC174">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AD174">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE174">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF174">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG174">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AH174" t="inlineStr">
         <is>
@@ -28741,10 +28741,10 @@
         </is>
       </c>
       <c r="AJ174">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK174">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL174">
         <v>0</v>
@@ -28775,7 +28775,7 @@
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>2026-08-08 18:30:00</t>
+          <t>2026-08-08 17:30:00</t>
         </is>
       </c>
     </row>
@@ -28787,12 +28787,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,13 +28834,13 @@
         </is>
       </c>
       <c r="N175">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O175">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P175">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="Q175">
         <v>0</v>
@@ -28873,10 +28873,10 @@
         <v>0</v>
       </c>
       <c r="AA175">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB175">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC175">
         <v>0</v>
@@ -28938,7 +28938,7 @@
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>2026-08-08 18:30:00</t>
+          <t>2026-08-08 18:00:00</t>
         </is>
       </c>
     </row>
@@ -28950,12 +28950,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G176">
@@ -29101,7 +29101,7 @@
       </c>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>2026-08-08 19:30:00</t>
+          <t>2026-08-08 18:15:00</t>
         </is>
       </c>
     </row>
@@ -29113,12 +29113,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G177">
@@ -29264,7 +29264,7 @@
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>2026-08-08 19:30:00</t>
+          <t>2026-08-08 18:30:00</t>
         </is>
       </c>
     </row>
@@ -29276,12 +29276,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,13 +29323,13 @@
         </is>
       </c>
       <c r="N178">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O178">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P178">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q178">
         <v>0</v>
@@ -29362,10 +29362,10 @@
         <v>0</v>
       </c>
       <c r="AA178">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB178">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC178">
         <v>0</v>
@@ -29427,7 +29427,7 @@
       </c>
       <c r="AU178" t="inlineStr">
         <is>
-          <t>2026-08-08 19:30:00</t>
+          <t>2026-08-08 18:30:00</t>
         </is>
       </c>
     </row>
@@ -29439,12 +29439,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G179">
@@ -29590,7 +29590,7 @@
       </c>
       <c r="AU179" t="inlineStr">
         <is>
-          <t>2026-08-08 20:00:00</t>
+          <t>2026-08-08 18:30:00</t>
         </is>
       </c>
     </row>
@@ -29602,12 +29602,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G180">
@@ -29753,7 +29753,7 @@
       </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>2026-08-08 20:00:00</t>
+          <t>2026-08-08 18:30:00</t>
         </is>
       </c>
     </row>
@@ -29765,12 +29765,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G181">
@@ -29812,13 +29812,13 @@
         </is>
       </c>
       <c r="N181">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O181">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P181">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="Q181">
         <v>0</v>
@@ -29851,10 +29851,10 @@
         <v>0</v>
       </c>
       <c r="AA181">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB181">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC181">
         <v>0</v>
@@ -29916,7 +29916,7 @@
       </c>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>2026-08-08 20:00:00</t>
+          <t>2026-08-08 18:30:00</t>
         </is>
       </c>
     </row>
@@ -29928,12 +29928,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G182">
@@ -30079,7 +30079,7 @@
       </c>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>2026-08-08 20:00:00</t>
+          <t>2026-08-08 19:30:00</t>
         </is>
       </c>
     </row>
@@ -30091,12 +30091,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G183">
@@ -30242,7 +30242,7 @@
       </c>
       <c r="AU183" t="inlineStr">
         <is>
-          <t>2026-08-08 20:00:00</t>
+          <t>2026-08-08 19:30:00</t>
         </is>
       </c>
     </row>
@@ -30254,12 +30254,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G184">
@@ -30301,13 +30301,13 @@
         </is>
       </c>
       <c r="N184">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="O184">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="P184">
-        <v>6.23</v>
+        <v>0</v>
       </c>
       <c r="Q184">
         <v>0</v>
@@ -30340,10 +30340,10 @@
         <v>0</v>
       </c>
       <c r="AA184">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB184">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC184">
         <v>0</v>
@@ -30405,7 +30405,7 @@
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>2026-08-08 20:30:00</t>
+          <t>2026-08-08 19:30:00</t>
         </is>
       </c>
     </row>
@@ -30417,7 +30417,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G185">
@@ -30568,7 +30568,7 @@
       </c>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>2026-08-08 20:30:00</t>
+          <t>2026-08-08 20:00:00</t>
         </is>
       </c>
     </row>
@@ -30580,12 +30580,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G186">
@@ -30731,7 +30731,7 @@
       </c>
       <c r="AU186" t="inlineStr">
         <is>
-          <t>2026-08-08 20:30:00</t>
+          <t>2026-08-08 20:00:00</t>
         </is>
       </c>
     </row>
@@ -30743,12 +30743,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G187">
@@ -30894,7 +30894,7 @@
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>2026-08-08 21:00:00</t>
+          <t>2026-08-08 20:00:00</t>
         </is>
       </c>
     </row>
@@ -30906,12 +30906,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,13 +30953,13 @@
         </is>
       </c>
       <c r="N188">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O188">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P188">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q188">
         <v>0</v>
@@ -30992,10 +30992,10 @@
         <v>0</v>
       </c>
       <c r="AA188">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB188">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC188">
         <v>0</v>
@@ -31057,7 +31057,7 @@
       </c>
       <c r="AU188" t="inlineStr">
         <is>
-          <t>2026-08-08 21:00:00</t>
+          <t>2026-08-08 20:00:00</t>
         </is>
       </c>
     </row>
@@ -31069,7 +31069,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G189">
@@ -31220,7 +31220,7 @@
       </c>
       <c r="AU189" t="inlineStr">
         <is>
-          <t>2026-08-08 21:00:00</t>
+          <t>2026-08-08 20:00:00</t>
         </is>
       </c>
     </row>
@@ -31232,27 +31232,27 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G190">
@@ -31279,13 +31279,13 @@
         </is>
       </c>
       <c r="N190">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O190">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="P190">
-        <v>0</v>
+        <v>6.23</v>
       </c>
       <c r="Q190">
         <v>0</v>
@@ -31318,10 +31318,10 @@
         <v>0</v>
       </c>
       <c r="AA190">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB190">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC190">
         <v>0</v>
@@ -31383,7 +31383,7 @@
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>2026-08-08 21:00:00</t>
+          <t>2026-08-08 20:30:00</t>
         </is>
       </c>
     </row>
@@ -31395,27 +31395,27 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G191">
@@ -31546,7 +31546,7 @@
       </c>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>2026-08-08 21:00:00</t>
+          <t>2026-08-08 20:30:00</t>
         </is>
       </c>
     </row>
@@ -31558,12 +31558,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="G192">
@@ -31709,7 +31709,7 @@
       </c>
       <c r="AU192" t="inlineStr">
         <is>
-          <t>2026-08-08 21:00:00</t>
+          <t>2026-08-08 20:30:00</t>
         </is>
       </c>
     </row>
@@ -31726,7 +31726,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G193">
@@ -31889,22 +31889,22 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G194">
@@ -31931,13 +31931,13 @@
         </is>
       </c>
       <c r="N194">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O194">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P194">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q194">
         <v>0</v>
@@ -31970,10 +31970,10 @@
         <v>0</v>
       </c>
       <c r="AA194">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB194">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC194">
         <v>0</v>
@@ -32052,22 +32052,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G195">
@@ -32210,27 +32210,27 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G196">
@@ -32361,7 +32361,7 @@
       </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>2026-08-08 21:30:00</t>
+          <t>2026-08-08 21:00:00</t>
         </is>
       </c>
     </row>
@@ -32373,27 +32373,27 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G197">
@@ -32524,7 +32524,7 @@
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>2026-08-08 21:45:00</t>
+          <t>2026-08-08 21:00:00</t>
         </is>
       </c>
     </row>
@@ -32536,12 +32536,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G198">
@@ -32687,7 +32687,7 @@
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>2026-08-08 22:00:00</t>
+          <t>2026-08-08 21:00:00</t>
         </is>
       </c>
     </row>
@@ -32699,12 +32699,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G199">
@@ -32850,7 +32850,7 @@
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>2026-08-08 23:00:00</t>
+          <t>2026-08-08 21:00:00</t>
         </is>
       </c>
     </row>
@@ -32862,156 +32862,1134 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Portugal Liga NOS</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Moreirense FC</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Sporting Braga</t>
+        </is>
+      </c>
+      <c r="G200">
+        <v>0</v>
+      </c>
+      <c r="H200">
+        <v>0</v>
+      </c>
+      <c r="I200">
+        <v>0</v>
+      </c>
+      <c r="J200">
+        <v>0</v>
+      </c>
+      <c r="K200">
+        <v>0</v>
+      </c>
+      <c r="L200">
+        <v>0</v>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N200">
+        <v>0</v>
+      </c>
+      <c r="O200">
+        <v>0</v>
+      </c>
+      <c r="P200">
+        <v>0</v>
+      </c>
+      <c r="Q200">
+        <v>0</v>
+      </c>
+      <c r="R200">
+        <v>0</v>
+      </c>
+      <c r="S200">
+        <v>0</v>
+      </c>
+      <c r="T200">
+        <v>0</v>
+      </c>
+      <c r="U200">
+        <v>0</v>
+      </c>
+      <c r="V200">
+        <v>0</v>
+      </c>
+      <c r="W200">
+        <v>0</v>
+      </c>
+      <c r="X200">
+        <v>0</v>
+      </c>
+      <c r="Y200">
+        <v>0</v>
+      </c>
+      <c r="Z200">
+        <v>0</v>
+      </c>
+      <c r="AA200">
+        <v>0</v>
+      </c>
+      <c r="AB200">
+        <v>0</v>
+      </c>
+      <c r="AC200">
+        <v>0</v>
+      </c>
+      <c r="AD200">
+        <v>0</v>
+      </c>
+      <c r="AE200">
+        <v>0</v>
+      </c>
+      <c r="AF200">
+        <v>0</v>
+      </c>
+      <c r="AG200">
+        <v>0</v>
+      </c>
+      <c r="AH200" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI200" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ200">
+        <v>0</v>
+      </c>
+      <c r="AK200">
+        <v>0</v>
+      </c>
+      <c r="AL200">
+        <v>0</v>
+      </c>
+      <c r="AM200">
+        <v>-1</v>
+      </c>
+      <c r="AN200">
+        <v>-1</v>
+      </c>
+      <c r="AO200">
+        <v>-1</v>
+      </c>
+      <c r="AP200">
+        <v>-1</v>
+      </c>
+      <c r="AQ200">
+        <v>0</v>
+      </c>
+      <c r="AR200">
+        <v>0</v>
+      </c>
+      <c r="AS200">
+        <v>0</v>
+      </c>
+      <c r="AT200">
+        <v>0</v>
+      </c>
+      <c r="AU200" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Portugal Liga NOS</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Benfica</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Academico Viseu</t>
+        </is>
+      </c>
+      <c r="G201">
+        <v>0</v>
+      </c>
+      <c r="H201">
+        <v>0</v>
+      </c>
+      <c r="I201">
+        <v>0</v>
+      </c>
+      <c r="J201">
+        <v>0</v>
+      </c>
+      <c r="K201">
+        <v>0</v>
+      </c>
+      <c r="L201">
+        <v>0</v>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N201">
+        <v>0</v>
+      </c>
+      <c r="O201">
+        <v>0</v>
+      </c>
+      <c r="P201">
+        <v>0</v>
+      </c>
+      <c r="Q201">
+        <v>0</v>
+      </c>
+      <c r="R201">
+        <v>0</v>
+      </c>
+      <c r="S201">
+        <v>0</v>
+      </c>
+      <c r="T201">
+        <v>0</v>
+      </c>
+      <c r="U201">
+        <v>0</v>
+      </c>
+      <c r="V201">
+        <v>0</v>
+      </c>
+      <c r="W201">
+        <v>0</v>
+      </c>
+      <c r="X201">
+        <v>0</v>
+      </c>
+      <c r="Y201">
+        <v>0</v>
+      </c>
+      <c r="Z201">
+        <v>0</v>
+      </c>
+      <c r="AA201">
+        <v>0</v>
+      </c>
+      <c r="AB201">
+        <v>0</v>
+      </c>
+      <c r="AC201">
+        <v>0</v>
+      </c>
+      <c r="AD201">
+        <v>0</v>
+      </c>
+      <c r="AE201">
+        <v>0</v>
+      </c>
+      <c r="AF201">
+        <v>0</v>
+      </c>
+      <c r="AG201">
+        <v>0</v>
+      </c>
+      <c r="AH201" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI201" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ201">
+        <v>0</v>
+      </c>
+      <c r="AK201">
+        <v>0</v>
+      </c>
+      <c r="AL201">
+        <v>0</v>
+      </c>
+      <c r="AM201">
+        <v>-1</v>
+      </c>
+      <c r="AN201">
+        <v>-1</v>
+      </c>
+      <c r="AO201">
+        <v>-1</v>
+      </c>
+      <c r="AP201">
+        <v>-1</v>
+      </c>
+      <c r="AQ201">
+        <v>0</v>
+      </c>
+      <c r="AR201">
+        <v>0</v>
+      </c>
+      <c r="AS201">
+        <v>0</v>
+      </c>
+      <c r="AT201">
+        <v>0</v>
+      </c>
+      <c r="AU201" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Tulsa Roughnecks</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Detroit City FC</t>
+        </is>
+      </c>
+      <c r="G202">
+        <v>0</v>
+      </c>
+      <c r="H202">
+        <v>0</v>
+      </c>
+      <c r="I202">
+        <v>0</v>
+      </c>
+      <c r="J202">
+        <v>0</v>
+      </c>
+      <c r="K202">
+        <v>0</v>
+      </c>
+      <c r="L202">
+        <v>0</v>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N202">
+        <v>0</v>
+      </c>
+      <c r="O202">
+        <v>0</v>
+      </c>
+      <c r="P202">
+        <v>0</v>
+      </c>
+      <c r="Q202">
+        <v>0</v>
+      </c>
+      <c r="R202">
+        <v>0</v>
+      </c>
+      <c r="S202">
+        <v>0</v>
+      </c>
+      <c r="T202">
+        <v>0</v>
+      </c>
+      <c r="U202">
+        <v>0</v>
+      </c>
+      <c r="V202">
+        <v>0</v>
+      </c>
+      <c r="W202">
+        <v>0</v>
+      </c>
+      <c r="X202">
+        <v>0</v>
+      </c>
+      <c r="Y202">
+        <v>0</v>
+      </c>
+      <c r="Z202">
+        <v>0</v>
+      </c>
+      <c r="AA202">
+        <v>0</v>
+      </c>
+      <c r="AB202">
+        <v>0</v>
+      </c>
+      <c r="AC202">
+        <v>0</v>
+      </c>
+      <c r="AD202">
+        <v>0</v>
+      </c>
+      <c r="AE202">
+        <v>0</v>
+      </c>
+      <c r="AF202">
+        <v>0</v>
+      </c>
+      <c r="AG202">
+        <v>0</v>
+      </c>
+      <c r="AH202" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI202" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ202">
+        <v>0</v>
+      </c>
+      <c r="AK202">
+        <v>0</v>
+      </c>
+      <c r="AL202">
+        <v>0</v>
+      </c>
+      <c r="AM202">
+        <v>-1</v>
+      </c>
+      <c r="AN202">
+        <v>-1</v>
+      </c>
+      <c r="AO202">
+        <v>-1</v>
+      </c>
+      <c r="AP202">
+        <v>-1</v>
+      </c>
+      <c r="AQ202">
+        <v>0</v>
+      </c>
+      <c r="AR202">
+        <v>0</v>
+      </c>
+      <c r="AS202">
+        <v>0</v>
+      </c>
+      <c r="AT202">
+        <v>0</v>
+      </c>
+      <c r="AU202" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Houston Dash</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Kansas City</t>
+        </is>
+      </c>
+      <c r="G203">
+        <v>0</v>
+      </c>
+      <c r="H203">
+        <v>0</v>
+      </c>
+      <c r="I203">
+        <v>0</v>
+      </c>
+      <c r="J203">
+        <v>0</v>
+      </c>
+      <c r="K203">
+        <v>0</v>
+      </c>
+      <c r="L203">
+        <v>0</v>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N203">
+        <v>0</v>
+      </c>
+      <c r="O203">
+        <v>0</v>
+      </c>
+      <c r="P203">
+        <v>0</v>
+      </c>
+      <c r="Q203">
+        <v>0</v>
+      </c>
+      <c r="R203">
+        <v>0</v>
+      </c>
+      <c r="S203">
+        <v>0</v>
+      </c>
+      <c r="T203">
+        <v>0</v>
+      </c>
+      <c r="U203">
+        <v>0</v>
+      </c>
+      <c r="V203">
+        <v>0</v>
+      </c>
+      <c r="W203">
+        <v>0</v>
+      </c>
+      <c r="X203">
+        <v>0</v>
+      </c>
+      <c r="Y203">
+        <v>0</v>
+      </c>
+      <c r="Z203">
+        <v>0</v>
+      </c>
+      <c r="AA203">
+        <v>0</v>
+      </c>
+      <c r="AB203">
+        <v>0</v>
+      </c>
+      <c r="AC203">
+        <v>0</v>
+      </c>
+      <c r="AD203">
+        <v>0</v>
+      </c>
+      <c r="AE203">
+        <v>0</v>
+      </c>
+      <c r="AF203">
+        <v>0</v>
+      </c>
+      <c r="AG203">
+        <v>0</v>
+      </c>
+      <c r="AH203" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI203" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ203">
+        <v>0</v>
+      </c>
+      <c r="AK203">
+        <v>0</v>
+      </c>
+      <c r="AL203">
+        <v>0</v>
+      </c>
+      <c r="AM203">
+        <v>-1</v>
+      </c>
+      <c r="AN203">
+        <v>-1</v>
+      </c>
+      <c r="AO203">
+        <v>-1</v>
+      </c>
+      <c r="AP203">
+        <v>-1</v>
+      </c>
+      <c r="AQ203">
+        <v>0</v>
+      </c>
+      <c r="AR203">
+        <v>0</v>
+      </c>
+      <c r="AS203">
+        <v>0</v>
+      </c>
+      <c r="AT203">
+        <v>0</v>
+      </c>
+      <c r="AU203" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>El Paso Locomotive</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Oakland Roots</t>
+        </is>
+      </c>
+      <c r="G204">
+        <v>0</v>
+      </c>
+      <c r="H204">
+        <v>0</v>
+      </c>
+      <c r="I204">
+        <v>0</v>
+      </c>
+      <c r="J204">
+        <v>0</v>
+      </c>
+      <c r="K204">
+        <v>0</v>
+      </c>
+      <c r="L204">
+        <v>0</v>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N204">
+        <v>0</v>
+      </c>
+      <c r="O204">
+        <v>0</v>
+      </c>
+      <c r="P204">
+        <v>0</v>
+      </c>
+      <c r="Q204">
+        <v>0</v>
+      </c>
+      <c r="R204">
+        <v>0</v>
+      </c>
+      <c r="S204">
+        <v>0</v>
+      </c>
+      <c r="T204">
+        <v>0</v>
+      </c>
+      <c r="U204">
+        <v>0</v>
+      </c>
+      <c r="V204">
+        <v>0</v>
+      </c>
+      <c r="W204">
+        <v>0</v>
+      </c>
+      <c r="X204">
+        <v>0</v>
+      </c>
+      <c r="Y204">
+        <v>0</v>
+      </c>
+      <c r="Z204">
+        <v>0</v>
+      </c>
+      <c r="AA204">
+        <v>0</v>
+      </c>
+      <c r="AB204">
+        <v>0</v>
+      </c>
+      <c r="AC204">
+        <v>0</v>
+      </c>
+      <c r="AD204">
+        <v>0</v>
+      </c>
+      <c r="AE204">
+        <v>0</v>
+      </c>
+      <c r="AF204">
+        <v>0</v>
+      </c>
+      <c r="AG204">
+        <v>0</v>
+      </c>
+      <c r="AH204" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI204" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ204">
+        <v>0</v>
+      </c>
+      <c r="AK204">
+        <v>0</v>
+      </c>
+      <c r="AL204">
+        <v>0</v>
+      </c>
+      <c r="AM204">
+        <v>-1</v>
+      </c>
+      <c r="AN204">
+        <v>-1</v>
+      </c>
+      <c r="AO204">
+        <v>-1</v>
+      </c>
+      <c r="AP204">
+        <v>-1</v>
+      </c>
+      <c r="AQ204">
+        <v>0</v>
+      </c>
+      <c r="AR204">
+        <v>0</v>
+      </c>
+      <c r="AS204">
+        <v>0</v>
+      </c>
+      <c r="AT204">
+        <v>0</v>
+      </c>
+      <c r="AU204" t="inlineStr">
+        <is>
+          <t>2026-08-08 22:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C200" t="inlineStr">
+      <c r="C205" t="inlineStr">
         <is>
           <t>USA USL Championship</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr">
+      <c r="D205" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E200" t="inlineStr">
+      <c r="E205" t="inlineStr">
         <is>
           <t>Monterey Bay</t>
         </is>
       </c>
-      <c r="F200" t="inlineStr">
+      <c r="F205" t="inlineStr">
         <is>
           <t>New Mexico United</t>
         </is>
       </c>
-      <c r="G200">
-        <v>0</v>
-      </c>
-      <c r="H200">
-        <v>0</v>
-      </c>
-      <c r="I200">
-        <v>0</v>
-      </c>
-      <c r="J200">
-        <v>0</v>
-      </c>
-      <c r="K200">
-        <v>0</v>
-      </c>
-      <c r="L200">
-        <v>0</v>
-      </c>
-      <c r="M200" t="inlineStr">
+      <c r="G205">
+        <v>0</v>
+      </c>
+      <c r="H205">
+        <v>0</v>
+      </c>
+      <c r="I205">
+        <v>0</v>
+      </c>
+      <c r="J205">
+        <v>0</v>
+      </c>
+      <c r="K205">
+        <v>0</v>
+      </c>
+      <c r="L205">
+        <v>0</v>
+      </c>
+      <c r="M205" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N200">
-        <v>0</v>
-      </c>
-      <c r="O200">
-        <v>0</v>
-      </c>
-      <c r="P200">
-        <v>0</v>
-      </c>
-      <c r="Q200">
-        <v>0</v>
-      </c>
-      <c r="R200">
-        <v>0</v>
-      </c>
-      <c r="S200">
-        <v>0</v>
-      </c>
-      <c r="T200">
-        <v>0</v>
-      </c>
-      <c r="U200">
-        <v>0</v>
-      </c>
-      <c r="V200">
-        <v>0</v>
-      </c>
-      <c r="W200">
-        <v>0</v>
-      </c>
-      <c r="X200">
-        <v>0</v>
-      </c>
-      <c r="Y200">
-        <v>0</v>
-      </c>
-      <c r="Z200">
-        <v>0</v>
-      </c>
-      <c r="AA200">
-        <v>0</v>
-      </c>
-      <c r="AB200">
-        <v>0</v>
-      </c>
-      <c r="AC200">
-        <v>0</v>
-      </c>
-      <c r="AD200">
-        <v>0</v>
-      </c>
-      <c r="AE200">
-        <v>0</v>
-      </c>
-      <c r="AF200">
-        <v>0</v>
-      </c>
-      <c r="AG200">
-        <v>0</v>
-      </c>
-      <c r="AH200" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI200" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ200">
-        <v>0</v>
-      </c>
-      <c r="AK200">
-        <v>0</v>
-      </c>
-      <c r="AL200">
-        <v>0</v>
-      </c>
-      <c r="AM200">
-        <v>-1</v>
-      </c>
-      <c r="AN200">
-        <v>-1</v>
-      </c>
-      <c r="AO200">
-        <v>-1</v>
-      </c>
-      <c r="AP200">
-        <v>-1</v>
-      </c>
-      <c r="AQ200">
-        <v>0</v>
-      </c>
-      <c r="AR200">
-        <v>0</v>
-      </c>
-      <c r="AS200">
-        <v>0</v>
-      </c>
-      <c r="AT200">
-        <v>0</v>
-      </c>
-      <c r="AU200" t="inlineStr">
+      <c r="N205">
+        <v>0</v>
+      </c>
+      <c r="O205">
+        <v>0</v>
+      </c>
+      <c r="P205">
+        <v>0</v>
+      </c>
+      <c r="Q205">
+        <v>0</v>
+      </c>
+      <c r="R205">
+        <v>0</v>
+      </c>
+      <c r="S205">
+        <v>0</v>
+      </c>
+      <c r="T205">
+        <v>0</v>
+      </c>
+      <c r="U205">
+        <v>0</v>
+      </c>
+      <c r="V205">
+        <v>0</v>
+      </c>
+      <c r="W205">
+        <v>0</v>
+      </c>
+      <c r="X205">
+        <v>0</v>
+      </c>
+      <c r="Y205">
+        <v>0</v>
+      </c>
+      <c r="Z205">
+        <v>0</v>
+      </c>
+      <c r="AA205">
+        <v>0</v>
+      </c>
+      <c r="AB205">
+        <v>0</v>
+      </c>
+      <c r="AC205">
+        <v>0</v>
+      </c>
+      <c r="AD205">
+        <v>0</v>
+      </c>
+      <c r="AE205">
+        <v>0</v>
+      </c>
+      <c r="AF205">
+        <v>0</v>
+      </c>
+      <c r="AG205">
+        <v>0</v>
+      </c>
+      <c r="AH205" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI205" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ205">
+        <v>0</v>
+      </c>
+      <c r="AK205">
+        <v>0</v>
+      </c>
+      <c r="AL205">
+        <v>0</v>
+      </c>
+      <c r="AM205">
+        <v>-1</v>
+      </c>
+      <c r="AN205">
+        <v>-1</v>
+      </c>
+      <c r="AO205">
+        <v>-1</v>
+      </c>
+      <c r="AP205">
+        <v>-1</v>
+      </c>
+      <c r="AQ205">
+        <v>0</v>
+      </c>
+      <c r="AR205">
+        <v>0</v>
+      </c>
+      <c r="AS205">
+        <v>0</v>
+      </c>
+      <c r="AT205">
+        <v>0</v>
+      </c>
+      <c r="AU205" t="inlineStr">
+        <is>
+          <t>2026-08-08 23:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Orange County SC</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rowdies</t>
+        </is>
+      </c>
+      <c r="G206">
+        <v>0</v>
+      </c>
+      <c r="H206">
+        <v>0</v>
+      </c>
+      <c r="I206">
+        <v>0</v>
+      </c>
+      <c r="J206">
+        <v>0</v>
+      </c>
+      <c r="K206">
+        <v>0</v>
+      </c>
+      <c r="L206">
+        <v>0</v>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N206">
+        <v>0</v>
+      </c>
+      <c r="O206">
+        <v>0</v>
+      </c>
+      <c r="P206">
+        <v>0</v>
+      </c>
+      <c r="Q206">
+        <v>0</v>
+      </c>
+      <c r="R206">
+        <v>0</v>
+      </c>
+      <c r="S206">
+        <v>0</v>
+      </c>
+      <c r="T206">
+        <v>0</v>
+      </c>
+      <c r="U206">
+        <v>0</v>
+      </c>
+      <c r="V206">
+        <v>0</v>
+      </c>
+      <c r="W206">
+        <v>0</v>
+      </c>
+      <c r="X206">
+        <v>0</v>
+      </c>
+      <c r="Y206">
+        <v>0</v>
+      </c>
+      <c r="Z206">
+        <v>0</v>
+      </c>
+      <c r="AA206">
+        <v>0</v>
+      </c>
+      <c r="AB206">
+        <v>0</v>
+      </c>
+      <c r="AC206">
+        <v>0</v>
+      </c>
+      <c r="AD206">
+        <v>0</v>
+      </c>
+      <c r="AE206">
+        <v>0</v>
+      </c>
+      <c r="AF206">
+        <v>0</v>
+      </c>
+      <c r="AG206">
+        <v>0</v>
+      </c>
+      <c r="AH206" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI206" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ206">
+        <v>0</v>
+      </c>
+      <c r="AK206">
+        <v>0</v>
+      </c>
+      <c r="AL206">
+        <v>0</v>
+      </c>
+      <c r="AM206">
+        <v>-1</v>
+      </c>
+      <c r="AN206">
+        <v>-1</v>
+      </c>
+      <c r="AO206">
+        <v>-1</v>
+      </c>
+      <c r="AP206">
+        <v>-1</v>
+      </c>
+      <c r="AQ206">
+        <v>0</v>
+      </c>
+      <c r="AR206">
+        <v>0</v>
+      </c>
+      <c r="AS206">
+        <v>0</v>
+      </c>
+      <c r="AT206">
+        <v>0</v>
+      </c>
+      <c r="AU206" t="inlineStr">
         <is>
           <t>2026-08-08 23:00:00</t>
         </is>

--- a/jogos_2026-08-08.xlsx
+++ b/jogos_2026-08-08.xlsx
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="G49">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G50">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G51">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G59">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G60">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G78">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G79">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G82">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G83">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G84">

--- a/jogos_2026-08-08.xlsx
+++ b/jogos_2026-08-08.xlsx
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G29">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G43">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="G48">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G49">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="G51">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G70">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G71">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G72">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="G74">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G75">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G78">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G79">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G103">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G104">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G105">
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G171">
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G172">
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G187">
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G188">
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G189">

--- a/jogos_2026-08-08.xlsx
+++ b/jogos_2026-08-08.xlsx
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shimizu S-Pulse</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Shimizu S-Pulse</t>
         </is>
       </c>
       <c r="G20">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="G23">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5075,10 +5075,10 @@
         <v>0</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC29">
         <v>0</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5564,10 +5564,10 @@
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC32">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>5.68</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -8830,10 +8830,10 @@
         <v>0</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AE52">
         <v>0</v>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O80">
-        <v>0</v>
+        <v>5.47</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O98">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="Q98">
         <v>0</v>
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O113">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P113">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -24596,13 +24596,13 @@
         </is>
       </c>
       <c r="N149">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O149">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P149">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q149">
         <v>0</v>
@@ -24759,13 +24759,13 @@
         </is>
       </c>
       <c r="N150">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O150">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P150">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="Q150">
         <v>0</v>
@@ -24922,13 +24922,13 @@
         </is>
       </c>
       <c r="N151">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O151">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P151">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q151">
         <v>0</v>
@@ -25085,13 +25085,13 @@
         </is>
       </c>
       <c r="N152">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O152">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P152">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="Q152">
         <v>0</v>
@@ -25248,13 +25248,13 @@
         </is>
       </c>
       <c r="N153">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="O153">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P153">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -25574,13 +25574,13 @@
         </is>
       </c>
       <c r="N155">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="O155">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P155">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q155">
         <v>0</v>
@@ -25737,13 +25737,13 @@
         </is>
       </c>
       <c r="N156">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O156">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P156">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q156">
         <v>0</v>
@@ -25900,13 +25900,13 @@
         </is>
       </c>
       <c r="N157">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O157">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P157">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="Q157">
         <v>0</v>
@@ -28667,7 +28667,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N174">

--- a/jogos_2026-08-08.xlsx
+++ b/jogos_2026-08-08.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU206"/>
+  <dimension ref="A1:AU204"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -11921,10 +11921,10 @@
         <v>0</v>
       </c>
       <c r="AA71">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB71">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC71">
         <v>0</v>
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O72">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="Q72">
         <v>0</v>
@@ -12084,10 +12084,10 @@
         <v>0</v>
       </c>
       <c r="AA72">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB72">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC72">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G82">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G83">
@@ -13959,7 +13959,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G84">
@@ -14122,22 +14122,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G85">
@@ -14285,7 +14285,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G86">
@@ -14443,12 +14443,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G87">
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>2026-08-08 11:00:00</t>
+          <t>2026-08-08 11:30:00</t>
         </is>
       </c>
     </row>
@@ -14611,22 +14611,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="G88">
@@ -14774,7 +14774,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O89">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -14855,10 +14855,10 @@
         <v>0</v>
       </c>
       <c r="AA89">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB89">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC89">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O90">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P90">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q90">
         <v>0</v>
@@ -15018,10 +15018,10 @@
         <v>0</v>
       </c>
       <c r="AA90">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB90">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC90">
         <v>0</v>
@@ -15100,7 +15100,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G91">
@@ -15258,27 +15258,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G92">
@@ -15409,7 +15409,7 @@
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>2026-08-08 11:30:00</t>
+          <t>2026-08-08 12:00:00</t>
         </is>
       </c>
     </row>
@@ -15426,7 +15426,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G93">
@@ -15589,22 +15589,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G94">
@@ -15752,7 +15752,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G95">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G96">
@@ -16078,22 +16078,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O97">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P97">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="Q97">
         <v>0</v>
@@ -16241,22 +16241,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O98">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="P98">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="Q98">
         <v>0</v>
@@ -16404,7 +16404,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O99">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="P99">
-        <v>0</v>
+        <v>6.51</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -16567,7 +16567,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O100">
-        <v>4.94</v>
+        <v>0</v>
       </c>
       <c r="P100">
-        <v>6.51</v>
+        <v>0</v>
       </c>
       <c r="Q100">
         <v>0</v>
@@ -16730,22 +16730,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G101">
@@ -16888,27 +16888,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G102">
@@ -17039,7 +17039,7 @@
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>2026-08-08 12:00:00</t>
+          <t>2026-08-08 12:30:00</t>
         </is>
       </c>
     </row>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G103">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G104">
@@ -17382,7 +17382,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G105">
@@ -17545,7 +17545,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G106">
@@ -17708,22 +17708,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G107">
@@ -17871,22 +17871,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,13 +17913,13 @@
         </is>
       </c>
       <c r="N108">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O108">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P108">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q108">
         <v>0</v>
@@ -18029,12 +18029,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O109">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P109">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q109">
         <v>0</v>
@@ -18180,7 +18180,7 @@
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>2026-08-08 12:30:00</t>
+          <t>2026-08-08 13:00:00</t>
         </is>
       </c>
     </row>
@@ -18197,22 +18197,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G110">
@@ -18360,7 +18360,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G111">
@@ -18523,7 +18523,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O112">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q112">
         <v>0</v>
@@ -18686,22 +18686,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O113">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="P113">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G114">
@@ -19012,22 +19012,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G115">
@@ -19175,22 +19175,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G116">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="G117">
@@ -19501,7 +19501,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G118">
@@ -19659,12 +19659,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,13 +19706,13 @@
         </is>
       </c>
       <c r="N119">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O119">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P119">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q119">
         <v>0</v>
@@ -19810,7 +19810,7 @@
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>2026-08-08 13:00:00</t>
+          <t>2026-08-08 13:15:00</t>
         </is>
       </c>
     </row>
@@ -19822,27 +19822,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,13 +19869,13 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O120">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P120">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="Q120">
         <v>0</v>
@@ -19973,7 +19973,7 @@
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>2026-08-08 13:15:00</t>
+          <t>2026-08-08 13:30:00</t>
         </is>
       </c>
     </row>
@@ -19990,22 +19990,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G121">
@@ -20153,7 +20153,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G122">
@@ -20311,12 +20311,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G123">
@@ -20462,7 +20462,7 @@
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>2026-08-08 13:30:00</t>
+          <t>2026-08-08 13:45:00</t>
         </is>
       </c>
     </row>
@@ -20474,27 +20474,27 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G124">
@@ -20625,7 +20625,7 @@
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>2026-08-08 13:45:00</t>
+          <t>2026-08-08 14:00:00</t>
         </is>
       </c>
     </row>
@@ -20642,22 +20642,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G125">
@@ -20805,7 +20805,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G126">
@@ -20968,22 +20968,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G127">
@@ -21131,22 +21131,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,13 +21173,13 @@
         </is>
       </c>
       <c r="N128">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O128">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P128">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="Q128">
         <v>0</v>
@@ -21212,10 +21212,10 @@
         <v>0</v>
       </c>
       <c r="AA128">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB128">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC128">
         <v>0</v>
@@ -21294,7 +21294,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,13 +21336,13 @@
         </is>
       </c>
       <c r="N129">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O129">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="P129">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="Q129">
         <v>0</v>
@@ -21375,10 +21375,10 @@
         <v>0</v>
       </c>
       <c r="AA129">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB129">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC129">
         <v>0</v>
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G132">
@@ -21941,12 +21941,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,13 +21988,13 @@
         </is>
       </c>
       <c r="N133">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="O133">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P133">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q133">
         <v>0</v>
@@ -22027,10 +22027,10 @@
         <v>0</v>
       </c>
       <c r="AA133">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB133">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC133">
         <v>0</v>
@@ -22092,7 +22092,7 @@
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>2026-08-08 14:00:00</t>
+          <t>2026-08-08 14:30:00</t>
         </is>
       </c>
     </row>
@@ -22109,7 +22109,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,13 +22151,13 @@
         </is>
       </c>
       <c r="N134">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="O134">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P134">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q134">
         <v>0</v>
@@ -22282,14 +22282,14 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
+          <t>CSKA Moskva</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
           <t>Rostov</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>CSKA Moskva</t>
-        </is>
-      </c>
       <c r="G135">
         <v>0</v>
       </c>
@@ -22314,13 +22314,13 @@
         </is>
       </c>
       <c r="N135">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="O135">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P135">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q135">
         <v>0</v>
@@ -22430,12 +22430,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G136">
@@ -22581,7 +22581,7 @@
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>2026-08-08 14:30:00</t>
+          <t>2026-08-08 15:00:00</t>
         </is>
       </c>
     </row>
@@ -22598,7 +22598,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G137">
@@ -22761,7 +22761,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G138">
@@ -22924,7 +22924,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G139">
@@ -23082,12 +23082,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Podbeskidzie</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G140">
@@ -23233,7 +23233,7 @@
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>2026-08-08 15:00:00</t>
+          <t>2026-08-08 15:15:00</t>
         </is>
       </c>
     </row>
@@ -23250,7 +23250,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Podbeskidzie</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G141">
@@ -23413,7 +23413,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G142">
@@ -23576,7 +23576,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Dunav 2010</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G143">
@@ -23734,12 +23734,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Dunav 2010</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G144">
@@ -23885,7 +23885,7 @@
       </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>2026-08-08 15:15:00</t>
+          <t>2026-08-08 15:30:00</t>
         </is>
       </c>
     </row>
@@ -23902,7 +23902,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G145">
@@ -24065,7 +24065,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G146">
@@ -24228,7 +24228,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Voluntari</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,13 +24270,13 @@
         </is>
       </c>
       <c r="N147">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O147">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P147">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q147">
         <v>0</v>
@@ -24386,12 +24386,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Voluntari</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G148">
@@ -24433,13 +24433,13 @@
         </is>
       </c>
       <c r="N148">
-        <v>1.64</v>
+        <v>1.99</v>
       </c>
       <c r="O148">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="P148">
-        <v>4.8</v>
+        <v>3.54</v>
       </c>
       <c r="Q148">
         <v>0</v>
@@ -24537,7 +24537,7 @@
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>2026-08-08 15:30:00</t>
+          <t>2026-08-08 15:45:00</t>
         </is>
       </c>
     </row>
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G149">
@@ -24596,13 +24596,13 @@
         </is>
       </c>
       <c r="N149">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="O149">
-        <v>3.54</v>
+        <v>3.68</v>
       </c>
       <c r="P149">
-        <v>3.54</v>
+        <v>4.08</v>
       </c>
       <c r="Q149">
         <v>0</v>
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G150">
@@ -24759,13 +24759,13 @@
         </is>
       </c>
       <c r="N150">
-        <v>1.82</v>
+        <v>2.38</v>
       </c>
       <c r="O150">
-        <v>3.68</v>
+        <v>3.46</v>
       </c>
       <c r="P150">
-        <v>4.08</v>
+        <v>2.75</v>
       </c>
       <c r="Q150">
         <v>0</v>
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G151">
@@ -24922,13 +24922,13 @@
         </is>
       </c>
       <c r="N151">
-        <v>2.38</v>
+        <v>1.67</v>
       </c>
       <c r="O151">
-        <v>3.46</v>
+        <v>3.58</v>
       </c>
       <c r="P151">
-        <v>2.75</v>
+        <v>5.28</v>
       </c>
       <c r="Q151">
         <v>0</v>
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,13 +25085,13 @@
         </is>
       </c>
       <c r="N152">
-        <v>1.67</v>
+        <v>4.18</v>
       </c>
       <c r="O152">
-        <v>3.58</v>
+        <v>3.52</v>
       </c>
       <c r="P152">
-        <v>5.28</v>
+        <v>1.84</v>
       </c>
       <c r="Q152">
         <v>0</v>
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,13 +25248,13 @@
         </is>
       </c>
       <c r="N153">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="O153">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="P153">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="N154">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="O154">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P154">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,13 +25574,13 @@
         </is>
       </c>
       <c r="N155">
-        <v>4.08</v>
+        <v>2.47</v>
       </c>
       <c r="O155">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="P155">
-        <v>1.84</v>
+        <v>2.74</v>
       </c>
       <c r="Q155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,13 +25737,13 @@
         </is>
       </c>
       <c r="N156">
-        <v>2.47</v>
+        <v>1.85</v>
       </c>
       <c r="O156">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="P156">
-        <v>2.74</v>
+        <v>4.03</v>
       </c>
       <c r="Q156">
         <v>0</v>
@@ -25858,7 +25858,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,13 +25900,13 @@
         </is>
       </c>
       <c r="N157">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="O157">
-        <v>3.58</v>
+        <v>3.79</v>
       </c>
       <c r="P157">
-        <v>4.03</v>
+        <v>4.66</v>
       </c>
       <c r="Q157">
         <v>0</v>
@@ -25939,10 +25939,10 @@
         <v>0</v>
       </c>
       <c r="AA157">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB157">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC157">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,13 +26063,13 @@
         </is>
       </c>
       <c r="N158">
-        <v>1.76</v>
+        <v>4.55</v>
       </c>
       <c r="O158">
-        <v>3.79</v>
+        <v>3.77</v>
       </c>
       <c r="P158">
-        <v>4.66</v>
+        <v>1.78</v>
       </c>
       <c r="Q158">
         <v>0</v>
@@ -26179,27 +26179,27 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,13 +26226,13 @@
         </is>
       </c>
       <c r="N159">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="O159">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="P159">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q159">
         <v>0</v>
@@ -26265,10 +26265,10 @@
         <v>0</v>
       </c>
       <c r="AA159">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB159">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC159">
         <v>0</v>
@@ -26330,7 +26330,7 @@
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>2026-08-08 15:45:00</t>
+          <t>2026-08-08 16:00:00</t>
         </is>
       </c>
     </row>
@@ -26347,22 +26347,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G160">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G161">
@@ -26673,22 +26673,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G162">
@@ -26715,13 +26715,13 @@
         </is>
       </c>
       <c r="N162">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O162">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="P162">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="Q162">
         <v>0</v>
@@ -26754,10 +26754,10 @@
         <v>0</v>
       </c>
       <c r="AA162">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB162">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC162">
         <v>0</v>
@@ -26836,7 +26836,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G163">
@@ -26878,13 +26878,13 @@
         </is>
       </c>
       <c r="N163">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O163">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="P163">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="Q163">
         <v>0</v>
@@ -26917,10 +26917,10 @@
         <v>0</v>
       </c>
       <c r="AA163">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB163">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC163">
         <v>0</v>
@@ -26999,7 +26999,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G164">
@@ -27162,22 +27162,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G165">
@@ -27325,7 +27325,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G166">
@@ -27488,7 +27488,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G167">
@@ -27651,22 +27651,22 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G168">
@@ -27693,13 +27693,13 @@
         </is>
       </c>
       <c r="N168">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O168">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P168">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q168">
         <v>0</v>
@@ -27732,10 +27732,10 @@
         <v>0</v>
       </c>
       <c r="AA168">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB168">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC168">
         <v>0</v>
@@ -27809,27 +27809,27 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G169">
@@ -27856,13 +27856,13 @@
         </is>
       </c>
       <c r="N169">
-        <v>2.24</v>
+        <v>12.1</v>
       </c>
       <c r="O169">
-        <v>3.18</v>
+        <v>6.35</v>
       </c>
       <c r="P169">
-        <v>3.2</v>
+        <v>1.26</v>
       </c>
       <c r="Q169">
         <v>0</v>
@@ -27895,16 +27895,16 @@
         <v>0</v>
       </c>
       <c r="AA169">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB169">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC169">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD169">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE169">
         <v>0</v>
@@ -27960,7 +27960,7 @@
       </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>2026-08-08 16:00:00</t>
+          <t>2026-08-08 16:30:00</t>
         </is>
       </c>
     </row>
@@ -27972,27 +27972,27 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G170">
@@ -28019,13 +28019,13 @@
         </is>
       </c>
       <c r="N170">
-        <v>12.1</v>
+        <v>0</v>
       </c>
       <c r="O170">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="P170">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Q170">
         <v>0</v>
@@ -28064,10 +28064,10 @@
         <v>0</v>
       </c>
       <c r="AC170">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD170">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE170">
         <v>0</v>
@@ -28123,7 +28123,7 @@
       </c>
       <c r="AU170" t="inlineStr">
         <is>
-          <t>2026-08-08 16:30:00</t>
+          <t>2026-08-08 17:00:00</t>
         </is>
       </c>
     </row>
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G171">
@@ -28303,7 +28303,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G172">
@@ -28461,12 +28461,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G173">
@@ -28508,64 +28508,64 @@
         </is>
       </c>
       <c r="N173">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O173">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P173">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q173">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R173">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S173">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T173">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="U173">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V173">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W173">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X173">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y173">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z173">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="AA173">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB173">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC173">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AD173">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE173">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF173">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG173">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AH173" t="inlineStr">
         <is>
@@ -28578,10 +28578,10 @@
         </is>
       </c>
       <c r="AJ173">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK173">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL173">
         <v>0</v>
@@ -28612,7 +28612,7 @@
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>2026-08-08 17:00:00</t>
+          <t>2026-08-08 17:30:00</t>
         </is>
       </c>
     </row>
@@ -28624,12 +28624,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G174">
@@ -28671,64 +28671,64 @@
         </is>
       </c>
       <c r="N174">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O174">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="P174">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q174">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R174">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S174">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T174">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="U174">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="V174">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W174">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X174">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y174">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z174">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="AA174">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB174">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC174">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="AD174">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE174">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF174">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG174">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AH174" t="inlineStr">
         <is>
@@ -28741,10 +28741,10 @@
         </is>
       </c>
       <c r="AJ174">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK174">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL174">
         <v>0</v>
@@ -28775,7 +28775,7 @@
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>2026-08-08 17:30:00</t>
+          <t>2026-08-08 18:00:00</t>
         </is>
       </c>
     </row>
@@ -28787,12 +28787,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G175">
@@ -28938,7 +28938,7 @@
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>2026-08-08 18:00:00</t>
+          <t>2026-08-08 18:15:00</t>
         </is>
       </c>
     </row>
@@ -28950,12 +28950,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G176">
@@ -29101,7 +29101,7 @@
       </c>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>2026-08-08 18:15:00</t>
+          <t>2026-08-08 18:30:00</t>
         </is>
       </c>
     </row>
@@ -29118,7 +29118,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,13 +29160,13 @@
         </is>
       </c>
       <c r="N177">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O177">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P177">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q177">
         <v>0</v>
@@ -29199,10 +29199,10 @@
         <v>0</v>
       </c>
       <c r="AA177">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB177">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC177">
         <v>0</v>
@@ -29281,7 +29281,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,13 +29323,13 @@
         </is>
       </c>
       <c r="N178">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="O178">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P178">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q178">
         <v>0</v>
@@ -29362,10 +29362,10 @@
         <v>0</v>
       </c>
       <c r="AA178">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB178">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC178">
         <v>0</v>
@@ -29444,7 +29444,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G179">
@@ -29607,7 +29607,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G180">
@@ -29649,13 +29649,13 @@
         </is>
       </c>
       <c r="N180">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O180">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P180">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="Q180">
         <v>0</v>
@@ -29688,10 +29688,10 @@
         <v>0</v>
       </c>
       <c r="AA180">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB180">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC180">
         <v>0</v>
@@ -29765,12 +29765,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G181">
@@ -29812,13 +29812,13 @@
         </is>
       </c>
       <c r="N181">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O181">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P181">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="Q181">
         <v>0</v>
@@ -29851,10 +29851,10 @@
         <v>0</v>
       </c>
       <c r="AA181">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB181">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC181">
         <v>0</v>
@@ -29916,7 +29916,7 @@
       </c>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>2026-08-08 18:30:00</t>
+          <t>2026-08-08 19:30:00</t>
         </is>
       </c>
     </row>
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G182">
@@ -30096,7 +30096,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G183">
@@ -30254,12 +30254,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G184">
@@ -30405,7 +30405,7 @@
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>2026-08-08 19:30:00</t>
+          <t>2026-08-08 20:00:00</t>
         </is>
       </c>
     </row>
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G185">
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G186">
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G187">
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G188">
@@ -31069,12 +31069,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G189">
@@ -31116,13 +31116,13 @@
         </is>
       </c>
       <c r="N189">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O189">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="P189">
-        <v>0</v>
+        <v>6.23</v>
       </c>
       <c r="Q189">
         <v>0</v>
@@ -31155,10 +31155,10 @@
         <v>0</v>
       </c>
       <c r="AA189">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB189">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC189">
         <v>0</v>
@@ -31220,7 +31220,7 @@
       </c>
       <c r="AU189" t="inlineStr">
         <is>
-          <t>2026-08-08 20:00:00</t>
+          <t>2026-08-08 20:30:00</t>
         </is>
       </c>
     </row>
@@ -31237,7 +31237,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G190">
@@ -31279,13 +31279,13 @@
         </is>
       </c>
       <c r="N190">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="O190">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="P190">
-        <v>6.23</v>
+        <v>0</v>
       </c>
       <c r="Q190">
         <v>0</v>
@@ -31318,10 +31318,10 @@
         <v>0</v>
       </c>
       <c r="AA190">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB190">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC190">
         <v>0</v>
@@ -31400,7 +31400,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="G191">
@@ -31558,12 +31558,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G192">
@@ -31709,7 +31709,7 @@
       </c>
       <c r="AU192" t="inlineStr">
         <is>
-          <t>2026-08-08 20:30:00</t>
+          <t>2026-08-08 21:00:00</t>
         </is>
       </c>
     </row>
@@ -31726,7 +31726,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,13 +31768,13 @@
         </is>
       </c>
       <c r="N193">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O193">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P193">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q193">
         <v>0</v>
@@ -31807,10 +31807,10 @@
         <v>0</v>
       </c>
       <c r="AA193">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB193">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC193">
         <v>0</v>
@@ -31889,7 +31889,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G194">
@@ -31931,13 +31931,13 @@
         </is>
       </c>
       <c r="N194">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O194">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P194">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q194">
         <v>0</v>
@@ -31970,10 +31970,10 @@
         <v>0</v>
       </c>
       <c r="AA194">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB194">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC194">
         <v>0</v>
@@ -32052,22 +32052,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G195">
@@ -32215,22 +32215,22 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G196">
@@ -32378,22 +32378,22 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G197">
@@ -32541,22 +32541,22 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G198">
@@ -32704,22 +32704,22 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G199">
@@ -32862,27 +32862,27 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G200">
@@ -33013,7 +33013,7 @@
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>2026-08-08 21:00:00</t>
+          <t>2026-08-08 21:30:00</t>
         </is>
       </c>
     </row>
@@ -33025,27 +33025,27 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G201">
@@ -33176,7 +33176,7 @@
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>2026-08-08 21:00:00</t>
+          <t>2026-08-08 21:45:00</t>
         </is>
       </c>
     </row>
@@ -33188,7 +33188,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G202">
@@ -33339,7 +33339,7 @@
       </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>2026-08-08 21:30:00</t>
+          <t>2026-08-08 22:00:00</t>
         </is>
       </c>
     </row>
@@ -33351,12 +33351,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G203">
@@ -33502,7 +33502,7 @@
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>2026-08-08 21:45:00</t>
+          <t>2026-08-08 23:00:00</t>
         </is>
       </c>
     </row>
@@ -33514,7 +33514,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G204">
@@ -33664,332 +33664,6 @@
         <v>0</v>
       </c>
       <c r="AU204" t="inlineStr">
-        <is>
-          <t>2026-08-08 22:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>Monterey Bay</t>
-        </is>
-      </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>New Mexico United</t>
-        </is>
-      </c>
-      <c r="G205">
-        <v>0</v>
-      </c>
-      <c r="H205">
-        <v>0</v>
-      </c>
-      <c r="I205">
-        <v>0</v>
-      </c>
-      <c r="J205">
-        <v>0</v>
-      </c>
-      <c r="K205">
-        <v>0</v>
-      </c>
-      <c r="L205">
-        <v>0</v>
-      </c>
-      <c r="M205" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N205">
-        <v>0</v>
-      </c>
-      <c r="O205">
-        <v>0</v>
-      </c>
-      <c r="P205">
-        <v>0</v>
-      </c>
-      <c r="Q205">
-        <v>0</v>
-      </c>
-      <c r="R205">
-        <v>0</v>
-      </c>
-      <c r="S205">
-        <v>0</v>
-      </c>
-      <c r="T205">
-        <v>0</v>
-      </c>
-      <c r="U205">
-        <v>0</v>
-      </c>
-      <c r="V205">
-        <v>0</v>
-      </c>
-      <c r="W205">
-        <v>0</v>
-      </c>
-      <c r="X205">
-        <v>0</v>
-      </c>
-      <c r="Y205">
-        <v>0</v>
-      </c>
-      <c r="Z205">
-        <v>0</v>
-      </c>
-      <c r="AA205">
-        <v>0</v>
-      </c>
-      <c r="AB205">
-        <v>0</v>
-      </c>
-      <c r="AC205">
-        <v>0</v>
-      </c>
-      <c r="AD205">
-        <v>0</v>
-      </c>
-      <c r="AE205">
-        <v>0</v>
-      </c>
-      <c r="AF205">
-        <v>0</v>
-      </c>
-      <c r="AG205">
-        <v>0</v>
-      </c>
-      <c r="AH205" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI205" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ205">
-        <v>0</v>
-      </c>
-      <c r="AK205">
-        <v>0</v>
-      </c>
-      <c r="AL205">
-        <v>0</v>
-      </c>
-      <c r="AM205">
-        <v>-1</v>
-      </c>
-      <c r="AN205">
-        <v>-1</v>
-      </c>
-      <c r="AO205">
-        <v>-1</v>
-      </c>
-      <c r="AP205">
-        <v>-1</v>
-      </c>
-      <c r="AQ205">
-        <v>0</v>
-      </c>
-      <c r="AR205">
-        <v>0</v>
-      </c>
-      <c r="AS205">
-        <v>0</v>
-      </c>
-      <c r="AT205">
-        <v>0</v>
-      </c>
-      <c r="AU205" t="inlineStr">
-        <is>
-          <t>2026-08-08 23:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>Orange County SC</t>
-        </is>
-      </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>Tampa Bay Rowdies</t>
-        </is>
-      </c>
-      <c r="G206">
-        <v>0</v>
-      </c>
-      <c r="H206">
-        <v>0</v>
-      </c>
-      <c r="I206">
-        <v>0</v>
-      </c>
-      <c r="J206">
-        <v>0</v>
-      </c>
-      <c r="K206">
-        <v>0</v>
-      </c>
-      <c r="L206">
-        <v>0</v>
-      </c>
-      <c r="M206" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N206">
-        <v>0</v>
-      </c>
-      <c r="O206">
-        <v>0</v>
-      </c>
-      <c r="P206">
-        <v>0</v>
-      </c>
-      <c r="Q206">
-        <v>0</v>
-      </c>
-      <c r="R206">
-        <v>0</v>
-      </c>
-      <c r="S206">
-        <v>0</v>
-      </c>
-      <c r="T206">
-        <v>0</v>
-      </c>
-      <c r="U206">
-        <v>0</v>
-      </c>
-      <c r="V206">
-        <v>0</v>
-      </c>
-      <c r="W206">
-        <v>0</v>
-      </c>
-      <c r="X206">
-        <v>0</v>
-      </c>
-      <c r="Y206">
-        <v>0</v>
-      </c>
-      <c r="Z206">
-        <v>0</v>
-      </c>
-      <c r="AA206">
-        <v>0</v>
-      </c>
-      <c r="AB206">
-        <v>0</v>
-      </c>
-      <c r="AC206">
-        <v>0</v>
-      </c>
-      <c r="AD206">
-        <v>0</v>
-      </c>
-      <c r="AE206">
-        <v>0</v>
-      </c>
-      <c r="AF206">
-        <v>0</v>
-      </c>
-      <c r="AG206">
-        <v>0</v>
-      </c>
-      <c r="AH206" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI206" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ206">
-        <v>0</v>
-      </c>
-      <c r="AK206">
-        <v>0</v>
-      </c>
-      <c r="AL206">
-        <v>0</v>
-      </c>
-      <c r="AM206">
-        <v>-1</v>
-      </c>
-      <c r="AN206">
-        <v>-1</v>
-      </c>
-      <c r="AO206">
-        <v>-1</v>
-      </c>
-      <c r="AP206">
-        <v>-1</v>
-      </c>
-      <c r="AQ206">
-        <v>0</v>
-      </c>
-      <c r="AR206">
-        <v>0</v>
-      </c>
-      <c r="AS206">
-        <v>0</v>
-      </c>
-      <c r="AT206">
-        <v>0</v>
-      </c>
-      <c r="AU206" t="inlineStr">
         <is>
           <t>2026-08-08 23:00:00</t>
         </is>

--- a/jogos_2026-08-08.xlsx
+++ b/jogos_2026-08-08.xlsx
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q61">
         <v>0</v>
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O73">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P73">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q73">
         <v>0</v>
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O75">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P75">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O104">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P104">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -17750,13 +17750,13 @@
         </is>
       </c>
       <c r="N107">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O107">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P107">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q107">
         <v>0</v>
@@ -17789,10 +17789,10 @@
         <v>0</v>
       </c>
       <c r="AA107">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB107">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC107">
         <v>0</v>
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O109">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P109">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q109">
         <v>0</v>
@@ -25248,13 +25248,13 @@
         </is>
       </c>
       <c r="N153">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O153">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="P153">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -30627,13 +30627,13 @@
         </is>
       </c>
       <c r="N186">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O186">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P186">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q186">
         <v>0</v>
@@ -30790,13 +30790,13 @@
         </is>
       </c>
       <c r="N187">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O187">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P187">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q187">
         <v>0</v>
@@ -30953,13 +30953,13 @@
         </is>
       </c>
       <c r="N188">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O188">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P188">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q188">
         <v>0</v>
@@ -31279,13 +31279,13 @@
         </is>
       </c>
       <c r="N190">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O190">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P190">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q190">
         <v>0</v>
@@ -31318,10 +31318,10 @@
         <v>0</v>
       </c>
       <c r="AA190">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB190">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC190">
         <v>0</v>
@@ -31931,13 +31931,13 @@
         </is>
       </c>
       <c r="N194">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O194">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P194">
-        <v>0</v>
+        <v>5.43</v>
       </c>
       <c r="Q194">
         <v>0</v>
@@ -33072,13 +33072,13 @@
         </is>
       </c>
       <c r="N201">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O201">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P201">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q201">
         <v>0</v>
@@ -33561,13 +33561,13 @@
         </is>
       </c>
       <c r="N204">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="O204">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P204">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q204">
         <v>0</v>
@@ -33600,10 +33600,10 @@
         <v>0</v>
       </c>
       <c r="AA204">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB204">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC204">
         <v>0</v>

--- a/jogos_2026-08-08.xlsx
+++ b/jogos_2026-08-08.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU204"/>
+  <dimension ref="A1:AU206"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22435,7 +22435,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G136">
@@ -22598,7 +22598,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G137">
@@ -22761,7 +22761,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G138">
@@ -22924,7 +22924,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G139">
@@ -23082,12 +23082,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Podbeskidzie</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G140">
@@ -23233,7 +23233,7 @@
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>2026-08-08 15:15:00</t>
+          <t>2026-08-08 15:00:00</t>
         </is>
       </c>
     </row>
@@ -23245,12 +23245,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G141">
@@ -23396,7 +23396,7 @@
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>2026-08-08 15:15:00</t>
+          <t>2026-08-08 15:00:00</t>
         </is>
       </c>
     </row>
@@ -23413,7 +23413,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Podbeskidzie</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G142">
@@ -23576,7 +23576,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Dunav 2010</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G143">
@@ -23734,12 +23734,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G144">
@@ -23885,7 +23885,7 @@
       </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>2026-08-08 15:30:00</t>
+          <t>2026-08-08 15:15:00</t>
         </is>
       </c>
     </row>
@@ -23897,12 +23897,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Dunav 2010</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G145">
@@ -24048,7 +24048,7 @@
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>2026-08-08 15:30:00</t>
+          <t>2026-08-08 15:15:00</t>
         </is>
       </c>
     </row>
@@ -24065,7 +24065,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G146">
@@ -24228,7 +24228,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Voluntari</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,13 +24270,13 @@
         </is>
       </c>
       <c r="N147">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="O147">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P147">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="Q147">
         <v>0</v>
@@ -24386,12 +24386,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G148">
@@ -24433,13 +24433,13 @@
         </is>
       </c>
       <c r="N148">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O148">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P148">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q148">
         <v>0</v>
@@ -24537,7 +24537,7 @@
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>2026-08-08 15:45:00</t>
+          <t>2026-08-08 15:30:00</t>
         </is>
       </c>
     </row>
@@ -24549,12 +24549,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Voluntari</t>
         </is>
       </c>
       <c r="G149">
@@ -24596,13 +24596,13 @@
         </is>
       </c>
       <c r="N149">
-        <v>1.82</v>
+        <v>1.64</v>
       </c>
       <c r="O149">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="P149">
-        <v>4.08</v>
+        <v>4.8</v>
       </c>
       <c r="Q149">
         <v>0</v>
@@ -24700,7 +24700,7 @@
       </c>
       <c r="AU149" t="inlineStr">
         <is>
-          <t>2026-08-08 15:45:00</t>
+          <t>2026-08-08 15:30:00</t>
         </is>
       </c>
     </row>
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G150">
@@ -24759,13 +24759,13 @@
         </is>
       </c>
       <c r="N150">
-        <v>2.38</v>
+        <v>1.67</v>
       </c>
       <c r="O150">
-        <v>3.46</v>
+        <v>3.58</v>
       </c>
       <c r="P150">
-        <v>2.75</v>
+        <v>5.28</v>
       </c>
       <c r="Q150">
         <v>0</v>
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G151">
@@ -24922,13 +24922,13 @@
         </is>
       </c>
       <c r="N151">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="O151">
         <v>3.58</v>
       </c>
       <c r="P151">
-        <v>5.28</v>
+        <v>4.03</v>
       </c>
       <c r="Q151">
         <v>0</v>
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,13 +25085,13 @@
         </is>
       </c>
       <c r="N152">
-        <v>4.18</v>
+        <v>1.99</v>
       </c>
       <c r="O152">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="P152">
-        <v>1.84</v>
+        <v>3.54</v>
       </c>
       <c r="Q152">
         <v>0</v>
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,13 +25248,13 @@
         </is>
       </c>
       <c r="N153">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="O153">
-        <v>3.64</v>
+        <v>3.68</v>
       </c>
       <c r="P153">
-        <v>4.75</v>
+        <v>4.08</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="N154">
-        <v>4.08</v>
+        <v>2.38</v>
       </c>
       <c r="O154">
-        <v>3.58</v>
+        <v>3.46</v>
       </c>
       <c r="P154">
-        <v>1.84</v>
+        <v>2.75</v>
       </c>
       <c r="Q154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,13 +25574,13 @@
         </is>
       </c>
       <c r="N155">
-        <v>2.47</v>
+        <v>1.72</v>
       </c>
       <c r="O155">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="P155">
-        <v>2.74</v>
+        <v>4.75</v>
       </c>
       <c r="Q155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,13 +25737,13 @@
         </is>
       </c>
       <c r="N156">
-        <v>1.85</v>
+        <v>2.47</v>
       </c>
       <c r="O156">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="P156">
-        <v>4.03</v>
+        <v>2.74</v>
       </c>
       <c r="Q156">
         <v>0</v>
@@ -25858,7 +25858,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,13 +25900,13 @@
         </is>
       </c>
       <c r="N157">
-        <v>1.76</v>
+        <v>4.18</v>
       </c>
       <c r="O157">
-        <v>3.79</v>
+        <v>3.52</v>
       </c>
       <c r="P157">
-        <v>4.66</v>
+        <v>1.84</v>
       </c>
       <c r="Q157">
         <v>0</v>
@@ -25939,10 +25939,10 @@
         <v>0</v>
       </c>
       <c r="AA157">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB157">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC157">
         <v>0</v>
@@ -26021,7 +26021,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,13 +26063,13 @@
         </is>
       </c>
       <c r="N158">
-        <v>4.55</v>
+        <v>4.08</v>
       </c>
       <c r="O158">
-        <v>3.77</v>
+        <v>3.58</v>
       </c>
       <c r="P158">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="Q158">
         <v>0</v>
@@ -26102,10 +26102,10 @@
         <v>0</v>
       </c>
       <c r="AA158">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB158">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC158">
         <v>0</v>
@@ -26179,27 +26179,27 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,13 +26226,13 @@
         </is>
       </c>
       <c r="N159">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O159">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="P159">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="Q159">
         <v>0</v>
@@ -26265,10 +26265,10 @@
         <v>0</v>
       </c>
       <c r="AA159">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB159">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC159">
         <v>0</v>
@@ -26330,7 +26330,7 @@
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>2026-08-08 16:00:00</t>
+          <t>2026-08-08 15:45:00</t>
         </is>
       </c>
     </row>
@@ -26342,12 +26342,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G160">
@@ -26389,13 +26389,13 @@
         </is>
       </c>
       <c r="N160">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="O160">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="P160">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q160">
         <v>0</v>
@@ -26428,10 +26428,10 @@
         <v>0</v>
       </c>
       <c r="AA160">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB160">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC160">
         <v>0</v>
@@ -26493,7 +26493,7 @@
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>2026-08-08 16:00:00</t>
+          <t>2026-08-08 15:45:00</t>
         </is>
       </c>
     </row>
@@ -26510,22 +26510,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G161">
@@ -26673,22 +26673,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G162">
@@ -26715,13 +26715,13 @@
         </is>
       </c>
       <c r="N162">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O162">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="P162">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="Q162">
         <v>0</v>
@@ -26754,10 +26754,10 @@
         <v>0</v>
       </c>
       <c r="AA162">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB162">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC162">
         <v>0</v>
@@ -26836,22 +26836,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G163">
@@ -26999,7 +26999,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G164">
@@ -27041,13 +27041,13 @@
         </is>
       </c>
       <c r="N164">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O164">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="P164">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="Q164">
         <v>0</v>
@@ -27080,10 +27080,10 @@
         <v>0</v>
       </c>
       <c r="AA164">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB164">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC164">
         <v>0</v>
@@ -27162,22 +27162,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G165">
@@ -27325,22 +27325,22 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G166">
@@ -27488,7 +27488,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G167">
@@ -27651,22 +27651,22 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G168">
@@ -27693,13 +27693,13 @@
         </is>
       </c>
       <c r="N168">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="O168">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="P168">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q168">
         <v>0</v>
@@ -27732,10 +27732,10 @@
         <v>0</v>
       </c>
       <c r="AA168">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB168">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC168">
         <v>0</v>
@@ -27809,12 +27809,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G169">
@@ -27856,13 +27856,13 @@
         </is>
       </c>
       <c r="N169">
-        <v>12.1</v>
+        <v>0</v>
       </c>
       <c r="O169">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="P169">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Q169">
         <v>0</v>
@@ -27901,10 +27901,10 @@
         <v>0</v>
       </c>
       <c r="AC169">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD169">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE169">
         <v>0</v>
@@ -27960,7 +27960,7 @@
       </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>2026-08-08 16:30:00</t>
+          <t>2026-08-08 16:00:00</t>
         </is>
       </c>
     </row>
@@ -27972,12 +27972,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G170">
@@ -28019,13 +28019,13 @@
         </is>
       </c>
       <c r="N170">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O170">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P170">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q170">
         <v>0</v>
@@ -28058,10 +28058,10 @@
         <v>0</v>
       </c>
       <c r="AA170">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB170">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC170">
         <v>0</v>
@@ -28123,7 +28123,7 @@
       </c>
       <c r="AU170" t="inlineStr">
         <is>
-          <t>2026-08-08 17:00:00</t>
+          <t>2026-08-08 16:00:00</t>
         </is>
       </c>
     </row>
@@ -28135,27 +28135,27 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G171">
@@ -28182,13 +28182,13 @@
         </is>
       </c>
       <c r="N171">
-        <v>0</v>
+        <v>12.1</v>
       </c>
       <c r="O171">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="P171">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Q171">
         <v>0</v>
@@ -28227,10 +28227,10 @@
         <v>0</v>
       </c>
       <c r="AC171">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD171">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE171">
         <v>0</v>
@@ -28286,7 +28286,7 @@
       </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>2026-08-08 17:00:00</t>
+          <t>2026-08-08 16:30:00</t>
         </is>
       </c>
     </row>
@@ -28303,7 +28303,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G172">
@@ -28461,12 +28461,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G173">
@@ -28508,64 +28508,64 @@
         </is>
       </c>
       <c r="N173">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O173">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="P173">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q173">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R173">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S173">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T173">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="U173">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="V173">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W173">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X173">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y173">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z173">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="AA173">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB173">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC173">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="AD173">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE173">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF173">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG173">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AH173" t="inlineStr">
         <is>
@@ -28578,10 +28578,10 @@
         </is>
       </c>
       <c r="AJ173">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK173">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL173">
         <v>0</v>
@@ -28612,7 +28612,7 @@
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>2026-08-08 17:30:00</t>
+          <t>2026-08-08 17:00:00</t>
         </is>
       </c>
     </row>
@@ -28624,12 +28624,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G174">
@@ -28775,7 +28775,7 @@
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>2026-08-08 18:00:00</t>
+          <t>2026-08-08 17:00:00</t>
         </is>
       </c>
     </row>
@@ -28787,12 +28787,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,64 +28834,64 @@
         </is>
       </c>
       <c r="N175">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O175">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P175">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q175">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R175">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S175">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T175">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="U175">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V175">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W175">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X175">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y175">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z175">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="AA175">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB175">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC175">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AD175">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE175">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF175">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG175">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK175">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -28938,7 +28938,7 @@
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>2026-08-08 18:15:00</t>
+          <t>2026-08-08 17:30:00</t>
         </is>
       </c>
     </row>
@@ -28950,12 +28950,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G176">
@@ -29101,7 +29101,7 @@
       </c>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>2026-08-08 18:30:00</t>
+          <t>2026-08-08 18:00:00</t>
         </is>
       </c>
     </row>
@@ -29113,12 +29113,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,13 +29160,13 @@
         </is>
       </c>
       <c r="N177">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="O177">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P177">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q177">
         <v>0</v>
@@ -29199,10 +29199,10 @@
         <v>0</v>
       </c>
       <c r="AA177">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB177">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC177">
         <v>0</v>
@@ -29264,7 +29264,7 @@
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>2026-08-08 18:30:00</t>
+          <t>2026-08-08 18:15:00</t>
         </is>
       </c>
     </row>
@@ -29281,7 +29281,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G178">
@@ -29444,7 +29444,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G179">
@@ -29486,13 +29486,13 @@
         </is>
       </c>
       <c r="N179">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O179">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P179">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q179">
         <v>0</v>
@@ -29525,10 +29525,10 @@
         <v>0</v>
       </c>
       <c r="AA179">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB179">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC179">
         <v>0</v>
@@ -29607,7 +29607,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G180">
@@ -29649,13 +29649,13 @@
         </is>
       </c>
       <c r="N180">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O180">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P180">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="Q180">
         <v>0</v>
@@ -29688,10 +29688,10 @@
         <v>0</v>
       </c>
       <c r="AA180">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB180">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC180">
         <v>0</v>
@@ -29765,12 +29765,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G181">
@@ -29916,7 +29916,7 @@
       </c>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>2026-08-08 19:30:00</t>
+          <t>2026-08-08 18:30:00</t>
         </is>
       </c>
     </row>
@@ -29928,12 +29928,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G182">
@@ -29975,13 +29975,13 @@
         </is>
       </c>
       <c r="N182">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O182">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P182">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="Q182">
         <v>0</v>
@@ -30014,10 +30014,10 @@
         <v>0</v>
       </c>
       <c r="AA182">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB182">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC182">
         <v>0</v>
@@ -30079,7 +30079,7 @@
       </c>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>2026-08-08 19:30:00</t>
+          <t>2026-08-08 18:30:00</t>
         </is>
       </c>
     </row>
@@ -30096,7 +30096,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G183">
@@ -30254,12 +30254,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G184">
@@ -30405,7 +30405,7 @@
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>2026-08-08 20:00:00</t>
+          <t>2026-08-08 19:30:00</t>
         </is>
       </c>
     </row>
@@ -30417,12 +30417,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G185">
@@ -30568,7 +30568,7 @@
       </c>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>2026-08-08 20:00:00</t>
+          <t>2026-08-08 19:30:00</t>
         </is>
       </c>
     </row>
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G186">
@@ -30627,13 +30627,13 @@
         </is>
       </c>
       <c r="N186">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O186">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P186">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Q186">
         <v>0</v>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,13 +30790,13 @@
         </is>
       </c>
       <c r="N187">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O187">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P187">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q187">
         <v>0</v>
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,13 +30953,13 @@
         </is>
       </c>
       <c r="N188">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="O188">
-        <v>3.65</v>
+        <v>3.58</v>
       </c>
       <c r="P188">
-        <v>3.34</v>
+        <v>2.95</v>
       </c>
       <c r="Q188">
         <v>0</v>
@@ -31069,12 +31069,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G189">
@@ -31116,13 +31116,13 @@
         </is>
       </c>
       <c r="N189">
-        <v>1.58</v>
+        <v>1.9</v>
       </c>
       <c r="O189">
-        <v>4.06</v>
+        <v>3.65</v>
       </c>
       <c r="P189">
-        <v>6.23</v>
+        <v>3.34</v>
       </c>
       <c r="Q189">
         <v>0</v>
@@ -31155,10 +31155,10 @@
         <v>0</v>
       </c>
       <c r="AA189">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB189">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC189">
         <v>0</v>
@@ -31220,7 +31220,7 @@
       </c>
       <c r="AU189" t="inlineStr">
         <is>
-          <t>2026-08-08 20:30:00</t>
+          <t>2026-08-08 20:00:00</t>
         </is>
       </c>
     </row>
@@ -31232,7 +31232,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G190">
@@ -31279,13 +31279,13 @@
         </is>
       </c>
       <c r="N190">
-        <v>2.34</v>
+        <v>3.5</v>
       </c>
       <c r="O190">
-        <v>3.13</v>
+        <v>3.54</v>
       </c>
       <c r="P190">
-        <v>2.85</v>
+        <v>1.88</v>
       </c>
       <c r="Q190">
         <v>0</v>
@@ -31318,10 +31318,10 @@
         <v>0</v>
       </c>
       <c r="AA190">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB190">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC190">
         <v>0</v>
@@ -31383,7 +31383,7 @@
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>2026-08-08 20:30:00</t>
+          <t>2026-08-08 20:00:00</t>
         </is>
       </c>
     </row>
@@ -31400,7 +31400,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G191">
@@ -31442,13 +31442,13 @@
         </is>
       </c>
       <c r="N191">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O191">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="P191">
-        <v>0</v>
+        <v>6.23</v>
       </c>
       <c r="Q191">
         <v>0</v>
@@ -31481,10 +31481,10 @@
         <v>0</v>
       </c>
       <c r="AA191">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB191">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC191">
         <v>0</v>
@@ -31558,12 +31558,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G192">
@@ -31605,13 +31605,13 @@
         </is>
       </c>
       <c r="N192">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O192">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P192">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q192">
         <v>0</v>
@@ -31644,10 +31644,10 @@
         <v>0</v>
       </c>
       <c r="AA192">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB192">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC192">
         <v>0</v>
@@ -31709,7 +31709,7 @@
       </c>
       <c r="AU192" t="inlineStr">
         <is>
-          <t>2026-08-08 21:00:00</t>
+          <t>2026-08-08 20:30:00</t>
         </is>
       </c>
     </row>
@@ -31721,12 +31721,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,13 +31768,13 @@
         </is>
       </c>
       <c r="N193">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O193">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P193">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q193">
         <v>0</v>
@@ -31807,10 +31807,10 @@
         <v>0</v>
       </c>
       <c r="AA193">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB193">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC193">
         <v>0</v>
@@ -31872,7 +31872,7 @@
       </c>
       <c r="AU193" t="inlineStr">
         <is>
-          <t>2026-08-08 21:00:00</t>
+          <t>2026-08-08 20:30:00</t>
         </is>
       </c>
     </row>
@@ -31889,7 +31889,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G194">
@@ -31931,13 +31931,13 @@
         </is>
       </c>
       <c r="N194">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="O194">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P194">
-        <v>5.43</v>
+        <v>0</v>
       </c>
       <c r="Q194">
         <v>0</v>
@@ -32052,22 +32052,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G195">
@@ -32094,13 +32094,13 @@
         </is>
       </c>
       <c r="N195">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O195">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P195">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q195">
         <v>0</v>
@@ -32133,10 +32133,10 @@
         <v>0</v>
       </c>
       <c r="AA195">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB195">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC195">
         <v>0</v>
@@ -32215,7 +32215,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,13 +32257,13 @@
         </is>
       </c>
       <c r="N196">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O196">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P196">
-        <v>0</v>
+        <v>5.43</v>
       </c>
       <c r="Q196">
         <v>0</v>
@@ -32378,22 +32378,22 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G197">
@@ -32541,22 +32541,22 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G198">
@@ -32704,22 +32704,22 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G199">
@@ -32862,27 +32862,27 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G200">
@@ -33013,7 +33013,7 @@
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>2026-08-08 21:30:00</t>
+          <t>2026-08-08 21:00:00</t>
         </is>
       </c>
     </row>
@@ -33025,27 +33025,27 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G201">
@@ -33072,13 +33072,13 @@
         </is>
       </c>
       <c r="N201">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="O201">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P201">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q201">
         <v>0</v>
@@ -33176,7 +33176,7 @@
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>2026-08-08 21:45:00</t>
+          <t>2026-08-08 21:00:00</t>
         </is>
       </c>
     </row>
@@ -33188,7 +33188,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G202">
@@ -33339,7 +33339,7 @@
       </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>2026-08-08 22:00:00</t>
+          <t>2026-08-08 21:30:00</t>
         </is>
       </c>
     </row>
@@ -33351,12 +33351,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G203">
@@ -33398,13 +33398,13 @@
         </is>
       </c>
       <c r="N203">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O203">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P203">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q203">
         <v>0</v>
@@ -33502,7 +33502,7 @@
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>2026-08-08 23:00:00</t>
+          <t>2026-08-08 21:45:00</t>
         </is>
       </c>
     </row>
@@ -33514,156 +33514,482 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>El Paso Locomotive</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Oakland Roots</t>
+        </is>
+      </c>
+      <c r="G204">
+        <v>0</v>
+      </c>
+      <c r="H204">
+        <v>0</v>
+      </c>
+      <c r="I204">
+        <v>0</v>
+      </c>
+      <c r="J204">
+        <v>0</v>
+      </c>
+      <c r="K204">
+        <v>0</v>
+      </c>
+      <c r="L204">
+        <v>0</v>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N204">
+        <v>0</v>
+      </c>
+      <c r="O204">
+        <v>0</v>
+      </c>
+      <c r="P204">
+        <v>0</v>
+      </c>
+      <c r="Q204">
+        <v>0</v>
+      </c>
+      <c r="R204">
+        <v>0</v>
+      </c>
+      <c r="S204">
+        <v>0</v>
+      </c>
+      <c r="T204">
+        <v>0</v>
+      </c>
+      <c r="U204">
+        <v>0</v>
+      </c>
+      <c r="V204">
+        <v>0</v>
+      </c>
+      <c r="W204">
+        <v>0</v>
+      </c>
+      <c r="X204">
+        <v>0</v>
+      </c>
+      <c r="Y204">
+        <v>0</v>
+      </c>
+      <c r="Z204">
+        <v>0</v>
+      </c>
+      <c r="AA204">
+        <v>0</v>
+      </c>
+      <c r="AB204">
+        <v>0</v>
+      </c>
+      <c r="AC204">
+        <v>0</v>
+      </c>
+      <c r="AD204">
+        <v>0</v>
+      </c>
+      <c r="AE204">
+        <v>0</v>
+      </c>
+      <c r="AF204">
+        <v>0</v>
+      </c>
+      <c r="AG204">
+        <v>0</v>
+      </c>
+      <c r="AH204" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI204" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ204">
+        <v>0</v>
+      </c>
+      <c r="AK204">
+        <v>0</v>
+      </c>
+      <c r="AL204">
+        <v>0</v>
+      </c>
+      <c r="AM204">
+        <v>-1</v>
+      </c>
+      <c r="AN204">
+        <v>-1</v>
+      </c>
+      <c r="AO204">
+        <v>-1</v>
+      </c>
+      <c r="AP204">
+        <v>-1</v>
+      </c>
+      <c r="AQ204">
+        <v>0</v>
+      </c>
+      <c r="AR204">
+        <v>0</v>
+      </c>
+      <c r="AS204">
+        <v>0</v>
+      </c>
+      <c r="AT204">
+        <v>0</v>
+      </c>
+      <c r="AU204" t="inlineStr">
+        <is>
+          <t>2026-08-08 22:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C204" t="inlineStr">
+      <c r="C205" t="inlineStr">
         <is>
           <t>USA USL Championship</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr">
+      <c r="D205" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr">
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Monterey Bay</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>New Mexico United</t>
+        </is>
+      </c>
+      <c r="G205">
+        <v>0</v>
+      </c>
+      <c r="H205">
+        <v>0</v>
+      </c>
+      <c r="I205">
+        <v>0</v>
+      </c>
+      <c r="J205">
+        <v>0</v>
+      </c>
+      <c r="K205">
+        <v>0</v>
+      </c>
+      <c r="L205">
+        <v>0</v>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N205">
+        <v>0</v>
+      </c>
+      <c r="O205">
+        <v>0</v>
+      </c>
+      <c r="P205">
+        <v>0</v>
+      </c>
+      <c r="Q205">
+        <v>0</v>
+      </c>
+      <c r="R205">
+        <v>0</v>
+      </c>
+      <c r="S205">
+        <v>0</v>
+      </c>
+      <c r="T205">
+        <v>0</v>
+      </c>
+      <c r="U205">
+        <v>0</v>
+      </c>
+      <c r="V205">
+        <v>0</v>
+      </c>
+      <c r="W205">
+        <v>0</v>
+      </c>
+      <c r="X205">
+        <v>0</v>
+      </c>
+      <c r="Y205">
+        <v>0</v>
+      </c>
+      <c r="Z205">
+        <v>0</v>
+      </c>
+      <c r="AA205">
+        <v>0</v>
+      </c>
+      <c r="AB205">
+        <v>0</v>
+      </c>
+      <c r="AC205">
+        <v>0</v>
+      </c>
+      <c r="AD205">
+        <v>0</v>
+      </c>
+      <c r="AE205">
+        <v>0</v>
+      </c>
+      <c r="AF205">
+        <v>0</v>
+      </c>
+      <c r="AG205">
+        <v>0</v>
+      </c>
+      <c r="AH205" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI205" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ205">
+        <v>0</v>
+      </c>
+      <c r="AK205">
+        <v>0</v>
+      </c>
+      <c r="AL205">
+        <v>0</v>
+      </c>
+      <c r="AM205">
+        <v>-1</v>
+      </c>
+      <c r="AN205">
+        <v>-1</v>
+      </c>
+      <c r="AO205">
+        <v>-1</v>
+      </c>
+      <c r="AP205">
+        <v>-1</v>
+      </c>
+      <c r="AQ205">
+        <v>0</v>
+      </c>
+      <c r="AR205">
+        <v>0</v>
+      </c>
+      <c r="AS205">
+        <v>0</v>
+      </c>
+      <c r="AT205">
+        <v>0</v>
+      </c>
+      <c r="AU205" t="inlineStr">
+        <is>
+          <t>2026-08-08 23:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
         <is>
           <t>Orange County SC</t>
         </is>
       </c>
-      <c r="F204" t="inlineStr">
+      <c r="F206" t="inlineStr">
         <is>
           <t>Tampa Bay Rowdies</t>
         </is>
       </c>
-      <c r="G204">
-        <v>0</v>
-      </c>
-      <c r="H204">
-        <v>0</v>
-      </c>
-      <c r="I204">
-        <v>0</v>
-      </c>
-      <c r="J204">
-        <v>0</v>
-      </c>
-      <c r="K204">
-        <v>0</v>
-      </c>
-      <c r="L204">
-        <v>0</v>
-      </c>
-      <c r="M204" t="inlineStr">
+      <c r="G206">
+        <v>0</v>
+      </c>
+      <c r="H206">
+        <v>0</v>
+      </c>
+      <c r="I206">
+        <v>0</v>
+      </c>
+      <c r="J206">
+        <v>0</v>
+      </c>
+      <c r="K206">
+        <v>0</v>
+      </c>
+      <c r="L206">
+        <v>0</v>
+      </c>
+      <c r="M206" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N204">
+      <c r="N206">
         <v>3.79</v>
       </c>
-      <c r="O204">
+      <c r="O206">
         <v>3.5</v>
       </c>
-      <c r="P204">
+      <c r="P206">
         <v>1.82</v>
       </c>
-      <c r="Q204">
-        <v>0</v>
-      </c>
-      <c r="R204">
-        <v>0</v>
-      </c>
-      <c r="S204">
-        <v>0</v>
-      </c>
-      <c r="T204">
-        <v>0</v>
-      </c>
-      <c r="U204">
-        <v>0</v>
-      </c>
-      <c r="V204">
-        <v>0</v>
-      </c>
-      <c r="W204">
-        <v>0</v>
-      </c>
-      <c r="X204">
-        <v>0</v>
-      </c>
-      <c r="Y204">
-        <v>0</v>
-      </c>
-      <c r="Z204">
-        <v>0</v>
-      </c>
-      <c r="AA204">
+      <c r="Q206">
+        <v>0</v>
+      </c>
+      <c r="R206">
+        <v>0</v>
+      </c>
+      <c r="S206">
+        <v>0</v>
+      </c>
+      <c r="T206">
+        <v>0</v>
+      </c>
+      <c r="U206">
+        <v>0</v>
+      </c>
+      <c r="V206">
+        <v>0</v>
+      </c>
+      <c r="W206">
+        <v>0</v>
+      </c>
+      <c r="X206">
+        <v>0</v>
+      </c>
+      <c r="Y206">
+        <v>0</v>
+      </c>
+      <c r="Z206">
+        <v>0</v>
+      </c>
+      <c r="AA206">
         <v>1.81</v>
       </c>
-      <c r="AB204">
+      <c r="AB206">
         <v>1.89</v>
       </c>
-      <c r="AC204">
-        <v>0</v>
-      </c>
-      <c r="AD204">
-        <v>0</v>
-      </c>
-      <c r="AE204">
-        <v>0</v>
-      </c>
-      <c r="AF204">
-        <v>0</v>
-      </c>
-      <c r="AG204">
-        <v>0</v>
-      </c>
-      <c r="AH204" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI204" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ204">
-        <v>0</v>
-      </c>
-      <c r="AK204">
-        <v>0</v>
-      </c>
-      <c r="AL204">
-        <v>0</v>
-      </c>
-      <c r="AM204">
-        <v>-1</v>
-      </c>
-      <c r="AN204">
-        <v>-1</v>
-      </c>
-      <c r="AO204">
-        <v>-1</v>
-      </c>
-      <c r="AP204">
-        <v>-1</v>
-      </c>
-      <c r="AQ204">
-        <v>0</v>
-      </c>
-      <c r="AR204">
-        <v>0</v>
-      </c>
-      <c r="AS204">
-        <v>0</v>
-      </c>
-      <c r="AT204">
-        <v>0</v>
-      </c>
-      <c r="AU204" t="inlineStr">
+      <c r="AC206">
+        <v>0</v>
+      </c>
+      <c r="AD206">
+        <v>0</v>
+      </c>
+      <c r="AE206">
+        <v>0</v>
+      </c>
+      <c r="AF206">
+        <v>0</v>
+      </c>
+      <c r="AG206">
+        <v>0</v>
+      </c>
+      <c r="AH206" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI206" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ206">
+        <v>0</v>
+      </c>
+      <c r="AK206">
+        <v>0</v>
+      </c>
+      <c r="AL206">
+        <v>0</v>
+      </c>
+      <c r="AM206">
+        <v>-1</v>
+      </c>
+      <c r="AN206">
+        <v>-1</v>
+      </c>
+      <c r="AO206">
+        <v>-1</v>
+      </c>
+      <c r="AP206">
+        <v>-1</v>
+      </c>
+      <c r="AQ206">
+        <v>0</v>
+      </c>
+      <c r="AR206">
+        <v>0</v>
+      </c>
+      <c r="AS206">
+        <v>0</v>
+      </c>
+      <c r="AT206">
+        <v>0</v>
+      </c>
+      <c r="AU206" t="inlineStr">
         <is>
           <t>2026-08-08 23:00:00</t>
         </is>

--- a/jogos_2026-08-08.xlsx
+++ b/jogos_2026-08-08.xlsx
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,13 +26226,13 @@
         </is>
       </c>
       <c r="N159">
-        <v>1.76</v>
+        <v>4.55</v>
       </c>
       <c r="O159">
-        <v>3.79</v>
+        <v>3.77</v>
       </c>
       <c r="P159">
-        <v>4.66</v>
+        <v>1.78</v>
       </c>
       <c r="Q159">
         <v>0</v>
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G160">
@@ -26389,13 +26389,13 @@
         </is>
       </c>
       <c r="N160">
-        <v>4.55</v>
+        <v>1.76</v>
       </c>
       <c r="O160">
-        <v>3.77</v>
+        <v>3.79</v>
       </c>
       <c r="P160">
-        <v>1.78</v>
+        <v>4.66</v>
       </c>
       <c r="Q160">
         <v>0</v>

--- a/jogos_2026-08-08.xlsx
+++ b/jogos_2026-08-08.xlsx
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -4912,10 +4912,10 @@
         <v>0</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="O29">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="P29">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5075,10 +5075,10 @@
         <v>0</v>
       </c>
       <c r="AA29">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB29">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC29">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O102">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P102">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G103">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O104">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P104">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G151">
@@ -24922,13 +24922,13 @@
         </is>
       </c>
       <c r="N151">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="O151">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="P151">
-        <v>4.03</v>
+        <v>4.08</v>
       </c>
       <c r="Q151">
         <v>0</v>
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,13 +25085,13 @@
         </is>
       </c>
       <c r="N152">
-        <v>1.99</v>
+        <v>1.72</v>
       </c>
       <c r="O152">
-        <v>3.54</v>
+        <v>3.64</v>
       </c>
       <c r="P152">
-        <v>3.54</v>
+        <v>4.75</v>
       </c>
       <c r="Q152">
         <v>0</v>
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,13 +25248,13 @@
         </is>
       </c>
       <c r="N153">
-        <v>1.82</v>
+        <v>2.47</v>
       </c>
       <c r="O153">
-        <v>3.68</v>
+        <v>3.3</v>
       </c>
       <c r="P153">
-        <v>4.08</v>
+        <v>2.74</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="N154">
-        <v>2.38</v>
+        <v>4.08</v>
       </c>
       <c r="O154">
-        <v>3.46</v>
+        <v>3.58</v>
       </c>
       <c r="P154">
-        <v>2.75</v>
+        <v>1.84</v>
       </c>
       <c r="Q154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,13 +25574,13 @@
         </is>
       </c>
       <c r="N155">
-        <v>1.72</v>
+        <v>4.18</v>
       </c>
       <c r="O155">
-        <v>3.64</v>
+        <v>3.52</v>
       </c>
       <c r="P155">
-        <v>4.75</v>
+        <v>1.84</v>
       </c>
       <c r="Q155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,13 +25737,13 @@
         </is>
       </c>
       <c r="N156">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="O156">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="P156">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="Q156">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,13 +25900,13 @@
         </is>
       </c>
       <c r="N157">
-        <v>4.18</v>
+        <v>1.99</v>
       </c>
       <c r="O157">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="P157">
-        <v>1.84</v>
+        <v>3.54</v>
       </c>
       <c r="Q157">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,13 +26063,13 @@
         </is>
       </c>
       <c r="N158">
-        <v>4.08</v>
+        <v>1.85</v>
       </c>
       <c r="O158">
         <v>3.58</v>
       </c>
       <c r="P158">
-        <v>1.84</v>
+        <v>4.03</v>
       </c>
       <c r="Q158">
         <v>0</v>

--- a/jogos_2026-08-08.xlsx
+++ b/jogos_2026-08-08.xlsx
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4749,10 +4749,10 @@
         <v>0</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC27">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5075,10 +5075,10 @@
         <v>0</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC29">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O76">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -12736,10 +12736,10 @@
         <v>0</v>
       </c>
       <c r="AA76">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB76">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC76">
         <v>0</v>
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q82">
         <v>0</v>
@@ -13714,10 +13714,10 @@
         <v>0</v>
       </c>
       <c r="AA82">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB82">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC82">
         <v>0</v>
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O83">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q83">
         <v>0</v>
@@ -13877,10 +13877,10 @@
         <v>0</v>
       </c>
       <c r="AA83">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB83">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC83">
         <v>0</v>
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O98">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q98">
         <v>0</v>
@@ -16322,10 +16322,10 @@
         <v>0</v>
       </c>
       <c r="AA98">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB98">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC98">
         <v>0</v>
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O104">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P104">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -17300,10 +17300,10 @@
         <v>0</v>
       </c>
       <c r="AA104">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB104">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC104">
         <v>0</v>
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O118">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P118">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q118">
         <v>0</v>
@@ -19582,10 +19582,10 @@
         <v>0</v>
       </c>
       <c r="AA118">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB118">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC118">
         <v>0</v>
@@ -23944,13 +23944,13 @@
         </is>
       </c>
       <c r="N145">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O145">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P145">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q145">
         <v>0</v>
@@ -23983,10 +23983,10 @@
         <v>0</v>
       </c>
       <c r="AA145">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB145">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC145">
         <v>0</v>
@@ -24107,13 +24107,13 @@
         </is>
       </c>
       <c r="N146">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O146">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P146">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="Q146">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,13 +25900,13 @@
         </is>
       </c>
       <c r="N157">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="O157">
-        <v>3.54</v>
+        <v>3.58</v>
       </c>
       <c r="P157">
-        <v>3.54</v>
+        <v>4.03</v>
       </c>
       <c r="Q157">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,13 +26063,13 @@
         </is>
       </c>
       <c r="N158">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="O158">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="P158">
-        <v>4.03</v>
+        <v>3.54</v>
       </c>
       <c r="Q158">
         <v>0</v>

--- a/jogos_2026-08-08.xlsx
+++ b/jogos_2026-08-08.xlsx
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>7.9</v>
+        <v>1.93</v>
       </c>
       <c r="O70">
-        <v>5.05</v>
+        <v>3.64</v>
       </c>
       <c r="P70">
-        <v>1.29</v>
+        <v>3.26</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -11758,10 +11758,10 @@
         <v>0</v>
       </c>
       <c r="AA70">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.93</v>
+        <v>1.59</v>
       </c>
       <c r="O71">
-        <v>3.64</v>
+        <v>3.82</v>
       </c>
       <c r="P71">
-        <v>3.26</v>
+        <v>4.81</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -11921,10 +11921,10 @@
         <v>0</v>
       </c>
       <c r="AA71">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AB71">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AC71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.59</v>
+        <v>7.9</v>
       </c>
       <c r="O72">
-        <v>3.82</v>
+        <v>5.05</v>
       </c>
       <c r="P72">
-        <v>4.81</v>
+        <v>1.29</v>
       </c>
       <c r="Q72">
         <v>0</v>
@@ -12084,10 +12084,10 @@
         <v>0</v>
       </c>
       <c r="AA72">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB72">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC72">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,13 +25900,13 @@
         </is>
       </c>
       <c r="N157">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="O157">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="P157">
-        <v>4.03</v>
+        <v>3.54</v>
       </c>
       <c r="Q157">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,13 +26063,13 @@
         </is>
       </c>
       <c r="N158">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="O158">
-        <v>3.54</v>
+        <v>3.58</v>
       </c>
       <c r="P158">
-        <v>3.54</v>
+        <v>4.03</v>
       </c>
       <c r="Q158">
         <v>0</v>

--- a/jogos_2026-08-08.xlsx
+++ b/jogos_2026-08-08.xlsx
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6216,10 +6216,10 @@
         <v>0</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC36">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>5.86</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6379,10 +6379,10 @@
         <v>0</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC37">
         <v>0</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6548,10 +6548,10 @@
         <v>0</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE38">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -6711,10 +6711,10 @@
         <v>0</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE39">
         <v>0</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9476,10 +9476,10 @@
         <v>0</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC56">
         <v>0</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>5.76</v>
       </c>
       <c r="Q90">
         <v>0</v>
@@ -15024,10 +15024,10 @@
         <v>0</v>
       </c>
       <c r="AC90">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD90">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE90">
         <v>0</v>
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="O103">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17137,10 +17137,10 @@
         <v>0</v>
       </c>
       <c r="AA103">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB103">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC103">
         <v>0</v>
@@ -20358,13 +20358,13 @@
         </is>
       </c>
       <c r="N123">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O123">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="P123">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="Q123">
         <v>0</v>
@@ -20397,10 +20397,10 @@
         <v>0</v>
       </c>
       <c r="AA123">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB123">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC123">
         <v>0</v>
@@ -23129,13 +23129,13 @@
         </is>
       </c>
       <c r="N140">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="O140">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="P140">
-        <v>0</v>
+        <v>13.9</v>
       </c>
       <c r="Q140">
         <v>0</v>
@@ -23180,7 +23180,7 @@
         <v>0</v>
       </c>
       <c r="AE140">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF140">
         <v>0</v>
@@ -23781,13 +23781,13 @@
         </is>
       </c>
       <c r="N144">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O144">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P144">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q144">
         <v>0</v>
@@ -24270,13 +24270,13 @@
         </is>
       </c>
       <c r="N147">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O147">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="P147">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="Q147">
         <v>0</v>
@@ -24315,10 +24315,10 @@
         <v>0</v>
       </c>
       <c r="AC147">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD147">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE147">
         <v>0</v>
@@ -27856,13 +27856,13 @@
         </is>
       </c>
       <c r="N169">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O169">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="P169">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="Q169">
         <v>0</v>
@@ -27901,10 +27901,10 @@
         <v>0</v>
       </c>
       <c r="AC169">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD169">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE169">
         <v>0</v>

--- a/jogos_2026-08-08.xlsx
+++ b/jogos_2026-08-08.xlsx
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.12</v>
+        <v>1.5</v>
       </c>
       <c r="O36">
-        <v>3.58</v>
+        <v>4.35</v>
       </c>
       <c r="P36">
-        <v>3.16</v>
+        <v>5.86</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6216,10 +6216,10 @@
         <v>0</v>
       </c>
       <c r="AA36">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AB36">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.5</v>
+        <v>2.12</v>
       </c>
       <c r="O37">
-        <v>4.35</v>
+        <v>3.58</v>
       </c>
       <c r="P37">
-        <v>5.86</v>
+        <v>3.16</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6379,10 +6379,10 @@
         <v>0</v>
       </c>
       <c r="AA37">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AB37">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC37">
         <v>0</v>
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O114">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P114">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Q114">
         <v>0</v>
@@ -20032,13 +20032,13 @@
         </is>
       </c>
       <c r="N121">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O121">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P121">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Q121">
         <v>0</v>
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G150">
@@ -24759,13 +24759,13 @@
         </is>
       </c>
       <c r="N150">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="O150">
         <v>3.58</v>
       </c>
       <c r="P150">
-        <v>5.28</v>
+        <v>4.03</v>
       </c>
       <c r="Q150">
         <v>0</v>
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G151">
@@ -24922,13 +24922,13 @@
         </is>
       </c>
       <c r="N151">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="O151">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="P151">
-        <v>4.08</v>
+        <v>5.28</v>
       </c>
       <c r="Q151">
         <v>0</v>
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,13 +25085,13 @@
         </is>
       </c>
       <c r="N152">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="O152">
-        <v>3.64</v>
+        <v>3.68</v>
       </c>
       <c r="P152">
-        <v>4.75</v>
+        <v>4.08</v>
       </c>
       <c r="Q152">
         <v>0</v>
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,13 +25248,13 @@
         </is>
       </c>
       <c r="N153">
-        <v>2.47</v>
+        <v>1.72</v>
       </c>
       <c r="O153">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="P153">
-        <v>2.74</v>
+        <v>4.75</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="N154">
-        <v>4.08</v>
+        <v>2.47</v>
       </c>
       <c r="O154">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="P154">
-        <v>1.84</v>
+        <v>2.74</v>
       </c>
       <c r="Q154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,10 +25574,10 @@
         </is>
       </c>
       <c r="N155">
-        <v>4.18</v>
+        <v>4.08</v>
       </c>
       <c r="O155">
-        <v>3.52</v>
+        <v>3.58</v>
       </c>
       <c r="P155">
         <v>1.84</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,13 +25737,13 @@
         </is>
       </c>
       <c r="N156">
-        <v>2.38</v>
+        <v>4.18</v>
       </c>
       <c r="O156">
-        <v>3.46</v>
+        <v>3.52</v>
       </c>
       <c r="P156">
-        <v>2.75</v>
+        <v>1.84</v>
       </c>
       <c r="Q156">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,13 +25900,13 @@
         </is>
       </c>
       <c r="N157">
-        <v>1.99</v>
+        <v>2.38</v>
       </c>
       <c r="O157">
-        <v>3.54</v>
+        <v>3.46</v>
       </c>
       <c r="P157">
-        <v>3.54</v>
+        <v>2.75</v>
       </c>
       <c r="Q157">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,13 +26063,13 @@
         </is>
       </c>
       <c r="N158">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="O158">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="P158">
-        <v>4.03</v>
+        <v>3.54</v>
       </c>
       <c r="Q158">
         <v>0</v>

--- a/jogos_2026-08-08.xlsx
+++ b/jogos_2026-08-08.xlsx
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3608,10 +3608,10 @@
         <v>0</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC20">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -3934,10 +3934,10 @@
         <v>0</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC22">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>5.89</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -4097,10 +4097,10 @@
         <v>0</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC23">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>6.29</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -10750,55 +10750,55 @@
         <v>3.41</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T64">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U64">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V64">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W64">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X64">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z64">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC64">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD64">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE64">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF64">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG64">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK64">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10913,55 +10913,55 @@
         <v>0</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T65">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U65">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W65">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD65">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE65">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK65">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O67">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O69">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11595,10 +11595,10 @@
         <v>0</v>
       </c>
       <c r="AA69">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.93</v>
+        <v>1.31</v>
       </c>
       <c r="O70">
-        <v>3.64</v>
+        <v>4.85</v>
       </c>
       <c r="P70">
-        <v>3.26</v>
+        <v>7.65</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -11758,10 +11758,10 @@
         <v>0</v>
       </c>
       <c r="AA70">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB70">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC70">
         <v>0</v>
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="O74">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -12410,10 +12410,10 @@
         <v>0</v>
       </c>
       <c r="AA74">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB74">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC74">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G77">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G78">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G79">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O84">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S84">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T84">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U84">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="V84">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W84">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X84">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y84">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z84">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="AA84">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC84">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD84">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE84">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF84">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG84">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK84">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O88">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q88">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R88">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S88">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T88">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U88">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V88">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W88">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X88">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y88">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z88">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA88">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB88">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC88">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD88">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE88">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF88">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG88">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK88">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14988,40 +14988,40 @@
         <v>5.76</v>
       </c>
       <c r="Q90">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="S90">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T90">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="U90">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V90">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W90">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X90">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y90">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z90">
-        <v>0</v>
+        <v>6.07</v>
       </c>
       <c r="AA90">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB90">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AC90">
         <v>1.95</v>
@@ -15030,13 +15030,13 @@
         <v>1.73</v>
       </c>
       <c r="AE90">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF90">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG90">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK90">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O91">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q91">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R91">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S91">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T91">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U91">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V91">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W91">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X91">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y91">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z91">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA91">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB91">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AC91">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AD91">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE91">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF91">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG91">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK91">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -17922,55 +17922,55 @@
         <v>4</v>
       </c>
       <c r="Q108">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="R108">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S108">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T108">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U108">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V108">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W108">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X108">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y108">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z108">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA108">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB108">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC108">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD108">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE108">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF108">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG108">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK108">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="O115">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="P115">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -19552,34 +19552,34 @@
         <v>1.9</v>
       </c>
       <c r="Q118">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R118">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S118">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T118">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U118">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V118">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W118">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X118">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y118">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z118">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA118">
         <v>1.84</v>
@@ -19588,19 +19588,19 @@
         <v>1.83</v>
       </c>
       <c r="AC118">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD118">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE118">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF118">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG118">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK118">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -21010,13 +21010,13 @@
         </is>
       </c>
       <c r="N127">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O127">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P127">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="Q127">
         <v>0</v>
@@ -23618,13 +23618,13 @@
         </is>
       </c>
       <c r="N143">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O143">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P143">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -32583,13 +32583,13 @@
         </is>
       </c>
       <c r="N198">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="O198">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="P198">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Q198">
         <v>0</v>
@@ -33561,13 +33561,13 @@
         </is>
       </c>
       <c r="N204">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O204">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P204">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Q204">
         <v>0</v>

--- a/jogos_2026-08-08.xlsx
+++ b/jogos_2026-08-08.xlsx
@@ -1785,55 +1785,55 @@
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.46</v>
+        <v>4.02</v>
       </c>
       <c r="O19">
-        <v>3.13</v>
+        <v>3.28</v>
       </c>
       <c r="P19">
-        <v>3.11</v>
+        <v>2.03</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3578,34 +3578,34 @@
         <v>3.46</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA20">
         <v>1.84</v>
@@ -3614,19 +3614,19 @@
         <v>1.89</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>4.02</v>
+        <v>1.9</v>
       </c>
       <c r="O21">
-        <v>3.28</v>
+        <v>3.77</v>
       </c>
       <c r="P21">
-        <v>2.03</v>
+        <v>3.93</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.9</v>
+        <v>2.46</v>
       </c>
       <c r="O22">
-        <v>3.77</v>
+        <v>3.13</v>
       </c>
       <c r="P22">
-        <v>3.93</v>
+        <v>3.11</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AA22">
-        <v>1.75</v>
+        <v>2.32</v>
       </c>
       <c r="AB22">
-        <v>1.96</v>
+        <v>1.62</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4067,34 +4067,34 @@
         <v>5.89</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AA23">
         <v>2</v>
@@ -4103,19 +4103,19 @@
         <v>1.81</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4230,55 +4230,55 @@
         <v>6.29</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.75</v>
+        <v>3.81</v>
       </c>
       <c r="O25">
-        <v>3.22</v>
+        <v>3.52</v>
       </c>
       <c r="P25">
-        <v>2.51</v>
+        <v>1.92</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.95</v>
+        <v>2.67</v>
       </c>
       <c r="O26">
         <v>3.22</v>
       </c>
       <c r="P26">
-        <v>4.09</v>
+        <v>2.58</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.78</v>
+        <v>2.75</v>
       </c>
       <c r="O27">
-        <v>3.58</v>
+        <v>3.22</v>
       </c>
       <c r="P27">
-        <v>4.42</v>
+        <v>2.51</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA27">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AB27">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>3.81</v>
+        <v>1.95</v>
       </c>
       <c r="O28">
-        <v>3.52</v>
+        <v>3.22</v>
       </c>
       <c r="P28">
-        <v>1.92</v>
+        <v>4.09</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AA28">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AB28">
-        <v>1.87</v>
+        <v>1.52</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.67</v>
+        <v>1.78</v>
       </c>
       <c r="O29">
-        <v>3.22</v>
+        <v>3.58</v>
       </c>
       <c r="P29">
-        <v>2.58</v>
+        <v>4.42</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA29">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="AB29">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O32">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P32">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5564,10 +5564,10 @@
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB32">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC32">
         <v>0</v>
@@ -5697,55 +5697,55 @@
         <v>1.92</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>5.67</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5860,55 +5860,55 @@
         <v>3.09</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6023,55 +6023,55 @@
         <v>2.6</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
+        <v>2.12</v>
+      </c>
+      <c r="O36">
+        <v>3.58</v>
+      </c>
+      <c r="P36">
+        <v>3.16</v>
+      </c>
+      <c r="Q36">
+        <v>2.6</v>
+      </c>
+      <c r="R36">
+        <v>2.25</v>
+      </c>
+      <c r="S36">
+        <v>1.3</v>
+      </c>
+      <c r="T36">
+        <v>3.3</v>
+      </c>
+      <c r="U36">
+        <v>2.35</v>
+      </c>
+      <c r="V36">
+        <v>1.53</v>
+      </c>
+      <c r="W36">
+        <v>1.15</v>
+      </c>
+      <c r="X36">
+        <v>1.03</v>
+      </c>
+      <c r="Y36">
+        <v>1.18</v>
+      </c>
+      <c r="Z36">
+        <v>4.89</v>
+      </c>
+      <c r="AA36">
+        <v>1.58</v>
+      </c>
+      <c r="AB36">
+        <v>2.2</v>
+      </c>
+      <c r="AC36">
+        <v>2.29</v>
+      </c>
+      <c r="AD36">
         <v>1.5</v>
       </c>
-      <c r="O36">
-        <v>4.35</v>
-      </c>
-      <c r="P36">
-        <v>5.86</v>
-      </c>
-      <c r="Q36">
-        <v>0</v>
-      </c>
-      <c r="R36">
-        <v>0</v>
-      </c>
-      <c r="S36">
-        <v>0</v>
-      </c>
-      <c r="T36">
-        <v>0</v>
-      </c>
-      <c r="U36">
-        <v>0</v>
-      </c>
-      <c r="V36">
-        <v>0</v>
-      </c>
-      <c r="W36">
-        <v>0</v>
-      </c>
-      <c r="X36">
-        <v>0</v>
-      </c>
-      <c r="Y36">
-        <v>0</v>
-      </c>
-      <c r="Z36">
-        <v>0</v>
-      </c>
-      <c r="AA36">
-        <v>1.65</v>
-      </c>
-      <c r="AB36">
-        <v>2.1</v>
-      </c>
-      <c r="AC36">
-        <v>0</v>
-      </c>
-      <c r="AD36">
-        <v>0</v>
-      </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,65 +6340,65 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.12</v>
+        <v>1.72</v>
       </c>
       <c r="O37">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="P37">
-        <v>3.16</v>
+        <v>4.26</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA37">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AB37">
+        <v>2.09</v>
+      </c>
+      <c r="AC37">
+        <v>2.25</v>
+      </c>
+      <c r="AD37">
+        <v>1.55</v>
+      </c>
+      <c r="AE37">
+        <v>1.14</v>
+      </c>
+      <c r="AF37">
+        <v>1.61</v>
+      </c>
+      <c r="AG37">
         <v>2.2</v>
       </c>
-      <c r="AC37">
-        <v>0</v>
-      </c>
-      <c r="AD37">
-        <v>0</v>
-      </c>
-      <c r="AE37">
-        <v>0</v>
-      </c>
-      <c r="AF37">
-        <v>0</v>
-      </c>
-      <c r="AG37">
-        <v>0</v>
-      </c>
       <c r="AH37" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="O38">
-        <v>4</v>
+        <v>4.35</v>
       </c>
       <c r="P38">
-        <v>4.26</v>
+        <v>5.86</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC38">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="AD38">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6675,40 +6675,40 @@
         <v>2.72</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC39">
         <v>2.1</v>
@@ -6717,13 +6717,13 @@
         <v>1.63</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G42">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>5.66</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O45">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="P45">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7816,55 +7816,55 @@
         <v>1.96</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>6.08</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="O47">
         <v>3.4</v>
       </c>
       <c r="P47">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="Q47">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="R47">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="S47">
+        <v>1.28</v>
+      </c>
+      <c r="T47">
+        <v>3.18</v>
+      </c>
+      <c r="U47">
+        <v>2.38</v>
+      </c>
+      <c r="V47">
+        <v>1.53</v>
+      </c>
+      <c r="W47">
+        <v>1.08</v>
+      </c>
+      <c r="X47">
+        <v>1.03</v>
+      </c>
+      <c r="Y47">
+        <v>1.16</v>
+      </c>
+      <c r="Z47">
+        <v>4.33</v>
+      </c>
+      <c r="AA47">
+        <v>1.63</v>
+      </c>
+      <c r="AB47">
+        <v>2.14</v>
+      </c>
+      <c r="AC47">
+        <v>2.55</v>
+      </c>
+      <c r="AD47">
+        <v>1.5</v>
+      </c>
+      <c r="AE47">
         <v>1.2</v>
       </c>
-      <c r="T47">
-        <v>3.34</v>
-      </c>
-      <c r="U47">
-        <v>1.94</v>
-      </c>
-      <c r="V47">
-        <v>1.46</v>
-      </c>
-      <c r="W47">
-        <v>1.15</v>
-      </c>
-      <c r="X47">
-        <v>1.01</v>
-      </c>
-      <c r="Y47">
-        <v>1.17</v>
-      </c>
-      <c r="Z47">
-        <v>4.65</v>
-      </c>
-      <c r="AA47">
-        <v>1.57</v>
-      </c>
-      <c r="AB47">
-        <v>2.29</v>
-      </c>
-      <c r="AC47">
-        <v>2.35</v>
-      </c>
-      <c r="AD47">
-        <v>1.47</v>
-      </c>
-      <c r="AE47">
-        <v>1.16</v>
-      </c>
       <c r="AF47">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AG47">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>1.22</v>
       </c>
       <c r="AK47">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.5</v>
+        <v>2.37</v>
       </c>
       <c r="O48">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="P48">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="Q48">
-        <v>1.95</v>
+        <v>2.88</v>
       </c>
       <c r="R48">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="S48">
         <v>1.2</v>
       </c>
       <c r="T48">
-        <v>4</v>
+        <v>3.34</v>
       </c>
       <c r="U48">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="V48">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="W48">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X48">
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="Z48">
-        <v>5.35</v>
+        <v>4.65</v>
       </c>
       <c r="AA48">
+        <v>1.57</v>
+      </c>
+      <c r="AB48">
+        <v>2.29</v>
+      </c>
+      <c r="AC48">
+        <v>2.35</v>
+      </c>
+      <c r="AD48">
+        <v>1.47</v>
+      </c>
+      <c r="AE48">
+        <v>1.16</v>
+      </c>
+      <c r="AF48">
         <v>1.44</v>
       </c>
-      <c r="AB48">
-        <v>2.6</v>
-      </c>
-      <c r="AC48">
-        <v>2.09</v>
-      </c>
-      <c r="AD48">
-        <v>1.66</v>
-      </c>
-      <c r="AE48">
-        <v>1.25</v>
-      </c>
-      <c r="AF48">
-        <v>1.51</v>
-      </c>
       <c r="AG48">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AK48">
-        <v>2.33</v>
+        <v>1.48</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,65 +8296,65 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="O49">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="P49">
-        <v>2.62</v>
+        <v>5</v>
       </c>
       <c r="Q49">
-        <v>2.82</v>
+        <v>1.95</v>
       </c>
       <c r="R49">
-        <v>2.22</v>
+        <v>2.6</v>
       </c>
       <c r="S49">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="T49">
-        <v>3.18</v>
+        <v>4</v>
       </c>
       <c r="U49">
+        <v>2.1</v>
+      </c>
+      <c r="V49">
+        <v>1.65</v>
+      </c>
+      <c r="W49">
+        <v>1.17</v>
+      </c>
+      <c r="X49">
+        <v>1.01</v>
+      </c>
+      <c r="Y49">
+        <v>1.09</v>
+      </c>
+      <c r="Z49">
+        <v>5.35</v>
+      </c>
+      <c r="AA49">
+        <v>1.44</v>
+      </c>
+      <c r="AB49">
+        <v>2.6</v>
+      </c>
+      <c r="AC49">
+        <v>2.09</v>
+      </c>
+      <c r="AD49">
+        <v>1.66</v>
+      </c>
+      <c r="AE49">
+        <v>1.25</v>
+      </c>
+      <c r="AF49">
+        <v>1.51</v>
+      </c>
+      <c r="AG49">
         <v>2.38</v>
       </c>
-      <c r="V49">
-        <v>1.53</v>
-      </c>
-      <c r="W49">
-        <v>1.08</v>
-      </c>
-      <c r="X49">
-        <v>1.03</v>
-      </c>
-      <c r="Y49">
-        <v>1.16</v>
-      </c>
-      <c r="Z49">
-        <v>4.33</v>
-      </c>
-      <c r="AA49">
-        <v>1.63</v>
-      </c>
-      <c r="AB49">
-        <v>2.14</v>
-      </c>
-      <c r="AC49">
-        <v>2.55</v>
-      </c>
-      <c r="AD49">
-        <v>1.5</v>
-      </c>
-      <c r="AE49">
-        <v>1.2</v>
-      </c>
-      <c r="AF49">
-        <v>1.52</v>
-      </c>
-      <c r="AG49">
-        <v>2.3</v>
-      </c>
       <c r="AH49" t="inlineStr">
         <is>
           <t>[]</t>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK49">
-        <v>1.53</v>
+        <v>2.33</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8794,40 +8794,40 @@
         <v>1.48</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AC52">
         <v>1.79</v>
@@ -8836,13 +8836,13 @@
         <v>1.96</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9283,55 +9283,55 @@
         <v>2.57</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="T55">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U55">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="V55">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y55">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z55">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA55">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF55">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG55">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AK55">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9446,34 +9446,34 @@
         <v>2.3</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T56">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U56">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="V56">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X56">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y56">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z56">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA56">
         <v>1.87</v>
@@ -9482,19 +9482,19 @@
         <v>1.83</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF56">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG56">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK56">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9609,55 +9609,55 @@
         <v>0</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T57">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U57">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="V57">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W57">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X57">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y57">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z57">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC57">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD57">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE57">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF57">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG57">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK57">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9772,55 +9772,55 @@
         <v>2.35</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T58">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U58">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V58">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W58">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X58">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y58">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z58">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA58">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB58">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC58">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE58">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF58">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG58">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK58">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10261,55 +10261,55 @@
         <v>1.71</v>
       </c>
       <c r="Q61">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T61">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U61">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V61">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W61">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X61">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z61">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA61">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB61">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD61">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE61">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF61">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG61">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AK61">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10424,55 +10424,55 @@
         <v>3.16</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T62">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U62">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V62">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W62">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X62">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z62">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE62">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF62">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG62">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK62">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10587,55 +10587,55 @@
         <v>0</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T63">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF63">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK63">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -11239,55 +11239,55 @@
         <v>3.21</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S67">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T67">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="U67">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V67">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W67">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X67">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y67">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z67">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA67">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC67">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD67">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE67">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF67">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG67">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AK67">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11565,34 +11565,34 @@
         <v>3.26</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S69">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T69">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U69">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V69">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W69">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y69">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z69">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AA69">
         <v>1.81</v>
@@ -11601,19 +11601,19 @@
         <v>1.86</v>
       </c>
       <c r="AC69">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD69">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE69">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF69">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG69">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK69">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11728,55 +11728,55 @@
         <v>7.65</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="S70">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T70">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U70">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V70">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W70">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y70">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z70">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA70">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC70">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AD70">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE70">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF70">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG70">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK70">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11891,34 +11891,34 @@
         <v>4.81</v>
       </c>
       <c r="Q71">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R71">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S71">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T71">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U71">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V71">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W71">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y71">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z71">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA71">
         <v>1.77</v>
@@ -11927,19 +11927,19 @@
         <v>1.92</v>
       </c>
       <c r="AC71">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="AD71">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE71">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF71">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG71">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK71">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12054,55 +12054,55 @@
         <v>1.29</v>
       </c>
       <c r="Q72">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R72">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S72">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T72">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U72">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V72">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W72">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X72">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y72">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z72">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA72">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB72">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC72">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD72">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE72">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF72">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG72">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AK72">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>3.55</v>
+        <v>2.51</v>
       </c>
       <c r="O73">
-        <v>3.13</v>
+        <v>3.3</v>
       </c>
       <c r="P73">
-        <v>2.01</v>
+        <v>2.45</v>
       </c>
       <c r="Q73">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R73">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S73">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T73">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U73">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V73">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W73">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X73">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y73">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z73">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA73">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB73">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC73">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD73">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE73">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF73">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG73">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK73">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,65 +12371,65 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.51</v>
+        <v>2.21</v>
       </c>
       <c r="O74">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="P74">
-        <v>2.45</v>
+        <v>3.17</v>
       </c>
       <c r="Q74">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S74">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T74">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U74">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V74">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W74">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X74">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y74">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z74">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA74">
+        <v>1.98</v>
+      </c>
+      <c r="AB74">
+        <v>1.78</v>
+      </c>
+      <c r="AC74">
+        <v>3.14</v>
+      </c>
+      <c r="AD74">
+        <v>1.27</v>
+      </c>
+      <c r="AE74">
+        <v>1.1</v>
+      </c>
+      <c r="AF74">
+        <v>1.73</v>
+      </c>
+      <c r="AG74">
         <v>2</v>
       </c>
-      <c r="AB74">
-        <v>1.68</v>
-      </c>
-      <c r="AC74">
-        <v>0</v>
-      </c>
-      <c r="AD74">
-        <v>0</v>
-      </c>
-      <c r="AE74">
-        <v>0</v>
-      </c>
-      <c r="AF74">
-        <v>0</v>
-      </c>
-      <c r="AG74">
-        <v>0</v>
-      </c>
       <c r="AH74" t="inlineStr">
         <is>
           <t>[]</t>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK74">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.1</v>
+        <v>3.55</v>
       </c>
       <c r="O75">
+        <v>3.13</v>
+      </c>
+      <c r="P75">
+        <v>2.01</v>
+      </c>
+      <c r="Q75">
+        <v>4.18</v>
+      </c>
+      <c r="R75">
+        <v>2.15</v>
+      </c>
+      <c r="S75">
+        <v>1.39</v>
+      </c>
+      <c r="T75">
+        <v>2.85</v>
+      </c>
+      <c r="U75">
+        <v>2.8</v>
+      </c>
+      <c r="V75">
+        <v>1.36</v>
+      </c>
+      <c r="W75">
+        <v>1.03</v>
+      </c>
+      <c r="X75">
+        <v>1.06</v>
+      </c>
+      <c r="Y75">
+        <v>1.31</v>
+      </c>
+      <c r="Z75">
         <v>3.08</v>
       </c>
-      <c r="P75">
-        <v>3.35</v>
-      </c>
-      <c r="Q75">
-        <v>0</v>
-      </c>
-      <c r="R75">
-        <v>0</v>
-      </c>
-      <c r="S75">
-        <v>0</v>
-      </c>
-      <c r="T75">
-        <v>0</v>
-      </c>
-      <c r="U75">
-        <v>0</v>
-      </c>
-      <c r="V75">
-        <v>0</v>
-      </c>
-      <c r="W75">
-        <v>0</v>
-      </c>
-      <c r="X75">
-        <v>0</v>
-      </c>
-      <c r="Y75">
-        <v>0</v>
-      </c>
-      <c r="Z75">
-        <v>0</v>
-      </c>
       <c r="AA75">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB75">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC75">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD75">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE75">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF75">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG75">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK75">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="O76">
+        <v>3.08</v>
+      </c>
+      <c r="P76">
+        <v>3.35</v>
+      </c>
+      <c r="Q76">
+        <v>2.5</v>
+      </c>
+      <c r="R76">
+        <v>1.95</v>
+      </c>
+      <c r="S76">
+        <v>1.44</v>
+      </c>
+      <c r="T76">
+        <v>2.75</v>
+      </c>
+      <c r="U76">
         <v>3.02</v>
       </c>
-      <c r="P76">
-        <v>3.17</v>
-      </c>
-      <c r="Q76">
-        <v>0</v>
-      </c>
-      <c r="R76">
-        <v>0</v>
-      </c>
-      <c r="S76">
-        <v>0</v>
-      </c>
-      <c r="T76">
-        <v>0</v>
-      </c>
-      <c r="U76">
-        <v>0</v>
-      </c>
       <c r="V76">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W76">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X76">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y76">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z76">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA76">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="AB76">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AC76">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD76">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE76">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF76">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG76">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK76">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12869,55 +12869,55 @@
         <v>0</v>
       </c>
       <c r="Q77">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="R77">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S77">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T77">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U77">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="V77">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W77">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X77">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y77">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z77">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA77">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB77">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC77">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD77">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE77">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF77">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG77">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK77">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13032,55 +13032,55 @@
         <v>0</v>
       </c>
       <c r="Q78">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="R78">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S78">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T78">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U78">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V78">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W78">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y78">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z78">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA78">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB78">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC78">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD78">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE78">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF78">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG78">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK78">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13195,55 +13195,55 @@
         <v>0</v>
       </c>
       <c r="Q79">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R79">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S79">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T79">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U79">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="V79">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W79">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X79">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z79">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA79">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC79">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AD79">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE79">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF79">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG79">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK79">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13358,55 +13358,55 @@
         <v>7.55</v>
       </c>
       <c r="Q80">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R80">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S80">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T80">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U80">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V80">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W80">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X80">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y80">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z80">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA80">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB80">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AC80">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD80">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE80">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF80">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG80">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK80">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.16</v>
+        <v>2.48</v>
       </c>
       <c r="O82">
-        <v>3.54</v>
+        <v>3.48</v>
       </c>
       <c r="P82">
-        <v>3.11</v>
+        <v>2.62</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S82">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T82">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U82">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V82">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W82">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X82">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y82">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z82">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA82">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AB82">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AC82">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD82">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG82">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK82">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.48</v>
+        <v>2.16</v>
       </c>
       <c r="O83">
-        <v>3.48</v>
+        <v>3.54</v>
       </c>
       <c r="P83">
-        <v>2.62</v>
+        <v>3.11</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S83">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T83">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="U83">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V83">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W83">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y83">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z83">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="AA83">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AB83">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AC83">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD83">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG83">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK83">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O85">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q85">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R85">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S85">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T85">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U85">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V85">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W85">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X85">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z85">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AA85">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AB85">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC85">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AD85">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE85">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF85">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG85">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK85">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14336,55 +14336,55 @@
         <v>0</v>
       </c>
       <c r="Q86">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S86">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T86">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="U86">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="V86">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W86">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X86">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z86">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA86">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD86">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG86">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK86">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14825,34 +14825,34 @@
         <v>2.48</v>
       </c>
       <c r="Q89">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R89">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S89">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T89">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U89">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V89">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W89">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X89">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z89">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AA89">
         <v>1.91</v>
@@ -14861,19 +14861,19 @@
         <v>1.79</v>
       </c>
       <c r="AC89">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AD89">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE89">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF89">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG89">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK89">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="O95">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P95">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q95">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="R95">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S95">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T95">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U95">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V95">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W95">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X95">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y95">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z95">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA95">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB95">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC95">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD95">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE95">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF95">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG95">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK95">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15966,55 +15966,55 @@
         <v>0</v>
       </c>
       <c r="Q96">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R96">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S96">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T96">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U96">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V96">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W96">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X96">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y96">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z96">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA96">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB96">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC96">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD96">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE96">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF96">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG96">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AK96">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16129,55 +16129,55 @@
         <v>4.05</v>
       </c>
       <c r="Q97">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="R97">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S97">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T97">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U97">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V97">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W97">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X97">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y97">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z97">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA97">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB97">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AC97">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD97">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE97">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF97">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG97">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK97">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16292,34 +16292,34 @@
         <v>2.68</v>
       </c>
       <c r="Q98">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R98">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S98">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T98">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="U98">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V98">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W98">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X98">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y98">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z98">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA98">
         <v>1.93</v>
@@ -16328,19 +16328,19 @@
         <v>1.8</v>
       </c>
       <c r="AC98">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AD98">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE98">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF98">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG98">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK98">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16455,55 +16455,55 @@
         <v>6.51</v>
       </c>
       <c r="Q99">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="R99">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S99">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T99">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="U99">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V99">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W99">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X99">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y99">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z99">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="AA99">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB99">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AC99">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD99">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE99">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF99">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG99">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK99">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16781,55 +16781,55 @@
         <v>0</v>
       </c>
       <c r="Q101">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R101">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S101">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T101">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U101">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V101">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W101">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X101">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y101">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z101">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA101">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AB101">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC101">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD101">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE101">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF101">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG101">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK101">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.05</v>
+        <v>4.68</v>
       </c>
       <c r="O102">
         <v>3.8</v>
       </c>
       <c r="P102">
-        <v>3.11</v>
+        <v>1.67</v>
       </c>
       <c r="Q102">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R102">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S102">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T102">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U102">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="V102">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W102">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X102">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y102">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z102">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA102">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB102">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC102">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD102">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE102">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF102">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG102">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK102">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>4.68</v>
+        <v>2.05</v>
       </c>
       <c r="O103">
         <v>3.8</v>
       </c>
       <c r="P103">
-        <v>1.67</v>
+        <v>3.11</v>
       </c>
       <c r="Q103">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R103">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S103">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T103">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U103">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V103">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W103">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X103">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y103">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z103">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA103">
-        <v>1.87</v>
+        <v>1.44</v>
       </c>
       <c r="AB103">
-        <v>1.79</v>
+        <v>2.43</v>
       </c>
       <c r="AC103">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD103">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE103">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF103">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG103">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK103">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17759,34 +17759,34 @@
         <v>3.4</v>
       </c>
       <c r="Q107">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="R107">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S107">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T107">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U107">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V107">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W107">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X107">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y107">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z107">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AA107">
         <v>1.82</v>
@@ -17795,19 +17795,19 @@
         <v>1.88</v>
       </c>
       <c r="AC107">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AD107">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE107">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF107">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG107">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK107">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -18085,55 +18085,55 @@
         <v>2.17</v>
       </c>
       <c r="Q109">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R109">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S109">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T109">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U109">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V109">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W109">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X109">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y109">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z109">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AA109">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB109">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC109">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD109">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE109">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF109">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG109">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK109">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18574,55 +18574,55 @@
         <v>3.11</v>
       </c>
       <c r="Q112">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R112">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S112">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T112">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U112">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V112">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W112">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X112">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y112">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z112">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA112">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB112">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC112">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AD112">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE112">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF112">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG112">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK112">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -19063,55 +19063,55 @@
         <v>1.42</v>
       </c>
       <c r="Q115">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="R115">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S115">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T115">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U115">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V115">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W115">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y115">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z115">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA115">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB115">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC115">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD115">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE115">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF115">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG115">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK115">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -21049,10 +21049,10 @@
         <v>0</v>
       </c>
       <c r="AA127">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB127">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC127">
         <v>0</v>
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G129">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G130">

--- a/jogos_2026-08-08.xlsx
+++ b/jogos_2026-08-08.xlsx
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.67</v>
+        <v>1.95</v>
       </c>
       <c r="O26">
         <v>3.22</v>
       </c>
       <c r="P26">
-        <v>2.58</v>
+        <v>4.09</v>
       </c>
       <c r="Q26">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="R26">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="S26">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="T26">
-        <v>2.88</v>
+        <v>2.44</v>
       </c>
       <c r="U26">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="V26">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="W26">
+        <v>1.01</v>
+      </c>
+      <c r="X26">
         <v>1.04</v>
       </c>
-      <c r="X26">
+      <c r="Y26">
+        <v>1.42</v>
+      </c>
+      <c r="Z26">
+        <v>2.87</v>
+      </c>
+      <c r="AA26">
+        <v>2.3</v>
+      </c>
+      <c r="AB26">
+        <v>1.52</v>
+      </c>
+      <c r="AC26">
+        <v>4.15</v>
+      </c>
+      <c r="AD26">
+        <v>1.22</v>
+      </c>
+      <c r="AE26">
         <v>1.01</v>
       </c>
-      <c r="Y26">
-        <v>1.27</v>
-      </c>
-      <c r="Z26">
-        <v>3.56</v>
-      </c>
-      <c r="AA26">
-        <v>1.93</v>
-      </c>
-      <c r="AB26">
-        <v>1.8</v>
-      </c>
-      <c r="AC26">
-        <v>3.4</v>
-      </c>
-      <c r="AD26">
-        <v>1.26</v>
-      </c>
-      <c r="AE26">
-        <v>1.06</v>
-      </c>
       <c r="AF26">
-        <v>1.71</v>
+        <v>2.05</v>
       </c>
       <c r="AG26">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AK26">
-        <v>1.39</v>
+        <v>1.75</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,19 +4710,19 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.75</v>
+        <v>1.78</v>
       </c>
       <c r="O27">
-        <v>3.22</v>
+        <v>3.58</v>
       </c>
       <c r="P27">
-        <v>2.51</v>
+        <v>4.42</v>
       </c>
       <c r="Q27">
-        <v>3.25</v>
+        <v>2.36</v>
       </c>
       <c r="R27">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S27">
         <v>1.36</v>
@@ -4731,43 +4731,43 @@
         <v>2.88</v>
       </c>
       <c r="U27">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="V27">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W27">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X27">
         <v>1.06</v>
       </c>
       <c r="Y27">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z27">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="AA27">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AB27">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AC27">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="AD27">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AE27">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF27">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="AG27">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AK27">
-        <v>1.41</v>
+        <v>1.99</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.95</v>
+        <v>2.67</v>
       </c>
       <c r="O28">
         <v>3.22</v>
       </c>
       <c r="P28">
-        <v>4.09</v>
+        <v>2.58</v>
       </c>
       <c r="Q28">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="R28">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="S28">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="T28">
-        <v>2.44</v>
+        <v>2.88</v>
       </c>
       <c r="U28">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="V28">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="W28">
+        <v>1.04</v>
+      </c>
+      <c r="X28">
         <v>1.01</v>
       </c>
-      <c r="X28">
-        <v>1.04</v>
-      </c>
       <c r="Y28">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="Z28">
-        <v>2.87</v>
+        <v>3.56</v>
       </c>
       <c r="AA28">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="AB28">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="AC28">
-        <v>4.15</v>
+        <v>3.4</v>
       </c>
       <c r="AD28">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AE28">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF28">
-        <v>2.05</v>
+        <v>1.71</v>
       </c>
       <c r="AG28">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="AK28">
-        <v>1.75</v>
+        <v>1.39</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,19 +5036,19 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.78</v>
+        <v>2.75</v>
       </c>
       <c r="O29">
-        <v>3.58</v>
+        <v>3.22</v>
       </c>
       <c r="P29">
-        <v>4.42</v>
+        <v>2.51</v>
       </c>
       <c r="Q29">
-        <v>2.36</v>
+        <v>3.25</v>
       </c>
       <c r="R29">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S29">
         <v>1.36</v>
@@ -5057,59 +5057,59 @@
         <v>2.88</v>
       </c>
       <c r="U29">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="V29">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W29">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X29">
         <v>1.06</v>
       </c>
       <c r="Y29">
+        <v>1.28</v>
+      </c>
+      <c r="Z29">
+        <v>3.15</v>
+      </c>
+      <c r="AA29">
+        <v>1.95</v>
+      </c>
+      <c r="AB29">
+        <v>1.73</v>
+      </c>
+      <c r="AC29">
+        <v>3.65</v>
+      </c>
+      <c r="AD29">
+        <v>1.23</v>
+      </c>
+      <c r="AE29">
+        <v>1.08</v>
+      </c>
+      <c r="AF29">
+        <v>1.71</v>
+      </c>
+      <c r="AG29">
+        <v>1.95</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29">
         <v>1.25</v>
       </c>
-      <c r="Z29">
-        <v>3.3</v>
-      </c>
-      <c r="AA29">
-        <v>2.01</v>
-      </c>
-      <c r="AB29">
-        <v>1.81</v>
-      </c>
-      <c r="AC29">
-        <v>3.55</v>
-      </c>
-      <c r="AD29">
-        <v>1.27</v>
-      </c>
-      <c r="AE29">
-        <v>1.07</v>
-      </c>
-      <c r="AF29">
-        <v>1.83</v>
-      </c>
-      <c r="AG29">
-        <v>1.85</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ29">
-        <v>1.12</v>
-      </c>
       <c r="AK29">
-        <v>1.99</v>
+        <v>1.41</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.11</v>
+        <v>2.45</v>
       </c>
       <c r="O34">
-        <v>3.62</v>
+        <v>3.4</v>
       </c>
       <c r="P34">
-        <v>3.09</v>
+        <v>2.6</v>
       </c>
       <c r="Q34">
-        <v>2.6</v>
+        <v>3.13</v>
       </c>
       <c r="R34">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S34">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T34">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="U34">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="V34">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="W34">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="Z34">
-        <v>4.15</v>
+        <v>3.58</v>
       </c>
       <c r="AA34">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AB34">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="AC34">
-        <v>2.52</v>
+        <v>2.96</v>
       </c>
       <c r="AD34">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AE34">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF34">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG34">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="AK34">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.45</v>
+        <v>2.11</v>
       </c>
       <c r="O35">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="P35">
+        <v>3.09</v>
+      </c>
+      <c r="Q35">
         <v>2.6</v>
       </c>
-      <c r="Q35">
-        <v>3.13</v>
-      </c>
       <c r="R35">
+        <v>2.3</v>
+      </c>
+      <c r="S35">
+        <v>1.29</v>
+      </c>
+      <c r="T35">
+        <v>3.6</v>
+      </c>
+      <c r="U35">
         <v>2.25</v>
       </c>
-      <c r="S35">
-        <v>1.3</v>
-      </c>
-      <c r="T35">
-        <v>3.2</v>
-      </c>
-      <c r="U35">
-        <v>2.5</v>
-      </c>
       <c r="V35">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="W35">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X35">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y35">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="Z35">
-        <v>3.58</v>
+        <v>4.15</v>
       </c>
       <c r="AA35">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AB35">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="AC35">
-        <v>2.96</v>
+        <v>2.52</v>
       </c>
       <c r="AD35">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AE35">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF35">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG35">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="AK35">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="O37">
-        <v>4</v>
+        <v>4.35</v>
       </c>
       <c r="P37">
-        <v>4.26</v>
+        <v>5.86</v>
       </c>
       <c r="Q37">
-        <v>2.27</v>
+        <v>2.1</v>
       </c>
       <c r="R37">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S37">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T37">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="U37">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="V37">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="W37">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X37">
         <v>1.04</v>
       </c>
       <c r="Y37">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z37">
-        <v>4.4</v>
+        <v>4.15</v>
       </c>
       <c r="AA37">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AB37">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AC37">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="AD37">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AE37">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF37">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AG37">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK37">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="O38">
-        <v>4.35</v>
+        <v>4</v>
       </c>
       <c r="P38">
-        <v>5.86</v>
+        <v>4.26</v>
       </c>
       <c r="Q38">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="R38">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="S38">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T38">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="U38">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="V38">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="W38">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X38">
         <v>1.04</v>
       </c>
       <c r="Y38">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z38">
-        <v>4.15</v>
+        <v>4.4</v>
       </c>
       <c r="AA38">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AB38">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AC38">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="AD38">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AE38">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF38">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AG38">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK38">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="AL38">
         <v>0</v>

--- a/jogos_2026-08-08.xlsx
+++ b/jogos_2026-08-08.xlsx
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.45</v>
+        <v>2.11</v>
       </c>
       <c r="O34">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="P34">
+        <v>3.09</v>
+      </c>
+      <c r="Q34">
         <v>2.6</v>
       </c>
-      <c r="Q34">
-        <v>3.13</v>
-      </c>
       <c r="R34">
+        <v>2.3</v>
+      </c>
+      <c r="S34">
+        <v>1.29</v>
+      </c>
+      <c r="T34">
+        <v>3.6</v>
+      </c>
+      <c r="U34">
         <v>2.25</v>
       </c>
-      <c r="S34">
-        <v>1.3</v>
-      </c>
-      <c r="T34">
-        <v>3.2</v>
-      </c>
-      <c r="U34">
-        <v>2.5</v>
-      </c>
       <c r="V34">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="W34">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X34">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="Z34">
-        <v>3.58</v>
+        <v>4.15</v>
       </c>
       <c r="AA34">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AB34">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="AC34">
-        <v>2.96</v>
+        <v>2.52</v>
       </c>
       <c r="AD34">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AE34">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF34">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG34">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="AK34">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.11</v>
+        <v>2.45</v>
       </c>
       <c r="O35">
-        <v>3.62</v>
+        <v>3.4</v>
       </c>
       <c r="P35">
-        <v>3.09</v>
+        <v>2.6</v>
       </c>
       <c r="Q35">
-        <v>2.6</v>
+        <v>3.13</v>
       </c>
       <c r="R35">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S35">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T35">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="U35">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="V35">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="W35">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="Z35">
-        <v>4.15</v>
+        <v>3.58</v>
       </c>
       <c r="AA35">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AB35">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="AC35">
-        <v>2.52</v>
+        <v>2.96</v>
       </c>
       <c r="AD35">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AE35">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF35">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG35">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="AK35">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AL35">
         <v>0</v>

--- a/jogos_2026-08-08.xlsx
+++ b/jogos_2026-08-08.xlsx
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="O26">
-        <v>3.22</v>
+        <v>3.58</v>
       </c>
       <c r="P26">
-        <v>4.09</v>
+        <v>4.42</v>
       </c>
       <c r="Q26">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="R26">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="S26">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="T26">
-        <v>2.44</v>
+        <v>2.88</v>
       </c>
       <c r="U26">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="V26">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="W26">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X26">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y26">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="Z26">
-        <v>2.87</v>
+        <v>3.3</v>
       </c>
       <c r="AA26">
-        <v>2.3</v>
+        <v>2.01</v>
       </c>
       <c r="AB26">
-        <v>1.52</v>
+        <v>1.81</v>
       </c>
       <c r="AC26">
-        <v>4.15</v>
+        <v>3.55</v>
       </c>
       <c r="AD26">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AE26">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AF26">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AG26">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="AK26">
-        <v>1.75</v>
+        <v>1.99</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,61 +4710,61 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.78</v>
+        <v>2.67</v>
       </c>
       <c r="O27">
-        <v>3.58</v>
+        <v>3.22</v>
       </c>
       <c r="P27">
-        <v>4.42</v>
+        <v>2.58</v>
       </c>
       <c r="Q27">
-        <v>2.36</v>
+        <v>3.1</v>
       </c>
       <c r="R27">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="S27">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T27">
         <v>2.88</v>
       </c>
       <c r="U27">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="V27">
         <v>1.36</v>
       </c>
       <c r="W27">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X27">
+        <v>1.01</v>
+      </c>
+      <c r="Y27">
+        <v>1.27</v>
+      </c>
+      <c r="Z27">
+        <v>3.56</v>
+      </c>
+      <c r="AA27">
+        <v>1.93</v>
+      </c>
+      <c r="AB27">
+        <v>1.8</v>
+      </c>
+      <c r="AC27">
+        <v>3.4</v>
+      </c>
+      <c r="AD27">
+        <v>1.26</v>
+      </c>
+      <c r="AE27">
         <v>1.06</v>
       </c>
-      <c r="Y27">
-        <v>1.25</v>
-      </c>
-      <c r="Z27">
-        <v>3.3</v>
-      </c>
-      <c r="AA27">
-        <v>2.01</v>
-      </c>
-      <c r="AB27">
-        <v>1.81</v>
-      </c>
-      <c r="AC27">
-        <v>3.55</v>
-      </c>
-      <c r="AD27">
-        <v>1.27</v>
-      </c>
-      <c r="AE27">
-        <v>1.07</v>
-      </c>
       <c r="AF27">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AG27">
         <v>1.85</v>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.12</v>
+        <v>1.32</v>
       </c>
       <c r="AK27">
-        <v>1.99</v>
+        <v>1.39</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.67</v>
+        <v>1.95</v>
       </c>
       <c r="O28">
         <v>3.22</v>
       </c>
       <c r="P28">
-        <v>2.58</v>
+        <v>4.09</v>
       </c>
       <c r="Q28">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="R28">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="S28">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="T28">
-        <v>2.88</v>
+        <v>2.44</v>
       </c>
       <c r="U28">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="V28">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="W28">
+        <v>1.01</v>
+      </c>
+      <c r="X28">
         <v>1.04</v>
       </c>
-      <c r="X28">
+      <c r="Y28">
+        <v>1.42</v>
+      </c>
+      <c r="Z28">
+        <v>2.87</v>
+      </c>
+      <c r="AA28">
+        <v>2.3</v>
+      </c>
+      <c r="AB28">
+        <v>1.52</v>
+      </c>
+      <c r="AC28">
+        <v>4.15</v>
+      </c>
+      <c r="AD28">
+        <v>1.22</v>
+      </c>
+      <c r="AE28">
         <v>1.01</v>
       </c>
-      <c r="Y28">
-        <v>1.27</v>
-      </c>
-      <c r="Z28">
-        <v>3.56</v>
-      </c>
-      <c r="AA28">
-        <v>1.93</v>
-      </c>
-      <c r="AB28">
-        <v>1.8</v>
-      </c>
-      <c r="AC28">
-        <v>3.4</v>
-      </c>
-      <c r="AD28">
-        <v>1.26</v>
-      </c>
-      <c r="AE28">
-        <v>1.06</v>
-      </c>
       <c r="AF28">
-        <v>1.71</v>
+        <v>2.05</v>
       </c>
       <c r="AG28">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AK28">
-        <v>1.39</v>
+        <v>1.75</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,22 +7481,22 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O44">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="P44">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="Q44">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="R44">
-        <v>2.49</v>
+        <v>2.56</v>
       </c>
       <c r="S44">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="T44">
         <v>4</v>
@@ -7505,7 +7505,7 @@
         <v>2.05</v>
       </c>
       <c r="V44">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="W44">
         <v>1.17</v>
@@ -7514,31 +7514,31 @@
         <v>1.02</v>
       </c>
       <c r="Y44">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Z44">
-        <v>5.66</v>
+        <v>5.85</v>
       </c>
       <c r="AA44">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AB44">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AC44">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AD44">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AE44">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AF44">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AG44">
-        <v>2.51</v>
+        <v>2.46</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK44">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,22 +7644,22 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="Q45">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="R45">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="S45">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="T45">
         <v>4</v>
@@ -7668,7 +7668,7 @@
         <v>2.05</v>
       </c>
       <c r="V45">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="W45">
         <v>1.17</v>
@@ -7677,31 +7677,31 @@
         <v>1.02</v>
       </c>
       <c r="Y45">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Z45">
-        <v>5.85</v>
+        <v>5.66</v>
       </c>
       <c r="AA45">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AB45">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AC45">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AD45">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AE45">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AF45">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AG45">
-        <v>2.46</v>
+        <v>2.51</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK45">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -10587,31 +10587,31 @@
         <v>0</v>
       </c>
       <c r="Q63">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="R63">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="S63">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T63">
+        <v>2.45</v>
+      </c>
+      <c r="U63">
         <v>2.5</v>
       </c>
-      <c r="U63">
-        <v>3.1</v>
-      </c>
       <c r="V63">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="W63">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X63">
         <v>1.06</v>
       </c>
       <c r="Y63">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="Z63">
         <v>3.5</v>
@@ -10620,22 +10620,22 @@
         <v>2.23</v>
       </c>
       <c r="AB63">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="AC63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD63">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AE63">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF63">
-        <v>2.08</v>
+        <v>1.72</v>
       </c>
       <c r="AG63">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK63">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -11076,55 +11076,55 @@
         <v>0</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S66">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T66">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U66">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="V66">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W66">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X66">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z66">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA66">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB66">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC66">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AD66">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE66">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF66">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG66">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK66">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,80 +13675,80 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.48</v>
+        <v>2.16</v>
       </c>
       <c r="O82">
-        <v>3.48</v>
+        <v>3.54</v>
       </c>
       <c r="P82">
-        <v>2.62</v>
+        <v>3.11</v>
       </c>
       <c r="Q82">
-        <v>2.9</v>
+        <v>2.72</v>
       </c>
       <c r="R82">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="S82">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T82">
-        <v>3.02</v>
+        <v>3.06</v>
       </c>
       <c r="U82">
-        <v>2.62</v>
+        <v>2.81</v>
       </c>
       <c r="V82">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W82">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X82">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y82">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z82">
-        <v>3.62</v>
+        <v>3.66</v>
       </c>
       <c r="AA82">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AB82">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AC82">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="AD82">
+        <v>1.29</v>
+      </c>
+      <c r="AE82">
+        <v>1.12</v>
+      </c>
+      <c r="AF82">
+        <v>1.67</v>
+      </c>
+      <c r="AG82">
+        <v>2.05</v>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ82">
         <v>1.36</v>
       </c>
-      <c r="AE82">
-        <v>1.13</v>
-      </c>
-      <c r="AF82">
-        <v>1.62</v>
-      </c>
-      <c r="AG82">
-        <v>2.14</v>
-      </c>
-      <c r="AH82" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI82" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ82">
-        <v>1.3</v>
-      </c>
       <c r="AK82">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.16</v>
+        <v>2.48</v>
       </c>
       <c r="O83">
-        <v>3.54</v>
+        <v>3.48</v>
       </c>
       <c r="P83">
-        <v>3.11</v>
+        <v>2.62</v>
       </c>
       <c r="Q83">
-        <v>2.72</v>
+        <v>2.9</v>
       </c>
       <c r="R83">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="S83">
+        <v>1.33</v>
+      </c>
+      <c r="T83">
+        <v>3.02</v>
+      </c>
+      <c r="U83">
+        <v>2.62</v>
+      </c>
+      <c r="V83">
+        <v>1.43</v>
+      </c>
+      <c r="W83">
+        <v>1.06</v>
+      </c>
+      <c r="X83">
+        <v>1.04</v>
+      </c>
+      <c r="Y83">
+        <v>1.25</v>
+      </c>
+      <c r="Z83">
+        <v>3.62</v>
+      </c>
+      <c r="AA83">
+        <v>1.75</v>
+      </c>
+      <c r="AB83">
+        <v>1.95</v>
+      </c>
+      <c r="AC83">
+        <v>2.9</v>
+      </c>
+      <c r="AD83">
         <v>1.36</v>
       </c>
-      <c r="T83">
-        <v>3.06</v>
-      </c>
-      <c r="U83">
-        <v>2.81</v>
-      </c>
-      <c r="V83">
-        <v>1.4</v>
-      </c>
-      <c r="W83">
-        <v>1.05</v>
-      </c>
-      <c r="X83">
-        <v>1</v>
-      </c>
-      <c r="Y83">
-        <v>1.28</v>
-      </c>
-      <c r="Z83">
-        <v>3.66</v>
-      </c>
-      <c r="AA83">
-        <v>1.83</v>
-      </c>
-      <c r="AB83">
-        <v>1.89</v>
-      </c>
-      <c r="AC83">
-        <v>3.05</v>
-      </c>
-      <c r="AD83">
-        <v>1.29</v>
-      </c>
       <c r="AE83">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF83">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG83">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK83">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14336,10 +14336,10 @@
         <v>0</v>
       </c>
       <c r="Q86">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="R86">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="S86">
         <v>1.27</v>
@@ -14348,10 +14348,10 @@
         <v>3.45</v>
       </c>
       <c r="U86">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="V86">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="W86">
         <v>1.15</v>
@@ -14366,10 +14366,10 @@
         <v>4.3</v>
       </c>
       <c r="AA86">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="AB86">
-        <v>1.98</v>
+        <v>2.3</v>
       </c>
       <c r="AC86">
         <v>2.8</v>
@@ -14378,13 +14378,13 @@
         <v>1.38</v>
       </c>
       <c r="AE86">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AF86">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="AG86">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AK86">
-        <v>2.75</v>
+        <v>3.34</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O105">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P105">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q105">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R105">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S105">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T105">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="U105">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V105">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W105">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X105">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y105">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z105">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA105">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB105">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AC105">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD105">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE105">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF105">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG105">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK105">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -18900,55 +18900,55 @@
         <v>2.64</v>
       </c>
       <c r="Q114">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R114">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S114">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T114">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U114">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="V114">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W114">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X114">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y114">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z114">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA114">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB114">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC114">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="AD114">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE114">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF114">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG114">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK114">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19217,64 +19217,64 @@
         </is>
       </c>
       <c r="N116">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O116">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P116">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q116">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R116">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S116">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T116">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U116">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V116">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W116">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X116">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y116">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z116">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA116">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB116">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC116">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD116">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE116">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF116">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG116">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK116">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19745,10 +19745,10 @@
         <v>0</v>
       </c>
       <c r="AA119">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB119">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC119">
         <v>0</v>
@@ -20367,34 +20367,34 @@
         <v>4.37</v>
       </c>
       <c r="Q123">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R123">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S123">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T123">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U123">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V123">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W123">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X123">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y123">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z123">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA123">
         <v>1.58</v>
@@ -20403,19 +20403,19 @@
         <v>2.2</v>
       </c>
       <c r="AC123">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD123">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE123">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF123">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG123">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK123">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -21182,34 +21182,34 @@
         <v>3.89</v>
       </c>
       <c r="Q128">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="R128">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S128">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T128">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="U128">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V128">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W128">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X128">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y128">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z128">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA128">
         <v>1.86</v>
@@ -21218,19 +21218,19 @@
         <v>1.84</v>
       </c>
       <c r="AC128">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="AD128">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE128">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF128">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG128">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK128">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21997,34 +21997,34 @@
         <v>1.72</v>
       </c>
       <c r="Q133">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R133">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S133">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T133">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U133">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V133">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W133">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X133">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y133">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z133">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA133">
         <v>1.77</v>
@@ -22033,19 +22033,19 @@
         <v>1.97</v>
       </c>
       <c r="AC133">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AD133">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE133">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF133">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG133">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK133">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22323,55 +22323,55 @@
         <v>0</v>
       </c>
       <c r="Q135">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="R135">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S135">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T135">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U135">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V135">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W135">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X135">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y135">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z135">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA135">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB135">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC135">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AD135">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE135">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF135">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG135">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AK135">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22477,13 +22477,13 @@
         </is>
       </c>
       <c r="N136">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O136">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="P136">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -22522,10 +22522,10 @@
         <v>0</v>
       </c>
       <c r="AC136">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD136">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE136">
         <v>0</v>
@@ -22640,13 +22640,13 @@
         </is>
       </c>
       <c r="N137">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O137">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P137">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q137">
         <v>0</v>
@@ -22803,64 +22803,64 @@
         </is>
       </c>
       <c r="N138">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="O138">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P138">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q138">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R138">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S138">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T138">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="U138">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V138">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W138">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X138">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y138">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z138">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA138">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB138">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC138">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AD138">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE138">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF138">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG138">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK138">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -23138,55 +23138,55 @@
         <v>13.9</v>
       </c>
       <c r="Q140">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R140">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="S140">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="T140">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="U140">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="V140">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="W140">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X140">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y140">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Z140">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA140">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB140">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AC140">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD140">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE140">
         <v>1.6</v>
       </c>
       <c r="AF140">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG140">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK140">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -23790,55 +23790,55 @@
         <v>2.5</v>
       </c>
       <c r="Q144">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R144">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S144">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T144">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U144">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V144">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W144">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X144">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y144">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z144">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA144">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB144">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC144">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD144">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE144">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF144">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG144">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK144">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23953,34 +23953,34 @@
         <v>2.34</v>
       </c>
       <c r="Q145">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="R145">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S145">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T145">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U145">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="V145">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W145">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X145">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y145">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z145">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA145">
         <v>2</v>
@@ -23989,19 +23989,19 @@
         <v>1.8</v>
       </c>
       <c r="AC145">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD145">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE145">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF145">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG145">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AK145">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24279,40 +24279,40 @@
         <v>4.87</v>
       </c>
       <c r="Q147">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R147">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S147">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T147">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U147">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V147">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W147">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X147">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y147">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z147">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA147">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB147">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC147">
         <v>2.25</v>
@@ -24321,13 +24321,13 @@
         <v>1.57</v>
       </c>
       <c r="AE147">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF147">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG147">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK147">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -24768,55 +24768,55 @@
         <v>4.03</v>
       </c>
       <c r="Q150">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R150">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S150">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T150">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U150">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V150">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W150">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X150">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y150">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z150">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA150">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB150">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC150">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AD150">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE150">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF150">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG150">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH150" t="inlineStr">
         <is>
@@ -24829,10 +24829,10 @@
         </is>
       </c>
       <c r="AJ150">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK150">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL150">
         <v>0</v>
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G151">
@@ -24922,64 +24922,64 @@
         </is>
       </c>
       <c r="N151">
-        <v>1.67</v>
+        <v>1.99</v>
       </c>
       <c r="O151">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="P151">
-        <v>5.28</v>
+        <v>3.54</v>
       </c>
       <c r="Q151">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="R151">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S151">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T151">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U151">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V151">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W151">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X151">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y151">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z151">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA151">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB151">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC151">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AD151">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE151">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF151">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG151">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
@@ -24992,10 +24992,10 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK151">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL151">
         <v>0</v>
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,64 +25085,64 @@
         </is>
       </c>
       <c r="N152">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="O152">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="P152">
-        <v>4.08</v>
+        <v>5.28</v>
       </c>
       <c r="Q152">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R152">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S152">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T152">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U152">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V152">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W152">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X152">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y152">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z152">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA152">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB152">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC152">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AD152">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE152">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF152">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG152">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK152">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,64 +25248,64 @@
         </is>
       </c>
       <c r="N153">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="O153">
-        <v>3.64</v>
+        <v>3.68</v>
       </c>
       <c r="P153">
-        <v>4.75</v>
+        <v>4.08</v>
       </c>
       <c r="Q153">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R153">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S153">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T153">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U153">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="V153">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W153">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X153">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y153">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z153">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA153">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB153">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC153">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AD153">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE153">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF153">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG153">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25318,10 +25318,10 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK153">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,64 +25411,64 @@
         </is>
       </c>
       <c r="N154">
-        <v>2.47</v>
+        <v>1.72</v>
       </c>
       <c r="O154">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="P154">
-        <v>2.74</v>
+        <v>4.75</v>
       </c>
       <c r="Q154">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R154">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S154">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T154">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U154">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="V154">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W154">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X154">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y154">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z154">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA154">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB154">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC154">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AD154">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE154">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF154">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG154">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK154">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,13 +25574,13 @@
         </is>
       </c>
       <c r="N155">
-        <v>4.08</v>
+        <v>2.47</v>
       </c>
       <c r="O155">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="P155">
-        <v>1.84</v>
+        <v>2.74</v>
       </c>
       <c r="Q155">
         <v>0</v>
@@ -25613,10 +25613,10 @@
         <v>0</v>
       </c>
       <c r="AA155">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB155">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>4.18</v>
+        <v>4.08</v>
       </c>
       <c r="O156">
-        <v>3.52</v>
+        <v>3.58</v>
       </c>
       <c r="P156">
         <v>1.84</v>
       </c>
       <c r="Q156">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R156">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S156">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T156">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U156">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V156">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W156">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X156">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y156">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z156">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA156">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB156">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC156">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD156">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE156">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF156">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG156">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK156">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,64 +25900,64 @@
         </is>
       </c>
       <c r="N157">
-        <v>2.38</v>
+        <v>4.18</v>
       </c>
       <c r="O157">
-        <v>3.46</v>
+        <v>3.52</v>
       </c>
       <c r="P157">
-        <v>2.75</v>
+        <v>1.84</v>
       </c>
       <c r="Q157">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R157">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S157">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T157">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U157">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="V157">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W157">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X157">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y157">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z157">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA157">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB157">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC157">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD157">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE157">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF157">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG157">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25970,10 +25970,10 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK157">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,64 +26063,64 @@
         </is>
       </c>
       <c r="N158">
-        <v>1.99</v>
+        <v>2.38</v>
       </c>
       <c r="O158">
-        <v>3.54</v>
+        <v>3.46</v>
       </c>
       <c r="P158">
-        <v>3.54</v>
+        <v>2.75</v>
       </c>
       <c r="Q158">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="R158">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S158">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T158">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U158">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V158">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W158">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X158">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y158">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z158">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA158">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB158">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC158">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AD158">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE158">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF158">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG158">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK158">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -27693,64 +27693,64 @@
         </is>
       </c>
       <c r="N168">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O168">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P168">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q168">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R168">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S168">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T168">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U168">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V168">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W168">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X168">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y168">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z168">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA168">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB168">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC168">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD168">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE168">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF168">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG168">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH168" t="inlineStr">
         <is>
@@ -27763,10 +27763,10 @@
         </is>
       </c>
       <c r="AJ168">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK168">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL168">
         <v>0</v>
@@ -27865,40 +27865,40 @@
         <v>4.68</v>
       </c>
       <c r="Q169">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R169">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S169">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T169">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="U169">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V169">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W169">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X169">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y169">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z169">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA169">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AB169">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC169">
         <v>2.3</v>
@@ -27907,13 +27907,13 @@
         <v>1.53</v>
       </c>
       <c r="AE169">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF169">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG169">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH169" t="inlineStr">
         <is>
@@ -27926,10 +27926,10 @@
         </is>
       </c>
       <c r="AJ169">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK169">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AL169">
         <v>0</v>
@@ -28191,40 +28191,40 @@
         <v>1.26</v>
       </c>
       <c r="Q171">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R171">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S171">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T171">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U171">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V171">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W171">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X171">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y171">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z171">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA171">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB171">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC171">
         <v>2.25</v>
@@ -28233,13 +28233,13 @@
         <v>1.55</v>
       </c>
       <c r="AE171">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF171">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG171">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH171" t="inlineStr">
         <is>
@@ -28252,10 +28252,10 @@
         </is>
       </c>
       <c r="AJ171">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AK171">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AL171">
         <v>0</v>
@@ -32909,64 +32909,64 @@
         </is>
       </c>
       <c r="N200">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="O200">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P200">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q200">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R200">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S200">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T200">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U200">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V200">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W200">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X200">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y200">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z200">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA200">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB200">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC200">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="AD200">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE200">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF200">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG200">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH200" t="inlineStr">
         <is>
@@ -32979,10 +32979,10 @@
         </is>
       </c>
       <c r="AJ200">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AK200">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL200">
         <v>0</v>
@@ -33072,64 +33072,64 @@
         </is>
       </c>
       <c r="N201">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="O201">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="P201">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q201">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R201">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S201">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T201">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="U201">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V201">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="W201">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X201">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y201">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z201">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AA201">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB201">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC201">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD201">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE201">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF201">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AG201">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH201" t="inlineStr">
         <is>
@@ -33142,10 +33142,10 @@
         </is>
       </c>
       <c r="AJ201">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK201">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AL201">
         <v>0</v>

--- a/jogos_2026-08-08.xlsx
+++ b/jogos_2026-08-08.xlsx
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.95</v>
+        <v>2.67</v>
       </c>
       <c r="O26">
         <v>3.22</v>
       </c>
       <c r="P26">
-        <v>4.09</v>
+        <v>2.58</v>
       </c>
       <c r="Q26">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="R26">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="S26">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="T26">
-        <v>2.44</v>
+        <v>2.88</v>
       </c>
       <c r="U26">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="V26">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="W26">
+        <v>1.04</v>
+      </c>
+      <c r="X26">
         <v>1.01</v>
       </c>
-      <c r="X26">
-        <v>1.04</v>
-      </c>
       <c r="Y26">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="Z26">
-        <v>2.87</v>
+        <v>3.56</v>
       </c>
       <c r="AA26">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="AB26">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="AC26">
-        <v>4.15</v>
+        <v>3.4</v>
       </c>
       <c r="AD26">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AE26">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF26">
-        <v>2.05</v>
+        <v>1.71</v>
       </c>
       <c r="AG26">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="AK26">
-        <v>1.75</v>
+        <v>1.39</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.75</v>
+        <v>1.95</v>
       </c>
       <c r="O27">
         <v>3.22</v>
       </c>
       <c r="P27">
-        <v>2.51</v>
+        <v>4.09</v>
       </c>
       <c r="Q27">
+        <v>2.5</v>
+      </c>
+      <c r="R27">
+        <v>2</v>
+      </c>
+      <c r="S27">
+        <v>1.49</v>
+      </c>
+      <c r="T27">
+        <v>2.44</v>
+      </c>
+      <c r="U27">
         <v>3.25</v>
       </c>
-      <c r="R27">
-        <v>2.1</v>
-      </c>
-      <c r="S27">
-        <v>1.36</v>
-      </c>
-      <c r="T27">
-        <v>2.88</v>
-      </c>
-      <c r="U27">
-        <v>2.8</v>
-      </c>
       <c r="V27">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="W27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X27">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y27">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="Z27">
-        <v>3.15</v>
+        <v>2.87</v>
       </c>
       <c r="AA27">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AB27">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="AC27">
-        <v>3.65</v>
+        <v>4.15</v>
       </c>
       <c r="AD27">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE27">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AF27">
-        <v>1.71</v>
+        <v>2.05</v>
       </c>
       <c r="AG27">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK27">
-        <v>1.41</v>
+        <v>1.75</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,19 +4873,19 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.78</v>
+        <v>2.75</v>
       </c>
       <c r="O28">
-        <v>3.58</v>
+        <v>3.22</v>
       </c>
       <c r="P28">
-        <v>4.42</v>
+        <v>2.51</v>
       </c>
       <c r="Q28">
-        <v>2.36</v>
+        <v>3.25</v>
       </c>
       <c r="R28">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S28">
         <v>1.36</v>
@@ -4894,59 +4894,59 @@
         <v>2.88</v>
       </c>
       <c r="U28">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="V28">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W28">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X28">
         <v>1.06</v>
       </c>
       <c r="Y28">
+        <v>1.28</v>
+      </c>
+      <c r="Z28">
+        <v>3.15</v>
+      </c>
+      <c r="AA28">
+        <v>1.95</v>
+      </c>
+      <c r="AB28">
+        <v>1.73</v>
+      </c>
+      <c r="AC28">
+        <v>3.65</v>
+      </c>
+      <c r="AD28">
+        <v>1.23</v>
+      </c>
+      <c r="AE28">
+        <v>1.08</v>
+      </c>
+      <c r="AF28">
+        <v>1.71</v>
+      </c>
+      <c r="AG28">
+        <v>1.95</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28">
         <v>1.25</v>
       </c>
-      <c r="Z28">
-        <v>3.3</v>
-      </c>
-      <c r="AA28">
-        <v>2.01</v>
-      </c>
-      <c r="AB28">
-        <v>1.81</v>
-      </c>
-      <c r="AC28">
-        <v>3.55</v>
-      </c>
-      <c r="AD28">
-        <v>1.27</v>
-      </c>
-      <c r="AE28">
-        <v>1.07</v>
-      </c>
-      <c r="AF28">
-        <v>1.83</v>
-      </c>
-      <c r="AG28">
-        <v>1.85</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28">
-        <v>1.12</v>
-      </c>
       <c r="AK28">
-        <v>1.99</v>
+        <v>1.41</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,61 +5036,61 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.67</v>
+        <v>1.78</v>
       </c>
       <c r="O29">
-        <v>3.22</v>
+        <v>3.58</v>
       </c>
       <c r="P29">
-        <v>2.58</v>
+        <v>4.42</v>
       </c>
       <c r="Q29">
-        <v>3.1</v>
+        <v>2.36</v>
       </c>
       <c r="R29">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="S29">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T29">
         <v>2.88</v>
       </c>
       <c r="U29">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="V29">
         <v>1.36</v>
       </c>
       <c r="W29">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X29">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y29">
+        <v>1.25</v>
+      </c>
+      <c r="Z29">
+        <v>3.3</v>
+      </c>
+      <c r="AA29">
+        <v>2.01</v>
+      </c>
+      <c r="AB29">
+        <v>1.81</v>
+      </c>
+      <c r="AC29">
+        <v>3.55</v>
+      </c>
+      <c r="AD29">
         <v>1.27</v>
       </c>
-      <c r="Z29">
-        <v>3.56</v>
-      </c>
-      <c r="AA29">
-        <v>1.93</v>
-      </c>
-      <c r="AB29">
-        <v>1.8</v>
-      </c>
-      <c r="AC29">
-        <v>3.4</v>
-      </c>
-      <c r="AD29">
-        <v>1.26</v>
-      </c>
       <c r="AE29">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF29">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="AG29">
         <v>1.85</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="AK29">
-        <v>1.39</v>
+        <v>1.99</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.45</v>
+        <v>2.11</v>
       </c>
       <c r="O34">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="P34">
+        <v>3.09</v>
+      </c>
+      <c r="Q34">
         <v>2.6</v>
       </c>
-      <c r="Q34">
-        <v>3.13</v>
-      </c>
       <c r="R34">
+        <v>2.3</v>
+      </c>
+      <c r="S34">
+        <v>1.29</v>
+      </c>
+      <c r="T34">
+        <v>3.6</v>
+      </c>
+      <c r="U34">
         <v>2.25</v>
       </c>
-      <c r="S34">
-        <v>1.3</v>
-      </c>
-      <c r="T34">
-        <v>3.2</v>
-      </c>
-      <c r="U34">
-        <v>2.5</v>
-      </c>
       <c r="V34">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="W34">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X34">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="Z34">
-        <v>3.58</v>
+        <v>4.15</v>
       </c>
       <c r="AA34">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AB34">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="AC34">
-        <v>2.96</v>
+        <v>2.52</v>
       </c>
       <c r="AD34">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AE34">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF34">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG34">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="AK34">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.11</v>
+        <v>2.45</v>
       </c>
       <c r="O35">
-        <v>3.62</v>
+        <v>3.4</v>
       </c>
       <c r="P35">
-        <v>3.09</v>
+        <v>2.6</v>
       </c>
       <c r="Q35">
-        <v>2.6</v>
+        <v>3.13</v>
       </c>
       <c r="R35">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S35">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T35">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="U35">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="V35">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="W35">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="Z35">
-        <v>4.15</v>
+        <v>3.58</v>
       </c>
       <c r="AA35">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AB35">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="AC35">
-        <v>2.52</v>
+        <v>2.96</v>
       </c>
       <c r="AD35">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AE35">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF35">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG35">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="AK35">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.72</v>
+        <v>2.35</v>
       </c>
       <c r="O38">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="P38">
-        <v>4.26</v>
+        <v>2.72</v>
       </c>
       <c r="Q38">
-        <v>2.27</v>
+        <v>3.13</v>
       </c>
       <c r="R38">
         <v>2.38</v>
       </c>
       <c r="S38">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T38">
-        <v>3.1</v>
+        <v>3.66</v>
       </c>
       <c r="U38">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="V38">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="W38">
+        <v>1.14</v>
+      </c>
+      <c r="X38">
+        <v>1.02</v>
+      </c>
+      <c r="Y38">
         <v>1.09</v>
       </c>
-      <c r="X38">
-        <v>1.04</v>
-      </c>
-      <c r="Y38">
-        <v>1.18</v>
-      </c>
       <c r="Z38">
-        <v>4.4</v>
+        <v>5.25</v>
       </c>
       <c r="AA38">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="AB38">
-        <v>2.09</v>
+        <v>2.55</v>
       </c>
       <c r="AC38">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD38">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="AE38">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AF38">
-        <v>1.61</v>
+        <v>1.41</v>
       </c>
       <c r="AG38">
-        <v>2.2</v>
+        <v>2.69</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK38">
-        <v>2.04</v>
+        <v>1.4</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.35</v>
+        <v>1.72</v>
       </c>
       <c r="O39">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="P39">
-        <v>2.72</v>
+        <v>4.26</v>
       </c>
       <c r="Q39">
-        <v>3.13</v>
+        <v>2.27</v>
       </c>
       <c r="R39">
         <v>2.38</v>
       </c>
       <c r="S39">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T39">
-        <v>3.66</v>
+        <v>3.1</v>
       </c>
       <c r="U39">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="V39">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="W39">
+        <v>1.09</v>
+      </c>
+      <c r="X39">
+        <v>1.04</v>
+      </c>
+      <c r="Y39">
+        <v>1.18</v>
+      </c>
+      <c r="Z39">
+        <v>4.4</v>
+      </c>
+      <c r="AA39">
+        <v>1.6</v>
+      </c>
+      <c r="AB39">
+        <v>2.09</v>
+      </c>
+      <c r="AC39">
+        <v>2.25</v>
+      </c>
+      <c r="AD39">
+        <v>1.55</v>
+      </c>
+      <c r="AE39">
         <v>1.14</v>
       </c>
-      <c r="X39">
-        <v>1.02</v>
-      </c>
-      <c r="Y39">
-        <v>1.09</v>
-      </c>
-      <c r="Z39">
-        <v>5.25</v>
-      </c>
-      <c r="AA39">
-        <v>1.43</v>
-      </c>
-      <c r="AB39">
-        <v>2.55</v>
-      </c>
-      <c r="AC39">
-        <v>2.1</v>
-      </c>
-      <c r="AD39">
-        <v>1.63</v>
-      </c>
-      <c r="AE39">
-        <v>1.27</v>
-      </c>
       <c r="AF39">
-        <v>1.41</v>
+        <v>1.61</v>
       </c>
       <c r="AG39">
-        <v>2.69</v>
+        <v>2.2</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK39">
-        <v>1.4</v>
+        <v>2.04</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,22 +7481,22 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="Q44">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="R44">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="S44">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="T44">
         <v>4</v>
@@ -7505,7 +7505,7 @@
         <v>2.05</v>
       </c>
       <c r="V44">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="W44">
         <v>1.17</v>
@@ -7514,31 +7514,31 @@
         <v>1.02</v>
       </c>
       <c r="Y44">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Z44">
-        <v>5.85</v>
+        <v>5.66</v>
       </c>
       <c r="AA44">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AB44">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AC44">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AD44">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AE44">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AF44">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AG44">
-        <v>2.46</v>
+        <v>2.51</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK44">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,22 +7644,22 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O45">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="P45">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="Q45">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="R45">
-        <v>2.49</v>
+        <v>2.56</v>
       </c>
       <c r="S45">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="T45">
         <v>4</v>
@@ -7668,7 +7668,7 @@
         <v>2.05</v>
       </c>
       <c r="V45">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="W45">
         <v>1.17</v>
@@ -7677,31 +7677,31 @@
         <v>1.02</v>
       </c>
       <c r="Y45">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Z45">
-        <v>5.66</v>
+        <v>5.85</v>
       </c>
       <c r="AA45">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AB45">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AC45">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AD45">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AE45">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AF45">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AG45">
-        <v>2.51</v>
+        <v>2.46</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK45">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,31 +12697,31 @@
         </is>
       </c>
       <c r="N76">
+        <v>2.51</v>
+      </c>
+      <c r="O76">
+        <v>3.3</v>
+      </c>
+      <c r="P76">
+        <v>2.45</v>
+      </c>
+      <c r="Q76">
+        <v>3.4</v>
+      </c>
+      <c r="R76">
         <v>2.1</v>
       </c>
-      <c r="O76">
-        <v>3.08</v>
-      </c>
-      <c r="P76">
-        <v>3.35</v>
-      </c>
-      <c r="Q76">
-        <v>2.5</v>
-      </c>
-      <c r="R76">
-        <v>1.95</v>
-      </c>
       <c r="S76">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T76">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="U76">
-        <v>3.02</v>
+        <v>2.91</v>
       </c>
       <c r="V76">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W76">
         <v>1.02</v>
@@ -12730,31 +12730,31 @@
         <v>1.06</v>
       </c>
       <c r="Y76">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z76">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AA76">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AB76">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AC76">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="AD76">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE76">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF76">
         <v>1.8</v>
       </c>
       <c r="AG76">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK76">
-        <v>1.73</v>
+        <v>1.34</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,31 +12860,31 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.51</v>
+        <v>2.1</v>
       </c>
       <c r="O77">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="P77">
-        <v>2.45</v>
+        <v>3.35</v>
       </c>
       <c r="Q77">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="R77">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="S77">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T77">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="U77">
-        <v>2.91</v>
+        <v>3.02</v>
       </c>
       <c r="V77">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W77">
         <v>1.02</v>
@@ -12893,31 +12893,31 @@
         <v>1.06</v>
       </c>
       <c r="Y77">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z77">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AA77">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AB77">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AC77">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="AD77">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE77">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF77">
         <v>1.8</v>
       </c>
       <c r="AG77">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK77">
-        <v>1.34</v>
+        <v>1.73</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.16</v>
+        <v>2.48</v>
       </c>
       <c r="O83">
-        <v>3.54</v>
+        <v>3.48</v>
       </c>
       <c r="P83">
-        <v>3.11</v>
+        <v>2.62</v>
       </c>
       <c r="Q83">
-        <v>2.72</v>
+        <v>2.9</v>
       </c>
       <c r="R83">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="S83">
+        <v>1.33</v>
+      </c>
+      <c r="T83">
+        <v>3.02</v>
+      </c>
+      <c r="U83">
+        <v>2.62</v>
+      </c>
+      <c r="V83">
+        <v>1.43</v>
+      </c>
+      <c r="W83">
+        <v>1.06</v>
+      </c>
+      <c r="X83">
+        <v>1.04</v>
+      </c>
+      <c r="Y83">
+        <v>1.25</v>
+      </c>
+      <c r="Z83">
+        <v>3.62</v>
+      </c>
+      <c r="AA83">
+        <v>1.75</v>
+      </c>
+      <c r="AB83">
+        <v>1.95</v>
+      </c>
+      <c r="AC83">
+        <v>2.9</v>
+      </c>
+      <c r="AD83">
         <v>1.36</v>
       </c>
-      <c r="T83">
-        <v>3.06</v>
-      </c>
-      <c r="U83">
-        <v>2.81</v>
-      </c>
-      <c r="V83">
-        <v>1.4</v>
-      </c>
-      <c r="W83">
-        <v>1.05</v>
-      </c>
-      <c r="X83">
-        <v>1</v>
-      </c>
-      <c r="Y83">
-        <v>1.28</v>
-      </c>
-      <c r="Z83">
-        <v>3.66</v>
-      </c>
-      <c r="AA83">
-        <v>1.83</v>
-      </c>
-      <c r="AB83">
-        <v>1.89</v>
-      </c>
-      <c r="AC83">
-        <v>3.05</v>
-      </c>
-      <c r="AD83">
-        <v>1.29</v>
-      </c>
       <c r="AE83">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF83">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG83">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK83">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,80 +14001,80 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.48</v>
+        <v>2.16</v>
       </c>
       <c r="O84">
-        <v>3.48</v>
+        <v>3.54</v>
       </c>
       <c r="P84">
-        <v>2.62</v>
+        <v>3.11</v>
       </c>
       <c r="Q84">
-        <v>2.9</v>
+        <v>2.72</v>
       </c>
       <c r="R84">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="S84">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T84">
-        <v>3.02</v>
+        <v>3.06</v>
       </c>
       <c r="U84">
-        <v>2.62</v>
+        <v>2.81</v>
       </c>
       <c r="V84">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W84">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X84">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y84">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z84">
-        <v>3.62</v>
+        <v>3.66</v>
       </c>
       <c r="AA84">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AB84">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AC84">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="AD84">
+        <v>1.29</v>
+      </c>
+      <c r="AE84">
+        <v>1.12</v>
+      </c>
+      <c r="AF84">
+        <v>1.67</v>
+      </c>
+      <c r="AG84">
+        <v>2.05</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ84">
         <v>1.36</v>
       </c>
-      <c r="AE84">
-        <v>1.13</v>
-      </c>
-      <c r="AF84">
-        <v>1.62</v>
-      </c>
-      <c r="AG84">
-        <v>2.14</v>
-      </c>
-      <c r="AH84" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI84" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ84">
-        <v>1.3</v>
-      </c>
       <c r="AK84">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G142">
@@ -23455,64 +23455,64 @@
         </is>
       </c>
       <c r="N142">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="O142">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="P142">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Q142">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="R142">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="S142">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="T142">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="U142">
-        <v>4.45</v>
+        <v>3.8</v>
       </c>
       <c r="V142">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="W142">
+        <v>1.01</v>
+      </c>
+      <c r="X142">
+        <v>1.1</v>
+      </c>
+      <c r="Y142">
+        <v>1.61</v>
+      </c>
+      <c r="Z142">
+        <v>2.28</v>
+      </c>
+      <c r="AA142">
+        <v>2.86</v>
+      </c>
+      <c r="AB142">
+        <v>1.39</v>
+      </c>
+      <c r="AC142">
+        <v>5.35</v>
+      </c>
+      <c r="AD142">
+        <v>1.09</v>
+      </c>
+      <c r="AE142">
         <v>1.03</v>
       </c>
-      <c r="X142">
-        <v>1.15</v>
-      </c>
-      <c r="Y142">
-        <v>1.7</v>
-      </c>
-      <c r="Z142">
-        <v>2.03</v>
-      </c>
-      <c r="AA142">
-        <v>3.14</v>
-      </c>
-      <c r="AB142">
-        <v>1.27</v>
-      </c>
-      <c r="AC142">
-        <v>6.75</v>
-      </c>
-      <c r="AD142">
-        <v>1.1</v>
-      </c>
-      <c r="AE142">
-        <v>1.02</v>
-      </c>
       <c r="AF142">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="AG142">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
@@ -23525,10 +23525,10 @@
         </is>
       </c>
       <c r="AJ142">
-        <v>1.1</v>
+        <v>1.31</v>
       </c>
       <c r="AK142">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,80 +23618,80 @@
         </is>
       </c>
       <c r="N143">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="O143">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="P143">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Q143">
+        <v>2.75</v>
+      </c>
+      <c r="R143">
+        <v>1.68</v>
+      </c>
+      <c r="S143">
+        <v>1.62</v>
+      </c>
+      <c r="T143">
+        <v>2.2</v>
+      </c>
+      <c r="U143">
+        <v>4.45</v>
+      </c>
+      <c r="V143">
+        <v>1.14</v>
+      </c>
+      <c r="W143">
+        <v>1.03</v>
+      </c>
+      <c r="X143">
+        <v>1.15</v>
+      </c>
+      <c r="Y143">
+        <v>1.7</v>
+      </c>
+      <c r="Z143">
+        <v>2.03</v>
+      </c>
+      <c r="AA143">
+        <v>3.14</v>
+      </c>
+      <c r="AB143">
+        <v>1.27</v>
+      </c>
+      <c r="AC143">
+        <v>6.75</v>
+      </c>
+      <c r="AD143">
+        <v>1.1</v>
+      </c>
+      <c r="AE143">
+        <v>1.02</v>
+      </c>
+      <c r="AF143">
         <v>2.6</v>
       </c>
-      <c r="R143">
-        <v>1.81</v>
-      </c>
-      <c r="S143">
-        <v>1.61</v>
-      </c>
-      <c r="T143">
-        <v>2.24</v>
-      </c>
-      <c r="U143">
-        <v>3.8</v>
-      </c>
-      <c r="V143">
-        <v>1.19</v>
-      </c>
-      <c r="W143">
-        <v>1.01</v>
-      </c>
-      <c r="X143">
+      <c r="AG143">
+        <v>1.44</v>
+      </c>
+      <c r="AH143" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI143" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ143">
         <v>1.1</v>
       </c>
-      <c r="Y143">
-        <v>1.61</v>
-      </c>
-      <c r="Z143">
-        <v>2.28</v>
-      </c>
-      <c r="AA143">
-        <v>2.86</v>
-      </c>
-      <c r="AB143">
-        <v>1.39</v>
-      </c>
-      <c r="AC143">
-        <v>5.35</v>
-      </c>
-      <c r="AD143">
-        <v>1.09</v>
-      </c>
-      <c r="AE143">
-        <v>1.03</v>
-      </c>
-      <c r="AF143">
-        <v>2.3</v>
-      </c>
-      <c r="AG143">
-        <v>1.57</v>
-      </c>
-      <c r="AH143" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI143" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ143">
-        <v>1.31</v>
-      </c>
       <c r="AK143">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G160">
@@ -26389,64 +26389,64 @@
         </is>
       </c>
       <c r="N160">
-        <v>1.99</v>
+        <v>1.67</v>
       </c>
       <c r="O160">
+        <v>3.58</v>
+      </c>
+      <c r="P160">
+        <v>5.28</v>
+      </c>
+      <c r="Q160">
+        <v>2.55</v>
+      </c>
+      <c r="R160">
+        <v>2.1</v>
+      </c>
+      <c r="S160">
+        <v>1.44</v>
+      </c>
+      <c r="T160">
+        <v>2.65</v>
+      </c>
+      <c r="U160">
+        <v>2.9</v>
+      </c>
+      <c r="V160">
+        <v>1.36</v>
+      </c>
+      <c r="W160">
+        <v>1.07</v>
+      </c>
+      <c r="X160">
+        <v>1.06</v>
+      </c>
+      <c r="Y160">
+        <v>1.36</v>
+      </c>
+      <c r="Z160">
+        <v>2.88</v>
+      </c>
+      <c r="AA160">
+        <v>2.05</v>
+      </c>
+      <c r="AB160">
+        <v>1.65</v>
+      </c>
+      <c r="AC160">
         <v>3.54</v>
       </c>
-      <c r="P160">
-        <v>3.54</v>
-      </c>
-      <c r="Q160">
-        <v>2.44</v>
-      </c>
-      <c r="R160">
-        <v>2.14</v>
-      </c>
-      <c r="S160">
-        <v>1.36</v>
-      </c>
-      <c r="T160">
-        <v>2.85</v>
-      </c>
-      <c r="U160">
-        <v>2.88</v>
-      </c>
-      <c r="V160">
-        <v>1.42</v>
-      </c>
-      <c r="W160">
+      <c r="AD160">
+        <v>1.22</v>
+      </c>
+      <c r="AE160">
         <v>1.06</v>
       </c>
-      <c r="X160">
-        <v>1.03</v>
-      </c>
-      <c r="Y160">
-        <v>1.3</v>
-      </c>
-      <c r="Z160">
-        <v>3.3</v>
-      </c>
-      <c r="AA160">
-        <v>1.87</v>
-      </c>
-      <c r="AB160">
-        <v>1.83</v>
-      </c>
-      <c r="AC160">
-        <v>2.99</v>
-      </c>
-      <c r="AD160">
-        <v>1.3</v>
-      </c>
-      <c r="AE160">
-        <v>1.1</v>
-      </c>
       <c r="AF160">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AG160">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
@@ -26459,7 +26459,7 @@
         </is>
       </c>
       <c r="AJ160">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK160">
         <v>1.8</v>
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G161">
@@ -26552,49 +26552,49 @@
         </is>
       </c>
       <c r="N161">
-        <v>1.82</v>
+        <v>1.99</v>
       </c>
       <c r="O161">
-        <v>3.68</v>
+        <v>3.54</v>
       </c>
       <c r="P161">
-        <v>4.08</v>
+        <v>3.54</v>
       </c>
       <c r="Q161">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="R161">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="S161">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T161">
-        <v>2.93</v>
+        <v>2.85</v>
       </c>
       <c r="U161">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="V161">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W161">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X161">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y161">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z161">
         <v>3.3</v>
       </c>
       <c r="AA161">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AB161">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC161">
         <v>2.99</v>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK161">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G162">
@@ -26715,64 +26715,64 @@
         </is>
       </c>
       <c r="N162">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="O162">
-        <v>3.58</v>
+        <v>3.64</v>
       </c>
       <c r="P162">
-        <v>5.28</v>
+        <v>4.75</v>
       </c>
       <c r="Q162">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="R162">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S162">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="T162">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="U162">
-        <v>2.9</v>
+        <v>3.01</v>
       </c>
       <c r="V162">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W162">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X162">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y162">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z162">
-        <v>2.88</v>
+        <v>3.24</v>
       </c>
       <c r="AA162">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AB162">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AC162">
-        <v>3.54</v>
+        <v>3.18</v>
       </c>
       <c r="AD162">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AE162">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF162">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AG162">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
@@ -26785,10 +26785,10 @@
         </is>
       </c>
       <c r="AJ162">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AK162">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL162">
         <v>0</v>
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G163">
@@ -26878,64 +26878,64 @@
         </is>
       </c>
       <c r="N163">
-        <v>1.72</v>
+        <v>2.47</v>
       </c>
       <c r="O163">
-        <v>3.64</v>
+        <v>3.3</v>
       </c>
       <c r="P163">
-        <v>4.75</v>
+        <v>2.74</v>
       </c>
       <c r="Q163">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R163">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S163">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T163">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U163">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="V163">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W163">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X163">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y163">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z163">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AA163">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AB163">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AC163">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AD163">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE163">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF163">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG163">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
@@ -26948,10 +26948,10 @@
         </is>
       </c>
       <c r="AJ163">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK163">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G164">
@@ -27041,64 +27041,64 @@
         </is>
       </c>
       <c r="N164">
-        <v>2.47</v>
+        <v>4.08</v>
       </c>
       <c r="O164">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="P164">
-        <v>2.74</v>
+        <v>1.84</v>
       </c>
       <c r="Q164">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R164">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S164">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T164">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U164">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V164">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W164">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X164">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y164">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z164">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA164">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AB164">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AC164">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD164">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE164">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF164">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG164">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH164" t="inlineStr">
         <is>
@@ -27111,10 +27111,10 @@
         </is>
       </c>
       <c r="AJ164">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK164">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL164">
         <v>0</v>
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G165">
@@ -27204,64 +27204,64 @@
         </is>
       </c>
       <c r="N165">
-        <v>4.08</v>
+        <v>4.18</v>
       </c>
       <c r="O165">
-        <v>3.58</v>
+        <v>3.52</v>
       </c>
       <c r="P165">
         <v>1.84</v>
       </c>
       <c r="Q165">
-        <v>4.2</v>
+        <v>4.32</v>
       </c>
       <c r="R165">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="S165">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T165">
         <v>2.69</v>
       </c>
       <c r="U165">
-        <v>2.77</v>
+        <v>3.05</v>
       </c>
       <c r="V165">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W165">
         <v>1.05</v>
       </c>
       <c r="X165">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y165">
         <v>1.33</v>
       </c>
       <c r="Z165">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AA165">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AB165">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AC165">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AD165">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AE165">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF165">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AG165">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH165" t="inlineStr">
         <is>
@@ -27274,10 +27274,10 @@
         </is>
       </c>
       <c r="AJ165">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK165">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AL165">
         <v>0</v>
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G166">
@@ -27367,80 +27367,80 @@
         </is>
       </c>
       <c r="N166">
-        <v>4.18</v>
+        <v>2.38</v>
       </c>
       <c r="O166">
-        <v>3.52</v>
+        <v>3.46</v>
       </c>
       <c r="P166">
-        <v>1.84</v>
+        <v>2.75</v>
       </c>
       <c r="Q166">
-        <v>4.32</v>
+        <v>2.84</v>
       </c>
       <c r="R166">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="S166">
+        <v>1.35</v>
+      </c>
+      <c r="T166">
+        <v>2.94</v>
+      </c>
+      <c r="U166">
+        <v>2.53</v>
+      </c>
+      <c r="V166">
+        <v>1.43</v>
+      </c>
+      <c r="W166">
+        <v>1.07</v>
+      </c>
+      <c r="X166">
+        <v>1.05</v>
+      </c>
+      <c r="Y166">
+        <v>1.25</v>
+      </c>
+      <c r="Z166">
+        <v>3.5</v>
+      </c>
+      <c r="AA166">
+        <v>1.78</v>
+      </c>
+      <c r="AB166">
+        <v>2</v>
+      </c>
+      <c r="AC166">
+        <v>3.02</v>
+      </c>
+      <c r="AD166">
+        <v>1.35</v>
+      </c>
+      <c r="AE166">
+        <v>1.11</v>
+      </c>
+      <c r="AF166">
+        <v>1.6</v>
+      </c>
+      <c r="AG166">
+        <v>2.05</v>
+      </c>
+      <c r="AH166" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI166" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ166">
         <v>1.41</v>
       </c>
-      <c r="T166">
-        <v>2.69</v>
-      </c>
-      <c r="U166">
-        <v>3.05</v>
-      </c>
-      <c r="V166">
-        <v>1.35</v>
-      </c>
-      <c r="W166">
-        <v>1.05</v>
-      </c>
-      <c r="X166">
-        <v>1.02</v>
-      </c>
-      <c r="Y166">
-        <v>1.33</v>
-      </c>
-      <c r="Z166">
-        <v>3.1</v>
-      </c>
-      <c r="AA166">
-        <v>2.05</v>
-      </c>
-      <c r="AB166">
-        <v>1.73</v>
-      </c>
-      <c r="AC166">
-        <v>3.6</v>
-      </c>
-      <c r="AD166">
-        <v>1.27</v>
-      </c>
-      <c r="AE166">
-        <v>1.08</v>
-      </c>
-      <c r="AF166">
-        <v>1.85</v>
-      </c>
-      <c r="AG166">
-        <v>1.85</v>
-      </c>
-      <c r="AH166" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI166" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ166">
-        <v>1.33</v>
-      </c>
       <c r="AK166">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AL166">
         <v>0</v>
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G167">
@@ -27530,34 +27530,34 @@
         </is>
       </c>
       <c r="N167">
-        <v>2.38</v>
+        <v>1.82</v>
       </c>
       <c r="O167">
-        <v>3.46</v>
+        <v>3.68</v>
       </c>
       <c r="P167">
-        <v>2.75</v>
+        <v>4.08</v>
       </c>
       <c r="Q167">
-        <v>2.84</v>
+        <v>2.62</v>
       </c>
       <c r="R167">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="S167">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T167">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="U167">
-        <v>2.53</v>
+        <v>2.64</v>
       </c>
       <c r="V167">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W167">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X167">
         <v>1.05</v>
@@ -27566,28 +27566,28 @@
         <v>1.25</v>
       </c>
       <c r="Z167">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA167">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="AB167">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AC167">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="AD167">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE167">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF167">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG167">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
@@ -27600,10 +27600,10 @@
         </is>
       </c>
       <c r="AJ167">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AK167">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AL167">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G196">
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,64 +32420,64 @@
         </is>
       </c>
       <c r="N197">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O197">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P197">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Q197">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R197">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S197">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T197">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U197">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="V197">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W197">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X197">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y197">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z197">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA197">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AB197">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AC197">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD197">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE197">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF197">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG197">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32490,10 +32490,10 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK197">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G198">
@@ -32583,64 +32583,64 @@
         </is>
       </c>
       <c r="N198">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O198">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P198">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q198">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R198">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S198">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T198">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U198">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V198">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W198">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X198">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y198">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z198">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA198">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB198">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC198">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD198">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE198">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF198">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG198">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH198" t="inlineStr">
         <is>
@@ -32653,10 +32653,10 @@
         </is>
       </c>
       <c r="AJ198">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK198">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL198">
         <v>0</v>

--- a/jogos_2026-08-08.xlsx
+++ b/jogos_2026-08-08.xlsx
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="O26">
         <v>3.22</v>
       </c>
       <c r="P26">
-        <v>2.58</v>
+        <v>2.51</v>
       </c>
       <c r="Q26">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R26">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="S26">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T26">
         <v>2.88</v>
       </c>
       <c r="U26">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="V26">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W26">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y26">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z26">
-        <v>3.56</v>
+        <v>3.15</v>
       </c>
       <c r="AA26">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB26">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AC26">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="AD26">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AE26">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF26">
         <v>1.71</v>
       </c>
       <c r="AG26">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.95</v>
+        <v>2.67</v>
       </c>
       <c r="O27">
         <v>3.22</v>
       </c>
       <c r="P27">
-        <v>4.09</v>
+        <v>2.58</v>
       </c>
       <c r="Q27">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="R27">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="S27">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="T27">
-        <v>2.44</v>
+        <v>2.88</v>
       </c>
       <c r="U27">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="V27">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="W27">
+        <v>1.04</v>
+      </c>
+      <c r="X27">
         <v>1.01</v>
       </c>
-      <c r="X27">
-        <v>1.04</v>
-      </c>
       <c r="Y27">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="Z27">
-        <v>2.87</v>
+        <v>3.56</v>
       </c>
       <c r="AA27">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="AB27">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="AC27">
-        <v>4.15</v>
+        <v>3.4</v>
       </c>
       <c r="AD27">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AE27">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF27">
-        <v>2.05</v>
+        <v>1.71</v>
       </c>
       <c r="AG27">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="AK27">
-        <v>1.75</v>
+        <v>1.39</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,19 +4873,19 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.75</v>
+        <v>1.78</v>
       </c>
       <c r="O28">
-        <v>3.22</v>
+        <v>3.58</v>
       </c>
       <c r="P28">
-        <v>2.51</v>
+        <v>4.42</v>
       </c>
       <c r="Q28">
-        <v>3.25</v>
+        <v>2.36</v>
       </c>
       <c r="R28">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S28">
         <v>1.36</v>
@@ -4894,43 +4894,43 @@
         <v>2.88</v>
       </c>
       <c r="U28">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="V28">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W28">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X28">
         <v>1.06</v>
       </c>
       <c r="Y28">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z28">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="AA28">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AB28">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AC28">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="AD28">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AE28">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF28">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="AG28">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AK28">
-        <v>1.41</v>
+        <v>1.99</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="O29">
-        <v>3.58</v>
+        <v>3.22</v>
       </c>
       <c r="P29">
-        <v>4.42</v>
+        <v>4.09</v>
       </c>
       <c r="Q29">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="R29">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="S29">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="T29">
-        <v>2.88</v>
+        <v>2.44</v>
       </c>
       <c r="U29">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="V29">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="W29">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X29">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y29">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="Z29">
-        <v>3.3</v>
+        <v>2.87</v>
       </c>
       <c r="AA29">
-        <v>2.01</v>
+        <v>2.3</v>
       </c>
       <c r="AB29">
-        <v>1.81</v>
+        <v>1.52</v>
       </c>
       <c r="AC29">
-        <v>3.55</v>
+        <v>4.15</v>
       </c>
       <c r="AD29">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE29">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="AF29">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AG29">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AK29">
-        <v>1.99</v>
+        <v>1.75</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,22 +7481,22 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O44">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="P44">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="Q44">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="R44">
-        <v>2.49</v>
+        <v>2.56</v>
       </c>
       <c r="S44">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="T44">
         <v>4</v>
@@ -7505,7 +7505,7 @@
         <v>2.05</v>
       </c>
       <c r="V44">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="W44">
         <v>1.17</v>
@@ -7514,31 +7514,31 @@
         <v>1.02</v>
       </c>
       <c r="Y44">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Z44">
-        <v>5.66</v>
+        <v>5.85</v>
       </c>
       <c r="AA44">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AB44">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AC44">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AD44">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AE44">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AF44">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AG44">
-        <v>2.51</v>
+        <v>2.46</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK44">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,22 +7644,22 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="Q45">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="R45">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="S45">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="T45">
         <v>4</v>
@@ -7668,7 +7668,7 @@
         <v>2.05</v>
       </c>
       <c r="V45">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="W45">
         <v>1.17</v>
@@ -7677,31 +7677,31 @@
         <v>1.02</v>
       </c>
       <c r="Y45">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Z45">
-        <v>5.85</v>
+        <v>5.66</v>
       </c>
       <c r="AA45">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AB45">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AC45">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AD45">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AE45">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AF45">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AG45">
-        <v>2.46</v>
+        <v>2.51</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK45">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,31 +12697,31 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.51</v>
+        <v>2.1</v>
       </c>
       <c r="O76">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="P76">
-        <v>2.45</v>
+        <v>3.35</v>
       </c>
       <c r="Q76">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="R76">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="S76">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T76">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="U76">
-        <v>2.91</v>
+        <v>3.02</v>
       </c>
       <c r="V76">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W76">
         <v>1.02</v>
@@ -12730,31 +12730,31 @@
         <v>1.06</v>
       </c>
       <c r="Y76">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z76">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AA76">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AB76">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AC76">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="AD76">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE76">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF76">
         <v>1.8</v>
       </c>
       <c r="AG76">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK76">
-        <v>1.34</v>
+        <v>1.73</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,31 +12860,31 @@
         </is>
       </c>
       <c r="N77">
+        <v>2.51</v>
+      </c>
+      <c r="O77">
+        <v>3.3</v>
+      </c>
+      <c r="P77">
+        <v>2.45</v>
+      </c>
+      <c r="Q77">
+        <v>3.4</v>
+      </c>
+      <c r="R77">
         <v>2.1</v>
       </c>
-      <c r="O77">
-        <v>3.08</v>
-      </c>
-      <c r="P77">
-        <v>3.35</v>
-      </c>
-      <c r="Q77">
-        <v>2.5</v>
-      </c>
-      <c r="R77">
-        <v>1.95</v>
-      </c>
       <c r="S77">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T77">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="U77">
-        <v>3.02</v>
+        <v>2.91</v>
       </c>
       <c r="V77">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W77">
         <v>1.02</v>
@@ -12893,31 +12893,31 @@
         <v>1.06</v>
       </c>
       <c r="Y77">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z77">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AA77">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AB77">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AC77">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="AD77">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE77">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF77">
         <v>1.8</v>
       </c>
       <c r="AG77">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK77">
-        <v>1.73</v>
+        <v>1.34</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G161">
@@ -26552,64 +26552,64 @@
         </is>
       </c>
       <c r="N161">
-        <v>1.99</v>
+        <v>1.72</v>
       </c>
       <c r="O161">
-        <v>3.54</v>
+        <v>3.64</v>
       </c>
       <c r="P161">
-        <v>3.54</v>
+        <v>4.75</v>
       </c>
       <c r="Q161">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="R161">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="S161">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T161">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="U161">
-        <v>2.88</v>
+        <v>3.01</v>
       </c>
       <c r="V161">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="W161">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X161">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y161">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z161">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="AA161">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="AB161">
+        <v>1.78</v>
+      </c>
+      <c r="AC161">
+        <v>3.18</v>
+      </c>
+      <c r="AD161">
+        <v>1.27</v>
+      </c>
+      <c r="AE161">
+        <v>1.09</v>
+      </c>
+      <c r="AF161">
         <v>1.83</v>
       </c>
-      <c r="AC161">
-        <v>2.99</v>
-      </c>
-      <c r="AD161">
-        <v>1.3</v>
-      </c>
-      <c r="AE161">
-        <v>1.1</v>
-      </c>
-      <c r="AF161">
-        <v>1.75</v>
-      </c>
       <c r="AG161">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AK161">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G162">
@@ -26715,64 +26715,64 @@
         </is>
       </c>
       <c r="N162">
-        <v>1.72</v>
+        <v>2.47</v>
       </c>
       <c r="O162">
-        <v>3.64</v>
+        <v>3.3</v>
       </c>
       <c r="P162">
-        <v>4.75</v>
+        <v>2.74</v>
       </c>
       <c r="Q162">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R162">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S162">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T162">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U162">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="V162">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W162">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X162">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y162">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z162">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AA162">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AB162">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AC162">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AD162">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE162">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF162">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG162">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
@@ -26785,10 +26785,10 @@
         </is>
       </c>
       <c r="AJ162">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK162">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL162">
         <v>0</v>
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G163">
@@ -26878,64 +26878,64 @@
         </is>
       </c>
       <c r="N163">
-        <v>2.47</v>
+        <v>4.08</v>
       </c>
       <c r="O163">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="P163">
-        <v>2.74</v>
+        <v>1.84</v>
       </c>
       <c r="Q163">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R163">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S163">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T163">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U163">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V163">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W163">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X163">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y163">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z163">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA163">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AB163">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AC163">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD163">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE163">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF163">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG163">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
@@ -26948,10 +26948,10 @@
         </is>
       </c>
       <c r="AJ163">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK163">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G164">
@@ -27041,64 +27041,64 @@
         </is>
       </c>
       <c r="N164">
-        <v>4.08</v>
+        <v>4.18</v>
       </c>
       <c r="O164">
-        <v>3.58</v>
+        <v>3.52</v>
       </c>
       <c r="P164">
         <v>1.84</v>
       </c>
       <c r="Q164">
-        <v>4.2</v>
+        <v>4.32</v>
       </c>
       <c r="R164">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="S164">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T164">
         <v>2.69</v>
       </c>
       <c r="U164">
-        <v>2.77</v>
+        <v>3.05</v>
       </c>
       <c r="V164">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W164">
         <v>1.05</v>
       </c>
       <c r="X164">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y164">
         <v>1.33</v>
       </c>
       <c r="Z164">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AA164">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AB164">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AC164">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AD164">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AE164">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF164">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AG164">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH164" t="inlineStr">
         <is>
@@ -27111,10 +27111,10 @@
         </is>
       </c>
       <c r="AJ164">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK164">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AL164">
         <v>0</v>
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G165">
@@ -27204,80 +27204,80 @@
         </is>
       </c>
       <c r="N165">
-        <v>4.18</v>
+        <v>2.38</v>
       </c>
       <c r="O165">
-        <v>3.52</v>
+        <v>3.46</v>
       </c>
       <c r="P165">
-        <v>1.84</v>
+        <v>2.75</v>
       </c>
       <c r="Q165">
-        <v>4.32</v>
+        <v>2.84</v>
       </c>
       <c r="R165">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="S165">
+        <v>1.35</v>
+      </c>
+      <c r="T165">
+        <v>2.94</v>
+      </c>
+      <c r="U165">
+        <v>2.53</v>
+      </c>
+      <c r="V165">
+        <v>1.43</v>
+      </c>
+      <c r="W165">
+        <v>1.07</v>
+      </c>
+      <c r="X165">
+        <v>1.05</v>
+      </c>
+      <c r="Y165">
+        <v>1.25</v>
+      </c>
+      <c r="Z165">
+        <v>3.5</v>
+      </c>
+      <c r="AA165">
+        <v>1.78</v>
+      </c>
+      <c r="AB165">
+        <v>2</v>
+      </c>
+      <c r="AC165">
+        <v>3.02</v>
+      </c>
+      <c r="AD165">
+        <v>1.35</v>
+      </c>
+      <c r="AE165">
+        <v>1.11</v>
+      </c>
+      <c r="AF165">
+        <v>1.6</v>
+      </c>
+      <c r="AG165">
+        <v>2.05</v>
+      </c>
+      <c r="AH165" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI165" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ165">
         <v>1.41</v>
       </c>
-      <c r="T165">
-        <v>2.69</v>
-      </c>
-      <c r="U165">
-        <v>3.05</v>
-      </c>
-      <c r="V165">
-        <v>1.35</v>
-      </c>
-      <c r="W165">
-        <v>1.05</v>
-      </c>
-      <c r="X165">
-        <v>1.02</v>
-      </c>
-      <c r="Y165">
-        <v>1.33</v>
-      </c>
-      <c r="Z165">
-        <v>3.1</v>
-      </c>
-      <c r="AA165">
-        <v>2.05</v>
-      </c>
-      <c r="AB165">
-        <v>1.73</v>
-      </c>
-      <c r="AC165">
-        <v>3.6</v>
-      </c>
-      <c r="AD165">
-        <v>1.27</v>
-      </c>
-      <c r="AE165">
-        <v>1.08</v>
-      </c>
-      <c r="AF165">
-        <v>1.85</v>
-      </c>
-      <c r="AG165">
-        <v>1.85</v>
-      </c>
-      <c r="AH165" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI165" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ165">
-        <v>1.33</v>
-      </c>
       <c r="AK165">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AL165">
         <v>0</v>
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G166">
@@ -27367,34 +27367,34 @@
         </is>
       </c>
       <c r="N166">
-        <v>2.38</v>
+        <v>1.82</v>
       </c>
       <c r="O166">
-        <v>3.46</v>
+        <v>3.68</v>
       </c>
       <c r="P166">
-        <v>2.75</v>
+        <v>4.08</v>
       </c>
       <c r="Q166">
-        <v>2.84</v>
+        <v>2.62</v>
       </c>
       <c r="R166">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="S166">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T166">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="U166">
-        <v>2.53</v>
+        <v>2.64</v>
       </c>
       <c r="V166">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W166">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X166">
         <v>1.05</v>
@@ -27403,28 +27403,28 @@
         <v>1.25</v>
       </c>
       <c r="Z166">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA166">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="AB166">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AC166">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="AD166">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE166">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF166">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG166">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AH166" t="inlineStr">
         <is>
@@ -27437,10 +27437,10 @@
         </is>
       </c>
       <c r="AJ166">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AK166">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AL166">
         <v>0</v>
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G167">
@@ -27530,49 +27530,49 @@
         </is>
       </c>
       <c r="N167">
-        <v>1.82</v>
+        <v>1.99</v>
       </c>
       <c r="O167">
-        <v>3.68</v>
+        <v>3.54</v>
       </c>
       <c r="P167">
-        <v>4.08</v>
+        <v>3.54</v>
       </c>
       <c r="Q167">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="R167">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="S167">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T167">
-        <v>2.93</v>
+        <v>2.85</v>
       </c>
       <c r="U167">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="V167">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W167">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X167">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y167">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z167">
         <v>3.3</v>
       </c>
       <c r="AA167">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AB167">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC167">
         <v>2.99</v>
@@ -27600,10 +27600,10 @@
         </is>
       </c>
       <c r="AJ167">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK167">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AL167">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G196">
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,64 +32420,64 @@
         </is>
       </c>
       <c r="N197">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O197">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P197">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q197">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R197">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S197">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T197">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U197">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V197">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W197">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X197">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y197">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z197">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA197">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB197">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC197">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD197">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE197">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF197">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG197">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32490,10 +32490,10 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK197">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G198">
@@ -32583,64 +32583,64 @@
         </is>
       </c>
       <c r="N198">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="O198">
-        <v>3.58</v>
+        <v>3.65</v>
       </c>
       <c r="P198">
-        <v>2.95</v>
+        <v>3.34</v>
       </c>
       <c r="Q198">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="R198">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="S198">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="T198">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="U198">
-        <v>2.14</v>
+        <v>2.33</v>
       </c>
       <c r="V198">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="W198">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X198">
         <v>1.02</v>
       </c>
       <c r="Y198">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z198">
-        <v>4.1</v>
+        <v>4.48</v>
       </c>
       <c r="AA198">
         <v>1.64</v>
       </c>
       <c r="AB198">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="AC198">
-        <v>2.3</v>
+        <v>2.66</v>
       </c>
       <c r="AD198">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AE198">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF198">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AG198">
-        <v>2.23</v>
+        <v>2.43</v>
       </c>
       <c r="AH198" t="inlineStr">
         <is>
@@ -32653,10 +32653,10 @@
         </is>
       </c>
       <c r="AJ198">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK198">
-        <v>1.77</v>
+        <v>1.41</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G199">
@@ -32746,64 +32746,64 @@
         </is>
       </c>
       <c r="N199">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="O199">
-        <v>3.65</v>
+        <v>3.54</v>
       </c>
       <c r="P199">
-        <v>3.34</v>
+        <v>1.88</v>
       </c>
       <c r="Q199">
-        <v>2.7</v>
+        <v>4.36</v>
       </c>
       <c r="R199">
-        <v>2.26</v>
+        <v>2.39</v>
       </c>
       <c r="S199">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="T199">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="U199">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="V199">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="W199">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X199">
         <v>1.02</v>
       </c>
       <c r="Y199">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z199">
-        <v>4.48</v>
+        <v>4.35</v>
       </c>
       <c r="AA199">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="AB199">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="AC199">
-        <v>2.66</v>
+        <v>2.59</v>
       </c>
       <c r="AD199">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AE199">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF199">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="AG199">
-        <v>2.43</v>
+        <v>2.21</v>
       </c>
       <c r="AH199" t="inlineStr">
         <is>
@@ -32816,10 +32816,10 @@
         </is>
       </c>
       <c r="AJ199">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK199">
-        <v>1.41</v>
+        <v>1.19</v>
       </c>
       <c r="AL199">
         <v>0</v>
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G200">
@@ -32909,64 +32909,64 @@
         </is>
       </c>
       <c r="N200">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O200">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P200">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q200">
-        <v>4.36</v>
+        <v>0</v>
       </c>
       <c r="R200">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="S200">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T200">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U200">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V200">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W200">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X200">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y200">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z200">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AA200">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AB200">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AC200">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AD200">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE200">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF200">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG200">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AH200" t="inlineStr">
         <is>
@@ -32979,10 +32979,10 @@
         </is>
       </c>
       <c r="AJ200">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK200">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AL200">
         <v>0</v>

--- a/jogos_2026-08-08.xlsx
+++ b/jogos_2026-08-08.xlsx
@@ -1785,55 +1785,55 @@
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="R9">
-        <v>2.27</v>
+        <v>2.06</v>
       </c>
       <c r="S9">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="T9">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="U9">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="V9">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W9">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X9">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="Z9">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="AA9">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="AB9">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC9">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="AD9">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE9">
         <v>1.06</v>
       </c>
       <c r="AF9">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="AG9">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK9">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3406,40 +3406,40 @@
         </is>
       </c>
       <c r="N19">
-        <v>4.02</v>
+        <v>3.94</v>
       </c>
       <c r="O19">
-        <v>3.28</v>
+        <v>3.24</v>
       </c>
       <c r="P19">
         <v>2.03</v>
       </c>
       <c r="Q19">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="R19">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="S19">
         <v>1.54</v>
       </c>
       <c r="T19">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="U19">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="V19">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W19">
         <v>1.01</v>
       </c>
       <c r="X19">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Y19">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="Z19">
         <v>2.54</v>
@@ -3448,16 +3448,16 @@
         <v>2.42</v>
       </c>
       <c r="AB19">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AC19">
-        <v>4.7</v>
+        <v>5.09</v>
       </c>
       <c r="AD19">
         <v>1.16</v>
       </c>
       <c r="AE19">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AF19">
         <v>2.15</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.73</v>
+        <v>1.34</v>
       </c>
       <c r="AK19">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="O20">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="P20">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="Q20">
         <v>2.62</v>
@@ -3587,43 +3587,43 @@
         <v>1.33</v>
       </c>
       <c r="T20">
-        <v>2.94</v>
+        <v>2.73</v>
       </c>
       <c r="U20">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="V20">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W20">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X20">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y20">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z20">
         <v>3.72</v>
       </c>
       <c r="AA20">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AB20">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AC20">
         <v>3.08</v>
       </c>
       <c r="AD20">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE20">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF20">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AG20">
         <v>2.05</v>
@@ -3732,34 +3732,34 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="O21">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="P21">
-        <v>3.93</v>
+        <v>3.92</v>
       </c>
       <c r="Q21">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="R21">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S21">
         <v>1.33</v>
       </c>
       <c r="T21">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="U21">
         <v>2.62</v>
       </c>
       <c r="V21">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="W21">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X21">
         <v>1</v>
@@ -3768,19 +3768,19 @@
         <v>1.21</v>
       </c>
       <c r="Z21">
-        <v>3.82</v>
+        <v>3.62</v>
       </c>
       <c r="AA21">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AB21">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AC21">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="AD21">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AE21">
         <v>1.14</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK21">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,25 +3895,25 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.46</v>
+        <v>2.41</v>
       </c>
       <c r="O22">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="P22">
-        <v>3.11</v>
+        <v>2.93</v>
       </c>
       <c r="Q22">
         <v>2.96</v>
       </c>
       <c r="R22">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="S22">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="T22">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="U22">
         <v>3.34</v>
@@ -3928,31 +3928,31 @@
         <v>1.03</v>
       </c>
       <c r="Y22">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z22">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="AA22">
         <v>2.32</v>
       </c>
       <c r="AB22">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AC22">
-        <v>4.2</v>
+        <v>4.39</v>
       </c>
       <c r="AD22">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AE22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF22">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AG22">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AK22">
         <v>1.54</v>
@@ -4058,49 +4058,49 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="O23">
-        <v>3.98</v>
+        <v>3.8</v>
       </c>
       <c r="P23">
-        <v>5.89</v>
+        <v>5.85</v>
       </c>
       <c r="Q23">
         <v>2.13</v>
       </c>
       <c r="R23">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="S23">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="T23">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U23">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="V23">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W23">
         <v>1.04</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y23">
         <v>1.3</v>
       </c>
       <c r="Z23">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="AA23">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AB23">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AC23">
         <v>3.55</v>
@@ -4109,13 +4109,13 @@
         <v>1.28</v>
       </c>
       <c r="AE23">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF23">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AG23">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AK23">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,46 +4221,46 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="O24">
-        <v>4.3</v>
+        <v>4.35</v>
       </c>
       <c r="P24">
-        <v>6.29</v>
+        <v>6.35</v>
       </c>
       <c r="Q24">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="R24">
-        <v>2.46</v>
+        <v>2.35</v>
       </c>
       <c r="S24">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T24">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="U24">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="V24">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W24">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X24">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y24">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z24">
         <v>3.8</v>
       </c>
       <c r="AA24">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AB24">
         <v>2</v>
@@ -4269,16 +4269,16 @@
         <v>2.9</v>
       </c>
       <c r="AD24">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AE24">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF24">
         <v>1.89</v>
       </c>
       <c r="AG24">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AK24">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,61 +4710,61 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.67</v>
+        <v>1.78</v>
       </c>
       <c r="O27">
-        <v>3.22</v>
+        <v>3.58</v>
       </c>
       <c r="P27">
-        <v>2.58</v>
+        <v>4.42</v>
       </c>
       <c r="Q27">
-        <v>3.1</v>
+        <v>2.36</v>
       </c>
       <c r="R27">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="S27">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T27">
         <v>2.88</v>
       </c>
       <c r="U27">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="V27">
         <v>1.36</v>
       </c>
       <c r="W27">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y27">
+        <v>1.25</v>
+      </c>
+      <c r="Z27">
+        <v>3.3</v>
+      </c>
+      <c r="AA27">
+        <v>2.01</v>
+      </c>
+      <c r="AB27">
+        <v>1.81</v>
+      </c>
+      <c r="AC27">
+        <v>3.55</v>
+      </c>
+      <c r="AD27">
         <v>1.27</v>
       </c>
-      <c r="Z27">
-        <v>3.56</v>
-      </c>
-      <c r="AA27">
-        <v>1.93</v>
-      </c>
-      <c r="AB27">
-        <v>1.8</v>
-      </c>
-      <c r="AC27">
-        <v>3.4</v>
-      </c>
-      <c r="AD27">
-        <v>1.26</v>
-      </c>
       <c r="AE27">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF27">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="AG27">
         <v>1.85</v>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="AK27">
-        <v>1.39</v>
+        <v>1.99</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,61 +4873,61 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.78</v>
+        <v>2.67</v>
       </c>
       <c r="O28">
-        <v>3.58</v>
+        <v>3.22</v>
       </c>
       <c r="P28">
-        <v>4.42</v>
+        <v>2.58</v>
       </c>
       <c r="Q28">
-        <v>2.36</v>
+        <v>3.1</v>
       </c>
       <c r="R28">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="S28">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T28">
         <v>2.88</v>
       </c>
       <c r="U28">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="V28">
         <v>1.36</v>
       </c>
       <c r="W28">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X28">
+        <v>1.01</v>
+      </c>
+      <c r="Y28">
+        <v>1.27</v>
+      </c>
+      <c r="Z28">
+        <v>3.56</v>
+      </c>
+      <c r="AA28">
+        <v>1.93</v>
+      </c>
+      <c r="AB28">
+        <v>1.8</v>
+      </c>
+      <c r="AC28">
+        <v>3.4</v>
+      </c>
+      <c r="AD28">
+        <v>1.26</v>
+      </c>
+      <c r="AE28">
         <v>1.06</v>
       </c>
-      <c r="Y28">
-        <v>1.25</v>
-      </c>
-      <c r="Z28">
-        <v>3.3</v>
-      </c>
-      <c r="AA28">
-        <v>2.01</v>
-      </c>
-      <c r="AB28">
-        <v>1.81</v>
-      </c>
-      <c r="AC28">
-        <v>3.55</v>
-      </c>
-      <c r="AD28">
-        <v>1.27</v>
-      </c>
-      <c r="AE28">
-        <v>1.07</v>
-      </c>
       <c r="AF28">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AG28">
         <v>1.85</v>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.12</v>
+        <v>1.32</v>
       </c>
       <c r="AK28">
-        <v>1.99</v>
+        <v>1.39</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -6177,49 +6177,49 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="O36">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="P36">
-        <v>3.16</v>
+        <v>2.96</v>
       </c>
       <c r="Q36">
-        <v>2.6</v>
+        <v>2.51</v>
       </c>
       <c r="R36">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="S36">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T36">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U36">
         <v>2.35</v>
       </c>
       <c r="V36">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W36">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X36">
         <v>1.03</v>
       </c>
       <c r="Y36">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z36">
-        <v>4.89</v>
+        <v>4.5</v>
       </c>
       <c r="AA36">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AB36">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AC36">
         <v>2.29</v>
@@ -6231,7 +6231,7 @@
         <v>1.2</v>
       </c>
       <c r="AF36">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AG36">
         <v>2.5</v>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK36">
         <v>1.67</v>
@@ -6340,58 +6340,58 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="O37">
-        <v>4.35</v>
+        <v>3.74</v>
       </c>
       <c r="P37">
-        <v>5.86</v>
+        <v>5.46</v>
       </c>
       <c r="Q37">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="R37">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="S37">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T37">
         <v>2.99</v>
       </c>
       <c r="U37">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="V37">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="W37">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X37">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z37">
         <v>4.15</v>
       </c>
       <c r="AA37">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AB37">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AC37">
-        <v>2.47</v>
+        <v>2.63</v>
       </c>
       <c r="AD37">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE37">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF37">
         <v>1.67</v>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK37">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6512,22 +6512,22 @@
         <v>2.72</v>
       </c>
       <c r="Q38">
-        <v>3.13</v>
+        <v>2.99</v>
       </c>
       <c r="R38">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="S38">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T38">
-        <v>3.66</v>
+        <v>4</v>
       </c>
       <c r="U38">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="V38">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W38">
         <v>1.14</v>
@@ -6548,19 +6548,19 @@
         <v>2.55</v>
       </c>
       <c r="AC38">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD38">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AE38">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AF38">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AG38">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK38">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,55 +6666,55 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="O39">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P39">
         <v>4.26</v>
       </c>
       <c r="Q39">
-        <v>2.27</v>
+        <v>2.16</v>
       </c>
       <c r="R39">
         <v>2.38</v>
       </c>
       <c r="S39">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T39">
         <v>3.1</v>
       </c>
       <c r="U39">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="V39">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W39">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X39">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y39">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z39">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AA39">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB39">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AC39">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="AD39">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AE39">
         <v>1.14</v>
@@ -6723,7 +6723,7 @@
         <v>1.61</v>
       </c>
       <c r="AG39">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK39">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7970,80 +7970,80 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="O47">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P47">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="Q47">
-        <v>2.82</v>
+        <v>3.18</v>
       </c>
       <c r="R47">
-        <v>2.22</v>
+        <v>2.13</v>
       </c>
       <c r="S47">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="T47">
-        <v>3.18</v>
+        <v>3.02</v>
       </c>
       <c r="U47">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="V47">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="W47">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X47">
         <v>1.03</v>
       </c>
       <c r="Y47">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z47">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AA47">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB47">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AC47">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="AD47">
+        <v>1.38</v>
+      </c>
+      <c r="AE47">
+        <v>1.12</v>
+      </c>
+      <c r="AF47">
+        <v>1.57</v>
+      </c>
+      <c r="AG47">
+        <v>2.25</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ47">
+        <v>1.44</v>
+      </c>
+      <c r="AK47">
         <v>1.5</v>
-      </c>
-      <c r="AE47">
-        <v>1.2</v>
-      </c>
-      <c r="AF47">
-        <v>1.52</v>
-      </c>
-      <c r="AG47">
-        <v>2.3</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ47">
-        <v>1.22</v>
-      </c>
-      <c r="AK47">
-        <v>1.53</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,16 +8133,16 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="O48">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P48">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q48">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="R48">
         <v>2.4</v>
@@ -8151,7 +8151,7 @@
         <v>1.2</v>
       </c>
       <c r="T48">
-        <v>3.34</v>
+        <v>2.75</v>
       </c>
       <c r="U48">
         <v>1.94</v>
@@ -8160,37 +8160,37 @@
         <v>1.46</v>
       </c>
       <c r="W48">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X48">
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z48">
-        <v>4.65</v>
+        <v>3.3</v>
       </c>
       <c r="AA48">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AB48">
-        <v>2.29</v>
+        <v>1.96</v>
       </c>
       <c r="AC48">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="AD48">
         <v>1.47</v>
       </c>
       <c r="AE48">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AF48">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AG48">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8296,61 +8296,61 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="O49">
         <v>4.2</v>
       </c>
       <c r="P49">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="Q49">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="R49">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="S49">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T49">
-        <v>4</v>
+        <v>3.74</v>
       </c>
       <c r="U49">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="V49">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="W49">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X49">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Z49">
-        <v>5.35</v>
+        <v>4.95</v>
       </c>
       <c r="AA49">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AB49">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="AC49">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="AD49">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AE49">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AF49">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AG49">
         <v>2.38</v>
@@ -8369,7 +8369,7 @@
         <v>1.14</v>
       </c>
       <c r="AK49">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8468,49 +8468,49 @@
         <v>1.95</v>
       </c>
       <c r="Q50">
-        <v>3.3</v>
+        <v>3.59</v>
       </c>
       <c r="R50">
         <v>2.64</v>
       </c>
       <c r="S50">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="T50">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="U50">
-        <v>1.99</v>
+        <v>1.75</v>
       </c>
       <c r="V50">
         <v>1.73</v>
       </c>
       <c r="W50">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X50">
         <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Z50">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="AA50">
+        <v>1.25</v>
+      </c>
+      <c r="AB50">
+        <v>2.5</v>
+      </c>
+      <c r="AC50">
+        <v>1.67</v>
+      </c>
+      <c r="AD50">
+        <v>1.85</v>
+      </c>
+      <c r="AE50">
         <v>1.29</v>
-      </c>
-      <c r="AB50">
-        <v>3</v>
-      </c>
-      <c r="AC50">
-        <v>1.74</v>
-      </c>
-      <c r="AD50">
-        <v>1.83</v>
-      </c>
-      <c r="AE50">
-        <v>1.22</v>
       </c>
       <c r="AF50">
         <v>1.36</v>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.67</v>
+        <v>1.17</v>
       </c>
       <c r="AK50">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="O51">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="P51">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="Q51">
         <v>1.85</v>
@@ -8637,49 +8637,49 @@
         <v>2.48</v>
       </c>
       <c r="S51">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T51">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="U51">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="V51">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="W51">
         <v>1.14</v>
       </c>
       <c r="X51">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="Z51">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AA51">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AB51">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="AC51">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="AD51">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AE51">
         <v>1.24</v>
       </c>
       <c r="AF51">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG51">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>1.14</v>
       </c>
       <c r="AK51">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -9274,19 +9274,19 @@
         </is>
       </c>
       <c r="N55">
-        <v>3.09</v>
+        <v>2.96</v>
       </c>
       <c r="O55">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="P55">
-        <v>2.57</v>
+        <v>2.31</v>
       </c>
       <c r="Q55">
-        <v>3.94</v>
+        <v>3.45</v>
       </c>
       <c r="R55">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="S55">
         <v>1.52</v>
@@ -9316,13 +9316,13 @@
         <v>2.36</v>
       </c>
       <c r="AB55">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="AC55">
         <v>4.25</v>
       </c>
       <c r="AD55">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE55">
         <v>1.01</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="O56">
         <v>3.4</v>
@@ -9446,55 +9446,55 @@
         <v>2.3</v>
       </c>
       <c r="Q56">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R56">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="S56">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T56">
-        <v>2.85</v>
+        <v>3.09</v>
       </c>
       <c r="U56">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="V56">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W56">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X56">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z56">
-        <v>3.5</v>
+        <v>3.72</v>
       </c>
       <c r="AA56">
+        <v>1.8</v>
+      </c>
+      <c r="AB56">
         <v>1.87</v>
       </c>
-      <c r="AB56">
-        <v>1.83</v>
-      </c>
       <c r="AC56">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD56">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE56">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF56">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AG56">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK56">
         <v>1.36</v>
@@ -9600,61 +9600,61 @@
         </is>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q57">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="R57">
         <v>2.15</v>
       </c>
       <c r="S57">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T57">
-        <v>2.91</v>
+        <v>2.73</v>
       </c>
       <c r="U57">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="V57">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W57">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X57">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y57">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z57">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AA57">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AB57">
         <v>1.81</v>
       </c>
       <c r="AC57">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AD57">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AE57">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF57">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AG57">
         <v>1.95</v>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK57">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -10424,10 +10424,10 @@
         <v>3.16</v>
       </c>
       <c r="Q62">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="R62">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S62">
         <v>1.25</v>
@@ -10593,16 +10593,16 @@
         <v>2.23</v>
       </c>
       <c r="S63">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="T63">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="U63">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="V63">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W63">
         <v>1.06</v>
@@ -10611,19 +10611,19 @@
         <v>1.06</v>
       </c>
       <c r="Y63">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Z63">
-        <v>3.5</v>
+        <v>2.65</v>
       </c>
       <c r="AA63">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="AB63">
         <v>1.87</v>
       </c>
       <c r="AC63">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="AD63">
         <v>1.33</v>
@@ -10632,7 +10632,7 @@
         <v>1.06</v>
       </c>
       <c r="AF63">
-        <v>1.72</v>
+        <v>2.14</v>
       </c>
       <c r="AG63">
         <v>1.7</v>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.25</v>
+        <v>1.91</v>
       </c>
       <c r="AK63">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="O64">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="P64">
-        <v>3.41</v>
+        <v>3.15</v>
       </c>
       <c r="Q64">
         <v>2.38</v>
@@ -10759,13 +10759,13 @@
         <v>1.25</v>
       </c>
       <c r="T64">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="U64">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V64">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W64">
         <v>1.12</v>
@@ -10780,10 +10780,10 @@
         <v>4.4</v>
       </c>
       <c r="AA64">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AB64">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC64">
         <v>2.5</v>
@@ -10792,13 +10792,13 @@
         <v>1.44</v>
       </c>
       <c r="AE64">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF64">
         <v>1.5</v>
       </c>
       <c r="AG64">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK64">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O65">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T65">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U65">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="W65">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AD65">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE65">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK65">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O66">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S66">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T66">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U66">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V66">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W66">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X66">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z66">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA66">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB66">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC66">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD66">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE66">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF66">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG66">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK66">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11230,31 +11230,31 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.08</v>
+        <v>2.37</v>
       </c>
       <c r="O67">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="P67">
-        <v>3.21</v>
+        <v>2.5</v>
       </c>
       <c r="Q67">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="R67">
         <v>2.4</v>
       </c>
       <c r="S67">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T67">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="U67">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="V67">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W67">
         <v>1.12</v>
@@ -11266,19 +11266,19 @@
         <v>1.14</v>
       </c>
       <c r="Z67">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="AA67">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB67">
+        <v>2.36</v>
+      </c>
+      <c r="AC67">
         <v>2.3</v>
       </c>
-      <c r="AC67">
-        <v>2.4</v>
-      </c>
       <c r="AD67">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AE67">
         <v>1.17</v>
@@ -11303,7 +11303,7 @@
         <v>1.46</v>
       </c>
       <c r="AK67">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="O70">
-        <v>4.85</v>
+        <v>5.7</v>
       </c>
       <c r="P70">
-        <v>7.65</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="Q70">
         <v>1.68</v>
@@ -11734,50 +11734,50 @@
         <v>2.61</v>
       </c>
       <c r="S70">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T70">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="U70">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="V70">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W70">
         <v>1.14</v>
       </c>
       <c r="X70">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y70">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z70">
-        <v>4.95</v>
+        <v>4.78</v>
       </c>
       <c r="AA70">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AB70">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AC70">
-        <v>2.27</v>
+        <v>2.34</v>
       </c>
       <c r="AD70">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AE70">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF70">
+        <v>1.85</v>
+      </c>
+      <c r="AG70">
         <v>1.84</v>
       </c>
-      <c r="AG70">
-        <v>1.85</v>
-      </c>
       <c r="AH70" t="inlineStr">
         <is>
           <t>[]</t>
@@ -11789,7 +11789,7 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AK70">
         <v>3.38</v>
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="O71">
-        <v>3.64</v>
+        <v>4.05</v>
       </c>
       <c r="P71">
-        <v>3.26</v>
+        <v>3.8</v>
       </c>
       <c r="Q71">
         <v>2.3</v>
       </c>
       <c r="R71">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="S71">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T71">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U71">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="V71">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W71">
         <v>1.1</v>
       </c>
       <c r="X71">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y71">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z71">
-        <v>3.48</v>
+        <v>3.77</v>
       </c>
       <c r="AA71">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="AB71">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="AC71">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="AD71">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE71">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF71">
         <v>1.73</v>
       </c>
       <c r="AG71">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK71">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12045,37 +12045,37 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="O72">
-        <v>3.82</v>
+        <v>3.6</v>
       </c>
       <c r="P72">
-        <v>4.81</v>
+        <v>3.95</v>
       </c>
       <c r="Q72">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="R72">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="S72">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T72">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U72">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="V72">
         <v>1.44</v>
       </c>
       <c r="W72">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X72">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y72">
         <v>1.21</v>
@@ -12084,25 +12084,25 @@
         <v>3.58</v>
       </c>
       <c r="AA72">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AB72">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AC72">
-        <v>3.03</v>
+        <v>2.88</v>
       </c>
       <c r="AD72">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AE72">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF72">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG72">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK72">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>7.9</v>
+        <v>4.8</v>
       </c>
       <c r="O73">
-        <v>5.05</v>
+        <v>4.55</v>
       </c>
       <c r="P73">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="Q73">
-        <v>7</v>
+        <v>5.63</v>
       </c>
       <c r="R73">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="S73">
         <v>1.25</v>
       </c>
       <c r="T73">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U73">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="V73">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="W73">
         <v>1.15</v>
       </c>
       <c r="X73">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y73">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z73">
-        <v>4.65</v>
+        <v>4.55</v>
       </c>
       <c r="AA73">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AB73">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="AC73">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AD73">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AE73">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AF73">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AG73">
-        <v>2.01</v>
+        <v>2.08</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>2.63</v>
+        <v>2.41</v>
       </c>
       <c r="AK73">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12371,61 +12371,61 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.21</v>
+        <v>1.95</v>
       </c>
       <c r="O74">
-        <v>3.02</v>
+        <v>3.25</v>
       </c>
       <c r="P74">
-        <v>3.17</v>
+        <v>3.25</v>
       </c>
       <c r="Q74">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="R74">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="S74">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T74">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="U74">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="V74">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W74">
         <v>1.04</v>
       </c>
       <c r="X74">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y74">
         <v>1.25</v>
       </c>
       <c r="Z74">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AA74">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AB74">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AC74">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="AD74">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AE74">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF74">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG74">
         <v>2</v>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK74">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12534,31 +12534,31 @@
         </is>
       </c>
       <c r="N75">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="O75">
-        <v>3.13</v>
+        <v>3.4</v>
       </c>
       <c r="P75">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="Q75">
-        <v>4.18</v>
+        <v>4.55</v>
       </c>
       <c r="R75">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S75">
         <v>1.39</v>
       </c>
       <c r="T75">
-        <v>2.85</v>
+        <v>2.66</v>
       </c>
       <c r="U75">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="V75">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W75">
         <v>1.03</v>
@@ -12567,31 +12567,31 @@
         <v>1.06</v>
       </c>
       <c r="Y75">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z75">
         <v>3.08</v>
       </c>
       <c r="AA75">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AB75">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AC75">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AD75">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE75">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF75">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG75">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK75">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12697,46 +12697,46 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="O76">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="P76">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="Q76">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="R76">
         <v>1.95</v>
       </c>
       <c r="S76">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T76">
         <v>2.75</v>
       </c>
       <c r="U76">
-        <v>3.02</v>
+        <v>2.86</v>
       </c>
       <c r="V76">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="W76">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X76">
         <v>1.06</v>
       </c>
       <c r="Y76">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Z76">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="AA76">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="AB76">
         <v>1.67</v>
@@ -12745,16 +12745,16 @@
         <v>3.58</v>
       </c>
       <c r="AD76">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE76">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF76">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG76">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK76">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.51</v>
+        <v>2.8</v>
       </c>
       <c r="O77">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P77">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="Q77">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R77">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="S77">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T77">
-        <v>2.85</v>
+        <v>2.57</v>
       </c>
       <c r="U77">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="V77">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W77">
+        <v>1.08</v>
+      </c>
+      <c r="X77">
         <v>1.02</v>
       </c>
-      <c r="X77">
-        <v>1.06</v>
-      </c>
       <c r="Y77">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z77">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AA77">
         <v>2</v>
       </c>
       <c r="AB77">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AC77">
         <v>3.6</v>
       </c>
       <c r="AD77">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE77">
         <v>1.08</v>
       </c>
       <c r="AF77">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AG77">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AK77">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13032,16 +13032,16 @@
         <v>0</v>
       </c>
       <c r="Q78">
-        <v>3.43</v>
+        <v>3.1</v>
       </c>
       <c r="R78">
         <v>2.08</v>
       </c>
       <c r="S78">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="T78">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="U78">
         <v>3.05</v>
@@ -13062,7 +13062,7 @@
         <v>2.83</v>
       </c>
       <c r="AA78">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AB78">
         <v>1.68</v>
@@ -13096,7 +13096,7 @@
         <v>1.36</v>
       </c>
       <c r="AK78">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13195,55 +13195,55 @@
         <v>0</v>
       </c>
       <c r="Q79">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="R79">
-        <v>2.28</v>
+        <v>2.04</v>
       </c>
       <c r="S79">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="T79">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="U79">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="V79">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W79">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X79">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y79">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z79">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AA79">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="AB79">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC79">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="AD79">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE79">
         <v>1.06</v>
       </c>
       <c r="AF79">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AG79">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK79">
-        <v>2.39</v>
+        <v>2.46</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13358,22 +13358,22 @@
         <v>0</v>
       </c>
       <c r="Q80">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="R80">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="S80">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T80">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="U80">
-        <v>3.21</v>
+        <v>3.16</v>
       </c>
       <c r="V80">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W80">
         <v>1.01</v>
@@ -13382,31 +13382,31 @@
         <v>1.01</v>
       </c>
       <c r="Y80">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z80">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AA80">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AB80">
         <v>1.69</v>
       </c>
       <c r="AC80">
-        <v>3.88</v>
+        <v>3.8</v>
       </c>
       <c r="AD80">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AE80">
         <v>1.02</v>
       </c>
       <c r="AF80">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AG80">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK80">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="O83">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="P83">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="Q83">
         <v>2.9</v>
@@ -13853,49 +13853,49 @@
         <v>2.25</v>
       </c>
       <c r="S83">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T83">
-        <v>3.02</v>
+        <v>2.77</v>
       </c>
       <c r="U83">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="V83">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W83">
         <v>1.06</v>
       </c>
       <c r="X83">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y83">
         <v>1.25</v>
       </c>
       <c r="Z83">
-        <v>3.62</v>
+        <v>3.7</v>
       </c>
       <c r="AA83">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AB83">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC83">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AD83">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE83">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF83">
         <v>1.62</v>
       </c>
       <c r="AG83">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK83">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14001,80 +14001,80 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="O84">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="P84">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="Q84">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="R84">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="S84">
         <v>1.36</v>
       </c>
       <c r="T84">
-        <v>3.06</v>
+        <v>2.7</v>
       </c>
       <c r="U84">
         <v>2.81</v>
       </c>
       <c r="V84">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W84">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X84">
         <v>1</v>
       </c>
       <c r="Y84">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z84">
-        <v>3.66</v>
+        <v>3.5</v>
       </c>
       <c r="AA84">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB84">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AC84">
         <v>3.05</v>
       </c>
       <c r="AD84">
+        <v>1.35</v>
+      </c>
+      <c r="AE84">
+        <v>1.09</v>
+      </c>
+      <c r="AF84">
+        <v>1.7</v>
+      </c>
+      <c r="AG84">
+        <v>2.08</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ84">
         <v>1.29</v>
       </c>
-      <c r="AE84">
-        <v>1.12</v>
-      </c>
-      <c r="AF84">
-        <v>1.67</v>
-      </c>
-      <c r="AG84">
-        <v>2.05</v>
-      </c>
-      <c r="AH84" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI84" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ84">
-        <v>1.36</v>
-      </c>
       <c r="AK84">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14173,10 +14173,10 @@
         <v>3.25</v>
       </c>
       <c r="Q85">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="R85">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="S85">
         <v>1.4</v>
@@ -14188,16 +14188,16 @@
         <v>3.03</v>
       </c>
       <c r="V85">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W85">
         <v>1.02</v>
       </c>
       <c r="X85">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y85">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z85">
         <v>3.21</v>
@@ -14206,19 +14206,19 @@
         <v>2.04</v>
       </c>
       <c r="AB85">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC85">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="AD85">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE85">
         <v>1.04</v>
       </c>
       <c r="AF85">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AG85">
         <v>1.95</v>
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="O86">
-        <v>4.95</v>
+        <v>4.6</v>
       </c>
       <c r="P86">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Q86">
+        <v>1.85</v>
+      </c>
+      <c r="R86">
+        <v>2.8</v>
+      </c>
+      <c r="S86">
+        <v>1.15</v>
+      </c>
+      <c r="T86">
+        <v>4.5</v>
+      </c>
+      <c r="U86">
         <v>1.83</v>
       </c>
-      <c r="R86">
-        <v>2.7</v>
-      </c>
-      <c r="S86">
-        <v>1.18</v>
-      </c>
-      <c r="T86">
-        <v>4.4</v>
-      </c>
-      <c r="U86">
-        <v>2</v>
-      </c>
       <c r="V86">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="W86">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X86">
         <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z86">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="AA86">
         <v>1.32</v>
       </c>
       <c r="AB86">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="AC86">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="AD86">
-        <v>1.78</v>
+        <v>1.92</v>
       </c>
       <c r="AE86">
         <v>1.36</v>
       </c>
       <c r="AF86">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AG86">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK86">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14499,10 +14499,10 @@
         <v>0</v>
       </c>
       <c r="Q87">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="R87">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="S87">
         <v>1.27</v>
@@ -14517,22 +14517,22 @@
         <v>1.6</v>
       </c>
       <c r="W87">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X87">
         <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z87">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="AA87">
         <v>1.59</v>
       </c>
       <c r="AB87">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AC87">
         <v>2.8</v>
@@ -14541,7 +14541,7 @@
         <v>1.38</v>
       </c>
       <c r="AE87">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AF87">
         <v>2.02</v>
@@ -14560,7 +14560,7 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AK87">
         <v>3.34</v>
@@ -14819,61 +14819,61 @@
         <v>2.3</v>
       </c>
       <c r="O89">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P89">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="Q89">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="R89">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="S89">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="T89">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U89">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="V89">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="W89">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X89">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y89">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z89">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AA89">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AB89">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="AC89">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="AD89">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE89">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF89">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG89">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>1.22</v>
       </c>
       <c r="AK89">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
+        <v>2.46</v>
+      </c>
+      <c r="O90">
+        <v>3.3</v>
+      </c>
+      <c r="P90">
         <v>2.87</v>
       </c>
-      <c r="O90">
-        <v>3.58</v>
-      </c>
-      <c r="P90">
-        <v>2.48</v>
-      </c>
       <c r="Q90">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="R90">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S90">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="T90">
-        <v>2.73</v>
+        <v>2.95</v>
       </c>
       <c r="U90">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="V90">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W90">
+        <v>1.05</v>
+      </c>
+      <c r="X90">
+        <v>1.05</v>
+      </c>
+      <c r="Y90">
+        <v>1.26</v>
+      </c>
+      <c r="Z90">
+        <v>3.5</v>
+      </c>
+      <c r="AA90">
+        <v>1.97</v>
+      </c>
+      <c r="AB90">
+        <v>1.8</v>
+      </c>
+      <c r="AC90">
+        <v>3.3</v>
+      </c>
+      <c r="AD90">
+        <v>1.29</v>
+      </c>
+      <c r="AE90">
         <v>1.06</v>
-      </c>
-      <c r="X90">
-        <v>1.01</v>
-      </c>
-      <c r="Y90">
-        <v>1.29</v>
-      </c>
-      <c r="Z90">
-        <v>3.18</v>
-      </c>
-      <c r="AA90">
-        <v>1.91</v>
-      </c>
-      <c r="AB90">
-        <v>1.79</v>
-      </c>
-      <c r="AC90">
-        <v>3.18</v>
-      </c>
-      <c r="AD90">
-        <v>1.3</v>
-      </c>
-      <c r="AE90">
-        <v>1.07</v>
       </c>
       <c r="AF90">
         <v>1.7</v>
       </c>
       <c r="AG90">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="O91">
-        <v>4.73</v>
+        <v>5</v>
       </c>
       <c r="P91">
-        <v>5.76</v>
+        <v>5.75</v>
       </c>
       <c r="Q91">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="R91">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="S91">
         <v>1.19</v>
       </c>
       <c r="T91">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="U91">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="V91">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="W91">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X91">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y91">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z91">
-        <v>6.07</v>
+        <v>5.75</v>
       </c>
       <c r="AA91">
         <v>1.4</v>
       </c>
       <c r="AB91">
-        <v>2.85</v>
+        <v>2.68</v>
       </c>
       <c r="AC91">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AD91">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AE91">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AF91">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AG91">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AK91">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15314,46 +15314,46 @@
         <v>2.06</v>
       </c>
       <c r="Q92">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="R92">
         <v>2.5</v>
       </c>
       <c r="S92">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T92">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="U92">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="V92">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W92">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X92">
         <v>1.02</v>
       </c>
       <c r="Y92">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z92">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AA92">
         <v>1.4</v>
       </c>
       <c r="AB92">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AC92">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AD92">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AE92">
         <v>1.3</v>
@@ -15362,7 +15362,7 @@
         <v>1.36</v>
       </c>
       <c r="AG92">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,7 +15375,7 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK92">
         <v>1.4</v>
@@ -15957,49 +15957,49 @@
         </is>
       </c>
       <c r="N96">
-        <v>4.43</v>
+        <v>4.5</v>
       </c>
       <c r="O96">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P96">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="Q96">
-        <v>4.17</v>
+        <v>4.5</v>
       </c>
       <c r="R96">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="S96">
         <v>1.36</v>
       </c>
       <c r="T96">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U96">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="V96">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W96">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X96">
         <v>1.05</v>
       </c>
       <c r="Y96">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="Z96">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AA96">
         <v>1.83</v>
       </c>
       <c r="AB96">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC96">
         <v>2.92</v>
@@ -16008,13 +16008,13 @@
         <v>1.3</v>
       </c>
       <c r="AE96">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF96">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AG96">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.24</v>
+        <v>1.91</v>
       </c>
       <c r="AK96">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16129,19 +16129,19 @@
         <v>0</v>
       </c>
       <c r="Q97">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="R97">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="S97">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="T97">
-        <v>2.77</v>
+        <v>2.55</v>
       </c>
       <c r="U97">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="V97">
         <v>1.36</v>
@@ -16150,34 +16150,34 @@
         <v>1.04</v>
       </c>
       <c r="X97">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y97">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="Z97">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA97">
         <v>2</v>
       </c>
       <c r="AB97">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AC97">
         <v>3.2</v>
       </c>
       <c r="AD97">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AE97">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF97">
         <v>1.73</v>
       </c>
       <c r="AG97">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AK97">
         <v>1.5</v>
@@ -16446,25 +16446,25 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.49</v>
+        <v>2</v>
       </c>
       <c r="O99">
-        <v>3.36</v>
+        <v>3.2</v>
       </c>
       <c r="P99">
-        <v>2.68</v>
+        <v>3.3</v>
       </c>
       <c r="Q99">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="R99">
         <v>2.1</v>
       </c>
       <c r="S99">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T99">
-        <v>2.98</v>
+        <v>2.7</v>
       </c>
       <c r="U99">
         <v>2.89</v>
@@ -16473,22 +16473,22 @@
         <v>1.39</v>
       </c>
       <c r="W99">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X99">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y99">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z99">
         <v>3.3</v>
       </c>
       <c r="AA99">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AB99">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AC99">
         <v>3.24</v>
@@ -16497,13 +16497,13 @@
         <v>1.3</v>
       </c>
       <c r="AE99">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF99">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AG99">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>1.28</v>
       </c>
       <c r="AK99">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16609,19 +16609,19 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="O100">
-        <v>4.94</v>
+        <v>4.45</v>
       </c>
       <c r="P100">
-        <v>6.51</v>
+        <v>6</v>
       </c>
       <c r="Q100">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="R100">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="S100">
         <v>1.26</v>
@@ -16630,10 +16630,10 @@
         <v>3.54</v>
       </c>
       <c r="U100">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="V100">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="W100">
         <v>1.13</v>
@@ -16642,22 +16642,22 @@
         <v>1.01</v>
       </c>
       <c r="Y100">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z100">
-        <v>4.98</v>
+        <v>4.85</v>
       </c>
       <c r="AA100">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AB100">
         <v>2.36</v>
       </c>
       <c r="AC100">
-        <v>2.48</v>
+        <v>2.39</v>
       </c>
       <c r="AD100">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AE100">
         <v>1.19</v>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AK100">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16944,10 +16944,10 @@
         <v>0</v>
       </c>
       <c r="Q102">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="R102">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="S102">
         <v>1.47</v>
@@ -16962,34 +16962,34 @@
         <v>1.29</v>
       </c>
       <c r="W102">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X102">
         <v>1.04</v>
       </c>
       <c r="Y102">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="Z102">
-        <v>2.65</v>
+        <v>3.35</v>
       </c>
       <c r="AA102">
         <v>2.32</v>
       </c>
       <c r="AB102">
-        <v>1.58</v>
+        <v>1.83</v>
       </c>
       <c r="AC102">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="AD102">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AE102">
         <v>1.02</v>
       </c>
       <c r="AF102">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AG102">
         <v>1.73</v>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AK102">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O132">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P132">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q132">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R132">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S132">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T132">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U132">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V132">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W132">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X132">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y132">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z132">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA132">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB132">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC132">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AD132">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE132">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF132">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG132">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK132">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -24922,64 +24922,64 @@
         </is>
       </c>
       <c r="N151">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O151">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P151">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="Q151">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="R151">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S151">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T151">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U151">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V151">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W151">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X151">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y151">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z151">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="AA151">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB151">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AC151">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD151">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE151">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF151">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG151">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
@@ -24992,10 +24992,10 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK151">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AL151">
         <v>0</v>
@@ -26102,10 +26102,10 @@
         <v>0</v>
       </c>
       <c r="AA158">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB158">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC158">
         <v>0</v>
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G212">
@@ -34865,64 +34865,64 @@
         </is>
       </c>
       <c r="N212">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="O212">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P212">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q212">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="R212">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S212">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="T212">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="U212">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="V212">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W212">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X212">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y212">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z212">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA212">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB212">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC212">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AD212">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE212">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF212">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG212">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH212" t="inlineStr">
         <is>
@@ -34935,10 +34935,10 @@
         </is>
       </c>
       <c r="AJ212">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK212">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AL212">
         <v>0</v>
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G213">
@@ -35028,64 +35028,64 @@
         </is>
       </c>
       <c r="N213">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="O213">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P213">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q213">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="R213">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S213">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T213">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="U213">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V213">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W213">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X213">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y213">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z213">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA213">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB213">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC213">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD213">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE213">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF213">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG213">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH213" t="inlineStr">
         <is>
@@ -35098,10 +35098,10 @@
         </is>
       </c>
       <c r="AJ213">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK213">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL213">
         <v>0</v>

--- a/jogos_2026-08-08.xlsx
+++ b/jogos_2026-08-08.xlsx
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>3.81</v>
+        <v>3.75</v>
       </c>
       <c r="O25">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="P25">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="Q25">
         <v>3.61</v>
@@ -4402,31 +4402,31 @@
         <v>1.35</v>
       </c>
       <c r="T25">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="U25">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="V25">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W25">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X25">
         <v>1.05</v>
       </c>
       <c r="Y25">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z25">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AA25">
         <v>1.85</v>
       </c>
       <c r="AB25">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AC25">
         <v>3</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.85</v>
+        <v>1.23</v>
       </c>
       <c r="AK25">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,37 +4547,37 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="O26">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="P26">
-        <v>2.51</v>
+        <v>2.31</v>
       </c>
       <c r="Q26">
         <v>3.25</v>
       </c>
       <c r="R26">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S26">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T26">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="U26">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="V26">
         <v>1.38</v>
       </c>
       <c r="W26">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X26">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y26">
         <v>1.28</v>
@@ -4592,19 +4592,19 @@
         <v>1.73</v>
       </c>
       <c r="AC26">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="AD26">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AE26">
         <v>1.08</v>
       </c>
       <c r="AF26">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AG26">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK26">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,19 +4710,19 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.78</v>
+        <v>2.67</v>
       </c>
       <c r="O27">
-        <v>3.58</v>
+        <v>3.22</v>
       </c>
       <c r="P27">
-        <v>4.42</v>
+        <v>2.58</v>
       </c>
       <c r="Q27">
-        <v>2.36</v>
+        <v>3.32</v>
       </c>
       <c r="R27">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="S27">
         <v>1.36</v>
@@ -4737,37 +4737,37 @@
         <v>1.36</v>
       </c>
       <c r="W27">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X27">
+        <v>1.01</v>
+      </c>
+      <c r="Y27">
+        <v>1.27</v>
+      </c>
+      <c r="Z27">
+        <v>2.95</v>
+      </c>
+      <c r="AA27">
+        <v>1.95</v>
+      </c>
+      <c r="AB27">
+        <v>1.82</v>
+      </c>
+      <c r="AC27">
+        <v>3.4</v>
+      </c>
+      <c r="AD27">
+        <v>1.26</v>
+      </c>
+      <c r="AE27">
         <v>1.06</v>
       </c>
-      <c r="Y27">
-        <v>1.25</v>
-      </c>
-      <c r="Z27">
-        <v>3.3</v>
-      </c>
-      <c r="AA27">
-        <v>2.01</v>
-      </c>
-      <c r="AB27">
-        <v>1.81</v>
-      </c>
-      <c r="AC27">
-        <v>3.55</v>
-      </c>
-      <c r="AD27">
-        <v>1.27</v>
-      </c>
-      <c r="AE27">
-        <v>1.07</v>
-      </c>
       <c r="AF27">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AG27">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.12</v>
+        <v>1.32</v>
       </c>
       <c r="AK27">
-        <v>1.99</v>
+        <v>1.44</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,80 +4873,80 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.67</v>
+        <v>1.74</v>
       </c>
       <c r="O28">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="P28">
-        <v>2.58</v>
+        <v>4.5</v>
       </c>
       <c r="Q28">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="R28">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="S28">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T28">
+        <v>2.84</v>
+      </c>
+      <c r="U28">
         <v>2.88</v>
       </c>
-      <c r="U28">
-        <v>2.92</v>
-      </c>
       <c r="V28">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W28">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X28">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y28">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z28">
-        <v>3.56</v>
+        <v>2.99</v>
       </c>
       <c r="AA28">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="AB28">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC28">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="AD28">
+        <v>1.28</v>
+      </c>
+      <c r="AE28">
+        <v>1.05</v>
+      </c>
+      <c r="AF28">
+        <v>1.83</v>
+      </c>
+      <c r="AG28">
+        <v>1.83</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28">
         <v>1.26</v>
       </c>
-      <c r="AE28">
-        <v>1.06</v>
-      </c>
-      <c r="AF28">
-        <v>1.71</v>
-      </c>
-      <c r="AG28">
-        <v>1.85</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28">
-        <v>1.32</v>
-      </c>
       <c r="AK28">
-        <v>1.39</v>
+        <v>2</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,58 +5036,58 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="O29">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="P29">
-        <v>4.09</v>
+        <v>4.1</v>
       </c>
       <c r="Q29">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="R29">
         <v>2</v>
       </c>
       <c r="S29">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="T29">
-        <v>2.44</v>
+        <v>2.63</v>
       </c>
       <c r="U29">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="V29">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W29">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X29">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y29">
         <v>1.42</v>
       </c>
       <c r="Z29">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="AA29">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AB29">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AC29">
-        <v>4.15</v>
+        <v>4.33</v>
       </c>
       <c r="AD29">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AE29">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF29">
         <v>2.05</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AK29">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="O32">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P32">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="Q32">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="R32">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="S32">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="T32">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="U32">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="V32">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W32">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X32">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="Z32">
         <v>3.2</v>
       </c>
       <c r="AA32">
-        <v>1.87</v>
+        <v>2.03</v>
       </c>
       <c r="AB32">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AC32">
-        <v>3.48</v>
+        <v>3.45</v>
       </c>
       <c r="AD32">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE32">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF32">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AG32">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK32">
         <v>1.7</v>
@@ -5697,25 +5697,25 @@
         <v>1.92</v>
       </c>
       <c r="Q33">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="R33">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="S33">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="T33">
         <v>4</v>
       </c>
       <c r="U33">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="V33">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="W33">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X33">
         <v>1.02</v>
@@ -5727,25 +5727,25 @@
         <v>5.67</v>
       </c>
       <c r="AA33">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AB33">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="AC33">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="AD33">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AE33">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AF33">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AG33">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK33">
         <v>1.2</v>
@@ -5860,52 +5860,52 @@
         <v>3.09</v>
       </c>
       <c r="Q34">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="R34">
         <v>2.3</v>
       </c>
       <c r="S34">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T34">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U34">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="V34">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="W34">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X34">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y34">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z34">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="AA34">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AB34">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="AC34">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="AD34">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AE34">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF34">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="AG34">
         <v>2.25</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK34">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,61 +6014,61 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O35">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P35">
         <v>2.6</v>
       </c>
       <c r="Q35">
-        <v>3.13</v>
+        <v>2.8</v>
       </c>
       <c r="R35">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S35">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T35">
         <v>3.2</v>
       </c>
       <c r="U35">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="V35">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W35">
         <v>1.06</v>
       </c>
       <c r="X35">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y35">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="Z35">
-        <v>3.58</v>
+        <v>3.91</v>
       </c>
       <c r="AA35">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AB35">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AC35">
-        <v>2.96</v>
+        <v>2.81</v>
       </c>
       <c r="AD35">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE35">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF35">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AG35">
         <v>2.15</v>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AK35">
         <v>1.44</v>
@@ -7490,55 +7490,55 @@
         <v>0</v>
       </c>
       <c r="Q44">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="R44">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="S44">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T44">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="U44">
         <v>2.05</v>
       </c>
       <c r="V44">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="W44">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X44">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="Z44">
-        <v>5.85</v>
+        <v>5.2</v>
       </c>
       <c r="AA44">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AB44">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AC44">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AD44">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AE44">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AF44">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG44">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="O45">
-        <v>4.28</v>
+        <v>3.9</v>
       </c>
       <c r="P45">
-        <v>4.38</v>
+        <v>3.9</v>
       </c>
       <c r="Q45">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="R45">
-        <v>2.49</v>
+        <v>2.44</v>
       </c>
       <c r="S45">
         <v>1.22</v>
       </c>
       <c r="T45">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U45">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="V45">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="W45">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X45">
         <v>1.02</v>
       </c>
       <c r="Y45">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z45">
-        <v>5.66</v>
+        <v>5</v>
       </c>
       <c r="AA45">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AB45">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="AC45">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AD45">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AE45">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AF45">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AG45">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AK45">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>3.46</v>
+        <v>2.9</v>
       </c>
       <c r="O46">
-        <v>4.04</v>
+        <v>3.65</v>
       </c>
       <c r="P46">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="Q46">
-        <v>3.56</v>
+        <v>3.2</v>
       </c>
       <c r="R46">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="S46">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T46">
         <v>4</v>
       </c>
       <c r="U46">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="V46">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="W46">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X46">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z46">
-        <v>6.08</v>
+        <v>5.5</v>
       </c>
       <c r="AA46">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AB46">
-        <v>3.4</v>
+        <v>2.94</v>
       </c>
       <c r="AC46">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AD46">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AE46">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF46">
         <v>1.36</v>
       </c>
       <c r="AG46">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="AK46">
         <v>1.3</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="O47">
+        <v>3.7</v>
+      </c>
+      <c r="P47">
+        <v>2.6</v>
+      </c>
+      <c r="Q47">
+        <v>2.75</v>
+      </c>
+      <c r="R47">
+        <v>2.4</v>
+      </c>
+      <c r="S47">
+        <v>1.2</v>
+      </c>
+      <c r="T47">
+        <v>2.75</v>
+      </c>
+      <c r="U47">
+        <v>1.94</v>
+      </c>
+      <c r="V47">
+        <v>1.46</v>
+      </c>
+      <c r="W47">
+        <v>1.09</v>
+      </c>
+      <c r="X47">
+        <v>1.01</v>
+      </c>
+      <c r="Y47">
+        <v>1.11</v>
+      </c>
+      <c r="Z47">
         <v>3.3</v>
       </c>
-      <c r="P47">
-        <v>2.5</v>
-      </c>
-      <c r="Q47">
-        <v>3.18</v>
-      </c>
-      <c r="R47">
-        <v>2.13</v>
-      </c>
-      <c r="S47">
-        <v>1.31</v>
-      </c>
-      <c r="T47">
-        <v>3.02</v>
-      </c>
-      <c r="U47">
-        <v>2.47</v>
-      </c>
-      <c r="V47">
-        <v>1.45</v>
-      </c>
-      <c r="W47">
-        <v>1.11</v>
-      </c>
-      <c r="X47">
-        <v>1.03</v>
-      </c>
-      <c r="Y47">
-        <v>1.18</v>
-      </c>
-      <c r="Z47">
-        <v>4.2</v>
-      </c>
       <c r="AA47">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AB47">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AC47">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="AD47">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AE47">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AF47">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AG47">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AK47">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="O48">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P48">
-        <v>2.6</v>
+        <v>1.95</v>
       </c>
       <c r="Q48">
-        <v>2.75</v>
+        <v>3.59</v>
       </c>
       <c r="R48">
-        <v>2.4</v>
+        <v>2.64</v>
       </c>
       <c r="S48">
+        <v>1.14</v>
+      </c>
+      <c r="T48">
+        <v>3.1</v>
+      </c>
+      <c r="U48">
+        <v>1.75</v>
+      </c>
+      <c r="V48">
+        <v>1.73</v>
+      </c>
+      <c r="W48">
         <v>1.2</v>
-      </c>
-      <c r="T48">
-        <v>2.75</v>
-      </c>
-      <c r="U48">
-        <v>1.94</v>
-      </c>
-      <c r="V48">
-        <v>1.46</v>
-      </c>
-      <c r="W48">
-        <v>1.09</v>
       </c>
       <c r="X48">
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Z48">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="AA48">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AB48">
-        <v>1.96</v>
+        <v>2.5</v>
       </c>
       <c r="AC48">
-        <v>2.55</v>
+        <v>1.67</v>
       </c>
       <c r="AD48">
-        <v>1.47</v>
+        <v>1.85</v>
       </c>
       <c r="AE48">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AF48">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AG48">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK48">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,80 +8459,80 @@
         </is>
       </c>
       <c r="N50">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="O50">
+        <v>4.5</v>
+      </c>
+      <c r="P50">
+        <v>5.25</v>
+      </c>
+      <c r="Q50">
+        <v>1.85</v>
+      </c>
+      <c r="R50">
+        <v>2.48</v>
+      </c>
+      <c r="S50">
+        <v>1.22</v>
+      </c>
+      <c r="T50">
         <v>3.75</v>
       </c>
-      <c r="P50">
-        <v>1.95</v>
-      </c>
-      <c r="Q50">
-        <v>3.59</v>
-      </c>
-      <c r="R50">
-        <v>2.64</v>
-      </c>
-      <c r="S50">
+      <c r="U50">
+        <v>2.2</v>
+      </c>
+      <c r="V50">
+        <v>1.64</v>
+      </c>
+      <c r="W50">
         <v>1.14</v>
       </c>
-      <c r="T50">
-        <v>3.1</v>
-      </c>
-      <c r="U50">
-        <v>1.75</v>
-      </c>
-      <c r="V50">
-        <v>1.73</v>
-      </c>
-      <c r="W50">
-        <v>1.2</v>
-      </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="Z50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA50">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AB50">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AC50">
-        <v>1.67</v>
+        <v>2.11</v>
       </c>
       <c r="AD50">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AE50">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AF50">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AG50">
+        <v>2.29</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ50">
+        <v>1.14</v>
+      </c>
+      <c r="AK50">
         <v>2.8</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ50">
-        <v>1.17</v>
-      </c>
-      <c r="AK50">
-        <v>1.28</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,80 +8622,80 @@
         </is>
       </c>
       <c r="N51">
+        <v>2.37</v>
+      </c>
+      <c r="O51">
+        <v>3.3</v>
+      </c>
+      <c r="P51">
+        <v>2.5</v>
+      </c>
+      <c r="Q51">
+        <v>3.18</v>
+      </c>
+      <c r="R51">
+        <v>2.13</v>
+      </c>
+      <c r="S51">
+        <v>1.31</v>
+      </c>
+      <c r="T51">
+        <v>3.02</v>
+      </c>
+      <c r="U51">
+        <v>2.47</v>
+      </c>
+      <c r="V51">
+        <v>1.45</v>
+      </c>
+      <c r="W51">
+        <v>1.11</v>
+      </c>
+      <c r="X51">
+        <v>1.03</v>
+      </c>
+      <c r="Y51">
+        <v>1.18</v>
+      </c>
+      <c r="Z51">
+        <v>4.2</v>
+      </c>
+      <c r="AA51">
+        <v>1.65</v>
+      </c>
+      <c r="AB51">
+        <v>2.1</v>
+      </c>
+      <c r="AC51">
+        <v>2.8</v>
+      </c>
+      <c r="AD51">
+        <v>1.38</v>
+      </c>
+      <c r="AE51">
+        <v>1.12</v>
+      </c>
+      <c r="AF51">
+        <v>1.57</v>
+      </c>
+      <c r="AG51">
+        <v>2.25</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
+        <v>1.44</v>
+      </c>
+      <c r="AK51">
         <v>1.5</v>
-      </c>
-      <c r="O51">
-        <v>4.5</v>
-      </c>
-      <c r="P51">
-        <v>5.25</v>
-      </c>
-      <c r="Q51">
-        <v>1.85</v>
-      </c>
-      <c r="R51">
-        <v>2.48</v>
-      </c>
-      <c r="S51">
-        <v>1.22</v>
-      </c>
-      <c r="T51">
-        <v>3.75</v>
-      </c>
-      <c r="U51">
-        <v>2.2</v>
-      </c>
-      <c r="V51">
-        <v>1.64</v>
-      </c>
-      <c r="W51">
-        <v>1.14</v>
-      </c>
-      <c r="X51">
-        <v>1.02</v>
-      </c>
-      <c r="Y51">
-        <v>1.17</v>
-      </c>
-      <c r="Z51">
-        <v>5</v>
-      </c>
-      <c r="AA51">
-        <v>1.42</v>
-      </c>
-      <c r="AB51">
-        <v>2.55</v>
-      </c>
-      <c r="AC51">
-        <v>2.11</v>
-      </c>
-      <c r="AD51">
-        <v>1.61</v>
-      </c>
-      <c r="AE51">
-        <v>1.24</v>
-      </c>
-      <c r="AF51">
-        <v>1.62</v>
-      </c>
-      <c r="AG51">
-        <v>2.29</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>1.14</v>
-      </c>
-      <c r="AK51">
-        <v>2.8</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,34 +8785,34 @@
         </is>
       </c>
       <c r="N52">
+        <v>5.7</v>
+      </c>
+      <c r="O52">
+        <v>5</v>
+      </c>
+      <c r="P52">
+        <v>1.46</v>
+      </c>
+      <c r="Q52">
         <v>5.68</v>
       </c>
-      <c r="O52">
-        <v>5.12</v>
-      </c>
-      <c r="P52">
-        <v>1.48</v>
-      </c>
-      <c r="Q52">
-        <v>5</v>
-      </c>
       <c r="R52">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="S52">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T52">
         <v>4.25</v>
       </c>
       <c r="U52">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="V52">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="W52">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X52">
         <v>1.01</v>
@@ -8821,28 +8821,28 @@
         <v>1.1</v>
       </c>
       <c r="Z52">
-        <v>6.3</v>
+        <v>7.03</v>
       </c>
       <c r="AA52">
         <v>1.33</v>
       </c>
       <c r="AB52">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="AC52">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AD52">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="AE52">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AF52">
         <v>1.44</v>
       </c>
       <c r="AG52">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.17</v>
+        <v>2.75</v>
       </c>
       <c r="AK52">
         <v>1.13</v>
@@ -9763,34 +9763,34 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="O58">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P58">
-        <v>2.35</v>
+        <v>2.64</v>
       </c>
       <c r="Q58">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="R58">
-        <v>2.48</v>
+        <v>2.27</v>
       </c>
       <c r="S58">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T58">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="U58">
         <v>2.27</v>
       </c>
       <c r="V58">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W58">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X58">
         <v>1.03</v>
@@ -9799,44 +9799,44 @@
         <v>1.11</v>
       </c>
       <c r="Z58">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AA58">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AB58">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AC58">
-        <v>2.23</v>
+        <v>2.33</v>
       </c>
       <c r="AD58">
         <v>1.55</v>
       </c>
       <c r="AE58">
+        <v>1.18</v>
+      </c>
+      <c r="AF58">
+        <v>1.44</v>
+      </c>
+      <c r="AG58">
+        <v>2.5</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ58">
         <v>1.22</v>
       </c>
-      <c r="AF58">
-        <v>1.45</v>
-      </c>
-      <c r="AG58">
-        <v>2.55</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ58">
-        <v>1.25</v>
-      </c>
       <c r="AK58">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9935,10 +9935,10 @@
         <v>0</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="S59">
         <v>0</v>
@@ -9947,10 +9947,10 @@
         <v>0</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W59">
         <v>0</v>
@@ -9965,25 +9965,25 @@
         <v>0</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF59">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10098,10 +10098,10 @@
         <v>0</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S60">
         <v>0</v>
@@ -10110,10 +10110,10 @@
         <v>0</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W60">
         <v>0</v>
@@ -10122,31 +10122,31 @@
         <v>0</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z60">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE60">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF60">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG60">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK60">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,19 +10252,19 @@
         </is>
       </c>
       <c r="N61">
-        <v>4.36</v>
+        <v>3.12</v>
       </c>
       <c r="O61">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="P61">
-        <v>1.71</v>
+        <v>2.13</v>
       </c>
       <c r="Q61">
-        <v>3.65</v>
+        <v>3.26</v>
       </c>
       <c r="R61">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="S61">
         <v>1.29</v>
@@ -10273,10 +10273,10 @@
         <v>3.28</v>
       </c>
       <c r="U61">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="V61">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="W61">
         <v>1.1</v>
@@ -10288,16 +10288,16 @@
         <v>1.15</v>
       </c>
       <c r="Z61">
-        <v>4.3</v>
+        <v>4.64</v>
       </c>
       <c r="AA61">
         <v>1.6</v>
       </c>
       <c r="AB61">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="AC61">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="AD61">
         <v>1.52</v>
@@ -10306,10 +10306,10 @@
         <v>1.2</v>
       </c>
       <c r="AF61">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AG61">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.69</v>
+        <v>1.22</v>
       </c>
       <c r="AK61">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G78">
@@ -13032,55 +13032,55 @@
         <v>0</v>
       </c>
       <c r="Q78">
-        <v>3.1</v>
+        <v>2.07</v>
       </c>
       <c r="R78">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="S78">
         <v>1.44</v>
       </c>
       <c r="T78">
-        <v>2.68</v>
+        <v>2.54</v>
       </c>
       <c r="U78">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="V78">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W78">
         <v>1.03</v>
       </c>
       <c r="X78">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y78">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z78">
-        <v>2.83</v>
+        <v>3.05</v>
       </c>
       <c r="AA78">
-        <v>2.16</v>
+        <v>2.01</v>
       </c>
       <c r="AB78">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AC78">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="AD78">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE78">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF78">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AG78">
-        <v>1.87</v>
+        <v>1.66</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AK78">
-        <v>1.52</v>
+        <v>2.46</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G79">
@@ -13195,71 +13195,71 @@
         <v>0</v>
       </c>
       <c r="Q79">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="R79">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="S79">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T79">
-        <v>2.54</v>
+        <v>2.75</v>
       </c>
       <c r="U79">
-        <v>2.9</v>
+        <v>3.16</v>
       </c>
       <c r="V79">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W79">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X79">
+        <v>1.01</v>
+      </c>
+      <c r="Y79">
+        <v>1.31</v>
+      </c>
+      <c r="Z79">
+        <v>2.92</v>
+      </c>
+      <c r="AA79">
+        <v>2.13</v>
+      </c>
+      <c r="AB79">
+        <v>1.69</v>
+      </c>
+      <c r="AC79">
+        <v>3.8</v>
+      </c>
+      <c r="AD79">
+        <v>1.24</v>
+      </c>
+      <c r="AE79">
         <v>1.02</v>
       </c>
-      <c r="Y79">
-        <v>1.28</v>
-      </c>
-      <c r="Z79">
-        <v>3.05</v>
-      </c>
-      <c r="AA79">
-        <v>2.01</v>
-      </c>
-      <c r="AB79">
-        <v>1.76</v>
-      </c>
-      <c r="AC79">
-        <v>3.28</v>
-      </c>
-      <c r="AD79">
+      <c r="AF79">
+        <v>2.15</v>
+      </c>
+      <c r="AG79">
+        <v>1.63</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ79">
         <v>1.25</v>
       </c>
-      <c r="AE79">
-        <v>1.06</v>
-      </c>
-      <c r="AF79">
-        <v>2.1</v>
-      </c>
-      <c r="AG79">
-        <v>1.66</v>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ79">
-        <v>1.26</v>
-      </c>
       <c r="AK79">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G80">
@@ -13358,55 +13358,55 @@
         <v>0</v>
       </c>
       <c r="Q80">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="R80">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S80">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T80">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="U80">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="V80">
+        <v>1.32</v>
+      </c>
+      <c r="W80">
+        <v>1.03</v>
+      </c>
+      <c r="X80">
+        <v>1.03</v>
+      </c>
+      <c r="Y80">
         <v>1.33</v>
       </c>
-      <c r="W80">
-        <v>1.01</v>
-      </c>
-      <c r="X80">
-        <v>1.01</v>
-      </c>
-      <c r="Y80">
-        <v>1.31</v>
-      </c>
       <c r="Z80">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="AA80">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="AB80">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AC80">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="AD80">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AE80">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF80">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AG80">
-        <v>1.63</v>
+        <v>1.87</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK80">
-        <v>2.38</v>
+        <v>1.52</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13521,16 +13521,16 @@
         <v>7.55</v>
       </c>
       <c r="Q81">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="R81">
         <v>2.9</v>
       </c>
       <c r="S81">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T81">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="U81">
         <v>1.85</v>
@@ -13539,31 +13539,31 @@
         <v>1.85</v>
       </c>
       <c r="W81">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X81">
         <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Z81">
-        <v>6</v>
+        <v>6.75</v>
       </c>
       <c r="AA81">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AB81">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="AC81">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AD81">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AE81">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AF81">
         <v>1.5</v>
@@ -13582,7 +13582,7 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AK81">
         <v>3</v>
@@ -16283,43 +16283,43 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="O98">
-        <v>4.15</v>
+        <v>4.25</v>
       </c>
       <c r="P98">
-        <v>4.05</v>
+        <v>5.05</v>
       </c>
       <c r="Q98">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="R98">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="S98">
         <v>1.22</v>
       </c>
       <c r="T98">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U98">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="V98">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="W98">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X98">
         <v>1.02</v>
       </c>
       <c r="Y98">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z98">
-        <v>5.35</v>
+        <v>5.3</v>
       </c>
       <c r="AA98">
         <v>1.42</v>
@@ -16328,19 +16328,19 @@
         <v>2.49</v>
       </c>
       <c r="AC98">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="AD98">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AE98">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AF98">
         <v>1.5</v>
       </c>
       <c r="AG98">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK98">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -23292,37 +23292,37 @@
         </is>
       </c>
       <c r="N141">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="O141">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P141">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="Q141">
         <v>2.3</v>
       </c>
       <c r="R141">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="S141">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="T141">
         <v>2.33</v>
       </c>
       <c r="U141">
-        <v>3.1</v>
+        <v>3.58</v>
       </c>
       <c r="V141">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="W141">
         <v>1.05</v>
       </c>
       <c r="X141">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Y141">
         <v>1.5</v>
@@ -23331,10 +23331,10 @@
         <v>2.45</v>
       </c>
       <c r="AA141">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AB141">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AC141">
         <v>5.05</v>
@@ -23343,13 +23343,13 @@
         <v>1.1</v>
       </c>
       <c r="AE141">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF141">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AG141">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
@@ -23362,10 +23362,10 @@
         </is>
       </c>
       <c r="AJ141">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK141">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23461,28 +23461,28 @@
         <v>2.87</v>
       </c>
       <c r="P142">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="Q142">
         <v>2.6</v>
       </c>
       <c r="R142">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="S142">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="T142">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="U142">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="V142">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="W142">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X142">
         <v>1.1</v>
@@ -23491,7 +23491,7 @@
         <v>1.61</v>
       </c>
       <c r="Z142">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="AA142">
         <v>2.86</v>
@@ -23509,10 +23509,10 @@
         <v>1.03</v>
       </c>
       <c r="AF142">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AG142">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
@@ -23525,10 +23525,10 @@
         </is>
       </c>
       <c r="AJ142">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AK142">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -23627,10 +23627,10 @@
         <v>4.2</v>
       </c>
       <c r="Q143">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="R143">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="S143">
         <v>1.62</v>
@@ -23639,37 +23639,37 @@
         <v>2.2</v>
       </c>
       <c r="U143">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="V143">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="W143">
+        <v>1.02</v>
+      </c>
+      <c r="X143">
+        <v>1.12</v>
+      </c>
+      <c r="Y143">
+        <v>1.78</v>
+      </c>
+      <c r="Z143">
+        <v>1.99</v>
+      </c>
+      <c r="AA143">
+        <v>3.4</v>
+      </c>
+      <c r="AB143">
+        <v>1.26</v>
+      </c>
+      <c r="AC143">
+        <v>7.1</v>
+      </c>
+      <c r="AD143">
+        <v>1.04</v>
+      </c>
+      <c r="AE143">
         <v>1.03</v>
-      </c>
-      <c r="X143">
-        <v>1.15</v>
-      </c>
-      <c r="Y143">
-        <v>1.7</v>
-      </c>
-      <c r="Z143">
-        <v>2.03</v>
-      </c>
-      <c r="AA143">
-        <v>3.14</v>
-      </c>
-      <c r="AB143">
-        <v>1.27</v>
-      </c>
-      <c r="AC143">
-        <v>6.75</v>
-      </c>
-      <c r="AD143">
-        <v>1.1</v>
-      </c>
-      <c r="AE143">
-        <v>1.02</v>
       </c>
       <c r="AF143">
         <v>2.6</v>
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,80 +26226,80 @@
         </is>
       </c>
       <c r="N159">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="O159">
         <v>3.58</v>
       </c>
       <c r="P159">
-        <v>4.03</v>
+        <v>5.28</v>
       </c>
       <c r="Q159">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="R159">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S159">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="T159">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="U159">
-        <v>2.69</v>
+        <v>2.9</v>
       </c>
       <c r="V159">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="W159">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X159">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y159">
+        <v>1.36</v>
+      </c>
+      <c r="Z159">
+        <v>2.88</v>
+      </c>
+      <c r="AA159">
+        <v>2.05</v>
+      </c>
+      <c r="AB159">
+        <v>1.65</v>
+      </c>
+      <c r="AC159">
+        <v>3.54</v>
+      </c>
+      <c r="AD159">
+        <v>1.22</v>
+      </c>
+      <c r="AE159">
+        <v>1.06</v>
+      </c>
+      <c r="AF159">
+        <v>1.95</v>
+      </c>
+      <c r="AG159">
+        <v>1.8</v>
+      </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ159">
         <v>1.29</v>
       </c>
-      <c r="Z159">
-        <v>3.55</v>
-      </c>
-      <c r="AA159">
-        <v>1.94</v>
-      </c>
-      <c r="AB159">
-        <v>1.88</v>
-      </c>
-      <c r="AC159">
-        <v>2.99</v>
-      </c>
-      <c r="AD159">
-        <v>1.29</v>
-      </c>
-      <c r="AE159">
-        <v>1.08</v>
-      </c>
-      <c r="AF159">
-        <v>1.83</v>
-      </c>
-      <c r="AG159">
-        <v>1.91</v>
-      </c>
-      <c r="AH159" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI159" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ159">
-        <v>1.24</v>
-      </c>
       <c r="AK159">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G160">
@@ -26389,64 +26389,64 @@
         </is>
       </c>
       <c r="N160">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="O160">
-        <v>3.58</v>
+        <v>3.64</v>
       </c>
       <c r="P160">
-        <v>5.28</v>
+        <v>4.75</v>
       </c>
       <c r="Q160">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="R160">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S160">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="T160">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="U160">
-        <v>2.9</v>
+        <v>3.01</v>
       </c>
       <c r="V160">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W160">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X160">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y160">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z160">
-        <v>2.88</v>
+        <v>3.24</v>
       </c>
       <c r="AA160">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AB160">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AC160">
-        <v>3.54</v>
+        <v>3.18</v>
       </c>
       <c r="AD160">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AE160">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF160">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AG160">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
@@ -26459,10 +26459,10 @@
         </is>
       </c>
       <c r="AJ160">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AK160">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G161">
@@ -26552,64 +26552,64 @@
         </is>
       </c>
       <c r="N161">
-        <v>1.72</v>
+        <v>2.47</v>
       </c>
       <c r="O161">
-        <v>3.64</v>
+        <v>3.3</v>
       </c>
       <c r="P161">
-        <v>4.75</v>
+        <v>2.74</v>
       </c>
       <c r="Q161">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R161">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S161">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T161">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U161">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="V161">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W161">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X161">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y161">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z161">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AA161">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AB161">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AC161">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AD161">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE161">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF161">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG161">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK161">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G162">
@@ -26715,64 +26715,64 @@
         </is>
       </c>
       <c r="N162">
-        <v>2.47</v>
+        <v>4.08</v>
       </c>
       <c r="O162">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="P162">
-        <v>2.74</v>
+        <v>1.84</v>
       </c>
       <c r="Q162">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R162">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S162">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T162">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U162">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V162">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W162">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X162">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y162">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z162">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA162">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AB162">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AC162">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD162">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE162">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF162">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG162">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
@@ -26785,10 +26785,10 @@
         </is>
       </c>
       <c r="AJ162">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK162">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL162">
         <v>0</v>
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G163">
@@ -26878,64 +26878,64 @@
         </is>
       </c>
       <c r="N163">
-        <v>4.08</v>
+        <v>4.18</v>
       </c>
       <c r="O163">
-        <v>3.58</v>
+        <v>3.52</v>
       </c>
       <c r="P163">
         <v>1.84</v>
       </c>
       <c r="Q163">
-        <v>4.2</v>
+        <v>4.32</v>
       </c>
       <c r="R163">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="S163">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T163">
         <v>2.69</v>
       </c>
       <c r="U163">
-        <v>2.77</v>
+        <v>3.05</v>
       </c>
       <c r="V163">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W163">
         <v>1.05</v>
       </c>
       <c r="X163">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y163">
         <v>1.33</v>
       </c>
       <c r="Z163">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AA163">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AB163">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AC163">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AD163">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AE163">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF163">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AG163">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
@@ -26948,10 +26948,10 @@
         </is>
       </c>
       <c r="AJ163">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK163">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G164">
@@ -27041,80 +27041,80 @@
         </is>
       </c>
       <c r="N164">
-        <v>4.18</v>
+        <v>2.38</v>
       </c>
       <c r="O164">
-        <v>3.52</v>
+        <v>3.46</v>
       </c>
       <c r="P164">
-        <v>1.84</v>
+        <v>2.75</v>
       </c>
       <c r="Q164">
-        <v>4.32</v>
+        <v>2.84</v>
       </c>
       <c r="R164">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="S164">
+        <v>1.35</v>
+      </c>
+      <c r="T164">
+        <v>2.94</v>
+      </c>
+      <c r="U164">
+        <v>2.53</v>
+      </c>
+      <c r="V164">
+        <v>1.43</v>
+      </c>
+      <c r="W164">
+        <v>1.07</v>
+      </c>
+      <c r="X164">
+        <v>1.05</v>
+      </c>
+      <c r="Y164">
+        <v>1.25</v>
+      </c>
+      <c r="Z164">
+        <v>3.5</v>
+      </c>
+      <c r="AA164">
+        <v>1.78</v>
+      </c>
+      <c r="AB164">
+        <v>2</v>
+      </c>
+      <c r="AC164">
+        <v>3.02</v>
+      </c>
+      <c r="AD164">
+        <v>1.35</v>
+      </c>
+      <c r="AE164">
+        <v>1.11</v>
+      </c>
+      <c r="AF164">
+        <v>1.6</v>
+      </c>
+      <c r="AG164">
+        <v>2.05</v>
+      </c>
+      <c r="AH164" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI164" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ164">
         <v>1.41</v>
       </c>
-      <c r="T164">
-        <v>2.69</v>
-      </c>
-      <c r="U164">
-        <v>3.05</v>
-      </c>
-      <c r="V164">
-        <v>1.35</v>
-      </c>
-      <c r="W164">
-        <v>1.05</v>
-      </c>
-      <c r="X164">
-        <v>1.02</v>
-      </c>
-      <c r="Y164">
-        <v>1.33</v>
-      </c>
-      <c r="Z164">
-        <v>3.1</v>
-      </c>
-      <c r="AA164">
-        <v>2.05</v>
-      </c>
-      <c r="AB164">
-        <v>1.73</v>
-      </c>
-      <c r="AC164">
-        <v>3.6</v>
-      </c>
-      <c r="AD164">
-        <v>1.27</v>
-      </c>
-      <c r="AE164">
-        <v>1.08</v>
-      </c>
-      <c r="AF164">
-        <v>1.85</v>
-      </c>
-      <c r="AG164">
-        <v>1.85</v>
-      </c>
-      <c r="AH164" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI164" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ164">
-        <v>1.33</v>
-      </c>
       <c r="AK164">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AL164">
         <v>0</v>
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G165">
@@ -27204,34 +27204,34 @@
         </is>
       </c>
       <c r="N165">
-        <v>2.38</v>
+        <v>1.82</v>
       </c>
       <c r="O165">
-        <v>3.46</v>
+        <v>3.68</v>
       </c>
       <c r="P165">
-        <v>2.75</v>
+        <v>4.08</v>
       </c>
       <c r="Q165">
-        <v>2.84</v>
+        <v>2.62</v>
       </c>
       <c r="R165">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="S165">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T165">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="U165">
-        <v>2.53</v>
+        <v>2.64</v>
       </c>
       <c r="V165">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W165">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X165">
         <v>1.05</v>
@@ -27240,28 +27240,28 @@
         <v>1.25</v>
       </c>
       <c r="Z165">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA165">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="AB165">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AC165">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="AD165">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE165">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF165">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG165">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AH165" t="inlineStr">
         <is>
@@ -27274,10 +27274,10 @@
         </is>
       </c>
       <c r="AJ165">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AK165">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AL165">
         <v>0</v>
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G166">
@@ -27367,49 +27367,49 @@
         </is>
       </c>
       <c r="N166">
-        <v>1.82</v>
+        <v>1.99</v>
       </c>
       <c r="O166">
-        <v>3.68</v>
+        <v>3.54</v>
       </c>
       <c r="P166">
-        <v>4.08</v>
+        <v>3.54</v>
       </c>
       <c r="Q166">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="R166">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="S166">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T166">
-        <v>2.93</v>
+        <v>2.85</v>
       </c>
       <c r="U166">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="V166">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W166">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X166">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y166">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z166">
         <v>3.3</v>
       </c>
       <c r="AA166">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AB166">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC166">
         <v>2.99</v>
@@ -27437,10 +27437,10 @@
         </is>
       </c>
       <c r="AJ166">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK166">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AL166">
         <v>0</v>
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G167">
@@ -27530,64 +27530,64 @@
         </is>
       </c>
       <c r="N167">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="O167">
-        <v>3.54</v>
+        <v>3.58</v>
       </c>
       <c r="P167">
-        <v>3.54</v>
+        <v>4.03</v>
       </c>
       <c r="Q167">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="R167">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="S167">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T167">
         <v>2.85</v>
       </c>
       <c r="U167">
-        <v>2.88</v>
+        <v>2.69</v>
       </c>
       <c r="V167">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W167">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X167">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y167">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z167">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="AA167">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AB167">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AC167">
         <v>2.99</v>
       </c>
       <c r="AD167">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE167">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF167">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG167">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
@@ -27603,7 +27603,7 @@
         <v>1.24</v>
       </c>
       <c r="AK167">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AL167">
         <v>0</v>
@@ -29009,16 +29009,16 @@
         <v>3</v>
       </c>
       <c r="R176">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="S176">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="T176">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="U176">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="V176">
         <v>1.16</v>
@@ -29030,13 +29030,13 @@
         <v>1.15</v>
       </c>
       <c r="Y176">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="Z176">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AA176">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AB176">
         <v>1.31</v>
@@ -29045,10 +29045,10 @@
         <v>6.15</v>
       </c>
       <c r="AD176">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AE176">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF176">
         <v>2.4</v>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AK176">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AL176">
         <v>0</v>

--- a/jogos_2026-08-08.xlsx
+++ b/jogos_2026-08-08.xlsx
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.67</v>
+        <v>1.91</v>
       </c>
       <c r="O27">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="P27">
-        <v>2.58</v>
+        <v>4.1</v>
       </c>
       <c r="Q27">
-        <v>3.32</v>
+        <v>2.38</v>
       </c>
       <c r="R27">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="S27">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="T27">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="U27">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="V27">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="W27">
         <v>1.06</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="Z27">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="AA27">
-        <v>1.95</v>
+        <v>2.32</v>
       </c>
       <c r="AB27">
-        <v>1.82</v>
+        <v>1.62</v>
       </c>
       <c r="AC27">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="AD27">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AE27">
         <v>1.06</v>
       </c>
       <c r="AF27">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AG27">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AK27">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,65 +5036,65 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.91</v>
+        <v>2.67</v>
       </c>
       <c r="O29">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="P29">
-        <v>4.1</v>
+        <v>2.58</v>
       </c>
       <c r="Q29">
-        <v>2.38</v>
+        <v>3.32</v>
       </c>
       <c r="R29">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="S29">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T29">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="U29">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="V29">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="W29">
         <v>1.06</v>
       </c>
       <c r="X29">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="Z29">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="AA29">
-        <v>2.32</v>
+        <v>1.95</v>
       </c>
       <c r="AB29">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="AC29">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="AD29">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AE29">
         <v>1.06</v>
       </c>
       <c r="AF29">
+        <v>1.73</v>
+      </c>
+      <c r="AG29">
         <v>2.05</v>
       </c>
-      <c r="AG29">
-        <v>1.7</v>
-      </c>
       <c r="AH29" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AK29">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.15</v>
+        <v>1.62</v>
       </c>
       <c r="O36">
-        <v>3.6</v>
+        <v>3.74</v>
       </c>
       <c r="P36">
-        <v>2.96</v>
+        <v>5.46</v>
       </c>
       <c r="Q36">
-        <v>2.51</v>
+        <v>1.95</v>
       </c>
       <c r="R36">
-        <v>2.28</v>
+        <v>2.49</v>
       </c>
       <c r="S36">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T36">
-        <v>3.5</v>
+        <v>2.99</v>
       </c>
       <c r="U36">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="V36">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="W36">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X36">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z36">
-        <v>4.5</v>
+        <v>4.15</v>
       </c>
       <c r="AA36">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AB36">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AC36">
-        <v>2.29</v>
+        <v>2.63</v>
       </c>
       <c r="AD36">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AE36">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AF36">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="AG36">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AK36">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
+        <v>2.35</v>
+      </c>
+      <c r="O37">
+        <v>3.58</v>
+      </c>
+      <c r="P37">
+        <v>2.72</v>
+      </c>
+      <c r="Q37">
+        <v>2.99</v>
+      </c>
+      <c r="R37">
+        <v>2.32</v>
+      </c>
+      <c r="S37">
+        <v>1.22</v>
+      </c>
+      <c r="T37">
+        <v>4</v>
+      </c>
+      <c r="U37">
+        <v>2.26</v>
+      </c>
+      <c r="V37">
+        <v>1.65</v>
+      </c>
+      <c r="W37">
+        <v>1.14</v>
+      </c>
+      <c r="X37">
+        <v>1.02</v>
+      </c>
+      <c r="Y37">
+        <v>1.09</v>
+      </c>
+      <c r="Z37">
+        <v>5.25</v>
+      </c>
+      <c r="AA37">
+        <v>1.43</v>
+      </c>
+      <c r="AB37">
+        <v>2.55</v>
+      </c>
+      <c r="AC37">
+        <v>2.2</v>
+      </c>
+      <c r="AD37">
         <v>1.62</v>
       </c>
-      <c r="O37">
-        <v>3.74</v>
-      </c>
-      <c r="P37">
-        <v>5.46</v>
-      </c>
-      <c r="Q37">
-        <v>1.95</v>
-      </c>
-      <c r="R37">
-        <v>2.49</v>
-      </c>
-      <c r="S37">
-        <v>1.3</v>
-      </c>
-      <c r="T37">
-        <v>2.99</v>
-      </c>
-      <c r="U37">
-        <v>2.4</v>
-      </c>
-      <c r="V37">
-        <v>1.52</v>
-      </c>
-      <c r="W37">
-        <v>1.12</v>
-      </c>
-      <c r="X37">
-        <v>1.01</v>
-      </c>
-      <c r="Y37">
-        <v>1.16</v>
-      </c>
-      <c r="Z37">
-        <v>4.15</v>
-      </c>
-      <c r="AA37">
-        <v>1.68</v>
-      </c>
-      <c r="AB37">
-        <v>2.14</v>
-      </c>
-      <c r="AC37">
-        <v>2.63</v>
-      </c>
-      <c r="AD37">
-        <v>1.4</v>
-      </c>
       <c r="AE37">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AF37">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="AG37">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AK37">
-        <v>2.3</v>
+        <v>1.34</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.35</v>
+        <v>1.71</v>
       </c>
       <c r="O38">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="P38">
-        <v>2.72</v>
+        <v>4.26</v>
       </c>
       <c r="Q38">
-        <v>2.99</v>
+        <v>2.16</v>
       </c>
       <c r="R38">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="S38">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T38">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="U38">
-        <v>2.26</v>
+        <v>2.31</v>
       </c>
       <c r="V38">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="W38">
+        <v>1.11</v>
+      </c>
+      <c r="X38">
+        <v>1.03</v>
+      </c>
+      <c r="Y38">
+        <v>1.2</v>
+      </c>
+      <c r="Z38">
+        <v>4.33</v>
+      </c>
+      <c r="AA38">
+        <v>1.61</v>
+      </c>
+      <c r="AB38">
+        <v>2.08</v>
+      </c>
+      <c r="AC38">
+        <v>2.6</v>
+      </c>
+      <c r="AD38">
+        <v>1.47</v>
+      </c>
+      <c r="AE38">
         <v>1.14</v>
       </c>
-      <c r="X38">
-        <v>1.02</v>
-      </c>
-      <c r="Y38">
-        <v>1.09</v>
-      </c>
-      <c r="Z38">
-        <v>5.25</v>
-      </c>
-      <c r="AA38">
-        <v>1.43</v>
-      </c>
-      <c r="AB38">
-        <v>2.55</v>
-      </c>
-      <c r="AC38">
-        <v>2.2</v>
-      </c>
-      <c r="AD38">
-        <v>1.62</v>
-      </c>
-      <c r="AE38">
-        <v>1.25</v>
-      </c>
       <c r="AF38">
-        <v>1.42</v>
+        <v>1.61</v>
       </c>
       <c r="AG38">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AK38">
-        <v>1.34</v>
+        <v>2</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,31 +6666,31 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.71</v>
+        <v>2.15</v>
       </c>
       <c r="O39">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P39">
-        <v>4.26</v>
+        <v>2.96</v>
       </c>
       <c r="Q39">
-        <v>2.16</v>
+        <v>2.51</v>
       </c>
       <c r="R39">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="S39">
         <v>1.25</v>
       </c>
       <c r="T39">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="U39">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="V39">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W39">
         <v>1.11</v>
@@ -6699,31 +6699,31 @@
         <v>1.03</v>
       </c>
       <c r="Y39">
+        <v>1.15</v>
+      </c>
+      <c r="Z39">
+        <v>4.5</v>
+      </c>
+      <c r="AA39">
+        <v>1.57</v>
+      </c>
+      <c r="AB39">
+        <v>2.33</v>
+      </c>
+      <c r="AC39">
+        <v>2.29</v>
+      </c>
+      <c r="AD39">
+        <v>1.5</v>
+      </c>
+      <c r="AE39">
         <v>1.2</v>
       </c>
-      <c r="Z39">
-        <v>4.33</v>
-      </c>
-      <c r="AA39">
-        <v>1.61</v>
-      </c>
-      <c r="AB39">
-        <v>2.08</v>
-      </c>
-      <c r="AC39">
-        <v>2.6</v>
-      </c>
-      <c r="AD39">
-        <v>1.47</v>
-      </c>
-      <c r="AE39">
-        <v>1.14</v>
-      </c>
       <c r="AF39">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="AG39">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AK39">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,80 +8459,80 @@
         </is>
       </c>
       <c r="N50">
+        <v>2.37</v>
+      </c>
+      <c r="O50">
+        <v>3.3</v>
+      </c>
+      <c r="P50">
+        <v>2.5</v>
+      </c>
+      <c r="Q50">
+        <v>3.18</v>
+      </c>
+      <c r="R50">
+        <v>2.13</v>
+      </c>
+      <c r="S50">
+        <v>1.31</v>
+      </c>
+      <c r="T50">
+        <v>3.02</v>
+      </c>
+      <c r="U50">
+        <v>2.47</v>
+      </c>
+      <c r="V50">
+        <v>1.45</v>
+      </c>
+      <c r="W50">
+        <v>1.11</v>
+      </c>
+      <c r="X50">
+        <v>1.03</v>
+      </c>
+      <c r="Y50">
+        <v>1.18</v>
+      </c>
+      <c r="Z50">
+        <v>4.2</v>
+      </c>
+      <c r="AA50">
+        <v>1.65</v>
+      </c>
+      <c r="AB50">
+        <v>2.1</v>
+      </c>
+      <c r="AC50">
+        <v>2.8</v>
+      </c>
+      <c r="AD50">
+        <v>1.38</v>
+      </c>
+      <c r="AE50">
+        <v>1.12</v>
+      </c>
+      <c r="AF50">
+        <v>1.57</v>
+      </c>
+      <c r="AG50">
+        <v>2.25</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ50">
+        <v>1.44</v>
+      </c>
+      <c r="AK50">
         <v>1.5</v>
-      </c>
-      <c r="O50">
-        <v>4.5</v>
-      </c>
-      <c r="P50">
-        <v>5.25</v>
-      </c>
-      <c r="Q50">
-        <v>1.85</v>
-      </c>
-      <c r="R50">
-        <v>2.48</v>
-      </c>
-      <c r="S50">
-        <v>1.22</v>
-      </c>
-      <c r="T50">
-        <v>3.75</v>
-      </c>
-      <c r="U50">
-        <v>2.2</v>
-      </c>
-      <c r="V50">
-        <v>1.64</v>
-      </c>
-      <c r="W50">
-        <v>1.14</v>
-      </c>
-      <c r="X50">
-        <v>1.02</v>
-      </c>
-      <c r="Y50">
-        <v>1.17</v>
-      </c>
-      <c r="Z50">
-        <v>5</v>
-      </c>
-      <c r="AA50">
-        <v>1.42</v>
-      </c>
-      <c r="AB50">
-        <v>2.55</v>
-      </c>
-      <c r="AC50">
-        <v>2.11</v>
-      </c>
-      <c r="AD50">
-        <v>1.61</v>
-      </c>
-      <c r="AE50">
-        <v>1.24</v>
-      </c>
-      <c r="AF50">
-        <v>1.62</v>
-      </c>
-      <c r="AG50">
-        <v>2.29</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ50">
-        <v>1.14</v>
-      </c>
-      <c r="AK50">
-        <v>2.8</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,80 +8622,80 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.37</v>
+        <v>1.5</v>
       </c>
       <c r="O51">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="P51">
-        <v>2.5</v>
+        <v>5.25</v>
       </c>
       <c r="Q51">
-        <v>3.18</v>
+        <v>1.85</v>
       </c>
       <c r="R51">
-        <v>2.13</v>
+        <v>2.48</v>
       </c>
       <c r="S51">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="T51">
-        <v>3.02</v>
+        <v>3.75</v>
       </c>
       <c r="U51">
-        <v>2.47</v>
+        <v>2.2</v>
       </c>
       <c r="V51">
-        <v>1.45</v>
+        <v>1.64</v>
       </c>
       <c r="W51">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X51">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z51">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AA51">
-        <v>1.65</v>
+        <v>1.42</v>
       </c>
       <c r="AB51">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="AC51">
+        <v>2.11</v>
+      </c>
+      <c r="AD51">
+        <v>1.61</v>
+      </c>
+      <c r="AE51">
+        <v>1.24</v>
+      </c>
+      <c r="AF51">
+        <v>1.62</v>
+      </c>
+      <c r="AG51">
+        <v>2.29</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
+        <v>1.14</v>
+      </c>
+      <c r="AK51">
         <v>2.8</v>
-      </c>
-      <c r="AD51">
-        <v>1.38</v>
-      </c>
-      <c r="AE51">
-        <v>1.12</v>
-      </c>
-      <c r="AF51">
-        <v>1.57</v>
-      </c>
-      <c r="AG51">
-        <v>2.25</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>1.44</v>
-      </c>
-      <c r="AK51">
-        <v>1.5</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G59">
@@ -9935,10 +9935,10 @@
         <v>0</v>
       </c>
       <c r="Q59">
-        <v>1.61</v>
+        <v>3.55</v>
       </c>
       <c r="R59">
-        <v>2.95</v>
+        <v>2.3</v>
       </c>
       <c r="S59">
         <v>0</v>
@@ -9947,10 +9947,10 @@
         <v>0</v>
       </c>
       <c r="U59">
-        <v>1.84</v>
+        <v>2.35</v>
       </c>
       <c r="V59">
-        <v>1.75</v>
+        <v>1.45</v>
       </c>
       <c r="W59">
         <v>0</v>
@@ -9959,31 +9959,31 @@
         <v>0</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z59">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA59">
-        <v>1.34</v>
+        <v>1.65</v>
       </c>
       <c r="AB59">
-        <v>2.8</v>
+        <v>2.02</v>
       </c>
       <c r="AC59">
-        <v>1.84</v>
+        <v>2.6</v>
       </c>
       <c r="AD59">
-        <v>1.79</v>
+        <v>1.4</v>
       </c>
       <c r="AE59">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="AF59">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="AG59">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="AK59">
-        <v>3.05</v>
+        <v>1.24</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G60">
@@ -10098,10 +10098,10 @@
         <v>0</v>
       </c>
       <c r="Q60">
-        <v>3.55</v>
+        <v>1.61</v>
       </c>
       <c r="R60">
-        <v>2.3</v>
+        <v>2.95</v>
       </c>
       <c r="S60">
         <v>0</v>
@@ -10110,10 +10110,10 @@
         <v>0</v>
       </c>
       <c r="U60">
-        <v>2.35</v>
+        <v>1.84</v>
       </c>
       <c r="V60">
-        <v>1.45</v>
+        <v>1.75</v>
       </c>
       <c r="W60">
         <v>0</v>
@@ -10122,31 +10122,31 @@
         <v>0</v>
       </c>
       <c r="Y60">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z60">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA60">
-        <v>1.65</v>
+        <v>1.34</v>
       </c>
       <c r="AB60">
-        <v>2.02</v>
+        <v>2.8</v>
       </c>
       <c r="AC60">
-        <v>2.6</v>
+        <v>1.84</v>
       </c>
       <c r="AD60">
-        <v>1.4</v>
+        <v>1.79</v>
       </c>
       <c r="AE60">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="AF60">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="AG60">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="AK60">
-        <v>1.24</v>
+        <v>3.05</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O96">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P96">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Q96">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="R96">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="S96">
+        <v>1.43</v>
+      </c>
+      <c r="T96">
+        <v>2.55</v>
+      </c>
+      <c r="U96">
+        <v>2.8</v>
+      </c>
+      <c r="V96">
         <v>1.36</v>
       </c>
-      <c r="T96">
-        <v>2.88</v>
-      </c>
-      <c r="U96">
-        <v>2.87</v>
-      </c>
-      <c r="V96">
-        <v>1.42</v>
-      </c>
       <c r="W96">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X96">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y96">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z96">
         <v>3.3</v>
       </c>
       <c r="AA96">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AB96">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AC96">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="AD96">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE96">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF96">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG96">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.91</v>
+        <v>1.33</v>
       </c>
       <c r="AK96">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O97">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P97">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q97">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="R97">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S97">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="T97">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="U97">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="V97">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W97">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X97">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y97">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="Z97">
         <v>3.3</v>
       </c>
       <c r="AA97">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AB97">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AC97">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="AD97">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE97">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF97">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG97">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.33</v>
+        <v>1.91</v>
       </c>
       <c r="AK97">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="AL97">
         <v>0</v>

--- a/jogos_2026-08-08.xlsx
+++ b/jogos_2026-08-08.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="O2">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="P2">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -674,10 +674,10 @@
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -1000,10 +1000,10 @@
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC4">
         <v>0</v>
@@ -1133,55 +1133,55 @@
         <v>1.7</v>
       </c>
       <c r="Q5">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="R5">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U5">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="V5">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z5">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA5">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AB5">
         <v>1.94</v>
       </c>
       <c r="AC5">
-        <v>2.75</v>
+        <v>2.97</v>
       </c>
       <c r="AD5">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE5">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF5">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG5">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK5">
         <v>1.13</v>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="O6">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="P6">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="Q6">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="R6">
-        <v>2.26</v>
+        <v>2.43</v>
       </c>
       <c r="S6">
         <v>1.25</v>
       </c>
       <c r="T6">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="U6">
-        <v>2.31</v>
+        <v>2.12</v>
       </c>
       <c r="V6">
+        <v>1.55</v>
+      </c>
+      <c r="W6">
+        <v>1.13</v>
+      </c>
+      <c r="X6">
+        <v>1.01</v>
+      </c>
+      <c r="Y6">
+        <v>1.14</v>
+      </c>
+      <c r="Z6">
+        <v>4.4</v>
+      </c>
+      <c r="AA6">
         <v>1.5</v>
       </c>
-      <c r="W6">
-        <v>1.08</v>
-      </c>
-      <c r="X6">
-        <v>0</v>
-      </c>
-      <c r="Y6">
-        <v>1.13</v>
-      </c>
-      <c r="Z6">
-        <v>4.5</v>
-      </c>
-      <c r="AA6">
-        <v>1.55</v>
-      </c>
       <c r="AB6">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="AC6">
-        <v>2.46</v>
+        <v>2.25</v>
       </c>
       <c r="AD6">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="AE6">
         <v>1.14</v>
       </c>
       <c r="AF6">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AG6">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>1.2</v>
       </c>
       <c r="AK6">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1459,55 +1459,55 @@
         <v>2.95</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U7">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="V7">
         <v>1.49</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA7">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AB7">
         <v>2.08</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1622,16 +1622,16 @@
         <v>1.33</v>
       </c>
       <c r="Q8">
-        <v>5.63</v>
+        <v>5.8</v>
       </c>
       <c r="R8">
-        <v>2.57</v>
+        <v>2.52</v>
       </c>
       <c r="S8">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="T8">
-        <v>3.82</v>
+        <v>3.58</v>
       </c>
       <c r="U8">
         <v>2.04</v>
@@ -1643,34 +1643,34 @@
         <v>1.14</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y8">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Z8">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AA8">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AB8">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AC8">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="AD8">
         <v>1.58</v>
       </c>
       <c r="AE8">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF8">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AG8">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AK8">
         <v>1.06</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="N10">
-        <v>3.69</v>
+        <v>3.71</v>
       </c>
       <c r="O10">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="P10">
         <v>1.81</v>
@@ -1978,10 +1978,10 @@
         <v>0</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC10">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="O25">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P25">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="Q25">
         <v>3.61</v>
@@ -4411,7 +4411,7 @@
         <v>1.44</v>
       </c>
       <c r="W25">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X25">
         <v>1.05</v>
@@ -4429,7 +4429,7 @@
         <v>2</v>
       </c>
       <c r="AC25">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="AD25">
         <v>1.32</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.81</v>
+        <v>1.23</v>
       </c>
       <c r="AK25">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="O26">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="P26">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="Q26">
         <v>3.25</v>
@@ -4562,34 +4562,34 @@
         <v>2.06</v>
       </c>
       <c r="S26">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T26">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="U26">
         <v>2.81</v>
       </c>
       <c r="V26">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W26">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X26">
         <v>1.05</v>
       </c>
       <c r="Y26">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z26">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="AA26">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB26">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AC26">
         <v>3.18</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="O27">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="P27">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="Q27">
         <v>2.38</v>
@@ -4731,10 +4731,10 @@
         <v>2.63</v>
       </c>
       <c r="U27">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="V27">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W27">
         <v>1.06</v>
@@ -4743,16 +4743,16 @@
         <v>1.08</v>
       </c>
       <c r="Y27">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="Z27">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AA27">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AB27">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AC27">
         <v>4.33</v>
@@ -4764,7 +4764,7 @@
         <v>1.06</v>
       </c>
       <c r="AF27">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AG27">
         <v>1.7</v>
@@ -4873,22 +4873,22 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="O28">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P28">
-        <v>4.5</v>
+        <v>3.83</v>
       </c>
       <c r="Q28">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="R28">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="S28">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="T28">
         <v>2.8</v>
@@ -4909,7 +4909,7 @@
         <v>1.3</v>
       </c>
       <c r="Z28">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA28">
         <v>2.07</v>
@@ -4924,7 +4924,7 @@
         <v>1.28</v>
       </c>
       <c r="AE28">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF28">
         <v>1.85</v>
@@ -5069,16 +5069,16 @@
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="Z29">
         <v>2.95</v>
       </c>
       <c r="AA29">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AB29">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC29">
         <v>3.47</v>
@@ -5090,10 +5090,10 @@
         <v>1.06</v>
       </c>
       <c r="AF29">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AG29">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>1.32</v>
       </c>
       <c r="AK29">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5863,10 +5863,10 @@
         <v>2.44</v>
       </c>
       <c r="R34">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="S34">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T34">
         <v>3.3</v>
@@ -5878,31 +5878,31 @@
         <v>1.49</v>
       </c>
       <c r="W34">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X34">
         <v>1.04</v>
       </c>
       <c r="Y34">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z34">
         <v>4</v>
       </c>
       <c r="AA34">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AB34">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="AC34">
         <v>2.52</v>
       </c>
       <c r="AD34">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AE34">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF34">
         <v>1.45</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK34">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,22 +6014,22 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="O35">
         <v>3.3</v>
       </c>
       <c r="P35">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="Q35">
         <v>3</v>
       </c>
       <c r="R35">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S35">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T35">
         <v>2.9</v>
@@ -6050,10 +6050,10 @@
         <v>1.21</v>
       </c>
       <c r="Z35">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="AA35">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AB35">
         <v>1.97</v>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK35">
         <v>1.44</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.71</v>
+        <v>2.15</v>
       </c>
       <c r="O38">
+        <v>3.55</v>
+      </c>
+      <c r="P38">
+        <v>3.1</v>
+      </c>
+      <c r="Q38">
+        <v>2.51</v>
+      </c>
+      <c r="R38">
+        <v>2.27</v>
+      </c>
+      <c r="S38">
+        <v>1.22</v>
+      </c>
+      <c r="T38">
         <v>3.8</v>
       </c>
-      <c r="P38">
-        <v>4.2</v>
-      </c>
-      <c r="Q38">
-        <v>2.15</v>
-      </c>
-      <c r="R38">
-        <v>2.25</v>
-      </c>
-      <c r="S38">
-        <v>1.25</v>
-      </c>
-      <c r="T38">
-        <v>3.6</v>
-      </c>
       <c r="U38">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="V38">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="W38">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X38">
         <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z38">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="AA38">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AB38">
-        <v>2.08</v>
+        <v>2.45</v>
       </c>
       <c r="AC38">
-        <v>2.6</v>
+        <v>2.28</v>
       </c>
       <c r="AD38">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AE38">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AF38">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AG38">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AK38">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
+        <v>1.71</v>
+      </c>
+      <c r="O39">
+        <v>3.8</v>
+      </c>
+      <c r="P39">
+        <v>4.2</v>
+      </c>
+      <c r="Q39">
         <v>2.15</v>
       </c>
-      <c r="O39">
-        <v>3.55</v>
-      </c>
-      <c r="P39">
-        <v>3.1</v>
-      </c>
-      <c r="Q39">
-        <v>2.51</v>
-      </c>
       <c r="R39">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="S39">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T39">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U39">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="V39">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="W39">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X39">
         <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z39">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="AA39">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AB39">
-        <v>2.45</v>
+        <v>2.08</v>
       </c>
       <c r="AC39">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
       <c r="AD39">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AE39">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AF39">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AG39">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AK39">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.35</v>
+        <v>3.15</v>
       </c>
       <c r="O47">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P47">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="Q47">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="R47">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="S47">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="T47">
-        <v>3.5</v>
+        <v>4.15</v>
       </c>
       <c r="U47">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="V47">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="W47">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="X47">
         <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z47">
-        <v>4.85</v>
+        <v>6.29</v>
       </c>
       <c r="AA47">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="AB47">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="AC47">
-        <v>2.33</v>
+        <v>1.93</v>
       </c>
       <c r="AD47">
-        <v>1.47</v>
+        <v>1.72</v>
       </c>
       <c r="AE47">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AF47">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AG47">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AK47">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>3.15</v>
+        <v>1.63</v>
       </c>
       <c r="O48">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="P48">
-        <v>2</v>
+        <v>4.33</v>
       </c>
       <c r="Q48">
-        <v>3.4</v>
+        <v>2.04</v>
       </c>
       <c r="R48">
-        <v>2.48</v>
+        <v>2.35</v>
       </c>
       <c r="S48">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="T48">
-        <v>4.15</v>
+        <v>3.6</v>
       </c>
       <c r="U48">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="V48">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="W48">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="X48">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z48">
-        <v>6.29</v>
+        <v>4.9</v>
       </c>
       <c r="AA48">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="AB48">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="AC48">
-        <v>1.93</v>
+        <v>2.33</v>
       </c>
       <c r="AD48">
-        <v>1.72</v>
+        <v>1.56</v>
       </c>
       <c r="AE48">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AF48">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AG48">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AK48">
-        <v>1.25</v>
+        <v>2.05</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.63</v>
+        <v>2.22</v>
       </c>
       <c r="O49">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="P49">
-        <v>4.33</v>
+        <v>2.75</v>
       </c>
       <c r="Q49">
-        <v>2.04</v>
+        <v>3.21</v>
       </c>
       <c r="R49">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="S49">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T49">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="U49">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="V49">
-        <v>1.62</v>
+        <v>1.39</v>
       </c>
       <c r="W49">
+        <v>1.11</v>
+      </c>
+      <c r="X49">
+        <v>1.01</v>
+      </c>
+      <c r="Y49">
+        <v>1.18</v>
+      </c>
+      <c r="Z49">
+        <v>3.9</v>
+      </c>
+      <c r="AA49">
+        <v>1.73</v>
+      </c>
+      <c r="AB49">
+        <v>2</v>
+      </c>
+      <c r="AC49">
+        <v>2.72</v>
+      </c>
+      <c r="AD49">
+        <v>1.42</v>
+      </c>
+      <c r="AE49">
         <v>1.15</v>
       </c>
-      <c r="X49">
-        <v>1.02</v>
-      </c>
-      <c r="Y49">
-        <v>1.11</v>
-      </c>
-      <c r="Z49">
-        <v>4.9</v>
-      </c>
-      <c r="AA49">
-        <v>1.53</v>
-      </c>
-      <c r="AB49">
-        <v>2.38</v>
-      </c>
-      <c r="AC49">
-        <v>2.33</v>
-      </c>
-      <c r="AD49">
-        <v>1.56</v>
-      </c>
-      <c r="AE49">
-        <v>1.25</v>
-      </c>
       <c r="AF49">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG49">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AK49">
-        <v>2.05</v>
+        <v>1.48</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,80 +8459,80 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.22</v>
+        <v>1.5</v>
       </c>
       <c r="O50">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="P50">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="Q50">
-        <v>3.21</v>
+        <v>1.91</v>
       </c>
       <c r="R50">
-        <v>2.05</v>
+        <v>2.48</v>
       </c>
       <c r="S50">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="T50">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="U50">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="V50">
-        <v>1.39</v>
+        <v>1.64</v>
       </c>
       <c r="W50">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z50">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AA50">
-        <v>1.73</v>
+        <v>1.47</v>
       </c>
       <c r="AB50">
-        <v>2</v>
+        <v>2.49</v>
       </c>
       <c r="AC50">
-        <v>2.72</v>
+        <v>2.2</v>
       </c>
       <c r="AD50">
-        <v>1.42</v>
+        <v>1.65</v>
       </c>
       <c r="AE50">
+        <v>1.24</v>
+      </c>
+      <c r="AF50">
+        <v>1.53</v>
+      </c>
+      <c r="AG50">
+        <v>2.28</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ50">
         <v>1.15</v>
       </c>
-      <c r="AF50">
-        <v>1.55</v>
-      </c>
-      <c r="AG50">
-        <v>1.95</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ50">
-        <v>1.26</v>
-      </c>
       <c r="AK50">
-        <v>1.48</v>
+        <v>2.33</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.5</v>
+        <v>2.35</v>
       </c>
       <c r="O51">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="P51">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q51">
-        <v>1.91</v>
+        <v>2.75</v>
       </c>
       <c r="R51">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="S51">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="T51">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="U51">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="V51">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="W51">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
         <v>1.14</v>
       </c>
       <c r="Z51">
-        <v>3.6</v>
+        <v>4.85</v>
       </c>
       <c r="AA51">
+        <v>1.57</v>
+      </c>
+      <c r="AB51">
+        <v>2.25</v>
+      </c>
+      <c r="AC51">
+        <v>2.33</v>
+      </c>
+      <c r="AD51">
         <v>1.47</v>
       </c>
-      <c r="AB51">
-        <v>2.49</v>
-      </c>
-      <c r="AC51">
-        <v>2.2</v>
-      </c>
-      <c r="AD51">
-        <v>1.65</v>
-      </c>
       <c r="AE51">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AF51">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AG51">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AK51">
-        <v>2.33</v>
+        <v>1.49</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,16 +8785,16 @@
         </is>
       </c>
       <c r="N52">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="O52">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="P52">
         <v>1.46</v>
       </c>
       <c r="Q52">
-        <v>5.65</v>
+        <v>5</v>
       </c>
       <c r="R52">
         <v>2.85</v>
@@ -8818,25 +8818,25 @@
         <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Z52">
-        <v>6.1</v>
+        <v>6.25</v>
       </c>
       <c r="AA52">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AB52">
         <v>3.1</v>
       </c>
       <c r="AC52">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AD52">
         <v>1.85</v>
       </c>
       <c r="AE52">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AF52">
         <v>1.44</v>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>2.75</v>
+        <v>1.12</v>
       </c>
       <c r="AK52">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9763,19 +9763,19 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.35</v>
+        <v>2.18</v>
       </c>
       <c r="O58">
         <v>3.6</v>
       </c>
       <c r="P58">
-        <v>2.64</v>
+        <v>2.69</v>
       </c>
       <c r="Q58">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="R58">
-        <v>2.27</v>
+        <v>2.48</v>
       </c>
       <c r="S58">
         <v>1.22</v>
@@ -9790,22 +9790,22 @@
         <v>1.6</v>
       </c>
       <c r="W58">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X58">
         <v>1.03</v>
       </c>
       <c r="Y58">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z58">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AA58">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AB58">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="AC58">
         <v>2.3</v>
@@ -9814,7 +9814,7 @@
         <v>1.55</v>
       </c>
       <c r="AE58">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AF58">
         <v>1.44</v>
@@ -9836,7 +9836,7 @@
         <v>1.22</v>
       </c>
       <c r="AK58">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10252,16 +10252,16 @@
         </is>
       </c>
       <c r="N61">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="O61">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P61">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="Q61">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="R61">
         <v>2.43</v>
@@ -10270,16 +10270,16 @@
         <v>1.29</v>
       </c>
       <c r="T61">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="U61">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="V61">
         <v>1.55</v>
       </c>
       <c r="W61">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X61">
         <v>1.04</v>
@@ -10288,19 +10288,19 @@
         <v>1.15</v>
       </c>
       <c r="Z61">
-        <v>4.3</v>
+        <v>4.35</v>
       </c>
       <c r="AA61">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AB61">
         <v>2.19</v>
       </c>
       <c r="AC61">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="AD61">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AE61">
         <v>1.19</v>
@@ -10325,7 +10325,7 @@
         <v>1.22</v>
       </c>
       <c r="AK61">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10424,7 +10424,7 @@
         <v>3.16</v>
       </c>
       <c r="Q62">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="R62">
         <v>2.38</v>
@@ -10433,46 +10433,46 @@
         <v>1.25</v>
       </c>
       <c r="T62">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="U62">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="V62">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W62">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z62">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="AA62">
         <v>1.52</v>
       </c>
       <c r="AB62">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AC62">
         <v>2.3</v>
       </c>
       <c r="AD62">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AE62">
         <v>1.18</v>
       </c>
       <c r="AF62">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AG62">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -13533,10 +13533,10 @@
         <v>4.5</v>
       </c>
       <c r="U81">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="V81">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="W81">
         <v>1.22</v>
@@ -13548,7 +13548,7 @@
         <v>1.04</v>
       </c>
       <c r="Z81">
-        <v>6.75</v>
+        <v>6</v>
       </c>
       <c r="AA81">
         <v>1.32</v>
@@ -13566,10 +13566,10 @@
         <v>1.42</v>
       </c>
       <c r="AF81">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AG81">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AK81">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="O83">
         <v>3.4</v>
       </c>
       <c r="P83">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="Q83">
         <v>2.9</v>
       </c>
       <c r="R83">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="S83">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T83">
-        <v>2.85</v>
+        <v>3.06</v>
       </c>
       <c r="U83">
-        <v>2.71</v>
+        <v>2.77</v>
       </c>
       <c r="V83">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="W83">
         <v>1.08</v>
       </c>
       <c r="X83">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y83">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z83">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AA83">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AB83">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC83">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="AD83">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AE83">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF83">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AG83">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.47</v>
+        <v>1.31</v>
       </c>
       <c r="AK83">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="O84">
         <v>3.4</v>
       </c>
       <c r="P84">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="Q84">
         <v>2.9</v>
       </c>
       <c r="R84">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="S84">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T84">
-        <v>3.06</v>
+        <v>2.85</v>
       </c>
       <c r="U84">
-        <v>2.77</v>
+        <v>2.71</v>
       </c>
       <c r="V84">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="W84">
         <v>1.08</v>
       </c>
       <c r="X84">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y84">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z84">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AA84">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AB84">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC84">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="AD84">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AE84">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF84">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AG84">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="AK84">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -16283,16 +16283,16 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="O98">
+        <v>4.1</v>
+      </c>
+      <c r="P98">
         <v>4.35</v>
       </c>
-      <c r="P98">
-        <v>5.3</v>
-      </c>
       <c r="Q98">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="R98">
         <v>2.42</v>
@@ -16304,10 +16304,10 @@
         <v>3.8</v>
       </c>
       <c r="U98">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="V98">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="W98">
         <v>1.13</v>
@@ -16316,22 +16316,22 @@
         <v>1.02</v>
       </c>
       <c r="Y98">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Z98">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AA98">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AB98">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="AC98">
         <v>2.16</v>
       </c>
       <c r="AD98">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AE98">
         <v>1.22</v>
@@ -16340,7 +16340,7 @@
         <v>1.5</v>
       </c>
       <c r="AG98">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK98">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -17913,28 +17913,28 @@
         </is>
       </c>
       <c r="N108">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="O108">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P108">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q108">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="R108">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="S108">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T108">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="U108">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="V108">
         <v>1.4</v>
@@ -17958,13 +17958,13 @@
         <v>1.92</v>
       </c>
       <c r="AC108">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="AD108">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE108">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF108">
         <v>1.66</v>
@@ -17986,7 +17986,7 @@
         <v>1.53</v>
       </c>
       <c r="AK108">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -19706,13 +19706,13 @@
         </is>
       </c>
       <c r="N119">
-        <v>2.17</v>
+        <v>2.26</v>
       </c>
       <c r="O119">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="P119">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="Q119">
         <v>2.63</v>
@@ -19724,10 +19724,10 @@
         <v>1.33</v>
       </c>
       <c r="T119">
-        <v>3.27</v>
+        <v>3.24</v>
       </c>
       <c r="U119">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="V119">
         <v>1.45</v>
@@ -19742,28 +19742,28 @@
         <v>1.25</v>
       </c>
       <c r="Z119">
-        <v>4.06</v>
+        <v>4.04</v>
       </c>
       <c r="AA119">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AB119">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AC119">
         <v>2.8</v>
       </c>
       <c r="AD119">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE119">
         <v>1.12</v>
       </c>
       <c r="AF119">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG119">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -20201,10 +20201,10 @@
         <v>4</v>
       </c>
       <c r="P122">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Q122">
-        <v>5.66</v>
+        <v>5.5</v>
       </c>
       <c r="R122">
         <v>2.42</v>
@@ -20213,13 +20213,13 @@
         <v>1.25</v>
       </c>
       <c r="T122">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="U122">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V122">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="W122">
         <v>1.11</v>
@@ -20237,22 +20237,22 @@
         <v>1.53</v>
       </c>
       <c r="AB122">
-        <v>2.37</v>
+        <v>2.17</v>
       </c>
       <c r="AC122">
         <v>2.34</v>
       </c>
       <c r="AD122">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AE122">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF122">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AG122">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,7 +20265,7 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AK122">
         <v>1.1</v>
@@ -23292,31 +23292,31 @@
         </is>
       </c>
       <c r="N141">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="O141">
         <v>3.2</v>
       </c>
       <c r="P141">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="Q141">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="R141">
         <v>2</v>
       </c>
       <c r="S141">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="T141">
-        <v>2.33</v>
+        <v>2.39</v>
       </c>
       <c r="U141">
         <v>3.58</v>
       </c>
       <c r="V141">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="W141">
         <v>1.05</v>
@@ -23331,10 +23331,10 @@
         <v>2.45</v>
       </c>
       <c r="AA141">
-        <v>2.46</v>
+        <v>2.2</v>
       </c>
       <c r="AB141">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AC141">
         <v>5.05</v>
@@ -23343,7 +23343,7 @@
         <v>1.15</v>
       </c>
       <c r="AE141">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF141">
         <v>2.25</v>
@@ -23488,10 +23488,10 @@
         <v>1.09</v>
       </c>
       <c r="Y142">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="Z142">
-        <v>2.21</v>
+        <v>2.28</v>
       </c>
       <c r="AA142">
         <v>2.7</v>
@@ -23500,10 +23500,10 @@
         <v>1.4</v>
       </c>
       <c r="AC142">
-        <v>5</v>
+        <v>5.35</v>
       </c>
       <c r="AD142">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AE142">
         <v>1.03</v>
@@ -23618,7 +23618,7 @@
         </is>
       </c>
       <c r="N143">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="O143">
         <v>2.7</v>
@@ -23627,7 +23627,7 @@
         <v>4.33</v>
       </c>
       <c r="Q143">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="R143">
         <v>1.78</v>
@@ -23688,7 +23688,7 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AK143">
         <v>1.75</v>
@@ -28508,61 +28508,61 @@
         </is>
       </c>
       <c r="N173">
-        <v>2.32</v>
+        <v>2.37</v>
       </c>
       <c r="O173">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P173">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="Q173">
         <v>2.9</v>
       </c>
       <c r="R173">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S173">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T173">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="U173">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="V173">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W173">
         <v>1.08</v>
       </c>
       <c r="X173">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y173">
         <v>1.33</v>
       </c>
       <c r="Z173">
-        <v>3.27</v>
+        <v>3.1</v>
       </c>
       <c r="AA173">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AB173">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC173">
         <v>3.8</v>
       </c>
       <c r="AD173">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE173">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF173">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AG173">
         <v>1.85</v>
@@ -28674,10 +28674,10 @@
         <v>2.15</v>
       </c>
       <c r="O174">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P174">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="Q174">
         <v>2.94</v>
@@ -28695,7 +28695,7 @@
         <v>2.8</v>
       </c>
       <c r="V174">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W174">
         <v>1.07</v>
@@ -28704,31 +28704,31 @@
         <v>1.05</v>
       </c>
       <c r="Y174">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Z174">
         <v>3.4</v>
       </c>
       <c r="AA174">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="AB174">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AC174">
-        <v>3.35</v>
+        <v>2.92</v>
       </c>
       <c r="AD174">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AE174">
         <v>1.08</v>
       </c>
       <c r="AF174">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AG174">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AH174" t="inlineStr">
         <is>
@@ -28744,7 +28744,7 @@
         <v>1.25</v>
       </c>
       <c r="AK174">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AL174">
         <v>0</v>
@@ -29018,7 +29018,7 @@
         <v>2.05</v>
       </c>
       <c r="U176">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="V176">
         <v>1.16</v>
@@ -29030,25 +29030,25 @@
         <v>1.11</v>
       </c>
       <c r="Y176">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="Z176">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AA176">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AB176">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AC176">
-        <v>5.87</v>
+        <v>5.25</v>
       </c>
       <c r="AD176">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AE176">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF176">
         <v>2.4</v>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AK176">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -30467,10 +30467,10 @@
         <v>2.38</v>
       </c>
       <c r="O185">
-        <v>3.86</v>
+        <v>3.4</v>
       </c>
       <c r="P185">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="Q185">
         <v>2.88</v>
@@ -31128,10 +31128,10 @@
         <v>3.28</v>
       </c>
       <c r="R189">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="S189">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="T189">
         <v>2.56</v>
@@ -31143,7 +31143,7 @@
         <v>1.33</v>
       </c>
       <c r="W189">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X189">
         <v>1.03</v>
@@ -31164,10 +31164,10 @@
         <v>3.62</v>
       </c>
       <c r="AD189">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AE189">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF189">
         <v>1.8</v>
@@ -31189,7 +31189,7 @@
         <v>1.35</v>
       </c>
       <c r="AK189">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AL189">
         <v>0</v>
@@ -31282,49 +31282,49 @@
         <v>1.48</v>
       </c>
       <c r="O190">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P190">
-        <v>5.25</v>
+        <v>4.7</v>
       </c>
       <c r="Q190">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="R190">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S190">
         <v>1.32</v>
       </c>
       <c r="T190">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U190">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="V190">
         <v>1.44</v>
       </c>
       <c r="W190">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X190">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y190">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="Z190">
-        <v>3.68</v>
+        <v>3.89</v>
       </c>
       <c r="AA190">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AB190">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC190">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="AD190">
         <v>1.36</v>
@@ -31333,11 +31333,11 @@
         <v>1.11</v>
       </c>
       <c r="AF190">
+        <v>1.83</v>
+      </c>
+      <c r="AG190">
         <v>1.8</v>
       </c>
-      <c r="AG190">
-        <v>1.85</v>
-      </c>
       <c r="AH190" t="inlineStr">
         <is>
           <t>[]</t>
@@ -31349,10 +31349,10 @@
         </is>
       </c>
       <c r="AJ190">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AK190">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="AL190">
         <v>0</v>
@@ -31451,55 +31451,55 @@
         <v>0</v>
       </c>
       <c r="Q191">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R191">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S191">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T191">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U191">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="V191">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W191">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X191">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y191">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z191">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA191">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB191">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC191">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD191">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE191">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF191">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG191">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH191" t="inlineStr">
         <is>
@@ -31512,10 +31512,10 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK191">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,64 +32257,64 @@
         </is>
       </c>
       <c r="N196">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="O196">
+        <v>3.58</v>
+      </c>
+      <c r="P196">
         <v>2.95</v>
       </c>
-      <c r="P196">
-        <v>2.88</v>
-      </c>
       <c r="Q196">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="R196">
-        <v>1.98</v>
+        <v>2.38</v>
       </c>
       <c r="S196">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="T196">
-        <v>2.5</v>
+        <v>3.18</v>
       </c>
       <c r="U196">
-        <v>3.08</v>
+        <v>2.14</v>
       </c>
       <c r="V196">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="W196">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X196">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y196">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="Z196">
-        <v>2.69</v>
+        <v>4.3</v>
       </c>
       <c r="AA196">
-        <v>2.19</v>
+        <v>1.68</v>
       </c>
       <c r="AB196">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="AC196">
-        <v>3.9</v>
+        <v>2.56</v>
       </c>
       <c r="AD196">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="AE196">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AF196">
-        <v>1.88</v>
+        <v>1.5</v>
       </c>
       <c r="AG196">
-        <v>1.81</v>
+        <v>2.35</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK196">
-        <v>1.45</v>
+        <v>1.76</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,64 +32420,64 @@
         </is>
       </c>
       <c r="N197">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="O197">
-        <v>3.58</v>
+        <v>3.35</v>
       </c>
       <c r="P197">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="Q197">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="R197">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="S197">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T197">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="U197">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="V197">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W197">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X197">
         <v>1.02</v>
       </c>
       <c r="Y197">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z197">
-        <v>4.05</v>
+        <v>4.33</v>
       </c>
       <c r="AA197">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AB197">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC197">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="AD197">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AE197">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF197">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AG197">
-        <v>2.17</v>
+        <v>2.38</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32493,7 +32493,7 @@
         <v>1.21</v>
       </c>
       <c r="AK197">
-        <v>1.77</v>
+        <v>1.41</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G198">
@@ -32583,31 +32583,31 @@
         </is>
       </c>
       <c r="N198">
-        <v>2.07</v>
+        <v>3.55</v>
       </c>
       <c r="O198">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="P198">
-        <v>2.85</v>
+        <v>1.78</v>
       </c>
       <c r="Q198">
-        <v>2.75</v>
+        <v>3.45</v>
       </c>
       <c r="R198">
-        <v>2.37</v>
+        <v>2.43</v>
       </c>
       <c r="S198">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T198">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="U198">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="V198">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="W198">
         <v>1.08</v>
@@ -32616,31 +32616,31 @@
         <v>1.02</v>
       </c>
       <c r="Y198">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z198">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
       <c r="AA198">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="AB198">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="AC198">
-        <v>2.49</v>
+        <v>2.59</v>
       </c>
       <c r="AD198">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE198">
         <v>1.16</v>
       </c>
       <c r="AF198">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="AG198">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AH198" t="inlineStr">
         <is>
@@ -32653,10 +32653,10 @@
         </is>
       </c>
       <c r="AJ198">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK198">
-        <v>1.57</v>
+        <v>1.24</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G199">
@@ -32746,19 +32746,19 @@
         </is>
       </c>
       <c r="N199">
-        <v>3.6</v>
+        <v>2.18</v>
       </c>
       <c r="O199">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="P199">
-        <v>1.77</v>
+        <v>2.85</v>
       </c>
       <c r="Q199">
-        <v>4.33</v>
+        <v>2.74</v>
       </c>
       <c r="R199">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S199">
         <v>1.29</v>
@@ -32767,43 +32767,43 @@
         <v>3.25</v>
       </c>
       <c r="U199">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="V199">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="W199">
         <v>1.08</v>
       </c>
       <c r="X199">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y199">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="Z199">
-        <v>4.15</v>
+        <v>3.65</v>
       </c>
       <c r="AA199">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB199">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="AC199">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AD199">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AE199">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF199">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG199">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="AH199" t="inlineStr">
         <is>
@@ -32816,10 +32816,10 @@
         </is>
       </c>
       <c r="AJ199">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK199">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="AL199">
         <v>0</v>
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G200">
@@ -32909,64 +32909,64 @@
         </is>
       </c>
       <c r="N200">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="O200">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="P200">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="Q200">
-        <v>2.76</v>
+        <v>3.1</v>
       </c>
       <c r="R200">
-        <v>2.21</v>
+        <v>1.98</v>
       </c>
       <c r="S200">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="T200">
-        <v>3.15</v>
+        <v>2.4</v>
       </c>
       <c r="U200">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="V200">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="W200">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X200">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y200">
+        <v>1.38</v>
+      </c>
+      <c r="Z200">
+        <v>2.63</v>
+      </c>
+      <c r="AA200">
+        <v>2.19</v>
+      </c>
+      <c r="AB200">
+        <v>1.6</v>
+      </c>
+      <c r="AC200">
+        <v>3.92</v>
+      </c>
+      <c r="AD200">
         <v>1.18</v>
       </c>
-      <c r="Z200">
-        <v>3.88</v>
-      </c>
-      <c r="AA200">
-        <v>1.69</v>
-      </c>
-      <c r="AB200">
-        <v>2.04</v>
-      </c>
-      <c r="AC200">
-        <v>2.66</v>
-      </c>
-      <c r="AD200">
-        <v>1.37</v>
-      </c>
       <c r="AE200">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AF200">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AG200">
-        <v>2.23</v>
+        <v>1.76</v>
       </c>
       <c r="AH200" t="inlineStr">
         <is>
@@ -32979,10 +32979,10 @@
         </is>
       </c>
       <c r="AJ200">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK200">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AL200">
         <v>0</v>
@@ -33075,10 +33075,10 @@
         <v>1.64</v>
       </c>
       <c r="O201">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="P201">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="Q201">
         <v>0</v>
@@ -33235,13 +33235,13 @@
         </is>
       </c>
       <c r="N202">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="O202">
         <v>3.3</v>
       </c>
       <c r="P202">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q202">
         <v>2.75</v>
@@ -33250,7 +33250,7 @@
         <v>2.2</v>
       </c>
       <c r="S202">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T202">
         <v>2.75</v>
@@ -33262,25 +33262,25 @@
         <v>1.44</v>
       </c>
       <c r="W202">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X202">
         <v>1</v>
       </c>
       <c r="Y202">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z202">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="AA202">
         <v>1.83</v>
       </c>
       <c r="AB202">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AC202">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="AD202">
         <v>1.3</v>
@@ -33289,10 +33289,10 @@
         <v>1.07</v>
       </c>
       <c r="AF202">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AG202">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AH202" t="inlineStr">
         <is>
@@ -33724,13 +33724,13 @@
         </is>
       </c>
       <c r="N205">
-        <v>2.63</v>
+        <v>2.43</v>
       </c>
       <c r="O205">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="P205">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="Q205">
         <v>3.24</v>
@@ -33739,37 +33739,37 @@
         <v>1.95</v>
       </c>
       <c r="S205">
+        <v>1.43</v>
+      </c>
+      <c r="T205">
+        <v>2.62</v>
+      </c>
+      <c r="U205">
+        <v>2.65</v>
+      </c>
+      <c r="V205">
         <v>1.4</v>
       </c>
-      <c r="T205">
-        <v>3</v>
-      </c>
-      <c r="U205">
-        <v>2.88</v>
-      </c>
-      <c r="V205">
-        <v>1.42</v>
-      </c>
       <c r="W205">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X205">
         <v>1.03</v>
       </c>
       <c r="Y205">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z205">
         <v>3.4</v>
       </c>
       <c r="AA205">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="AB205">
         <v>1.86</v>
       </c>
       <c r="AC205">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AD205">
         <v>1.29</v>
@@ -34050,7 +34050,7 @@
         </is>
       </c>
       <c r="N207">
-        <v>4.75</v>
+        <v>4.97</v>
       </c>
       <c r="O207">
         <v>4</v>
@@ -34213,13 +34213,13 @@
         </is>
       </c>
       <c r="N208">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="O208">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P208">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="Q208">
         <v>2.38</v>
@@ -34228,22 +34228,22 @@
         <v>2.1</v>
       </c>
       <c r="S208">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T208">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="U208">
-        <v>2.96</v>
+        <v>3.14</v>
       </c>
       <c r="V208">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W208">
         <v>1.06</v>
       </c>
       <c r="X208">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y208">
         <v>1.33</v>
@@ -34252,25 +34252,25 @@
         <v>2.83</v>
       </c>
       <c r="AA208">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AB208">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AC208">
-        <v>3.38</v>
+        <v>3.7</v>
       </c>
       <c r="AD208">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE208">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF208">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG208">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AH208" t="inlineStr">
         <is>
@@ -34286,7 +34286,7 @@
         <v>1.26</v>
       </c>
       <c r="AK208">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AL208">
         <v>0</v>
@@ -34388,22 +34388,22 @@
         <v>3.05</v>
       </c>
       <c r="R209">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="S209">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T209">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="U209">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="V209">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W209">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X209">
         <v>1.01</v>
@@ -34446,10 +34446,10 @@
         </is>
       </c>
       <c r="AJ209">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AK209">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -34548,71 +34548,71 @@
         <v>1.77</v>
       </c>
       <c r="Q210">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="R210">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="S210">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T210">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U210">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="V210">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="W210">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X210">
         <v>1.03</v>
       </c>
       <c r="Y210">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z210">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AA210">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AB210">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="AC210">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="AD210">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE210">
+        <v>1.12</v>
+      </c>
+      <c r="AF210">
+        <v>1.68</v>
+      </c>
+      <c r="AG210">
+        <v>2.02</v>
+      </c>
+      <c r="AH210" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI210" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ210">
+        <v>2</v>
+      </c>
+      <c r="AK210">
         <v>1.15</v>
-      </c>
-      <c r="AF210">
-        <v>1.62</v>
-      </c>
-      <c r="AG210">
-        <v>2.08</v>
-      </c>
-      <c r="AH210" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI210" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ210">
-        <v>1.95</v>
-      </c>
-      <c r="AK210">
-        <v>1.22</v>
       </c>
       <c r="AL210">
         <v>0</v>
@@ -34717,19 +34717,19 @@
         <v>2.23</v>
       </c>
       <c r="S211">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T211">
         <v>3.15</v>
       </c>
       <c r="U211">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="V211">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W211">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X211">
         <v>1.02</v>
@@ -34741,7 +34741,7 @@
         <v>4</v>
       </c>
       <c r="AA211">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AB211">
         <v>2.2</v>
@@ -34756,7 +34756,7 @@
         <v>1.14</v>
       </c>
       <c r="AF211">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AG211">
         <v>2.23</v>
@@ -34775,7 +34775,7 @@
         <v>1.22</v>
       </c>
       <c r="AK211">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="AL211">
         <v>0</v>
@@ -34886,7 +34886,7 @@
         <v>2.96</v>
       </c>
       <c r="U212">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="V212">
         <v>1.38</v>
@@ -34895,7 +34895,7 @@
         <v>1.06</v>
       </c>
       <c r="X212">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y212">
         <v>1.22</v>
@@ -34904,25 +34904,25 @@
         <v>3.5</v>
       </c>
       <c r="AA212">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB212">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AC212">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AD212">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE212">
         <v>1.08</v>
       </c>
       <c r="AF212">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AG212">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="AH212" t="inlineStr">
         <is>
@@ -34938,7 +34938,7 @@
         <v>1.44</v>
       </c>
       <c r="AK212">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AL212">
         <v>0</v>
@@ -35037,22 +35037,22 @@
         <v>1.77</v>
       </c>
       <c r="Q213">
-        <v>4.62</v>
+        <v>4.2</v>
       </c>
       <c r="R213">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="S213">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T213">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="U213">
         <v>2.75</v>
       </c>
       <c r="V213">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="W213">
         <v>1.06</v>
@@ -35067,10 +35067,10 @@
         <v>3.4</v>
       </c>
       <c r="AA213">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB213">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC213">
         <v>3.05</v>
@@ -35098,10 +35098,10 @@
         </is>
       </c>
       <c r="AJ213">
-        <v>1.83</v>
+        <v>1.21</v>
       </c>
       <c r="AK213">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AL213">
         <v>0</v>

--- a/jogos_2026-08-08.xlsx
+++ b/jogos_2026-08-08.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O6">
-        <v>3.7</v>
+        <v>3.48</v>
       </c>
       <c r="P6">
+        <v>2.95</v>
+      </c>
+      <c r="Q6">
+        <v>2.38</v>
+      </c>
+      <c r="R6">
+        <v>2.35</v>
+      </c>
+      <c r="S6">
+        <v>1.29</v>
+      </c>
+      <c r="T6">
         <v>3.25</v>
       </c>
-      <c r="Q6">
-        <v>2.48</v>
-      </c>
-      <c r="R6">
-        <v>2.43</v>
-      </c>
-      <c r="S6">
-        <v>1.25</v>
-      </c>
-      <c r="T6">
-        <v>3.34</v>
-      </c>
       <c r="U6">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="V6">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="W6">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z6">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AA6">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AB6">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="AC6">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="AD6">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="AE6">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF6">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="AG6">
-        <v>2.48</v>
+        <v>2.23</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK6">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="O7">
-        <v>3.48</v>
+        <v>3.7</v>
       </c>
       <c r="P7">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="Q7">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="R7">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="S7">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T7">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="U7">
-        <v>2.44</v>
+        <v>2.12</v>
       </c>
       <c r="V7">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="W7">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X7">
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z7">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AA7">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AB7">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="AC7">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="AD7">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="AE7">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF7">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="AG7">
-        <v>2.23</v>
+        <v>2.48</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK7">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="O83">
         <v>3.4</v>
       </c>
       <c r="P83">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="Q83">
         <v>2.9</v>
       </c>
       <c r="R83">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="S83">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T83">
-        <v>3.06</v>
+        <v>2.85</v>
       </c>
       <c r="U83">
-        <v>2.77</v>
+        <v>2.71</v>
       </c>
       <c r="V83">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="W83">
         <v>1.08</v>
       </c>
       <c r="X83">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y83">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z83">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AA83">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AB83">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC83">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="AD83">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AE83">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF83">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AG83">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="AK83">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="O84">
         <v>3.4</v>
       </c>
       <c r="P84">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="Q84">
         <v>2.9</v>
       </c>
       <c r="R84">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="S84">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T84">
-        <v>2.85</v>
+        <v>3.06</v>
       </c>
       <c r="U84">
-        <v>2.71</v>
+        <v>2.77</v>
       </c>
       <c r="V84">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="W84">
         <v>1.08</v>
       </c>
       <c r="X84">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y84">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z84">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AA84">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AB84">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC84">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="AD84">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AE84">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF84">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AG84">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.47</v>
+        <v>1.31</v>
       </c>
       <c r="AK84">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G199">
@@ -32746,80 +32746,80 @@
         </is>
       </c>
       <c r="N199">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="O199">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="P199">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="Q199">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="R199">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="S199">
+        <v>1.43</v>
+      </c>
+      <c r="T199">
+        <v>2.4</v>
+      </c>
+      <c r="U199">
+        <v>3.2</v>
+      </c>
+      <c r="V199">
+        <v>1.3</v>
+      </c>
+      <c r="W199">
+        <v>1.03</v>
+      </c>
+      <c r="X199">
+        <v>1.03</v>
+      </c>
+      <c r="Y199">
+        <v>1.38</v>
+      </c>
+      <c r="Z199">
+        <v>2.63</v>
+      </c>
+      <c r="AA199">
+        <v>2.19</v>
+      </c>
+      <c r="AB199">
+        <v>1.6</v>
+      </c>
+      <c r="AC199">
+        <v>3.92</v>
+      </c>
+      <c r="AD199">
+        <v>1.18</v>
+      </c>
+      <c r="AE199">
+        <v>1.03</v>
+      </c>
+      <c r="AF199">
+        <v>1.91</v>
+      </c>
+      <c r="AG199">
+        <v>1.76</v>
+      </c>
+      <c r="AH199" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI199" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ199">
         <v>1.29</v>
       </c>
-      <c r="T199">
-        <v>3.25</v>
-      </c>
-      <c r="U199">
-        <v>2.44</v>
-      </c>
-      <c r="V199">
-        <v>1.43</v>
-      </c>
-      <c r="W199">
-        <v>1.08</v>
-      </c>
-      <c r="X199">
-        <v>1.01</v>
-      </c>
-      <c r="Y199">
-        <v>1.21</v>
-      </c>
-      <c r="Z199">
-        <v>3.65</v>
-      </c>
-      <c r="AA199">
-        <v>1.7</v>
-      </c>
-      <c r="AB199">
-        <v>2.03</v>
-      </c>
-      <c r="AC199">
-        <v>2.7</v>
-      </c>
-      <c r="AD199">
-        <v>1.37</v>
-      </c>
-      <c r="AE199">
-        <v>1.12</v>
-      </c>
-      <c r="AF199">
-        <v>1.57</v>
-      </c>
-      <c r="AG199">
-        <v>2.23</v>
-      </c>
-      <c r="AH199" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI199" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ199">
-        <v>1.22</v>
-      </c>
       <c r="AK199">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AL199">
         <v>0</v>
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G200">
@@ -32909,64 +32909,64 @@
         </is>
       </c>
       <c r="N200">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="O200">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="P200">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="Q200">
-        <v>3.1</v>
+        <v>2.74</v>
       </c>
       <c r="R200">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="S200">
+        <v>1.29</v>
+      </c>
+      <c r="T200">
+        <v>3.25</v>
+      </c>
+      <c r="U200">
+        <v>2.44</v>
+      </c>
+      <c r="V200">
         <v>1.43</v>
       </c>
-      <c r="T200">
-        <v>2.4</v>
-      </c>
-      <c r="U200">
-        <v>3.2</v>
-      </c>
-      <c r="V200">
-        <v>1.3</v>
-      </c>
       <c r="W200">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X200">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y200">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="Z200">
-        <v>2.63</v>
+        <v>3.65</v>
       </c>
       <c r="AA200">
-        <v>2.19</v>
+        <v>1.7</v>
       </c>
       <c r="AB200">
-        <v>1.6</v>
+        <v>2.03</v>
       </c>
       <c r="AC200">
-        <v>3.92</v>
+        <v>2.7</v>
       </c>
       <c r="AD200">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="AE200">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AF200">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AG200">
-        <v>1.76</v>
+        <v>2.23</v>
       </c>
       <c r="AH200" t="inlineStr">
         <is>
@@ -32979,10 +32979,10 @@
         </is>
       </c>
       <c r="AJ200">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK200">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AL200">
         <v>0</v>

--- a/jogos_2026-08-08.xlsx
+++ b/jogos_2026-08-08.xlsx
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
+        <v>1.71</v>
+      </c>
+      <c r="O38">
+        <v>3.8</v>
+      </c>
+      <c r="P38">
+        <v>4.2</v>
+      </c>
+      <c r="Q38">
         <v>2.15</v>
       </c>
-      <c r="O38">
-        <v>3.55</v>
-      </c>
-      <c r="P38">
-        <v>3.1</v>
-      </c>
-      <c r="Q38">
-        <v>2.51</v>
-      </c>
       <c r="R38">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="S38">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T38">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U38">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="V38">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="W38">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X38">
         <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z38">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="AA38">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AB38">
-        <v>2.45</v>
+        <v>2.08</v>
       </c>
       <c r="AC38">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
       <c r="AD38">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AE38">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AF38">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AG38">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AK38">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.71</v>
+        <v>2.15</v>
       </c>
       <c r="O39">
+        <v>3.55</v>
+      </c>
+      <c r="P39">
+        <v>3.1</v>
+      </c>
+      <c r="Q39">
+        <v>2.51</v>
+      </c>
+      <c r="R39">
+        <v>2.27</v>
+      </c>
+      <c r="S39">
+        <v>1.22</v>
+      </c>
+      <c r="T39">
         <v>3.8</v>
       </c>
-      <c r="P39">
-        <v>4.2</v>
-      </c>
-      <c r="Q39">
-        <v>2.15</v>
-      </c>
-      <c r="R39">
-        <v>2.25</v>
-      </c>
-      <c r="S39">
-        <v>1.25</v>
-      </c>
-      <c r="T39">
-        <v>3.6</v>
-      </c>
       <c r="U39">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="V39">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="W39">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X39">
         <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z39">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="AA39">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AB39">
-        <v>2.08</v>
+        <v>2.45</v>
       </c>
       <c r="AC39">
-        <v>2.6</v>
+        <v>2.28</v>
       </c>
       <c r="AD39">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AE39">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AF39">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AG39">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AK39">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -23307,13 +23307,13 @@
         <v>2</v>
       </c>
       <c r="S141">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="T141">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="U141">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="V141">
         <v>1.21</v>
@@ -23331,7 +23331,7 @@
         <v>2.45</v>
       </c>
       <c r="AA141">
-        <v>2.2</v>
+        <v>2.59</v>
       </c>
       <c r="AB141">
         <v>1.48</v>
@@ -23461,19 +23461,19 @@
         <v>3</v>
       </c>
       <c r="P142">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q142">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="R142">
         <v>1.81</v>
       </c>
       <c r="S142">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="T142">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="U142">
         <v>3.8</v>
@@ -23494,7 +23494,7 @@
         <v>2.28</v>
       </c>
       <c r="AA142">
-        <v>2.7</v>
+        <v>2.86</v>
       </c>
       <c r="AB142">
         <v>1.4</v>
@@ -23525,10 +23525,10 @@
         </is>
       </c>
       <c r="AJ142">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK142">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -23639,7 +23639,7 @@
         <v>2.1</v>
       </c>
       <c r="U143">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="V143">
         <v>1.17</v>
@@ -23648,16 +23648,16 @@
         <v>1.02</v>
       </c>
       <c r="X143">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Y143">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="Z143">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AA143">
-        <v>3.56</v>
+        <v>3.51</v>
       </c>
       <c r="AB143">
         <v>1.24</v>
@@ -23666,13 +23666,13 @@
         <v>7.6</v>
       </c>
       <c r="AD143">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AE143">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF143">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="AG143">
         <v>1.36</v>
@@ -23688,10 +23688,10 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="AK143">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="AK176">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G199">
@@ -32746,64 +32746,64 @@
         </is>
       </c>
       <c r="N199">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="O199">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="P199">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="Q199">
-        <v>3.1</v>
+        <v>2.74</v>
       </c>
       <c r="R199">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="S199">
+        <v>1.29</v>
+      </c>
+      <c r="T199">
+        <v>3.25</v>
+      </c>
+      <c r="U199">
+        <v>2.44</v>
+      </c>
+      <c r="V199">
         <v>1.43</v>
       </c>
-      <c r="T199">
-        <v>2.4</v>
-      </c>
-      <c r="U199">
-        <v>3.2</v>
-      </c>
-      <c r="V199">
-        <v>1.3</v>
-      </c>
       <c r="W199">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X199">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y199">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="Z199">
-        <v>2.63</v>
+        <v>3.65</v>
       </c>
       <c r="AA199">
-        <v>2.19</v>
+        <v>1.7</v>
       </c>
       <c r="AB199">
-        <v>1.6</v>
+        <v>2.03</v>
       </c>
       <c r="AC199">
-        <v>3.92</v>
+        <v>2.7</v>
       </c>
       <c r="AD199">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="AE199">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AF199">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AG199">
-        <v>1.76</v>
+        <v>2.23</v>
       </c>
       <c r="AH199" t="inlineStr">
         <is>
@@ -32816,10 +32816,10 @@
         </is>
       </c>
       <c r="AJ199">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK199">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AL199">
         <v>0</v>
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G200">
@@ -32909,80 +32909,80 @@
         </is>
       </c>
       <c r="N200">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="O200">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="P200">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="Q200">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="R200">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="S200">
+        <v>1.43</v>
+      </c>
+      <c r="T200">
+        <v>2.4</v>
+      </c>
+      <c r="U200">
+        <v>3.2</v>
+      </c>
+      <c r="V200">
+        <v>1.3</v>
+      </c>
+      <c r="W200">
+        <v>1.03</v>
+      </c>
+      <c r="X200">
+        <v>1.03</v>
+      </c>
+      <c r="Y200">
+        <v>1.38</v>
+      </c>
+      <c r="Z200">
+        <v>2.63</v>
+      </c>
+      <c r="AA200">
+        <v>2.19</v>
+      </c>
+      <c r="AB200">
+        <v>1.6</v>
+      </c>
+      <c r="AC200">
+        <v>3.92</v>
+      </c>
+      <c r="AD200">
+        <v>1.18</v>
+      </c>
+      <c r="AE200">
+        <v>1.03</v>
+      </c>
+      <c r="AF200">
+        <v>1.91</v>
+      </c>
+      <c r="AG200">
+        <v>1.76</v>
+      </c>
+      <c r="AH200" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI200" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ200">
         <v>1.29</v>
       </c>
-      <c r="T200">
-        <v>3.25</v>
-      </c>
-      <c r="U200">
-        <v>2.44</v>
-      </c>
-      <c r="V200">
-        <v>1.43</v>
-      </c>
-      <c r="W200">
-        <v>1.08</v>
-      </c>
-      <c r="X200">
-        <v>1.01</v>
-      </c>
-      <c r="Y200">
-        <v>1.21</v>
-      </c>
-      <c r="Z200">
-        <v>3.65</v>
-      </c>
-      <c r="AA200">
-        <v>1.7</v>
-      </c>
-      <c r="AB200">
-        <v>2.03</v>
-      </c>
-      <c r="AC200">
-        <v>2.7</v>
-      </c>
-      <c r="AD200">
-        <v>1.37</v>
-      </c>
-      <c r="AE200">
-        <v>1.12</v>
-      </c>
-      <c r="AF200">
-        <v>1.57</v>
-      </c>
-      <c r="AG200">
-        <v>2.23</v>
-      </c>
-      <c r="AH200" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI200" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ200">
-        <v>1.22</v>
-      </c>
       <c r="AK200">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AL200">
         <v>0</v>

--- a/jogos_2026-08-08.xlsx
+++ b/jogos_2026-08-08.xlsx
@@ -1776,19 +1776,19 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="O9">
-        <v>3.71</v>
+        <v>3.55</v>
       </c>
       <c r="P9">
-        <v>6.13</v>
+        <v>4.9</v>
       </c>
       <c r="Q9">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="R9">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="S9">
         <v>1.43</v>
@@ -1797,10 +1797,10 @@
         <v>2.59</v>
       </c>
       <c r="U9">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="V9">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W9">
         <v>1.04</v>
@@ -1815,10 +1815,10 @@
         <v>3.04</v>
       </c>
       <c r="AA9">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AB9">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AC9">
         <v>3.28</v>
@@ -3083,22 +3083,22 @@
         <v>1.99</v>
       </c>
       <c r="O17">
-        <v>3.11</v>
+        <v>3.15</v>
       </c>
       <c r="P17">
-        <v>3.7</v>
+        <v>4.21</v>
       </c>
       <c r="Q17">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="R17">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="S17">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="T17">
-        <v>2.7</v>
+        <v>2.44</v>
       </c>
       <c r="U17">
         <v>3</v>
@@ -3107,10 +3107,10 @@
         <v>1.33</v>
       </c>
       <c r="W17">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X17">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y17">
         <v>1.33</v>
@@ -3119,16 +3119,16 @@
         <v>2.83</v>
       </c>
       <c r="AA17">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AB17">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AC17">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="AD17">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE17">
         <v>1.02</v>
@@ -3137,7 +3137,7 @@
         <v>1.85</v>
       </c>
       <c r="AG17">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK17">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3406,22 +3406,22 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.75</v>
+        <v>4.15</v>
       </c>
       <c r="O19">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P19">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="Q19">
         <v>4.75</v>
       </c>
       <c r="R19">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="S19">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="T19">
         <v>2.4</v>
@@ -3457,7 +3457,7 @@
         <v>1.16</v>
       </c>
       <c r="AE19">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AF19">
         <v>2.15</v>
@@ -3572,10 +3572,10 @@
         <v>2.11</v>
       </c>
       <c r="O20">
-        <v>3.56</v>
+        <v>3.35</v>
       </c>
       <c r="P20">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="Q20">
         <v>2.62</v>
@@ -3614,13 +3614,13 @@
         <v>1.9</v>
       </c>
       <c r="AC20">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AD20">
         <v>1.33</v>
       </c>
       <c r="AE20">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF20">
         <v>1.7</v>
@@ -3735,10 +3735,10 @@
         <v>2.4</v>
       </c>
       <c r="O21">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P21">
-        <v>2.93</v>
+        <v>2.85</v>
       </c>
       <c r="Q21">
         <v>3.12</v>
@@ -3768,13 +3768,13 @@
         <v>1.36</v>
       </c>
       <c r="Z21">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="AA21">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="AB21">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AC21">
         <v>4.39</v>
@@ -3895,10 +3895,10 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="O22">
-        <v>3.68</v>
+        <v>3.98</v>
       </c>
       <c r="P22">
         <v>5.7</v>
@@ -3907,19 +3907,19 @@
         <v>2.14</v>
       </c>
       <c r="R22">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="S22">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T22">
-        <v>2.57</v>
+        <v>2.81</v>
       </c>
       <c r="U22">
-        <v>2.94</v>
+        <v>2.81</v>
       </c>
       <c r="V22">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W22">
         <v>1.05</v>
@@ -3931,19 +3931,19 @@
         <v>1.33</v>
       </c>
       <c r="Z22">
-        <v>2.99</v>
+        <v>3.4</v>
       </c>
       <c r="AA22">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AB22">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC22">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AD22">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE22">
         <v>1.05</v>
@@ -3952,7 +3952,7 @@
         <v>2</v>
       </c>
       <c r="AG22">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="O23">
         <v>3.65</v>
@@ -4076,7 +4076,7 @@
         <v>1.33</v>
       </c>
       <c r="T23">
-        <v>3.16</v>
+        <v>2.82</v>
       </c>
       <c r="U23">
         <v>2.62</v>
@@ -4094,10 +4094,10 @@
         <v>1.25</v>
       </c>
       <c r="Z23">
-        <v>3.75</v>
+        <v>3.82</v>
       </c>
       <c r="AA23">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AB23">
         <v>1.92</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="O24">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="P24">
-        <v>6.35</v>
+        <v>6.25</v>
       </c>
       <c r="Q24">
         <v>2</v>
@@ -4236,13 +4236,13 @@
         <v>2.31</v>
       </c>
       <c r="S24">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T24">
         <v>3.2</v>
       </c>
       <c r="U24">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="V24">
         <v>1.44</v>
@@ -4260,19 +4260,19 @@
         <v>3.79</v>
       </c>
       <c r="AA24">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AB24">
-        <v>1.94</v>
+        <v>2.03</v>
       </c>
       <c r="AC24">
-        <v>2.98</v>
+        <v>2.76</v>
       </c>
       <c r="AD24">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE24">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF24">
         <v>1.89</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,65 +4873,65 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.78</v>
+        <v>2.67</v>
       </c>
       <c r="O28">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="P28">
-        <v>3.83</v>
+        <v>2.58</v>
       </c>
       <c r="Q28">
-        <v>2.4</v>
+        <v>3.32</v>
       </c>
       <c r="R28">
-        <v>2.11</v>
+        <v>2.22</v>
       </c>
       <c r="S28">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T28">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="U28">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="V28">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W28">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X28">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z28">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="AA28">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AB28">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AC28">
-        <v>3.69</v>
+        <v>3.47</v>
       </c>
       <c r="AD28">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE28">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF28">
+        <v>1.76</v>
+      </c>
+      <c r="AG28">
         <v>1.85</v>
       </c>
-      <c r="AG28">
-        <v>1.82</v>
-      </c>
       <c r="AH28" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="AK28">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.67</v>
+        <v>1.78</v>
       </c>
       <c r="O29">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="P29">
-        <v>2.58</v>
+        <v>3.83</v>
       </c>
       <c r="Q29">
-        <v>3.32</v>
+        <v>2.4</v>
       </c>
       <c r="R29">
-        <v>2.22</v>
+        <v>2.11</v>
       </c>
       <c r="S29">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T29">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U29">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="V29">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W29">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X29">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y29">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z29">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="AA29">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AB29">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AC29">
-        <v>3.47</v>
+        <v>3.69</v>
       </c>
       <c r="AD29">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AE29">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF29">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AG29">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AK29">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5525,7 +5525,7 @@
         </is>
       </c>
       <c r="N32">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="O32">
         <v>3.2</v>
@@ -5552,7 +5552,7 @@
         <v>1.38</v>
       </c>
       <c r="W32">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X32">
         <v>1.05</v>
@@ -5564,10 +5564,10 @@
         <v>3.2</v>
       </c>
       <c r="AA32">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB32">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC32">
         <v>3.4</v>
@@ -5598,7 +5598,7 @@
         <v>1.22</v>
       </c>
       <c r="AK32">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5724,13 +5724,13 @@
         <v>1.09</v>
       </c>
       <c r="Z33">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AA33">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AB33">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="AC33">
         <v>2.2</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,80 +6177,80 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.62</v>
+        <v>2.35</v>
       </c>
       <c r="O36">
-        <v>3.78</v>
+        <v>3.58</v>
       </c>
       <c r="P36">
-        <v>5.25</v>
+        <v>2.72</v>
       </c>
       <c r="Q36">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="R36">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="S36">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T36">
-        <v>3.1</v>
+        <v>3.66</v>
       </c>
       <c r="U36">
+        <v>2.2</v>
+      </c>
+      <c r="V36">
+        <v>1.63</v>
+      </c>
+      <c r="W36">
+        <v>1.13</v>
+      </c>
+      <c r="X36">
+        <v>1.03</v>
+      </c>
+      <c r="Y36">
+        <v>1.1</v>
+      </c>
+      <c r="Z36">
+        <v>5</v>
+      </c>
+      <c r="AA36">
+        <v>1.44</v>
+      </c>
+      <c r="AB36">
         <v>2.45</v>
       </c>
-      <c r="V36">
+      <c r="AC36">
+        <v>2.27</v>
+      </c>
+      <c r="AD36">
+        <v>1.61</v>
+      </c>
+      <c r="AE36">
+        <v>1.2</v>
+      </c>
+      <c r="AF36">
+        <v>1.42</v>
+      </c>
+      <c r="AG36">
+        <v>2.63</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ36">
+        <v>1.51</v>
+      </c>
+      <c r="AK36">
         <v>1.48</v>
-      </c>
-      <c r="W36">
-        <v>1.12</v>
-      </c>
-      <c r="X36">
-        <v>1.02</v>
-      </c>
-      <c r="Y36">
-        <v>1.2</v>
-      </c>
-      <c r="Z36">
-        <v>4.33</v>
-      </c>
-      <c r="AA36">
-        <v>1.69</v>
-      </c>
-      <c r="AB36">
-        <v>2.04</v>
-      </c>
-      <c r="AC36">
-        <v>2.63</v>
-      </c>
-      <c r="AD36">
-        <v>1.41</v>
-      </c>
-      <c r="AE36">
-        <v>1.14</v>
-      </c>
-      <c r="AF36">
-        <v>1.67</v>
-      </c>
-      <c r="AG36">
-        <v>2.1</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ36">
-        <v>1.17</v>
-      </c>
-      <c r="AK36">
-        <v>2.12</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="O37">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="P37">
-        <v>2.72</v>
+        <v>3.1</v>
       </c>
       <c r="Q37">
-        <v>2.89</v>
+        <v>2.63</v>
       </c>
       <c r="R37">
-        <v>2.32</v>
+        <v>2.43</v>
       </c>
       <c r="S37">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T37">
-        <v>3.66</v>
+        <v>3.22</v>
       </c>
       <c r="U37">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="V37">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="W37">
+        <v>1.11</v>
+      </c>
+      <c r="X37">
+        <v>1.01</v>
+      </c>
+      <c r="Y37">
         <v>1.14</v>
       </c>
-      <c r="X37">
-        <v>1.02</v>
-      </c>
-      <c r="Y37">
-        <v>1.1</v>
-      </c>
       <c r="Z37">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AA37">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AB37">
         <v>2.45</v>
       </c>
       <c r="AC37">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="AD37">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AE37">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF37">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AG37">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.51</v>
+        <v>1.34</v>
       </c>
       <c r="AK37">
-        <v>1.41</v>
+        <v>1.65</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6506,16 +6506,16 @@
         <v>1.71</v>
       </c>
       <c r="O38">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="P38">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="Q38">
         <v>2.15</v>
       </c>
       <c r="R38">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S38">
         <v>1.25</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.15</v>
+        <v>1.62</v>
       </c>
       <c r="O39">
-        <v>3.55</v>
+        <v>3.78</v>
       </c>
       <c r="P39">
-        <v>3.1</v>
+        <v>5.3</v>
       </c>
       <c r="Q39">
-        <v>2.51</v>
+        <v>2.1</v>
       </c>
       <c r="R39">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="S39">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T39">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="U39">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="V39">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="W39">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y39">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z39">
-        <v>4.75</v>
+        <v>3.9</v>
       </c>
       <c r="AA39">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="AB39">
-        <v>2.45</v>
+        <v>2.14</v>
       </c>
       <c r="AC39">
-        <v>2.28</v>
+        <v>2.63</v>
       </c>
       <c r="AD39">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="AE39">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AF39">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="AG39">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AK39">
-        <v>1.67</v>
+        <v>2.12</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7490,10 +7490,10 @@
         <v>0</v>
       </c>
       <c r="Q44">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="R44">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="S44">
         <v>1.22</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK44">
         <v>2.2</v>
@@ -7644,22 +7644,22 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="O45">
         <v>4.05</v>
       </c>
       <c r="P45">
-        <v>3.9</v>
+        <v>4.25</v>
       </c>
       <c r="Q45">
         <v>2</v>
       </c>
       <c r="R45">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="S45">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T45">
         <v>3.9</v>
@@ -7677,16 +7677,16 @@
         <v>1.02</v>
       </c>
       <c r="Y45">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z45">
-        <v>6.01</v>
+        <v>6.29</v>
       </c>
       <c r="AA45">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AB45">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="AC45">
         <v>2.1</v>
@@ -7695,13 +7695,13 @@
         <v>1.71</v>
       </c>
       <c r="AE45">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AF45">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AG45">
-        <v>2.33</v>
+        <v>2.53</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7810,16 +7810,16 @@
         <v>2.88</v>
       </c>
       <c r="O46">
-        <v>3.7</v>
+        <v>3.48</v>
       </c>
       <c r="P46">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="Q46">
-        <v>3.04</v>
+        <v>3.54</v>
       </c>
       <c r="R46">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="S46">
         <v>1.18</v>
@@ -7828,10 +7828,10 @@
         <v>4.5</v>
       </c>
       <c r="U46">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="V46">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="W46">
         <v>1.18</v>
@@ -7840,25 +7840,25 @@
         <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z46">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AA46">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AB46">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="AC46">
         <v>1.97</v>
       </c>
       <c r="AD46">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AE46">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AF46">
         <v>1.38</v>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.75</v>
+        <v>1.22</v>
       </c>
       <c r="AK46">
         <v>1.3</v>
@@ -7970,10 +7970,10 @@
         </is>
       </c>
       <c r="N47">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O47">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="P47">
         <v>2</v>
@@ -7991,13 +7991,13 @@
         <v>4.15</v>
       </c>
       <c r="U47">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V47">
         <v>1.8</v>
       </c>
       <c r="W47">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="X47">
         <v>1.01</v>
@@ -8006,22 +8006,22 @@
         <v>1.1</v>
       </c>
       <c r="Z47">
-        <v>6.29</v>
+        <v>6.4</v>
       </c>
       <c r="AA47">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AB47">
         <v>3.1</v>
       </c>
       <c r="AC47">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AD47">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AE47">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AF47">
         <v>1.33</v>
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="O48">
         <v>4.2</v>
@@ -8142,37 +8142,37 @@
         <v>4.33</v>
       </c>
       <c r="Q48">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="R48">
-        <v>2.35</v>
+        <v>2.52</v>
       </c>
       <c r="S48">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="T48">
         <v>3.6</v>
       </c>
       <c r="U48">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="V48">
         <v>1.62</v>
       </c>
       <c r="W48">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X48">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y48">
         <v>1.11</v>
       </c>
       <c r="Z48">
-        <v>4.9</v>
+        <v>4.88</v>
       </c>
       <c r="AA48">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB48">
         <v>2.38</v>
@@ -8184,7 +8184,7 @@
         <v>1.56</v>
       </c>
       <c r="AE48">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF48">
         <v>1.57</v>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AK48">
         <v>2.05</v>
@@ -8296,19 +8296,19 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.22</v>
+        <v>2.6</v>
       </c>
       <c r="O49">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P49">
-        <v>2.75</v>
+        <v>2.34</v>
       </c>
       <c r="Q49">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="R49">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S49">
         <v>1.3</v>
@@ -8320,40 +8320,40 @@
         <v>2.5</v>
       </c>
       <c r="V49">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W49">
         <v>1.11</v>
       </c>
       <c r="X49">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y49">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z49">
-        <v>3.9</v>
+        <v>3.94</v>
       </c>
       <c r="AA49">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB49">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC49">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="AD49">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AE49">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF49">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AG49">
-        <v>1.95</v>
+        <v>2.21</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK49">
         <v>1.48</v>
@@ -8459,16 +8459,16 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="O50">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="P50">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="Q50">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="R50">
         <v>2.48</v>
@@ -8492,16 +8492,16 @@
         <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z50">
         <v>3.6</v>
       </c>
       <c r="AA50">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AB50">
-        <v>2.49</v>
+        <v>2.2</v>
       </c>
       <c r="AC50">
         <v>2.2</v>
@@ -8532,7 +8532,7 @@
         <v>1.15</v>
       </c>
       <c r="AK50">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="O51">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P51">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q51">
         <v>2.75</v>
@@ -8637,16 +8637,16 @@
         <v>2.4</v>
       </c>
       <c r="S51">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T51">
         <v>3.5</v>
       </c>
       <c r="U51">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="V51">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="W51">
         <v>1.14</v>
@@ -8655,7 +8655,7 @@
         <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z51">
         <v>4.85</v>
@@ -8667,13 +8667,13 @@
         <v>2.25</v>
       </c>
       <c r="AC51">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AD51">
         <v>1.47</v>
       </c>
       <c r="AE51">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AF51">
         <v>1.43</v>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK51">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -9274,7 +9274,7 @@
         </is>
       </c>
       <c r="N55">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="O55">
         <v>3.11</v>
@@ -9289,10 +9289,10 @@
         <v>1.9</v>
       </c>
       <c r="S55">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="T55">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="U55">
         <v>3.38</v>
@@ -9307,10 +9307,10 @@
         <v>1.04</v>
       </c>
       <c r="Y55">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="Z55">
-        <v>2.81</v>
+        <v>2.65</v>
       </c>
       <c r="AA55">
         <v>2.43</v>
@@ -9322,7 +9322,7 @@
         <v>4.3</v>
       </c>
       <c r="AD55">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE55">
         <v>1.01</v>
@@ -9331,7 +9331,7 @@
         <v>1.95</v>
       </c>
       <c r="AG55">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>1.3</v>
       </c>
       <c r="AK55">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9446,10 +9446,10 @@
         <v>2.16</v>
       </c>
       <c r="Q56">
-        <v>3.17</v>
+        <v>3.53</v>
       </c>
       <c r="R56">
-        <v>2.06</v>
+        <v>2.27</v>
       </c>
       <c r="S56">
         <v>1.35</v>
@@ -9476,13 +9476,13 @@
         <v>3.5</v>
       </c>
       <c r="AA56">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AB56">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AC56">
-        <v>3.04</v>
+        <v>3.13</v>
       </c>
       <c r="AD56">
         <v>1.29</v>
@@ -9491,10 +9491,10 @@
         <v>1.13</v>
       </c>
       <c r="AF56">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG56">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>1.28</v>
       </c>
       <c r="AK56">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>3.5</v>
       </c>
       <c r="Q57">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="R57">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="S57">
         <v>1.39</v>
@@ -9621,7 +9621,7 @@
         <v>2.73</v>
       </c>
       <c r="U57">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="V57">
         <v>1.37</v>
@@ -9654,10 +9654,10 @@
         <v>1.1</v>
       </c>
       <c r="AF57">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG57">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK57">
         <v>1.85</v>
@@ -10424,7 +10424,7 @@
         <v>3.16</v>
       </c>
       <c r="Q62">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="R62">
         <v>2.38</v>
@@ -10436,7 +10436,7 @@
         <v>3.28</v>
       </c>
       <c r="U62">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="V62">
         <v>1.55</v>
@@ -10454,13 +10454,13 @@
         <v>4.3</v>
       </c>
       <c r="AA62">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AB62">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AC62">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AD62">
         <v>1.5</v>
@@ -10472,7 +10472,7 @@
         <v>1.49</v>
       </c>
       <c r="AG62">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AK62">
         <v>1.68</v>
@@ -10590,7 +10590,7 @@
         <v>4.4</v>
       </c>
       <c r="R63">
-        <v>2.23</v>
+        <v>2.02</v>
       </c>
       <c r="S63">
         <v>1.4</v>
@@ -10599,19 +10599,19 @@
         <v>2.75</v>
       </c>
       <c r="U63">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="V63">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="W63">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X63">
         <v>1.06</v>
       </c>
       <c r="Y63">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="Z63">
         <v>3.5</v>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK63">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.07</v>
+        <v>1.99</v>
       </c>
       <c r="O64">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="P64">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="Q64">
         <v>2.5</v>
@@ -10759,19 +10759,19 @@
         <v>1.29</v>
       </c>
       <c r="T64">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="U64">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V64">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="W64">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X64">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y64">
         <v>1.19</v>
@@ -10783,16 +10783,16 @@
         <v>1.62</v>
       </c>
       <c r="AB64">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AC64">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AD64">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE64">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AF64">
         <v>1.57</v>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AK64">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10913,10 +10913,10 @@
         <v>4.55</v>
       </c>
       <c r="Q65">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="R65">
-        <v>2.49</v>
+        <v>2.63</v>
       </c>
       <c r="S65">
         <v>1.2</v>
@@ -10931,7 +10931,7 @@
         <v>1.7</v>
       </c>
       <c r="W65">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X65">
         <v>1.02</v>
@@ -10961,7 +10961,7 @@
         <v>1.45</v>
       </c>
       <c r="AG65">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AK65">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11076,7 +11076,7 @@
         <v>3.45</v>
       </c>
       <c r="Q66">
-        <v>2.72</v>
+        <v>2.87</v>
       </c>
       <c r="R66">
         <v>1.96</v>
@@ -11085,7 +11085,7 @@
         <v>1.4</v>
       </c>
       <c r="T66">
-        <v>2.66</v>
+        <v>2.81</v>
       </c>
       <c r="U66">
         <v>2.9</v>
@@ -11097,7 +11097,7 @@
         <v>1.07</v>
       </c>
       <c r="X66">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y66">
         <v>1.31</v>
@@ -11106,10 +11106,10 @@
         <v>2.92</v>
       </c>
       <c r="AA66">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="AB66">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC66">
         <v>3.69</v>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK66">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11230,19 +11230,19 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="O67">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P67">
         <v>2.5</v>
       </c>
       <c r="Q67">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="R67">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="S67">
         <v>1.25</v>
@@ -11275,7 +11275,7 @@
         <v>2.3</v>
       </c>
       <c r="AC67">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AD67">
         <v>1.54</v>
@@ -11284,26 +11284,26 @@
         <v>1.17</v>
       </c>
       <c r="AF67">
+        <v>1.48</v>
+      </c>
+      <c r="AG67">
+        <v>2.47</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ67">
         <v>1.44</v>
       </c>
-      <c r="AG67">
-        <v>2.35</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ67">
-        <v>1.25</v>
-      </c>
       <c r="AK67">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11725,7 +11725,7 @@
         <v>5.7</v>
       </c>
       <c r="P70">
-        <v>8.050000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="Q70">
         <v>1.68</v>
@@ -11737,13 +11737,13 @@
         <v>1.22</v>
       </c>
       <c r="T70">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U70">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="V70">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W70">
         <v>1.14</v>
@@ -11752,7 +11752,7 @@
         <v>1.02</v>
       </c>
       <c r="Y70">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z70">
         <v>4.78</v>
@@ -11764,10 +11764,10 @@
         <v>2.45</v>
       </c>
       <c r="AC70">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="AD70">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AE70">
         <v>1.22</v>
@@ -11776,7 +11776,7 @@
         <v>1.85</v>
       </c>
       <c r="AG70">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AK70">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11882,10 +11882,10 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="O71">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="P71">
         <v>3.8</v>
@@ -11897,7 +11897,7 @@
         <v>2.25</v>
       </c>
       <c r="S71">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T71">
         <v>3.2</v>
@@ -11915,10 +11915,10 @@
         <v>1.04</v>
       </c>
       <c r="Y71">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z71">
-        <v>3.85</v>
+        <v>3.58</v>
       </c>
       <c r="AA71">
         <v>1.74</v>
@@ -11930,7 +11930,7 @@
         <v>2.9</v>
       </c>
       <c r="AD71">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AE71">
         <v>1.13</v>
@@ -11955,7 +11955,7 @@
         <v>1.18</v>
       </c>
       <c r="AK71">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="O72">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P72">
-        <v>3.9</v>
+        <v>4.15</v>
       </c>
       <c r="Q72">
         <v>2.22</v>
@@ -12063,7 +12063,7 @@
         <v>1.33</v>
       </c>
       <c r="T72">
-        <v>2.91</v>
+        <v>3.17</v>
       </c>
       <c r="U72">
         <v>2.59</v>
@@ -12078,10 +12078,10 @@
         <v>1</v>
       </c>
       <c r="Y72">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z72">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AA72">
         <v>1.8</v>
@@ -12090,7 +12090,7 @@
         <v>1.92</v>
       </c>
       <c r="AC72">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="AD72">
         <v>1.36</v>
@@ -12102,7 +12102,7 @@
         <v>1.73</v>
       </c>
       <c r="AG72">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,7 +12115,7 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK72">
         <v>2</v>
@@ -12208,19 +12208,19 @@
         </is>
       </c>
       <c r="N73">
-        <v>4.6</v>
+        <v>4.95</v>
       </c>
       <c r="O73">
-        <v>4.45</v>
+        <v>4.05</v>
       </c>
       <c r="P73">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="Q73">
-        <v>5.52</v>
+        <v>5.56</v>
       </c>
       <c r="R73">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="S73">
         <v>1.25</v>
@@ -12229,7 +12229,7 @@
         <v>3.38</v>
       </c>
       <c r="U73">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="V73">
         <v>1.57</v>
@@ -12238,7 +12238,7 @@
         <v>1.15</v>
       </c>
       <c r="X73">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y73">
         <v>1.13</v>
@@ -12247,16 +12247,16 @@
         <v>4.5</v>
       </c>
       <c r="AA73">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AB73">
         <v>2.24</v>
       </c>
       <c r="AC73">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AD73">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AE73">
         <v>1.16</v>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.2</v>
+        <v>2.38</v>
       </c>
       <c r="AK73">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12371,10 +12371,10 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="O74">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P74">
         <v>3.25</v>
@@ -12404,10 +12404,10 @@
         <v>1.03</v>
       </c>
       <c r="Y74">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z74">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AA74">
         <v>1.89</v>
@@ -12416,7 +12416,7 @@
         <v>1.76</v>
       </c>
       <c r="AC74">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="AD74">
         <v>1.3</v>
@@ -12425,7 +12425,7 @@
         <v>1.06</v>
       </c>
       <c r="AF74">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG74">
         <v>1.98</v>
@@ -12534,7 +12534,7 @@
         </is>
       </c>
       <c r="N75">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="O75">
         <v>3.32</v>
@@ -12543,7 +12543,7 @@
         <v>1.91</v>
       </c>
       <c r="Q75">
-        <v>4.5</v>
+        <v>3.76</v>
       </c>
       <c r="R75">
         <v>2.18</v>
@@ -12552,13 +12552,13 @@
         <v>1.38</v>
       </c>
       <c r="T75">
+        <v>2.88</v>
+      </c>
+      <c r="U75">
         <v>2.7</v>
       </c>
-      <c r="U75">
-        <v>2.8</v>
-      </c>
       <c r="V75">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W75">
         <v>1.04</v>
@@ -12567,10 +12567,10 @@
         <v>1.01</v>
       </c>
       <c r="Y75">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z75">
-        <v>3.39</v>
+        <v>3.3</v>
       </c>
       <c r="AA75">
         <v>1.97</v>
@@ -12579,10 +12579,10 @@
         <v>1.82</v>
       </c>
       <c r="AC75">
-        <v>3.44</v>
+        <v>3.2</v>
       </c>
       <c r="AD75">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE75">
         <v>1.06</v>
@@ -12697,7 +12697,7 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="O76">
         <v>3.1</v>
@@ -12706,13 +12706,13 @@
         <v>3.4</v>
       </c>
       <c r="Q76">
-        <v>2.51</v>
+        <v>2.63</v>
       </c>
       <c r="R76">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="S76">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="T76">
         <v>2.75</v>
@@ -12733,7 +12733,7 @@
         <v>1.36</v>
       </c>
       <c r="Z76">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="AA76">
         <v>2.1</v>
@@ -12748,7 +12748,7 @@
         <v>1.21</v>
       </c>
       <c r="AE76">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF76">
         <v>1.85</v>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK76">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="O77">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P77">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="Q77">
         <v>3.31</v>
@@ -12878,16 +12878,16 @@
         <v>1.39</v>
       </c>
       <c r="T77">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="U77">
         <v>2.91</v>
       </c>
       <c r="V77">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W77">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X77">
         <v>1.04</v>
@@ -12896,28 +12896,28 @@
         <v>1.33</v>
       </c>
       <c r="Z77">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AA77">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB77">
         <v>1.76</v>
       </c>
       <c r="AC77">
-        <v>3.75</v>
+        <v>3.54</v>
       </c>
       <c r="AD77">
         <v>1.22</v>
       </c>
       <c r="AE77">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF77">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AG77">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,7 +12930,7 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="AK77">
         <v>1.36</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O78">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P78">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="Q78">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="R78">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="S78">
         <v>1.44</v>
       </c>
       <c r="T78">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="U78">
-        <v>2.9</v>
+        <v>3.22</v>
       </c>
       <c r="V78">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="W78">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X78">
         <v>1.02</v>
       </c>
       <c r="Y78">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="Z78">
-        <v>3.05</v>
+        <v>2.74</v>
       </c>
       <c r="AA78">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="AB78">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AC78">
-        <v>3.28</v>
+        <v>4.05</v>
       </c>
       <c r="AD78">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE78">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AF78">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AG78">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AK78">
-        <v>2.46</v>
+        <v>2.13</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.59</v>
+        <v>2.3</v>
       </c>
       <c r="O79">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="P79">
-        <v>5.8</v>
+        <v>2.73</v>
       </c>
       <c r="Q79">
-        <v>2.16</v>
+        <v>3.1</v>
       </c>
       <c r="R79">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="S79">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T79">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="U79">
-        <v>3.22</v>
+        <v>3.05</v>
       </c>
       <c r="V79">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W79">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X79">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y79">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z79">
-        <v>2.74</v>
+        <v>3.16</v>
       </c>
       <c r="AA79">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AB79">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AC79">
-        <v>4.05</v>
+        <v>3.58</v>
       </c>
       <c r="AD79">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE79">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF79">
-        <v>2.18</v>
+        <v>1.83</v>
       </c>
       <c r="AG79">
-        <v>1.61</v>
+        <v>1.87</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AK79">
-        <v>2.3</v>
+        <v>1.49</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.29</v>
+        <v>1.5</v>
       </c>
       <c r="O80">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="P80">
-        <v>2.73</v>
+        <v>5.6</v>
       </c>
       <c r="Q80">
-        <v>3.1</v>
+        <v>2.07</v>
       </c>
       <c r="R80">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="S80">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T80">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="U80">
-        <v>3.24</v>
+        <v>2.9</v>
       </c>
       <c r="V80">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W80">
         <v>1.03</v>
       </c>
       <c r="X80">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y80">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z80">
-        <v>2.83</v>
+        <v>3.05</v>
       </c>
       <c r="AA80">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AB80">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="AC80">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="AD80">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AE80">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF80">
-        <v>1.83</v>
+        <v>2.06</v>
       </c>
       <c r="AG80">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.36</v>
+        <v>1.1</v>
       </c>
       <c r="AK80">
-        <v>1.49</v>
+        <v>2.41</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O83">
         <v>3.4</v>
       </c>
       <c r="P83">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="Q83">
         <v>2.9</v>
@@ -13865,10 +13865,10 @@
         <v>1.43</v>
       </c>
       <c r="W83">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X83">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y83">
         <v>1.25</v>
@@ -13883,16 +13883,16 @@
         <v>1.95</v>
       </c>
       <c r="AC83">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AD83">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE83">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF83">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG83">
         <v>2.15</v>
@@ -14004,16 +14004,16 @@
         <v>2.3</v>
       </c>
       <c r="O84">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P84">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="Q84">
-        <v>2.9</v>
+        <v>2.69</v>
       </c>
       <c r="R84">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="S84">
         <v>1.36</v>
@@ -14022,13 +14022,13 @@
         <v>3.06</v>
       </c>
       <c r="U84">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="V84">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W84">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X84">
         <v>1.05</v>
@@ -14037,10 +14037,10 @@
         <v>1.29</v>
       </c>
       <c r="Z84">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA84">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AB84">
         <v>1.85</v>
@@ -14049,7 +14049,7 @@
         <v>3.25</v>
       </c>
       <c r="AD84">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE84">
         <v>1.09</v>
@@ -14071,7 +14071,7 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK84">
         <v>1.62</v>
@@ -14173,7 +14173,7 @@
         <v>3.1</v>
       </c>
       <c r="Q85">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="R85">
         <v>2.1</v>
@@ -14185,25 +14185,25 @@
         <v>2.59</v>
       </c>
       <c r="U85">
-        <v>2.91</v>
+        <v>3.03</v>
       </c>
       <c r="V85">
         <v>1.36</v>
       </c>
       <c r="W85">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X85">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y85">
         <v>1.28</v>
       </c>
       <c r="Z85">
-        <v>3.21</v>
+        <v>3.08</v>
       </c>
       <c r="AA85">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AB85">
         <v>1.73</v>
@@ -14212,13 +14212,13 @@
         <v>3.6</v>
       </c>
       <c r="AD85">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE85">
         <v>1.04</v>
       </c>
       <c r="AF85">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AG85">
         <v>1.95</v>
@@ -14327,7 +14327,7 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="O86">
         <v>5</v>
@@ -14336,7 +14336,7 @@
         <v>4.95</v>
       </c>
       <c r="Q86">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="R86">
         <v>2.74</v>
@@ -14345,10 +14345,10 @@
         <v>1.15</v>
       </c>
       <c r="T86">
-        <v>4.45</v>
+        <v>4.6</v>
       </c>
       <c r="U86">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="V86">
         <v>1.8</v>
@@ -14360,7 +14360,7 @@
         <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z86">
         <v>7.5</v>
@@ -14369,22 +14369,22 @@
         <v>1.28</v>
       </c>
       <c r="AB86">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="AC86">
         <v>1.79</v>
       </c>
       <c r="AD86">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AE86">
         <v>1.36</v>
       </c>
       <c r="AF86">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AG86">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14502,19 +14502,19 @@
         <v>1.67</v>
       </c>
       <c r="R87">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="S87">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T87">
         <v>3.45</v>
       </c>
       <c r="U87">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="V87">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="W87">
         <v>1.13</v>
@@ -14523,19 +14523,19 @@
         <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z87">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="AA87">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="AB87">
-        <v>1.98</v>
+        <v>2.31</v>
       </c>
       <c r="AC87">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="AD87">
         <v>1.38</v>
@@ -14544,10 +14544,10 @@
         <v>1.13</v>
       </c>
       <c r="AF87">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG87">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AK87">
-        <v>2.75</v>
+        <v>3.34</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O89">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P89">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="Q89">
         <v>3</v>
@@ -14831,13 +14831,13 @@
         <v>2.25</v>
       </c>
       <c r="S89">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T89">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="U89">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="V89">
         <v>1.43</v>
@@ -14846,7 +14846,7 @@
         <v>1.06</v>
       </c>
       <c r="X89">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y89">
         <v>1.22</v>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AK89">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14982,13 +14982,13 @@
         <v>2.37</v>
       </c>
       <c r="O90">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="P90">
         <v>2.85</v>
       </c>
       <c r="Q90">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="R90">
         <v>2.2</v>
@@ -15000,7 +15000,7 @@
         <v>2.95</v>
       </c>
       <c r="U90">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="V90">
         <v>1.38</v>
@@ -15033,7 +15033,7 @@
         <v>1.06</v>
       </c>
       <c r="AF90">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AG90">
         <v>1.99</v>
@@ -15142,7 +15142,7 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="O91">
         <v>4.68</v>
@@ -15181,22 +15181,22 @@
         <v>5.75</v>
       </c>
       <c r="AA91">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB91">
         <v>2.64</v>
       </c>
       <c r="AC91">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AD91">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AE91">
         <v>1.26</v>
       </c>
       <c r="AF91">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG91">
         <v>2.37</v>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AK91">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15311,13 +15311,13 @@
         <v>3.6</v>
       </c>
       <c r="P92">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="Q92">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="R92">
-        <v>2.61</v>
+        <v>2.45</v>
       </c>
       <c r="S92">
         <v>1.2</v>
@@ -15329,7 +15329,7 @@
         <v>2</v>
       </c>
       <c r="V92">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="W92">
         <v>1.2</v>
@@ -15347,16 +15347,16 @@
         <v>1.4</v>
       </c>
       <c r="AB92">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="AC92">
         <v>2</v>
       </c>
       <c r="AD92">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AE92">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AF92">
         <v>1.36</v>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK92">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15966,10 +15966,10 @@
         <v>0</v>
       </c>
       <c r="Q96">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R96">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S96">
         <v>1.4</v>
@@ -15993,7 +15993,7 @@
         <v>1.31</v>
       </c>
       <c r="Z96">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AA96">
         <v>1.94</v>
@@ -16120,7 +16120,7 @@
         </is>
       </c>
       <c r="N97">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="O97">
         <v>3.5</v>
@@ -16153,16 +16153,16 @@
         <v>1</v>
       </c>
       <c r="Y97">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Z97">
-        <v>3.35</v>
+        <v>3.43</v>
       </c>
       <c r="AA97">
+        <v>1.85</v>
+      </c>
+      <c r="AB97">
         <v>1.87</v>
-      </c>
-      <c r="AB97">
-        <v>1.8</v>
       </c>
       <c r="AC97">
         <v>2.92</v>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="AK97">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16449,10 +16449,10 @@
         <v>2.05</v>
       </c>
       <c r="O99">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P99">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q99">
         <v>2.63</v>
@@ -16464,13 +16464,13 @@
         <v>1.34</v>
       </c>
       <c r="T99">
-        <v>2.81</v>
+        <v>2.68</v>
       </c>
       <c r="U99">
         <v>2.88</v>
       </c>
       <c r="V99">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W99">
         <v>1.04</v>
@@ -16500,10 +16500,10 @@
         <v>1.09</v>
       </c>
       <c r="AF99">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG99">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16609,19 +16609,19 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="O100">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
       <c r="P100">
-        <v>6.15</v>
+        <v>6.55</v>
       </c>
       <c r="Q100">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="R100">
-        <v>2.71</v>
+        <v>2.53</v>
       </c>
       <c r="S100">
         <v>1.25</v>
@@ -16645,7 +16645,7 @@
         <v>1.1</v>
       </c>
       <c r="Z100">
-        <v>5.11</v>
+        <v>5</v>
       </c>
       <c r="AA100">
         <v>1.48</v>
@@ -16654,13 +16654,13 @@
         <v>2.41</v>
       </c>
       <c r="AC100">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="AD100">
         <v>1.6</v>
       </c>
       <c r="AE100">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AF100">
         <v>1.66</v>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AK100">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16947,7 +16947,7 @@
         <v>3</v>
       </c>
       <c r="R102">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S102">
         <v>1.47</v>
@@ -16965,19 +16965,19 @@
         <v>1.03</v>
       </c>
       <c r="X102">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y102">
-        <v>1.45</v>
+        <v>1.27</v>
       </c>
       <c r="Z102">
         <v>3.35</v>
       </c>
       <c r="AA102">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="AB102">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AC102">
         <v>3.1</v>
@@ -16989,10 +16989,10 @@
         <v>1.02</v>
       </c>
       <c r="AF102">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AG102">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK102">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17098,19 +17098,19 @@
         </is>
       </c>
       <c r="N103">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="O103">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P103">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q103">
         <v>5.13</v>
       </c>
       <c r="R103">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="S103">
         <v>1.35</v>
@@ -17134,16 +17134,16 @@
         <v>1.29</v>
       </c>
       <c r="Z103">
-        <v>3.46</v>
+        <v>3.42</v>
       </c>
       <c r="AA103">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AB103">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AC103">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AD103">
         <v>1.3</v>
@@ -17261,19 +17261,19 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="O104">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P104">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="Q104">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="R104">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="S104">
         <v>1.22</v>
@@ -17285,7 +17285,7 @@
         <v>2.2</v>
       </c>
       <c r="V104">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W104">
         <v>1.17</v>
@@ -17303,16 +17303,16 @@
         <v>1.5</v>
       </c>
       <c r="AB104">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="AC104">
         <v>2.26</v>
       </c>
       <c r="AD104">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AE104">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF104">
         <v>1.44</v>
@@ -17331,7 +17331,7 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK104">
         <v>1.8</v>
@@ -17424,13 +17424,13 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="O105">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P105">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
       <c r="Q105">
         <v>0</v>
@@ -17587,31 +17587,31 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="O106">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P106">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q106">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="R106">
         <v>2.3</v>
       </c>
       <c r="S106">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T106">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="U106">
         <v>2.25</v>
       </c>
       <c r="V106">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W106">
         <v>1.11</v>
@@ -17620,22 +17620,22 @@
         <v>1.03</v>
       </c>
       <c r="Y106">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z106">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AA106">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB106">
-        <v>2.27</v>
+        <v>2.32</v>
       </c>
       <c r="AC106">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="AD106">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AE106">
         <v>1.16</v>
@@ -17750,19 +17750,19 @@
         </is>
       </c>
       <c r="N107">
+        <v>2.45</v>
+      </c>
+      <c r="O107">
+        <v>3.2</v>
+      </c>
+      <c r="P107">
         <v>2.5</v>
       </c>
-      <c r="O107">
-        <v>3.3</v>
-      </c>
-      <c r="P107">
-        <v>2.53</v>
-      </c>
       <c r="Q107">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="R107">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="S107">
         <v>1.33</v>
@@ -17771,40 +17771,40 @@
         <v>2.88</v>
       </c>
       <c r="U107">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="V107">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W107">
         <v>1.05</v>
       </c>
       <c r="X107">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y107">
         <v>1.21</v>
       </c>
       <c r="Z107">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="AA107">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AB107">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AC107">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="AD107">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE107">
         <v>1.08</v>
       </c>
       <c r="AF107">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AG107">
         <v>2.2</v>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AK107">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -18082,7 +18082,7 @@
         <v>3.4</v>
       </c>
       <c r="P109">
-        <v>5.5</v>
+        <v>3.94</v>
       </c>
       <c r="Q109">
         <v>2</v>
@@ -18103,22 +18103,22 @@
         <v>1.45</v>
       </c>
       <c r="W109">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X109">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y109">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z109">
-        <v>4.1</v>
+        <v>3.92</v>
       </c>
       <c r="AA109">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AB109">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AC109">
         <v>2.75</v>
@@ -18133,7 +18133,7 @@
         <v>1.75</v>
       </c>
       <c r="AG109">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -19290,7 +19290,7 @@
         <v>1.22</v>
       </c>
       <c r="AK116">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -20041,7 +20041,7 @@
         <v>2.75</v>
       </c>
       <c r="Q121">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="R121">
         <v>1.84</v>
@@ -20050,7 +20050,7 @@
         <v>1.49</v>
       </c>
       <c r="T121">
-        <v>2.63</v>
+        <v>2.54</v>
       </c>
       <c r="U121">
         <v>3.34</v>
@@ -20059,28 +20059,28 @@
         <v>1.25</v>
       </c>
       <c r="W121">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X121">
         <v>1.06</v>
       </c>
       <c r="Y121">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Z121">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="AA121">
         <v>2.36</v>
       </c>
       <c r="AB121">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AC121">
         <v>4.3</v>
       </c>
       <c r="AD121">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AE121">
         <v>1.05</v>
@@ -20102,7 +20102,7 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AK121">
         <v>1.44</v>
@@ -20385,16 +20385,16 @@
         <v>1.4</v>
       </c>
       <c r="W123">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X123">
         <v>1</v>
       </c>
       <c r="Y123">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z123">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AA123">
         <v>1.8</v>
@@ -20684,10 +20684,10 @@
         </is>
       </c>
       <c r="N125">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="O125">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="P125">
         <v>2.25</v>
@@ -20705,13 +20705,13 @@
         <v>2.62</v>
       </c>
       <c r="U125">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="V125">
         <v>1.38</v>
       </c>
       <c r="W125">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X125">
         <v>1.02</v>
@@ -20720,19 +20720,19 @@
         <v>1.29</v>
       </c>
       <c r="Z125">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AA125">
         <v>2</v>
       </c>
       <c r="AB125">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AC125">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AD125">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE125">
         <v>1.07</v>
@@ -20757,7 +20757,7 @@
         <v>1.5</v>
       </c>
       <c r="AK125">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20847,13 +20847,13 @@
         </is>
       </c>
       <c r="N126">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="O126">
-        <v>3.46</v>
+        <v>3.2</v>
       </c>
       <c r="P126">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="Q126">
         <v>0</v>
@@ -21499,16 +21499,16 @@
         </is>
       </c>
       <c r="N130">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="O130">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="P130">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="Q130">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="R130">
         <v>2.38</v>
@@ -21520,10 +21520,10 @@
         <v>3.6</v>
       </c>
       <c r="U130">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="V130">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="W130">
         <v>1.11</v>
@@ -21532,10 +21532,10 @@
         <v>1.02</v>
       </c>
       <c r="Y130">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z130">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="AA130">
         <v>1.57</v>
@@ -21544,7 +21544,7 @@
         <v>2.35</v>
       </c>
       <c r="AC130">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AD130">
         <v>1.49</v>
@@ -21556,7 +21556,7 @@
         <v>1.58</v>
       </c>
       <c r="AG130">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,7 +21569,7 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK130">
         <v>2.15</v>
@@ -21825,19 +21825,19 @@
         </is>
       </c>
       <c r="N132">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="O132">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P132">
-        <v>5.25</v>
+        <v>4.6</v>
       </c>
       <c r="Q132">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="R132">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="S132">
         <v>1.4</v>
@@ -21855,7 +21855,7 @@
         <v>1.07</v>
       </c>
       <c r="X132">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y132">
         <v>1.31</v>
@@ -21870,13 +21870,13 @@
         <v>1.69</v>
       </c>
       <c r="AC132">
-        <v>3.82</v>
+        <v>3.85</v>
       </c>
       <c r="AD132">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE132">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF132">
         <v>2.05</v>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AK132">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -22314,13 +22314,13 @@
         </is>
       </c>
       <c r="N135">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="O135">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P135">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="Q135">
         <v>2.4</v>
@@ -22368,10 +22368,10 @@
         <v>1.12</v>
       </c>
       <c r="AF135">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AG135">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22477,10 +22477,10 @@
         </is>
       </c>
       <c r="N136">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="O136">
-        <v>3.73</v>
+        <v>3.95</v>
       </c>
       <c r="P136">
         <v>1.61</v>
@@ -22492,10 +22492,10 @@
         <v>2.28</v>
       </c>
       <c r="S136">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T136">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="U136">
         <v>2.64</v>
@@ -22510,10 +22510,10 @@
         <v>1.05</v>
       </c>
       <c r="Y136">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z136">
-        <v>3.5</v>
+        <v>3.74</v>
       </c>
       <c r="AA136">
         <v>1.72</v>
@@ -22522,7 +22522,7 @@
         <v>2.12</v>
       </c>
       <c r="AC136">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="AD136">
         <v>1.35</v>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.2</v>
+        <v>2.15</v>
       </c>
       <c r="AK136">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22842,7 +22842,7 @@
         <v>3.42</v>
       </c>
       <c r="AA138">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="AB138">
         <v>1.93</v>
@@ -22966,64 +22966,64 @@
         </is>
       </c>
       <c r="N139">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="O139">
-        <v>8.5</v>
+        <v>7.05</v>
       </c>
       <c r="P139">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="Q139">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="R139">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="S139">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="T139">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="U139">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="V139">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="W139">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X139">
         <v>1</v>
       </c>
       <c r="Y139">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Z139">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AA139">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB139">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AC139">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AD139">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AE139">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AF139">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AG139">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AK139">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23141,52 +23141,52 @@
         <v>1.8</v>
       </c>
       <c r="R140">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="S140">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="T140">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="U140">
-        <v>2.17</v>
+        <v>2.27</v>
       </c>
       <c r="V140">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="W140">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X140">
         <v>1.04</v>
       </c>
       <c r="Y140">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z140">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="AA140">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AB140">
-        <v>2.41</v>
+        <v>2.24</v>
       </c>
       <c r="AC140">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="AD140">
-        <v>1.63</v>
+        <v>1.45</v>
       </c>
       <c r="AE140">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AF140">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AG140">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23298,22 +23298,22 @@
         <v>3.2</v>
       </c>
       <c r="P141">
-        <v>4.6</v>
+        <v>4.15</v>
       </c>
       <c r="Q141">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="R141">
         <v>2</v>
       </c>
       <c r="S141">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="T141">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="U141">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="V141">
         <v>1.21</v>
@@ -23331,16 +23331,16 @@
         <v>2.45</v>
       </c>
       <c r="AA141">
-        <v>2.59</v>
+        <v>2.49</v>
       </c>
       <c r="AB141">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AC141">
         <v>5.05</v>
       </c>
       <c r="AD141">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AE141">
         <v>1.01</v>
@@ -23455,16 +23455,16 @@
         </is>
       </c>
       <c r="N142">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="O142">
         <v>3</v>
       </c>
       <c r="P142">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="Q142">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="R142">
         <v>1.81</v>
@@ -23476,22 +23476,22 @@
         <v>2.15</v>
       </c>
       <c r="U142">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="V142">
         <v>1.19</v>
       </c>
       <c r="W142">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X142">
         <v>1.09</v>
       </c>
       <c r="Y142">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="Z142">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="AA142">
         <v>2.86</v>
@@ -23512,7 +23512,7 @@
         <v>2.28</v>
       </c>
       <c r="AG142">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
@@ -23528,7 +23528,7 @@
         <v>1.18</v>
       </c>
       <c r="AK142">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -23618,13 +23618,13 @@
         </is>
       </c>
       <c r="N143">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="O143">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="P143">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="Q143">
         <v>2.62</v>
@@ -23639,7 +23639,7 @@
         <v>2.1</v>
       </c>
       <c r="U143">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="V143">
         <v>1.17</v>
@@ -23654,7 +23654,7 @@
         <v>1.8</v>
       </c>
       <c r="Z143">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AA143">
         <v>3.51</v>
@@ -23688,10 +23688,10 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AK143">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23781,13 +23781,13 @@
         </is>
       </c>
       <c r="N144">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="O144">
         <v>3.75</v>
       </c>
       <c r="P144">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="Q144">
         <v>3.92</v>
@@ -23799,7 +23799,7 @@
         <v>1.23</v>
       </c>
       <c r="T144">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="U144">
         <v>2.3</v>
@@ -23820,22 +23820,22 @@
         <v>5.05</v>
       </c>
       <c r="AA144">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB144">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="AC144">
-        <v>2.38</v>
+        <v>2.21</v>
       </c>
       <c r="AD144">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AE144">
         <v>1.23</v>
       </c>
       <c r="AF144">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AG144">
         <v>2.4</v>
@@ -24596,7 +24596,7 @@
         </is>
       </c>
       <c r="N149">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="O149">
         <v>7.5</v>
@@ -24611,13 +24611,13 @@
         <v>3.19</v>
       </c>
       <c r="S149">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="T149">
         <v>5.6</v>
       </c>
       <c r="U149">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="V149">
         <v>2.1</v>
@@ -24632,7 +24632,7 @@
         <v>1.01</v>
       </c>
       <c r="Z149">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AA149">
         <v>1.22</v>
@@ -24641,7 +24641,7 @@
         <v>4.05</v>
       </c>
       <c r="AC149">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="AD149">
         <v>2.25</v>
@@ -24650,7 +24650,7 @@
         <v>1.61</v>
       </c>
       <c r="AF149">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AG149">
         <v>2.22</v>
@@ -24922,31 +24922,31 @@
         </is>
       </c>
       <c r="N151">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="O151">
-        <v>5.65</v>
+        <v>5.4</v>
       </c>
       <c r="P151">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="Q151">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R151">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="S151">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T151">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U151">
         <v>2.32</v>
       </c>
       <c r="V151">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W151">
         <v>1.14</v>
@@ -24955,31 +24955,31 @@
         <v>1.03</v>
       </c>
       <c r="Y151">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z151">
-        <v>4.57</v>
+        <v>4.6</v>
       </c>
       <c r="AA151">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AB151">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="AC151">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="AD151">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AE151">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF151">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AG151">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
@@ -24992,10 +24992,10 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AK151">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AL151">
         <v>0</v>
@@ -25085,13 +25085,13 @@
         </is>
       </c>
       <c r="N152">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="O152">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P152">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q152">
         <v>2.5</v>
@@ -25115,7 +25115,7 @@
         <v>1.15</v>
       </c>
       <c r="X152">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y152">
         <v>1.12</v>
@@ -25124,7 +25124,7 @@
         <v>4.8</v>
       </c>
       <c r="AA152">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AB152">
         <v>2.3</v>
@@ -25133,7 +25133,7 @@
         <v>2.27</v>
       </c>
       <c r="AD152">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AE152">
         <v>1.17</v>
@@ -25254,7 +25254,7 @@
         <v>3.1</v>
       </c>
       <c r="P153">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="Q153">
         <v>3.25</v>
@@ -25269,19 +25269,19 @@
         <v>2.85</v>
       </c>
       <c r="U153">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="V153">
         <v>1.36</v>
       </c>
       <c r="W153">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X153">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y153">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z153">
         <v>3.04</v>
@@ -25296,7 +25296,7 @@
         <v>3.5</v>
       </c>
       <c r="AD153">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE153">
         <v>1.05</v>
@@ -25411,7 +25411,7 @@
         </is>
       </c>
       <c r="N154">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="O154">
         <v>3.2</v>
@@ -25423,13 +25423,13 @@
         <v>4.2</v>
       </c>
       <c r="R154">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S154">
         <v>1.44</v>
       </c>
       <c r="T154">
-        <v>2.63</v>
+        <v>2.54</v>
       </c>
       <c r="U154">
         <v>3.1</v>
@@ -25438,37 +25438,37 @@
         <v>1.33</v>
       </c>
       <c r="W154">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X154">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y154">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Z154">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="AA154">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="AB154">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AC154">
-        <v>4.1</v>
+        <v>3.98</v>
       </c>
       <c r="AD154">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AE154">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF154">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AG154">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK154">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25586,13 +25586,13 @@
         <v>2</v>
       </c>
       <c r="R155">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S155">
         <v>1.3</v>
       </c>
       <c r="T155">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="U155">
         <v>2.4</v>
@@ -25622,16 +25622,16 @@
         <v>2.63</v>
       </c>
       <c r="AD155">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AE155">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF155">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AG155">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25737,22 +25737,22 @@
         </is>
       </c>
       <c r="N156">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="O156">
         <v>3.9</v>
       </c>
       <c r="P156">
-        <v>4.55</v>
+        <v>4.33</v>
       </c>
       <c r="Q156">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="R156">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="S156">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T156">
         <v>3.5</v>
@@ -25770,10 +25770,10 @@
         <v>1.03</v>
       </c>
       <c r="Y156">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z156">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AA156">
         <v>1.47</v>
@@ -25782,19 +25782,19 @@
         <v>2.38</v>
       </c>
       <c r="AC156">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="AD156">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AE156">
         <v>1.19</v>
       </c>
       <c r="AF156">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG156">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -26066,7 +26066,7 @@
         <v>1.5</v>
       </c>
       <c r="O158">
-        <v>4.3</v>
+        <v>3.72</v>
       </c>
       <c r="P158">
         <v>5.3</v>
@@ -26226,22 +26226,22 @@
         </is>
       </c>
       <c r="N159">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="O159">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P159">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="Q159">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="R159">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S159">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T159">
         <v>2.73</v>
@@ -26250,13 +26250,13 @@
         <v>3.17</v>
       </c>
       <c r="V159">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W159">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X159">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y159">
         <v>1.28</v>
@@ -26299,7 +26299,7 @@
         <v>1.25</v>
       </c>
       <c r="AK159">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26392,10 +26392,10 @@
         <v>1.84</v>
       </c>
       <c r="O160">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P160">
-        <v>3.8</v>
+        <v>4.15</v>
       </c>
       <c r="Q160">
         <v>2.3</v>
@@ -26419,7 +26419,7 @@
         <v>1.04</v>
       </c>
       <c r="X160">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y160">
         <v>1.33</v>
@@ -26431,13 +26431,13 @@
         <v>1.96</v>
       </c>
       <c r="AB160">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AC160">
         <v>3.6</v>
       </c>
       <c r="AD160">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE160">
         <v>1.06</v>
@@ -26462,7 +26462,7 @@
         <v>1.22</v>
       </c>
       <c r="AK160">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -26552,10 +26552,10 @@
         </is>
       </c>
       <c r="N161">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="O161">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P161">
         <v>2.79</v>
@@ -26715,34 +26715,34 @@
         </is>
       </c>
       <c r="N162">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O162">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P162">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="Q162">
-        <v>3.88</v>
+        <v>4.58</v>
       </c>
       <c r="R162">
         <v>2.16</v>
       </c>
       <c r="S162">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T162">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="U162">
         <v>2.94</v>
       </c>
       <c r="V162">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W162">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X162">
         <v>1.06</v>
@@ -26769,7 +26769,7 @@
         <v>1.08</v>
       </c>
       <c r="AF162">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AG162">
         <v>1.91</v>
@@ -26785,7 +26785,7 @@
         </is>
       </c>
       <c r="AJ162">
-        <v>1.83</v>
+        <v>1.3</v>
       </c>
       <c r="AK162">
         <v>1.2</v>
@@ -26878,13 +26878,13 @@
         </is>
       </c>
       <c r="N163">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O163">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="P163">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q163">
         <v>4.2</v>
@@ -26896,19 +26896,19 @@
         <v>1.41</v>
       </c>
       <c r="T163">
+        <v>2.69</v>
+      </c>
+      <c r="U163">
         <v>2.8</v>
       </c>
-      <c r="U163">
-        <v>2.9</v>
-      </c>
       <c r="V163">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W163">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X163">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y163">
         <v>1.3</v>
@@ -26920,22 +26920,22 @@
         <v>1.97</v>
       </c>
       <c r="AB163">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AC163">
-        <v>3.18</v>
+        <v>3.7</v>
       </c>
       <c r="AD163">
         <v>1.27</v>
       </c>
       <c r="AE163">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF163">
         <v>1.76</v>
       </c>
       <c r="AG163">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
@@ -27044,13 +27044,13 @@
         <v>2.45</v>
       </c>
       <c r="O164">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P164">
         <v>2.5</v>
       </c>
       <c r="Q164">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="R164">
         <v>2.25</v>
@@ -27068,7 +27068,7 @@
         <v>1.42</v>
       </c>
       <c r="W164">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X164">
         <v>1.05</v>
@@ -27083,16 +27083,16 @@
         <v>1.83</v>
       </c>
       <c r="AB164">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AC164">
-        <v>3.2</v>
+        <v>2.72</v>
       </c>
       <c r="AD164">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE164">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF164">
         <v>1.6</v>
@@ -27114,7 +27114,7 @@
         <v>1.29</v>
       </c>
       <c r="AK164">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AL164">
         <v>0</v>
@@ -27210,7 +27210,7 @@
         <v>3.2</v>
       </c>
       <c r="P165">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="Q165">
         <v>2.59</v>
@@ -27219,10 +27219,10 @@
         <v>2.12</v>
       </c>
       <c r="S165">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T165">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="U165">
         <v>2.66</v>
@@ -27246,10 +27246,10 @@
         <v>1.95</v>
       </c>
       <c r="AB165">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AC165">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="AD165">
         <v>1.29</v>
@@ -27367,19 +27367,19 @@
         </is>
       </c>
       <c r="N166">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="O166">
-        <v>3.3</v>
+        <v>3.52</v>
       </c>
       <c r="P166">
-        <v>3.5</v>
+        <v>3.59</v>
       </c>
       <c r="Q166">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="R166">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="S166">
         <v>1.4</v>
@@ -27406,10 +27406,10 @@
         <v>3.4</v>
       </c>
       <c r="AA166">
-        <v>2.06</v>
+        <v>1.87</v>
       </c>
       <c r="AB166">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AC166">
         <v>3.4</v>
@@ -27440,7 +27440,7 @@
         <v>1.29</v>
       </c>
       <c r="AK166">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AL166">
         <v>0</v>
@@ -27533,37 +27533,37 @@
         <v>2</v>
       </c>
       <c r="O167">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P167">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="Q167">
-        <v>2.44</v>
+        <v>2.57</v>
       </c>
       <c r="R167">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="S167">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T167">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U167">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="V167">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="W167">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X167">
         <v>1.01</v>
       </c>
       <c r="Y167">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="Z167">
         <v>3.55</v>
@@ -27572,7 +27572,7 @@
         <v>1.86</v>
       </c>
       <c r="AB167">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AC167">
         <v>3.4</v>
@@ -27584,7 +27584,7 @@
         <v>1.09</v>
       </c>
       <c r="AF167">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG167">
         <v>2</v>
@@ -27603,7 +27603,7 @@
         <v>1.3</v>
       </c>
       <c r="AK167">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AL167">
         <v>0</v>
@@ -27862,7 +27862,7 @@
         <v>3.9</v>
       </c>
       <c r="P169">
-        <v>5.25</v>
+        <v>5.46</v>
       </c>
       <c r="Q169">
         <v>0</v>
@@ -28843,55 +28843,55 @@
         <v>0</v>
       </c>
       <c r="Q175">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R175">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S175">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T175">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U175">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V175">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W175">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X175">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y175">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z175">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AA175">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AB175">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AC175">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AD175">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE175">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF175">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG175">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK175">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -28997,64 +28997,64 @@
         </is>
       </c>
       <c r="N176">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O176">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P176">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q176">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R176">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S176">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="T176">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U176">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="V176">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="W176">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X176">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y176">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Z176">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AA176">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AB176">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AC176">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AD176">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE176">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF176">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AG176">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK176">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29329,19 +29329,19 @@
         <v>3.3</v>
       </c>
       <c r="P178">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q178">
         <v>2.63</v>
       </c>
       <c r="R178">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="S178">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T178">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="U178">
         <v>2.88</v>
@@ -29350,7 +29350,7 @@
         <v>1.36</v>
       </c>
       <c r="W178">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X178">
         <v>1.01</v>
@@ -29362,10 +29362,10 @@
         <v>3.47</v>
       </c>
       <c r="AA178">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AB178">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AC178">
         <v>3.28</v>
@@ -29396,7 +29396,7 @@
         <v>1.28</v>
       </c>
       <c r="AK178">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -29495,10 +29495,10 @@
         <v>6</v>
       </c>
       <c r="Q179">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="R179">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="S179">
         <v>1.2</v>
@@ -29516,10 +29516,10 @@
         <v>1.17</v>
       </c>
       <c r="X179">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y179">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z179">
         <v>5.4</v>
@@ -29537,7 +29537,7 @@
         <v>1.62</v>
       </c>
       <c r="AE179">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF179">
         <v>1.62</v>
@@ -29559,7 +29559,7 @@
         <v>1.15</v>
       </c>
       <c r="AK179">
-        <v>2.57</v>
+        <v>2.72</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -29649,28 +29649,28 @@
         </is>
       </c>
       <c r="N180">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="O180">
         <v>3.2</v>
       </c>
       <c r="P180">
-        <v>3.19</v>
+        <v>2.85</v>
       </c>
       <c r="Q180">
         <v>2.85</v>
       </c>
       <c r="R180">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="S180">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="T180">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="U180">
-        <v>3.21</v>
+        <v>2.88</v>
       </c>
       <c r="V180">
         <v>1.35</v>
@@ -29685,13 +29685,13 @@
         <v>1.37</v>
       </c>
       <c r="Z180">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AA180">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AB180">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="AC180">
         <v>3.91</v>
@@ -29700,13 +29700,13 @@
         <v>1.24</v>
       </c>
       <c r="AE180">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF180">
         <v>1.91</v>
       </c>
       <c r="AG180">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH180" t="inlineStr">
         <is>
@@ -29812,13 +29812,13 @@
         </is>
       </c>
       <c r="N181">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="O181">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="P181">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Q181">
         <v>9</v>
@@ -29842,13 +29842,13 @@
         <v>1.17</v>
       </c>
       <c r="X181">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y181">
         <v>1.13</v>
       </c>
       <c r="Z181">
-        <v>4.72</v>
+        <v>5</v>
       </c>
       <c r="AA181">
         <v>1.53</v>
@@ -29857,7 +29857,7 @@
         <v>2.32</v>
       </c>
       <c r="AC181">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AD181">
         <v>1.63</v>
@@ -30799,55 +30799,55 @@
         <v>0</v>
       </c>
       <c r="Q187">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R187">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S187">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T187">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="U187">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="V187">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="W187">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X187">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y187">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z187">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA187">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB187">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AC187">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AD187">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE187">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF187">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG187">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
@@ -30860,10 +30860,10 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK187">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -31605,13 +31605,13 @@
         </is>
       </c>
       <c r="N192">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="O192">
-        <v>3.15</v>
+        <v>2.83</v>
       </c>
       <c r="P192">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="Q192">
         <v>2.55</v>
@@ -31620,7 +31620,7 @@
         <v>2</v>
       </c>
       <c r="S192">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T192">
         <v>2.4</v>
@@ -31632,7 +31632,7 @@
         <v>1.25</v>
       </c>
       <c r="W192">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X192">
         <v>1.1</v>
@@ -31659,10 +31659,10 @@
         <v>1.05</v>
       </c>
       <c r="AF192">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AG192">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
@@ -32278,22 +32278,22 @@
         <v>3.18</v>
       </c>
       <c r="U196">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="V196">
         <v>1.5</v>
       </c>
       <c r="W196">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X196">
         <v>1.02</v>
       </c>
       <c r="Y196">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="Z196">
-        <v>4.3</v>
+        <v>4.17</v>
       </c>
       <c r="AA196">
         <v>1.68</v>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK196">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32420,10 +32420,10 @@
         </is>
       </c>
       <c r="N197">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="O197">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="P197">
         <v>2.85</v>
@@ -32447,7 +32447,7 @@
         <v>1.57</v>
       </c>
       <c r="W197">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X197">
         <v>1.02</v>
@@ -32462,13 +32462,13 @@
         <v>1.61</v>
       </c>
       <c r="AB197">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AC197">
         <v>2.66</v>
       </c>
       <c r="AD197">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AE197">
         <v>1.16</v>
@@ -32477,7 +32477,7 @@
         <v>1.51</v>
       </c>
       <c r="AG197">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32490,10 +32490,10 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK197">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -32604,7 +32604,7 @@
         <v>3.25</v>
       </c>
       <c r="U198">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V198">
         <v>1.48</v>
@@ -32634,7 +32634,7 @@
         <v>1.44</v>
       </c>
       <c r="AE198">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AF198">
         <v>1.48</v>
@@ -32656,7 +32656,7 @@
         <v>1.2</v>
       </c>
       <c r="AK198">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -32746,80 +32746,80 @@
         </is>
       </c>
       <c r="N199">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="O199">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P199">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="Q199">
-        <v>2.74</v>
+        <v>2.65</v>
       </c>
       <c r="R199">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="S199">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T199">
         <v>3.25</v>
       </c>
       <c r="U199">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="V199">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W199">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X199">
         <v>1.01</v>
       </c>
       <c r="Y199">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z199">
-        <v>3.65</v>
+        <v>3.82</v>
       </c>
       <c r="AA199">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AB199">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AC199">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="AD199">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE199">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF199">
+        <v>1.58</v>
+      </c>
+      <c r="AG199">
+        <v>2.21</v>
+      </c>
+      <c r="AH199" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI199" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ199">
+        <v>1.34</v>
+      </c>
+      <c r="AK199">
         <v>1.57</v>
-      </c>
-      <c r="AG199">
-        <v>2.23</v>
-      </c>
-      <c r="AH199" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI199" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ199">
-        <v>1.22</v>
-      </c>
-      <c r="AK199">
-        <v>1.53</v>
       </c>
       <c r="AL199">
         <v>0</v>
@@ -32909,61 +32909,61 @@
         </is>
       </c>
       <c r="N200">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O200">
+        <v>3</v>
+      </c>
+      <c r="P200">
         <v>2.95</v>
       </c>
-      <c r="P200">
-        <v>2.88</v>
-      </c>
       <c r="Q200">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="R200">
+        <v>2.01</v>
+      </c>
+      <c r="S200">
+        <v>1.49</v>
+      </c>
+      <c r="T200">
+        <v>2.36</v>
+      </c>
+      <c r="U200">
+        <v>3.25</v>
+      </c>
+      <c r="V200">
+        <v>1.26</v>
+      </c>
+      <c r="W200">
+        <v>1.01</v>
+      </c>
+      <c r="X200">
+        <v>1.05</v>
+      </c>
+      <c r="Y200">
+        <v>1.44</v>
+      </c>
+      <c r="Z200">
+        <v>2.71</v>
+      </c>
+      <c r="AA200">
+        <v>2.36</v>
+      </c>
+      <c r="AB200">
+        <v>1.52</v>
+      </c>
+      <c r="AC200">
+        <v>4.33</v>
+      </c>
+      <c r="AD200">
+        <v>1.14</v>
+      </c>
+      <c r="AE200">
+        <v>1.01</v>
+      </c>
+      <c r="AF200">
         <v>1.98</v>
-      </c>
-      <c r="S200">
-        <v>1.43</v>
-      </c>
-      <c r="T200">
-        <v>2.4</v>
-      </c>
-      <c r="U200">
-        <v>3.2</v>
-      </c>
-      <c r="V200">
-        <v>1.3</v>
-      </c>
-      <c r="W200">
-        <v>1.03</v>
-      </c>
-      <c r="X200">
-        <v>1.03</v>
-      </c>
-      <c r="Y200">
-        <v>1.38</v>
-      </c>
-      <c r="Z200">
-        <v>2.63</v>
-      </c>
-      <c r="AA200">
-        <v>2.19</v>
-      </c>
-      <c r="AB200">
-        <v>1.6</v>
-      </c>
-      <c r="AC200">
-        <v>3.92</v>
-      </c>
-      <c r="AD200">
-        <v>1.18</v>
-      </c>
-      <c r="AE200">
-        <v>1.03</v>
-      </c>
-      <c r="AF200">
-        <v>1.91</v>
       </c>
       <c r="AG200">
         <v>1.76</v>
@@ -32979,10 +32979,10 @@
         </is>
       </c>
       <c r="AJ200">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK200">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AL200">
         <v>0</v>
@@ -33244,16 +33244,16 @@
         <v>3.15</v>
       </c>
       <c r="Q202">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="R202">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="S202">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T202">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U202">
         <v>2.62</v>
@@ -33262,25 +33262,25 @@
         <v>1.44</v>
       </c>
       <c r="W202">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X202">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y202">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z202">
         <v>3.25</v>
       </c>
       <c r="AA202">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB202">
         <v>1.95</v>
       </c>
       <c r="AC202">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="AD202">
         <v>1.3</v>
@@ -33289,7 +33289,7 @@
         <v>1.07</v>
       </c>
       <c r="AF202">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AG202">
         <v>2.07</v>
@@ -33305,10 +33305,10 @@
         </is>
       </c>
       <c r="AJ202">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK202">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AL202">
         <v>0</v>
@@ -33890,10 +33890,10 @@
         <v>1.41</v>
       </c>
       <c r="O206">
-        <v>4.45</v>
+        <v>4.6</v>
       </c>
       <c r="P206">
-        <v>6.64</v>
+        <v>6.25</v>
       </c>
       <c r="Q206">
         <v>0</v>
@@ -34376,28 +34376,28 @@
         </is>
       </c>
       <c r="N209">
-        <v>2.55</v>
+        <v>2.85</v>
       </c>
       <c r="O209">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="P209">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="Q209">
-        <v>3.05</v>
+        <v>3.54</v>
       </c>
       <c r="R209">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="S209">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T209">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="U209">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="V209">
         <v>1.4</v>
@@ -34409,22 +34409,22 @@
         <v>1.01</v>
       </c>
       <c r="Y209">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z209">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AA209">
-        <v>1.79</v>
+        <v>1.99</v>
       </c>
       <c r="AB209">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AC209">
-        <v>2.9</v>
+        <v>3.42</v>
       </c>
       <c r="AD209">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AE209">
         <v>1.04</v>
@@ -34433,7 +34433,7 @@
         <v>1.64</v>
       </c>
       <c r="AG209">
-        <v>2.07</v>
+        <v>1.96</v>
       </c>
       <c r="AH209" t="inlineStr">
         <is>
@@ -34446,10 +34446,10 @@
         </is>
       </c>
       <c r="AJ209">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AK209">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -34557,13 +34557,13 @@
         <v>1.27</v>
       </c>
       <c r="T210">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U210">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="V210">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="W210">
         <v>1.11</v>
@@ -34572,10 +34572,10 @@
         <v>1.03</v>
       </c>
       <c r="Y210">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="Z210">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="AA210">
         <v>1.63</v>
@@ -34590,13 +34590,13 @@
         <v>1.36</v>
       </c>
       <c r="AE210">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF210">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AG210">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AH210" t="inlineStr">
         <is>
@@ -34612,7 +34612,7 @@
         <v>2</v>
       </c>
       <c r="AK210">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AL210">
         <v>0</v>
@@ -34702,34 +34702,34 @@
         </is>
       </c>
       <c r="N211">
-        <v>1.99</v>
+        <v>1.78</v>
       </c>
       <c r="O211">
+        <v>3.75</v>
+      </c>
+      <c r="P211">
         <v>3.6</v>
       </c>
-      <c r="P211">
-        <v>3.14</v>
-      </c>
       <c r="Q211">
-        <v>2.55</v>
+        <v>2.34</v>
       </c>
       <c r="R211">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="S211">
         <v>1.29</v>
       </c>
       <c r="T211">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="U211">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="V211">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W211">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X211">
         <v>1.02</v>
@@ -34738,25 +34738,25 @@
         <v>1.17</v>
       </c>
       <c r="Z211">
-        <v>4</v>
+        <v>4.18</v>
       </c>
       <c r="AA211">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AB211">
         <v>2.2</v>
       </c>
       <c r="AC211">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="AD211">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AE211">
         <v>1.14</v>
       </c>
       <c r="AF211">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG211">
         <v>2.23</v>
@@ -34772,10 +34772,10 @@
         </is>
       </c>
       <c r="AJ211">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK211">
-        <v>1.54</v>
+        <v>1.79</v>
       </c>
       <c r="AL211">
         <v>0</v>
@@ -34865,31 +34865,31 @@
         </is>
       </c>
       <c r="N212">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="O212">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="P212">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="Q212">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="R212">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="S212">
         <v>1.32</v>
       </c>
       <c r="T212">
-        <v>2.96</v>
+        <v>3.22</v>
       </c>
       <c r="U212">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="V212">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="W212">
         <v>1.06</v>
@@ -34898,31 +34898,31 @@
         <v>1</v>
       </c>
       <c r="Y212">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z212">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AA212">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AB212">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AC212">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="AD212">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE212">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF212">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AG212">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="AH212" t="inlineStr">
         <is>
@@ -34935,10 +34935,10 @@
         </is>
       </c>
       <c r="AJ212">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="AK212">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AL212">
         <v>0</v>
@@ -35028,7 +35028,7 @@
         </is>
       </c>
       <c r="N213">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="O213">
         <v>3.4</v>
@@ -35040,7 +35040,7 @@
         <v>4.2</v>
       </c>
       <c r="R213">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="S213">
         <v>1.33</v>
@@ -35082,7 +35082,7 @@
         <v>1.08</v>
       </c>
       <c r="AF213">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG213">
         <v>1.95</v>
@@ -35098,7 +35098,7 @@
         </is>
       </c>
       <c r="AJ213">
-        <v>1.21</v>
+        <v>1.82</v>
       </c>
       <c r="AK213">
         <v>1.16</v>

--- a/jogos_2026-08-08.xlsx
+++ b/jogos_2026-08-08.xlsx
@@ -641,7 +641,7 @@
         <v>3.45</v>
       </c>
       <c r="P2">
-        <v>3.46</v>
+        <v>3.3</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -1133,28 +1133,28 @@
         <v>1.7</v>
       </c>
       <c r="Q5">
-        <v>4.7</v>
+        <v>5.02</v>
       </c>
       <c r="R5">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="S5">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T5">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U5">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="V5">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W5">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y5">
         <v>1.22</v>
@@ -1163,25 +1163,25 @@
         <v>3.5</v>
       </c>
       <c r="AA5">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AB5">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AC5">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AD5">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE5">
         <v>1.08</v>
       </c>
       <c r="AF5">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AG5">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1296,10 +1296,10 @@
         <v>2.95</v>
       </c>
       <c r="Q6">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="R6">
-        <v>2.35</v>
+        <v>2.16</v>
       </c>
       <c r="S6">
         <v>1.29</v>
@@ -1308,10 +1308,10 @@
         <v>3.25</v>
       </c>
       <c r="U6">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V6">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W6">
         <v>1.11</v>
@@ -1320,7 +1320,7 @@
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z6">
         <v>4</v>
@@ -1329,22 +1329,22 @@
         <v>1.7</v>
       </c>
       <c r="AB6">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AC6">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AD6">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AE6">
         <v>1.11</v>
       </c>
       <c r="AF6">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG6">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AK6">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1459,10 +1459,10 @@
         <v>3.25</v>
       </c>
       <c r="Q7">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="R7">
-        <v>2.43</v>
+        <v>2.23</v>
       </c>
       <c r="S7">
         <v>1.25</v>
@@ -1474,7 +1474,7 @@
         <v>2.12</v>
       </c>
       <c r="V7">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="W7">
         <v>1.13</v>
@@ -1483,10 +1483,10 @@
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z7">
-        <v>4.4</v>
+        <v>4.65</v>
       </c>
       <c r="AA7">
         <v>1.5</v>
@@ -1501,13 +1501,13 @@
         <v>1.52</v>
       </c>
       <c r="AE7">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AF7">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AG7">
-        <v>2.48</v>
+        <v>2.39</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK7">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1622,22 +1622,22 @@
         <v>1.33</v>
       </c>
       <c r="Q8">
-        <v>5.8</v>
+        <v>5.55</v>
       </c>
       <c r="R8">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="S8">
         <v>1.21</v>
       </c>
       <c r="T8">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="U8">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="V8">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="W8">
         <v>1.14</v>
@@ -1646,31 +1646,31 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z8">
         <v>5.4</v>
       </c>
       <c r="AA8">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB8">
-        <v>2.75</v>
+        <v>2.43</v>
       </c>
       <c r="AC8">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AD8">
         <v>1.58</v>
       </c>
       <c r="AE8">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF8">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AG8">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>1.13</v>
       </c>
       <c r="AK8">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1833,7 +1833,7 @@
         <v>1.99</v>
       </c>
       <c r="AG9">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.27</v>
+        <v>1.08</v>
       </c>
       <c r="AK9">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>3.71</v>
+        <v>3.6</v>
       </c>
       <c r="O10">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="P10">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -3086,7 +3086,7 @@
         <v>3.15</v>
       </c>
       <c r="P17">
-        <v>4.21</v>
+        <v>3.35</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -3110,10 +3110,10 @@
         <v>1.01</v>
       </c>
       <c r="X17">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y17">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z17">
         <v>2.83</v>
@@ -3125,13 +3125,13 @@
         <v>1.66</v>
       </c>
       <c r="AC17">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="AD17">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE17">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF17">
         <v>1.85</v>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O25">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P25">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q25">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R25">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S25">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T25">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="U25">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="V25">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W25">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X25">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y25">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z25">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AA25">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC25">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD25">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE25">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF25">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG25">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK25">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,31 +4547,31 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.62</v>
+        <v>3.3</v>
       </c>
       <c r="O26">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="P26">
-        <v>2.45</v>
+        <v>1.9</v>
       </c>
       <c r="Q26">
-        <v>3.25</v>
+        <v>3.61</v>
       </c>
       <c r="R26">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="S26">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T26">
-        <v>2.75</v>
+        <v>2.94</v>
       </c>
       <c r="U26">
-        <v>2.81</v>
+        <v>2.72</v>
       </c>
       <c r="V26">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W26">
         <v>1.06</v>
@@ -4580,31 +4580,31 @@
         <v>1.05</v>
       </c>
       <c r="Y26">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z26">
-        <v>3.24</v>
+        <v>3.54</v>
       </c>
       <c r="AA26">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB26">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AC26">
-        <v>3.18</v>
+        <v>2.89</v>
       </c>
       <c r="AD26">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AE26">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF26">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG26">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.35</v>
+        <v>1.85</v>
       </c>
       <c r="AK26">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>2026-08-08 07:30:00</t>
+          <t>2026-08-08 08:00:00</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.94</v>
+        <v>2.62</v>
       </c>
       <c r="O27">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="P27">
-        <v>3.9</v>
+        <v>2.37</v>
       </c>
       <c r="Q27">
-        <v>2.38</v>
+        <v>3.25</v>
       </c>
       <c r="R27">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S27">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="T27">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="U27">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="V27">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="W27">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X27">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y27">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="Z27">
-        <v>2.6</v>
+        <v>3.24</v>
       </c>
       <c r="AA27">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AB27">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="AC27">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="AD27">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="AE27">
         <v>1.06</v>
       </c>
       <c r="AF27">
-        <v>2.01</v>
+        <v>1.75</v>
       </c>
       <c r="AG27">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AK27">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>2026-08-08 07:30:00</t>
+          <t>2026-08-08 08:00:00</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,81 +4873,81 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.67</v>
+        <v>1.91</v>
       </c>
       <c r="O28">
-        <v>3.22</v>
+        <v>3.13</v>
       </c>
       <c r="P28">
-        <v>2.58</v>
+        <v>3.75</v>
       </c>
       <c r="Q28">
-        <v>3.32</v>
+        <v>2.38</v>
       </c>
       <c r="R28">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="S28">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="T28">
-        <v>2.88</v>
+        <v>2.64</v>
       </c>
       <c r="U28">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="V28">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="W28">
         <v>1.06</v>
       </c>
       <c r="X28">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y28">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="Z28">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="AA28">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AB28">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AC28">
-        <v>3.47</v>
+        <v>4.25</v>
       </c>
       <c r="AD28">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AE28">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF28">
-        <v>1.76</v>
+        <v>1.99</v>
       </c>
       <c r="AG28">
+        <v>1.75</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28">
+        <v>1.28</v>
+      </c>
+      <c r="AK28">
         <v>1.85</v>
       </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28">
-        <v>1.32</v>
-      </c>
-      <c r="AK28">
-        <v>1.4</v>
-      </c>
       <c r="AL28">
         <v>0</v>
       </c>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>2026-08-08 07:30:00</t>
+          <t>2026-08-08 08:00:00</t>
         </is>
       </c>
     </row>
@@ -4989,7 +4989,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.78</v>
+        <v>2.67</v>
       </c>
       <c r="O29">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="P29">
-        <v>3.83</v>
+        <v>2.58</v>
       </c>
       <c r="Q29">
-        <v>2.4</v>
+        <v>3.32</v>
       </c>
       <c r="R29">
-        <v>2.11</v>
+        <v>2.22</v>
       </c>
       <c r="S29">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T29">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="U29">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="V29">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W29">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X29">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
         <v>1.3</v>
       </c>
       <c r="Z29">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA29">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AB29">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AC29">
-        <v>3.69</v>
+        <v>3.47</v>
       </c>
       <c r="AD29">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE29">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF29">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AG29">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="AK29">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>2026-08-08 07:30:00</t>
+          <t>2026-08-08 08:00:00</t>
         </is>
       </c>
     </row>
@@ -5152,12 +5152,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>2026-08-08 07:30:00</t>
+          <t>2026-08-08 08:00:00</t>
         </is>
       </c>
     </row>
@@ -5315,12 +5315,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>2026-08-08 07:30:00</t>
+          <t>2026-08-08 08:00:00</t>
         </is>
       </c>
     </row>
@@ -5478,7 +5478,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="O32">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P32">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q32">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="R32">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S32">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="T32">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="U32">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="V32">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W32">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X32">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y32">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z32">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA32">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB32">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC32">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD32">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE32">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF32">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG32">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK32">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>2026-08-08 07:30:00</t>
+          <t>2026-08-08 08:00:00</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,80 +5688,80 @@
         </is>
       </c>
       <c r="N33">
-        <v>3.61</v>
+        <v>1.93</v>
       </c>
       <c r="O33">
-        <v>4.02</v>
+        <v>3.13</v>
       </c>
       <c r="P33">
-        <v>1.92</v>
+        <v>2.95</v>
       </c>
       <c r="Q33">
-        <v>4.33</v>
+        <v>2.64</v>
       </c>
       <c r="R33">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="S33">
+        <v>1.34</v>
+      </c>
+      <c r="T33">
+        <v>2.89</v>
+      </c>
+      <c r="U33">
+        <v>2.73</v>
+      </c>
+      <c r="V33">
+        <v>1.38</v>
+      </c>
+      <c r="W33">
+        <v>1.08</v>
+      </c>
+      <c r="X33">
+        <v>1.05</v>
+      </c>
+      <c r="Y33">
+        <v>1.26</v>
+      </c>
+      <c r="Z33">
+        <v>3.2</v>
+      </c>
+      <c r="AA33">
+        <v>1.95</v>
+      </c>
+      <c r="AB33">
+        <v>1.75</v>
+      </c>
+      <c r="AC33">
+        <v>3.4</v>
+      </c>
+      <c r="AD33">
+        <v>1.27</v>
+      </c>
+      <c r="AE33">
+        <v>1.08</v>
+      </c>
+      <c r="AF33">
+        <v>1.77</v>
+      </c>
+      <c r="AG33">
+        <v>1.9</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ33">
         <v>1.22</v>
       </c>
-      <c r="T33">
-        <v>4</v>
-      </c>
-      <c r="U33">
-        <v>2.05</v>
-      </c>
-      <c r="V33">
+      <c r="AK33">
         <v>1.7</v>
-      </c>
-      <c r="W33">
-        <v>1.2</v>
-      </c>
-      <c r="X33">
-        <v>1.02</v>
-      </c>
-      <c r="Y33">
-        <v>1.09</v>
-      </c>
-      <c r="Z33">
-        <v>5</v>
-      </c>
-      <c r="AA33">
-        <v>1.48</v>
-      </c>
-      <c r="AB33">
-        <v>2.6</v>
-      </c>
-      <c r="AC33">
-        <v>2.2</v>
-      </c>
-      <c r="AD33">
-        <v>1.69</v>
-      </c>
-      <c r="AE33">
-        <v>1.27</v>
-      </c>
-      <c r="AF33">
-        <v>1.47</v>
-      </c>
-      <c r="AG33">
-        <v>2.55</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ33">
-        <v>1.2</v>
-      </c>
-      <c r="AK33">
-        <v>1.2</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5863,13 +5863,13 @@
         <v>2.44</v>
       </c>
       <c r="R34">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="S34">
         <v>1.3</v>
       </c>
       <c r="T34">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="U34">
         <v>2.3</v>
@@ -5878,10 +5878,10 @@
         <v>1.49</v>
       </c>
       <c r="W34">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X34">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y34">
         <v>1.22</v>
@@ -5890,10 +5890,10 @@
         <v>4</v>
       </c>
       <c r="AA34">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB34">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AC34">
         <v>2.52</v>
@@ -5902,7 +5902,7 @@
         <v>1.53</v>
       </c>
       <c r="AE34">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF34">
         <v>1.45</v>
@@ -6014,16 +6014,16 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.17</v>
+        <v>2.35</v>
       </c>
       <c r="O35">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P35">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="Q35">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="R35">
         <v>2.2</v>
@@ -6032,7 +6032,7 @@
         <v>1.33</v>
       </c>
       <c r="T35">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="U35">
         <v>2.59</v>
@@ -6053,7 +6053,7 @@
         <v>3.58</v>
       </c>
       <c r="AA35">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AB35">
         <v>1.97</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.15</v>
+        <v>1.62</v>
       </c>
       <c r="O37">
-        <v>3.55</v>
+        <v>3.78</v>
       </c>
       <c r="P37">
-        <v>3.1</v>
+        <v>5.3</v>
       </c>
       <c r="Q37">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="R37">
-        <v>2.43</v>
+        <v>2.29</v>
       </c>
       <c r="S37">
         <v>1.3</v>
       </c>
       <c r="T37">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="U37">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="V37">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="W37">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X37">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y37">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z37">
-        <v>4.75</v>
+        <v>3.9</v>
       </c>
       <c r="AA37">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AB37">
-        <v>2.45</v>
+        <v>2.14</v>
       </c>
       <c r="AC37">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="AD37">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="AE37">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF37">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="AG37">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="AK37">
-        <v>1.65</v>
+        <v>2.12</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.62</v>
+        <v>2.15</v>
       </c>
       <c r="O39">
-        <v>3.78</v>
+        <v>3.55</v>
       </c>
       <c r="P39">
-        <v>5.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q39">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="R39">
-        <v>2.29</v>
+        <v>2.43</v>
       </c>
       <c r="S39">
         <v>1.3</v>
       </c>
       <c r="T39">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="U39">
+        <v>2.38</v>
+      </c>
+      <c r="V39">
+        <v>1.55</v>
+      </c>
+      <c r="W39">
+        <v>1.11</v>
+      </c>
+      <c r="X39">
+        <v>1.01</v>
+      </c>
+      <c r="Y39">
+        <v>1.14</v>
+      </c>
+      <c r="Z39">
+        <v>4.75</v>
+      </c>
+      <c r="AA39">
+        <v>1.6</v>
+      </c>
+      <c r="AB39">
         <v>2.45</v>
       </c>
-      <c r="V39">
-        <v>1.48</v>
-      </c>
-      <c r="W39">
-        <v>1.12</v>
-      </c>
-      <c r="X39">
-        <v>1.04</v>
-      </c>
-      <c r="Y39">
-        <v>1.2</v>
-      </c>
-      <c r="Z39">
-        <v>3.9</v>
-      </c>
-      <c r="AA39">
-        <v>1.69</v>
-      </c>
-      <c r="AB39">
-        <v>2.14</v>
-      </c>
       <c r="AC39">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="AD39">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="AE39">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF39">
-        <v>1.67</v>
+        <v>1.47</v>
       </c>
       <c r="AG39">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="AK39">
-        <v>2.12</v>
+        <v>1.65</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O52">
-        <v>4.9</v>
+        <v>4.75</v>
       </c>
       <c r="P52">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q52">
         <v>5</v>
@@ -8800,7 +8800,7 @@
         <v>2.85</v>
       </c>
       <c r="S52">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T52">
         <v>4.25</v>
@@ -8809,7 +8809,7 @@
         <v>1.91</v>
       </c>
       <c r="V52">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="W52">
         <v>1.22</v>
@@ -8821,7 +8821,7 @@
         <v>1.06</v>
       </c>
       <c r="Z52">
-        <v>6.25</v>
+        <v>6.3</v>
       </c>
       <c r="AA52">
         <v>1.3</v>
@@ -8830,13 +8830,13 @@
         <v>3.1</v>
       </c>
       <c r="AC52">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AD52">
         <v>1.85</v>
       </c>
       <c r="AE52">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AF52">
         <v>1.44</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O56">
-        <v>3.18</v>
+        <v>3.45</v>
       </c>
       <c r="P56">
-        <v>2.16</v>
+        <v>2.33</v>
       </c>
       <c r="Q56">
         <v>3.53</v>
@@ -9452,7 +9452,7 @@
         <v>2.27</v>
       </c>
       <c r="S56">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T56">
         <v>3</v>
@@ -9476,13 +9476,13 @@
         <v>3.5</v>
       </c>
       <c r="AA56">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB56">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AC56">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="AD56">
         <v>1.29</v>
@@ -9491,7 +9491,7 @@
         <v>1.13</v>
       </c>
       <c r="AF56">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG56">
         <v>2.05</v>
@@ -9600,19 +9600,19 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="O57">
         <v>3.3</v>
       </c>
       <c r="P57">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
       </c>
       <c r="R57">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S57">
         <v>1.39</v>
@@ -9621,7 +9621,7 @@
         <v>2.73</v>
       </c>
       <c r="U57">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="V57">
         <v>1.37</v>
@@ -9633,16 +9633,16 @@
         <v>1.05</v>
       </c>
       <c r="Y57">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z57">
         <v>3.25</v>
       </c>
       <c r="AA57">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AB57">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AC57">
         <v>3.2</v>
@@ -9657,7 +9657,7 @@
         <v>1.8</v>
       </c>
       <c r="AG57">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9763,19 +9763,19 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="O58">
         <v>3.6</v>
       </c>
       <c r="P58">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="Q58">
         <v>2.8</v>
       </c>
       <c r="R58">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="S58">
         <v>1.22</v>
@@ -9790,31 +9790,31 @@
         <v>1.6</v>
       </c>
       <c r="W58">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X58">
         <v>1.03</v>
       </c>
       <c r="Y58">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z58">
         <v>5</v>
       </c>
       <c r="AA58">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AB58">
         <v>2.45</v>
       </c>
       <c r="AC58">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AD58">
         <v>1.55</v>
       </c>
       <c r="AE58">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF58">
         <v>1.44</v>
@@ -9836,7 +9836,7 @@
         <v>1.22</v>
       </c>
       <c r="AK58">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10098,55 +10098,55 @@
         <v>0</v>
       </c>
       <c r="Q60">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="R60">
+        <v>3.05</v>
+      </c>
+      <c r="S60">
+        <v>0</v>
+      </c>
+      <c r="T60">
+        <v>0</v>
+      </c>
+      <c r="U60">
+        <v>1.79</v>
+      </c>
+      <c r="V60">
+        <v>1.8</v>
+      </c>
+      <c r="W60">
+        <v>0</v>
+      </c>
+      <c r="X60">
+        <v>0</v>
+      </c>
+      <c r="Y60">
+        <v>0</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+      <c r="AA60">
+        <v>1.3</v>
+      </c>
+      <c r="AB60">
         <v>2.95</v>
       </c>
-      <c r="S60">
-        <v>0</v>
-      </c>
-      <c r="T60">
-        <v>0</v>
-      </c>
-      <c r="U60">
-        <v>1.84</v>
-      </c>
-      <c r="V60">
-        <v>1.75</v>
-      </c>
-      <c r="W60">
-        <v>0</v>
-      </c>
-      <c r="X60">
-        <v>0</v>
-      </c>
-      <c r="Y60">
-        <v>0</v>
-      </c>
-      <c r="Z60">
-        <v>0</v>
-      </c>
-      <c r="AA60">
-        <v>1.34</v>
-      </c>
-      <c r="AB60">
-        <v>2.8</v>
-      </c>
       <c r="AC60">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="AD60">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AE60">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AF60">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AG60">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AK60">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="O61">
         <v>3.5</v>
       </c>
       <c r="P61">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="Q61">
         <v>3.3</v>
@@ -10270,16 +10270,16 @@
         <v>1.29</v>
       </c>
       <c r="T61">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="U61">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="V61">
         <v>1.55</v>
       </c>
       <c r="W61">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X61">
         <v>1.04</v>
@@ -10297,7 +10297,7 @@
         <v>2.19</v>
       </c>
       <c r="AC61">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="AD61">
         <v>1.55</v>
@@ -10587,55 +10587,55 @@
         <v>0</v>
       </c>
       <c r="Q63">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R63">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="S63">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T63">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U63">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V63">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W63">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X63">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y63">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z63">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA63">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AB63">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC63">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AD63">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE63">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF63">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AG63">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK63">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -13533,7 +13533,7 @@
         <v>4.5</v>
       </c>
       <c r="U81">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V81">
         <v>1.83</v>
@@ -13548,7 +13548,7 @@
         <v>1.04</v>
       </c>
       <c r="Z81">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA81">
         <v>1.32</v>
@@ -13557,19 +13557,19 @@
         <v>3</v>
       </c>
       <c r="AC81">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AD81">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AE81">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AF81">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AG81">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AK81">
-        <v>3.04</v>
+        <v>2.82</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13853,10 +13853,10 @@
         <v>2.08</v>
       </c>
       <c r="S83">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T83">
-        <v>2.85</v>
+        <v>3.16</v>
       </c>
       <c r="U83">
         <v>2.71</v>
@@ -13865,7 +13865,7 @@
         <v>1.43</v>
       </c>
       <c r="W83">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X83">
         <v>1.05</v>
@@ -13877,7 +13877,7 @@
         <v>3.6</v>
       </c>
       <c r="AA83">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AB83">
         <v>1.95</v>
@@ -13886,10 +13886,10 @@
         <v>3.1</v>
       </c>
       <c r="AD83">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE83">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF83">
         <v>1.62</v>
@@ -14001,16 +14001,16 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="O84">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P84">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="Q84">
-        <v>2.69</v>
+        <v>2.9</v>
       </c>
       <c r="R84">
         <v>2.05</v>
@@ -14019,16 +14019,16 @@
         <v>1.36</v>
       </c>
       <c r="T84">
-        <v>3.06</v>
+        <v>2.88</v>
       </c>
       <c r="U84">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="V84">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W84">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X84">
         <v>1.05</v>
@@ -14043,10 +14043,10 @@
         <v>1.85</v>
       </c>
       <c r="AB84">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AC84">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AD84">
         <v>1.3</v>
@@ -14499,55 +14499,55 @@
         <v>0</v>
       </c>
       <c r="Q87">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R87">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S87">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T87">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="U87">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V87">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W87">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X87">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y87">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z87">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AA87">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AB87">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AC87">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD87">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE87">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF87">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG87">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK87">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="O98">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="P98">
-        <v>4.35</v>
+        <v>5.2</v>
       </c>
       <c r="Q98">
         <v>1.98</v>
@@ -16316,31 +16316,31 @@
         <v>1.02</v>
       </c>
       <c r="Y98">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="Z98">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AA98">
         <v>1.5</v>
       </c>
       <c r="AB98">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AC98">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AD98">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AE98">
         <v>1.22</v>
       </c>
       <c r="AF98">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AG98">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK98">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -17587,25 +17587,25 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="O106">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P106">
         <v>3.1</v>
       </c>
       <c r="Q106">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="R106">
         <v>2.3</v>
       </c>
       <c r="S106">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T106">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="U106">
         <v>2.25</v>
@@ -17617,7 +17617,7 @@
         <v>1.11</v>
       </c>
       <c r="X106">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y106">
         <v>1.17</v>
@@ -17629,13 +17629,13 @@
         <v>1.57</v>
       </c>
       <c r="AB106">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AC106">
         <v>2.4</v>
       </c>
       <c r="AD106">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AE106">
         <v>1.16</v>
@@ -17913,28 +17913,28 @@
         </is>
       </c>
       <c r="N108">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="O108">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P108">
         <v>2.75</v>
       </c>
       <c r="Q108">
-        <v>2.75</v>
+        <v>3.08</v>
       </c>
       <c r="R108">
         <v>2.2</v>
       </c>
       <c r="S108">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T108">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U108">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="V108">
         <v>1.4</v>
@@ -17949,7 +17949,7 @@
         <v>1.23</v>
       </c>
       <c r="Z108">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="AA108">
         <v>1.88</v>
@@ -17983,7 +17983,7 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AK108">
         <v>1.57</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="G110">
@@ -18360,7 +18360,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G114">
@@ -19007,12 +19007,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O115">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P115">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q115">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R115">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S115">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T115">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U115">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V115">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W115">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X115">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y115">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z115">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA115">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AB115">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC115">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD115">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE115">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF115">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG115">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK115">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19158,7 +19158,7 @@
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>2026-08-08 12:30:00</t>
+          <t>2026-08-08 13:00:00</t>
         </is>
       </c>
     </row>
@@ -19175,22 +19175,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,65 +19217,65 @@
         </is>
       </c>
       <c r="N116">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O116">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P116">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q116">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R116">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S116">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T116">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="U116">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V116">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="W116">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X116">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y116">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="Z116">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA116">
-        <v>1.37</v>
+        <v>1.63</v>
       </c>
       <c r="AB116">
-        <v>2.75</v>
+        <v>2.04</v>
       </c>
       <c r="AC116">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="AD116">
+        <v>1.41</v>
+      </c>
+      <c r="AE116">
+        <v>1.15</v>
+      </c>
+      <c r="AF116">
+        <v>1.88</v>
+      </c>
+      <c r="AG116">
         <v>1.79</v>
       </c>
-      <c r="AE116">
-        <v>1.28</v>
-      </c>
-      <c r="AF116">
-        <v>1.36</v>
-      </c>
-      <c r="AG116">
-        <v>2.88</v>
-      </c>
       <c r="AH116" t="inlineStr">
         <is>
           <t>[]</t>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AK116">
-        <v>1.4</v>
+        <v>2.48</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G117">
@@ -19413,31 +19413,31 @@
         <v>0</v>
       </c>
       <c r="Y117">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z117">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AA117">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB117">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC117">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD117">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE117">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF117">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG117">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK117">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19501,7 +19501,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,64 +19543,64 @@
         </is>
       </c>
       <c r="N118">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O118">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P118">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="Q118">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R118">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S118">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T118">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U118">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V118">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W118">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X118">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y118">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z118">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="AA118">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB118">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC118">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD118">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE118">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF118">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG118">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK118">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19664,22 +19664,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,64 +19706,64 @@
         </is>
       </c>
       <c r="N119">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O119">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P119">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q119">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R119">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S119">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T119">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="U119">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="V119">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W119">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X119">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y119">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z119">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="AA119">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB119">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC119">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD119">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE119">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF119">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG119">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK119">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O120">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P120">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q120">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R120">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="S120">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T120">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U120">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="V120">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W120">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X120">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y120">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z120">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA120">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AB120">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC120">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD120">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE120">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF120">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG120">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK120">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -19990,22 +19990,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,80 +20032,80 @@
         </is>
       </c>
       <c r="N121">
-        <v>2.6</v>
+        <v>5.25</v>
       </c>
       <c r="O121">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="P121">
-        <v>2.75</v>
+        <v>1.47</v>
       </c>
       <c r="Q121">
-        <v>3.36</v>
+        <v>5.5</v>
       </c>
       <c r="R121">
-        <v>1.84</v>
+        <v>2.42</v>
       </c>
       <c r="S121">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="T121">
-        <v>2.54</v>
+        <v>3.5</v>
       </c>
       <c r="U121">
-        <v>3.34</v>
+        <v>2.28</v>
       </c>
       <c r="V121">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="W121">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X121">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y121">
-        <v>1.4</v>
+        <v>1.16</v>
       </c>
       <c r="Z121">
-        <v>2.75</v>
+        <v>4.45</v>
       </c>
       <c r="AA121">
-        <v>2.36</v>
+        <v>1.53</v>
       </c>
       <c r="AB121">
+        <v>2.26</v>
+      </c>
+      <c r="AC121">
+        <v>2.34</v>
+      </c>
+      <c r="AD121">
         <v>1.53</v>
       </c>
-      <c r="AC121">
-        <v>4.3</v>
-      </c>
-      <c r="AD121">
+      <c r="AE121">
+        <v>1.18</v>
+      </c>
+      <c r="AF121">
+        <v>1.66</v>
+      </c>
+      <c r="AG121">
+        <v>2.07</v>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ121">
         <v>1.14</v>
       </c>
-      <c r="AE121">
-        <v>1.05</v>
-      </c>
-      <c r="AF121">
-        <v>2</v>
-      </c>
-      <c r="AG121">
-        <v>1.76</v>
-      </c>
-      <c r="AH121" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI121" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ121">
-        <v>1.36</v>
-      </c>
       <c r="AK121">
-        <v>1.44</v>
+        <v>1.1</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20153,22 +20153,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>5.25</v>
+        <v>3.1</v>
       </c>
       <c r="O122">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="P122">
-        <v>1.47</v>
+        <v>2.05</v>
       </c>
       <c r="Q122">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="R122">
-        <v>2.42</v>
+        <v>2.25</v>
       </c>
       <c r="S122">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T122">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="U122">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="V122">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="W122">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X122">
         <v>1</v>
       </c>
       <c r="Y122">
+        <v>1.22</v>
+      </c>
+      <c r="Z122">
+        <v>3.5</v>
+      </c>
+      <c r="AA122">
+        <v>1.8</v>
+      </c>
+      <c r="AB122">
+        <v>1.9</v>
+      </c>
+      <c r="AC122">
+        <v>3.06</v>
+      </c>
+      <c r="AD122">
+        <v>1.35</v>
+      </c>
+      <c r="AE122">
         <v>1.13</v>
       </c>
-      <c r="Z122">
-        <v>4.5</v>
-      </c>
-      <c r="AA122">
-        <v>1.53</v>
-      </c>
-      <c r="AB122">
-        <v>2.17</v>
-      </c>
-      <c r="AC122">
-        <v>2.34</v>
-      </c>
-      <c r="AD122">
-        <v>1.45</v>
-      </c>
-      <c r="AE122">
-        <v>1.18</v>
-      </c>
       <c r="AF122">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG122">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AK122">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O123">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P123">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q123">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R123">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S123">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T123">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U123">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V123">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W123">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X123">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y123">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z123">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA123">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB123">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC123">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="AD123">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE123">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF123">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG123">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK123">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20479,7 +20479,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,64 +20521,64 @@
         </is>
       </c>
       <c r="N124">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O124">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P124">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q124">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R124">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S124">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T124">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U124">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V124">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W124">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X124">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y124">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z124">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA124">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB124">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC124">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD124">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE124">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF124">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG124">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK124">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20637,12 +20637,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,64 +20684,64 @@
         </is>
       </c>
       <c r="N125">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="O125">
         <v>3.2</v>
       </c>
       <c r="P125">
-        <v>2.25</v>
+        <v>2.91</v>
       </c>
       <c r="Q125">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R125">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="S125">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T125">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U125">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="V125">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W125">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X125">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y125">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z125">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AA125">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB125">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AC125">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD125">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE125">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF125">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG125">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AK125">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20788,7 +20788,7 @@
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>2026-08-08 13:00:00</t>
+          <t>2026-08-08 13:15:00</t>
         </is>
       </c>
     </row>
@@ -20800,27 +20800,27 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,13 +20847,13 @@
         </is>
       </c>
       <c r="N126">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="O126">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P126">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="Q126">
         <v>0</v>
@@ -20886,10 +20886,10 @@
         <v>0</v>
       </c>
       <c r="AA126">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB126">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC126">
         <v>0</v>
@@ -20951,7 +20951,7 @@
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>2026-08-08 13:15:00</t>
+          <t>2026-08-08 13:30:00</t>
         </is>
       </c>
     </row>
@@ -20968,22 +20968,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,13 +21010,13 @@
         </is>
       </c>
       <c r="N127">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O127">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P127">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Q127">
         <v>0</v>
@@ -21131,7 +21131,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,13 +21173,13 @@
         </is>
       </c>
       <c r="N128">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O128">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P128">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="Q128">
         <v>0</v>
@@ -21289,12 +21289,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,64 +21336,64 @@
         </is>
       </c>
       <c r="N129">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O129">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P129">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Q129">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R129">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S129">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T129">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U129">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V129">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W129">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X129">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y129">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z129">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA129">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB129">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC129">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD129">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE129">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF129">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG129">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK129">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21440,7 +21440,7 @@
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>2026-08-08 13:30:00</t>
+          <t>2026-08-08 13:45:00</t>
         </is>
       </c>
     </row>
@@ -21452,27 +21452,27 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,64 +21499,64 @@
         </is>
       </c>
       <c r="N130">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O130">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P130">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="Q130">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R130">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S130">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T130">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U130">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V130">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W130">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X130">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y130">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z130">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA130">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB130">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC130">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AD130">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE130">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF130">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG130">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK130">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21603,7 +21603,7 @@
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>2026-08-08 13:45:00</t>
+          <t>2026-08-08 14:00:00</t>
         </is>
       </c>
     </row>
@@ -21620,22 +21620,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,64 +21662,64 @@
         </is>
       </c>
       <c r="N131">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O131">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P131">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q131">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R131">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S131">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T131">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U131">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V131">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W131">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X131">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y131">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z131">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA131">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB131">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC131">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD131">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE131">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF131">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG131">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK131">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21783,7 +21783,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O132">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P132">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Q132">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R132">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S132">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T132">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U132">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V132">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W132">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X132">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y132">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z132">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA132">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB132">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AC132">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AD132">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE132">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF132">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG132">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK132">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21946,22 +21946,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,13 +21988,13 @@
         </is>
       </c>
       <c r="N133">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O133">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P133">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="Q133">
         <v>0</v>
@@ -22027,10 +22027,10 @@
         <v>0</v>
       </c>
       <c r="AA133">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB133">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC133">
         <v>0</v>
@@ -22109,22 +22109,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="O134">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="P134">
-        <v>3.89</v>
+        <v>3.85</v>
       </c>
       <c r="Q134">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R134">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S134">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T134">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U134">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V134">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W134">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X134">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y134">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z134">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA134">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AB134">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AC134">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD134">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE134">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF134">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG134">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK134">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22267,12 +22267,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>1.85</v>
+        <v>4.4</v>
       </c>
       <c r="O135">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="P135">
-        <v>3.85</v>
+        <v>1.61</v>
       </c>
       <c r="Q135">
-        <v>2.4</v>
+        <v>4.9</v>
       </c>
       <c r="R135">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="S135">
         <v>1.33</v>
       </c>
       <c r="T135">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="U135">
-        <v>2.77</v>
+        <v>2.64</v>
       </c>
       <c r="V135">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="W135">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X135">
         <v>1.05</v>
       </c>
       <c r="Y135">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z135">
-        <v>3.45</v>
+        <v>3.74</v>
       </c>
       <c r="AA135">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AB135">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="AC135">
-        <v>3.08</v>
+        <v>2.76</v>
       </c>
       <c r="AD135">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AE135">
         <v>1.12</v>
       </c>
       <c r="AF135">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG135">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.16</v>
+        <v>2.15</v>
       </c>
       <c r="AK135">
-        <v>1.94</v>
+        <v>1.17</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22418,7 +22418,7 @@
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>2026-08-08 14:00:00</t>
+          <t>2026-08-08 14:30:00</t>
         </is>
       </c>
     </row>
@@ -22435,7 +22435,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>4.4</v>
+        <v>3.69</v>
       </c>
       <c r="O136">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="P136">
-        <v>1.61</v>
+        <v>2.13</v>
       </c>
       <c r="Q136">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R136">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S136">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T136">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="U136">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="V136">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W136">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X136">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y136">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z136">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AA136">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB136">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AC136">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AD136">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE136">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF136">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG136">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AK136">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22608,14 +22608,14 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
+          <t>CSKA Moskva</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
           <t>Rostov</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>CSKA Moskva</t>
-        </is>
-      </c>
       <c r="G137">
         <v>0</v>
       </c>
@@ -22640,64 +22640,64 @@
         </is>
       </c>
       <c r="N137">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="O137">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P137">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q137">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="R137">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S137">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T137">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U137">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V137">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W137">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X137">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y137">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z137">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA137">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB137">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC137">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AD137">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE137">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF137">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG137">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK137">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22756,12 +22756,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G138">
@@ -22803,64 +22803,64 @@
         </is>
       </c>
       <c r="N138">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="O138">
-        <v>0</v>
+        <v>7.05</v>
       </c>
       <c r="P138">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q138">
-        <v>5.9</v>
+        <v>1.44</v>
       </c>
       <c r="R138">
-        <v>2.21</v>
+        <v>2.98</v>
       </c>
       <c r="S138">
-        <v>1.39</v>
+        <v>1.19</v>
       </c>
       <c r="T138">
-        <v>2.89</v>
+        <v>3.8</v>
       </c>
       <c r="U138">
-        <v>2.81</v>
+        <v>1.88</v>
       </c>
       <c r="V138">
-        <v>1.41</v>
+        <v>1.82</v>
       </c>
       <c r="W138">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="X138">
         <v>1</v>
       </c>
       <c r="Y138">
-        <v>1.27</v>
+        <v>1.08</v>
       </c>
       <c r="Z138">
-        <v>3.42</v>
+        <v>6.4</v>
       </c>
       <c r="AA138">
-        <v>1.97</v>
+        <v>1.33</v>
       </c>
       <c r="AB138">
+        <v>3.25</v>
+      </c>
+      <c r="AC138">
+        <v>1.8</v>
+      </c>
+      <c r="AD138">
         <v>1.93</v>
       </c>
-      <c r="AC138">
-        <v>3.16</v>
-      </c>
-      <c r="AD138">
-        <v>1.31</v>
-      </c>
       <c r="AE138">
-        <v>1.07</v>
+        <v>1.44</v>
       </c>
       <c r="AF138">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AG138">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="AK138">
-        <v>1.16</v>
+        <v>7</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -22907,7 +22907,7 @@
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>2026-08-08 14:30:00</t>
+          <t>2026-08-08 15:00:00</t>
         </is>
       </c>
     </row>
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G139">
@@ -22966,64 +22966,64 @@
         </is>
       </c>
       <c r="N139">
+        <v>1.36</v>
+      </c>
+      <c r="O139">
+        <v>4.5</v>
+      </c>
+      <c r="P139">
+        <v>8</v>
+      </c>
+      <c r="Q139">
+        <v>1.8</v>
+      </c>
+      <c r="R139">
+        <v>2.36</v>
+      </c>
+      <c r="S139">
+        <v>1.29</v>
+      </c>
+      <c r="T139">
+        <v>3.12</v>
+      </c>
+      <c r="U139">
+        <v>2.27</v>
+      </c>
+      <c r="V139">
+        <v>1.53</v>
+      </c>
+      <c r="W139">
         <v>1.11</v>
       </c>
-      <c r="O139">
-        <v>7.05</v>
-      </c>
-      <c r="P139">
-        <v>16</v>
-      </c>
-      <c r="Q139">
-        <v>1.44</v>
-      </c>
-      <c r="R139">
-        <v>2.98</v>
-      </c>
-      <c r="S139">
+      <c r="X139">
+        <v>1.04</v>
+      </c>
+      <c r="Y139">
+        <v>1.14</v>
+      </c>
+      <c r="Z139">
+        <v>4.4</v>
+      </c>
+      <c r="AA139">
+        <v>1.52</v>
+      </c>
+      <c r="AB139">
+        <v>2.24</v>
+      </c>
+      <c r="AC139">
+        <v>2.32</v>
+      </c>
+      <c r="AD139">
+        <v>1.45</v>
+      </c>
+      <c r="AE139">
         <v>1.19</v>
       </c>
-      <c r="T139">
-        <v>3.8</v>
-      </c>
-      <c r="U139">
-        <v>1.88</v>
-      </c>
-      <c r="V139">
-        <v>1.82</v>
-      </c>
-      <c r="W139">
-        <v>1.22</v>
-      </c>
-      <c r="X139">
-        <v>1</v>
-      </c>
-      <c r="Y139">
-        <v>1.08</v>
-      </c>
-      <c r="Z139">
-        <v>6.4</v>
-      </c>
-      <c r="AA139">
-        <v>1.33</v>
-      </c>
-      <c r="AB139">
-        <v>3.25</v>
-      </c>
-      <c r="AC139">
-        <v>1.8</v>
-      </c>
-      <c r="AD139">
-        <v>1.93</v>
-      </c>
-      <c r="AE139">
-        <v>1.44</v>
-      </c>
       <c r="AF139">
-        <v>2.05</v>
+        <v>1.79</v>
       </c>
       <c r="AG139">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AK139">
-        <v>7</v>
+        <v>2.8</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23087,22 +23087,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G140">
@@ -23129,64 +23129,64 @@
         </is>
       </c>
       <c r="N140">
-        <v>1.36</v>
+        <v>1.72</v>
       </c>
       <c r="O140">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="P140">
-        <v>8</v>
+        <v>4.6</v>
       </c>
       <c r="Q140">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="R140">
-        <v>2.36</v>
+        <v>2</v>
       </c>
       <c r="S140">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="T140">
-        <v>3.12</v>
+        <v>2.5</v>
       </c>
       <c r="U140">
-        <v>2.27</v>
+        <v>3.58</v>
       </c>
       <c r="V140">
-        <v>1.53</v>
+        <v>1.21</v>
       </c>
       <c r="W140">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X140">
         <v>1.04</v>
       </c>
       <c r="Y140">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="Z140">
-        <v>4.4</v>
+        <v>2.45</v>
       </c>
       <c r="AA140">
-        <v>1.52</v>
+        <v>2.2</v>
       </c>
       <c r="AB140">
-        <v>2.24</v>
+        <v>1.47</v>
       </c>
       <c r="AC140">
-        <v>2.32</v>
+        <v>5.1</v>
       </c>
       <c r="AD140">
-        <v>1.45</v>
+        <v>1.19</v>
       </c>
       <c r="AE140">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="AF140">
-        <v>1.79</v>
+        <v>2.25</v>
       </c>
       <c r="AG140">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AK140">
-        <v>2.8</v>
+        <v>1.91</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G141">
@@ -23292,64 +23292,64 @@
         </is>
       </c>
       <c r="N141">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="O141">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P141">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="Q141">
-        <v>2.46</v>
+        <v>2.65</v>
       </c>
       <c r="R141">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="S141">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="T141">
-        <v>2.33</v>
+        <v>2.24</v>
       </c>
       <c r="U141">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="V141">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W141">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X141">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Y141">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="Z141">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AA141">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="AB141">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AC141">
-        <v>5.05</v>
+        <v>5.35</v>
       </c>
       <c r="AD141">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AE141">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF141">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AG141">
-        <v>1.7</v>
+        <v>1.51</v>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
@@ -23362,10 +23362,10 @@
         </is>
       </c>
       <c r="AJ141">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AK141">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G142">
@@ -23455,64 +23455,64 @@
         </is>
       </c>
       <c r="N142">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="O142">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="P142">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="Q142">
-        <v>2.61</v>
+        <v>2.79</v>
       </c>
       <c r="R142">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="S142">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="T142">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="U142">
-        <v>3.75</v>
+        <v>4.75</v>
       </c>
       <c r="V142">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="W142">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X142">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Y142">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="Z142">
-        <v>2.23</v>
+        <v>1.91</v>
       </c>
       <c r="AA142">
-        <v>2.86</v>
+        <v>3.51</v>
       </c>
       <c r="AB142">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AC142">
-        <v>5.35</v>
+        <v>7.6</v>
       </c>
       <c r="AD142">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AE142">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF142">
-        <v>2.28</v>
+        <v>2.88</v>
       </c>
       <c r="AG142">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
@@ -23525,10 +23525,10 @@
         </is>
       </c>
       <c r="AJ142">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="AK142">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -23576,22 +23576,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,80 +23618,80 @@
         </is>
       </c>
       <c r="N143">
-        <v>1.91</v>
+        <v>3.7</v>
       </c>
       <c r="O143">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="P143">
-        <v>4.4</v>
+        <v>1.73</v>
       </c>
       <c r="Q143">
-        <v>2.62</v>
+        <v>3.92</v>
       </c>
       <c r="R143">
-        <v>1.78</v>
+        <v>2.45</v>
       </c>
       <c r="S143">
-        <v>1.67</v>
+        <v>1.23</v>
       </c>
       <c r="T143">
-        <v>2.1</v>
+        <v>3.52</v>
       </c>
       <c r="U143">
-        <v>4.75</v>
+        <v>2.3</v>
       </c>
       <c r="V143">
+        <v>1.57</v>
+      </c>
+      <c r="W143">
+        <v>1.13</v>
+      </c>
+      <c r="X143">
+        <v>1.03</v>
+      </c>
+      <c r="Y143">
+        <v>1.14</v>
+      </c>
+      <c r="Z143">
+        <v>5.05</v>
+      </c>
+      <c r="AA143">
+        <v>1.53</v>
+      </c>
+      <c r="AB143">
+        <v>2.38</v>
+      </c>
+      <c r="AC143">
+        <v>2.21</v>
+      </c>
+      <c r="AD143">
+        <v>1.53</v>
+      </c>
+      <c r="AE143">
+        <v>1.23</v>
+      </c>
+      <c r="AF143">
+        <v>1.57</v>
+      </c>
+      <c r="AG143">
+        <v>2.4</v>
+      </c>
+      <c r="AH143" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI143" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ143">
         <v>1.17</v>
       </c>
-      <c r="W143">
-        <v>1.02</v>
-      </c>
-      <c r="X143">
-        <v>1.18</v>
-      </c>
-      <c r="Y143">
-        <v>1.8</v>
-      </c>
-      <c r="Z143">
-        <v>1.93</v>
-      </c>
-      <c r="AA143">
-        <v>3.51</v>
-      </c>
-      <c r="AB143">
-        <v>1.24</v>
-      </c>
-      <c r="AC143">
-        <v>7.6</v>
-      </c>
-      <c r="AD143">
-        <v>1.06</v>
-      </c>
-      <c r="AE143">
-        <v>1.01</v>
-      </c>
-      <c r="AF143">
-        <v>2.88</v>
-      </c>
-      <c r="AG143">
-        <v>1.36</v>
-      </c>
-      <c r="AH143" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI143" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ143">
-        <v>1.36</v>
-      </c>
       <c r="AK143">
-        <v>1.75</v>
+        <v>1.15</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23739,7 +23739,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,64 +23781,64 @@
         </is>
       </c>
       <c r="N144">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O144">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P144">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q144">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R144">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S144">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="T144">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="U144">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V144">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W144">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X144">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y144">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z144">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AA144">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB144">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AC144">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AD144">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE144">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AF144">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG144">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK144">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -28514,7 +28514,7 @@
         <v>3.3</v>
       </c>
       <c r="P173">
-        <v>2.96</v>
+        <v>3.03</v>
       </c>
       <c r="Q173">
         <v>2.9</v>
@@ -28535,7 +28535,7 @@
         <v>1.4</v>
       </c>
       <c r="W173">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X173">
         <v>1.07</v>
@@ -28553,7 +28553,7 @@
         <v>1.75</v>
       </c>
       <c r="AC173">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AD173">
         <v>1.27</v>
@@ -28562,7 +28562,7 @@
         <v>1.08</v>
       </c>
       <c r="AF173">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AG173">
         <v>1.85</v>
@@ -28680,55 +28680,55 @@
         <v>3</v>
       </c>
       <c r="Q174">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="R174">
         <v>2.2</v>
       </c>
       <c r="S174">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T174">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U174">
-        <v>2.8</v>
+        <v>2.57</v>
       </c>
       <c r="V174">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W174">
         <v>1.07</v>
       </c>
       <c r="X174">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y174">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z174">
         <v>3.4</v>
       </c>
       <c r="AA174">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AB174">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AC174">
         <v>2.92</v>
       </c>
       <c r="AD174">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AE174">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF174">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AG174">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AH174" t="inlineStr">
         <is>
@@ -28741,10 +28741,10 @@
         </is>
       </c>
       <c r="AJ174">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK174">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AL174">
         <v>0</v>
@@ -29006,55 +29006,55 @@
         <v>3.7</v>
       </c>
       <c r="Q176">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R176">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S176">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T176">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U176">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V176">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W176">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X176">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y176">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="Z176">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AA176">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AB176">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC176">
-        <v>0</v>
+        <v>5.87</v>
       </c>
       <c r="AD176">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE176">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF176">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AG176">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK176">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -30310,55 +30310,55 @@
         <v>0</v>
       </c>
       <c r="Q184">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R184">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S184">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T184">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U184">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V184">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W184">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X184">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y184">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z184">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA184">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB184">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AC184">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD184">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE184">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF184">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG184">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH184" t="inlineStr">
         <is>
@@ -30371,10 +30371,10 @@
         </is>
       </c>
       <c r="AJ184">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK184">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL184">
         <v>0</v>
@@ -30464,10 +30464,10 @@
         </is>
       </c>
       <c r="N185">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="O185">
-        <v>3.4</v>
+        <v>3.78</v>
       </c>
       <c r="P185">
         <v>2.73</v>
@@ -31116,22 +31116,22 @@
         </is>
       </c>
       <c r="N189">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="O189">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="P189">
-        <v>2.57</v>
+        <v>2.33</v>
       </c>
       <c r="Q189">
-        <v>3.28</v>
+        <v>3.7</v>
       </c>
       <c r="R189">
         <v>2.05</v>
       </c>
       <c r="S189">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T189">
         <v>2.56</v>
@@ -31143,19 +31143,19 @@
         <v>1.33</v>
       </c>
       <c r="W189">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X189">
         <v>1.03</v>
       </c>
       <c r="Y189">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z189">
         <v>3.35</v>
       </c>
       <c r="AA189">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AB189">
         <v>1.7</v>
@@ -31164,10 +31164,10 @@
         <v>3.62</v>
       </c>
       <c r="AD189">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE189">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF189">
         <v>1.8</v>
@@ -31279,22 +31279,22 @@
         </is>
       </c>
       <c r="N190">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="O190">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P190">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="Q190">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="R190">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S190">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T190">
         <v>3.1</v>
@@ -31309,34 +31309,34 @@
         <v>1.1</v>
       </c>
       <c r="X190">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y190">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z190">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
       <c r="AA190">
         <v>1.73</v>
       </c>
       <c r="AB190">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AC190">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AD190">
         <v>1.36</v>
       </c>
       <c r="AE190">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF190">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG190">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AH190" t="inlineStr">
         <is>
@@ -31349,7 +31349,7 @@
         </is>
       </c>
       <c r="AJ190">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AK190">
         <v>2.38</v>
@@ -31451,28 +31451,28 @@
         <v>0</v>
       </c>
       <c r="Q191">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="R191">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="S191">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T191">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="U191">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="V191">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W191">
         <v>1.06</v>
       </c>
       <c r="X191">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y191">
         <v>1.36</v>
@@ -31484,22 +31484,22 @@
         <v>2.15</v>
       </c>
       <c r="AB191">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AC191">
-        <v>3.8</v>
+        <v>3.86</v>
       </c>
       <c r="AD191">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE191">
         <v>1.07</v>
       </c>
       <c r="AF191">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG191">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AH191" t="inlineStr">
         <is>
@@ -31512,10 +31512,10 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK191">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -32103,55 +32103,55 @@
         <v>0</v>
       </c>
       <c r="Q195">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R195">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S195">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T195">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U195">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="V195">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W195">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X195">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y195">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z195">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA195">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB195">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC195">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD195">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE195">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF195">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG195">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK195">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -33075,7 +33075,7 @@
         <v>1.64</v>
       </c>
       <c r="O201">
-        <v>3.86</v>
+        <v>3.9</v>
       </c>
       <c r="P201">
         <v>5.25</v>
@@ -33724,16 +33724,16 @@
         </is>
       </c>
       <c r="N205">
-        <v>2.43</v>
+        <v>2.61</v>
       </c>
       <c r="O205">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="P205">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="Q205">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="R205">
         <v>1.95</v>
@@ -33757,19 +33757,19 @@
         <v>1.03</v>
       </c>
       <c r="Y205">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z205">
         <v>3.4</v>
       </c>
       <c r="AA205">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AB205">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AC205">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AD205">
         <v>1.29</v>
@@ -33778,10 +33778,10 @@
         <v>1.07</v>
       </c>
       <c r="AF205">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG205">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AH205" t="inlineStr">
         <is>
@@ -34050,7 +34050,7 @@
         </is>
       </c>
       <c r="N207">
-        <v>4.97</v>
+        <v>4.75</v>
       </c>
       <c r="O207">
         <v>4</v>
@@ -34213,37 +34213,37 @@
         </is>
       </c>
       <c r="N208">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="O208">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P208">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="Q208">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="R208">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S208">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T208">
-        <v>2.76</v>
+        <v>2.31</v>
       </c>
       <c r="U208">
-        <v>3.14</v>
+        <v>3.02</v>
       </c>
       <c r="V208">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W208">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X208">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y208">
         <v>1.33</v>
@@ -34252,16 +34252,16 @@
         <v>2.83</v>
       </c>
       <c r="AA208">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AB208">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC208">
         <v>3.7</v>
       </c>
       <c r="AD208">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE208">
         <v>1.05</v>
@@ -34270,7 +34270,7 @@
         <v>1.85</v>
       </c>
       <c r="AG208">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AH208" t="inlineStr">
         <is>
@@ -34286,7 +34286,7 @@
         <v>1.26</v>
       </c>
       <c r="AK208">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="AL208">
         <v>0</v>

--- a/jogos_2026-08-08.xlsx
+++ b/jogos_2026-08-08.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="O6">
-        <v>3.48</v>
+        <v>3.7</v>
       </c>
       <c r="P6">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="Q6">
-        <v>3</v>
+        <v>2.54</v>
       </c>
       <c r="R6">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="S6">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T6">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="U6">
-        <v>2.46</v>
+        <v>2.12</v>
       </c>
       <c r="V6">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="W6">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X6">
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="Z6">
-        <v>4</v>
+        <v>4.65</v>
       </c>
       <c r="AA6">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AB6">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="AC6">
-        <v>2.66</v>
+        <v>2.25</v>
       </c>
       <c r="AD6">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
       <c r="AE6">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AF6">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AG6">
-        <v>2.28</v>
+        <v>2.39</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AK6">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,80 +1450,80 @@
         </is>
       </c>
       <c r="N7">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O7">
-        <v>3.7</v>
+        <v>3.48</v>
       </c>
       <c r="P7">
+        <v>2.95</v>
+      </c>
+      <c r="Q7">
+        <v>3</v>
+      </c>
+      <c r="R7">
+        <v>2.16</v>
+      </c>
+      <c r="S7">
+        <v>1.29</v>
+      </c>
+      <c r="T7">
         <v>3.25</v>
       </c>
-      <c r="Q7">
-        <v>2.54</v>
-      </c>
-      <c r="R7">
-        <v>2.23</v>
-      </c>
-      <c r="S7">
-        <v>1.25</v>
-      </c>
-      <c r="T7">
-        <v>3.34</v>
-      </c>
       <c r="U7">
-        <v>2.12</v>
+        <v>2.46</v>
       </c>
       <c r="V7">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="W7">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X7">
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="Z7">
-        <v>4.65</v>
+        <v>4</v>
       </c>
       <c r="AA7">
+        <v>1.7</v>
+      </c>
+      <c r="AB7">
+        <v>2.06</v>
+      </c>
+      <c r="AC7">
+        <v>2.66</v>
+      </c>
+      <c r="AD7">
+        <v>1.37</v>
+      </c>
+      <c r="AE7">
+        <v>1.11</v>
+      </c>
+      <c r="AF7">
+        <v>1.53</v>
+      </c>
+      <c r="AG7">
+        <v>2.28</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
+        <v>1.23</v>
+      </c>
+      <c r="AK7">
         <v>1.5</v>
-      </c>
-      <c r="AB7">
-        <v>2.3</v>
-      </c>
-      <c r="AC7">
-        <v>2.25</v>
-      </c>
-      <c r="AD7">
-        <v>1.52</v>
-      </c>
-      <c r="AE7">
-        <v>1.19</v>
-      </c>
-      <c r="AF7">
-        <v>1.47</v>
-      </c>
-      <c r="AG7">
-        <v>2.39</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7">
-        <v>1.28</v>
-      </c>
-      <c r="AK7">
-        <v>1.67</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.67</v>
+        <v>1.78</v>
       </c>
       <c r="O29">
-        <v>3.22</v>
+        <v>3.37</v>
       </c>
       <c r="P29">
-        <v>2.58</v>
+        <v>4.9</v>
       </c>
       <c r="Q29">
-        <v>3.32</v>
+        <v>2.36</v>
       </c>
       <c r="R29">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="S29">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T29">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U29">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="V29">
         <v>1.36</v>
       </c>
       <c r="W29">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X29">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y29">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z29">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="AA29">
         <v>2</v>
       </c>
       <c r="AB29">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC29">
-        <v>3.47</v>
+        <v>3.55</v>
       </c>
       <c r="AD29">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AE29">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF29">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AG29">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AK29">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.78</v>
+        <v>2.67</v>
       </c>
       <c r="O30">
-        <v>3.37</v>
+        <v>3.22</v>
       </c>
       <c r="P30">
-        <v>4.9</v>
+        <v>2.58</v>
       </c>
       <c r="Q30">
-        <v>2.36</v>
+        <v>3.32</v>
       </c>
       <c r="R30">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="S30">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T30">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U30">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="V30">
         <v>1.36</v>
       </c>
       <c r="W30">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X30">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z30">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="AA30">
         <v>2</v>
       </c>
       <c r="AB30">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC30">
-        <v>3.55</v>
+        <v>3.47</v>
       </c>
       <c r="AD30">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE30">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF30">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AG30">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="AK30">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.71</v>
+        <v>2.15</v>
       </c>
       <c r="O38">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="P38">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="Q38">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="R38">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="S38">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T38">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="U38">
         <v>2.38</v>
       </c>
       <c r="V38">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W38">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X38">
         <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z38">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="AA38">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB38">
-        <v>2.08</v>
+        <v>2.45</v>
       </c>
       <c r="AC38">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AD38">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AE38">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF38">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AG38">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="AK38">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
+        <v>1.71</v>
+      </c>
+      <c r="O39">
+        <v>3.85</v>
+      </c>
+      <c r="P39">
+        <v>4.5</v>
+      </c>
+      <c r="Q39">
         <v>2.15</v>
       </c>
-      <c r="O39">
-        <v>3.55</v>
-      </c>
-      <c r="P39">
-        <v>3.1</v>
-      </c>
-      <c r="Q39">
-        <v>2.63</v>
-      </c>
       <c r="R39">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="S39">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T39">
-        <v>3.22</v>
+        <v>3.6</v>
       </c>
       <c r="U39">
         <v>2.38</v>
       </c>
       <c r="V39">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W39">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X39">
         <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z39">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="AA39">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB39">
-        <v>2.45</v>
+        <v>2.08</v>
       </c>
       <c r="AC39">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="AD39">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AE39">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF39">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AG39">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="AK39">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -15627,7 +15627,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N94">

--- a/jogos_2026-08-08.xlsx
+++ b/jogos_2026-08-08.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,80 +1287,80 @@
         </is>
       </c>
       <c r="N6">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O6">
-        <v>3.7</v>
+        <v>3.48</v>
       </c>
       <c r="P6">
+        <v>2.95</v>
+      </c>
+      <c r="Q6">
+        <v>3</v>
+      </c>
+      <c r="R6">
+        <v>2.16</v>
+      </c>
+      <c r="S6">
+        <v>1.29</v>
+      </c>
+      <c r="T6">
         <v>3.25</v>
       </c>
-      <c r="Q6">
-        <v>2.54</v>
-      </c>
-      <c r="R6">
-        <v>2.23</v>
-      </c>
-      <c r="S6">
-        <v>1.25</v>
-      </c>
-      <c r="T6">
-        <v>3.34</v>
-      </c>
       <c r="U6">
-        <v>2.12</v>
+        <v>2.46</v>
       </c>
       <c r="V6">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="W6">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="Z6">
-        <v>4.65</v>
+        <v>4</v>
       </c>
       <c r="AA6">
+        <v>1.7</v>
+      </c>
+      <c r="AB6">
+        <v>2.06</v>
+      </c>
+      <c r="AC6">
+        <v>2.66</v>
+      </c>
+      <c r="AD6">
+        <v>1.37</v>
+      </c>
+      <c r="AE6">
+        <v>1.11</v>
+      </c>
+      <c r="AF6">
+        <v>1.53</v>
+      </c>
+      <c r="AG6">
+        <v>2.28</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6">
+        <v>1.23</v>
+      </c>
+      <c r="AK6">
         <v>1.5</v>
-      </c>
-      <c r="AB6">
-        <v>2.3</v>
-      </c>
-      <c r="AC6">
-        <v>2.25</v>
-      </c>
-      <c r="AD6">
-        <v>1.52</v>
-      </c>
-      <c r="AE6">
-        <v>1.19</v>
-      </c>
-      <c r="AF6">
-        <v>1.47</v>
-      </c>
-      <c r="AG6">
-        <v>2.39</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6">
-        <v>1.28</v>
-      </c>
-      <c r="AK6">
-        <v>1.67</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="O7">
-        <v>3.48</v>
+        <v>3.7</v>
       </c>
       <c r="P7">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="Q7">
-        <v>3</v>
+        <v>2.54</v>
       </c>
       <c r="R7">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="S7">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T7">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="U7">
-        <v>2.46</v>
+        <v>2.12</v>
       </c>
       <c r="V7">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="W7">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X7">
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="Z7">
-        <v>4</v>
+        <v>4.65</v>
       </c>
       <c r="AA7">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AB7">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="AC7">
-        <v>2.66</v>
+        <v>2.25</v>
       </c>
       <c r="AD7">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
       <c r="AE7">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AF7">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AG7">
-        <v>2.28</v>
+        <v>2.39</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AK7">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="O37">
-        <v>3.78</v>
+        <v>3.85</v>
       </c>
       <c r="P37">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="Q37">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="R37">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="S37">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T37">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U37">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="V37">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W37">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X37">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
         <v>1.2</v>
       </c>
       <c r="Z37">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="AA37">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="AB37">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="AC37">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AD37">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE37">
         <v>1.13</v>
       </c>
       <c r="AF37">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG37">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK37">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="O39">
-        <v>3.85</v>
+        <v>3.78</v>
       </c>
       <c r="P39">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="Q39">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="R39">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="S39">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T39">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U39">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="V39">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W39">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y39">
         <v>1.2</v>
       </c>
       <c r="Z39">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="AA39">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="AB39">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AC39">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AD39">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AE39">
         <v>1.13</v>
       </c>
       <c r="AF39">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AG39">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK39">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AL39">
         <v>0</v>

--- a/jogos_2026-08-08.xlsx
+++ b/jogos_2026-08-08.xlsx
@@ -641,7 +641,7 @@
         <v>3.45</v>
       </c>
       <c r="P2">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -961,43 +961,43 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="O4">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="P4">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA4">
         <v>1.5</v>
@@ -1006,19 +1006,19 @@
         <v>2.5</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,25 +1124,25 @@
         </is>
       </c>
       <c r="N5">
-        <v>4.27</v>
+        <v>4</v>
       </c>
       <c r="O5">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P5">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="Q5">
-        <v>5.02</v>
+        <v>5.18</v>
       </c>
       <c r="R5">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="S5">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="T5">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U5">
         <v>2.75</v>
@@ -1151,37 +1151,37 @@
         <v>1.4</v>
       </c>
       <c r="W5">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z5">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA5">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AB5">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AC5">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AD5">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE5">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF5">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG5">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="O6">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="P6">
-        <v>2.95</v>
+        <v>2.5</v>
       </c>
       <c r="Q6">
         <v>3</v>
       </c>
       <c r="R6">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="S6">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T6">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="U6">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="V6">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W6">
         <v>1.11</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y6">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z6">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AA6">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB6">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AC6">
-        <v>2.66</v>
+        <v>2.82</v>
       </c>
       <c r="AD6">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AE6">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF6">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AG6">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK6">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1459,13 +1459,13 @@
         <v>3.25</v>
       </c>
       <c r="Q7">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="R7">
-        <v>2.23</v>
+        <v>2.43</v>
       </c>
       <c r="S7">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T7">
         <v>3.34</v>
@@ -1474,31 +1474,31 @@
         <v>2.12</v>
       </c>
       <c r="V7">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="W7">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X7">
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="Z7">
         <v>4.65</v>
       </c>
       <c r="AA7">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AB7">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="AC7">
         <v>2.25</v>
       </c>
       <c r="AD7">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AE7">
         <v>1.19</v>
@@ -1507,7 +1507,7 @@
         <v>1.47</v>
       </c>
       <c r="AG7">
-        <v>2.39</v>
+        <v>2.48</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK7">
         <v>1.67</v>
@@ -1613,49 +1613,49 @@
         </is>
       </c>
       <c r="N8">
+        <v>5.9</v>
+      </c>
+      <c r="O8">
+        <v>4.35</v>
+      </c>
+      <c r="P8">
+        <v>1.39</v>
+      </c>
+      <c r="Q8">
         <v>6</v>
-      </c>
-      <c r="O8">
-        <v>5</v>
-      </c>
-      <c r="P8">
-        <v>1.33</v>
-      </c>
-      <c r="Q8">
-        <v>5.55</v>
       </c>
       <c r="R8">
         <v>2.5</v>
       </c>
       <c r="S8">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="T8">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U8">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="V8">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="W8">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X8">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
         <v>1.13</v>
       </c>
       <c r="Z8">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="AA8">
         <v>1.44</v>
       </c>
       <c r="AB8">
-        <v>2.43</v>
+        <v>2.28</v>
       </c>
       <c r="AC8">
         <v>2.12</v>
@@ -1664,13 +1664,13 @@
         <v>1.58</v>
       </c>
       <c r="AE8">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AF8">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="AG8">
-        <v>2.22</v>
+        <v>1.95</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AK8">
         <v>1.07</v>
@@ -1809,16 +1809,16 @@
         <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z9">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="AA9">
         <v>2.03</v>
       </c>
       <c r="AB9">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AC9">
         <v>3.28</v>
@@ -1849,7 +1849,7 @@
         <v>1.08</v>
       </c>
       <c r="AK9">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="O10">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="P10">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA10">
         <v>1.72</v>
       </c>
       <c r="AB10">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -3086,37 +3086,37 @@
         <v>3.15</v>
       </c>
       <c r="P17">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="Q17">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="R17">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S17">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="T17">
-        <v>2.44</v>
+        <v>2.75</v>
       </c>
       <c r="U17">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="V17">
+        <v>1.35</v>
+      </c>
+      <c r="W17">
+        <v>1.07</v>
+      </c>
+      <c r="X17">
+        <v>1.07</v>
+      </c>
+      <c r="Y17">
         <v>1.33</v>
       </c>
-      <c r="W17">
-        <v>1.01</v>
-      </c>
-      <c r="X17">
-        <v>1.06</v>
-      </c>
-      <c r="Y17">
-        <v>1.36</v>
-      </c>
       <c r="Z17">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="AA17">
         <v>2.15</v>
@@ -3125,19 +3125,19 @@
         <v>1.66</v>
       </c>
       <c r="AC17">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AD17">
         <v>1.22</v>
       </c>
       <c r="AE17">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF17">
         <v>1.85</v>
       </c>
       <c r="AG17">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3406,25 +3406,25 @@
         </is>
       </c>
       <c r="N19">
-        <v>4.15</v>
+        <v>4.35</v>
       </c>
       <c r="O19">
-        <v>3.15</v>
+        <v>2.87</v>
       </c>
       <c r="P19">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="Q19">
-        <v>4.75</v>
+        <v>5.48</v>
       </c>
       <c r="R19">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="S19">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="T19">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="U19">
         <v>3.6</v>
@@ -3436,34 +3436,34 @@
         <v>1.01</v>
       </c>
       <c r="X19">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y19">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Z19">
         <v>2.5</v>
       </c>
       <c r="AA19">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="AB19">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AC19">
-        <v>4.7</v>
+        <v>4.55</v>
       </c>
       <c r="AD19">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE19">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AF19">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AG19">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.3</v>
+        <v>1.85</v>
       </c>
       <c r="AK19">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>2.11</v>
       </c>
       <c r="O20">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="P20">
         <v>3.4</v>
@@ -3599,7 +3599,7 @@
         <v>1.1</v>
       </c>
       <c r="X20">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y20">
         <v>1.25</v>
@@ -3611,7 +3611,7 @@
         <v>1.83</v>
       </c>
       <c r="AB20">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AC20">
         <v>3.2</v>
@@ -3620,7 +3620,7 @@
         <v>1.33</v>
       </c>
       <c r="AE20">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF20">
         <v>1.7</v>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="O21">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P21">
         <v>2.85</v>
@@ -3744,37 +3744,37 @@
         <v>3.12</v>
       </c>
       <c r="R21">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="S21">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="T21">
         <v>2.55</v>
       </c>
       <c r="U21">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="V21">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W21">
         <v>1</v>
       </c>
       <c r="X21">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="Y21">
         <v>1.36</v>
       </c>
       <c r="Z21">
-        <v>2.62</v>
+        <v>2.89</v>
       </c>
       <c r="AA21">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="AB21">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC21">
         <v>4.39</v>
@@ -3789,7 +3789,7 @@
         <v>1.9</v>
       </c>
       <c r="AG21">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AK21">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,25 +3895,25 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="O22">
-        <v>3.98</v>
+        <v>3.8</v>
       </c>
       <c r="P22">
         <v>5.7</v>
       </c>
       <c r="Q22">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R22">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="S22">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="T22">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="U22">
         <v>2.81</v>
@@ -3922,37 +3922,37 @@
         <v>1.38</v>
       </c>
       <c r="W22">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X22">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y22">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z22">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="AA22">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="AB22">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC22">
-        <v>3.5</v>
+        <v>3.18</v>
       </c>
       <c r="AD22">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE22">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF22">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AG22">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK22">
-        <v>2.22</v>
+        <v>2.37</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4073,10 +4073,10 @@
         <v>2.25</v>
       </c>
       <c r="S23">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T23">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="U23">
         <v>2.62</v>
@@ -4091,19 +4091,19 @@
         <v>1</v>
       </c>
       <c r="Y23">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z23">
-        <v>3.82</v>
+        <v>3.6</v>
       </c>
       <c r="AA23">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AB23">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AC23">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="AD23">
         <v>1.37</v>
@@ -4112,10 +4112,10 @@
         <v>1.14</v>
       </c>
       <c r="AF23">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG23">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK23">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4224,10 +4224,10 @@
         <v>1.5</v>
       </c>
       <c r="O24">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="P24">
-        <v>6.25</v>
+        <v>6.35</v>
       </c>
       <c r="Q24">
         <v>2</v>
@@ -4242,7 +4242,7 @@
         <v>3.2</v>
       </c>
       <c r="U24">
-        <v>2.48</v>
+        <v>2.59</v>
       </c>
       <c r="V24">
         <v>1.44</v>
@@ -4260,16 +4260,16 @@
         <v>3.79</v>
       </c>
       <c r="AA24">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AB24">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AC24">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="AD24">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE24">
         <v>1.13</v>
@@ -4278,7 +4278,7 @@
         <v>1.89</v>
       </c>
       <c r="AG24">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="O26">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P26">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="Q26">
         <v>3.61</v>
@@ -4562,10 +4562,10 @@
         <v>2.12</v>
       </c>
       <c r="S26">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T26">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="U26">
         <v>2.72</v>
@@ -4604,7 +4604,7 @@
         <v>1.67</v>
       </c>
       <c r="AG26">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4710,43 +4710,43 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="O27">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P27">
-        <v>2.37</v>
+        <v>2.31</v>
       </c>
       <c r="Q27">
         <v>3.25</v>
       </c>
       <c r="R27">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S27">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T27">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U27">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="V27">
         <v>1.37</v>
       </c>
       <c r="W27">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X27">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
         <v>1.3</v>
       </c>
       <c r="Z27">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="AA27">
         <v>1.9</v>
@@ -4755,10 +4755,10 @@
         <v>1.87</v>
       </c>
       <c r="AC27">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AD27">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AE27">
         <v>1.06</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="O28">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="P28">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="Q28">
         <v>2.38</v>
@@ -4888,10 +4888,10 @@
         <v>2</v>
       </c>
       <c r="S28">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T28">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="U28">
         <v>3.25</v>
@@ -4903,13 +4903,13 @@
         <v>1.06</v>
       </c>
       <c r="X28">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y28">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="Z28">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="AA28">
         <v>2.3</v>
@@ -5036,19 +5036,19 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="O29">
-        <v>3.37</v>
+        <v>3.6</v>
       </c>
       <c r="P29">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="Q29">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="R29">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="S29">
         <v>1.41</v>
@@ -5069,31 +5069,31 @@
         <v>1.02</v>
       </c>
       <c r="Y29">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z29">
-        <v>3.28</v>
+        <v>3.12</v>
       </c>
       <c r="AA29">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AB29">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AC29">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="AD29">
         <v>1.28</v>
       </c>
       <c r="AE29">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF29">
         <v>1.85</v>
       </c>
       <c r="AG29">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK29">
         <v>2.1</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.67</v>
+        <v>2.48</v>
       </c>
       <c r="O30">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="P30">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="Q30">
         <v>3.32</v>
@@ -5226,16 +5226,16 @@
         <v>1.36</v>
       </c>
       <c r="W30">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X30">
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z30">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="AA30">
         <v>2</v>
@@ -5253,10 +5253,10 @@
         <v>1.1</v>
       </c>
       <c r="AF30">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AG30">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5362,19 +5362,19 @@
         </is>
       </c>
       <c r="N31">
-        <v>3.61</v>
+        <v>4</v>
       </c>
       <c r="O31">
-        <v>4.02</v>
+        <v>3.9</v>
       </c>
       <c r="P31">
-        <v>1.92</v>
+        <v>1.66</v>
       </c>
       <c r="Q31">
-        <v>4.33</v>
+        <v>4.45</v>
       </c>
       <c r="R31">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="S31">
         <v>1.22</v>
@@ -5395,22 +5395,22 @@
         <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Z31">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="AA31">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AB31">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AC31">
         <v>2.2</v>
       </c>
       <c r="AD31">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="AE31">
         <v>1.27</v>
@@ -5419,7 +5419,7 @@
         <v>1.47</v>
       </c>
       <c r="AG31">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5688,16 +5688,16 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="O33">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="P33">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="Q33">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="R33">
         <v>2.2</v>
@@ -5706,16 +5706,16 @@
         <v>1.34</v>
       </c>
       <c r="T33">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="U33">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="V33">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="W33">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X33">
         <v>1.05</v>
@@ -5739,7 +5739,7 @@
         <v>1.27</v>
       </c>
       <c r="AE33">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF33">
         <v>1.77</v>
@@ -5851,16 +5851,16 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.11</v>
+        <v>1.98</v>
       </c>
       <c r="O34">
-        <v>3.62</v>
+        <v>3.25</v>
       </c>
       <c r="P34">
-        <v>3.09</v>
+        <v>2.73</v>
       </c>
       <c r="Q34">
-        <v>2.44</v>
+        <v>2.63</v>
       </c>
       <c r="R34">
         <v>2.38</v>
@@ -5869,7 +5869,7 @@
         <v>1.3</v>
       </c>
       <c r="T34">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="U34">
         <v>2.3</v>
@@ -5902,10 +5902,10 @@
         <v>1.53</v>
       </c>
       <c r="AE34">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF34">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG34">
         <v>2.25</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AK34">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,16 +6014,16 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="O35">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P35">
-        <v>2.83</v>
+        <v>2.6</v>
       </c>
       <c r="Q35">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="R35">
         <v>2.2</v>
@@ -6053,7 +6053,7 @@
         <v>3.58</v>
       </c>
       <c r="AA35">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="AB35">
         <v>1.97</v>
@@ -6068,7 +6068,7 @@
         <v>1.13</v>
       </c>
       <c r="AF35">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG35">
         <v>2.15</v>
@@ -6177,25 +6177,25 @@
         </is>
       </c>
       <c r="N36">
+        <v>2.5</v>
+      </c>
+      <c r="O36">
+        <v>3.8</v>
+      </c>
+      <c r="P36">
         <v>2.35</v>
-      </c>
-      <c r="O36">
-        <v>3.58</v>
-      </c>
-      <c r="P36">
-        <v>2.72</v>
       </c>
       <c r="Q36">
         <v>3</v>
       </c>
       <c r="R36">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="S36">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T36">
-        <v>3.66</v>
+        <v>3.58</v>
       </c>
       <c r="U36">
         <v>2.2</v>
@@ -6222,13 +6222,13 @@
         <v>2.45</v>
       </c>
       <c r="AC36">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="AD36">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AE36">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF36">
         <v>1.42</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="AK36">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6343,10 +6343,10 @@
         <v>1.71</v>
       </c>
       <c r="O37">
+        <v>3.7</v>
+      </c>
+      <c r="P37">
         <v>3.85</v>
-      </c>
-      <c r="P37">
-        <v>4.5</v>
       </c>
       <c r="Q37">
         <v>2.15</v>
@@ -6355,10 +6355,10 @@
         <v>2.38</v>
       </c>
       <c r="S37">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T37">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U37">
         <v>2.38</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O38">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="P38">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q38">
         <v>2.63</v>
@@ -6518,25 +6518,25 @@
         <v>2.43</v>
       </c>
       <c r="S38">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T38">
-        <v>3.22</v>
+        <v>3.8</v>
       </c>
       <c r="U38">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="V38">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W38">
         <v>1.11</v>
       </c>
       <c r="X38">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y38">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z38">
         <v>4.75</v>
@@ -6548,19 +6548,19 @@
         <v>2.45</v>
       </c>
       <c r="AC38">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="AD38">
         <v>1.55</v>
       </c>
       <c r="AE38">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF38">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG38">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AK38">
         <v>1.65</v>
@@ -6669,10 +6669,10 @@
         <v>1.62</v>
       </c>
       <c r="O39">
-        <v>3.78</v>
+        <v>3.82</v>
       </c>
       <c r="P39">
-        <v>5.3</v>
+        <v>5.31</v>
       </c>
       <c r="Q39">
         <v>2.1</v>
@@ -6681,10 +6681,10 @@
         <v>2.29</v>
       </c>
       <c r="S39">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T39">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="U39">
         <v>2.45</v>
@@ -6708,7 +6708,7 @@
         <v>1.69</v>
       </c>
       <c r="AB39">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="AC39">
         <v>2.63</v>
@@ -6717,7 +6717,7 @@
         <v>1.41</v>
       </c>
       <c r="AE39">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF39">
         <v>1.67</v>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK39">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="O40">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="P40">
+        <v>2.35</v>
+      </c>
+      <c r="Q40">
+        <v>3.3</v>
+      </c>
+      <c r="R40">
+        <v>2.05</v>
+      </c>
+      <c r="S40">
+        <v>1.43</v>
+      </c>
+      <c r="T40">
+        <v>2.66</v>
+      </c>
+      <c r="U40">
+        <v>2.97</v>
+      </c>
+      <c r="V40">
+        <v>1.34</v>
+      </c>
+      <c r="W40">
+        <v>1.02</v>
+      </c>
+      <c r="X40">
+        <v>1.06</v>
+      </c>
+      <c r="Y40">
+        <v>1.33</v>
+      </c>
+      <c r="Z40">
+        <v>2.88</v>
+      </c>
+      <c r="AA40">
         <v>2.1</v>
       </c>
-      <c r="Q40">
-        <v>0</v>
-      </c>
-      <c r="R40">
-        <v>0</v>
-      </c>
-      <c r="S40">
-        <v>0</v>
-      </c>
-      <c r="T40">
-        <v>0</v>
-      </c>
-      <c r="U40">
-        <v>0</v>
-      </c>
-      <c r="V40">
-        <v>0</v>
-      </c>
-      <c r="W40">
-        <v>0</v>
-      </c>
-      <c r="X40">
-        <v>0</v>
-      </c>
-      <c r="Y40">
-        <v>0</v>
-      </c>
-      <c r="Z40">
-        <v>0</v>
-      </c>
-      <c r="AA40">
-        <v>0</v>
-      </c>
       <c r="AB40">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="O42">
         <v>3.05</v>
       </c>
       <c r="P42">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="O43">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="P43">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,16 +7481,16 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q44">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="R44">
         <v>2.5</v>
@@ -7508,7 +7508,7 @@
         <v>1.63</v>
       </c>
       <c r="W44">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X44">
         <v>1.03</v>
@@ -7532,13 +7532,13 @@
         <v>1.64</v>
       </c>
       <c r="AE44">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AF44">
         <v>1.5</v>
       </c>
       <c r="AG44">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK44">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7650,16 +7650,16 @@
         <v>4.05</v>
       </c>
       <c r="P45">
-        <v>4.25</v>
+        <v>3.61</v>
       </c>
       <c r="Q45">
         <v>2</v>
       </c>
       <c r="R45">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="S45">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T45">
         <v>3.9</v>
@@ -7680,13 +7680,13 @@
         <v>1.1</v>
       </c>
       <c r="Z45">
-        <v>6.29</v>
+        <v>5.2</v>
       </c>
       <c r="AA45">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB45">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AC45">
         <v>2.1</v>
@@ -7695,10 +7695,10 @@
         <v>1.71</v>
       </c>
       <c r="AE45">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AF45">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AG45">
         <v>2.53</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK45">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,16 +7807,16 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="O46">
-        <v>3.48</v>
+        <v>3.7</v>
       </c>
       <c r="P46">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="Q46">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="R46">
         <v>2.5</v>
@@ -7825,7 +7825,7 @@
         <v>1.18</v>
       </c>
       <c r="T46">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="U46">
         <v>2.01</v>
@@ -7834,7 +7834,7 @@
         <v>1.77</v>
       </c>
       <c r="W46">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X46">
         <v>1.01</v>
@@ -7843,22 +7843,22 @@
         <v>1.11</v>
       </c>
       <c r="Z46">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AA46">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="AB46">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="AC46">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="AD46">
         <v>1.79</v>
       </c>
       <c r="AE46">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AF46">
         <v>1.38</v>
@@ -7970,10 +7970,10 @@
         </is>
       </c>
       <c r="N47">
-        <v>3.1</v>
+        <v>2.79</v>
       </c>
       <c r="O47">
-        <v>4.05</v>
+        <v>3.6</v>
       </c>
       <c r="P47">
         <v>2</v>
@@ -7997,16 +7997,16 @@
         <v>1.8</v>
       </c>
       <c r="W47">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X47">
         <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Z47">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AA47">
         <v>1.32</v>
@@ -8015,16 +8015,16 @@
         <v>3.1</v>
       </c>
       <c r="AC47">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AD47">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AE47">
         <v>1.33</v>
       </c>
       <c r="AF47">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AG47">
         <v>3</v>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK47">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8136,19 +8136,19 @@
         <v>1.6</v>
       </c>
       <c r="O48">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P48">
         <v>4.33</v>
       </c>
       <c r="Q48">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="R48">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="S48">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="T48">
         <v>3.6</v>
@@ -8160,22 +8160,22 @@
         <v>1.62</v>
       </c>
       <c r="W48">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X48">
         <v>1.03</v>
       </c>
       <c r="Y48">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="Z48">
-        <v>4.88</v>
+        <v>4.85</v>
       </c>
       <c r="AA48">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB48">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AC48">
         <v>2.33</v>
@@ -8206,7 +8206,7 @@
         <v>1.14</v>
       </c>
       <c r="AK48">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,19 +8296,19 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O49">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P49">
-        <v>2.34</v>
+        <v>2.45</v>
       </c>
       <c r="Q49">
         <v>3.24</v>
       </c>
       <c r="R49">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S49">
         <v>1.3</v>
@@ -8317,22 +8317,22 @@
         <v>3.2</v>
       </c>
       <c r="U49">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V49">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="W49">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X49">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z49">
-        <v>3.94</v>
+        <v>4.2</v>
       </c>
       <c r="AA49">
         <v>1.75</v>
@@ -8341,19 +8341,19 @@
         <v>1.95</v>
       </c>
       <c r="AC49">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="AD49">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AE49">
         <v>1.1</v>
       </c>
       <c r="AF49">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AG49">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8459,37 +8459,37 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="O50">
         <v>4.2</v>
       </c>
       <c r="P50">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="Q50">
         <v>1.93</v>
       </c>
       <c r="R50">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="S50">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T50">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="U50">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="V50">
         <v>1.64</v>
       </c>
       <c r="W50">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y50">
         <v>1.17</v>
@@ -8501,19 +8501,19 @@
         <v>1.33</v>
       </c>
       <c r="AB50">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="AC50">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD50">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="AE50">
         <v>1.24</v>
       </c>
       <c r="AF50">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG50">
         <v>2.28</v>
@@ -8625,7 +8625,7 @@
         <v>2.3</v>
       </c>
       <c r="O51">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P51">
         <v>2.5</v>
@@ -8637,7 +8637,7 @@
         <v>2.4</v>
       </c>
       <c r="S51">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T51">
         <v>3.5</v>
@@ -8661,10 +8661,10 @@
         <v>4.85</v>
       </c>
       <c r="AA51">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AB51">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AC51">
         <v>2.43</v>
@@ -8673,7 +8673,7 @@
         <v>1.47</v>
       </c>
       <c r="AE51">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF51">
         <v>1.43</v>
@@ -8695,7 +8695,7 @@
         <v>1.22</v>
       </c>
       <c r="AK51">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,31 +8785,31 @@
         </is>
       </c>
       <c r="N52">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="O52">
-        <v>4.75</v>
+        <v>5.1</v>
       </c>
       <c r="P52">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="Q52">
         <v>5</v>
       </c>
       <c r="R52">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="S52">
         <v>1.18</v>
       </c>
       <c r="T52">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="U52">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="V52">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="W52">
         <v>1.22</v>
@@ -8818,22 +8818,22 @@
         <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Z52">
-        <v>6.3</v>
+        <v>7</v>
       </c>
       <c r="AA52">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AB52">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AC52">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AD52">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AE52">
         <v>1.36</v>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.12</v>
+        <v>2.62</v>
       </c>
       <c r="AK52">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T53">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U53">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V53">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W53">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X53">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z53">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA53">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB53">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC53">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD53">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE53">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF53">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG53">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK53">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,10 +9111,10 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="O54">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P54">
         <v>3.05</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="O55">
         <v>3.11</v>
       </c>
       <c r="P55">
-        <v>2.35</v>
+        <v>2.41</v>
       </c>
       <c r="Q55">
         <v>3.45</v>
@@ -9307,13 +9307,13 @@
         <v>1.04</v>
       </c>
       <c r="Y55">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="Z55">
         <v>2.65</v>
       </c>
       <c r="AA55">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="AB55">
         <v>1.59</v>
@@ -9331,7 +9331,7 @@
         <v>1.95</v>
       </c>
       <c r="AG55">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AK55">
         <v>1.38</v>
@@ -9437,22 +9437,22 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="O56">
-        <v>3.45</v>
+        <v>3.18</v>
       </c>
       <c r="P56">
-        <v>2.33</v>
+        <v>2.16</v>
       </c>
       <c r="Q56">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
       <c r="R56">
         <v>2.27</v>
       </c>
       <c r="S56">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T56">
         <v>3</v>
@@ -9476,10 +9476,10 @@
         <v>3.5</v>
       </c>
       <c r="AA56">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB56">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AC56">
         <v>3.1</v>
@@ -9510,7 +9510,7 @@
         <v>1.28</v>
       </c>
       <c r="AK56">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9600,19 +9600,19 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="O57">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P57">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
       </c>
       <c r="R57">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S57">
         <v>1.39</v>
@@ -9630,10 +9630,10 @@
         <v>1.05</v>
       </c>
       <c r="X57">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y57">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z57">
         <v>3.25</v>
@@ -9651,13 +9651,13 @@
         <v>1.26</v>
       </c>
       <c r="AE57">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF57">
         <v>1.8</v>
       </c>
       <c r="AG57">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>1.3</v>
       </c>
       <c r="AK57">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9763,28 +9763,28 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="O58">
-        <v>3.6</v>
+        <v>3.48</v>
       </c>
       <c r="P58">
-        <v>2.65</v>
+        <v>2.31</v>
       </c>
       <c r="Q58">
         <v>2.8</v>
       </c>
       <c r="R58">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="S58">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T58">
         <v>3.55</v>
       </c>
       <c r="U58">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="V58">
         <v>1.6</v>
@@ -9799,7 +9799,7 @@
         <v>1.11</v>
       </c>
       <c r="Z58">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AA58">
         <v>1.48</v>
@@ -9808,7 +9808,7 @@
         <v>2.45</v>
       </c>
       <c r="AC58">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AD58">
         <v>1.55</v>
@@ -9935,25 +9935,25 @@
         <v>0</v>
       </c>
       <c r="Q59">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="R59">
         <v>2.3</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U59">
-        <v>2.35</v>
+        <v>2.41</v>
       </c>
       <c r="V59">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X59">
         <v>0</v>
@@ -9965,16 +9965,16 @@
         <v>3.75</v>
       </c>
       <c r="AA59">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB59">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="AC59">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AD59">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE59">
         <v>1.14</v>
@@ -10101,31 +10101,31 @@
         <v>1.55</v>
       </c>
       <c r="R60">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T60">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U60">
         <v>1.79</v>
       </c>
       <c r="V60">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="W60">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X60">
         <v>0</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z60">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA60">
         <v>1.3</v>
@@ -10140,7 +10140,7 @@
         <v>1.85</v>
       </c>
       <c r="AE60">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AF60">
         <v>1.66</v>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AK60">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="O61">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="P61">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="Q61">
         <v>3.3</v>
@@ -10273,25 +10273,25 @@
         <v>3.3</v>
       </c>
       <c r="U61">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="V61">
         <v>1.55</v>
       </c>
       <c r="W61">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X61">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y61">
         <v>1.15</v>
       </c>
       <c r="Z61">
-        <v>4.35</v>
+        <v>4.75</v>
       </c>
       <c r="AA61">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AB61">
         <v>2.19</v>
@@ -10300,10 +10300,10 @@
         <v>2.48</v>
       </c>
       <c r="AD61">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="AE61">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AF61">
         <v>1.5</v>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="AK61">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="O62">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P62">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="Q62">
         <v>2.5</v>
@@ -10439,7 +10439,7 @@
         <v>2.25</v>
       </c>
       <c r="V62">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W62">
         <v>1.11</v>
@@ -10448,7 +10448,7 @@
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z62">
         <v>4.3</v>
@@ -10463,16 +10463,16 @@
         <v>2.33</v>
       </c>
       <c r="AD62">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AE62">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF62">
         <v>1.49</v>
       </c>
       <c r="AG62">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>1.3</v>
       </c>
       <c r="AK62">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T63">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF63">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK63">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,10 +10741,10 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="O64">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="P64">
         <v>3</v>
@@ -10765,7 +10765,7 @@
         <v>2.38</v>
       </c>
       <c r="V64">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W64">
         <v>1.13</v>
@@ -10783,19 +10783,19 @@
         <v>1.62</v>
       </c>
       <c r="AB64">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AC64">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="AD64">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AE64">
         <v>1.18</v>
       </c>
       <c r="AF64">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AG64">
         <v>2.3</v>
@@ -10811,7 +10811,7 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AK64">
         <v>1.67</v>
@@ -10910,13 +10910,13 @@
         <v>4.2</v>
       </c>
       <c r="P65">
-        <v>4.55</v>
+        <v>4.05</v>
       </c>
       <c r="Q65">
         <v>2</v>
       </c>
       <c r="R65">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="S65">
         <v>1.2</v>
@@ -10925,22 +10925,22 @@
         <v>4</v>
       </c>
       <c r="U65">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V65">
         <v>1.7</v>
       </c>
       <c r="W65">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X65">
         <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z65">
-        <v>5.75</v>
+        <v>5.65</v>
       </c>
       <c r="AA65">
         <v>1.38</v>
@@ -10952,16 +10952,16 @@
         <v>2.04</v>
       </c>
       <c r="AD65">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AE65">
         <v>1.25</v>
       </c>
       <c r="AF65">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AG65">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -11067,16 +11067,16 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="O66">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="P66">
-        <v>3.45</v>
+        <v>2.8</v>
       </c>
       <c r="Q66">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="R66">
         <v>1.96</v>
@@ -11085,16 +11085,16 @@
         <v>1.4</v>
       </c>
       <c r="T66">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="U66">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="V66">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W66">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X66">
         <v>1.02</v>
@@ -11140,7 +11140,7 @@
         <v>1.3</v>
       </c>
       <c r="AK66">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11236,10 +11236,10 @@
         <v>3.4</v>
       </c>
       <c r="P67">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="Q67">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="R67">
         <v>2.33</v>
@@ -11278,7 +11278,7 @@
         <v>2.3</v>
       </c>
       <c r="AD67">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AE67">
         <v>1.17</v>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.44</v>
+        <v>1.21</v>
       </c>
       <c r="AK67">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11749,7 +11749,7 @@
         <v>1.14</v>
       </c>
       <c r="X70">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y70">
         <v>1.11</v>
@@ -11764,10 +11764,10 @@
         <v>2.45</v>
       </c>
       <c r="AC70">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="AD70">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AE70">
         <v>1.22</v>
@@ -11776,7 +11776,7 @@
         <v>1.85</v>
       </c>
       <c r="AG70">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AK70">
         <v>3.5</v>
@@ -11882,22 +11882,22 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="O71">
         <v>4.05</v>
       </c>
       <c r="P71">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="Q71">
         <v>2.3</v>
       </c>
       <c r="R71">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S71">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T71">
         <v>3.2</v>
@@ -11906,16 +11906,16 @@
         <v>2.66</v>
       </c>
       <c r="V71">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W71">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X71">
         <v>1.04</v>
       </c>
       <c r="Y71">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z71">
         <v>3.58</v>
@@ -11924,22 +11924,22 @@
         <v>1.74</v>
       </c>
       <c r="AB71">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AC71">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="AD71">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AE71">
         <v>1.13</v>
       </c>
       <c r="AF71">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AG71">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>1.18</v>
       </c>
       <c r="AK71">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="O72">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P72">
-        <v>4.15</v>
+        <v>3.9</v>
       </c>
       <c r="Q72">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="R72">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="S72">
         <v>1.33</v>
       </c>
       <c r="T72">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="U72">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="V72">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W72">
         <v>1.1</v>
       </c>
       <c r="X72">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y72">
         <v>1.22</v>
       </c>
       <c r="Z72">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AA72">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB72">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AC72">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="AD72">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE72">
         <v>1.13</v>
       </c>
       <c r="AF72">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AG72">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK72">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12208,19 +12208,19 @@
         </is>
       </c>
       <c r="N73">
-        <v>4.95</v>
+        <v>5.25</v>
       </c>
       <c r="O73">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="P73">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="Q73">
-        <v>5.56</v>
+        <v>5.62</v>
       </c>
       <c r="R73">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="S73">
         <v>1.25</v>
@@ -12229,7 +12229,7 @@
         <v>3.38</v>
       </c>
       <c r="U73">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="V73">
         <v>1.57</v>
@@ -12238,7 +12238,7 @@
         <v>1.15</v>
       </c>
       <c r="X73">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y73">
         <v>1.13</v>
@@ -12247,25 +12247,25 @@
         <v>4.5</v>
       </c>
       <c r="AA73">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AB73">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="AC73">
         <v>2.45</v>
       </c>
       <c r="AD73">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AE73">
         <v>1.16</v>
       </c>
       <c r="AF73">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG73">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AK73">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="O74">
+        <v>3.25</v>
+      </c>
+      <c r="P74">
         <v>3.3</v>
-      </c>
-      <c r="P74">
-        <v>3.25</v>
       </c>
       <c r="Q74">
         <v>2.63</v>
@@ -12404,16 +12404,16 @@
         <v>1.03</v>
       </c>
       <c r="Y74">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z74">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="AA74">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AB74">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="AC74">
         <v>3.5</v>
@@ -12425,10 +12425,10 @@
         <v>1.06</v>
       </c>
       <c r="AF74">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG74">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12543,19 +12543,19 @@
         <v>1.91</v>
       </c>
       <c r="Q75">
-        <v>3.76</v>
+        <v>4.25</v>
       </c>
       <c r="R75">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="S75">
         <v>1.38</v>
       </c>
       <c r="T75">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="U75">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="V75">
         <v>1.39</v>
@@ -12564,7 +12564,7 @@
         <v>1.04</v>
       </c>
       <c r="X75">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y75">
         <v>1.27</v>
@@ -12579,13 +12579,13 @@
         <v>1.82</v>
       </c>
       <c r="AC75">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="AD75">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AE75">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF75">
         <v>1.8</v>
@@ -12697,31 +12697,31 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="O76">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P76">
         <v>3.4</v>
       </c>
       <c r="Q76">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="R76">
         <v>2.05</v>
       </c>
       <c r="S76">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="T76">
         <v>2.75</v>
       </c>
       <c r="U76">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="V76">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W76">
         <v>1.05</v>
@@ -12733,7 +12733,7 @@
         <v>1.36</v>
       </c>
       <c r="Z76">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AA76">
         <v>2.1</v>
@@ -12748,10 +12748,10 @@
         <v>1.21</v>
       </c>
       <c r="AE76">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF76">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG76">
         <v>1.83</v>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK76">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12860,31 +12860,31 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="O77">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P77">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q77">
-        <v>3.31</v>
+        <v>3.34</v>
       </c>
       <c r="R77">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="S77">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="T77">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="U77">
         <v>2.91</v>
       </c>
       <c r="V77">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W77">
         <v>1.07</v>
@@ -12899,25 +12899,25 @@
         <v>3</v>
       </c>
       <c r="AA77">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AB77">
         <v>1.76</v>
       </c>
       <c r="AC77">
-        <v>3.54</v>
+        <v>3.75</v>
       </c>
       <c r="AD77">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AE77">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF77">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AG77">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -13044,10 +13044,10 @@
         <v>2.56</v>
       </c>
       <c r="U78">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="V78">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="W78">
         <v>1.01</v>
@@ -13062,7 +13062,7 @@
         <v>2.74</v>
       </c>
       <c r="AA78">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="AB78">
         <v>1.66</v>
@@ -13080,7 +13080,7 @@
         <v>2.18</v>
       </c>
       <c r="AG78">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK78">
         <v>2.13</v>
@@ -13186,7 +13186,7 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="O79">
         <v>3.15</v>
@@ -13201,13 +13201,13 @@
         <v>2.08</v>
       </c>
       <c r="S79">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T79">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="U79">
-        <v>3.05</v>
+        <v>3.24</v>
       </c>
       <c r="V79">
         <v>1.32</v>
@@ -13361,7 +13361,7 @@
         <v>2.07</v>
       </c>
       <c r="R80">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="S80">
         <v>1.42</v>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AK80">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="O81">
-        <v>5.47</v>
+        <v>5.35</v>
       </c>
       <c r="P81">
-        <v>7.55</v>
+        <v>6.4</v>
       </c>
       <c r="Q81">
         <v>1.67</v>
@@ -13536,7 +13536,7 @@
         <v>1.91</v>
       </c>
       <c r="V81">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="W81">
         <v>1.22</v>
@@ -13548,7 +13548,7 @@
         <v>1.04</v>
       </c>
       <c r="Z81">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AA81">
         <v>1.32</v>
@@ -13557,19 +13557,19 @@
         <v>3</v>
       </c>
       <c r="AC81">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AD81">
         <v>1.96</v>
       </c>
       <c r="AE81">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AF81">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AG81">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         <v>1.08</v>
       </c>
       <c r="AK81">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13838,7 +13838,7 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="O83">
         <v>3.4</v>
@@ -13850,13 +13850,13 @@
         <v>2.9</v>
       </c>
       <c r="R83">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="S83">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T83">
-        <v>3.16</v>
+        <v>2.88</v>
       </c>
       <c r="U83">
         <v>2.71</v>
@@ -13877,22 +13877,22 @@
         <v>3.6</v>
       </c>
       <c r="AA83">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AB83">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AC83">
         <v>3.1</v>
       </c>
       <c r="AD83">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE83">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF83">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG83">
         <v>2.15</v>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AK83">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14001,25 +14001,25 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="O84">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P84">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="Q84">
         <v>2.9</v>
       </c>
       <c r="R84">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="S84">
         <v>1.36</v>
       </c>
       <c r="T84">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="U84">
         <v>2.65</v>
@@ -14034,7 +14034,7 @@
         <v>1.05</v>
       </c>
       <c r="Y84">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z84">
         <v>3.5</v>
@@ -14043,13 +14043,13 @@
         <v>1.85</v>
       </c>
       <c r="AB84">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="AC84">
         <v>3.1</v>
       </c>
       <c r="AD84">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE84">
         <v>1.09</v>
@@ -14058,7 +14058,7 @@
         <v>1.65</v>
       </c>
       <c r="AG84">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14185,22 +14185,22 @@
         <v>2.59</v>
       </c>
       <c r="U85">
-        <v>3.03</v>
+        <v>2.91</v>
       </c>
       <c r="V85">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W85">
         <v>1.02</v>
       </c>
       <c r="X85">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y85">
         <v>1.28</v>
       </c>
       <c r="Z85">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AA85">
         <v>1.99</v>
@@ -14218,7 +14218,7 @@
         <v>1.04</v>
       </c>
       <c r="AF85">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AG85">
         <v>1.95</v>
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="O86">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="P86">
-        <v>4.95</v>
+        <v>5.65</v>
       </c>
       <c r="Q86">
         <v>1.85</v>
@@ -14342,16 +14342,16 @@
         <v>2.74</v>
       </c>
       <c r="S86">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="T86">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="U86">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="V86">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="W86">
         <v>1.22</v>
@@ -14360,7 +14360,7 @@
         <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Z86">
         <v>7.5</v>
@@ -14369,22 +14369,22 @@
         <v>1.28</v>
       </c>
       <c r="AB86">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="AC86">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AD86">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="AE86">
         <v>1.36</v>
       </c>
       <c r="AF86">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AG86">
-        <v>2.53</v>
+        <v>2.58</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK86">
-        <v>2.71</v>
+        <v>2.43</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="O87">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>9.85</v>
       </c>
       <c r="Q87">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="R87">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S87">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T87">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="U87">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V87">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W87">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X87">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z87">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA87">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB87">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC87">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD87">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE87">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF87">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG87">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK87">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.35</v>
+        <v>2.22</v>
       </c>
       <c r="O89">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P89">
-        <v>2.5</v>
+        <v>2.84</v>
       </c>
       <c r="Q89">
         <v>3</v>
@@ -14834,13 +14834,13 @@
         <v>1.32</v>
       </c>
       <c r="T89">
-        <v>2.96</v>
+        <v>2.39</v>
       </c>
       <c r="U89">
         <v>2.4</v>
       </c>
       <c r="V89">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="W89">
         <v>1.06</v>
@@ -14852,10 +14852,10 @@
         <v>1.22</v>
       </c>
       <c r="Z89">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="AA89">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AB89">
         <v>2.1</v>
@@ -14889,7 +14889,7 @@
         <v>1.38</v>
       </c>
       <c r="AK89">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14979,7 +14979,7 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.37</v>
+        <v>2.44</v>
       </c>
       <c r="O90">
         <v>3.3</v>
@@ -14988,7 +14988,7 @@
         <v>2.85</v>
       </c>
       <c r="Q90">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="R90">
         <v>2.2</v>
@@ -15009,10 +15009,10 @@
         <v>1.05</v>
       </c>
       <c r="X90">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y90">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z90">
         <v>3.5</v>
@@ -15024,7 +15024,7 @@
         <v>1.8</v>
       </c>
       <c r="AC90">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AD90">
         <v>1.29</v>
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="O91">
         <v>4.68</v>
       </c>
       <c r="P91">
-        <v>5.75</v>
+        <v>5.55</v>
       </c>
       <c r="Q91">
         <v>1.83</v>
@@ -15160,7 +15160,7 @@
         <v>1.2</v>
       </c>
       <c r="T91">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U91">
         <v>2.07</v>
@@ -15181,22 +15181,22 @@
         <v>5.75</v>
       </c>
       <c r="AA91">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB91">
         <v>2.64</v>
       </c>
       <c r="AC91">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AD91">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AE91">
         <v>1.26</v>
       </c>
       <c r="AF91">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AG91">
         <v>2.37</v>
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.97</v>
+        <v>2.66</v>
       </c>
       <c r="O92">
         <v>3.6</v>
       </c>
       <c r="P92">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="Q92">
         <v>3.4</v>
@@ -15353,7 +15353,7 @@
         <v>2</v>
       </c>
       <c r="AD92">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AE92">
         <v>1.32</v>
@@ -15957,19 +15957,19 @@
         </is>
       </c>
       <c r="N96">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O96">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P96">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
       </c>
       <c r="R96">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S96">
         <v>1.4</v>
@@ -15978,10 +15978,10 @@
         <v>2.84</v>
       </c>
       <c r="U96">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="V96">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W96">
         <v>1.04</v>
@@ -15993,7 +15993,7 @@
         <v>1.31</v>
       </c>
       <c r="Z96">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA96">
         <v>1.94</v>
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AK96">
         <v>1.5</v>
@@ -16120,7 +16120,7 @@
         </is>
       </c>
       <c r="N97">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="O97">
         <v>3.5</v>
@@ -16141,7 +16141,7 @@
         <v>2.9</v>
       </c>
       <c r="U97">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="V97">
         <v>1.42</v>
@@ -16153,22 +16153,22 @@
         <v>1</v>
       </c>
       <c r="Y97">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z97">
-        <v>3.43</v>
+        <v>3.42</v>
       </c>
       <c r="AA97">
+        <v>1.9</v>
+      </c>
+      <c r="AB97">
         <v>1.85</v>
-      </c>
-      <c r="AB97">
-        <v>1.87</v>
       </c>
       <c r="AC97">
         <v>2.92</v>
       </c>
       <c r="AD97">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE97">
         <v>1.1</v>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
+        <v>1.29</v>
+      </c>
+      <c r="AK97">
         <v>1.2</v>
-      </c>
-      <c r="AK97">
-        <v>1.19</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="O98">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="P98">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="Q98">
         <v>1.98</v>
@@ -16310,7 +16310,7 @@
         <v>1.67</v>
       </c>
       <c r="W98">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X98">
         <v>1.02</v>
@@ -16328,19 +16328,19 @@
         <v>2.62</v>
       </c>
       <c r="AC98">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="AD98">
         <v>1.67</v>
       </c>
       <c r="AE98">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF98">
         <v>1.54</v>
       </c>
       <c r="AG98">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="O99">
-        <v>3.4</v>
+        <v>3.23</v>
       </c>
       <c r="P99">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q99">
         <v>2.63</v>
@@ -16464,7 +16464,7 @@
         <v>1.34</v>
       </c>
       <c r="T99">
-        <v>2.68</v>
+        <v>2.85</v>
       </c>
       <c r="U99">
         <v>2.88</v>
@@ -16494,7 +16494,7 @@
         <v>3.24</v>
       </c>
       <c r="AD99">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AE99">
         <v>1.09</v>
@@ -16609,19 +16609,19 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="O100">
-        <v>4.65</v>
+        <v>4.5</v>
       </c>
       <c r="P100">
-        <v>6.55</v>
+        <v>5.6</v>
       </c>
       <c r="Q100">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="R100">
-        <v>2.53</v>
+        <v>2.71</v>
       </c>
       <c r="S100">
         <v>1.25</v>
@@ -16944,19 +16944,19 @@
         <v>0</v>
       </c>
       <c r="Q102">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="R102">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="S102">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="T102">
         <v>2.5</v>
       </c>
       <c r="U102">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="V102">
         <v>1.38</v>
@@ -16974,10 +16974,10 @@
         <v>3.35</v>
       </c>
       <c r="AA102">
-        <v>2.2</v>
+        <v>1.86</v>
       </c>
       <c r="AB102">
-        <v>1.58</v>
+        <v>1.83</v>
       </c>
       <c r="AC102">
         <v>3.1</v>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK102">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O103">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P103">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="Q103">
         <v>5.13</v>
@@ -17131,19 +17131,19 @@
         <v>1.05</v>
       </c>
       <c r="Y103">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z103">
         <v>3.42</v>
       </c>
       <c r="AA103">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AB103">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC103">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="AD103">
         <v>1.3</v>
@@ -17264,28 +17264,28 @@
         <v>2</v>
       </c>
       <c r="O104">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P104">
         <v>3</v>
       </c>
       <c r="Q104">
-        <v>2.33</v>
+        <v>2.54</v>
       </c>
       <c r="R104">
-        <v>2.38</v>
+        <v>2.51</v>
       </c>
       <c r="S104">
         <v>1.22</v>
       </c>
       <c r="T104">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U104">
         <v>2.2</v>
       </c>
       <c r="V104">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W104">
         <v>1.17</v>
@@ -17300,10 +17300,10 @@
         <v>4.75</v>
       </c>
       <c r="AA104">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB104">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="AC104">
         <v>2.26</v>
@@ -17312,7 +17312,7 @@
         <v>1.62</v>
       </c>
       <c r="AE104">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF104">
         <v>1.44</v>
@@ -17424,10 +17424,10 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="O105">
-        <v>3.1</v>
+        <v>3.51</v>
       </c>
       <c r="P105">
         <v>2.57</v>
@@ -17596,7 +17596,7 @@
         <v>3.1</v>
       </c>
       <c r="Q106">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="R106">
         <v>2.3</v>
@@ -17605,7 +17605,7 @@
         <v>1.25</v>
       </c>
       <c r="T106">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="U106">
         <v>2.25</v>
@@ -17620,22 +17620,22 @@
         <v>1.04</v>
       </c>
       <c r="Y106">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z106">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA106">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AB106">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AC106">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AD106">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AE106">
         <v>1.16</v>
@@ -17750,19 +17750,19 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O107">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P107">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q107">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="R107">
-        <v>2.07</v>
+        <v>2.27</v>
       </c>
       <c r="S107">
         <v>1.33</v>
@@ -17771,7 +17771,7 @@
         <v>2.88</v>
       </c>
       <c r="U107">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="V107">
         <v>1.4</v>
@@ -17786,16 +17786,16 @@
         <v>1.21</v>
       </c>
       <c r="Z107">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="AA107">
         <v>1.83</v>
       </c>
       <c r="AB107">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AC107">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="AD107">
         <v>1.33</v>
@@ -17916,22 +17916,22 @@
         <v>2.3</v>
       </c>
       <c r="O108">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P108">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Q108">
-        <v>3.08</v>
+        <v>2.95</v>
       </c>
       <c r="R108">
         <v>2.2</v>
       </c>
       <c r="S108">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T108">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U108">
         <v>2.73</v>
@@ -17949,7 +17949,7 @@
         <v>1.23</v>
       </c>
       <c r="Z108">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="AA108">
         <v>1.88</v>
@@ -17961,10 +17961,10 @@
         <v>3.1</v>
       </c>
       <c r="AD108">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AE108">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF108">
         <v>1.66</v>
@@ -17983,7 +17983,7 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="AK108">
         <v>1.57</v>
@@ -18076,10 +18076,10 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.9</v>
+        <v>1.48</v>
       </c>
       <c r="O109">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="P109">
         <v>3.94</v>
@@ -18103,37 +18103,37 @@
         <v>1.45</v>
       </c>
       <c r="W109">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X109">
         <v>1.02</v>
       </c>
       <c r="Y109">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z109">
-        <v>3.92</v>
+        <v>4.19</v>
       </c>
       <c r="AA109">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB109">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AC109">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AD109">
         <v>1.4</v>
       </c>
       <c r="AE109">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF109">
         <v>1.75</v>
       </c>
       <c r="AG109">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="O115">
-        <v>3.9</v>
+        <v>3.96</v>
       </c>
       <c r="P115">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="Q115">
         <v>3.25</v>
@@ -19090,7 +19090,7 @@
         <v>1.08</v>
       </c>
       <c r="Z115">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA115">
         <v>1.37</v>
@@ -19102,7 +19102,7 @@
         <v>1.95</v>
       </c>
       <c r="AD115">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AE115">
         <v>1.28</v>
@@ -19127,7 +19127,7 @@
         <v>1.22</v>
       </c>
       <c r="AK115">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19217,37 +19217,37 @@
         </is>
       </c>
       <c r="N116">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O116">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P116">
-        <v>0</v>
+        <v>6.66</v>
       </c>
       <c r="Q116">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="R116">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S116">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T116">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U116">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V116">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W116">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X116">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y116">
         <v>1.19</v>
@@ -19256,25 +19256,25 @@
         <v>3.8</v>
       </c>
       <c r="AA116">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AB116">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AC116">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="AD116">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AE116">
         <v>1.15</v>
       </c>
       <c r="AF116">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AG116">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19290,7 +19290,7 @@
         <v>1.13</v>
       </c>
       <c r="AK116">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19543,7 +19543,7 @@
         </is>
       </c>
       <c r="N118">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="O118">
         <v>3.3</v>
@@ -19552,10 +19552,10 @@
         <v>3.09</v>
       </c>
       <c r="Q118">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="R118">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="S118">
         <v>1.3</v>
@@ -19564,16 +19564,16 @@
         <v>3.24</v>
       </c>
       <c r="U118">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="V118">
         <v>1.45</v>
       </c>
       <c r="W118">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X118">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y118">
         <v>1.25</v>
@@ -19585,10 +19585,10 @@
         <v>1.79</v>
       </c>
       <c r="AB118">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AC118">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="AD118">
         <v>1.38</v>
@@ -19869,25 +19869,25 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="O120">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P120">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="Q120">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="R120">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="S120">
         <v>1.49</v>
       </c>
       <c r="T120">
-        <v>2.54</v>
+        <v>2.34</v>
       </c>
       <c r="U120">
         <v>3.34</v>
@@ -19902,13 +19902,13 @@
         <v>1.06</v>
       </c>
       <c r="Y120">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Z120">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="AA120">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AB120">
         <v>1.53</v>
@@ -19926,7 +19926,7 @@
         <v>2</v>
       </c>
       <c r="AG120">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -20032,80 +20032,80 @@
         </is>
       </c>
       <c r="N121">
-        <v>5.25</v>
+        <v>4.2</v>
       </c>
       <c r="O121">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P121">
-        <v>1.47</v>
+        <v>1.63</v>
       </c>
       <c r="Q121">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="R121">
-        <v>2.42</v>
+        <v>2.37</v>
       </c>
       <c r="S121">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T121">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U121">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="V121">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W121">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X121">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y121">
         <v>1.16</v>
       </c>
       <c r="Z121">
-        <v>4.45</v>
+        <v>3.95</v>
       </c>
       <c r="AA121">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AB121">
-        <v>2.26</v>
+        <v>2.05</v>
       </c>
       <c r="AC121">
-        <v>2.34</v>
+        <v>2.62</v>
       </c>
       <c r="AD121">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AE121">
+        <v>1.13</v>
+      </c>
+      <c r="AF121">
+        <v>1.62</v>
+      </c>
+      <c r="AG121">
+        <v>2.15</v>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ121">
+        <v>2.1</v>
+      </c>
+      <c r="AK121">
         <v>1.18</v>
-      </c>
-      <c r="AF121">
-        <v>1.66</v>
-      </c>
-      <c r="AG121">
-        <v>2.07</v>
-      </c>
-      <c r="AH121" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI121" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ121">
-        <v>1.14</v>
-      </c>
-      <c r="AK121">
-        <v>1.1</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20195,7 +20195,7 @@
         </is>
       </c>
       <c r="N122">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O122">
         <v>3.45</v>
@@ -20222,7 +20222,7 @@
         <v>1.4</v>
       </c>
       <c r="W122">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X122">
         <v>1</v>
@@ -20521,10 +20521,10 @@
         </is>
       </c>
       <c r="N124">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="O124">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P124">
         <v>2.25</v>
@@ -20533,7 +20533,7 @@
         <v>3.3</v>
       </c>
       <c r="R124">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="S124">
         <v>1.42</v>
@@ -20542,13 +20542,13 @@
         <v>2.62</v>
       </c>
       <c r="U124">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="V124">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W124">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X124">
         <v>1.02</v>
@@ -20569,7 +20569,7 @@
         <v>3.3</v>
       </c>
       <c r="AD124">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE124">
         <v>1.07</v>
@@ -20594,7 +20594,7 @@
         <v>1.5</v>
       </c>
       <c r="AK124">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20684,13 +20684,13 @@
         </is>
       </c>
       <c r="N125">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="O125">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="P125">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="Q125">
         <v>0</v>
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="O127">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="P127">
         <v>4.75</v>
       </c>
       <c r="Q127">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R127">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S127">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T127">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U127">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V127">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W127">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X127">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y127">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z127">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA127">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB127">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC127">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD127">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE127">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF127">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG127">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK127">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21336,10 +21336,10 @@
         </is>
       </c>
       <c r="N129">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="O129">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P129">
         <v>4.75</v>
@@ -21351,16 +21351,16 @@
         <v>2.38</v>
       </c>
       <c r="S129">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T129">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U129">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V129">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W129">
         <v>1.11</v>
@@ -21372,7 +21372,7 @@
         <v>1.13</v>
       </c>
       <c r="Z129">
-        <v>4.75</v>
+        <v>4.87</v>
       </c>
       <c r="AA129">
         <v>1.57</v>
@@ -21384,7 +21384,7 @@
         <v>2.45</v>
       </c>
       <c r="AD129">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="AE129">
         <v>1.22</v>
@@ -21406,7 +21406,7 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK129">
         <v>2.15</v>
@@ -21665,7 +21665,7 @@
         <v>1.61</v>
       </c>
       <c r="O131">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P131">
         <v>4.6</v>
@@ -21692,13 +21692,13 @@
         <v>1.07</v>
       </c>
       <c r="X131">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y131">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="Z131">
-        <v>2.92</v>
+        <v>3.03</v>
       </c>
       <c r="AA131">
         <v>2.13</v>
@@ -21707,10 +21707,10 @@
         <v>1.69</v>
       </c>
       <c r="AC131">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="AD131">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE131">
         <v>1.08</v>
@@ -21735,7 +21735,7 @@
         <v>1.15</v>
       </c>
       <c r="AK131">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21988,13 +21988,13 @@
         </is>
       </c>
       <c r="N133">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="O133">
-        <v>3.54</v>
+        <v>3.55</v>
       </c>
       <c r="P133">
-        <v>3.89</v>
+        <v>3.5</v>
       </c>
       <c r="Q133">
         <v>0</v>
@@ -22151,13 +22151,13 @@
         </is>
       </c>
       <c r="N134">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="O134">
         <v>3.5</v>
       </c>
       <c r="P134">
-        <v>3.85</v>
+        <v>4.02</v>
       </c>
       <c r="Q134">
         <v>2.4</v>
@@ -22199,16 +22199,16 @@
         <v>3.08</v>
       </c>
       <c r="AD134">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE134">
         <v>1.12</v>
       </c>
       <c r="AF134">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AG134">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22317,7 +22317,7 @@
         <v>4.4</v>
       </c>
       <c r="O135">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="P135">
         <v>1.61</v>
@@ -22341,10 +22341,10 @@
         <v>1.46</v>
       </c>
       <c r="W135">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X135">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y135">
         <v>1.2</v>
@@ -22353,10 +22353,10 @@
         <v>3.74</v>
       </c>
       <c r="AA135">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AB135">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AC135">
         <v>2.76</v>
@@ -22368,7 +22368,7 @@
         <v>1.12</v>
       </c>
       <c r="AF135">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG135">
         <v>2.05</v>
@@ -22679,7 +22679,7 @@
         <v>3.42</v>
       </c>
       <c r="AA137">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="AB137">
         <v>1.93</v>
@@ -22697,7 +22697,7 @@
         <v>1.9</v>
       </c>
       <c r="AG137">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22803,10 +22803,10 @@
         </is>
       </c>
       <c r="N138">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="O138">
-        <v>7.05</v>
+        <v>7.5</v>
       </c>
       <c r="P138">
         <v>16</v>
@@ -22815,31 +22815,31 @@
         <v>1.44</v>
       </c>
       <c r="R138">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="S138">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="T138">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="U138">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="V138">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="W138">
         <v>1.22</v>
       </c>
       <c r="X138">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y138">
         <v>1.08</v>
       </c>
       <c r="Z138">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="AA138">
         <v>1.33</v>
@@ -22860,7 +22860,7 @@
         <v>2.05</v>
       </c>
       <c r="AG138">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AK138">
-        <v>7</v>
+        <v>5.45</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -22975,55 +22975,55 @@
         <v>8</v>
       </c>
       <c r="Q139">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="R139">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="S139">
         <v>1.29</v>
       </c>
       <c r="T139">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="U139">
-        <v>2.27</v>
+        <v>2.62</v>
       </c>
       <c r="V139">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="W139">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X139">
         <v>1.04</v>
       </c>
       <c r="Y139">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z139">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="AA139">
-        <v>1.52</v>
+        <v>1.71</v>
       </c>
       <c r="AB139">
-        <v>2.24</v>
+        <v>2.02</v>
       </c>
       <c r="AC139">
-        <v>2.32</v>
+        <v>2.66</v>
       </c>
       <c r="AD139">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="AE139">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AF139">
-        <v>1.79</v>
+        <v>2.15</v>
       </c>
       <c r="AG139">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AK139">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23144,13 +23144,13 @@
         <v>2</v>
       </c>
       <c r="S140">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="T140">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="U140">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="V140">
         <v>1.21</v>
@@ -23168,16 +23168,16 @@
         <v>2.45</v>
       </c>
       <c r="AA140">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AB140">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="AC140">
         <v>5.1</v>
       </c>
       <c r="AD140">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AE140">
         <v>1.01</v>
@@ -23307,34 +23307,34 @@
         <v>1.81</v>
       </c>
       <c r="S141">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="T141">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="U141">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="V141">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W141">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X141">
         <v>1.09</v>
       </c>
       <c r="Y141">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Z141">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AA141">
-        <v>2.7</v>
+        <v>2.86</v>
       </c>
       <c r="AB141">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AC141">
         <v>5.35</v>
@@ -23464,7 +23464,7 @@
         <v>4.4</v>
       </c>
       <c r="Q142">
-        <v>2.79</v>
+        <v>2.63</v>
       </c>
       <c r="R142">
         <v>1.78</v>
@@ -23476,7 +23476,7 @@
         <v>2.1</v>
       </c>
       <c r="U142">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="V142">
         <v>1.17</v>
@@ -23509,7 +23509,7 @@
         <v>1.01</v>
       </c>
       <c r="AF142">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="AG142">
         <v>1.36</v>
@@ -23525,7 +23525,7 @@
         </is>
       </c>
       <c r="AJ142">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AK142">
         <v>1.75</v>
@@ -23618,19 +23618,19 @@
         </is>
       </c>
       <c r="N143">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="O143">
         <v>3.75</v>
       </c>
       <c r="P143">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="Q143">
         <v>3.92</v>
       </c>
       <c r="R143">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="S143">
         <v>1.23</v>
@@ -23660,7 +23660,7 @@
         <v>1.53</v>
       </c>
       <c r="AB143">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="AC143">
         <v>2.21</v>
@@ -23672,7 +23672,7 @@
         <v>1.23</v>
       </c>
       <c r="AF143">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="AG143">
         <v>2.4</v>
@@ -23688,10 +23688,10 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>1.17</v>
+        <v>2.09</v>
       </c>
       <c r="AK143">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -24596,7 +24596,7 @@
         </is>
       </c>
       <c r="N149">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="O149">
         <v>7.5</v>
@@ -24611,10 +24611,10 @@
         <v>3.19</v>
       </c>
       <c r="S149">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="T149">
-        <v>5.6</v>
+        <v>5.55</v>
       </c>
       <c r="U149">
         <v>1.67</v>
@@ -24626,34 +24626,34 @@
         <v>1.36</v>
       </c>
       <c r="X149">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y149">
         <v>1.01</v>
       </c>
       <c r="Z149">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA149">
         <v>1.22</v>
       </c>
       <c r="AB149">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="AC149">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="AD149">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AE149">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AF149">
         <v>1.57</v>
       </c>
       <c r="AG149">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="AH149" t="inlineStr">
         <is>
@@ -24931,19 +24931,19 @@
         <v>8</v>
       </c>
       <c r="Q151">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="R151">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="S151">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T151">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="U151">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="V151">
         <v>1.57</v>
@@ -24958,25 +24958,25 @@
         <v>1.17</v>
       </c>
       <c r="Z151">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="AA151">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AB151">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="AC151">
         <v>2.4</v>
       </c>
       <c r="AD151">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AE151">
         <v>1.2</v>
       </c>
       <c r="AF151">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AG151">
         <v>1.7</v>
@@ -24992,10 +24992,10 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AK151">
-        <v>3.7</v>
+        <v>3.84</v>
       </c>
       <c r="AL151">
         <v>0</v>
@@ -25085,10 +25085,10 @@
         </is>
       </c>
       <c r="N152">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="O152">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P152">
         <v>3.1</v>
@@ -25100,10 +25100,10 @@
         <v>2.28</v>
       </c>
       <c r="S152">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T152">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="U152">
         <v>2.2</v>
@@ -25124,22 +25124,22 @@
         <v>4.8</v>
       </c>
       <c r="AA152">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AB152">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="AC152">
         <v>2.27</v>
       </c>
       <c r="AD152">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AE152">
         <v>1.17</v>
       </c>
       <c r="AF152">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AG152">
         <v>2.45</v>
@@ -25248,13 +25248,13 @@
         </is>
       </c>
       <c r="N153">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="O153">
         <v>3.1</v>
       </c>
       <c r="P153">
-        <v>2.49</v>
+        <v>2.23</v>
       </c>
       <c r="Q153">
         <v>3.25</v>
@@ -25269,7 +25269,7 @@
         <v>2.85</v>
       </c>
       <c r="U153">
-        <v>2.95</v>
+        <v>2.81</v>
       </c>
       <c r="V153">
         <v>1.36</v>
@@ -25281,7 +25281,7 @@
         <v>1.06</v>
       </c>
       <c r="Y153">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z153">
         <v>3.04</v>
@@ -25296,7 +25296,7 @@
         <v>3.5</v>
       </c>
       <c r="AD153">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE153">
         <v>1.05</v>
@@ -25411,19 +25411,19 @@
         </is>
       </c>
       <c r="N154">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="O154">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P154">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="Q154">
         <v>4.2</v>
       </c>
       <c r="R154">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S154">
         <v>1.44</v>
@@ -25438,7 +25438,7 @@
         <v>1.33</v>
       </c>
       <c r="W154">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X154">
         <v>1.06</v>
@@ -25459,10 +25459,10 @@
         <v>3.98</v>
       </c>
       <c r="AD154">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AE154">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF154">
         <v>1.91</v>
@@ -25484,7 +25484,7 @@
         <v>1.29</v>
       </c>
       <c r="AK154">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25574,13 +25574,13 @@
         </is>
       </c>
       <c r="N155">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="O155">
         <v>4.1</v>
       </c>
       <c r="P155">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="Q155">
         <v>2</v>
@@ -25592,7 +25592,7 @@
         <v>1.3</v>
       </c>
       <c r="T155">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="U155">
         <v>2.4</v>
@@ -25604,7 +25604,7 @@
         <v>1.09</v>
       </c>
       <c r="X155">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y155">
         <v>1.2</v>
@@ -25619,19 +25619,19 @@
         <v>2.15</v>
       </c>
       <c r="AC155">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AD155">
         <v>1.48</v>
       </c>
       <c r="AE155">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF155">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AG155">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25743,7 +25743,7 @@
         <v>3.9</v>
       </c>
       <c r="P156">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="Q156">
         <v>2.05</v>
@@ -25788,7 +25788,7 @@
         <v>1.53</v>
       </c>
       <c r="AE156">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AF156">
         <v>1.6</v>
@@ -26066,7 +26066,7 @@
         <v>1.5</v>
       </c>
       <c r="O158">
-        <v>3.72</v>
+        <v>3.73</v>
       </c>
       <c r="P158">
         <v>5.3</v>
@@ -26226,25 +26226,25 @@
         </is>
       </c>
       <c r="N159">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="O159">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P159">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="Q159">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="R159">
         <v>2.05</v>
       </c>
       <c r="S159">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T159">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="U159">
         <v>3.17</v>
@@ -26262,16 +26262,16 @@
         <v>1.28</v>
       </c>
       <c r="Z159">
-        <v>3.12</v>
+        <v>2.88</v>
       </c>
       <c r="AA159">
         <v>2.05</v>
       </c>
       <c r="AB159">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AC159">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AD159">
         <v>1.22</v>
@@ -26299,7 +26299,7 @@
         <v>1.25</v>
       </c>
       <c r="AK159">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26389,13 +26389,13 @@
         </is>
       </c>
       <c r="N160">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="O160">
         <v>3.4</v>
       </c>
       <c r="P160">
-        <v>4.15</v>
+        <v>4.05</v>
       </c>
       <c r="Q160">
         <v>2.3</v>
@@ -26413,13 +26413,13 @@
         <v>2.8</v>
       </c>
       <c r="V160">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W160">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X160">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y160">
         <v>1.33</v>
@@ -26431,19 +26431,19 @@
         <v>1.96</v>
       </c>
       <c r="AB160">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AC160">
-        <v>3.6</v>
+        <v>3.18</v>
       </c>
       <c r="AD160">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE160">
         <v>1.06</v>
       </c>
       <c r="AF160">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AG160">
         <v>1.87</v>
@@ -26552,64 +26552,64 @@
         </is>
       </c>
       <c r="N161">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="O161">
         <v>3.25</v>
       </c>
       <c r="P161">
-        <v>2.79</v>
+        <v>2.62</v>
       </c>
       <c r="Q161">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R161">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S161">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T161">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U161">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V161">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W161">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X161">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y161">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z161">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA161">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB161">
         <v>1.7</v>
       </c>
       <c r="AC161">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD161">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE161">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF161">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG161">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK161">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -26715,13 +26715,13 @@
         </is>
       </c>
       <c r="N162">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="O162">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P162">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Q162">
         <v>4.58</v>
@@ -26730,10 +26730,10 @@
         <v>2.16</v>
       </c>
       <c r="S162">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="T162">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="U162">
         <v>2.94</v>
@@ -26757,7 +26757,7 @@
         <v>2.1</v>
       </c>
       <c r="AB162">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AC162">
         <v>3.9</v>
@@ -26766,13 +26766,13 @@
         <v>1.22</v>
       </c>
       <c r="AE162">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF162">
         <v>1.82</v>
       </c>
       <c r="AG162">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
@@ -26785,7 +26785,7 @@
         </is>
       </c>
       <c r="AJ162">
-        <v>1.3</v>
+        <v>1.81</v>
       </c>
       <c r="AK162">
         <v>1.2</v>
@@ -26878,7 +26878,7 @@
         </is>
       </c>
       <c r="N163">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O163">
         <v>3.1</v>
@@ -26899,13 +26899,13 @@
         <v>2.69</v>
       </c>
       <c r="U163">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="V163">
         <v>1.37</v>
       </c>
       <c r="W163">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X163">
         <v>1.06</v>
@@ -26920,10 +26920,10 @@
         <v>1.97</v>
       </c>
       <c r="AB163">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AC163">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AD163">
         <v>1.27</v>
@@ -26932,7 +26932,7 @@
         <v>1.06</v>
       </c>
       <c r="AF163">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AG163">
         <v>1.85</v>
@@ -27044,7 +27044,7 @@
         <v>2.45</v>
       </c>
       <c r="O164">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P164">
         <v>2.5</v>
@@ -27059,7 +27059,7 @@
         <v>1.36</v>
       </c>
       <c r="T164">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="U164">
         <v>2.62</v>
@@ -27077,7 +27077,7 @@
         <v>1.21</v>
       </c>
       <c r="Z164">
-        <v>3.62</v>
+        <v>3.25</v>
       </c>
       <c r="AA164">
         <v>1.83</v>
@@ -27086,10 +27086,10 @@
         <v>1.95</v>
       </c>
       <c r="AC164">
-        <v>2.72</v>
+        <v>3.2</v>
       </c>
       <c r="AD164">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE164">
         <v>1.09</v>
@@ -27204,13 +27204,13 @@
         </is>
       </c>
       <c r="N165">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="O165">
+        <v>3.44</v>
+      </c>
+      <c r="P165">
         <v>3.2</v>
-      </c>
-      <c r="P165">
-        <v>3.35</v>
       </c>
       <c r="Q165">
         <v>2.59</v>
@@ -27219,10 +27219,10 @@
         <v>2.12</v>
       </c>
       <c r="S165">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T165">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="U165">
         <v>2.66</v>
@@ -27246,10 +27246,10 @@
         <v>1.95</v>
       </c>
       <c r="AB165">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="AC165">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="AD165">
         <v>1.29</v>
@@ -27258,10 +27258,10 @@
         <v>1.08</v>
       </c>
       <c r="AF165">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG165">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AH165" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>1.3</v>
       </c>
       <c r="AK165">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AL165">
         <v>0</v>
@@ -27376,7 +27376,7 @@
         <v>3.59</v>
       </c>
       <c r="Q166">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="R166">
         <v>2.14</v>
@@ -27397,16 +27397,16 @@
         <v>1.06</v>
       </c>
       <c r="X166">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y166">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Z166">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="AA166">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="AB166">
         <v>1.9</v>
@@ -27418,10 +27418,10 @@
         <v>1.29</v>
       </c>
       <c r="AE166">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF166">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AG166">
         <v>1.9</v>
@@ -27533,19 +27533,19 @@
         <v>2</v>
       </c>
       <c r="O167">
+        <v>3.25</v>
+      </c>
+      <c r="P167">
         <v>3.4</v>
       </c>
-      <c r="P167">
-        <v>3.35</v>
-      </c>
       <c r="Q167">
-        <v>2.57</v>
+        <v>2.65</v>
       </c>
       <c r="R167">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="S167">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T167">
         <v>2.88</v>
@@ -27554,16 +27554,16 @@
         <v>2.69</v>
       </c>
       <c r="V167">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W167">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X167">
         <v>1.01</v>
       </c>
       <c r="Y167">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z167">
         <v>3.55</v>
@@ -27572,19 +27572,19 @@
         <v>1.86</v>
       </c>
       <c r="AB167">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AC167">
         <v>3.4</v>
       </c>
       <c r="AD167">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE167">
         <v>1.09</v>
       </c>
       <c r="AF167">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AG167">
         <v>2</v>
@@ -27693,10 +27693,10 @@
         </is>
       </c>
       <c r="N168">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="O168">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P168">
         <v>1.75</v>
@@ -27856,13 +27856,13 @@
         </is>
       </c>
       <c r="N169">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="O169">
         <v>3.9</v>
       </c>
       <c r="P169">
-        <v>5.46</v>
+        <v>5.41</v>
       </c>
       <c r="Q169">
         <v>0</v>
@@ -28671,13 +28671,13 @@
         </is>
       </c>
       <c r="N174">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="O174">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P174">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="Q174">
         <v>3</v>
@@ -28692,7 +28692,7 @@
         <v>2.7</v>
       </c>
       <c r="U174">
-        <v>2.57</v>
+        <v>2.74</v>
       </c>
       <c r="V174">
         <v>1.43</v>
@@ -28710,7 +28710,7 @@
         <v>3.4</v>
       </c>
       <c r="AA174">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AB174">
         <v>1.83</v>
@@ -28741,10 +28741,10 @@
         </is>
       </c>
       <c r="AJ174">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK174">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL174">
         <v>0</v>
@@ -28834,13 +28834,13 @@
         </is>
       </c>
       <c r="N175">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O175">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P175">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q175">
         <v>2.8</v>
@@ -28852,13 +28852,13 @@
         <v>1.21</v>
       </c>
       <c r="T175">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U175">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V175">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W175">
         <v>1.18</v>
@@ -28882,10 +28882,10 @@
         <v>2.07</v>
       </c>
       <c r="AD175">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AE175">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF175">
         <v>1.4</v>
@@ -28904,7 +28904,7 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK175">
         <v>1.53</v>
@@ -28997,10 +28997,10 @@
         </is>
       </c>
       <c r="N176">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O176">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="P176">
         <v>3.7</v>
@@ -29018,7 +29018,7 @@
         <v>2.05</v>
       </c>
       <c r="U176">
-        <v>3.8</v>
+        <v>4.15</v>
       </c>
       <c r="V176">
         <v>1.16</v>
@@ -29027,28 +29027,28 @@
         <v>1.03</v>
       </c>
       <c r="X176">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y176">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="Z176">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AA176">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AB176">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AC176">
-        <v>5.87</v>
+        <v>6.15</v>
       </c>
       <c r="AD176">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AE176">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF176">
         <v>2.42</v>
@@ -29326,22 +29326,22 @@
         <v>2.15</v>
       </c>
       <c r="O178">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P178">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q178">
         <v>2.63</v>
       </c>
       <c r="R178">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="S178">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T178">
-        <v>2.98</v>
+        <v>2.7</v>
       </c>
       <c r="U178">
         <v>2.88</v>
@@ -29350,10 +29350,10 @@
         <v>1.36</v>
       </c>
       <c r="W178">
+        <v>1.07</v>
+      </c>
+      <c r="X178">
         <v>1.05</v>
-      </c>
-      <c r="X178">
-        <v>1.01</v>
       </c>
       <c r="Y178">
         <v>1.22</v>
@@ -29362,10 +29362,10 @@
         <v>3.47</v>
       </c>
       <c r="AA178">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB178">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AC178">
         <v>3.28</v>
@@ -29393,10 +29393,10 @@
         </is>
       </c>
       <c r="AJ178">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK178">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -29489,16 +29489,16 @@
         <v>1.48</v>
       </c>
       <c r="O179">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="P179">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="Q179">
         <v>1.91</v>
       </c>
       <c r="R179">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="S179">
         <v>1.2</v>
@@ -29513,7 +29513,7 @@
         <v>1.7</v>
       </c>
       <c r="W179">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X179">
         <v>1.03</v>
@@ -29531,13 +29531,13 @@
         <v>2.39</v>
       </c>
       <c r="AC179">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AD179">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AE179">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF179">
         <v>1.62</v>
@@ -29556,7 +29556,7 @@
         </is>
       </c>
       <c r="AJ179">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AK179">
         <v>2.72</v>
@@ -29649,19 +29649,19 @@
         </is>
       </c>
       <c r="N180">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="O180">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="P180">
         <v>2.85</v>
       </c>
       <c r="Q180">
-        <v>2.85</v>
+        <v>2.76</v>
       </c>
       <c r="R180">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="S180">
         <v>1.4</v>
@@ -29673,40 +29673,40 @@
         <v>2.88</v>
       </c>
       <c r="V180">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W180">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X180">
         <v>1.04</v>
       </c>
       <c r="Y180">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z180">
         <v>2.88</v>
       </c>
       <c r="AA180">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB180">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AC180">
-        <v>3.91</v>
+        <v>3.88</v>
       </c>
       <c r="AD180">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE180">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF180">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AG180">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH180" t="inlineStr">
         <is>
@@ -29812,13 +29812,13 @@
         </is>
       </c>
       <c r="N181">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O181">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="P181">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Q181">
         <v>9</v>
@@ -29833,10 +29833,10 @@
         <v>4</v>
       </c>
       <c r="U181">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="V181">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W181">
         <v>1.17</v>
@@ -29848,19 +29848,19 @@
         <v>1.13</v>
       </c>
       <c r="Z181">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AA181">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AB181">
         <v>2.32</v>
       </c>
       <c r="AC181">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AD181">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AE181">
         <v>1.22</v>
@@ -29882,7 +29882,7 @@
         </is>
       </c>
       <c r="AJ181">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AK181">
         <v>1.02</v>
@@ -29975,13 +29975,13 @@
         </is>
       </c>
       <c r="N182">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O182">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P182">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q182">
         <v>0</v>
@@ -30138,64 +30138,64 @@
         </is>
       </c>
       <c r="N183">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O183">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P183">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q183">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R183">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S183">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T183">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U183">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V183">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W183">
         <v>0</v>
       </c>
       <c r="X183">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y183">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z183">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA183">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB183">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC183">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD183">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE183">
         <v>0</v>
       </c>
       <c r="AF183">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG183">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH183" t="inlineStr">
         <is>
@@ -30208,10 +30208,10 @@
         </is>
       </c>
       <c r="AJ183">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK183">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL183">
         <v>0</v>
@@ -30301,34 +30301,34 @@
         </is>
       </c>
       <c r="N184">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O184">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P184">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q184">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="R184">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="S184">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T184">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="U184">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="V184">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="W184">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X184">
         <v>1.03</v>
@@ -30340,16 +30340,16 @@
         <v>4.33</v>
       </c>
       <c r="AA184">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AB184">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AC184">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="AD184">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE184">
         <v>1.17</v>
@@ -30371,10 +30371,10 @@
         </is>
       </c>
       <c r="AJ184">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AK184">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AL184">
         <v>0</v>
@@ -30627,13 +30627,13 @@
         </is>
       </c>
       <c r="N186">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O186">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P186">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q186">
         <v>0</v>
@@ -30666,10 +30666,10 @@
         <v>0</v>
       </c>
       <c r="AA186">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB186">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC186">
         <v>0</v>
@@ -30790,13 +30790,13 @@
         </is>
       </c>
       <c r="N187">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="O187">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="P187">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Q187">
         <v>1.53</v>
@@ -30832,7 +30832,7 @@
         <v>1.25</v>
       </c>
       <c r="AB187">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="AC187">
         <v>1.66</v>
@@ -31294,7 +31294,7 @@
         <v>2.38</v>
       </c>
       <c r="S190">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T190">
         <v>3.1</v>
@@ -31312,28 +31312,28 @@
         <v>1.04</v>
       </c>
       <c r="Y190">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z190">
-        <v>3.8</v>
+        <v>3.89</v>
       </c>
       <c r="AA190">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AB190">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="AC190">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="AD190">
         <v>1.36</v>
       </c>
       <c r="AE190">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF190">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG190">
         <v>1.91</v>
@@ -31442,19 +31442,19 @@
         </is>
       </c>
       <c r="N191">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O191">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="P191">
-        <v>0</v>
+        <v>6.02</v>
       </c>
       <c r="Q191">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="R191">
-        <v>2.12</v>
+        <v>1.99</v>
       </c>
       <c r="S191">
         <v>1.45</v>
@@ -31469,7 +31469,7 @@
         <v>1.3</v>
       </c>
       <c r="W191">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X191">
         <v>1.07</v>
@@ -31481,13 +31481,13 @@
         <v>2.75</v>
       </c>
       <c r="AA191">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB191">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AC191">
-        <v>3.86</v>
+        <v>3.85</v>
       </c>
       <c r="AD191">
         <v>1.18</v>
@@ -31496,10 +31496,10 @@
         <v>1.07</v>
       </c>
       <c r="AF191">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AG191">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AH191" t="inlineStr">
         <is>
@@ -31605,16 +31605,16 @@
         </is>
       </c>
       <c r="N192">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="O192">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="P192">
-        <v>3.55</v>
+        <v>4.25</v>
       </c>
       <c r="Q192">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="R192">
         <v>2</v>
@@ -31632,13 +31632,13 @@
         <v>1.25</v>
       </c>
       <c r="W192">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X192">
         <v>1.1</v>
       </c>
       <c r="Y192">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Z192">
         <v>2.44</v>
@@ -31647,7 +31647,7 @@
         <v>2.33</v>
       </c>
       <c r="AB192">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AC192">
         <v>5</v>
@@ -31656,7 +31656,7 @@
         <v>1.17</v>
       </c>
       <c r="AE192">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AF192">
         <v>2.1</v>
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,64 +31768,64 @@
         </is>
       </c>
       <c r="N193">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O193">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P193">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q193">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R193">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S193">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T193">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U193">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V193">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W193">
         <v>0</v>
       </c>
       <c r="X193">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y193">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z193">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA193">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB193">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC193">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD193">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE193">
         <v>0</v>
       </c>
       <c r="AF193">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG193">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31838,10 +31838,10 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK193">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G194">
@@ -31931,31 +31931,31 @@
         </is>
       </c>
       <c r="N194">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O194">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P194">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q194">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R194">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S194">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T194">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U194">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V194">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W194">
         <v>0</v>
@@ -31964,31 +31964,31 @@
         <v>0</v>
       </c>
       <c r="Y194">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z194">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA194">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB194">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC194">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD194">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE194">
         <v>0</v>
       </c>
       <c r="AF194">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG194">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH194" t="inlineStr">
         <is>
@@ -32001,10 +32001,10 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK194">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32094,13 +32094,13 @@
         </is>
       </c>
       <c r="N195">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O195">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P195">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q195">
         <v>2.3</v>
@@ -32109,43 +32109,43 @@
         <v>2.3</v>
       </c>
       <c r="S195">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T195">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="U195">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="V195">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="W195">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X195">
         <v>1.03</v>
       </c>
       <c r="Y195">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z195">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="AA195">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB195">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AC195">
-        <v>2.4</v>
+        <v>2.66</v>
       </c>
       <c r="AD195">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE195">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF195">
         <v>1.53</v>
@@ -34050,13 +34050,13 @@
         </is>
       </c>
       <c r="N207">
-        <v>4.75</v>
+        <v>3.69</v>
       </c>
       <c r="O207">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="P207">
-        <v>1.55</v>
+        <v>1.88</v>
       </c>
       <c r="Q207">
         <v>0</v>
@@ -34089,10 +34089,10 @@
         <v>0</v>
       </c>
       <c r="AA207">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AB207">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AC207">
         <v>0</v>
@@ -34228,16 +34228,16 @@
         <v>2.05</v>
       </c>
       <c r="S208">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="T208">
-        <v>2.31</v>
+        <v>2.6</v>
       </c>
       <c r="U208">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="V208">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W208">
         <v>1.04</v>
@@ -34283,10 +34283,10 @@
         </is>
       </c>
       <c r="AJ208">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK208">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AL208">
         <v>0</v>
@@ -34560,7 +34560,7 @@
         <v>3.2</v>
       </c>
       <c r="U210">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="V210">
         <v>1.48</v>

--- a/jogos_2026-08-08.xlsx
+++ b/jogos_2026-08-08.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="O4">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P4">
-        <v>2.7</v>
+        <v>1.73</v>
       </c>
       <c r="Q4">
-        <v>2.4</v>
+        <v>5.18</v>
       </c>
       <c r="R4">
-        <v>2.36</v>
+        <v>2.12</v>
       </c>
       <c r="S4">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="T4">
-        <v>3.75</v>
+        <v>2.9</v>
       </c>
       <c r="U4">
-        <v>2.13</v>
+        <v>2.75</v>
       </c>
       <c r="V4">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="W4">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
         <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="Z4">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA4">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AB4">
-        <v>2.5</v>
+        <v>1.93</v>
       </c>
       <c r="AC4">
-        <v>2.16</v>
+        <v>3.1</v>
       </c>
       <c r="AD4">
-        <v>1.66</v>
+        <v>1.33</v>
       </c>
       <c r="AE4">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AF4">
-        <v>1.39</v>
+        <v>1.75</v>
       </c>
       <c r="AG4">
-        <v>2.69</v>
+        <v>1.82</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK4">
-        <v>1.56</v>
+        <v>1.13</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="O5">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P5">
-        <v>1.73</v>
+        <v>2.7</v>
       </c>
       <c r="Q5">
-        <v>5.18</v>
+        <v>2.4</v>
       </c>
       <c r="R5">
-        <v>2.12</v>
+        <v>2.36</v>
       </c>
       <c r="S5">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="T5">
-        <v>2.9</v>
+        <v>3.75</v>
       </c>
       <c r="U5">
-        <v>2.75</v>
+        <v>2.13</v>
       </c>
       <c r="V5">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="W5">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X5">
         <v>1.02</v>
       </c>
       <c r="Y5">
+        <v>1.1</v>
+      </c>
+      <c r="Z5">
+        <v>4.5</v>
+      </c>
+      <c r="AA5">
+        <v>1.5</v>
+      </c>
+      <c r="AB5">
+        <v>2.5</v>
+      </c>
+      <c r="AC5">
+        <v>2.16</v>
+      </c>
+      <c r="AD5">
+        <v>1.66</v>
+      </c>
+      <c r="AE5">
         <v>1.25</v>
       </c>
-      <c r="Z5">
-        <v>3.6</v>
-      </c>
-      <c r="AA5">
-        <v>1.8</v>
-      </c>
-      <c r="AB5">
-        <v>1.93</v>
-      </c>
-      <c r="AC5">
-        <v>3.1</v>
-      </c>
-      <c r="AD5">
-        <v>1.33</v>
-      </c>
-      <c r="AE5">
-        <v>1.12</v>
-      </c>
       <c r="AF5">
-        <v>1.75</v>
+        <v>1.39</v>
       </c>
       <c r="AG5">
-        <v>1.82</v>
+        <v>2.69</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK5">
-        <v>1.13</v>
+        <v>1.56</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="O37">
-        <v>3.7</v>
+        <v>3.82</v>
       </c>
       <c r="P37">
-        <v>3.85</v>
+        <v>5.31</v>
       </c>
       <c r="Q37">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="R37">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="S37">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T37">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="U37">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="V37">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W37">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X37">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y37">
         <v>1.2</v>
       </c>
       <c r="Z37">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="AA37">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="AB37">
         <v>2.08</v>
       </c>
       <c r="AC37">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AD37">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AE37">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF37">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AG37">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK37">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="O39">
-        <v>3.82</v>
+        <v>3.7</v>
       </c>
       <c r="P39">
-        <v>5.31</v>
+        <v>3.85</v>
       </c>
       <c r="Q39">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="R39">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="S39">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T39">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="U39">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="V39">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W39">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X39">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
         <v>1.2</v>
       </c>
       <c r="Z39">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="AA39">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="AB39">
         <v>2.08</v>
       </c>
       <c r="AC39">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AD39">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE39">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF39">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG39">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK39">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O126">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P126">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q126">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R126">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S126">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T126">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U126">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V126">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W126">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X126">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y126">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z126">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA126">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB126">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC126">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD126">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE126">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF126">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG126">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK126">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G161">
@@ -26552,64 +26552,64 @@
         </is>
       </c>
       <c r="N161">
-        <v>2.47</v>
+        <v>3.75</v>
       </c>
       <c r="O161">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P161">
-        <v>2.62</v>
+        <v>1.95</v>
       </c>
       <c r="Q161">
-        <v>3</v>
+        <v>4.58</v>
       </c>
       <c r="R161">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="S161">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="T161">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="U161">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="V161">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W161">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X161">
         <v>1.06</v>
       </c>
       <c r="Y161">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z161">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="AA161">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB161">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC161">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AD161">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE161">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF161">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AG161">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>1.33</v>
+        <v>1.81</v>
       </c>
       <c r="AK161">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G162">
@@ -26715,64 +26715,64 @@
         </is>
       </c>
       <c r="N162">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="O162">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P162">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q162">
-        <v>4.58</v>
+        <v>4.2</v>
       </c>
       <c r="R162">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="S162">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="T162">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="U162">
-        <v>2.94</v>
+        <v>2.77</v>
       </c>
       <c r="V162">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W162">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X162">
         <v>1.06</v>
       </c>
       <c r="Y162">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z162">
-        <v>3.09</v>
+        <v>3.25</v>
       </c>
       <c r="AA162">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AB162">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="AC162">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AD162">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AE162">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF162">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AG162">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
@@ -26785,10 +26785,10 @@
         </is>
       </c>
       <c r="AJ162">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="AK162">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AL162">
         <v>0</v>
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G163">
@@ -26878,64 +26878,64 @@
         </is>
       </c>
       <c r="N163">
-        <v>3.55</v>
+        <v>2.45</v>
       </c>
       <c r="O163">
+        <v>3.25</v>
+      </c>
+      <c r="P163">
+        <v>2.5</v>
+      </c>
+      <c r="Q163">
         <v>3.1</v>
       </c>
-      <c r="P163">
-        <v>2</v>
-      </c>
-      <c r="Q163">
-        <v>4.2</v>
-      </c>
       <c r="R163">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S163">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T163">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="U163">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="V163">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="W163">
+        <v>1.07</v>
+      </c>
+      <c r="X163">
         <v>1.05</v>
       </c>
-      <c r="X163">
-        <v>1.06</v>
-      </c>
       <c r="Y163">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="Z163">
         <v>3.25</v>
       </c>
       <c r="AA163">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AB163">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AC163">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="AD163">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AE163">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF163">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AG163">
-        <v>1.85</v>
+        <v>2.19</v>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
@@ -26948,10 +26948,10 @@
         </is>
       </c>
       <c r="AJ163">
-        <v>1.74</v>
+        <v>1.29</v>
       </c>
       <c r="AK163">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G164">
@@ -27041,64 +27041,64 @@
         </is>
       </c>
       <c r="N164">
-        <v>2.45</v>
+        <v>2.06</v>
       </c>
       <c r="O164">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="P164">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="Q164">
-        <v>3.1</v>
+        <v>2.59</v>
       </c>
       <c r="R164">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="S164">
         <v>1.36</v>
       </c>
       <c r="T164">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="U164">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="V164">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W164">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X164">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y164">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="Z164">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AA164">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AB164">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AC164">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="AD164">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AE164">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF164">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AG164">
-        <v>2.19</v>
+        <v>1.86</v>
       </c>
       <c r="AH164" t="inlineStr">
         <is>
@@ -27111,10 +27111,10 @@
         </is>
       </c>
       <c r="AJ164">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK164">
-        <v>1.48</v>
+        <v>1.72</v>
       </c>
       <c r="AL164">
         <v>0</v>
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G165">
@@ -27204,28 +27204,28 @@
         </is>
       </c>
       <c r="N165">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="O165">
-        <v>3.44</v>
+        <v>3.52</v>
       </c>
       <c r="P165">
-        <v>3.2</v>
+        <v>3.59</v>
       </c>
       <c r="Q165">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="R165">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="S165">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T165">
-        <v>2.9</v>
+        <v>2.67</v>
       </c>
       <c r="U165">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="V165">
         <v>1.4</v>
@@ -27234,34 +27234,34 @@
         <v>1.06</v>
       </c>
       <c r="X165">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y165">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="Z165">
+        <v>3.38</v>
+      </c>
+      <c r="AA165">
+        <v>1.96</v>
+      </c>
+      <c r="AB165">
+        <v>1.9</v>
+      </c>
+      <c r="AC165">
         <v>3.4</v>
-      </c>
-      <c r="AA165">
-        <v>1.95</v>
-      </c>
-      <c r="AB165">
-        <v>1.89</v>
-      </c>
-      <c r="AC165">
-        <v>3.05</v>
       </c>
       <c r="AD165">
         <v>1.29</v>
       </c>
       <c r="AE165">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF165">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AG165">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AH165" t="inlineStr">
         <is>
@@ -27274,10 +27274,10 @@
         </is>
       </c>
       <c r="AJ165">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK165">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AL165">
         <v>0</v>
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G166">
@@ -27367,64 +27367,64 @@
         </is>
       </c>
       <c r="N166">
-        <v>1.98</v>
+        <v>2.47</v>
       </c>
       <c r="O166">
-        <v>3.52</v>
+        <v>3.25</v>
       </c>
       <c r="P166">
-        <v>3.59</v>
+        <v>2.62</v>
       </c>
       <c r="Q166">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="R166">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="S166">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T166">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="U166">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="V166">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W166">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X166">
         <v>1.06</v>
       </c>
       <c r="Y166">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="Z166">
-        <v>3.38</v>
+        <v>3</v>
       </c>
       <c r="AA166">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="AB166">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AC166">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="AD166">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE166">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF166">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AG166">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH166" t="inlineStr">
         <is>
@@ -27437,10 +27437,10 @@
         </is>
       </c>
       <c r="AJ166">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK166">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AL166">
         <v>0</v>
@@ -28019,64 +28019,64 @@
         </is>
       </c>
       <c r="N170">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O170">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P170">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q170">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R170">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S170">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T170">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U170">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V170">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W170">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X170">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y170">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z170">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA170">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB170">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC170">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD170">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE170">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF170">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG170">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH170" t="inlineStr">
         <is>
@@ -28089,10 +28089,10 @@
         </is>
       </c>
       <c r="AJ170">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK170">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL170">
         <v>0</v>
@@ -28508,13 +28508,13 @@
         </is>
       </c>
       <c r="N173">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="O173">
         <v>3.3</v>
       </c>
       <c r="P173">
-        <v>3.03</v>
+        <v>2.9</v>
       </c>
       <c r="Q173">
         <v>2.9</v>
@@ -28523,19 +28523,19 @@
         <v>2.1</v>
       </c>
       <c r="S173">
+        <v>1.4</v>
+      </c>
+      <c r="T173">
+        <v>2.82</v>
+      </c>
+      <c r="U173">
+        <v>2.8</v>
+      </c>
+      <c r="V173">
         <v>1.38</v>
       </c>
-      <c r="T173">
-        <v>2.88</v>
-      </c>
-      <c r="U173">
-        <v>2.75</v>
-      </c>
-      <c r="V173">
-        <v>1.4</v>
-      </c>
       <c r="W173">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X173">
         <v>1.07</v>
@@ -28544,7 +28544,7 @@
         <v>1.33</v>
       </c>
       <c r="Z173">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="AA173">
         <v>2.11</v>
@@ -28556,7 +28556,7 @@
         <v>3.7</v>
       </c>
       <c r="AD173">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE173">
         <v>1.08</v>
@@ -28565,7 +28565,7 @@
         <v>1.71</v>
       </c>
       <c r="AG173">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AH173" t="inlineStr">
         <is>
@@ -30467,77 +30467,77 @@
         <v>2.25</v>
       </c>
       <c r="O185">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="P185">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="Q185">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="R185">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="S185">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T185">
-        <v>3.2</v>
+        <v>3.27</v>
       </c>
       <c r="U185">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="V185">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W185">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X185">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y185">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z185">
-        <v>4.06</v>
+        <v>3.75</v>
       </c>
       <c r="AA185">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB185">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC185">
         <v>2.9</v>
       </c>
       <c r="AD185">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AE185">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF185">
+        <v>1.62</v>
+      </c>
+      <c r="AG185">
+        <v>2.15</v>
+      </c>
+      <c r="AH185" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI185" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ185">
+        <v>1.25</v>
+      </c>
+      <c r="AK185">
         <v>1.57</v>
-      </c>
-      <c r="AG185">
-        <v>2.27</v>
-      </c>
-      <c r="AH185" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI185" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ185">
-        <v>1.43</v>
-      </c>
-      <c r="AK185">
-        <v>1.53</v>
       </c>
       <c r="AL185">
         <v>0</v>
@@ -30953,64 +30953,64 @@
         </is>
       </c>
       <c r="N188">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O188">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P188">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q188">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R188">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S188">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T188">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U188">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V188">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W188">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X188">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y188">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z188">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA188">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB188">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC188">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD188">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE188">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF188">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG188">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31023,10 +31023,10 @@
         </is>
       </c>
       <c r="AJ188">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK188">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -31116,16 +31116,16 @@
         </is>
       </c>
       <c r="N189">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="O189">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P189">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="Q189">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="R189">
         <v>2.05</v>
@@ -31146,34 +31146,34 @@
         <v>1.03</v>
       </c>
       <c r="X189">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y189">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z189">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="AA189">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AB189">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC189">
-        <v>3.62</v>
+        <v>3.85</v>
       </c>
       <c r="AD189">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AE189">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF189">
         <v>1.8</v>
       </c>
       <c r="AG189">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AH189" t="inlineStr">
         <is>
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,64 +31768,64 @@
         </is>
       </c>
       <c r="N193">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="O193">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P193">
         <v>4</v>
       </c>
       <c r="Q193">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="R193">
-        <v>1.91</v>
+        <v>2.14</v>
       </c>
       <c r="S193">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="T193">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U193">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="V193">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W193">
         <v>0</v>
       </c>
       <c r="X193">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y193">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="Z193">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AA193">
-        <v>2.23</v>
+        <v>2.08</v>
       </c>
       <c r="AB193">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="AC193">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="AD193">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE193">
         <v>0</v>
       </c>
       <c r="AF193">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="AG193">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31838,10 +31838,10 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AK193">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G194">
@@ -31931,64 +31931,64 @@
         </is>
       </c>
       <c r="N194">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="O194">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P194">
         <v>4</v>
       </c>
       <c r="Q194">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="R194">
-        <v>2.14</v>
+        <v>1.91</v>
       </c>
       <c r="S194">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="T194">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U194">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="V194">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W194">
         <v>0</v>
       </c>
       <c r="X194">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y194">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="Z194">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AA194">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
       <c r="AB194">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="AC194">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AD194">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE194">
         <v>0</v>
       </c>
       <c r="AF194">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="AG194">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AH194" t="inlineStr">
         <is>
@@ -32001,10 +32001,10 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AK194">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -33078,58 +33078,58 @@
         <v>3.9</v>
       </c>
       <c r="P201">
-        <v>5.25</v>
+        <v>4.7</v>
       </c>
       <c r="Q201">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R201">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S201">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T201">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U201">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V201">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W201">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X201">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y201">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z201">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA201">
         <v>1.95</v>
       </c>
       <c r="AB201">
+        <v>1.86</v>
+      </c>
+      <c r="AC201">
+        <v>3.4</v>
+      </c>
+      <c r="AD201">
+        <v>1.32</v>
+      </c>
+      <c r="AE201">
+        <v>1.09</v>
+      </c>
+      <c r="AF201">
         <v>1.85</v>
       </c>
-      <c r="AC201">
-        <v>0</v>
-      </c>
-      <c r="AD201">
-        <v>0</v>
-      </c>
-      <c r="AE201">
-        <v>0</v>
-      </c>
-      <c r="AF201">
-        <v>0</v>
-      </c>
       <c r="AG201">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH201" t="inlineStr">
         <is>
@@ -33142,10 +33142,10 @@
         </is>
       </c>
       <c r="AJ201">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK201">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AL201">
         <v>0</v>
@@ -33561,64 +33561,64 @@
         </is>
       </c>
       <c r="N204">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O204">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P204">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q204">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R204">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S204">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T204">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="U204">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V204">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W204">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X204">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y204">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z204">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA204">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB204">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC204">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD204">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE204">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF204">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG204">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH204" t="inlineStr">
         <is>
@@ -33631,10 +33631,10 @@
         </is>
       </c>
       <c r="AJ204">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK204">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL204">
         <v>0</v>
@@ -33724,16 +33724,16 @@
         </is>
       </c>
       <c r="N205">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="O205">
-        <v>3.35</v>
+        <v>3.13</v>
       </c>
       <c r="P205">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="Q205">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="R205">
         <v>1.95</v>
@@ -33751,25 +33751,25 @@
         <v>1.4</v>
       </c>
       <c r="W205">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X205">
         <v>1.03</v>
       </c>
       <c r="Y205">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z205">
         <v>3.4</v>
       </c>
       <c r="AA205">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="AB205">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AC205">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AD205">
         <v>1.29</v>

--- a/jogos_2026-08-08.xlsx
+++ b/jogos_2026-08-08.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.37</v>
+        <v>2</v>
       </c>
       <c r="O6">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="P6">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="Q6">
-        <v>3</v>
+        <v>2.48</v>
       </c>
       <c r="R6">
-        <v>2.25</v>
+        <v>2.43</v>
       </c>
       <c r="S6">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="T6">
-        <v>3.08</v>
+        <v>3.34</v>
       </c>
       <c r="U6">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="V6">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="W6">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X6">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
         <v>1.18</v>
       </c>
       <c r="Z6">
-        <v>3.9</v>
+        <v>4.65</v>
       </c>
       <c r="AA6">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AB6">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="AC6">
-        <v>2.82</v>
+        <v>2.25</v>
       </c>
       <c r="AD6">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AE6">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="AF6">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AG6">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK6">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2</v>
+        <v>2.37</v>
       </c>
       <c r="O7">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="P7">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q7">
-        <v>2.48</v>
+        <v>3</v>
       </c>
       <c r="R7">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="S7">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="T7">
-        <v>3.34</v>
+        <v>3.08</v>
       </c>
       <c r="U7">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="V7">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="W7">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y7">
         <v>1.18</v>
       </c>
       <c r="Z7">
-        <v>4.65</v>
+        <v>3.9</v>
       </c>
       <c r="AA7">
+        <v>1.75</v>
+      </c>
+      <c r="AB7">
+        <v>2</v>
+      </c>
+      <c r="AC7">
+        <v>2.82</v>
+      </c>
+      <c r="AD7">
+        <v>1.39</v>
+      </c>
+      <c r="AE7">
+        <v>1.09</v>
+      </c>
+      <c r="AF7">
         <v>1.6</v>
       </c>
-      <c r="AB7">
-        <v>2.24</v>
-      </c>
-      <c r="AC7">
-        <v>2.25</v>
-      </c>
-      <c r="AD7">
-        <v>1.5</v>
-      </c>
-      <c r="AE7">
-        <v>1.19</v>
-      </c>
-      <c r="AF7">
-        <v>1.47</v>
-      </c>
       <c r="AG7">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK7">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,80 +6503,80 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="O38">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="P38">
-        <v>3</v>
+        <v>3.85</v>
       </c>
       <c r="Q38">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="R38">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="S38">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T38">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="U38">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="V38">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="W38">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X38">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z38">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="AA38">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB38">
-        <v>2.45</v>
+        <v>2.08</v>
       </c>
       <c r="AC38">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="AD38">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AE38">
+        <v>1.13</v>
+      </c>
+      <c r="AF38">
+        <v>1.57</v>
+      </c>
+      <c r="AG38">
+        <v>2.18</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38">
         <v>1.18</v>
       </c>
-      <c r="AF38">
-        <v>1.44</v>
-      </c>
-      <c r="AG38">
-        <v>2.43</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ38">
-        <v>1.36</v>
-      </c>
       <c r="AK38">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="O39">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="P39">
-        <v>3.85</v>
+        <v>3</v>
       </c>
       <c r="Q39">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="R39">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="S39">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T39">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="U39">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="V39">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="W39">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y39">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z39">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="AA39">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB39">
-        <v>2.08</v>
+        <v>2.45</v>
       </c>
       <c r="AC39">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="AD39">
+        <v>1.55</v>
+      </c>
+      <c r="AE39">
+        <v>1.18</v>
+      </c>
+      <c r="AF39">
         <v>1.44</v>
       </c>
-      <c r="AE39">
-        <v>1.13</v>
-      </c>
-      <c r="AF39">
-        <v>1.57</v>
-      </c>
       <c r="AG39">
-        <v>2.18</v>
+        <v>2.43</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AK39">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,80 +6992,80 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.81</v>
+        <v>3.6</v>
       </c>
       <c r="O41">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="P41">
-        <v>3.95</v>
+        <v>2</v>
       </c>
       <c r="Q41">
-        <v>2.37</v>
+        <v>4</v>
       </c>
       <c r="R41">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="S41">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T41">
-        <v>2.94</v>
+        <v>2.62</v>
       </c>
       <c r="U41">
-        <v>2.71</v>
+        <v>2.9</v>
       </c>
       <c r="V41">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W41">
         <v>1.06</v>
       </c>
       <c r="X41">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y41">
+        <v>1.36</v>
+      </c>
+      <c r="Z41">
+        <v>2.83</v>
+      </c>
+      <c r="AA41">
+        <v>2.12</v>
+      </c>
+      <c r="AB41">
+        <v>1.63</v>
+      </c>
+      <c r="AC41">
+        <v>3.76</v>
+      </c>
+      <c r="AD41">
+        <v>1.19</v>
+      </c>
+      <c r="AE41">
+        <v>1.03</v>
+      </c>
+      <c r="AF41">
+        <v>1.91</v>
+      </c>
+      <c r="AG41">
+        <v>1.81</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41">
+        <v>1.33</v>
+      </c>
+      <c r="AK41">
         <v>1.25</v>
-      </c>
-      <c r="Z41">
-        <v>3.4</v>
-      </c>
-      <c r="AA41">
-        <v>1.9</v>
-      </c>
-      <c r="AB41">
-        <v>1.9</v>
-      </c>
-      <c r="AC41">
-        <v>3.1</v>
-      </c>
-      <c r="AD41">
-        <v>1.3</v>
-      </c>
-      <c r="AE41">
-        <v>1.08</v>
-      </c>
-      <c r="AF41">
-        <v>1.75</v>
-      </c>
-      <c r="AG41">
-        <v>1.95</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ41">
-        <v>1.29</v>
-      </c>
-      <c r="AK41">
-        <v>1.83</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,55 +7155,55 @@
         </is>
       </c>
       <c r="N42">
+        <v>3.05</v>
+      </c>
+      <c r="O42">
+        <v>2.95</v>
+      </c>
+      <c r="P42">
+        <v>2.25</v>
+      </c>
+      <c r="Q42">
         <v>3.6</v>
       </c>
-      <c r="O42">
-        <v>3.05</v>
-      </c>
-      <c r="P42">
+      <c r="R42">
         <v>2</v>
-      </c>
-      <c r="Q42">
-        <v>4</v>
-      </c>
-      <c r="R42">
-        <v>2.05</v>
       </c>
       <c r="S42">
         <v>1.4</v>
       </c>
       <c r="T42">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="U42">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="V42">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W42">
         <v>1.06</v>
       </c>
       <c r="X42">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y42">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z42">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="AA42">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="AB42">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AC42">
-        <v>3.76</v>
+        <v>3.9</v>
       </c>
       <c r="AD42">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE42">
         <v>1.03</v>
@@ -7212,7 +7212,7 @@
         <v>1.91</v>
       </c>
       <c r="AG42">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK42">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>3.05</v>
+        <v>1.81</v>
       </c>
       <c r="O43">
-        <v>2.95</v>
+        <v>3.35</v>
       </c>
       <c r="P43">
-        <v>2.25</v>
+        <v>3.95</v>
       </c>
       <c r="Q43">
-        <v>3.6</v>
+        <v>2.37</v>
       </c>
       <c r="R43">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="S43">
+        <v>1.36</v>
+      </c>
+      <c r="T43">
+        <v>2.94</v>
+      </c>
+      <c r="U43">
+        <v>2.71</v>
+      </c>
+      <c r="V43">
         <v>1.4</v>
-      </c>
-      <c r="T43">
-        <v>2.6</v>
-      </c>
-      <c r="U43">
-        <v>3</v>
-      </c>
-      <c r="V43">
-        <v>1.3</v>
       </c>
       <c r="W43">
         <v>1.06</v>
       </c>
       <c r="X43">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="Z43">
-        <v>2.82</v>
+        <v>3.4</v>
       </c>
       <c r="AA43">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AB43">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AC43">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="AD43">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AE43">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF43">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AG43">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AK43">
-        <v>1.35</v>
+        <v>1.83</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -28834,22 +28834,22 @@
         </is>
       </c>
       <c r="N175">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="O175">
-        <v>3.66</v>
+        <v>3.6</v>
       </c>
       <c r="P175">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="Q175">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="R175">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="S175">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T175">
         <v>3.8</v>
@@ -28867,7 +28867,7 @@
         <v>1.02</v>
       </c>
       <c r="Y175">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z175">
         <v>5.65</v>
@@ -30808,13 +30808,13 @@
         <v>1.15</v>
       </c>
       <c r="T187">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="U187">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="V187">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="W187">
         <v>1.26</v>
@@ -30835,10 +30835,10 @@
         <v>3.3</v>
       </c>
       <c r="AC187">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AD187">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AE187">
         <v>1.44</v>
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,64 +31768,64 @@
         </is>
       </c>
       <c r="N193">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="O193">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P193">
         <v>4</v>
       </c>
       <c r="Q193">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="R193">
-        <v>2.14</v>
+        <v>1.91</v>
       </c>
       <c r="S193">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="T193">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U193">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="V193">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W193">
         <v>0</v>
       </c>
       <c r="X193">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y193">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="Z193">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AA193">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
       <c r="AB193">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="AC193">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AD193">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE193">
         <v>0</v>
       </c>
       <c r="AF193">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="AG193">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31838,10 +31838,10 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AK193">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G194">
@@ -31931,64 +31931,64 @@
         </is>
       </c>
       <c r="N194">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="O194">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P194">
         <v>4</v>
       </c>
       <c r="Q194">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="R194">
-        <v>1.91</v>
+        <v>2.14</v>
       </c>
       <c r="S194">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="T194">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U194">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="V194">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W194">
         <v>0</v>
       </c>
       <c r="X194">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y194">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="Z194">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AA194">
-        <v>2.23</v>
+        <v>2.08</v>
       </c>
       <c r="AB194">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="AC194">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="AD194">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE194">
         <v>0</v>
       </c>
       <c r="AF194">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="AG194">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AH194" t="inlineStr">
         <is>
@@ -32001,10 +32001,10 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AK194">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AL194">
         <v>0</v>

--- a/jogos_2026-08-08.xlsx
+++ b/jogos_2026-08-08.xlsx
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G166">
@@ -27367,65 +27367,65 @@
         </is>
       </c>
       <c r="N166">
-        <v>2.47</v>
+        <v>2</v>
       </c>
       <c r="O166">
         <v>3.25</v>
       </c>
       <c r="P166">
-        <v>2.62</v>
+        <v>3.4</v>
       </c>
       <c r="Q166">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="R166">
+        <v>2.25</v>
+      </c>
+      <c r="S166">
+        <v>1.36</v>
+      </c>
+      <c r="T166">
+        <v>2.88</v>
+      </c>
+      <c r="U166">
+        <v>2.69</v>
+      </c>
+      <c r="V166">
+        <v>1.4</v>
+      </c>
+      <c r="W166">
+        <v>1.05</v>
+      </c>
+      <c r="X166">
+        <v>1.01</v>
+      </c>
+      <c r="Y166">
+        <v>1.3</v>
+      </c>
+      <c r="Z166">
+        <v>3.55</v>
+      </c>
+      <c r="AA166">
+        <v>1.86</v>
+      </c>
+      <c r="AB166">
+        <v>1.88</v>
+      </c>
+      <c r="AC166">
+        <v>3.4</v>
+      </c>
+      <c r="AD166">
+        <v>1.29</v>
+      </c>
+      <c r="AE166">
+        <v>1.09</v>
+      </c>
+      <c r="AF166">
+        <v>1.69</v>
+      </c>
+      <c r="AG166">
         <v>2</v>
       </c>
-      <c r="S166">
-        <v>1.43</v>
-      </c>
-      <c r="T166">
-        <v>2.62</v>
-      </c>
-      <c r="U166">
-        <v>2.89</v>
-      </c>
-      <c r="V166">
-        <v>1.36</v>
-      </c>
-      <c r="W166">
-        <v>1.04</v>
-      </c>
-      <c r="X166">
-        <v>1.06</v>
-      </c>
-      <c r="Y166">
-        <v>1.33</v>
-      </c>
-      <c r="Z166">
-        <v>3</v>
-      </c>
-      <c r="AA166">
-        <v>2.05</v>
-      </c>
-      <c r="AB166">
-        <v>1.7</v>
-      </c>
-      <c r="AC166">
-        <v>3.75</v>
-      </c>
-      <c r="AD166">
-        <v>1.25</v>
-      </c>
-      <c r="AE166">
-        <v>1.08</v>
-      </c>
-      <c r="AF166">
-        <v>1.78</v>
-      </c>
-      <c r="AG166">
-        <v>1.91</v>
-      </c>
       <c r="AH166" t="inlineStr">
         <is>
           <t>[]</t>
@@ -27437,10 +27437,10 @@
         </is>
       </c>
       <c r="AJ166">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK166">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AL166">
         <v>0</v>
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G167">
@@ -27530,64 +27530,64 @@
         </is>
       </c>
       <c r="N167">
-        <v>2</v>
+        <v>2.47</v>
       </c>
       <c r="O167">
         <v>3.25</v>
       </c>
       <c r="P167">
-        <v>3.4</v>
+        <v>2.62</v>
       </c>
       <c r="Q167">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="R167">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="S167">
+        <v>1.43</v>
+      </c>
+      <c r="T167">
+        <v>2.62</v>
+      </c>
+      <c r="U167">
+        <v>2.89</v>
+      </c>
+      <c r="V167">
         <v>1.36</v>
       </c>
-      <c r="T167">
-        <v>2.88</v>
-      </c>
-      <c r="U167">
-        <v>2.69</v>
-      </c>
-      <c r="V167">
-        <v>1.4</v>
-      </c>
       <c r="W167">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X167">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y167">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z167">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="AA167">
-        <v>1.86</v>
+        <v>2.05</v>
       </c>
       <c r="AB167">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="AC167">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="AD167">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE167">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF167">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="AG167">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
@@ -27600,10 +27600,10 @@
         </is>
       </c>
       <c r="AJ167">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK167">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AL167">
         <v>0</v>
@@ -28834,16 +28834,16 @@
         </is>
       </c>
       <c r="N175">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O175">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P175">
         <v>2.45</v>
       </c>
       <c r="Q175">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="R175">
         <v>2.34</v>
@@ -28855,7 +28855,7 @@
         <v>3.8</v>
       </c>
       <c r="U175">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="V175">
         <v>1.65</v>
@@ -28867,7 +28867,7 @@
         <v>1.02</v>
       </c>
       <c r="Y175">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z175">
         <v>5.65</v>
@@ -28888,7 +28888,7 @@
         <v>1.25</v>
       </c>
       <c r="AF175">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG175">
         <v>2.84</v>
@@ -28907,7 +28907,7 @@
         <v>1.19</v>
       </c>
       <c r="AK175">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -30790,19 +30790,19 @@
         </is>
       </c>
       <c r="N187">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="O187">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="P187">
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="Q187">
         <v>1.53</v>
       </c>
       <c r="R187">
-        <v>3.25</v>
+        <v>2.81</v>
       </c>
       <c r="S187">
         <v>1.15</v>
@@ -30811,34 +30811,34 @@
         <v>5</v>
       </c>
       <c r="U187">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="V187">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="W187">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="X187">
         <v>1.01</v>
       </c>
       <c r="Y187">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Z187">
         <v>6.75</v>
       </c>
       <c r="AA187">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AB187">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AC187">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AD187">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AE187">
         <v>1.44</v>
@@ -30863,7 +30863,7 @@
         <v>1.05</v>
       </c>
       <c r="AK187">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -32257,25 +32257,25 @@
         </is>
       </c>
       <c r="N196">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="O196">
-        <v>3.58</v>
+        <v>3.65</v>
       </c>
       <c r="P196">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="Q196">
         <v>2.4</v>
       </c>
       <c r="R196">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S196">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T196">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="U196">
         <v>2.5</v>
@@ -32284,16 +32284,16 @@
         <v>1.5</v>
       </c>
       <c r="W196">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X196">
         <v>1.02</v>
       </c>
       <c r="Y196">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z196">
-        <v>4.17</v>
+        <v>4.05</v>
       </c>
       <c r="AA196">
         <v>1.68</v>
@@ -32327,7 +32327,7 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK196">
         <v>1.77</v>
@@ -32420,16 +32420,16 @@
         </is>
       </c>
       <c r="N197">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="O197">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="P197">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="Q197">
-        <v>2.6</v>
+        <v>2.69</v>
       </c>
       <c r="R197">
         <v>2.3</v>
@@ -32441,10 +32441,10 @@
         <v>3.5</v>
       </c>
       <c r="U197">
-        <v>2.46</v>
+        <v>2.33</v>
       </c>
       <c r="V197">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W197">
         <v>1.08</v>
@@ -32453,22 +32453,22 @@
         <v>1.02</v>
       </c>
       <c r="Y197">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z197">
         <v>4.33</v>
       </c>
       <c r="AA197">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AB197">
         <v>2.17</v>
       </c>
       <c r="AC197">
-        <v>2.66</v>
+        <v>2.49</v>
       </c>
       <c r="AD197">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AE197">
         <v>1.16</v>
@@ -32477,7 +32477,7 @@
         <v>1.51</v>
       </c>
       <c r="AG197">
-        <v>2.32</v>
+        <v>2.43</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32493,7 +32493,7 @@
         <v>1.22</v>
       </c>
       <c r="AK197">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -32622,22 +32622,22 @@
         <v>4.15</v>
       </c>
       <c r="AA198">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AB198">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AC198">
         <v>2.59</v>
       </c>
       <c r="AD198">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AE198">
         <v>1.19</v>
       </c>
       <c r="AF198">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="AG198">
         <v>2.2</v>
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="AJ198">
-        <v>1.2</v>
+        <v>1.83</v>
       </c>
       <c r="AK198">
         <v>1.2</v>
@@ -32746,19 +32746,19 @@
         </is>
       </c>
       <c r="N199">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O199">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P199">
         <v>2.8</v>
       </c>
       <c r="Q199">
-        <v>2.65</v>
+        <v>2.87</v>
       </c>
       <c r="R199">
-        <v>2.17</v>
+        <v>2.31</v>
       </c>
       <c r="S199">
         <v>1.3</v>
@@ -32776,25 +32776,25 @@
         <v>1.07</v>
       </c>
       <c r="X199">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y199">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="Z199">
-        <v>3.82</v>
+        <v>3.97</v>
       </c>
       <c r="AA199">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AB199">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="AC199">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="AD199">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE199">
         <v>1.1</v>
@@ -32803,7 +32803,7 @@
         <v>1.58</v>
       </c>
       <c r="AG199">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="AH199" t="inlineStr">
         <is>
@@ -32909,61 +32909,61 @@
         </is>
       </c>
       <c r="N200">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="O200">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P200">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="Q200">
-        <v>3.18</v>
+        <v>3.04</v>
       </c>
       <c r="R200">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="S200">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="T200">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="U200">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="V200">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="W200">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X200">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y200">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="Z200">
-        <v>2.71</v>
+        <v>2.78</v>
       </c>
       <c r="AA200">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="AB200">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AC200">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="AD200">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AE200">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF200">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AG200">
         <v>1.76</v>
@@ -32979,10 +32979,10 @@
         </is>
       </c>
       <c r="AJ200">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK200">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AL200">
         <v>0</v>
@@ -33235,13 +33235,13 @@
         </is>
       </c>
       <c r="N202">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="O202">
         <v>3.3</v>
       </c>
       <c r="P202">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q202">
         <v>2.45</v>
@@ -33268,10 +33268,10 @@
         <v>1.01</v>
       </c>
       <c r="Y202">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z202">
-        <v>3.25</v>
+        <v>3.61</v>
       </c>
       <c r="AA202">
         <v>1.85</v>
@@ -33280,7 +33280,7 @@
         <v>1.95</v>
       </c>
       <c r="AC202">
-        <v>2.97</v>
+        <v>3.07</v>
       </c>
       <c r="AD202">
         <v>1.3</v>
@@ -33292,7 +33292,7 @@
         <v>1.66</v>
       </c>
       <c r="AG202">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="AH202" t="inlineStr">
         <is>
@@ -33308,7 +33308,7 @@
         <v>1.25</v>
       </c>
       <c r="AK202">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AL202">
         <v>0</v>
@@ -33887,10 +33887,10 @@
         </is>
       </c>
       <c r="N206">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="O206">
-        <v>4.6</v>
+        <v>4.72</v>
       </c>
       <c r="P206">
         <v>6.25</v>
@@ -34376,16 +34376,16 @@
         </is>
       </c>
       <c r="N209">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="O209">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P209">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q209">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="R209">
         <v>2.18</v>
@@ -34394,46 +34394,46 @@
         <v>1.36</v>
       </c>
       <c r="T209">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="U209">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="V209">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W209">
         <v>1.08</v>
       </c>
       <c r="X209">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y209">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z209">
-        <v>3.08</v>
+        <v>3.28</v>
       </c>
       <c r="AA209">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AB209">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AC209">
-        <v>3.42</v>
+        <v>2.9</v>
       </c>
       <c r="AD209">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AE209">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF209">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="AG209">
-        <v>1.96</v>
+        <v>2.07</v>
       </c>
       <c r="AH209" t="inlineStr">
         <is>
@@ -34446,10 +34446,10 @@
         </is>
       </c>
       <c r="AJ209">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AK209">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -34702,64 +34702,64 @@
         </is>
       </c>
       <c r="N211">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="O211">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P211">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="Q211">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="R211">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="S211">
         <v>1.29</v>
       </c>
       <c r="T211">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="U211">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V211">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W211">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X211">
         <v>1.02</v>
       </c>
       <c r="Y211">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z211">
-        <v>4.18</v>
+        <v>3.96</v>
       </c>
       <c r="AA211">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AB211">
         <v>2.2</v>
       </c>
       <c r="AC211">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="AD211">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AE211">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF211">
         <v>1.57</v>
       </c>
       <c r="AG211">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AH211" t="inlineStr">
         <is>
@@ -34772,10 +34772,10 @@
         </is>
       </c>
       <c r="AJ211">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK211">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AL211">
         <v>0</v>
@@ -34865,64 +34865,64 @@
         </is>
       </c>
       <c r="N212">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="O212">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P212">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="Q212">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="R212">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="S212">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T212">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="U212">
-        <v>2.63</v>
+        <v>2.49</v>
       </c>
       <c r="V212">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="W212">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X212">
         <v>1</v>
       </c>
       <c r="Y212">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z212">
-        <v>3.58</v>
+        <v>3.98</v>
       </c>
       <c r="AA212">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="AB212">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AC212">
-        <v>2.81</v>
+        <v>2.59</v>
       </c>
       <c r="AD212">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AE212">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF212">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AG212">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="AH212" t="inlineStr">
         <is>
@@ -34935,7 +34935,7 @@
         </is>
       </c>
       <c r="AJ212">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AK212">
         <v>1.57</v>
@@ -35028,10 +35028,10 @@
         </is>
       </c>
       <c r="N213">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="O213">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P213">
         <v>1.77</v>
@@ -35040,19 +35040,19 @@
         <v>4.2</v>
       </c>
       <c r="R213">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S213">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T213">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="U213">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="V213">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W213">
         <v>1.06</v>
@@ -35067,16 +35067,16 @@
         <v>3.4</v>
       </c>
       <c r="AA213">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB213">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AC213">
-        <v>3.05</v>
+        <v>3.26</v>
       </c>
       <c r="AD213">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE213">
         <v>1.08</v>
@@ -35085,7 +35085,7 @@
         <v>1.73</v>
       </c>
       <c r="AG213">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AH213" t="inlineStr">
         <is>
@@ -35101,7 +35101,7 @@
         <v>1.82</v>
       </c>
       <c r="AK213">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AL213">
         <v>0</v>

--- a/jogos_2026-08-08.xlsx
+++ b/jogos_2026-08-08.xlsx
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="O38">
-        <v>3.55</v>
+        <v>3.73</v>
       </c>
       <c r="P38">
-        <v>3</v>
+        <v>3.88</v>
       </c>
       <c r="Q38">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="R38">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="S38">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T38">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="U38">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="V38">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W38">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X38">
         <v>1.03</v>
       </c>
       <c r="Y38">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z38">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="AA38">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB38">
-        <v>2.45</v>
+        <v>2.08</v>
       </c>
       <c r="AC38">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="AD38">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AE38">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF38">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AG38">
-        <v>2.47</v>
+        <v>2.18</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AK38">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="O39">
-        <v>3.73</v>
+        <v>3.55</v>
       </c>
       <c r="P39">
-        <v>3.88</v>
+        <v>3</v>
       </c>
       <c r="Q39">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="R39">
+        <v>2.43</v>
+      </c>
+      <c r="S39">
+        <v>1.3</v>
+      </c>
+      <c r="T39">
+        <v>3.2</v>
+      </c>
+      <c r="U39">
         <v>2.3</v>
       </c>
-      <c r="S39">
-        <v>1.31</v>
-      </c>
-      <c r="T39">
-        <v>3.15</v>
-      </c>
-      <c r="U39">
-        <v>2.38</v>
-      </c>
       <c r="V39">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W39">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X39">
         <v>1.03</v>
       </c>
       <c r="Y39">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z39">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="AA39">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB39">
-        <v>2.08</v>
+        <v>2.45</v>
       </c>
       <c r="AC39">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AD39">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AE39">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF39">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AG39">
-        <v>2.18</v>
+        <v>2.47</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AK39">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AL39">
         <v>0</v>

--- a/jogos_2026-08-08.xlsx
+++ b/jogos_2026-08-08.xlsx
@@ -3406,25 +3406,25 @@
         </is>
       </c>
       <c r="N19">
-        <v>4.2</v>
+        <v>4.35</v>
       </c>
       <c r="O19">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P19">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="Q19">
-        <v>4.62</v>
+        <v>5.41</v>
       </c>
       <c r="R19">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="S19">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="T19">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="U19">
         <v>3.6</v>
@@ -3436,22 +3436,22 @@
         <v>1.01</v>
       </c>
       <c r="X19">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Y19">
         <v>1.5</v>
       </c>
       <c r="Z19">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AA19">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AB19">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AC19">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="AD19">
         <v>1.17</v>
@@ -3460,7 +3460,7 @@
         <v>1.01</v>
       </c>
       <c r="AF19">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AG19">
         <v>1.57</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.82</v>
+        <v>1.29</v>
       </c>
       <c r="AK19">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3572,10 +3572,10 @@
         <v>2.11</v>
       </c>
       <c r="O20">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="P20">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="Q20">
         <v>2.62</v>
@@ -3587,46 +3587,46 @@
         <v>1.33</v>
       </c>
       <c r="T20">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="U20">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="V20">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W20">
         <v>1.08</v>
       </c>
       <c r="X20">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y20">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z20">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="AA20">
         <v>1.83</v>
       </c>
       <c r="AB20">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AC20">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AD20">
         <v>1.33</v>
       </c>
       <c r="AE20">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF20">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG20">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3750,31 +3750,31 @@
         <v>1.49</v>
       </c>
       <c r="T21">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="U21">
         <v>3.3</v>
       </c>
       <c r="V21">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W21">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X21">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="Y21">
         <v>1.36</v>
       </c>
       <c r="Z21">
-        <v>2.62</v>
+        <v>2.92</v>
       </c>
       <c r="AA21">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AB21">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AC21">
         <v>4.43</v>
@@ -3783,13 +3783,13 @@
         <v>1.16</v>
       </c>
       <c r="AE21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF21">
         <v>1.9</v>
       </c>
       <c r="AG21">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3895,31 +3895,31 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="O22">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="P22">
-        <v>5.7</v>
+        <v>5.25</v>
       </c>
       <c r="Q22">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="R22">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="S22">
+        <v>1.38</v>
+      </c>
+      <c r="T22">
+        <v>2.81</v>
+      </c>
+      <c r="U22">
+        <v>2.77</v>
+      </c>
+      <c r="V22">
         <v>1.39</v>
-      </c>
-      <c r="T22">
-        <v>2.77</v>
-      </c>
-      <c r="U22">
-        <v>2.81</v>
-      </c>
-      <c r="V22">
-        <v>1.38</v>
       </c>
       <c r="W22">
         <v>1.06</v>
@@ -3931,16 +3931,16 @@
         <v>1.3</v>
       </c>
       <c r="Z22">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="AA22">
         <v>2.02</v>
       </c>
       <c r="AB22">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AC22">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="AD22">
         <v>1.29</v>
@@ -3949,7 +3949,7 @@
         <v>1.1</v>
       </c>
       <c r="AF22">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AG22">
         <v>1.75</v>
@@ -4061,10 +4061,10 @@
         <v>1.84</v>
       </c>
       <c r="O23">
+        <v>3.7</v>
+      </c>
+      <c r="P23">
         <v>3.65</v>
-      </c>
-      <c r="P23">
-        <v>3.92</v>
       </c>
       <c r="Q23">
         <v>2.38</v>
@@ -4091,10 +4091,10 @@
         <v>1</v>
       </c>
       <c r="Y23">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z23">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="AA23">
         <v>1.86</v>
@@ -4115,7 +4115,7 @@
         <v>1.67</v>
       </c>
       <c r="AG23">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4224,16 +4224,16 @@
         <v>1.45</v>
       </c>
       <c r="O24">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="P24">
-        <v>6.34</v>
+        <v>6.5</v>
       </c>
       <c r="Q24">
         <v>1.95</v>
       </c>
       <c r="R24">
-        <v>2.17</v>
+        <v>2.31</v>
       </c>
       <c r="S24">
         <v>1.33</v>
@@ -4245,7 +4245,7 @@
         <v>2.6</v>
       </c>
       <c r="V24">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W24">
         <v>1.06</v>
@@ -4263,7 +4263,7 @@
         <v>1.75</v>
       </c>
       <c r="AB24">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AC24">
         <v>2.85</v>
@@ -5362,25 +5362,25 @@
         </is>
       </c>
       <c r="N31">
-        <v>3.57</v>
+        <v>3.9</v>
       </c>
       <c r="O31">
-        <v>3.77</v>
+        <v>3.8</v>
       </c>
       <c r="P31">
         <v>1.64</v>
       </c>
       <c r="Q31">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="R31">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="S31">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T31">
-        <v>3.85</v>
+        <v>3.68</v>
       </c>
       <c r="U31">
         <v>2.1</v>
@@ -5395,13 +5395,13 @@
         <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Z31">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="AA31">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AB31">
         <v>2.63</v>
@@ -5410,13 +5410,13 @@
         <v>2.16</v>
       </c>
       <c r="AD31">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AE31">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AF31">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AG31">
         <v>2.55</v>
@@ -5528,10 +5528,10 @@
         <v>3.6</v>
       </c>
       <c r="O32">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P32">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q32">
         <v>3.75</v>
@@ -5543,7 +5543,7 @@
         <v>1.3</v>
       </c>
       <c r="T32">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="U32">
         <v>2.5</v>
@@ -5555,25 +5555,25 @@
         <v>1.11</v>
       </c>
       <c r="X32">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y32">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z32">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="AA32">
         <v>1.68</v>
       </c>
       <c r="AB32">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AC32">
         <v>2.48</v>
       </c>
       <c r="AD32">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE32">
         <v>1.13</v>
@@ -5582,7 +5582,7 @@
         <v>1.6</v>
       </c>
       <c r="AG32">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>1.22</v>
       </c>
       <c r="AK32">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,7 +5688,7 @@
         </is>
       </c>
       <c r="N33">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O33">
         <v>3.25</v>
@@ -5706,16 +5706,16 @@
         <v>1.34</v>
       </c>
       <c r="T33">
-        <v>2.61</v>
+        <v>2.8</v>
       </c>
       <c r="U33">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="V33">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W33">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X33">
         <v>1.05</v>
@@ -5761,7 +5761,7 @@
         <v>1.22</v>
       </c>
       <c r="AK33">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="O38">
-        <v>3.73</v>
+        <v>3.55</v>
       </c>
       <c r="P38">
-        <v>3.88</v>
+        <v>3</v>
       </c>
       <c r="Q38">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="R38">
+        <v>2.43</v>
+      </c>
+      <c r="S38">
+        <v>1.3</v>
+      </c>
+      <c r="T38">
+        <v>3.2</v>
+      </c>
+      <c r="U38">
         <v>2.3</v>
       </c>
-      <c r="S38">
-        <v>1.31</v>
-      </c>
-      <c r="T38">
-        <v>3.15</v>
-      </c>
-      <c r="U38">
-        <v>2.38</v>
-      </c>
       <c r="V38">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W38">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X38">
         <v>1.03</v>
       </c>
       <c r="Y38">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z38">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="AA38">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB38">
-        <v>2.08</v>
+        <v>2.45</v>
       </c>
       <c r="AC38">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AD38">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AE38">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF38">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AG38">
-        <v>2.18</v>
+        <v>2.47</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AK38">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="O39">
-        <v>3.55</v>
+        <v>3.73</v>
       </c>
       <c r="P39">
-        <v>3</v>
+        <v>3.88</v>
       </c>
       <c r="Q39">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="R39">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="S39">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T39">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="U39">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="V39">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W39">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X39">
         <v>1.03</v>
       </c>
       <c r="Y39">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z39">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="AA39">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB39">
-        <v>2.45</v>
+        <v>2.08</v>
       </c>
       <c r="AC39">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="AD39">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AE39">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF39">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AG39">
-        <v>2.47</v>
+        <v>2.18</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AK39">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7481,25 +7481,25 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="O44">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="P44">
-        <v>4.57</v>
+        <v>4.4</v>
       </c>
       <c r="Q44">
         <v>1.95</v>
       </c>
       <c r="R44">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="S44">
         <v>1.22</v>
       </c>
       <c r="T44">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U44">
         <v>2.02</v>
@@ -7520,7 +7520,7 @@
         <v>5.4</v>
       </c>
       <c r="AA44">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AB44">
         <v>2.43</v>
@@ -7532,7 +7532,7 @@
         <v>1.64</v>
       </c>
       <c r="AE44">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AF44">
         <v>1.5</v>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK44">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,19 +7644,19 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="O45">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="P45">
-        <v>4.41</v>
+        <v>3.8</v>
       </c>
       <c r="Q45">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="R45">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="S45">
         <v>1.22</v>
@@ -7665,10 +7665,10 @@
         <v>3.9</v>
       </c>
       <c r="U45">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="V45">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="W45">
         <v>1.16</v>
@@ -7677,13 +7677,13 @@
         <v>1.02</v>
       </c>
       <c r="Y45">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z45">
-        <v>5.5</v>
+        <v>5.58</v>
       </c>
       <c r="AA45">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB45">
         <v>2.63</v>
@@ -7692,16 +7692,16 @@
         <v>2.1</v>
       </c>
       <c r="AD45">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AE45">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AF45">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AG45">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK45">
-        <v>2.11</v>
+        <v>2.03</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>3.22</v>
+        <v>2.73</v>
       </c>
       <c r="O46">
         <v>3.75</v>
       </c>
       <c r="P46">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q46">
         <v>3.2</v>
@@ -7822,16 +7822,16 @@
         <v>2.5</v>
       </c>
       <c r="S46">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T46">
         <v>4</v>
       </c>
       <c r="U46">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="V46">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="W46">
         <v>1.2</v>
@@ -7843,19 +7843,19 @@
         <v>1.06</v>
       </c>
       <c r="Z46">
-        <v>7.27</v>
+        <v>6</v>
       </c>
       <c r="AA46">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB46">
-        <v>2.87</v>
+        <v>3.12</v>
       </c>
       <c r="AC46">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AD46">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AE46">
         <v>1.29</v>
@@ -14164,61 +14164,61 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="O85">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P85">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="Q85">
         <v>2.64</v>
       </c>
       <c r="R85">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="S85">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="T85">
-        <v>2.88</v>
+        <v>2.53</v>
       </c>
       <c r="U85">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="V85">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W85">
         <v>1.02</v>
       </c>
       <c r="X85">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y85">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z85">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="AA85">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB85">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AC85">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AD85">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE85">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF85">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG85">
         <v>1.95</v>
@@ -14237,7 +14237,7 @@
         <v>1.28</v>
       </c>
       <c r="AK85">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="O110">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P110">
-        <v>5.25</v>
+        <v>5.57</v>
       </c>
       <c r="Q110">
         <v>2</v>
@@ -18257,7 +18257,7 @@
         <v>1.3</v>
       </c>
       <c r="T110">
-        <v>3.05</v>
+        <v>3.24</v>
       </c>
       <c r="U110">
         <v>2.5</v>
@@ -18266,7 +18266,7 @@
         <v>1.45</v>
       </c>
       <c r="W110">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X110">
         <v>1</v>
@@ -18284,16 +18284,16 @@
         <v>2.04</v>
       </c>
       <c r="AC110">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AD110">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AE110">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AF110">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG110">
         <v>1.95</v>
@@ -20358,19 +20358,19 @@
         </is>
       </c>
       <c r="N123">
-        <v>3.15</v>
+        <v>3.02</v>
       </c>
       <c r="O123">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P123">
         <v>2.05</v>
       </c>
       <c r="Q123">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="R123">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S123">
         <v>1.3</v>
@@ -20403,10 +20403,10 @@
         <v>1.9</v>
       </c>
       <c r="AC123">
-        <v>3.06</v>
+        <v>3.14</v>
       </c>
       <c r="AD123">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AE123">
         <v>1.13</v>
@@ -20521,64 +20521,64 @@
         </is>
       </c>
       <c r="N124">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O124">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P124">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q124">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R124">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S124">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T124">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U124">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="V124">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W124">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X124">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y124">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z124">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA124">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB124">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC124">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD124">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE124">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF124">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG124">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK124">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -26063,64 +26063,64 @@
         </is>
       </c>
       <c r="N158">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O158">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P158">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q158">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R158">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S158">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T158">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U158">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V158">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W158">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X158">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y158">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z158">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA158">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB158">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC158">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD158">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE158">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF158">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG158">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK158">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -28689,10 +28689,10 @@
         <v>1.42</v>
       </c>
       <c r="T174">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="U174">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="V174">
         <v>1.36</v>
@@ -28707,19 +28707,19 @@
         <v>1.33</v>
       </c>
       <c r="Z174">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AA174">
         <v>2.17</v>
       </c>
       <c r="AB174">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AC174">
         <v>3.93</v>
       </c>
       <c r="AD174">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE174">
         <v>1.08</v>
@@ -28728,7 +28728,7 @@
         <v>1.71</v>
       </c>
       <c r="AG174">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH174" t="inlineStr">
         <is>
@@ -31282,16 +31282,16 @@
         <v>2.95</v>
       </c>
       <c r="O190">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="P190">
         <v>2.4</v>
       </c>
       <c r="Q190">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="R190">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="S190">
         <v>1.42</v>
@@ -31312,25 +31312,25 @@
         <v>1.03</v>
       </c>
       <c r="Y190">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z190">
         <v>3.25</v>
       </c>
       <c r="AA190">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AB190">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AC190">
         <v>3.8</v>
       </c>
       <c r="AD190">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE190">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AF190">
         <v>1.8</v>
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G194">
@@ -31931,64 +31931,64 @@
         </is>
       </c>
       <c r="N194">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="O194">
         <v>3</v>
       </c>
       <c r="P194">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="Q194">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="R194">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="S194">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T194">
-        <v>2.49</v>
+        <v>2.26</v>
       </c>
       <c r="U194">
         <v>3.4</v>
       </c>
       <c r="V194">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="W194">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X194">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y194">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="Z194">
-        <v>2.88</v>
+        <v>2.41</v>
       </c>
       <c r="AA194">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="AB194">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AC194">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="AD194">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AE194">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF194">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AG194">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AH194" t="inlineStr">
         <is>
@@ -32001,10 +32001,10 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK194">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G195">
@@ -32094,64 +32094,64 @@
         </is>
       </c>
       <c r="N195">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="O195">
         <v>3</v>
       </c>
       <c r="P195">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="Q195">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="R195">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="S195">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T195">
-        <v>2.26</v>
+        <v>2.49</v>
       </c>
       <c r="U195">
         <v>3.4</v>
       </c>
       <c r="V195">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="W195">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X195">
+        <v>1.07</v>
+      </c>
+      <c r="Y195">
+        <v>1.4</v>
+      </c>
+      <c r="Z195">
+        <v>2.88</v>
+      </c>
+      <c r="AA195">
+        <v>2.3</v>
+      </c>
+      <c r="AB195">
+        <v>1.6</v>
+      </c>
+      <c r="AC195">
+        <v>3.7</v>
+      </c>
+      <c r="AD195">
+        <v>1.22</v>
+      </c>
+      <c r="AE195">
         <v>1.06</v>
       </c>
-      <c r="Y195">
-        <v>1.45</v>
-      </c>
-      <c r="Z195">
-        <v>2.41</v>
-      </c>
-      <c r="AA195">
-        <v>2.63</v>
-      </c>
-      <c r="AB195">
-        <v>1.47</v>
-      </c>
-      <c r="AC195">
-        <v>4.6</v>
-      </c>
-      <c r="AD195">
-        <v>1.13</v>
-      </c>
-      <c r="AE195">
-        <v>1.02</v>
-      </c>
       <c r="AF195">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AG195">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AK195">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G199">
@@ -32746,80 +32746,80 @@
         </is>
       </c>
       <c r="N199">
-        <v>1.76</v>
+        <v>2.35</v>
       </c>
       <c r="O199">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="P199">
-        <v>3.73</v>
+        <v>2.92</v>
       </c>
       <c r="Q199">
-        <v>2.25</v>
+        <v>3.02</v>
       </c>
       <c r="R199">
-        <v>2.41</v>
+        <v>1.94</v>
       </c>
       <c r="S199">
+        <v>1.44</v>
+      </c>
+      <c r="T199">
+        <v>2.5</v>
+      </c>
+      <c r="U199">
+        <v>3.1</v>
+      </c>
+      <c r="V199">
+        <v>1.33</v>
+      </c>
+      <c r="W199">
+        <v>1.06</v>
+      </c>
+      <c r="X199">
+        <v>1.04</v>
+      </c>
+      <c r="Y199">
+        <v>1.38</v>
+      </c>
+      <c r="Z199">
+        <v>2.62</v>
+      </c>
+      <c r="AA199">
+        <v>2.2</v>
+      </c>
+      <c r="AB199">
+        <v>1.62</v>
+      </c>
+      <c r="AC199">
+        <v>4.05</v>
+      </c>
+      <c r="AD199">
+        <v>1.19</v>
+      </c>
+      <c r="AE199">
+        <v>1.02</v>
+      </c>
+      <c r="AF199">
+        <v>1.92</v>
+      </c>
+      <c r="AG199">
+        <v>1.77</v>
+      </c>
+      <c r="AH199" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI199" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ199">
         <v>1.29</v>
       </c>
-      <c r="T199">
-        <v>3.4</v>
-      </c>
-      <c r="U199">
-        <v>2.14</v>
-      </c>
-      <c r="V199">
-        <v>1.54</v>
-      </c>
-      <c r="W199">
-        <v>1.12</v>
-      </c>
-      <c r="X199">
-        <v>1.02</v>
-      </c>
-      <c r="Y199">
-        <v>1.16</v>
-      </c>
-      <c r="Z199">
-        <v>4.1</v>
-      </c>
-      <c r="AA199">
-        <v>1.67</v>
-      </c>
-      <c r="AB199">
-        <v>2.17</v>
-      </c>
-      <c r="AC199">
-        <v>2.3</v>
-      </c>
-      <c r="AD199">
-        <v>1.4</v>
-      </c>
-      <c r="AE199">
-        <v>1.19</v>
-      </c>
-      <c r="AF199">
-        <v>1.59</v>
-      </c>
-      <c r="AG199">
-        <v>2.35</v>
-      </c>
-      <c r="AH199" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI199" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ199">
-        <v>1.22</v>
-      </c>
       <c r="AK199">
-        <v>1.86</v>
+        <v>1.47</v>
       </c>
       <c r="AL199">
         <v>0</v>
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G200">
@@ -32909,80 +32909,80 @@
         </is>
       </c>
       <c r="N200">
+        <v>1.76</v>
+      </c>
+      <c r="O200">
+        <v>3.7</v>
+      </c>
+      <c r="P200">
+        <v>3.73</v>
+      </c>
+      <c r="Q200">
         <v>2.25</v>
       </c>
-      <c r="O200">
+      <c r="R200">
+        <v>2.41</v>
+      </c>
+      <c r="S200">
+        <v>1.29</v>
+      </c>
+      <c r="T200">
         <v>3.4</v>
       </c>
-      <c r="P200">
-        <v>2.8</v>
-      </c>
-      <c r="Q200">
-        <v>2.87</v>
-      </c>
-      <c r="R200">
-        <v>2.31</v>
-      </c>
-      <c r="S200">
-        <v>1.31</v>
-      </c>
-      <c r="T200">
-        <v>3.25</v>
-      </c>
       <c r="U200">
-        <v>2.47</v>
+        <v>2.14</v>
       </c>
       <c r="V200">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="W200">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X200">
         <v>1.02</v>
       </c>
       <c r="Y200">
+        <v>1.16</v>
+      </c>
+      <c r="Z200">
+        <v>4.1</v>
+      </c>
+      <c r="AA200">
+        <v>1.67</v>
+      </c>
+      <c r="AB200">
+        <v>2.17</v>
+      </c>
+      <c r="AC200">
+        <v>2.3</v>
+      </c>
+      <c r="AD200">
+        <v>1.4</v>
+      </c>
+      <c r="AE200">
+        <v>1.19</v>
+      </c>
+      <c r="AF200">
+        <v>1.59</v>
+      </c>
+      <c r="AG200">
+        <v>2.35</v>
+      </c>
+      <c r="AH200" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI200" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ200">
         <v>1.22</v>
       </c>
-      <c r="Z200">
-        <v>3.95</v>
-      </c>
-      <c r="AA200">
-        <v>1.72</v>
-      </c>
-      <c r="AB200">
-        <v>2</v>
-      </c>
-      <c r="AC200">
-        <v>2.75</v>
-      </c>
-      <c r="AD200">
-        <v>1.42</v>
-      </c>
-      <c r="AE200">
-        <v>1.12</v>
-      </c>
-      <c r="AF200">
-        <v>1.55</v>
-      </c>
-      <c r="AG200">
-        <v>2.17</v>
-      </c>
-      <c r="AH200" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI200" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ200">
-        <v>1.34</v>
-      </c>
       <c r="AK200">
-        <v>1.57</v>
+        <v>1.86</v>
       </c>
       <c r="AL200">
         <v>0</v>
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G201">
@@ -33072,64 +33072,64 @@
         </is>
       </c>
       <c r="N201">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="O201">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P201">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="Q201">
-        <v>3.02</v>
+        <v>2.87</v>
       </c>
       <c r="R201">
-        <v>1.94</v>
+        <v>2.31</v>
       </c>
       <c r="S201">
+        <v>1.31</v>
+      </c>
+      <c r="T201">
+        <v>3.25</v>
+      </c>
+      <c r="U201">
+        <v>2.47</v>
+      </c>
+      <c r="V201">
         <v>1.44</v>
       </c>
-      <c r="T201">
-        <v>2.5</v>
-      </c>
-      <c r="U201">
-        <v>3.1</v>
-      </c>
-      <c r="V201">
-        <v>1.33</v>
-      </c>
       <c r="W201">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X201">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y201">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="Z201">
-        <v>2.62</v>
+        <v>3.95</v>
       </c>
       <c r="AA201">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="AB201">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AC201">
-        <v>4.05</v>
+        <v>2.75</v>
       </c>
       <c r="AD201">
-        <v>1.19</v>
+        <v>1.42</v>
       </c>
       <c r="AE201">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="AF201">
-        <v>1.92</v>
+        <v>1.55</v>
       </c>
       <c r="AG201">
-        <v>1.77</v>
+        <v>2.17</v>
       </c>
       <c r="AH201" t="inlineStr">
         <is>
@@ -33142,10 +33142,10 @@
         </is>
       </c>
       <c r="AJ201">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AK201">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AL201">
         <v>0</v>
@@ -33238,19 +33238,19 @@
         <v>1.64</v>
       </c>
       <c r="O202">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="P202">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="Q202">
         <v>2.16</v>
       </c>
       <c r="R202">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="S202">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T202">
         <v>2.81</v>
@@ -33259,7 +33259,7 @@
         <v>2.8</v>
       </c>
       <c r="V202">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W202">
         <v>1.05</v>
@@ -33887,25 +33887,25 @@
         </is>
       </c>
       <c r="N206">
-        <v>2.37</v>
+        <v>2.55</v>
       </c>
       <c r="O206">
-        <v>3.13</v>
+        <v>3.4</v>
       </c>
       <c r="P206">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="Q206">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="R206">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="S206">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T206">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="U206">
         <v>2.65</v>
@@ -33926,7 +33926,7 @@
         <v>3.4</v>
       </c>
       <c r="AA206">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB206">
         <v>1.8</v>
@@ -33944,7 +33944,7 @@
         <v>1.68</v>
       </c>
       <c r="AG206">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH206" t="inlineStr">
         <is>

--- a/jogos_2026-08-08.xlsx
+++ b/jogos_2026-08-08.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>4</v>
+        <v>2.13</v>
       </c>
       <c r="O4">
-        <v>3.18</v>
+        <v>3.39</v>
       </c>
       <c r="P4">
-        <v>1.7</v>
+        <v>2.47</v>
       </c>
       <c r="Q4">
-        <v>4.24</v>
+        <v>2.4</v>
       </c>
       <c r="R4">
-        <v>2.04</v>
+        <v>2.36</v>
       </c>
       <c r="S4">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="T4">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="U4">
-        <v>2.75</v>
+        <v>2.13</v>
       </c>
       <c r="V4">
+        <v>1.62</v>
+      </c>
+      <c r="W4">
+        <v>1.18</v>
+      </c>
+      <c r="X4">
+        <v>1.02</v>
+      </c>
+      <c r="Y4">
+        <v>1.14</v>
+      </c>
+      <c r="Z4">
+        <v>5.15</v>
+      </c>
+      <c r="AA4">
+        <v>1.43</v>
+      </c>
+      <c r="AB4">
+        <v>2.5</v>
+      </c>
+      <c r="AC4">
+        <v>2.2</v>
+      </c>
+      <c r="AD4">
+        <v>1.66</v>
+      </c>
+      <c r="AE4">
+        <v>1.2</v>
+      </c>
+      <c r="AF4">
         <v>1.4</v>
       </c>
-      <c r="W4">
-        <v>1.08</v>
-      </c>
-      <c r="X4">
-        <v>1</v>
-      </c>
-      <c r="Y4">
-        <v>1.26</v>
-      </c>
-      <c r="Z4">
-        <v>3.2</v>
-      </c>
-      <c r="AA4">
-        <v>1.97</v>
-      </c>
-      <c r="AB4">
-        <v>1.79</v>
-      </c>
-      <c r="AC4">
-        <v>3.5</v>
-      </c>
-      <c r="AD4">
-        <v>1.25</v>
-      </c>
-      <c r="AE4">
-        <v>1.12</v>
-      </c>
-      <c r="AF4">
-        <v>1.82</v>
-      </c>
       <c r="AG4">
-        <v>1.85</v>
+        <v>2.62</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.21</v>
       </c>
       <c r="AK4">
-        <v>1.13</v>
+        <v>1.53</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.13</v>
+        <v>4</v>
       </c>
       <c r="O5">
-        <v>3.39</v>
+        <v>3.18</v>
       </c>
       <c r="P5">
-        <v>2.47</v>
+        <v>1.7</v>
       </c>
       <c r="Q5">
-        <v>2.4</v>
+        <v>4.24</v>
       </c>
       <c r="R5">
-        <v>2.36</v>
+        <v>2.04</v>
       </c>
       <c r="S5">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="T5">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="U5">
-        <v>2.13</v>
+        <v>2.75</v>
       </c>
       <c r="V5">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="W5">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="X5">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="Z5">
-        <v>5.15</v>
+        <v>3.2</v>
       </c>
       <c r="AA5">
-        <v>1.43</v>
+        <v>1.97</v>
       </c>
       <c r="AB5">
-        <v>2.5</v>
+        <v>1.79</v>
       </c>
       <c r="AC5">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="AD5">
-        <v>1.66</v>
+        <v>1.25</v>
       </c>
       <c r="AE5">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AF5">
-        <v>1.4</v>
+        <v>1.82</v>
       </c>
       <c r="AG5">
-        <v>2.62</v>
+        <v>1.85</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>1.21</v>
       </c>
       <c r="AK5">
-        <v>1.53</v>
+        <v>1.13</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="O13">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="P13">
-        <v>2.99</v>
+        <v>2.47</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2467,10 +2467,10 @@
         <v>0</v>
       </c>
       <c r="AA13">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AB13">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AC13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
+        <v>2.37</v>
+      </c>
+      <c r="O14">
         <v>3</v>
       </c>
-      <c r="O14">
-        <v>3.2</v>
-      </c>
       <c r="P14">
-        <v>2.47</v>
+        <v>2.7</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2630,10 +2630,10 @@
         <v>0</v>
       </c>
       <c r="AA14">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AB14">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AC14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Tegevajaro Miyazaki</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="O15">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="P15">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2793,10 +2793,10 @@
         <v>0</v>
       </c>
       <c r="AA15">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AB15">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AC15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tegevajaro Miyazaki</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="O16">
-        <v>3.08</v>
+        <v>3.16</v>
       </c>
       <c r="P16">
-        <v>2.9</v>
+        <v>2.99</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -2956,10 +2956,10 @@
         <v>0</v>
       </c>
       <c r="AA16">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="AB16">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AC16">
         <v>0</v>
@@ -6222,13 +6222,13 @@
         <v>2.3</v>
       </c>
       <c r="AC36">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AD36">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AE36">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF36">
         <v>1.44</v>
@@ -6343,10 +6343,10 @@
         <v>1.64</v>
       </c>
       <c r="O37">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="P37">
-        <v>4.5</v>
+        <v>5.24</v>
       </c>
       <c r="Q37">
         <v>2.1</v>
@@ -6355,10 +6355,10 @@
         <v>2.29</v>
       </c>
       <c r="S37">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T37">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="U37">
         <v>2.45</v>
@@ -6376,22 +6376,22 @@
         <v>1.2</v>
       </c>
       <c r="Z37">
-        <v>4.45</v>
+        <v>4.48</v>
       </c>
       <c r="AA37">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AB37">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AC37">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="AD37">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AE37">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF37">
         <v>1.67</v>
@@ -6506,10 +6506,10 @@
         <v>1.73</v>
       </c>
       <c r="O38">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P38">
-        <v>3.88</v>
+        <v>4.25</v>
       </c>
       <c r="Q38">
         <v>2.15</v>
@@ -6518,7 +6518,7 @@
         <v>2.38</v>
       </c>
       <c r="S38">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T38">
         <v>3.15</v>
@@ -6669,22 +6669,22 @@
         <v>2.2</v>
       </c>
       <c r="O39">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="P39">
         <v>3</v>
       </c>
       <c r="Q39">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="R39">
         <v>2.35</v>
       </c>
       <c r="S39">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="T39">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="U39">
         <v>2.36</v>
@@ -6699,10 +6699,10 @@
         <v>1</v>
       </c>
       <c r="Y39">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z39">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AA39">
         <v>1.62</v>
@@ -6711,7 +6711,7 @@
         <v>2.38</v>
       </c>
       <c r="AC39">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="AD39">
         <v>1.51</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,80 +6992,80 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.8</v>
+        <v>3.03</v>
       </c>
       <c r="O41">
-        <v>3.21</v>
+        <v>3.15</v>
       </c>
       <c r="P41">
-        <v>3.21</v>
+        <v>1.98</v>
       </c>
       <c r="Q41">
-        <v>2.15</v>
+        <v>4.2</v>
       </c>
       <c r="R41">
-        <v>2.3</v>
+        <v>1.94</v>
       </c>
       <c r="S41">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="T41">
-        <v>3.2</v>
+        <v>2.56</v>
       </c>
       <c r="U41">
-        <v>2.53</v>
+        <v>3</v>
       </c>
       <c r="V41">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="W41">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X41">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y41">
+        <v>1.45</v>
+      </c>
+      <c r="Z41">
+        <v>2.6</v>
+      </c>
+      <c r="AA41">
+        <v>2.38</v>
+      </c>
+      <c r="AB41">
+        <v>1.6</v>
+      </c>
+      <c r="AC41">
+        <v>3.88</v>
+      </c>
+      <c r="AD41">
+        <v>1.17</v>
+      </c>
+      <c r="AE41">
+        <v>1.06</v>
+      </c>
+      <c r="AF41">
+        <v>1.92</v>
+      </c>
+      <c r="AG41">
+        <v>1.83</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41">
+        <v>1.33</v>
+      </c>
+      <c r="AK41">
         <v>1.22</v>
-      </c>
-      <c r="Z41">
-        <v>4.1</v>
-      </c>
-      <c r="AA41">
-        <v>1.73</v>
-      </c>
-      <c r="AB41">
-        <v>2.07</v>
-      </c>
-      <c r="AC41">
-        <v>3.1</v>
-      </c>
-      <c r="AD41">
-        <v>1.37</v>
-      </c>
-      <c r="AE41">
-        <v>1.13</v>
-      </c>
-      <c r="AF41">
-        <v>1.73</v>
-      </c>
-      <c r="AG41">
-        <v>2.01</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ41">
-        <v>1.2</v>
-      </c>
-      <c r="AK41">
-        <v>1.81</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,80 +7155,80 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.83</v>
+        <v>1.8</v>
       </c>
       <c r="O42">
-        <v>3.05</v>
+        <v>3.21</v>
       </c>
       <c r="P42">
-        <v>2.03</v>
+        <v>3.21</v>
       </c>
       <c r="Q42">
-        <v>4.25</v>
+        <v>2.15</v>
       </c>
       <c r="R42">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="S42">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T42">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="U42">
-        <v>2.9</v>
+        <v>2.53</v>
       </c>
       <c r="V42">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="W42">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X42">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y42">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="Z42">
-        <v>2.88</v>
+        <v>4.1</v>
       </c>
       <c r="AA42">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AB42">
-        <v>1.64</v>
+        <v>2.07</v>
       </c>
       <c r="AC42">
-        <v>3.68</v>
+        <v>3.1</v>
       </c>
       <c r="AD42">
+        <v>1.37</v>
+      </c>
+      <c r="AE42">
+        <v>1.13</v>
+      </c>
+      <c r="AF42">
+        <v>1.73</v>
+      </c>
+      <c r="AG42">
+        <v>2.01</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ42">
         <v>1.2</v>
       </c>
-      <c r="AE42">
-        <v>1.06</v>
-      </c>
-      <c r="AF42">
-        <v>1.83</v>
-      </c>
-      <c r="AG42">
+      <c r="AK42">
         <v>1.81</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ42">
-        <v>1.28</v>
-      </c>
-      <c r="AK42">
-        <v>1.25</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>3.03</v>
+        <v>2.83</v>
       </c>
       <c r="O43">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="P43">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="Q43">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="R43">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="S43">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T43">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="U43">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="V43">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W43">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X43">
         <v>1.06</v>
       </c>
       <c r="Y43">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="Z43">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="AA43">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AB43">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AC43">
-        <v>3.88</v>
+        <v>3.68</v>
       </c>
       <c r="AD43">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE43">
         <v>1.06</v>
       </c>
       <c r="AF43">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AG43">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK43">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="O56">
         <v>3.18</v>
@@ -9482,7 +9482,7 @@
         <v>1.9</v>
       </c>
       <c r="AC56">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD56">
         <v>1.29</v>
@@ -10753,7 +10753,7 @@
         <v>2.07</v>
       </c>
       <c r="R64">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="S64">
         <v>1.2</v>
@@ -10762,7 +10762,7 @@
         <v>4</v>
       </c>
       <c r="U64">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="V64">
         <v>1.68</v>
@@ -10795,10 +10795,10 @@
         <v>1.24</v>
       </c>
       <c r="AF64">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AG64">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O65">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P65">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q65">
         <v>2.76</v>
@@ -10919,7 +10919,7 @@
         <v>1.96</v>
       </c>
       <c r="S65">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T65">
         <v>2.66</v>
@@ -10928,7 +10928,7 @@
         <v>2.88</v>
       </c>
       <c r="V65">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W65">
         <v>1.07</v>
@@ -10952,7 +10952,7 @@
         <v>3.73</v>
       </c>
       <c r="AD65">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE65">
         <v>1.08</v>
@@ -10977,7 +10977,7 @@
         <v>1.33</v>
       </c>
       <c r="AK65">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11094,7 +11094,7 @@
         <v>1.53</v>
       </c>
       <c r="W66">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X66">
         <v>1.02</v>
@@ -11112,7 +11112,7 @@
         <v>2.2</v>
       </c>
       <c r="AC66">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="AD66">
         <v>1.47</v>
@@ -11137,7 +11137,7 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK66">
         <v>1.67</v>
@@ -11230,16 +11230,16 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="O67">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P67">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q67">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="R67">
         <v>2.35</v>
@@ -11272,7 +11272,7 @@
         <v>1.57</v>
       </c>
       <c r="AB67">
-        <v>2.39</v>
+        <v>2.23</v>
       </c>
       <c r="AC67">
         <v>2.3</v>
@@ -11303,7 +11303,7 @@
         <v>1.47</v>
       </c>
       <c r="AK67">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11719,10 +11719,10 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O70">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="P70">
         <v>8.75</v>
@@ -11755,16 +11755,16 @@
         <v>1.1</v>
       </c>
       <c r="Z70">
-        <v>5.05</v>
+        <v>5.11</v>
       </c>
       <c r="AA70">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AB70">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="AC70">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AD70">
         <v>1.62</v>
@@ -11773,7 +11773,7 @@
         <v>1.2</v>
       </c>
       <c r="AF70">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AG70">
         <v>1.76</v>
@@ -11789,7 +11789,7 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AK70">
         <v>3.78</v>
@@ -11897,13 +11897,13 @@
         <v>2.05</v>
       </c>
       <c r="S71">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="T71">
         <v>3.2</v>
       </c>
       <c r="U71">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="V71">
         <v>1.43</v>
@@ -11918,10 +11918,10 @@
         <v>1.25</v>
       </c>
       <c r="Z71">
-        <v>3.79</v>
+        <v>4.1</v>
       </c>
       <c r="AA71">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AB71">
         <v>1.98</v>
@@ -11933,7 +11933,7 @@
         <v>1.33</v>
       </c>
       <c r="AE71">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF71">
         <v>1.67</v>
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="O72">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P72">
-        <v>3.9</v>
+        <v>4.15</v>
       </c>
       <c r="Q72">
         <v>2.3</v>
@@ -12075,13 +12075,13 @@
         <v>1.1</v>
       </c>
       <c r="X72">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y72">
         <v>1.25</v>
       </c>
       <c r="Z72">
-        <v>3.64</v>
+        <v>3.67</v>
       </c>
       <c r="AA72">
         <v>1.85</v>
@@ -12090,7 +12090,7 @@
         <v>1.9</v>
       </c>
       <c r="AC72">
-        <v>3.08</v>
+        <v>3.11</v>
       </c>
       <c r="AD72">
         <v>1.31</v>
@@ -12099,10 +12099,10 @@
         <v>1.13</v>
       </c>
       <c r="AF72">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AG72">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>1.21</v>
       </c>
       <c r="AK72">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12211,13 +12211,13 @@
         <v>5.25</v>
       </c>
       <c r="O73">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="P73">
         <v>1.56</v>
       </c>
       <c r="Q73">
-        <v>5.42</v>
+        <v>5.52</v>
       </c>
       <c r="R73">
         <v>2.45</v>
@@ -12226,10 +12226,10 @@
         <v>1.25</v>
       </c>
       <c r="T73">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="U73">
-        <v>1.97</v>
+        <v>2.42</v>
       </c>
       <c r="V73">
         <v>1.57</v>
@@ -12238,7 +12238,7 @@
         <v>1.12</v>
       </c>
       <c r="X73">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y73">
         <v>1.14</v>
@@ -12374,7 +12374,7 @@
         <v>1.92</v>
       </c>
       <c r="O74">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P74">
         <v>3.4</v>
@@ -12386,7 +12386,7 @@
         <v>2.1</v>
       </c>
       <c r="S74">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T74">
         <v>2.74</v>
@@ -12404,7 +12404,7 @@
         <v>1.03</v>
       </c>
       <c r="Y74">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z74">
         <v>3.28</v>
@@ -12534,7 +12534,7 @@
         </is>
       </c>
       <c r="N75">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="O75">
         <v>3.35</v>
@@ -12570,7 +12570,7 @@
         <v>1.27</v>
       </c>
       <c r="Z75">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AA75">
         <v>1.99</v>
@@ -12579,7 +12579,7 @@
         <v>1.83</v>
       </c>
       <c r="AC75">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AD75">
         <v>1.25</v>
@@ -12697,16 +12697,16 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O76">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="P76">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="Q76">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="R76">
         <v>2.1</v>
@@ -12718,7 +12718,7 @@
         <v>2.75</v>
       </c>
       <c r="U76">
-        <v>2.86</v>
+        <v>3.02</v>
       </c>
       <c r="V76">
         <v>1.31</v>
@@ -12733,10 +12733,10 @@
         <v>1.36</v>
       </c>
       <c r="Z76">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AA76">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AB76">
         <v>1.66</v>
@@ -12748,13 +12748,13 @@
         <v>1.21</v>
       </c>
       <c r="AE76">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AF76">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG76">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12863,7 +12863,7 @@
         <v>2.87</v>
       </c>
       <c r="O77">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P77">
         <v>2.2</v>
@@ -12890,7 +12890,7 @@
         <v>1.07</v>
       </c>
       <c r="X77">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y77">
         <v>1.33</v>
@@ -12914,7 +12914,7 @@
         <v>1.05</v>
       </c>
       <c r="AF77">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AG77">
         <v>1.89</v>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AK77">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -14179,10 +14179,10 @@
         <v>2.14</v>
       </c>
       <c r="S85">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T85">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="U85">
         <v>3.02</v>
@@ -14197,16 +14197,16 @@
         <v>1.06</v>
       </c>
       <c r="Y85">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z85">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AA85">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AB85">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AC85">
         <v>3.75</v>
@@ -14979,34 +14979,34 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="O90">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="P90">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="Q90">
         <v>3</v>
       </c>
       <c r="R90">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S90">
         <v>1.41</v>
       </c>
       <c r="T90">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="U90">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="V90">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W90">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X90">
         <v>1.06</v>
@@ -15015,19 +15015,19 @@
         <v>1.26</v>
       </c>
       <c r="Z90">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AA90">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AB90">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC90">
         <v>3.4</v>
       </c>
       <c r="AD90">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE90">
         <v>1.06</v>
@@ -15049,7 +15049,7 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK90">
         <v>1.5</v>
@@ -15145,10 +15145,10 @@
         <v>1.37</v>
       </c>
       <c r="O91">
-        <v>4.68</v>
+        <v>4.72</v>
       </c>
       <c r="P91">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Q91">
         <v>1.83</v>
@@ -15160,7 +15160,7 @@
         <v>1.2</v>
       </c>
       <c r="T91">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="U91">
         <v>2.07</v>
@@ -15190,7 +15190,7 @@
         <v>2.11</v>
       </c>
       <c r="AD91">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AE91">
         <v>1.26</v>
@@ -15314,10 +15314,10 @@
         <v>2.1</v>
       </c>
       <c r="Q92">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="R92">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S92">
         <v>1.2</v>
@@ -15329,7 +15329,7 @@
         <v>2</v>
       </c>
       <c r="V92">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="W92">
         <v>1.2</v>
@@ -15356,7 +15356,7 @@
         <v>1.77</v>
       </c>
       <c r="AE92">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AF92">
         <v>1.36</v>
@@ -16621,13 +16621,13 @@
         <v>2.6</v>
       </c>
       <c r="R100">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S100">
         <v>1.39</v>
       </c>
       <c r="T100">
-        <v>2.69</v>
+        <v>3.02</v>
       </c>
       <c r="U100">
         <v>2.88</v>
@@ -16654,7 +16654,7 @@
         <v>1.79</v>
       </c>
       <c r="AC100">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="AD100">
         <v>1.26</v>
@@ -16663,7 +16663,7 @@
         <v>1.09</v>
       </c>
       <c r="AF100">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG100">
         <v>1.95</v>
@@ -16679,7 +16679,7 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK100">
         <v>1.73</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>2</v>
+        <v>2.64</v>
       </c>
       <c r="O104">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="P104">
-        <v>3</v>
+        <v>2.52</v>
       </c>
       <c r="Q104">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R104">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S104">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T104">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U104">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V104">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="W104">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X104">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y104">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z104">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="AA104">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="AB104">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="AC104">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AD104">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE104">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF104">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG104">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK104">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.47</v>
+        <v>2</v>
       </c>
       <c r="O105">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="P105">
-        <v>2.52</v>
+        <v>3</v>
       </c>
       <c r="Q105">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R105">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S105">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T105">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U105">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V105">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W105">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X105">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y105">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z105">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AA105">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AB105">
-        <v>1.85</v>
+        <v>2.37</v>
       </c>
       <c r="AC105">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD105">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE105">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF105">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG105">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK105">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17593,34 +17593,34 @@
         <v>3.7</v>
       </c>
       <c r="P106">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Q106">
-        <v>5.13</v>
+        <v>5.28</v>
       </c>
       <c r="R106">
-        <v>2.31</v>
+        <v>2.16</v>
       </c>
       <c r="S106">
         <v>1.35</v>
       </c>
       <c r="T106">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="U106">
         <v>2.73</v>
       </c>
       <c r="V106">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W106">
         <v>1.08</v>
       </c>
       <c r="X106">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y106">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z106">
         <v>3.42</v>
@@ -17635,7 +17635,7 @@
         <v>3.25</v>
       </c>
       <c r="AD106">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE106">
         <v>1.06</v>
@@ -17750,49 +17750,49 @@
         </is>
       </c>
       <c r="N107">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O107">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P107">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="Q107">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="R107">
         <v>2.3</v>
       </c>
       <c r="S107">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T107">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U107">
         <v>2.35</v>
       </c>
       <c r="V107">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W107">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X107">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y107">
         <v>1.13</v>
       </c>
       <c r="Z107">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="AA107">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AB107">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="AC107">
         <v>2.45</v>
@@ -17804,10 +17804,10 @@
         <v>1.17</v>
       </c>
       <c r="AF107">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AG107">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="O110">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P110">
-        <v>5.57</v>
+        <v>6.2</v>
       </c>
       <c r="Q110">
         <v>2</v>
@@ -18257,7 +18257,7 @@
         <v>1.3</v>
       </c>
       <c r="T110">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="U110">
         <v>2.5</v>
@@ -18272,7 +18272,7 @@
         <v>1</v>
       </c>
       <c r="Y110">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z110">
         <v>3.92</v>
@@ -18293,7 +18293,7 @@
         <v>1.12</v>
       </c>
       <c r="AF110">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG110">
         <v>1.95</v>
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="O118">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P118">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q118">
         <v>0</v>
@@ -19582,10 +19582,10 @@
         <v>0</v>
       </c>
       <c r="AA118">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB118">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AC118">
         <v>0</v>
@@ -19869,13 +19869,13 @@
         </is>
       </c>
       <c r="N120">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O120">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P120">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q120">
         <v>0</v>
@@ -20044,7 +20044,7 @@
         <v>3.38</v>
       </c>
       <c r="R121">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="S121">
         <v>1.5</v>
@@ -20059,10 +20059,10 @@
         <v>1.25</v>
       </c>
       <c r="W121">
+        <v>1.03</v>
+      </c>
+      <c r="X121">
         <v>1.05</v>
-      </c>
-      <c r="X121">
-        <v>1.06</v>
       </c>
       <c r="Y121">
         <v>1.38</v>
@@ -20071,16 +20071,16 @@
         <v>2.74</v>
       </c>
       <c r="AA121">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AB121">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC121">
         <v>4.46</v>
       </c>
       <c r="AD121">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AE121">
         <v>1.05</v>
@@ -20358,19 +20358,19 @@
         </is>
       </c>
       <c r="N123">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="O123">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P123">
         <v>2.05</v>
       </c>
       <c r="Q123">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="R123">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S123">
         <v>1.3</v>
@@ -20403,13 +20403,13 @@
         <v>1.9</v>
       </c>
       <c r="AC123">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
       <c r="AD123">
         <v>1.34</v>
       </c>
       <c r="AE123">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF123">
         <v>1.67</v>
@@ -20521,31 +20521,31 @@
         </is>
       </c>
       <c r="N124">
-        <v>2.18</v>
+        <v>2.31</v>
       </c>
       <c r="O124">
         <v>3.2</v>
       </c>
       <c r="P124">
-        <v>2.95</v>
+        <v>2.74</v>
       </c>
       <c r="Q124">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="R124">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="S124">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T124">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="U124">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="V124">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W124">
         <v>1.04</v>
@@ -20554,31 +20554,31 @@
         <v>1.01</v>
       </c>
       <c r="Y124">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z124">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA124">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AB124">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AC124">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AD124">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE124">
         <v>1.11</v>
       </c>
       <c r="AF124">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG124">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK124">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20684,16 +20684,16 @@
         </is>
       </c>
       <c r="N125">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="O125">
         <v>3.25</v>
       </c>
       <c r="P125">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q125">
-        <v>3.45</v>
+        <v>3.66</v>
       </c>
       <c r="R125">
         <v>2.15</v>
@@ -20705,7 +20705,7 @@
         <v>2.66</v>
       </c>
       <c r="U125">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="V125">
         <v>1.39</v>
@@ -20726,10 +20726,10 @@
         <v>1.95</v>
       </c>
       <c r="AB125">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AC125">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AD125">
         <v>1.28</v>
@@ -20847,13 +20847,13 @@
         </is>
       </c>
       <c r="N126">
-        <v>2.3</v>
+        <v>2.47</v>
       </c>
       <c r="O126">
         <v>3.2</v>
       </c>
       <c r="P126">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="Q126">
         <v>0</v>
@@ -21173,19 +21173,19 @@
         </is>
       </c>
       <c r="N128">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="O128">
         <v>3.5</v>
       </c>
       <c r="P128">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="Q128">
         <v>2.3</v>
       </c>
       <c r="R128">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="S128">
         <v>1.43</v>
@@ -21197,7 +21197,7 @@
         <v>3.04</v>
       </c>
       <c r="V128">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W128">
         <v>1.05</v>
@@ -21206,22 +21206,22 @@
         <v>1.06</v>
       </c>
       <c r="Y128">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Z128">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AA128">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AB128">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AC128">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="AD128">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AE128">
         <v>1.07</v>
@@ -21230,7 +21230,7 @@
         <v>2.05</v>
       </c>
       <c r="AG128">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AK128">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21532,10 +21532,10 @@
         <v>1.02</v>
       </c>
       <c r="Y130">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z130">
-        <v>4.55</v>
+        <v>4.9</v>
       </c>
       <c r="AA130">
         <v>1.57</v>
@@ -21547,7 +21547,7 @@
         <v>2.4</v>
       </c>
       <c r="AD130">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AE130">
         <v>1.22</v>
@@ -22320,7 +22320,7 @@
         <v>3.55</v>
       </c>
       <c r="P135">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="Q135">
         <v>2.4</v>
@@ -22362,10 +22362,10 @@
         <v>3.12</v>
       </c>
       <c r="AD135">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE135">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF135">
         <v>1.75</v>
@@ -22384,7 +22384,7 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK135">
         <v>1.85</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,64 +24270,64 @@
         </is>
       </c>
       <c r="N147">
-        <v>2.95</v>
+        <v>4.3</v>
       </c>
       <c r="O147">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="P147">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="Q147">
-        <v>3.78</v>
+        <v>5.03</v>
       </c>
       <c r="R147">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="S147">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T147">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="U147">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="V147">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W147">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X147">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y147">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="Z147">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AA147">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="AB147">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AC147">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="AD147">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE147">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF147">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AG147">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AK147">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G148">
@@ -24433,19 +24433,19 @@
         </is>
       </c>
       <c r="N148">
-        <v>4.3</v>
+        <v>2.65</v>
       </c>
       <c r="O148">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="P148">
-        <v>1.7</v>
+        <v>2.35</v>
       </c>
       <c r="Q148">
-        <v>5.03</v>
+        <v>3.4</v>
       </c>
       <c r="R148">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="S148">
         <v>1.4</v>
@@ -24457,25 +24457,25 @@
         <v>2.9</v>
       </c>
       <c r="V148">
+        <v>1.34</v>
+      </c>
+      <c r="W148">
+        <v>1.04</v>
+      </c>
+      <c r="X148">
+        <v>1.05</v>
+      </c>
+      <c r="Y148">
         <v>1.35</v>
-      </c>
-      <c r="W148">
-        <v>1.05</v>
-      </c>
-      <c r="X148">
-        <v>1.03</v>
-      </c>
-      <c r="Y148">
-        <v>1.34</v>
       </c>
       <c r="Z148">
         <v>2.9</v>
       </c>
       <c r="AA148">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AB148">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AC148">
         <v>3.7</v>
@@ -24484,13 +24484,13 @@
         <v>1.22</v>
       </c>
       <c r="AE148">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF148">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="AG148">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
@@ -24503,10 +24503,10 @@
         </is>
       </c>
       <c r="AJ148">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AK148">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="AL148">
         <v>0</v>
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G149">
@@ -24596,31 +24596,31 @@
         </is>
       </c>
       <c r="N149">
-        <v>2.65</v>
+        <v>2.95</v>
       </c>
       <c r="O149">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P149">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="Q149">
-        <v>3.4</v>
+        <v>3.78</v>
       </c>
       <c r="R149">
         <v>2.08</v>
       </c>
       <c r="S149">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T149">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U149">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="V149">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="W149">
         <v>1.04</v>
@@ -24629,31 +24629,31 @@
         <v>1.05</v>
       </c>
       <c r="Y149">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="Z149">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AA149">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AB149">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC149">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AD149">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE149">
         <v>1.05</v>
       </c>
       <c r="AF149">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AG149">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AH149" t="inlineStr">
         <is>
@@ -24669,7 +24669,7 @@
         <v>1.32</v>
       </c>
       <c r="AK149">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="AL149">
         <v>0</v>
@@ -24759,13 +24759,13 @@
         </is>
       </c>
       <c r="N150">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="O150">
-        <v>8.4</v>
+        <v>7.5</v>
       </c>
       <c r="P150">
-        <v>11.41</v>
+        <v>11</v>
       </c>
       <c r="Q150">
         <v>1.44</v>
@@ -24774,10 +24774,10 @@
         <v>3.2</v>
       </c>
       <c r="S150">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="T150">
-        <v>5.4</v>
+        <v>5.55</v>
       </c>
       <c r="U150">
         <v>1.7</v>
@@ -24801,13 +24801,13 @@
         <v>1.22</v>
       </c>
       <c r="AB150">
-        <v>3.96</v>
+        <v>3.98</v>
       </c>
       <c r="AC150">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AD150">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AE150">
         <v>1.6</v>
@@ -25100,7 +25100,7 @@
         <v>2.59</v>
       </c>
       <c r="S152">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T152">
         <v>3.5</v>
@@ -25109,28 +25109,28 @@
         <v>2.24</v>
       </c>
       <c r="V152">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W152">
         <v>1.15</v>
       </c>
       <c r="X152">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y152">
         <v>1.14</v>
       </c>
       <c r="Z152">
-        <v>4.55</v>
+        <v>4.8</v>
       </c>
       <c r="AA152">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AB152">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="AC152">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="AD152">
         <v>1.5</v>
@@ -25139,10 +25139,10 @@
         <v>1.2</v>
       </c>
       <c r="AF152">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG152">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -25155,7 +25155,7 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AK152">
         <v>3.6</v>
@@ -25462,7 +25462,7 @@
         <v>1.25</v>
       </c>
       <c r="AE154">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF154">
         <v>1.75</v>
@@ -25592,7 +25592,7 @@
         <v>1.44</v>
       </c>
       <c r="T155">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="U155">
         <v>3.16</v>
@@ -25601,7 +25601,7 @@
         <v>1.3</v>
       </c>
       <c r="W155">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X155">
         <v>1.06</v>
@@ -25622,10 +25622,10 @@
         <v>4</v>
       </c>
       <c r="AD155">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE155">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF155">
         <v>1.91</v>
@@ -25909,7 +25909,7 @@
         <v>4.6</v>
       </c>
       <c r="Q157">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="R157">
         <v>2.48</v>
@@ -25918,10 +25918,10 @@
         <v>1.24</v>
       </c>
       <c r="T157">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U157">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="V157">
         <v>1.62</v>
@@ -25939,10 +25939,10 @@
         <v>5</v>
       </c>
       <c r="AA157">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AB157">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="AC157">
         <v>2.23</v>
@@ -25951,7 +25951,7 @@
         <v>1.56</v>
       </c>
       <c r="AE157">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF157">
         <v>1.6</v>
@@ -25970,7 +25970,7 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK157">
         <v>2.1</v>
@@ -26063,61 +26063,61 @@
         </is>
       </c>
       <c r="N158">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="O158">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="P158">
         <v>3.4</v>
       </c>
       <c r="Q158">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="R158">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="S158">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T158">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="U158">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="V158">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="W158">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X158">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y158">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z158">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="AA158">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB158">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AC158">
-        <v>3.12</v>
+        <v>3.09</v>
       </c>
       <c r="AD158">
         <v>1.34</v>
       </c>
       <c r="AE158">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF158">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AG158">
         <v>2</v>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK158">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26232,7 +26232,7 @@
         <v>3.73</v>
       </c>
       <c r="P159">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Q159">
         <v>0</v>
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G163">
@@ -26878,64 +26878,64 @@
         </is>
       </c>
       <c r="N163">
-        <v>3.3</v>
+        <v>2.45</v>
       </c>
       <c r="O163">
-        <v>3.03</v>
+        <v>3.25</v>
       </c>
       <c r="P163">
-        <v>1.94</v>
+        <v>2.45</v>
       </c>
       <c r="Q163">
-        <v>3.85</v>
+        <v>3.08</v>
       </c>
       <c r="R163">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S163">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T163">
-        <v>2.8</v>
+        <v>3.16</v>
       </c>
       <c r="U163">
-        <v>2.85</v>
+        <v>2.62</v>
       </c>
       <c r="V163">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="W163">
+        <v>1.07</v>
+      </c>
+      <c r="X163">
         <v>1.05</v>
       </c>
-      <c r="X163">
-        <v>1.04</v>
-      </c>
       <c r="Y163">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z163">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="AA163">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AB163">
-        <v>1.72</v>
+        <v>2.01</v>
       </c>
       <c r="AC163">
-        <v>3.6</v>
+        <v>2.72</v>
       </c>
       <c r="AD163">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AE163">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF163">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AG163">
-        <v>1.85</v>
+        <v>2.19</v>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
@@ -26948,10 +26948,10 @@
         </is>
       </c>
       <c r="AJ163">
-        <v>1.74</v>
+        <v>1.29</v>
       </c>
       <c r="AK163">
-        <v>1.29</v>
+        <v>1.47</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G164">
@@ -27041,64 +27041,64 @@
         </is>
       </c>
       <c r="N164">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="O164">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P164">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="Q164">
-        <v>3.08</v>
+        <v>2.65</v>
       </c>
       <c r="R164">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="S164">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T164">
-        <v>3.16</v>
+        <v>2.7</v>
       </c>
       <c r="U164">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="V164">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W164">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X164">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y164">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z164">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AA164">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AB164">
-        <v>2.01</v>
+        <v>1.89</v>
       </c>
       <c r="AC164">
-        <v>2.72</v>
+        <v>3.4</v>
       </c>
       <c r="AD164">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE164">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF164">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG164">
-        <v>2.19</v>
+        <v>1.86</v>
       </c>
       <c r="AH164" t="inlineStr">
         <is>
@@ -27111,10 +27111,10 @@
         </is>
       </c>
       <c r="AJ164">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK164">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="AL164">
         <v>0</v>
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G165">
@@ -27204,28 +27204,28 @@
         </is>
       </c>
       <c r="N165">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="O165">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P165">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="Q165">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="R165">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="S165">
         <v>1.4</v>
       </c>
       <c r="T165">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="U165">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="V165">
         <v>1.4</v>
@@ -27234,19 +27234,19 @@
         <v>1.06</v>
       </c>
       <c r="X165">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y165">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="Z165">
         <v>3.4</v>
       </c>
       <c r="AA165">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB165">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="AC165">
         <v>3.4</v>
@@ -27255,13 +27255,13 @@
         <v>1.29</v>
       </c>
       <c r="AE165">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF165">
         <v>1.75</v>
       </c>
       <c r="AG165">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AH165" t="inlineStr">
         <is>
@@ -27274,10 +27274,10 @@
         </is>
       </c>
       <c r="AJ165">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK165">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AL165">
         <v>0</v>
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G166">
@@ -27367,61 +27367,61 @@
         </is>
       </c>
       <c r="N166">
-        <v>1.94</v>
+        <v>2.22</v>
       </c>
       <c r="O166">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P166">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="Q166">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="R166">
-        <v>2.14</v>
+        <v>1.96</v>
       </c>
       <c r="S166">
         <v>1.4</v>
       </c>
       <c r="T166">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="U166">
         <v>2.88</v>
       </c>
       <c r="V166">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W166">
+        <v>1.04</v>
+      </c>
+      <c r="X166">
         <v>1.06</v>
       </c>
-      <c r="X166">
-        <v>1.01</v>
-      </c>
       <c r="Y166">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Z166">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="AA166">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB166">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="AC166">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="AD166">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE166">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF166">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AG166">
         <v>1.9</v>
@@ -27437,10 +27437,10 @@
         </is>
       </c>
       <c r="AJ166">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AK166">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AL166">
         <v>0</v>
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G168">
@@ -27693,80 +27693,80 @@
         </is>
       </c>
       <c r="N168">
-        <v>2.22</v>
+        <v>3.3</v>
       </c>
       <c r="O168">
-        <v>3.1</v>
+        <v>3.03</v>
       </c>
       <c r="P168">
-        <v>2.75</v>
+        <v>1.94</v>
       </c>
       <c r="Q168">
-        <v>2.88</v>
+        <v>3.85</v>
       </c>
       <c r="R168">
+        <v>2.1</v>
+      </c>
+      <c r="S168">
+        <v>1.41</v>
+      </c>
+      <c r="T168">
+        <v>2.8</v>
+      </c>
+      <c r="U168">
+        <v>2.85</v>
+      </c>
+      <c r="V168">
+        <v>1.37</v>
+      </c>
+      <c r="W168">
+        <v>1.05</v>
+      </c>
+      <c r="X168">
+        <v>1.04</v>
+      </c>
+      <c r="Y168">
+        <v>1.3</v>
+      </c>
+      <c r="Z168">
+        <v>3.2</v>
+      </c>
+      <c r="AA168">
         <v>1.96</v>
       </c>
-      <c r="S168">
-        <v>1.4</v>
-      </c>
-      <c r="T168">
-        <v>2.7</v>
-      </c>
-      <c r="U168">
-        <v>2.88</v>
-      </c>
-      <c r="V168">
-        <v>1.33</v>
-      </c>
-      <c r="W168">
-        <v>1.04</v>
-      </c>
-      <c r="X168">
+      <c r="AB168">
+        <v>1.72</v>
+      </c>
+      <c r="AC168">
+        <v>3.6</v>
+      </c>
+      <c r="AD168">
+        <v>1.26</v>
+      </c>
+      <c r="AE168">
         <v>1.06</v>
       </c>
-      <c r="Y168">
+      <c r="AF168">
+        <v>1.76</v>
+      </c>
+      <c r="AG168">
+        <v>1.85</v>
+      </c>
+      <c r="AH168" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI168" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ168">
+        <v>1.74</v>
+      </c>
+      <c r="AK168">
         <v>1.29</v>
-      </c>
-      <c r="Z168">
-        <v>3.05</v>
-      </c>
-      <c r="AA168">
-        <v>2</v>
-      </c>
-      <c r="AB168">
-        <v>1.68</v>
-      </c>
-      <c r="AC168">
-        <v>3.55</v>
-      </c>
-      <c r="AD168">
-        <v>1.25</v>
-      </c>
-      <c r="AE168">
-        <v>1.07</v>
-      </c>
-      <c r="AF168">
-        <v>1.87</v>
-      </c>
-      <c r="AG168">
-        <v>1.9</v>
-      </c>
-      <c r="AH168" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI168" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ168">
-        <v>1.41</v>
-      </c>
-      <c r="AK168">
-        <v>1.5</v>
       </c>
       <c r="AL168">
         <v>0</v>
@@ -27859,10 +27859,10 @@
         <v>4.11</v>
       </c>
       <c r="O169">
-        <v>3.76</v>
+        <v>3.82</v>
       </c>
       <c r="P169">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Q169">
         <v>0</v>
@@ -28025,7 +28025,7 @@
         <v>4.14</v>
       </c>
       <c r="P170">
-        <v>5.41</v>
+        <v>5.52</v>
       </c>
       <c r="Q170">
         <v>0</v>
@@ -28345,43 +28345,43 @@
         </is>
       </c>
       <c r="N172">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="O172">
         <v>3.1</v>
       </c>
       <c r="P172">
-        <v>3.65</v>
+        <v>3.89</v>
       </c>
       <c r="Q172">
-        <v>2.61</v>
+        <v>2.91</v>
       </c>
       <c r="R172">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="S172">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="T172">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="U172">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="V172">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W172">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X172">
         <v>1.05</v>
       </c>
       <c r="Y172">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="Z172">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="AA172">
         <v>2.25</v>
@@ -28390,19 +28390,19 @@
         <v>1.57</v>
       </c>
       <c r="AC172">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AD172">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AE172">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF172">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AG172">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AH172" t="inlineStr">
         <is>
@@ -28415,10 +28415,10 @@
         </is>
       </c>
       <c r="AJ172">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK172">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -28508,64 +28508,64 @@
         </is>
       </c>
       <c r="N173">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="O173">
         <v>4.1</v>
       </c>
       <c r="P173">
-        <v>7.25</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="Q173">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="R173">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="S173">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T173">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="U173">
         <v>2.82</v>
       </c>
       <c r="V173">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W173">
         <v>1.06</v>
       </c>
       <c r="X173">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y173">
         <v>1.26</v>
       </c>
       <c r="Z173">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="AA173">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AB173">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AC173">
-        <v>3.28</v>
+        <v>3.05</v>
       </c>
       <c r="AD173">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE173">
         <v>1.07</v>
       </c>
       <c r="AF173">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="AG173">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="AH173" t="inlineStr">
         <is>
@@ -28578,10 +28578,10 @@
         </is>
       </c>
       <c r="AJ173">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK173">
-        <v>2.88</v>
+        <v>3.12</v>
       </c>
       <c r="AL173">
         <v>0</v>
@@ -28671,13 +28671,13 @@
         </is>
       </c>
       <c r="N174">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="O174">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P174">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q174">
         <v>2.9</v>
@@ -28707,28 +28707,28 @@
         <v>1.33</v>
       </c>
       <c r="Z174">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AA174">
         <v>2.17</v>
       </c>
       <c r="AB174">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AC174">
-        <v>3.93</v>
+        <v>3.54</v>
       </c>
       <c r="AD174">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE174">
         <v>1.08</v>
       </c>
       <c r="AF174">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AG174">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH174" t="inlineStr">
         <is>
@@ -28744,7 +28744,7 @@
         <v>1.3</v>
       </c>
       <c r="AK174">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL174">
         <v>0</v>
@@ -29000,13 +29000,13 @@
         <v>2.25</v>
       </c>
       <c r="O176">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P176">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="Q176">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="R176">
         <v>2.34</v>
@@ -29015,10 +29015,10 @@
         <v>1.22</v>
       </c>
       <c r="T176">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="U176">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V176">
         <v>1.65</v>
@@ -29027,34 +29027,34 @@
         <v>1.18</v>
       </c>
       <c r="X176">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y176">
         <v>1.11</v>
       </c>
       <c r="Z176">
-        <v>6</v>
+        <v>4.95</v>
       </c>
       <c r="AA176">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AB176">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AC176">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AD176">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AE176">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AF176">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AG176">
-        <v>2.75</v>
+        <v>2.57</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,7 +29067,7 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="AK176">
         <v>1.5</v>
@@ -29652,13 +29652,13 @@
         <v>1.48</v>
       </c>
       <c r="O180">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="P180">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="Q180">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="R180">
         <v>2.42</v>
@@ -29679,7 +29679,7 @@
         <v>1.14</v>
       </c>
       <c r="X180">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y180">
         <v>1.14</v>
@@ -29981,7 +29981,7 @@
         <v>5.8</v>
       </c>
       <c r="P182">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="Q182">
         <v>8.5</v>
@@ -30002,7 +30002,7 @@
         <v>1.58</v>
       </c>
       <c r="W182">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X182">
         <v>1.03</v>
@@ -30045,7 +30045,7 @@
         </is>
       </c>
       <c r="AJ182">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="AK182">
         <v>1.02</v>
@@ -30959,7 +30959,7 @@
         <v>7</v>
       </c>
       <c r="P188">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q188">
         <v>1.53</v>
@@ -30992,7 +30992,7 @@
         <v>8.5</v>
       </c>
       <c r="AA188">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AB188">
         <v>3.6</v>
@@ -31279,10 +31279,10 @@
         </is>
       </c>
       <c r="N190">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="O190">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="P190">
         <v>2.4</v>
@@ -31330,13 +31330,13 @@
         <v>1.22</v>
       </c>
       <c r="AE190">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF190">
         <v>1.8</v>
       </c>
       <c r="AG190">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AH190" t="inlineStr">
         <is>
@@ -32423,13 +32423,13 @@
         <v>2.14</v>
       </c>
       <c r="O197">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="P197">
         <v>2.85</v>
       </c>
       <c r="Q197">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="R197">
         <v>2.23</v>
@@ -32444,7 +32444,7 @@
         <v>2.38</v>
       </c>
       <c r="V197">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W197">
         <v>1.13</v>
@@ -32453,25 +32453,25 @@
         <v>1.02</v>
       </c>
       <c r="Y197">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="Z197">
         <v>4.33</v>
       </c>
       <c r="AA197">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AB197">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="AC197">
         <v>2.49</v>
       </c>
       <c r="AD197">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AE197">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF197">
         <v>1.51</v>
@@ -32493,7 +32493,7 @@
         <v>1.22</v>
       </c>
       <c r="AK197">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -32583,13 +32583,13 @@
         </is>
       </c>
       <c r="N198">
-        <v>3.25</v>
+        <v>3.57</v>
       </c>
       <c r="O198">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="P198">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="Q198">
         <v>3.75</v>
@@ -32619,28 +32619,28 @@
         <v>1.16</v>
       </c>
       <c r="Z198">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="AA198">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AB198">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="AC198">
         <v>2.59</v>
       </c>
       <c r="AD198">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AE198">
         <v>1.19</v>
       </c>
       <c r="AF198">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG198">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AH198" t="inlineStr">
         <is>
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G199">
@@ -32746,64 +32746,64 @@
         </is>
       </c>
       <c r="N199">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="O199">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P199">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="Q199">
-        <v>2.87</v>
+        <v>3.02</v>
       </c>
       <c r="R199">
-        <v>2.31</v>
+        <v>1.94</v>
       </c>
       <c r="S199">
-        <v>1.31</v>
+        <v>1.46</v>
       </c>
       <c r="T199">
-        <v>3.25</v>
+        <v>2.44</v>
       </c>
       <c r="U199">
-        <v>2.47</v>
+        <v>3.2</v>
       </c>
       <c r="V199">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="W199">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X199">
+        <v>1.04</v>
+      </c>
+      <c r="Y199">
+        <v>1.38</v>
+      </c>
+      <c r="Z199">
+        <v>2.62</v>
+      </c>
+      <c r="AA199">
+        <v>2.2</v>
+      </c>
+      <c r="AB199">
+        <v>1.62</v>
+      </c>
+      <c r="AC199">
+        <v>4.05</v>
+      </c>
+      <c r="AD199">
+        <v>1.2</v>
+      </c>
+      <c r="AE199">
         <v>1.02</v>
       </c>
-      <c r="Y199">
-        <v>1.22</v>
-      </c>
-      <c r="Z199">
-        <v>3.95</v>
-      </c>
-      <c r="AA199">
-        <v>1.72</v>
-      </c>
-      <c r="AB199">
-        <v>2</v>
-      </c>
-      <c r="AC199">
-        <v>2.75</v>
-      </c>
-      <c r="AD199">
-        <v>1.42</v>
-      </c>
-      <c r="AE199">
-        <v>1.12</v>
-      </c>
       <c r="AF199">
-        <v>1.55</v>
+        <v>1.92</v>
       </c>
       <c r="AG199">
-        <v>2.17</v>
+        <v>1.77</v>
       </c>
       <c r="AH199" t="inlineStr">
         <is>
@@ -32816,10 +32816,10 @@
         </is>
       </c>
       <c r="AJ199">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AK199">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AL199">
         <v>0</v>
@@ -32909,7 +32909,7 @@
         </is>
       </c>
       <c r="N200">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="O200">
         <v>3.7</v>
@@ -32924,19 +32924,19 @@
         <v>2.41</v>
       </c>
       <c r="S200">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="T200">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U200">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="V200">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="W200">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X200">
         <v>1.02</v>
@@ -32951,22 +32951,22 @@
         <v>1.67</v>
       </c>
       <c r="AB200">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="AC200">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="AD200">
         <v>1.4</v>
       </c>
       <c r="AE200">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AF200">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AG200">
-        <v>2.35</v>
+        <v>2.19</v>
       </c>
       <c r="AH200" t="inlineStr">
         <is>
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G201">
@@ -33072,64 +33072,64 @@
         </is>
       </c>
       <c r="N201">
-        <v>2.35</v>
+        <v>2.58</v>
       </c>
       <c r="O201">
+        <v>3.4</v>
+      </c>
+      <c r="P201">
+        <v>2.29</v>
+      </c>
+      <c r="Q201">
         <v>3.1</v>
       </c>
-      <c r="P201">
-        <v>2.92</v>
-      </c>
-      <c r="Q201">
-        <v>3.02</v>
-      </c>
       <c r="R201">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="S201">
+        <v>1.31</v>
+      </c>
+      <c r="T201">
+        <v>3.2</v>
+      </c>
+      <c r="U201">
+        <v>2.44</v>
+      </c>
+      <c r="V201">
         <v>1.44</v>
       </c>
-      <c r="T201">
-        <v>2.5</v>
-      </c>
-      <c r="U201">
-        <v>3.1</v>
-      </c>
-      <c r="V201">
-        <v>1.33</v>
-      </c>
       <c r="W201">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X201">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y201">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="Z201">
-        <v>2.62</v>
+        <v>3.95</v>
       </c>
       <c r="AA201">
-        <v>2.2</v>
+        <v>1.69</v>
       </c>
       <c r="AB201">
-        <v>1.62</v>
+        <v>2.04</v>
       </c>
       <c r="AC201">
-        <v>4.05</v>
+        <v>2.78</v>
       </c>
       <c r="AD201">
-        <v>1.19</v>
+        <v>1.42</v>
       </c>
       <c r="AE201">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AF201">
-        <v>1.92</v>
+        <v>1.55</v>
       </c>
       <c r="AG201">
-        <v>1.77</v>
+        <v>2.23</v>
       </c>
       <c r="AH201" t="inlineStr">
         <is>
@@ -33142,10 +33142,10 @@
         </is>
       </c>
       <c r="AJ201">
-        <v>1.29</v>
+        <v>1.52</v>
       </c>
       <c r="AK201">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AL201">
         <v>0</v>
@@ -33259,10 +33259,10 @@
         <v>2.8</v>
       </c>
       <c r="V202">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W202">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X202">
         <v>1.03</v>
@@ -33283,7 +33283,7 @@
         <v>3.4</v>
       </c>
       <c r="AD202">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE202">
         <v>1.11</v>
@@ -33292,7 +33292,7 @@
         <v>1.9</v>
       </c>
       <c r="AG202">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AH202" t="inlineStr">
         <is>
@@ -33305,7 +33305,7 @@
         </is>
       </c>
       <c r="AJ202">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK202">
         <v>2.3</v>
@@ -33401,16 +33401,16 @@
         <v>2.08</v>
       </c>
       <c r="O203">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P203">
-        <v>3.16</v>
+        <v>3.4</v>
       </c>
       <c r="Q203">
         <v>2.59</v>
       </c>
       <c r="R203">
-        <v>2.27</v>
+        <v>2.09</v>
       </c>
       <c r="S203">
         <v>1.3</v>
@@ -33425,7 +33425,7 @@
         <v>1.44</v>
       </c>
       <c r="W203">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X203">
         <v>1</v>
@@ -33440,10 +33440,10 @@
         <v>1.8</v>
       </c>
       <c r="AB203">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AC203">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="AD203">
         <v>1.3</v>
@@ -33455,7 +33455,7 @@
         <v>1.66</v>
       </c>
       <c r="AG203">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH203" t="inlineStr">
         <is>
@@ -33887,16 +33887,16 @@
         </is>
       </c>
       <c r="N206">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="O206">
-        <v>3.4</v>
+        <v>3.13</v>
       </c>
       <c r="P206">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="Q206">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="R206">
         <v>1.99</v>
@@ -33914,7 +33914,7 @@
         <v>1.4</v>
       </c>
       <c r="W206">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X206">
         <v>1.06</v>
@@ -34053,61 +34053,61 @@
         <v>1.38</v>
       </c>
       <c r="O207">
+        <v>4.6</v>
+      </c>
+      <c r="P207">
+        <v>6</v>
+      </c>
+      <c r="Q207">
+        <v>1.88</v>
+      </c>
+      <c r="R207">
+        <v>2.41</v>
+      </c>
+      <c r="S207">
+        <v>1.27</v>
+      </c>
+      <c r="T207">
+        <v>3.25</v>
+      </c>
+      <c r="U207">
+        <v>2.52</v>
+      </c>
+      <c r="V207">
+        <v>1.51</v>
+      </c>
+      <c r="W207">
+        <v>1.1</v>
+      </c>
+      <c r="X207">
+        <v>1.02</v>
+      </c>
+      <c r="Y207">
+        <v>1.18</v>
+      </c>
+      <c r="Z207">
         <v>4.4</v>
       </c>
-      <c r="P207">
-        <v>5.9</v>
-      </c>
-      <c r="Q207">
-        <v>0</v>
-      </c>
-      <c r="R207">
-        <v>0</v>
-      </c>
-      <c r="S207">
-        <v>0</v>
-      </c>
-      <c r="T207">
-        <v>0</v>
-      </c>
-      <c r="U207">
-        <v>0</v>
-      </c>
-      <c r="V207">
-        <v>0</v>
-      </c>
-      <c r="W207">
-        <v>0</v>
-      </c>
-      <c r="X207">
-        <v>0</v>
-      </c>
-      <c r="Y207">
-        <v>0</v>
-      </c>
-      <c r="Z207">
-        <v>0</v>
-      </c>
       <c r="AA207">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB207">
         <v>2.1</v>
       </c>
       <c r="AC207">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD207">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE207">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF207">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG207">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
@@ -34120,10 +34120,10 @@
         </is>
       </c>
       <c r="AJ207">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK207">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34539,64 +34539,64 @@
         </is>
       </c>
       <c r="N210">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="O210">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="P210">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q210">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="R210">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="S210">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T210">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U210">
-        <v>2.65</v>
+        <v>3.19</v>
       </c>
       <c r="V210">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="W210">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X210">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y210">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z210">
-        <v>3.35</v>
+        <v>2.92</v>
       </c>
       <c r="AA210">
-        <v>1.9</v>
+        <v>2.07</v>
       </c>
       <c r="AB210">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AC210">
-        <v>2.9</v>
+        <v>3.81</v>
       </c>
       <c r="AD210">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AE210">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF210">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="AG210">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AH210" t="inlineStr">
         <is>
@@ -34609,10 +34609,10 @@
         </is>
       </c>
       <c r="AJ210">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AK210">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AL210">
         <v>0</v>
@@ -34871,7 +34871,7 @@
         <v>3.65</v>
       </c>
       <c r="P212">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="Q212">
         <v>2.44</v>
@@ -34904,7 +34904,7 @@
         <v>3.96</v>
       </c>
       <c r="AA212">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AB212">
         <v>2.2</v>
@@ -34938,7 +34938,7 @@
         <v>1.24</v>
       </c>
       <c r="AK212">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AL212">
         <v>0</v>
@@ -35028,13 +35028,13 @@
         </is>
       </c>
       <c r="N213">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="O213">
         <v>3.45</v>
       </c>
       <c r="P213">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="Q213">
         <v>2.62</v>
@@ -35049,7 +35049,7 @@
         <v>3.12</v>
       </c>
       <c r="U213">
-        <v>2.38</v>
+        <v>2.51</v>
       </c>
       <c r="V213">
         <v>1.51</v>
@@ -35058,7 +35058,7 @@
         <v>1.12</v>
       </c>
       <c r="X213">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y213">
         <v>1.17</v>
@@ -35067,10 +35067,10 @@
         <v>3.98</v>
       </c>
       <c r="AA213">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB213">
-        <v>2.09</v>
+        <v>1.81</v>
       </c>
       <c r="AC213">
         <v>2.59</v>
@@ -35082,10 +35082,10 @@
         <v>1.12</v>
       </c>
       <c r="AF213">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AG213">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AH213" t="inlineStr">
         <is>
@@ -35197,7 +35197,7 @@
         <v>3.6</v>
       </c>
       <c r="P214">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="Q214">
         <v>4.6</v>
@@ -35212,7 +35212,7 @@
         <v>3</v>
       </c>
       <c r="U214">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V214">
         <v>1.44</v>
@@ -35221,25 +35221,25 @@
         <v>1.06</v>
       </c>
       <c r="X214">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y214">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z214">
-        <v>3.47</v>
+        <v>3.49</v>
       </c>
       <c r="AA214">
         <v>1.84</v>
       </c>
       <c r="AB214">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AC214">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AD214">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE214">
         <v>1.08</v>

--- a/jogos_2026-08-08.xlsx
+++ b/jogos_2026-08-08.xlsx
@@ -801,10 +801,10 @@
         <v>2.5</v>
       </c>
       <c r="O3">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="P3">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>4</v>
+        <v>2.13</v>
       </c>
       <c r="O4">
-        <v>3.18</v>
+        <v>3.39</v>
       </c>
       <c r="P4">
-        <v>1.7</v>
+        <v>2.47</v>
       </c>
       <c r="Q4">
-        <v>4.24</v>
+        <v>2.4</v>
       </c>
       <c r="R4">
-        <v>2.04</v>
+        <v>2.36</v>
       </c>
       <c r="S4">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="T4">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="U4">
-        <v>2.75</v>
+        <v>2.13</v>
       </c>
       <c r="V4">
+        <v>1.62</v>
+      </c>
+      <c r="W4">
+        <v>1.18</v>
+      </c>
+      <c r="X4">
+        <v>1.02</v>
+      </c>
+      <c r="Y4">
+        <v>1.14</v>
+      </c>
+      <c r="Z4">
+        <v>5.15</v>
+      </c>
+      <c r="AA4">
+        <v>1.43</v>
+      </c>
+      <c r="AB4">
+        <v>2.5</v>
+      </c>
+      <c r="AC4">
+        <v>2.2</v>
+      </c>
+      <c r="AD4">
+        <v>1.66</v>
+      </c>
+      <c r="AE4">
+        <v>1.2</v>
+      </c>
+      <c r="AF4">
         <v>1.4</v>
       </c>
-      <c r="W4">
-        <v>1.08</v>
-      </c>
-      <c r="X4">
-        <v>1</v>
-      </c>
-      <c r="Y4">
-        <v>1.26</v>
-      </c>
-      <c r="Z4">
-        <v>3.2</v>
-      </c>
-      <c r="AA4">
-        <v>1.97</v>
-      </c>
-      <c r="AB4">
-        <v>1.79</v>
-      </c>
-      <c r="AC4">
-        <v>3.5</v>
-      </c>
-      <c r="AD4">
-        <v>1.25</v>
-      </c>
-      <c r="AE4">
-        <v>1.12</v>
-      </c>
-      <c r="AF4">
-        <v>1.82</v>
-      </c>
       <c r="AG4">
-        <v>1.85</v>
+        <v>2.62</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.21</v>
       </c>
       <c r="AK4">
-        <v>1.13</v>
+        <v>1.53</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.13</v>
+        <v>4</v>
       </c>
       <c r="O5">
-        <v>3.39</v>
+        <v>3.18</v>
       </c>
       <c r="P5">
-        <v>2.47</v>
+        <v>1.7</v>
       </c>
       <c r="Q5">
-        <v>2.4</v>
+        <v>4.24</v>
       </c>
       <c r="R5">
-        <v>2.36</v>
+        <v>2.04</v>
       </c>
       <c r="S5">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="T5">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="U5">
-        <v>2.13</v>
+        <v>2.75</v>
       </c>
       <c r="V5">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="W5">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="X5">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="Z5">
-        <v>5.15</v>
+        <v>3.2</v>
       </c>
       <c r="AA5">
-        <v>1.43</v>
+        <v>1.97</v>
       </c>
       <c r="AB5">
-        <v>2.5</v>
+        <v>1.79</v>
       </c>
       <c r="AC5">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="AD5">
-        <v>1.66</v>
+        <v>1.25</v>
       </c>
       <c r="AE5">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AF5">
-        <v>1.4</v>
+        <v>1.82</v>
       </c>
       <c r="AG5">
-        <v>2.62</v>
+        <v>1.85</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>1.21</v>
       </c>
       <c r="AK5">
-        <v>1.53</v>
+        <v>1.13</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1785,55 +1785,55 @@
         <v>5.23</v>
       </c>
       <c r="Q9">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="R9">
         <v>2.09</v>
       </c>
       <c r="S9">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T9">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="U9">
-        <v>2.84</v>
+        <v>2.73</v>
       </c>
       <c r="V9">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="W9">
         <v>1.05</v>
       </c>
       <c r="X9">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z9">
-        <v>3.29</v>
+        <v>3.2</v>
       </c>
       <c r="AA9">
         <v>1.96</v>
       </c>
       <c r="AB9">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AC9">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="AD9">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AE9">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF9">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AG9">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>3.35</v>
+        <v>3.18</v>
       </c>
       <c r="O11">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="P11">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="O12">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P12">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2304,10 +2304,10 @@
         <v>0</v>
       </c>
       <c r="AA12">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB12">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AC12">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>3</v>
+        <v>2.68</v>
       </c>
       <c r="O13">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="P13">
-        <v>2.47</v>
+        <v>2.37</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="O14">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P14">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="O15">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="P15">
         <v>2.9</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O16">
-        <v>3.16</v>
+        <v>3.35</v>
       </c>
       <c r="P16">
-        <v>2.99</v>
+        <v>3.25</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -2956,10 +2956,10 @@
         <v>0</v>
       </c>
       <c r="AA16">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB16">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC16">
         <v>0</v>
@@ -3080,25 +3080,25 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="O17">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="P17">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="Q17">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="R17">
         <v>2.1</v>
       </c>
       <c r="S17">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T17">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="U17">
         <v>3.16</v>
@@ -3110,28 +3110,28 @@
         <v>1.01</v>
       </c>
       <c r="X17">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z17">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="AA17">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="AB17">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC17">
-        <v>3.78</v>
+        <v>4.1</v>
       </c>
       <c r="AD17">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE17">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF17">
         <v>1.85</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="N19">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="O19">
         <v>3.1</v>
@@ -3415,16 +3415,16 @@
         <v>1.91</v>
       </c>
       <c r="Q19">
-        <v>5.57</v>
+        <v>5.55</v>
       </c>
       <c r="R19">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="S19">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="T19">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="U19">
         <v>3.6</v>
@@ -3436,19 +3436,19 @@
         <v>1.01</v>
       </c>
       <c r="X19">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Y19">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Z19">
         <v>2.5</v>
       </c>
       <c r="AA19">
-        <v>2.4</v>
+        <v>2.64</v>
       </c>
       <c r="AB19">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AC19">
         <v>4.55</v>
@@ -3460,10 +3460,10 @@
         <v>1.01</v>
       </c>
       <c r="AF19">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AG19">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK19">
         <v>1.22</v>
@@ -3569,25 +3569,25 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="O20">
         <v>3.55</v>
       </c>
       <c r="P20">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q20">
         <v>2.62</v>
       </c>
       <c r="R20">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="S20">
         <v>1.33</v>
       </c>
       <c r="T20">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="U20">
         <v>2.59</v>
@@ -3605,28 +3605,28 @@
         <v>1.28</v>
       </c>
       <c r="Z20">
-        <v>3.73</v>
+        <v>3.77</v>
       </c>
       <c r="AA20">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AB20">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AC20">
-        <v>3.08</v>
+        <v>3.34</v>
       </c>
       <c r="AD20">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AE20">
         <v>1.06</v>
       </c>
       <c r="AF20">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG20">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3735,10 +3735,10 @@
         <v>2.44</v>
       </c>
       <c r="O21">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="P21">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="Q21">
         <v>3.14</v>
@@ -3747,19 +3747,19 @@
         <v>1.91</v>
       </c>
       <c r="S21">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="T21">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="U21">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="V21">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W21">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X21">
         <v>1.03</v>
@@ -3768,28 +3768,28 @@
         <v>1.36</v>
       </c>
       <c r="Z21">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="AA21">
         <v>2.25</v>
       </c>
       <c r="AB21">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AC21">
-        <v>4.47</v>
+        <v>4.52</v>
       </c>
       <c r="AD21">
         <v>1.16</v>
       </c>
       <c r="AE21">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF21">
         <v>1.91</v>
       </c>
       <c r="AG21">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3895,31 +3895,31 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="O22">
         <v>3.6</v>
       </c>
       <c r="P22">
-        <v>5.25</v>
+        <v>5.69</v>
       </c>
       <c r="Q22">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="R22">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="S22">
         <v>1.38</v>
       </c>
       <c r="T22">
-        <v>2.66</v>
+        <v>2.81</v>
       </c>
       <c r="U22">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="V22">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W22">
         <v>1.06</v>
@@ -3931,22 +3931,22 @@
         <v>1.3</v>
       </c>
       <c r="Z22">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA22">
         <v>2.02</v>
       </c>
       <c r="AB22">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="AC22">
-        <v>3.4</v>
+        <v>3.43</v>
       </c>
       <c r="AD22">
         <v>1.29</v>
       </c>
       <c r="AE22">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF22">
         <v>1.93</v>
@@ -4058,25 +4058,25 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="O23">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="P23">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="Q23">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R23">
         <v>2.25</v>
       </c>
       <c r="S23">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T23">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="U23">
         <v>2.62</v>
@@ -4091,22 +4091,22 @@
         <v>1</v>
       </c>
       <c r="Y23">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="Z23">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AA23">
         <v>1.8</v>
       </c>
       <c r="AB23">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC23">
-        <v>3.11</v>
+        <v>3.14</v>
       </c>
       <c r="AD23">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE23">
         <v>1.14</v>
@@ -4115,7 +4115,7 @@
         <v>1.65</v>
       </c>
       <c r="AG23">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>1.26</v>
       </c>
       <c r="AK23">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,31 +4221,31 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="O24">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="P24">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="Q24">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="R24">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="S24">
         <v>1.33</v>
       </c>
       <c r="T24">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U24">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="V24">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W24">
         <v>1.06</v>
@@ -4254,19 +4254,19 @@
         <v>1.04</v>
       </c>
       <c r="Y24">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="Z24">
-        <v>3.86</v>
+        <v>3.62</v>
       </c>
       <c r="AA24">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AB24">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC24">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="AD24">
         <v>1.33</v>
@@ -4294,7 +4294,7 @@
         <v>1.21</v>
       </c>
       <c r="AK24">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="O25">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P25">
-        <v>3.6</v>
+        <v>3.74</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -6180,7 +6180,7 @@
         <v>2.6</v>
       </c>
       <c r="O36">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P36">
         <v>2.4</v>
@@ -6207,7 +6207,7 @@
         <v>1.13</v>
       </c>
       <c r="X36">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y36">
         <v>1.11</v>
@@ -6222,13 +6222,13 @@
         <v>2.3</v>
       </c>
       <c r="AC36">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AD36">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AE36">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF36">
         <v>1.44</v>
@@ -6250,7 +6250,7 @@
         <v>1.48</v>
       </c>
       <c r="AK36">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="O37">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="P37">
-        <v>5.24</v>
+        <v>5.25</v>
       </c>
       <c r="Q37">
         <v>2.1</v>
@@ -6355,16 +6355,16 @@
         <v>2.29</v>
       </c>
       <c r="S37">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T37">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U37">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="V37">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W37">
         <v>1.12</v>
@@ -6376,16 +6376,16 @@
         <v>1.2</v>
       </c>
       <c r="Z37">
-        <v>4.48</v>
+        <v>4.52</v>
       </c>
       <c r="AA37">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AB37">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AC37">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="AD37">
         <v>1.42</v>
@@ -6394,10 +6394,10 @@
         <v>1.13</v>
       </c>
       <c r="AF37">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG37">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,80 +6503,80 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="O38">
-        <v>3.42</v>
+        <v>3.7</v>
       </c>
       <c r="P38">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="Q38">
-        <v>2.77</v>
+        <v>2.15</v>
       </c>
       <c r="R38">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S38">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T38">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U38">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V38">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W38">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X38">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z38">
         <v>4.33</v>
       </c>
       <c r="AA38">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AB38">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="AC38">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AD38">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AE38">
+        <v>1.13</v>
+      </c>
+      <c r="AF38">
+        <v>1.57</v>
+      </c>
+      <c r="AG38">
+        <v>2.18</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38">
         <v>1.18</v>
       </c>
-      <c r="AF38">
-        <v>1.5</v>
-      </c>
-      <c r="AG38">
-        <v>2.35</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ38">
-        <v>1.35</v>
-      </c>
       <c r="AK38">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,80 +6666,80 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="O39">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P39">
-        <v>4.25</v>
+        <v>3</v>
       </c>
       <c r="Q39">
+        <v>2.74</v>
+      </c>
+      <c r="R39">
+        <v>2.35</v>
+      </c>
+      <c r="S39">
+        <v>1.25</v>
+      </c>
+      <c r="T39">
+        <v>3.6</v>
+      </c>
+      <c r="U39">
         <v>2.15</v>
       </c>
-      <c r="R39">
-        <v>2.38</v>
-      </c>
-      <c r="S39">
-        <v>1.31</v>
-      </c>
-      <c r="T39">
-        <v>3.15</v>
-      </c>
-      <c r="U39">
-        <v>2.38</v>
-      </c>
       <c r="V39">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W39">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y39">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z39">
         <v>4.33</v>
       </c>
       <c r="AA39">
+        <v>1.57</v>
+      </c>
+      <c r="AB39">
+        <v>2.38</v>
+      </c>
+      <c r="AC39">
+        <v>2.55</v>
+      </c>
+      <c r="AD39">
+        <v>1.52</v>
+      </c>
+      <c r="AE39">
+        <v>1.16</v>
+      </c>
+      <c r="AF39">
+        <v>1.51</v>
+      </c>
+      <c r="AG39">
+        <v>2.55</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39">
+        <v>1.35</v>
+      </c>
+      <c r="AK39">
         <v>1.61</v>
-      </c>
-      <c r="AB39">
-        <v>2.08</v>
-      </c>
-      <c r="AC39">
-        <v>2.6</v>
-      </c>
-      <c r="AD39">
-        <v>1.44</v>
-      </c>
-      <c r="AE39">
-        <v>1.13</v>
-      </c>
-      <c r="AF39">
-        <v>1.57</v>
-      </c>
-      <c r="AG39">
-        <v>2.18</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39">
-        <v>1.18</v>
-      </c>
-      <c r="AK39">
-        <v>2</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>3.03</v>
+        <v>2.83</v>
       </c>
       <c r="O41">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="P41">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="Q41">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="R41">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="S41">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T41">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="U41">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="V41">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W41">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X41">
         <v>1.06</v>
       </c>
       <c r="Y41">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="Z41">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="AA41">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AB41">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AC41">
-        <v>3.88</v>
+        <v>3.68</v>
       </c>
       <c r="AD41">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE41">
         <v>1.06</v>
       </c>
       <c r="AF41">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AG41">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK41">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,80 +7155,80 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.8</v>
+        <v>3.03</v>
       </c>
       <c r="O42">
-        <v>3.21</v>
+        <v>3.15</v>
       </c>
       <c r="P42">
-        <v>3.21</v>
+        <v>1.98</v>
       </c>
       <c r="Q42">
-        <v>2.15</v>
+        <v>4.2</v>
       </c>
       <c r="R42">
-        <v>2.3</v>
+        <v>1.94</v>
       </c>
       <c r="S42">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="T42">
-        <v>3.2</v>
+        <v>2.56</v>
       </c>
       <c r="U42">
-        <v>2.53</v>
+        <v>3</v>
       </c>
       <c r="V42">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="W42">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X42">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y42">
+        <v>1.45</v>
+      </c>
+      <c r="Z42">
+        <v>2.6</v>
+      </c>
+      <c r="AA42">
+        <v>2.38</v>
+      </c>
+      <c r="AB42">
+        <v>1.6</v>
+      </c>
+      <c r="AC42">
+        <v>3.88</v>
+      </c>
+      <c r="AD42">
+        <v>1.17</v>
+      </c>
+      <c r="AE42">
+        <v>1.06</v>
+      </c>
+      <c r="AF42">
+        <v>1.92</v>
+      </c>
+      <c r="AG42">
+        <v>1.83</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ42">
+        <v>1.33</v>
+      </c>
+      <c r="AK42">
         <v>1.22</v>
-      </c>
-      <c r="Z42">
-        <v>4.1</v>
-      </c>
-      <c r="AA42">
-        <v>1.73</v>
-      </c>
-      <c r="AB42">
-        <v>2.07</v>
-      </c>
-      <c r="AC42">
-        <v>3.1</v>
-      </c>
-      <c r="AD42">
-        <v>1.37</v>
-      </c>
-      <c r="AE42">
-        <v>1.13</v>
-      </c>
-      <c r="AF42">
-        <v>1.73</v>
-      </c>
-      <c r="AG42">
-        <v>2.01</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ42">
-        <v>1.2</v>
-      </c>
-      <c r="AK42">
-        <v>1.81</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,80 +7318,80 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.83</v>
+        <v>1.8</v>
       </c>
       <c r="O43">
-        <v>3.05</v>
+        <v>3.21</v>
       </c>
       <c r="P43">
-        <v>2.03</v>
+        <v>3.21</v>
       </c>
       <c r="Q43">
-        <v>4.25</v>
+        <v>2.15</v>
       </c>
       <c r="R43">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="S43">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T43">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="U43">
-        <v>2.9</v>
+        <v>2.53</v>
       </c>
       <c r="V43">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="W43">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X43">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="Z43">
-        <v>2.88</v>
+        <v>4.1</v>
       </c>
       <c r="AA43">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AB43">
-        <v>1.64</v>
+        <v>2.07</v>
       </c>
       <c r="AC43">
-        <v>3.68</v>
+        <v>3.1</v>
       </c>
       <c r="AD43">
+        <v>1.37</v>
+      </c>
+      <c r="AE43">
+        <v>1.13</v>
+      </c>
+      <c r="AF43">
+        <v>1.73</v>
+      </c>
+      <c r="AG43">
+        <v>2.01</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ43">
         <v>1.2</v>
       </c>
-      <c r="AE43">
-        <v>1.06</v>
-      </c>
-      <c r="AF43">
-        <v>1.83</v>
-      </c>
-      <c r="AG43">
+      <c r="AK43">
         <v>1.81</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ43">
-        <v>1.28</v>
-      </c>
-      <c r="AK43">
-        <v>1.25</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.79</v>
+        <v>3</v>
       </c>
       <c r="O47">
         <v>3.6</v>
       </c>
       <c r="P47">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q47">
         <v>3.34</v>
@@ -7991,37 +7991,37 @@
         <v>4.15</v>
       </c>
       <c r="U47">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="V47">
         <v>1.77</v>
       </c>
       <c r="W47">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="X47">
         <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Z47">
         <v>6</v>
       </c>
       <c r="AA47">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AB47">
         <v>3</v>
       </c>
       <c r="AC47">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AD47">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AE47">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AF47">
         <v>1.36</v>
@@ -8043,7 +8043,7 @@
         <v>1.17</v>
       </c>
       <c r="AK47">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="O48">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="P48">
         <v>4.33</v>
       </c>
       <c r="Q48">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R48">
         <v>2.45</v>
       </c>
       <c r="S48">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T48">
         <v>3.6</v>
       </c>
       <c r="U48">
-        <v>2.29</v>
+        <v>1.91</v>
       </c>
       <c r="V48">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="W48">
         <v>1.11</v>
       </c>
       <c r="X48">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y48">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Z48">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AA48">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AB48">
-        <v>2.47</v>
+        <v>2.33</v>
       </c>
       <c r="AC48">
-        <v>1.96</v>
+        <v>2.35</v>
       </c>
       <c r="AD48">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="AE48">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF48">
         <v>1.57</v>
       </c>
       <c r="AG48">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AK48">
         <v>2</v>
@@ -8296,19 +8296,19 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.65</v>
+        <v>2.22</v>
       </c>
       <c r="O49">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P49">
-        <v>2.39</v>
+        <v>2.61</v>
       </c>
       <c r="Q49">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="R49">
-        <v>2.14</v>
+        <v>2.33</v>
       </c>
       <c r="S49">
         <v>1.3</v>
@@ -8317,22 +8317,22 @@
         <v>3.2</v>
       </c>
       <c r="U49">
-        <v>2.45</v>
+        <v>2.11</v>
       </c>
       <c r="V49">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="W49">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X49">
         <v>1</v>
       </c>
       <c r="Y49">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z49">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="AA49">
         <v>1.75</v>
@@ -8341,7 +8341,7 @@
         <v>1.95</v>
       </c>
       <c r="AC49">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="AD49">
         <v>1.35</v>
@@ -8350,10 +8350,10 @@
         <v>1.1</v>
       </c>
       <c r="AF49">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AG49">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         <v>1.22</v>
       </c>
       <c r="AK49">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,19 +8459,19 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="O50">
         <v>4.5</v>
       </c>
       <c r="P50">
-        <v>5.19</v>
+        <v>5</v>
       </c>
       <c r="Q50">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="R50">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="S50">
         <v>1.22</v>
@@ -8480,28 +8480,28 @@
         <v>3.75</v>
       </c>
       <c r="U50">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="V50">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W50">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X50">
         <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z50">
         <v>5.1</v>
       </c>
       <c r="AA50">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AB50">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="AC50">
         <v>2.15</v>
@@ -8510,13 +8510,13 @@
         <v>1.62</v>
       </c>
       <c r="AE50">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AF50">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AG50">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AK50">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,58 +8622,58 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="O51">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P51">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="Q51">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="R51">
         <v>2.4</v>
       </c>
       <c r="S51">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="T51">
-        <v>3.32</v>
+        <v>3.5</v>
       </c>
       <c r="U51">
-        <v>2.25</v>
+        <v>1.96</v>
       </c>
       <c r="V51">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="W51">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="X51">
         <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z51">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="AA51">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AB51">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AC51">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AD51">
         <v>1.48</v>
       </c>
       <c r="AE51">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AF51">
         <v>1.43</v>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK51">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="O54">
-        <v>3.28</v>
+        <v>3.03</v>
       </c>
       <c r="P54">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9150,10 +9150,10 @@
         <v>0</v>
       </c>
       <c r="AA54">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AB54">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AC54">
         <v>0</v>
@@ -9274,22 +9274,22 @@
         </is>
       </c>
       <c r="N55">
-        <v>3.14</v>
+        <v>2.92</v>
       </c>
       <c r="O55">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="P55">
         <v>2.4</v>
       </c>
       <c r="Q55">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="R55">
         <v>1.95</v>
       </c>
       <c r="S55">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="T55">
         <v>2.45</v>
@@ -9316,13 +9316,13 @@
         <v>2.43</v>
       </c>
       <c r="AB55">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AC55">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="AD55">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE55">
         <v>1.01</v>
@@ -9331,7 +9331,7 @@
         <v>1.95</v>
       </c>
       <c r="AG55">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AK55">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9437,19 +9437,19 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="O56">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="P56">
-        <v>2.16</v>
+        <v>2.45</v>
       </c>
       <c r="Q56">
         <v>3.49</v>
       </c>
       <c r="R56">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="S56">
         <v>1.36</v>
@@ -9476,13 +9476,13 @@
         <v>3.5</v>
       </c>
       <c r="AA56">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AB56">
         <v>1.9</v>
       </c>
       <c r="AC56">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="AD56">
         <v>1.29</v>
@@ -9600,19 +9600,19 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="O57">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P57">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="Q57">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="R57">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="S57">
         <v>1.38</v>
@@ -9621,22 +9621,22 @@
         <v>2.77</v>
       </c>
       <c r="U57">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="V57">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W57">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X57">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y57">
         <v>1.3</v>
       </c>
       <c r="Z57">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="AA57">
         <v>1.9</v>
@@ -9651,7 +9651,7 @@
         <v>1.28</v>
       </c>
       <c r="AE57">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF57">
         <v>1.77</v>
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>4.4</v>
+        <v>5.25</v>
       </c>
       <c r="O63">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P63">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="Q63">
-        <v>4.5</v>
+        <v>5.75</v>
       </c>
       <c r="R63">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="S63">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="T63">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="U63">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="V63">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="W63">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X63">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y63">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z63">
-        <v>3.08</v>
+        <v>3.55</v>
       </c>
       <c r="AA63">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AB63">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AC63">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="AD63">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE63">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF63">
-        <v>2.18</v>
+        <v>1.92</v>
       </c>
       <c r="AG63">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
         <v>1.25</v>
       </c>
       <c r="AK63">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10750,25 +10750,25 @@
         <v>4.2</v>
       </c>
       <c r="Q64">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="R64">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="S64">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T64">
         <v>4</v>
       </c>
       <c r="U64">
-        <v>2.12</v>
+        <v>1.92</v>
       </c>
       <c r="V64">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="W64">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X64">
         <v>1.02</v>
@@ -10777,7 +10777,7 @@
         <v>1.08</v>
       </c>
       <c r="Z64">
-        <v>5.65</v>
+        <v>5.55</v>
       </c>
       <c r="AA64">
         <v>1.39</v>
@@ -10789,16 +10789,16 @@
         <v>2.06</v>
       </c>
       <c r="AD64">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AE64">
         <v>1.24</v>
       </c>
       <c r="AF64">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AG64">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>1.22</v>
       </c>
       <c r="AK64">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10907,13 +10907,13 @@
         <v>2.15</v>
       </c>
       <c r="O65">
+        <v>3.25</v>
+      </c>
+      <c r="P65">
         <v>3.2</v>
       </c>
-      <c r="P65">
-        <v>3.1</v>
-      </c>
       <c r="Q65">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="R65">
         <v>1.96</v>
@@ -10922,46 +10922,46 @@
         <v>1.36</v>
       </c>
       <c r="T65">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="U65">
         <v>2.88</v>
       </c>
       <c r="V65">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W65">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X65">
         <v>1.06</v>
       </c>
       <c r="Y65">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="Z65">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="AA65">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="AB65">
         <v>1.7</v>
       </c>
       <c r="AC65">
-        <v>3.73</v>
+        <v>3.25</v>
       </c>
       <c r="AD65">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AE65">
         <v>1.08</v>
       </c>
       <c r="AF65">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AG65">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>1.33</v>
       </c>
       <c r="AK65">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="O66">
         <v>3.4</v>
       </c>
       <c r="P66">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="Q66">
         <v>2.5</v>
@@ -11082,19 +11082,19 @@
         <v>2.3</v>
       </c>
       <c r="S66">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T66">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U66">
         <v>2.38</v>
       </c>
       <c r="V66">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="W66">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X66">
         <v>1.02</v>
@@ -11103,22 +11103,22 @@
         <v>1.2</v>
       </c>
       <c r="Z66">
-        <v>4.49</v>
+        <v>4.4</v>
       </c>
       <c r="AA66">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AB66">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC66">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AD66">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AE66">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF66">
         <v>1.53</v>
@@ -11137,7 +11137,7 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK66">
         <v>1.67</v>
@@ -11230,16 +11230,16 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="O67">
         <v>3.7</v>
       </c>
       <c r="P67">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q67">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="R67">
         <v>2.35</v>
@@ -11251,43 +11251,43 @@
         <v>3.5</v>
       </c>
       <c r="U67">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="V67">
         <v>1.57</v>
       </c>
       <c r="W67">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X67">
         <v>1.03</v>
       </c>
       <c r="Y67">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z67">
-        <v>4.89</v>
+        <v>4.81</v>
       </c>
       <c r="AA67">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AB67">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AC67">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AD67">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AE67">
         <v>1.18</v>
       </c>
       <c r="AF67">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AG67">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11722,28 +11722,28 @@
         <v>1.25</v>
       </c>
       <c r="O70">
-        <v>5.25</v>
+        <v>6.3</v>
       </c>
       <c r="P70">
-        <v>8.75</v>
+        <v>9.5</v>
       </c>
       <c r="Q70">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="R70">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="S70">
         <v>1.22</v>
       </c>
       <c r="T70">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="U70">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="V70">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="W70">
         <v>1.14</v>
@@ -11755,19 +11755,19 @@
         <v>1.1</v>
       </c>
       <c r="Z70">
-        <v>5.11</v>
+        <v>5.19</v>
       </c>
       <c r="AA70">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AB70">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="AC70">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AD70">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AE70">
         <v>1.2</v>
@@ -11776,7 +11776,7 @@
         <v>1.73</v>
       </c>
       <c r="AG70">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AK70">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11882,7 +11882,7 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="O71">
         <v>3.5</v>
@@ -11903,13 +11903,13 @@
         <v>3.2</v>
       </c>
       <c r="U71">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="V71">
         <v>1.43</v>
       </c>
       <c r="W71">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X71">
         <v>1.04</v>
@@ -11918,7 +11918,7 @@
         <v>1.25</v>
       </c>
       <c r="Z71">
-        <v>4.1</v>
+        <v>3.58</v>
       </c>
       <c r="AA71">
         <v>1.74</v>
@@ -12045,16 +12045,16 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="O72">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="P72">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="Q72">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="R72">
         <v>2.3</v>
@@ -12066,10 +12066,10 @@
         <v>3.1</v>
       </c>
       <c r="U72">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="V72">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W72">
         <v>1.1</v>
@@ -12081,28 +12081,28 @@
         <v>1.25</v>
       </c>
       <c r="Z72">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="AA72">
         <v>1.85</v>
       </c>
       <c r="AB72">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC72">
-        <v>3.11</v>
+        <v>2.9</v>
       </c>
       <c r="AD72">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE72">
         <v>1.13</v>
       </c>
       <c r="AF72">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AG72">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK72">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12211,10 +12211,10 @@
         <v>5.25</v>
       </c>
       <c r="O73">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="P73">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q73">
         <v>5.52</v>
@@ -12226,10 +12226,10 @@
         <v>1.25</v>
       </c>
       <c r="T73">
-        <v>2.7</v>
+        <v>3.55</v>
       </c>
       <c r="U73">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="V73">
         <v>1.57</v>
@@ -12253,10 +12253,10 @@
         <v>2.21</v>
       </c>
       <c r="AC73">
-        <v>2.06</v>
+        <v>2.55</v>
       </c>
       <c r="AD73">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AE73">
         <v>1.15</v>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>2.29</v>
+        <v>1.17</v>
       </c>
       <c r="AK73">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12371,10 +12371,10 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="O74">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P74">
         <v>3.4</v>
@@ -12416,7 +12416,7 @@
         <v>1.69</v>
       </c>
       <c r="AC74">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AD74">
         <v>1.31</v>
@@ -12444,7 +12444,7 @@
         <v>1.29</v>
       </c>
       <c r="AK74">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12537,37 +12537,37 @@
         <v>3.4</v>
       </c>
       <c r="O75">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P75">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="Q75">
         <v>4.68</v>
       </c>
       <c r="R75">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S75">
         <v>1.38</v>
       </c>
       <c r="T75">
+        <v>2.88</v>
+      </c>
+      <c r="U75">
         <v>2.8</v>
       </c>
-      <c r="U75">
-        <v>2.73</v>
-      </c>
       <c r="V75">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W75">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X75">
         <v>1.03</v>
       </c>
       <c r="Y75">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z75">
         <v>3.3</v>
@@ -12585,13 +12585,13 @@
         <v>1.25</v>
       </c>
       <c r="AE75">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF75">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG75">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12697,31 +12697,31 @@
         </is>
       </c>
       <c r="N76">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="O76">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="P76">
         <v>3.2</v>
       </c>
       <c r="Q76">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="R76">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="S76">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="T76">
         <v>2.75</v>
       </c>
       <c r="U76">
-        <v>3.02</v>
+        <v>2.96</v>
       </c>
       <c r="V76">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W76">
         <v>1.05</v>
@@ -12733,13 +12733,13 @@
         <v>1.36</v>
       </c>
       <c r="Z76">
-        <v>2.88</v>
+        <v>3.16</v>
       </c>
       <c r="AA76">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="AB76">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AC76">
         <v>3.58</v>
@@ -12748,13 +12748,13 @@
         <v>1.21</v>
       </c>
       <c r="AE76">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF76">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AG76">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12863,7 +12863,7 @@
         <v>2.87</v>
       </c>
       <c r="O77">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P77">
         <v>2.2</v>
@@ -12875,7 +12875,7 @@
         <v>2.05</v>
       </c>
       <c r="S77">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="T77">
         <v>2.88</v>
@@ -12884,7 +12884,7 @@
         <v>2.77</v>
       </c>
       <c r="V77">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W77">
         <v>1.07</v>
@@ -12905,19 +12905,19 @@
         <v>1.76</v>
       </c>
       <c r="AC77">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="AD77">
         <v>1.27</v>
       </c>
       <c r="AE77">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF77">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AG77">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -13023,7 +13023,7 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="O78">
         <v>3.8</v>
@@ -13032,22 +13032,22 @@
         <v>5.55</v>
       </c>
       <c r="Q78">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="R78">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="S78">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T78">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="U78">
-        <v>3.29</v>
+        <v>3.16</v>
       </c>
       <c r="V78">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W78">
         <v>1.01</v>
@@ -13056,31 +13056,31 @@
         <v>1.01</v>
       </c>
       <c r="Y78">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z78">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="AA78">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="AB78">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AC78">
-        <v>4.03</v>
+        <v>3.99</v>
       </c>
       <c r="AD78">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE78">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF78">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="AG78">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AK78">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13192,58 +13192,58 @@
         <v>3.1</v>
       </c>
       <c r="P79">
-        <v>2.64</v>
+        <v>2.81</v>
       </c>
       <c r="Q79">
+        <v>3.04</v>
+      </c>
+      <c r="R79">
+        <v>1.94</v>
+      </c>
+      <c r="S79">
+        <v>1.47</v>
+      </c>
+      <c r="T79">
+        <v>2.44</v>
+      </c>
+      <c r="U79">
         <v>3.1</v>
       </c>
-      <c r="R79">
-        <v>2.08</v>
-      </c>
-      <c r="S79">
-        <v>1.46</v>
-      </c>
-      <c r="T79">
-        <v>2.5</v>
-      </c>
-      <c r="U79">
-        <v>3.26</v>
-      </c>
       <c r="V79">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W79">
+        <v>1.02</v>
+      </c>
+      <c r="X79">
+        <v>1.04</v>
+      </c>
+      <c r="Y79">
+        <v>1.35</v>
+      </c>
+      <c r="Z79">
+        <v>2.74</v>
+      </c>
+      <c r="AA79">
+        <v>2.24</v>
+      </c>
+      <c r="AB79">
+        <v>1.64</v>
+      </c>
+      <c r="AC79">
+        <v>3.8</v>
+      </c>
+      <c r="AD79">
+        <v>1.19</v>
+      </c>
+      <c r="AE79">
         <v>1.03</v>
       </c>
-      <c r="X79">
-        <v>1.03</v>
-      </c>
-      <c r="Y79">
-        <v>1.33</v>
-      </c>
-      <c r="Z79">
-        <v>2.83</v>
-      </c>
-      <c r="AA79">
-        <v>2.19</v>
-      </c>
-      <c r="AB79">
-        <v>1.67</v>
-      </c>
-      <c r="AC79">
-        <v>3.58</v>
-      </c>
-      <c r="AD79">
-        <v>1.21</v>
-      </c>
-      <c r="AE79">
-        <v>1.04</v>
-      </c>
       <c r="AF79">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AG79">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13259,7 +13259,7 @@
         <v>1.36</v>
       </c>
       <c r="AK79">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13349,7 +13349,7 @@
         </is>
       </c>
       <c r="N80">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="O80">
         <v>3.75</v>
@@ -13358,22 +13358,22 @@
         <v>5.66</v>
       </c>
       <c r="Q80">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="R80">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="S80">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T80">
-        <v>2.66</v>
+        <v>2.89</v>
       </c>
       <c r="U80">
-        <v>3.06</v>
+        <v>2.9</v>
       </c>
       <c r="V80">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W80">
         <v>1.03</v>
@@ -13382,31 +13382,31 @@
         <v>1.01</v>
       </c>
       <c r="Y80">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z80">
-        <v>3.04</v>
+        <v>3.24</v>
       </c>
       <c r="AA80">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AB80">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AC80">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AD80">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AE80">
         <v>1.05</v>
       </c>
       <c r="AF80">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AG80">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,7 +13419,7 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK80">
         <v>2.22</v>
@@ -13844,7 +13844,7 @@
         <v>3.4</v>
       </c>
       <c r="P83">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q83">
         <v>3.1</v>
@@ -13853,13 +13853,13 @@
         <v>2.09</v>
       </c>
       <c r="S83">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T83">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="U83">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="V83">
         <v>1.43</v>
@@ -13868,25 +13868,25 @@
         <v>1.06</v>
       </c>
       <c r="X83">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y83">
         <v>1.25</v>
       </c>
       <c r="Z83">
-        <v>3.95</v>
+        <v>3.54</v>
       </c>
       <c r="AA83">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AB83">
         <v>1.97</v>
       </c>
       <c r="AC83">
-        <v>3.1</v>
+        <v>2.89</v>
       </c>
       <c r="AD83">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE83">
         <v>1.09</v>
@@ -13895,7 +13895,7 @@
         <v>1.65</v>
       </c>
       <c r="AG83">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AK83">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14001,16 +14001,16 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="O84">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P84">
         <v>2.9</v>
       </c>
       <c r="Q84">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="R84">
         <v>2.15</v>
@@ -14019,7 +14019,7 @@
         <v>1.36</v>
       </c>
       <c r="T84">
-        <v>2.89</v>
+        <v>2.76</v>
       </c>
       <c r="U84">
         <v>2.65</v>
@@ -14043,13 +14043,13 @@
         <v>1.85</v>
       </c>
       <c r="AB84">
-        <v>2.03</v>
+        <v>1.88</v>
       </c>
       <c r="AC84">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AD84">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE84">
         <v>1.09</v>
@@ -14058,7 +14058,7 @@
         <v>1.65</v>
       </c>
       <c r="AG84">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="O85">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P85">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q85">
         <v>2.64</v>
@@ -14179,37 +14179,37 @@
         <v>2.14</v>
       </c>
       <c r="S85">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="T85">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="U85">
-        <v>3.02</v>
+        <v>2.84</v>
       </c>
       <c r="V85">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="W85">
         <v>1.02</v>
       </c>
       <c r="X85">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y85">
         <v>1.31</v>
       </c>
       <c r="Z85">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AA85">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="AB85">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AC85">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="AD85">
         <v>1.21</v>
@@ -14218,7 +14218,7 @@
         <v>1.03</v>
       </c>
       <c r="AF85">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AG85">
         <v>1.95</v>
@@ -14490,34 +14490,34 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="O87">
-        <v>5.23</v>
+        <v>5</v>
       </c>
       <c r="P87">
-        <v>9.800000000000001</v>
+        <v>6.5</v>
       </c>
       <c r="Q87">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="R87">
         <v>2.5</v>
       </c>
       <c r="S87">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T87">
-        <v>3.45</v>
+        <v>3.08</v>
       </c>
       <c r="U87">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="V87">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="W87">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X87">
         <v>1.01</v>
@@ -14526,28 +14526,28 @@
         <v>1.22</v>
       </c>
       <c r="Z87">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="AA87">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="AB87">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AC87">
-        <v>2.35</v>
+        <v>2.56</v>
       </c>
       <c r="AD87">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="AE87">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AF87">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AG87">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AK87">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O89">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P89">
-        <v>2.84</v>
+        <v>2.6</v>
       </c>
       <c r="Q89">
         <v>3</v>
@@ -14831,49 +14831,49 @@
         <v>2.25</v>
       </c>
       <c r="S89">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="T89">
-        <v>2.39</v>
+        <v>3.2</v>
       </c>
       <c r="U89">
         <v>2.45</v>
       </c>
       <c r="V89">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W89">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X89">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y89">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z89">
-        <v>3.88</v>
+        <v>2.9</v>
       </c>
       <c r="AA89">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AB89">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC89">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="AD89">
         <v>1.36</v>
       </c>
       <c r="AE89">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF89">
         <v>1.56</v>
       </c>
       <c r="AG89">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>1.44</v>
       </c>
       <c r="AK89">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14982,28 +14982,28 @@
         <v>2.32</v>
       </c>
       <c r="O90">
-        <v>3.26</v>
+        <v>3.22</v>
       </c>
       <c r="P90">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="Q90">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="R90">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S90">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T90">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="U90">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="V90">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W90">
         <v>1.04</v>
@@ -15015,10 +15015,10 @@
         <v>1.26</v>
       </c>
       <c r="Z90">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="AA90">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AB90">
         <v>1.75</v>
@@ -15145,10 +15145,10 @@
         <v>1.37</v>
       </c>
       <c r="O91">
-        <v>4.72</v>
+        <v>4.78</v>
       </c>
       <c r="P91">
-        <v>5.9</v>
+        <v>5.75</v>
       </c>
       <c r="Q91">
         <v>1.83</v>
@@ -15157,16 +15157,16 @@
         <v>2.7</v>
       </c>
       <c r="S91">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T91">
-        <v>3.85</v>
+        <v>3.94</v>
       </c>
       <c r="U91">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="V91">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W91">
         <v>1.18</v>
@@ -15175,7 +15175,7 @@
         <v>1.02</v>
       </c>
       <c r="Y91">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="Z91">
         <v>5.75</v>
@@ -15184,10 +15184,10 @@
         <v>1.4</v>
       </c>
       <c r="AB91">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="AC91">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="AD91">
         <v>1.7</v>
@@ -15196,10 +15196,10 @@
         <v>1.26</v>
       </c>
       <c r="AF91">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AG91">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK91">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="O92">
         <v>3.6</v>
       </c>
       <c r="P92">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="Q92">
         <v>3.39</v>
@@ -15347,7 +15347,7 @@
         <v>1.4</v>
       </c>
       <c r="AB92">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="AC92">
         <v>2</v>
@@ -15356,7 +15356,7 @@
         <v>1.77</v>
       </c>
       <c r="AE92">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF92">
         <v>1.36</v>
@@ -15794,25 +15794,25 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="O95">
         <v>3.2</v>
       </c>
       <c r="P95">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="Q95">
-        <v>3.13</v>
+        <v>3.04</v>
       </c>
       <c r="R95">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="S95">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T95">
-        <v>2.78</v>
+        <v>2.54</v>
       </c>
       <c r="U95">
         <v>3.05</v>
@@ -15827,10 +15827,10 @@
         <v>1.02</v>
       </c>
       <c r="Y95">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z95">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AA95">
         <v>2.11</v>
@@ -15848,10 +15848,10 @@
         <v>1.03</v>
       </c>
       <c r="AF95">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AG95">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15867,7 +15867,7 @@
         <v>1.32</v>
       </c>
       <c r="AK95">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -16120,10 +16120,10 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="O97">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P97">
         <v>2.6</v>
@@ -16156,7 +16156,7 @@
         <v>1.32</v>
       </c>
       <c r="Z97">
-        <v>3.1</v>
+        <v>3.33</v>
       </c>
       <c r="AA97">
         <v>1.94</v>
@@ -16174,7 +16174,7 @@
         <v>1.06</v>
       </c>
       <c r="AF97">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG97">
         <v>2.02</v>
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>4.23</v>
+        <v>4</v>
       </c>
       <c r="O98">
-        <v>3.68</v>
+        <v>3.4</v>
       </c>
       <c r="P98">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="Q98">
         <v>4.5</v>
@@ -16304,7 +16304,7 @@
         <v>2.95</v>
       </c>
       <c r="U98">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="V98">
         <v>1.42</v>
@@ -16322,16 +16322,16 @@
         <v>3.46</v>
       </c>
       <c r="AA98">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AB98">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AC98">
         <v>2.92</v>
       </c>
       <c r="AD98">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE98">
         <v>1.1</v>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK98">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16624,22 +16624,22 @@
         <v>2.15</v>
       </c>
       <c r="S100">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T100">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="U100">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="V100">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W100">
         <v>1.08</v>
       </c>
       <c r="X100">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y100">
         <v>1.28</v>
@@ -16651,22 +16651,22 @@
         <v>1.8</v>
       </c>
       <c r="AB100">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AC100">
         <v>3</v>
       </c>
       <c r="AD100">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE100">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF100">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AG100">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16778,19 +16778,19 @@
         <v>3.4</v>
       </c>
       <c r="P101">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="Q101">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="R101">
         <v>2.1</v>
       </c>
       <c r="S101">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T101">
-        <v>3.02</v>
+        <v>2.88</v>
       </c>
       <c r="U101">
         <v>2.88</v>
@@ -16802,7 +16802,7 @@
         <v>1.04</v>
       </c>
       <c r="X101">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y101">
         <v>1.3</v>
@@ -16817,7 +16817,7 @@
         <v>1.79</v>
       </c>
       <c r="AC101">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="AD101">
         <v>1.26</v>
@@ -16826,10 +16826,10 @@
         <v>1.09</v>
       </c>
       <c r="AF101">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG101">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,7 +16842,7 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK101">
         <v>1.73</v>
@@ -16935,19 +16935,19 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="O102">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="P102">
-        <v>6.35</v>
+        <v>6.1</v>
       </c>
       <c r="Q102">
         <v>1.89</v>
       </c>
       <c r="R102">
-        <v>2.53</v>
+        <v>2.74</v>
       </c>
       <c r="S102">
         <v>1.25</v>
@@ -16956,7 +16956,7 @@
         <v>3.62</v>
       </c>
       <c r="U102">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="V102">
         <v>1.62</v>
@@ -16983,16 +16983,16 @@
         <v>2.36</v>
       </c>
       <c r="AD102">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AE102">
         <v>1.2</v>
       </c>
       <c r="AF102">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG102">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AK102">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.32</v>
+        <v>2.05</v>
       </c>
       <c r="O104">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P104">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="Q104">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="R104">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S104">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T104">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="U104">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="V104">
         <v>1.38</v>
       </c>
       <c r="W104">
+        <v>1.02</v>
+      </c>
+      <c r="X104">
+        <v>1.02</v>
+      </c>
+      <c r="Y104">
+        <v>1.28</v>
+      </c>
+      <c r="Z104">
+        <v>3.08</v>
+      </c>
+      <c r="AA104">
+        <v>2</v>
+      </c>
+      <c r="AB104">
+        <v>1.75</v>
+      </c>
+      <c r="AC104">
+        <v>3.4</v>
+      </c>
+      <c r="AD104">
+        <v>1.28</v>
+      </c>
+      <c r="AE104">
         <v>1.05</v>
       </c>
-      <c r="X104">
-        <v>1.06</v>
-      </c>
-      <c r="Y104">
-        <v>1.36</v>
-      </c>
-      <c r="Z104">
-        <v>3.1</v>
-      </c>
-      <c r="AA104">
-        <v>2.2</v>
-      </c>
-      <c r="AB104">
-        <v>1.6</v>
-      </c>
-      <c r="AC104">
-        <v>4.2</v>
-      </c>
-      <c r="AD104">
-        <v>1.22</v>
-      </c>
-      <c r="AE104">
-        <v>1.03</v>
-      </c>
       <c r="AF104">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="AG104">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK104">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17424,13 +17424,13 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="O105">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P105">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="Q105">
         <v>0</v>
@@ -17590,22 +17590,22 @@
         <v>2</v>
       </c>
       <c r="O106">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P106">
-        <v>3</v>
+        <v>3.16</v>
       </c>
       <c r="Q106">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="R106">
         <v>2.35</v>
       </c>
       <c r="S106">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T106">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="U106">
         <v>2.2</v>
@@ -17623,19 +17623,19 @@
         <v>1.15</v>
       </c>
       <c r="Z106">
-        <v>5.15</v>
+        <v>4.75</v>
       </c>
       <c r="AA106">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AB106">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="AC106">
         <v>2.25</v>
       </c>
       <c r="AD106">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AE106">
         <v>1.2</v>
@@ -17657,7 +17657,7 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AK106">
         <v>1.8</v>
@@ -17753,7 +17753,7 @@
         <v>4.45</v>
       </c>
       <c r="O107">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P107">
         <v>1.67</v>
@@ -17765,7 +17765,7 @@
         <v>2.16</v>
       </c>
       <c r="S107">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T107">
         <v>2.9</v>
@@ -17774,16 +17774,16 @@
         <v>2.73</v>
       </c>
       <c r="V107">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W107">
         <v>1.08</v>
       </c>
       <c r="X107">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y107">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="Z107">
         <v>3.42</v>
@@ -17798,13 +17798,13 @@
         <v>3.25</v>
       </c>
       <c r="AD107">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE107">
         <v>1.06</v>
       </c>
       <c r="AF107">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG107">
         <v>1.91</v>
@@ -17913,31 +17913,31 @@
         </is>
       </c>
       <c r="N108">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="O108">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P108">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="Q108">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="R108">
         <v>2.3</v>
       </c>
       <c r="S108">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T108">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="U108">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="V108">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="W108">
         <v>1.11</v>
@@ -17949,7 +17949,7 @@
         <v>1.13</v>
       </c>
       <c r="Z108">
-        <v>4.95</v>
+        <v>4.1</v>
       </c>
       <c r="AA108">
         <v>1.59</v>
@@ -17961,13 +17961,13 @@
         <v>2.45</v>
       </c>
       <c r="AD108">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AE108">
         <v>1.17</v>
       </c>
       <c r="AF108">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AG108">
         <v>2.5</v>
@@ -18079,22 +18079,22 @@
         <v>2.5</v>
       </c>
       <c r="O109">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P109">
         <v>2.5</v>
       </c>
       <c r="Q109">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="R109">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="S109">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T109">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="U109">
         <v>2.75</v>
@@ -18109,13 +18109,13 @@
         <v>1.05</v>
       </c>
       <c r="Y109">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z109">
-        <v>3.58</v>
+        <v>3.78</v>
       </c>
       <c r="AA109">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AB109">
         <v>2</v>
@@ -18124,13 +18124,13 @@
         <v>2.9</v>
       </c>
       <c r="AD109">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AE109">
         <v>1.13</v>
       </c>
       <c r="AF109">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AG109">
         <v>2.2</v>
@@ -18402,25 +18402,25 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="O111">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P111">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="Q111">
         <v>2</v>
       </c>
       <c r="R111">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="S111">
         <v>1.3</v>
       </c>
       <c r="T111">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U111">
         <v>2.5</v>
@@ -18429,7 +18429,7 @@
         <v>1.45</v>
       </c>
       <c r="W111">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X111">
         <v>1</v>
@@ -18438,16 +18438,16 @@
         <v>1.2</v>
       </c>
       <c r="Z111">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="AA111">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB111">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AC111">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="AD111">
         <v>1.48</v>
@@ -18456,7 +18456,7 @@
         <v>1.12</v>
       </c>
       <c r="AF111">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG111">
         <v>1.95</v>
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O112">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Q112">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="R112">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S112">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="T112">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U112">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V112">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W112">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X112">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y112">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z112">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA112">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB112">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC112">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AD112">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE112">
         <v>0</v>
       </c>
       <c r="AF112">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AG112">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AK112">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O113">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P113">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="O117">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="P117">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="Q117">
         <v>3.34</v>
@@ -19407,7 +19407,7 @@
         <v>1.77</v>
       </c>
       <c r="W117">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X117">
         <v>1.01</v>
@@ -19416,16 +19416,16 @@
         <v>1.08</v>
       </c>
       <c r="Z117">
-        <v>6.46</v>
+        <v>6.3</v>
       </c>
       <c r="AA117">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AB117">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="AC117">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="AD117">
         <v>1.8</v>
@@ -19450,7 +19450,7 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.75</v>
+        <v>1.18</v>
       </c>
       <c r="AK117">
         <v>1.3</v>
@@ -20032,13 +20032,13 @@
         </is>
       </c>
       <c r="N121">
-        <v>2.27</v>
+        <v>2.34</v>
       </c>
       <c r="O121">
+        <v>3.07</v>
+      </c>
+      <c r="P121">
         <v>3.25</v>
-      </c>
-      <c r="P121">
-        <v>3</v>
       </c>
       <c r="Q121">
         <v>0</v>
@@ -20195,25 +20195,25 @@
         </is>
       </c>
       <c r="N122">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="O122">
         <v>2.9</v>
       </c>
       <c r="P122">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="Q122">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="R122">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="S122">
         <v>1.5</v>
       </c>
       <c r="T122">
-        <v>2.31</v>
+        <v>2.54</v>
       </c>
       <c r="U122">
         <v>3.34</v>
@@ -20222,25 +20222,25 @@
         <v>1.25</v>
       </c>
       <c r="W122">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X122">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y122">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z122">
         <v>2.74</v>
       </c>
       <c r="AA122">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="AB122">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC122">
-        <v>4.46</v>
+        <v>4.2</v>
       </c>
       <c r="AD122">
         <v>1.15</v>
@@ -20252,7 +20252,7 @@
         <v>1.91</v>
       </c>
       <c r="AG122">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AK122">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20521,7 +20521,7 @@
         </is>
       </c>
       <c r="N124">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O124">
         <v>3.4</v>
@@ -20533,7 +20533,7 @@
         <v>3.6</v>
       </c>
       <c r="R124">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="S124">
         <v>1.3</v>
@@ -20545,7 +20545,7 @@
         <v>2.5</v>
       </c>
       <c r="V124">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W124">
         <v>1.1</v>
@@ -20554,16 +20554,16 @@
         <v>1</v>
       </c>
       <c r="Y124">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z124">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AA124">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB124">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AC124">
         <v>3.16</v>
@@ -20591,7 +20591,7 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK124">
         <v>1.27</v>
@@ -20693,55 +20693,55 @@
         <v>2.74</v>
       </c>
       <c r="Q125">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="R125">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="S125">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T125">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="U125">
-        <v>2.77</v>
+        <v>2.91</v>
       </c>
       <c r="V125">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W125">
         <v>1.04</v>
       </c>
       <c r="X125">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y125">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z125">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA125">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AB125">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AC125">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="AD125">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE125">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF125">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG125">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK125">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20847,19 +20847,19 @@
         </is>
       </c>
       <c r="N126">
-        <v>2.76</v>
+        <v>2.85</v>
       </c>
       <c r="O126">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P126">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="Q126">
-        <v>3.66</v>
+        <v>3.12</v>
       </c>
       <c r="R126">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S126">
         <v>1.41</v>
@@ -20868,13 +20868,13 @@
         <v>2.66</v>
       </c>
       <c r="U126">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="V126">
         <v>1.39</v>
       </c>
       <c r="W126">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X126">
         <v>1.02</v>
@@ -20883,19 +20883,19 @@
         <v>1.27</v>
       </c>
       <c r="Z126">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AA126">
         <v>1.95</v>
       </c>
       <c r="AB126">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AC126">
         <v>3.25</v>
       </c>
       <c r="AD126">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE126">
         <v>1.07</v>
@@ -21010,13 +21010,13 @@
         </is>
       </c>
       <c r="N127">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="O127">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P127">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q127">
         <v>0</v>
@@ -21342,25 +21342,25 @@
         <v>3.5</v>
       </c>
       <c r="P129">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="Q129">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="R129">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="S129">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T129">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="U129">
         <v>3.04</v>
       </c>
       <c r="V129">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W129">
         <v>1.05</v>
@@ -21369,31 +21369,31 @@
         <v>1.06</v>
       </c>
       <c r="Y129">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="Z129">
         <v>2.78</v>
       </c>
       <c r="AA129">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AB129">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AC129">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="AD129">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AE129">
         <v>1.07</v>
       </c>
       <c r="AF129">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG129">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,7 +21406,7 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AK129">
         <v>2.11</v>
@@ -21662,43 +21662,43 @@
         </is>
       </c>
       <c r="N131">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="O131">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="P131">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="Q131">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R131">
         <v>2.36</v>
       </c>
       <c r="S131">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T131">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="U131">
         <v>2.3</v>
       </c>
       <c r="V131">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W131">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X131">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y131">
         <v>1.18</v>
       </c>
       <c r="Z131">
-        <v>4.9</v>
+        <v>4.75</v>
       </c>
       <c r="AA131">
         <v>1.57</v>
@@ -21710,7 +21710,7 @@
         <v>2.4</v>
       </c>
       <c r="AD131">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AE131">
         <v>1.22</v>
@@ -21719,7 +21719,7 @@
         <v>1.58</v>
       </c>
       <c r="AG131">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="O133">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="P133">
-        <v>4.6</v>
+        <v>5.13</v>
       </c>
       <c r="Q133">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="R133">
         <v>2.1</v>
       </c>
       <c r="S133">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T133">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="U133">
-        <v>3.19</v>
+        <v>2.87</v>
       </c>
       <c r="V133">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W133">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X133">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y133">
         <v>1.33</v>
       </c>
       <c r="Z133">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AA133">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB133">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AC133">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="AD133">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE133">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF133">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AG133">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22151,31 +22151,31 @@
         </is>
       </c>
       <c r="N134">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="O134">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P134">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="Q134">
         <v>2.75</v>
       </c>
       <c r="R134">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="S134">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T134">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="U134">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="V134">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W134">
         <v>1.1</v>
@@ -22190,16 +22190,16 @@
         <v>3.5</v>
       </c>
       <c r="AA134">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB134">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AC134">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AD134">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE134">
         <v>1.13</v>
@@ -22208,7 +22208,7 @@
         <v>1.62</v>
       </c>
       <c r="AG134">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22480,10 +22480,10 @@
         <v>1.95</v>
       </c>
       <c r="O136">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P136">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="Q136">
         <v>2.4</v>
@@ -22492,7 +22492,7 @@
         <v>2.15</v>
       </c>
       <c r="S136">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T136">
         <v>3</v>
@@ -22507,7 +22507,7 @@
         <v>1.05</v>
       </c>
       <c r="X136">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y136">
         <v>1.25</v>
@@ -22516,25 +22516,25 @@
         <v>3.45</v>
       </c>
       <c r="AA136">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AB136">
         <v>1.85</v>
       </c>
       <c r="AC136">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="AD136">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AE136">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF136">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG136">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22550,7 +22550,7 @@
         <v>1.25</v>
       </c>
       <c r="AK136">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22640,37 +22640,37 @@
         </is>
       </c>
       <c r="N137">
-        <v>4.25</v>
+        <v>4.65</v>
       </c>
       <c r="O137">
-        <v>3.73</v>
+        <v>3.8</v>
       </c>
       <c r="P137">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="Q137">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="R137">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="S137">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T137">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="U137">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="V137">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W137">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X137">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y137">
         <v>1.22</v>
@@ -22682,10 +22682,10 @@
         <v>1.72</v>
       </c>
       <c r="AB137">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AC137">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AD137">
         <v>1.4</v>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="AK137">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -23005,10 +23005,10 @@
         <v>3.42</v>
       </c>
       <c r="AA139">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="AB139">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="AC139">
         <v>3.16</v>
@@ -23023,7 +23023,7 @@
         <v>1.9</v>
       </c>
       <c r="AG139">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23039,7 +23039,7 @@
         <v>1.28</v>
       </c>
       <c r="AK139">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23144,16 +23144,16 @@
         <v>2.33</v>
       </c>
       <c r="S140">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T140">
         <v>2.91</v>
       </c>
       <c r="U140">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="V140">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W140">
         <v>1.08</v>
@@ -23174,10 +23174,10 @@
         <v>1.98</v>
       </c>
       <c r="AC140">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="AD140">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AE140">
         <v>1.11</v>
@@ -23186,7 +23186,7 @@
         <v>1.93</v>
       </c>
       <c r="AG140">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AK140">
-        <v>2.94</v>
+        <v>3.02</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -23292,34 +23292,34 @@
         </is>
       </c>
       <c r="N141">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="O141">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="P141">
         <v>14</v>
       </c>
       <c r="Q141">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="R141">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="S141">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="T141">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="U141">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="V141">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="W141">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="X141">
         <v>1.01</v>
@@ -23328,13 +23328,13 @@
         <v>1.02</v>
       </c>
       <c r="Z141">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="AA141">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AB141">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AC141">
         <v>1.62</v>
@@ -23343,10 +23343,10 @@
         <v>2.2</v>
       </c>
       <c r="AE141">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AF141">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AG141">
         <v>1.8</v>
@@ -23362,10 +23362,10 @@
         </is>
       </c>
       <c r="AJ141">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK141">
-        <v>6.3</v>
+        <v>5.2</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23944,16 +23944,16 @@
         </is>
       </c>
       <c r="N145">
-        <v>3.7</v>
+        <v>3.99</v>
       </c>
       <c r="O145">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P145">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q145">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="R145">
         <v>2.4</v>
@@ -23980,28 +23980,28 @@
         <v>1.14</v>
       </c>
       <c r="Z145">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="AA145">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AB145">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="AC145">
-        <v>2.37</v>
+        <v>2.24</v>
       </c>
       <c r="AD145">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AE145">
         <v>1.23</v>
       </c>
       <c r="AF145">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG145">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,7 +24014,7 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK145">
         <v>1.22</v>
@@ -24113,19 +24113,19 @@
         <v>2.95</v>
       </c>
       <c r="P146">
-        <v>3.15</v>
+        <v>3.07</v>
       </c>
       <c r="Q146">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="R146">
         <v>2</v>
       </c>
       <c r="S146">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T146">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="U146">
         <v>3.2</v>
@@ -24140,19 +24140,19 @@
         <v>1.05</v>
       </c>
       <c r="Y146">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="Z146">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="AA146">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AB146">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC146">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AD146">
         <v>1.17</v>
@@ -24161,10 +24161,10 @@
         <v>1.03</v>
       </c>
       <c r="AF146">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AG146">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24270,10 +24270,10 @@
         </is>
       </c>
       <c r="N147">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="O147">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="P147">
         <v>2.75</v>
@@ -24291,10 +24291,10 @@
         <v>2.47</v>
       </c>
       <c r="U147">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="V147">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W147">
         <v>1.02</v>
@@ -24303,31 +24303,31 @@
         <v>1.06</v>
       </c>
       <c r="Y147">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="Z147">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AA147">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AB147">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AC147">
         <v>4.8</v>
       </c>
       <c r="AD147">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE147">
         <v>1.02</v>
       </c>
       <c r="AF147">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AG147">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24343,7 +24343,7 @@
         <v>1.33</v>
       </c>
       <c r="AK147">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -24442,16 +24442,16 @@
         <v>1.7</v>
       </c>
       <c r="Q148">
-        <v>5.03</v>
+        <v>5.25</v>
       </c>
       <c r="R148">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="S148">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T148">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U148">
         <v>2.9</v>
@@ -24472,10 +24472,10 @@
         <v>2.9</v>
       </c>
       <c r="AA148">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AB148">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC148">
         <v>3.7</v>
@@ -24503,10 +24503,10 @@
         </is>
       </c>
       <c r="AJ148">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK148">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AL148">
         <v>0</v>
@@ -24596,7 +24596,7 @@
         </is>
       </c>
       <c r="N149">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="O149">
         <v>3.05</v>
@@ -24605,7 +24605,7 @@
         <v>2.35</v>
       </c>
       <c r="Q149">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R149">
         <v>2.08</v>
@@ -24623,37 +24623,37 @@
         <v>1.34</v>
       </c>
       <c r="W149">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X149">
         <v>1.05</v>
       </c>
       <c r="Y149">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z149">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AA149">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB149">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC149">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AD149">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE149">
         <v>1.05</v>
       </c>
       <c r="AF149">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AG149">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AH149" t="inlineStr">
         <is>
@@ -24765,7 +24765,7 @@
         <v>3</v>
       </c>
       <c r="P150">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q150">
         <v>3.78</v>
@@ -24774,37 +24774,37 @@
         <v>2.08</v>
       </c>
       <c r="S150">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="T150">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="U150">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="V150">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W150">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X150">
         <v>1.05</v>
       </c>
       <c r="Y150">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z150">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AA150">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AB150">
         <v>1.62</v>
       </c>
       <c r="AC150">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AD150">
         <v>1.2</v>
@@ -24813,10 +24813,10 @@
         <v>1.05</v>
       </c>
       <c r="AF150">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AG150">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH150" t="inlineStr">
         <is>
@@ -24922,13 +24922,13 @@
         </is>
       </c>
       <c r="N151">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="O151">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="P151">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q151">
         <v>1.44</v>
@@ -24937,37 +24937,37 @@
         <v>3.2</v>
       </c>
       <c r="S151">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="T151">
-        <v>5.55</v>
+        <v>5.65</v>
       </c>
       <c r="U151">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="V151">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="W151">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X151">
         <v>1.01</v>
       </c>
       <c r="Y151">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Z151">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AA151">
         <v>1.22</v>
       </c>
       <c r="AB151">
-        <v>3.98</v>
+        <v>4.1</v>
       </c>
       <c r="AC151">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AD151">
         <v>2.25</v>
@@ -24976,7 +24976,7 @@
         <v>1.6</v>
       </c>
       <c r="AF151">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG151">
         <v>2.3</v>
@@ -24995,7 +24995,7 @@
         <v>1.05</v>
       </c>
       <c r="AK151">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AL151">
         <v>0</v>
@@ -25085,64 +25085,64 @@
         </is>
       </c>
       <c r="N152">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O152">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P152">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q152">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R152">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S152">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="T152">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="U152">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V152">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W152">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X152">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y152">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z152">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AA152">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB152">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC152">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD152">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE152">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF152">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG152">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK152">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25248,22 +25248,22 @@
         </is>
       </c>
       <c r="N153">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="O153">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="P153">
-        <v>8.68</v>
+        <v>8.75</v>
       </c>
       <c r="Q153">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="R153">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="S153">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T153">
         <v>3.5</v>
@@ -25272,31 +25272,31 @@
         <v>2.24</v>
       </c>
       <c r="V153">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W153">
         <v>1.15</v>
       </c>
       <c r="X153">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y153">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z153">
-        <v>4.8</v>
+        <v>4.55</v>
       </c>
       <c r="AA153">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AB153">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AC153">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="AD153">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AE153">
         <v>1.2</v>
@@ -25305,7 +25305,7 @@
         <v>2</v>
       </c>
       <c r="AG153">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AK153">
         <v>3.6</v>
@@ -25414,16 +25414,16 @@
         <v>2.05</v>
       </c>
       <c r="O154">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P154">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q154">
         <v>2.6</v>
       </c>
       <c r="R154">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="S154">
         <v>1.25</v>
@@ -25432,40 +25432,40 @@
         <v>3.5</v>
       </c>
       <c r="U154">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="V154">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="W154">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X154">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y154">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z154">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AA154">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AB154">
         <v>2.21</v>
       </c>
       <c r="AC154">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AD154">
         <v>1.51</v>
       </c>
       <c r="AE154">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF154">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AG154">
         <v>2.45</v>
@@ -25574,10 +25574,10 @@
         </is>
       </c>
       <c r="N155">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="O155">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P155">
         <v>2.5</v>
@@ -25589,13 +25589,13 @@
         <v>2.1</v>
       </c>
       <c r="S155">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T155">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="U155">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="V155">
         <v>1.36</v>
@@ -25604,7 +25604,7 @@
         <v>1.03</v>
       </c>
       <c r="X155">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y155">
         <v>1.29</v>
@@ -25613,19 +25613,19 @@
         <v>3.04</v>
       </c>
       <c r="AA155">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="AB155">
         <v>1.74</v>
       </c>
       <c r="AC155">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AD155">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE155">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF155">
         <v>1.75</v>
@@ -25740,22 +25740,22 @@
         <v>3.6</v>
       </c>
       <c r="O156">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P156">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="Q156">
         <v>4.2</v>
       </c>
       <c r="R156">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="S156">
         <v>1.44</v>
       </c>
       <c r="T156">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="U156">
         <v>3.16</v>
@@ -25770,7 +25770,7 @@
         <v>1.06</v>
       </c>
       <c r="Y156">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z156">
         <v>2.8</v>
@@ -25788,7 +25788,7 @@
         <v>1.2</v>
       </c>
       <c r="AE156">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF156">
         <v>1.91</v>
@@ -25900,13 +25900,13 @@
         </is>
       </c>
       <c r="N157">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="O157">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="P157">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="Q157">
         <v>2</v>
@@ -25915,7 +25915,7 @@
         <v>2.35</v>
       </c>
       <c r="S157">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T157">
         <v>3.3</v>
@@ -25927,7 +25927,7 @@
         <v>1.55</v>
       </c>
       <c r="W157">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X157">
         <v>1.03</v>
@@ -25948,16 +25948,16 @@
         <v>2.6</v>
       </c>
       <c r="AD157">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AE157">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF157">
         <v>1.69</v>
       </c>
       <c r="AG157">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -26063,28 +26063,28 @@
         </is>
       </c>
       <c r="N158">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="O158">
         <v>3.9</v>
       </c>
       <c r="P158">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="Q158">
         <v>2.05</v>
       </c>
       <c r="R158">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="S158">
         <v>1.24</v>
       </c>
       <c r="T158">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="U158">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="V158">
         <v>1.62</v>
@@ -26102,10 +26102,10 @@
         <v>5</v>
       </c>
       <c r="AA158">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AB158">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="AC158">
         <v>2.23</v>
@@ -26114,13 +26114,13 @@
         <v>1.56</v>
       </c>
       <c r="AE158">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AF158">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG158">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26226,37 +26226,37 @@
         </is>
       </c>
       <c r="N159">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="O159">
-        <v>3.12</v>
+        <v>3.45</v>
       </c>
       <c r="P159">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="Q159">
         <v>2.3</v>
       </c>
       <c r="R159">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="S159">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T159">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U159">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="V159">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W159">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X159">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y159">
         <v>1.27</v>
@@ -26265,25 +26265,25 @@
         <v>4.1</v>
       </c>
       <c r="AA159">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AB159">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AC159">
-        <v>3.09</v>
+        <v>3.2</v>
       </c>
       <c r="AD159">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AE159">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF159">
         <v>1.67</v>
       </c>
       <c r="AG159">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
@@ -26299,7 +26299,7 @@
         <v>1.19</v>
       </c>
       <c r="AK159">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26389,10 +26389,10 @@
         </is>
       </c>
       <c r="N160">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="O160">
-        <v>3.73</v>
+        <v>4.35</v>
       </c>
       <c r="P160">
         <v>5.4</v>
@@ -26555,40 +26555,40 @@
         <v>1.91</v>
       </c>
       <c r="O161">
-        <v>3.2</v>
+        <v>3.01</v>
       </c>
       <c r="P161">
-        <v>3.6</v>
+        <v>3.31</v>
       </c>
       <c r="Q161">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="R161">
         <v>2.05</v>
       </c>
       <c r="S161">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T161">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="U161">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
       <c r="V161">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W161">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X161">
         <v>1.07</v>
       </c>
       <c r="Y161">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="Z161">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="AA161">
         <v>2.02</v>
@@ -26609,7 +26609,7 @@
         <v>1.85</v>
       </c>
       <c r="AG161">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26625,7 +26625,7 @@
         <v>1.25</v>
       </c>
       <c r="AK161">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -26715,13 +26715,13 @@
         </is>
       </c>
       <c r="N162">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="O162">
-        <v>3.07</v>
+        <v>3.4</v>
       </c>
       <c r="P162">
-        <v>3.9</v>
+        <v>4.16</v>
       </c>
       <c r="Q162">
         <v>2.3</v>
@@ -26739,13 +26739,13 @@
         <v>2.8</v>
       </c>
       <c r="V162">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W162">
         <v>1.04</v>
       </c>
       <c r="X162">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y162">
         <v>1.33</v>
@@ -26766,13 +26766,13 @@
         <v>1.27</v>
       </c>
       <c r="AE162">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF162">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="AG162">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
@@ -26788,7 +26788,7 @@
         <v>1.16</v>
       </c>
       <c r="AK162">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL162">
         <v>0</v>
@@ -26878,28 +26878,28 @@
         </is>
       </c>
       <c r="N163">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="O163">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P163">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="Q163">
-        <v>4.2</v>
+        <v>3.88</v>
       </c>
       <c r="R163">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="S163">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="T163">
-        <v>2.54</v>
+        <v>2.69</v>
       </c>
       <c r="U163">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="V163">
         <v>1.35</v>
@@ -26908,31 +26908,31 @@
         <v>1.03</v>
       </c>
       <c r="X163">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y163">
         <v>1.36</v>
       </c>
       <c r="Z163">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="AA163">
         <v>2.1</v>
       </c>
       <c r="AB163">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AC163">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AD163">
         <v>1.24</v>
       </c>
       <c r="AE163">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF163">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AG163">
         <v>1.91</v>
@@ -26948,10 +26948,10 @@
         </is>
       </c>
       <c r="AJ163">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK163">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -27059,7 +27059,7 @@
         <v>1.36</v>
       </c>
       <c r="T164">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="U164">
         <v>2.62</v>
@@ -27074,22 +27074,22 @@
         <v>1.05</v>
       </c>
       <c r="Y164">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z164">
         <v>3.6</v>
       </c>
       <c r="AA164">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AB164">
-        <v>2.01</v>
+        <v>1.89</v>
       </c>
       <c r="AC164">
-        <v>2.72</v>
+        <v>3.15</v>
       </c>
       <c r="AD164">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE164">
         <v>1.11</v>
@@ -27114,7 +27114,7 @@
         <v>1.29</v>
       </c>
       <c r="AK164">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AL164">
         <v>0</v>
@@ -27204,13 +27204,13 @@
         </is>
       </c>
       <c r="N165">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="O165">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P165">
-        <v>2.9</v>
+        <v>3.32</v>
       </c>
       <c r="Q165">
         <v>2.65</v>
@@ -27219,10 +27219,10 @@
         <v>2.12</v>
       </c>
       <c r="S165">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T165">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="U165">
         <v>2.66</v>
@@ -27231,7 +27231,7 @@
         <v>1.4</v>
       </c>
       <c r="W165">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X165">
         <v>1.03</v>
@@ -27246,10 +27246,10 @@
         <v>1.95</v>
       </c>
       <c r="AB165">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AC165">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="AD165">
         <v>1.29</v>
@@ -27277,7 +27277,7 @@
         <v>1.28</v>
       </c>
       <c r="AK165">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AL165">
         <v>0</v>
@@ -27367,19 +27367,19 @@
         </is>
       </c>
       <c r="N166">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="O166">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P166">
         <v>3.4</v>
       </c>
       <c r="Q166">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="R166">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="S166">
         <v>1.4</v>
@@ -27394,31 +27394,31 @@
         <v>1.4</v>
       </c>
       <c r="W166">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X166">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y166">
         <v>1.24</v>
       </c>
       <c r="Z166">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="AA166">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AB166">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AC166">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="AD166">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE166">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF166">
         <v>1.75</v>
@@ -27437,10 +27437,10 @@
         </is>
       </c>
       <c r="AJ166">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK166">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AL166">
         <v>0</v>
@@ -27530,31 +27530,31 @@
         </is>
       </c>
       <c r="N167">
-        <v>2.22</v>
+        <v>2.37</v>
       </c>
       <c r="O167">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="P167">
+        <v>2.62</v>
+      </c>
+      <c r="Q167">
+        <v>3.18</v>
+      </c>
+      <c r="R167">
+        <v>2</v>
+      </c>
+      <c r="S167">
+        <v>1.44</v>
+      </c>
+      <c r="T167">
         <v>2.75</v>
       </c>
-      <c r="Q167">
-        <v>2.88</v>
-      </c>
-      <c r="R167">
-        <v>1.96</v>
-      </c>
-      <c r="S167">
-        <v>1.4</v>
-      </c>
-      <c r="T167">
-        <v>2.7</v>
-      </c>
       <c r="U167">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="V167">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="W167">
         <v>1.04</v>
@@ -27563,31 +27563,31 @@
         <v>1.06</v>
       </c>
       <c r="Y167">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z167">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="AA167">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="AB167">
         <v>1.68</v>
       </c>
       <c r="AC167">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="AD167">
         <v>1.25</v>
       </c>
       <c r="AE167">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF167">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AG167">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
@@ -27600,7 +27600,7 @@
         </is>
       </c>
       <c r="AJ167">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AK167">
         <v>1.5</v>
@@ -27693,16 +27693,16 @@
         </is>
       </c>
       <c r="N168">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O168">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P168">
-        <v>3.4</v>
+        <v>2.91</v>
       </c>
       <c r="Q168">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="R168">
         <v>2.1</v>
@@ -27711,13 +27711,13 @@
         <v>1.36</v>
       </c>
       <c r="T168">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U168">
         <v>2.69</v>
       </c>
       <c r="V168">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="W168">
         <v>1.05</v>
@@ -27729,25 +27729,25 @@
         <v>1.29</v>
       </c>
       <c r="Z168">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="AA168">
         <v>1.85</v>
       </c>
       <c r="AB168">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AC168">
-        <v>3.25</v>
+        <v>3.39</v>
       </c>
       <c r="AD168">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE168">
         <v>1.09</v>
       </c>
       <c r="AF168">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG168">
         <v>2</v>
@@ -27859,7 +27859,7 @@
         <v>3.3</v>
       </c>
       <c r="O169">
-        <v>3.03</v>
+        <v>3.2</v>
       </c>
       <c r="P169">
         <v>1.94</v>
@@ -27871,13 +27871,13 @@
         <v>2.1</v>
       </c>
       <c r="S169">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T169">
         <v>2.8</v>
       </c>
       <c r="U169">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="V169">
         <v>1.37</v>
@@ -27886,25 +27886,25 @@
         <v>1.05</v>
       </c>
       <c r="X169">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y169">
         <v>1.3</v>
       </c>
       <c r="Z169">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AA169">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AB169">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AC169">
         <v>3.6</v>
       </c>
       <c r="AD169">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AE169">
         <v>1.06</v>
@@ -27926,7 +27926,7 @@
         </is>
       </c>
       <c r="AJ169">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AK169">
         <v>1.29</v>
@@ -28019,10 +28019,10 @@
         </is>
       </c>
       <c r="N170">
-        <v>4.11</v>
+        <v>3.93</v>
       </c>
       <c r="O170">
-        <v>3.82</v>
+        <v>3.45</v>
       </c>
       <c r="P170">
         <v>1.75</v>
@@ -28185,10 +28185,10 @@
         <v>1.6</v>
       </c>
       <c r="O171">
-        <v>4.14</v>
+        <v>3.9</v>
       </c>
       <c r="P171">
-        <v>5.52</v>
+        <v>5.51</v>
       </c>
       <c r="Q171">
         <v>0</v>
@@ -28508,7 +28508,7 @@
         </is>
       </c>
       <c r="N173">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="O173">
         <v>4.1</v>
@@ -28517,25 +28517,25 @@
         <v>8.050000000000001</v>
       </c>
       <c r="Q173">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="R173">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S173">
         <v>1.36</v>
       </c>
       <c r="T173">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="U173">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="V173">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="W173">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X173">
         <v>1.02</v>
@@ -28544,28 +28544,28 @@
         <v>1.26</v>
       </c>
       <c r="Z173">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="AA173">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AB173">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AC173">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="AD173">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AE173">
         <v>1.07</v>
       </c>
       <c r="AF173">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AG173">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="AH173" t="inlineStr">
         <is>
@@ -28578,10 +28578,10 @@
         </is>
       </c>
       <c r="AJ173">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AK173">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="AL173">
         <v>0</v>
@@ -28671,64 +28671,64 @@
         </is>
       </c>
       <c r="N174">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="O174">
+        <v>3</v>
+      </c>
+      <c r="P174">
         <v>3.1</v>
       </c>
-      <c r="P174">
-        <v>3.89</v>
-      </c>
       <c r="Q174">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="R174">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="S174">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="T174">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="U174">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="V174">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W174">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X174">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y174">
         <v>1.44</v>
       </c>
       <c r="Z174">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="AA174">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="AB174">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="AC174">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="AD174">
         <v>1.13</v>
       </c>
       <c r="AE174">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF174">
         <v>2.05</v>
       </c>
       <c r="AG174">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AH174" t="inlineStr">
         <is>
@@ -28741,10 +28741,10 @@
         </is>
       </c>
       <c r="AJ174">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AK174">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AL174">
         <v>0</v>
@@ -28997,10 +28997,10 @@
         </is>
       </c>
       <c r="N176">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="O176">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="P176">
         <v>2.85</v>
@@ -29018,28 +29018,28 @@
         <v>2.7</v>
       </c>
       <c r="U176">
-        <v>2.76</v>
+        <v>2.55</v>
       </c>
       <c r="V176">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W176">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X176">
         <v>1.05</v>
       </c>
       <c r="Y176">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z176">
         <v>3.4</v>
       </c>
       <c r="AA176">
+        <v>1.89</v>
+      </c>
+      <c r="AB176">
         <v>1.96</v>
-      </c>
-      <c r="AB176">
-        <v>1.85</v>
       </c>
       <c r="AC176">
         <v>3.1</v>
@@ -29048,7 +29048,7 @@
         <v>1.3</v>
       </c>
       <c r="AE176">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF176">
         <v>1.71</v>
@@ -29160,13 +29160,13 @@
         </is>
       </c>
       <c r="N177">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="O177">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P177">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="Q177">
         <v>2.7</v>
@@ -29486,64 +29486,64 @@
         </is>
       </c>
       <c r="N179">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O179">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P179">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q179">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R179">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S179">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T179">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U179">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V179">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W179">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X179">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y179">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z179">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA179">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB179">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC179">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD179">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE179">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF179">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG179">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH179" t="inlineStr">
         <is>
@@ -29556,10 +29556,10 @@
         </is>
       </c>
       <c r="AJ179">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK179">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -29661,7 +29661,7 @@
         <v>2.63</v>
       </c>
       <c r="R180">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="S180">
         <v>1.33</v>
@@ -29815,7 +29815,7 @@
         <v>1.48</v>
       </c>
       <c r="O181">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="P181">
         <v>6.5</v>
@@ -29824,7 +29824,7 @@
         <v>1.83</v>
       </c>
       <c r="R181">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="S181">
         <v>1.2</v>
@@ -29833,10 +29833,10 @@
         <v>4</v>
       </c>
       <c r="U181">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="V181">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="W181">
         <v>1.14</v>
@@ -29845,22 +29845,22 @@
         <v>1.01</v>
       </c>
       <c r="Y181">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z181">
         <v>5.4</v>
       </c>
       <c r="AA181">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AB181">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AC181">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AD181">
-        <v>1.59</v>
+        <v>1.68</v>
       </c>
       <c r="AE181">
         <v>1.22</v>
@@ -29882,10 +29882,10 @@
         </is>
       </c>
       <c r="AJ181">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AK181">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AL181">
         <v>0</v>
@@ -29981,7 +29981,7 @@
         <v>2.9</v>
       </c>
       <c r="P182">
-        <v>2.85</v>
+        <v>3.35</v>
       </c>
       <c r="Q182">
         <v>2.85</v>
@@ -29990,10 +29990,10 @@
         <v>1.9</v>
       </c>
       <c r="S182">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="T182">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="U182">
         <v>3.2</v>
@@ -30002,7 +30002,7 @@
         <v>1.31</v>
       </c>
       <c r="W182">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X182">
         <v>1.04</v>
@@ -30011,10 +30011,10 @@
         <v>1.38</v>
       </c>
       <c r="Z182">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AA182">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB182">
         <v>1.71</v>
@@ -30029,7 +30029,7 @@
         <v>1.06</v>
       </c>
       <c r="AF182">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AG182">
         <v>1.83</v>
@@ -30138,7 +30138,7 @@
         </is>
       </c>
       <c r="N183">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="O183">
         <v>5.8</v>
@@ -30147,25 +30147,25 @@
         <v>1.17</v>
       </c>
       <c r="Q183">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="R183">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="S183">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T183">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U183">
-        <v>2.29</v>
+        <v>2.08</v>
       </c>
       <c r="V183">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W183">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="X183">
         <v>1.03</v>
@@ -30174,28 +30174,28 @@
         <v>1.13</v>
       </c>
       <c r="Z183">
-        <v>4.68</v>
+        <v>4.6</v>
       </c>
       <c r="AA183">
         <v>1.55</v>
       </c>
       <c r="AB183">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="AC183">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AD183">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AE183">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AF183">
         <v>2</v>
       </c>
       <c r="AG183">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AH183" t="inlineStr">
         <is>
@@ -30301,13 +30301,13 @@
         </is>
       </c>
       <c r="N184">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="O184">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="P184">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="Q184">
         <v>0</v>
@@ -30340,10 +30340,10 @@
         <v>0</v>
       </c>
       <c r="AA184">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AB184">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AC184">
         <v>0</v>
@@ -30470,28 +30470,28 @@
         <v>2.85</v>
       </c>
       <c r="P185">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="Q185">
-        <v>3.05</v>
+        <v>2.62</v>
       </c>
       <c r="R185">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="S185">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="T185">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="U185">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="V185">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="W185">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X185">
         <v>1.07</v>
@@ -30503,22 +30503,22 @@
         <v>2.5</v>
       </c>
       <c r="AA185">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AB185">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AC185">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="AD185">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AE185">
         <v>1.01</v>
       </c>
       <c r="AF185">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="AG185">
         <v>1.67</v>
@@ -31122,7 +31122,7 @@
         <v>7</v>
       </c>
       <c r="P189">
-        <v>12.17</v>
+        <v>9.52</v>
       </c>
       <c r="Q189">
         <v>1.53</v>
@@ -31158,7 +31158,7 @@
         <v>1.25</v>
       </c>
       <c r="AB189">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="AC189">
         <v>1.79</v>
@@ -31167,13 +31167,13 @@
         <v>1.96</v>
       </c>
       <c r="AE189">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AF189">
         <v>1.77</v>
       </c>
       <c r="AG189">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AH189" t="inlineStr">
         <is>
@@ -31605,22 +31605,22 @@
         </is>
       </c>
       <c r="N192">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="O192">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="P192">
-        <v>5.69</v>
+        <v>5.75</v>
       </c>
       <c r="Q192">
         <v>1.91</v>
       </c>
       <c r="R192">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S192">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T192">
         <v>3.1</v>
@@ -31635,7 +31635,7 @@
         <v>1.1</v>
       </c>
       <c r="X192">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y192">
         <v>1.25</v>
@@ -31647,22 +31647,22 @@
         <v>1.76</v>
       </c>
       <c r="AB192">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC192">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="AD192">
         <v>1.36</v>
       </c>
       <c r="AE192">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF192">
         <v>1.83</v>
       </c>
       <c r="AG192">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
@@ -31675,10 +31675,10 @@
         </is>
       </c>
       <c r="AJ192">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK192">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AL192">
         <v>0</v>
@@ -31931,16 +31931,16 @@
         </is>
       </c>
       <c r="N194">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="O194">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P194">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="Q194">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="R194">
         <v>2</v>
@@ -31949,7 +31949,7 @@
         <v>1.48</v>
       </c>
       <c r="T194">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="U194">
         <v>3.6</v>
@@ -32004,7 +32004,7 @@
         <v>1.2</v>
       </c>
       <c r="AK194">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G195">
@@ -32094,61 +32094,61 @@
         </is>
       </c>
       <c r="N195">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="O195">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P195">
-        <v>3.83</v>
+        <v>3.99</v>
       </c>
       <c r="Q195">
         <v>2.59</v>
       </c>
       <c r="R195">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="S195">
         <v>1.44</v>
       </c>
       <c r="T195">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="U195">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="V195">
         <v>1.29</v>
       </c>
       <c r="W195">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X195">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y195">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="Z195">
-        <v>2.75</v>
+        <v>2.42</v>
       </c>
       <c r="AA195">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="AB195">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AC195">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="AD195">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AE195">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF195">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="AG195">
         <v>1.7</v>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK195">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,64 +32257,64 @@
         </is>
       </c>
       <c r="N196">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="O196">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P196">
-        <v>3.99</v>
+        <v>3.5</v>
       </c>
       <c r="Q196">
-        <v>2.59</v>
+        <v>2.48</v>
       </c>
       <c r="R196">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="S196">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="T196">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="U196">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="V196">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="W196">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X196">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y196">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="Z196">
-        <v>2.42</v>
+        <v>2.69</v>
       </c>
       <c r="AA196">
-        <v>2.5</v>
+        <v>2.21</v>
       </c>
       <c r="AB196">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AC196">
-        <v>4.55</v>
+        <v>4.4</v>
       </c>
       <c r="AD196">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AE196">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF196">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AG196">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK196">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G200">
@@ -32909,64 +32909,64 @@
         </is>
       </c>
       <c r="N200">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="O200">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="P200">
-        <v>2.76</v>
+        <v>3.73</v>
       </c>
       <c r="Q200">
-        <v>3.02</v>
+        <v>2.25</v>
       </c>
       <c r="R200">
-        <v>1.94</v>
+        <v>2.41</v>
       </c>
       <c r="S200">
-        <v>1.46</v>
+        <v>1.27</v>
       </c>
       <c r="T200">
-        <v>2.44</v>
+        <v>3.25</v>
       </c>
       <c r="U200">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="V200">
-        <v>1.29</v>
+        <v>1.49</v>
       </c>
       <c r="W200">
+        <v>1.08</v>
+      </c>
+      <c r="X200">
         <v>1.02</v>
       </c>
-      <c r="X200">
-        <v>1.04</v>
-      </c>
       <c r="Y200">
-        <v>1.38</v>
+        <v>1.16</v>
       </c>
       <c r="Z200">
-        <v>2.62</v>
+        <v>4.1</v>
       </c>
       <c r="AA200">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AB200">
-        <v>1.62</v>
+        <v>2.18</v>
       </c>
       <c r="AC200">
-        <v>4.05</v>
+        <v>2.56</v>
       </c>
       <c r="AD200">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AE200">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="AF200">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="AG200">
-        <v>1.77</v>
+        <v>2.19</v>
       </c>
       <c r="AH200" t="inlineStr">
         <is>
@@ -32979,10 +32979,10 @@
         </is>
       </c>
       <c r="AJ200">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK200">
-        <v>1.47</v>
+        <v>1.86</v>
       </c>
       <c r="AL200">
         <v>0</v>
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G201">
@@ -33072,64 +33072,64 @@
         </is>
       </c>
       <c r="N201">
-        <v>1.75</v>
+        <v>2.35</v>
       </c>
       <c r="O201">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="P201">
-        <v>3.73</v>
+        <v>2.76</v>
       </c>
       <c r="Q201">
-        <v>2.25</v>
+        <v>3.02</v>
       </c>
       <c r="R201">
-        <v>2.41</v>
+        <v>1.94</v>
       </c>
       <c r="S201">
-        <v>1.27</v>
+        <v>1.46</v>
       </c>
       <c r="T201">
-        <v>3.25</v>
+        <v>2.44</v>
       </c>
       <c r="U201">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="V201">
-        <v>1.49</v>
+        <v>1.29</v>
       </c>
       <c r="W201">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X201">
+        <v>1.04</v>
+      </c>
+      <c r="Y201">
+        <v>1.38</v>
+      </c>
+      <c r="Z201">
+        <v>2.62</v>
+      </c>
+      <c r="AA201">
+        <v>2.2</v>
+      </c>
+      <c r="AB201">
+        <v>1.62</v>
+      </c>
+      <c r="AC201">
+        <v>4.05</v>
+      </c>
+      <c r="AD201">
+        <v>1.2</v>
+      </c>
+      <c r="AE201">
         <v>1.02</v>
       </c>
-      <c r="Y201">
-        <v>1.16</v>
-      </c>
-      <c r="Z201">
-        <v>4.1</v>
-      </c>
-      <c r="AA201">
-        <v>1.67</v>
-      </c>
-      <c r="AB201">
-        <v>2.18</v>
-      </c>
-      <c r="AC201">
-        <v>2.56</v>
-      </c>
-      <c r="AD201">
-        <v>1.4</v>
-      </c>
-      <c r="AE201">
-        <v>1.17</v>
-      </c>
       <c r="AF201">
-        <v>1.6</v>
+        <v>1.92</v>
       </c>
       <c r="AG201">
-        <v>2.19</v>
+        <v>1.77</v>
       </c>
       <c r="AH201" t="inlineStr">
         <is>
@@ -33142,10 +33142,10 @@
         </is>
       </c>
       <c r="AJ201">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK201">
-        <v>1.86</v>
+        <v>1.47</v>
       </c>
       <c r="AL201">
         <v>0</v>

--- a/jogos_2026-08-08.xlsx
+++ b/jogos_2026-08-08.xlsx
@@ -2070,75 +2070,75 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="O11">
+        <v>3.3</v>
+      </c>
+      <c r="P11">
+        <v>2.43</v>
+      </c>
+      <c r="Q11">
         <v>3.5</v>
       </c>
-      <c r="P11">
-        <v>2</v>
-      </c>
-      <c r="Q11">
-        <v>0</v>
-      </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA11">
         <v>2.15</v>
@@ -2147,62 +2147,62 @@
         <v>1.66</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
+          <t>["6", "48"]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN11">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO11">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -2233,75 +2233,75 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12">
         <v>0</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="O12">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P12">
-        <v>2.43</v>
+        <v>2</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA12">
         <v>2.15</v>
@@ -2310,62 +2310,62 @@
         <v>1.66</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
+          <t>["12", "73"]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN12">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -2408,13 +2408,13 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
@@ -2437,34 +2437,34 @@
         <v>2.42</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA13">
         <v>2.35</v>
@@ -2473,19 +2473,19 @@
         <v>1.57</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2494,41 +2494,41 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["43"]</t>
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -2559,19 +2559,19 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Tegevajaro Miyazaki</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G14">
         <v>0</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -2583,72 +2583,72 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14">
-        <v>2.54</v>
+        <v>2.65</v>
       </c>
       <c r="O14">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P14">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA14">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB14">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2657,41 +2657,41 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["77"]</t>
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP14">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
@@ -2722,22 +2722,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tegevajaro Miyazaki</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15">
         <v>0</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2750,111 +2750,111 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15">
-        <v>2.65</v>
+        <v>2.03</v>
       </c>
       <c r="O15">
+        <v>3.27</v>
+      </c>
+      <c r="P15">
+        <v>3.35</v>
+      </c>
+      <c r="Q15">
+        <v>2.7</v>
+      </c>
+      <c r="R15">
+        <v>2.15</v>
+      </c>
+      <c r="S15">
+        <v>1.36</v>
+      </c>
+      <c r="T15">
+        <v>2.78</v>
+      </c>
+      <c r="U15">
+        <v>2.7</v>
+      </c>
+      <c r="V15">
+        <v>1.38</v>
+      </c>
+      <c r="W15">
+        <v>1.04</v>
+      </c>
+      <c r="X15">
+        <v>1.05</v>
+      </c>
+      <c r="Y15">
+        <v>1.25</v>
+      </c>
+      <c r="Z15">
+        <v>3.5</v>
+      </c>
+      <c r="AA15">
+        <v>1.9</v>
+      </c>
+      <c r="AB15">
+        <v>1.9</v>
+      </c>
+      <c r="AC15">
+        <v>3.1</v>
+      </c>
+      <c r="AD15">
+        <v>1.3</v>
+      </c>
+      <c r="AE15">
+        <v>1.11</v>
+      </c>
+      <c r="AF15">
+        <v>1.7</v>
+      </c>
+      <c r="AG15">
+        <v>2.05</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>["5"]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15">
+        <v>1.3</v>
+      </c>
+      <c r="AK15">
+        <v>1.7</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>2</v>
+      </c>
+      <c r="AN15">
+        <v>0</v>
+      </c>
+      <c r="AO15">
+        <v>14</v>
+      </c>
+      <c r="AP15">
         <v>3</v>
       </c>
-      <c r="P15">
-        <v>2.62</v>
-      </c>
-      <c r="Q15">
-        <v>0</v>
-      </c>
-      <c r="R15">
-        <v>0</v>
-      </c>
-      <c r="S15">
-        <v>0</v>
-      </c>
-      <c r="T15">
-        <v>0</v>
-      </c>
-      <c r="U15">
-        <v>0</v>
-      </c>
-      <c r="V15">
-        <v>0</v>
-      </c>
-      <c r="W15">
-        <v>0</v>
-      </c>
-      <c r="X15">
-        <v>0</v>
-      </c>
-      <c r="Y15">
-        <v>0</v>
-      </c>
-      <c r="Z15">
-        <v>0</v>
-      </c>
-      <c r="AA15">
-        <v>2.1</v>
-      </c>
-      <c r="AB15">
-        <v>1.7</v>
-      </c>
-      <c r="AC15">
-        <v>0</v>
-      </c>
-      <c r="AD15">
-        <v>0</v>
-      </c>
-      <c r="AE15">
-        <v>0</v>
-      </c>
-      <c r="AF15">
-        <v>0</v>
-      </c>
-      <c r="AG15">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15">
-        <v>0</v>
-      </c>
-      <c r="AK15">
-        <v>0</v>
-      </c>
-      <c r="AL15">
-        <v>0</v>
-      </c>
-      <c r="AM15">
-        <v>-1</v>
-      </c>
-      <c r="AN15">
-        <v>-1</v>
-      </c>
-      <c r="AO15">
-        <v>-1</v>
-      </c>
-      <c r="AP15">
-        <v>-1</v>
-      </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>0.76</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
@@ -2885,22 +2885,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2909,115 +2909,115 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
-        <v>2.03</v>
+        <v>2.54</v>
       </c>
       <c r="O16">
-        <v>3.27</v>
+        <v>2.9</v>
       </c>
       <c r="P16">
-        <v>3.35</v>
+        <v>2.75</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA16">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AB16">
-        <v>1.9</v>
+        <v>1.66</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["1"]</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["61"]</t>
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL16">
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN16">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
@@ -3057,36 +3057,36 @@
         </is>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="O17">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P17">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="Q17">
         <v>2.43</v>
@@ -3095,10 +3095,10 @@
         <v>2.1</v>
       </c>
       <c r="S17">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T17">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="U17">
         <v>3.16</v>
@@ -3116,7 +3116,7 @@
         <v>1.36</v>
       </c>
       <c r="Z17">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AA17">
         <v>2.23</v>
@@ -3141,12 +3141,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["85"]</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["7", "38", "63", "78"]</t>
         </is>
       </c>
       <c r="AJ17">
@@ -3159,28 +3159,28 @@
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO17">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
@@ -3239,35 +3239,35 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="O18">
-        <v>3.46</v>
+        <v>3.65</v>
       </c>
       <c r="P18">
-        <v>3.61</v>
+        <v>3.65</v>
       </c>
       <c r="Q18">
-        <v>2.64</v>
+        <v>2.31</v>
       </c>
       <c r="R18">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="S18">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T18">
         <v>2.75</v>
       </c>
       <c r="U18">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="V18">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W18">
         <v>1.07</v>
@@ -3282,13 +3282,13 @@
         <v>3.08</v>
       </c>
       <c r="AA18">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AB18">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AC18">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AD18">
         <v>1.22</v>
@@ -3300,7 +3300,7 @@
         <v>1.95</v>
       </c>
       <c r="AG18">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3316,34 +3316,34 @@
         <v>1.24</v>
       </c>
       <c r="AK18">
-        <v>1.77</v>
+        <v>1.88</v>
       </c>
       <c r="AL18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
@@ -3386,13 +3386,13 @@
         <v>0</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19">
         <v>0</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19">
         <v>0</v>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N19">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["23"]</t>
         </is>
       </c>
       <c r="AJ19">
@@ -3485,28 +3485,28 @@
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN19">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO19">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
@@ -3549,13 +3549,13 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20">
         <v>0</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20">
         <v>0</v>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N20">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["38"]</t>
         </is>
       </c>
       <c r="AJ20">
@@ -3648,28 +3648,28 @@
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO20">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP20">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
@@ -3709,26 +3709,26 @@
         </is>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K21">
         <v>0</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N21">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["5"]</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["27", "45+2", "52", "65", "80"]</t>
         </is>
       </c>
       <c r="AJ21">
@@ -3811,28 +3811,28 @@
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP21">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -3887,11 +3887,11 @@
         <v>0</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N22">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["5", "36"]</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["68"]</t>
         </is>
       </c>
       <c r="AJ22">
@@ -3974,28 +3974,28 @@
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN22">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP22">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
@@ -4035,16 +4035,16 @@
         </is>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N23">
@@ -4119,12 +4119,12 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["20", "24"]</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["8"]</t>
         </is>
       </c>
       <c r="AJ23">
@@ -4137,28 +4137,28 @@
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP23">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
@@ -4198,26 +4198,26 @@
         </is>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H24">
         <v>0</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24">
         <v>0</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L24">
         <v>0</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N24">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["3", "79", "88"]</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
@@ -4300,28 +4300,28 @@
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN24">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO24">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AP24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AR24">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AT24">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
@@ -4361,26 +4361,26 @@
         </is>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H25">
         <v>0</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25">
         <v>0</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25">
         <v>0</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N25">
@@ -4393,34 +4393,34 @@
         <v>3.9</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA25">
         <v>2.3</v>
@@ -4429,62 +4429,62 @@
         <v>1.6</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
+          <t>["42", "87"]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL25">
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO25">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP25">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ25">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AR25">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AS25">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT25">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
@@ -4543,17 +4543,17 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N26">
         <v>3.5</v>
       </c>
       <c r="O26">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P26">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="Q26">
         <v>3.61</v>
@@ -4568,7 +4568,7 @@
         <v>2.77</v>
       </c>
       <c r="U26">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="V26">
         <v>1.44</v>
@@ -4586,10 +4586,10 @@
         <v>3.54</v>
       </c>
       <c r="AA26">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AB26">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="AC26">
         <v>3.1</v>
@@ -4626,28 +4626,28 @@
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN26">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO26">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP26">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ26">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="AR26">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="AS26">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AT26">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G27">
@@ -4706,111 +4706,111 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N27">
-        <v>2.75</v>
+        <v>1.95</v>
       </c>
       <c r="O27">
         <v>3.1</v>
       </c>
       <c r="P27">
-        <v>2.34</v>
+        <v>4.1</v>
       </c>
       <c r="Q27">
+        <v>2.38</v>
+      </c>
+      <c r="R27">
+        <v>2</v>
+      </c>
+      <c r="S27">
+        <v>1.44</v>
+      </c>
+      <c r="T27">
+        <v>2.53</v>
+      </c>
+      <c r="U27">
         <v>3.25</v>
       </c>
-      <c r="R27">
-        <v>2.1</v>
-      </c>
-      <c r="S27">
-        <v>1.34</v>
-      </c>
-      <c r="T27">
-        <v>2.75</v>
-      </c>
-      <c r="U27">
-        <v>2.88</v>
-      </c>
       <c r="V27">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="W27">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y27">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="Z27">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AA27">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AB27">
+        <v>1.66</v>
+      </c>
+      <c r="AC27">
+        <v>4.2</v>
+      </c>
+      <c r="AD27">
+        <v>1.17</v>
+      </c>
+      <c r="AE27">
+        <v>1.02</v>
+      </c>
+      <c r="AF27">
+        <v>1.99</v>
+      </c>
+      <c r="AG27">
+        <v>1.73</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
+        <v>1.28</v>
+      </c>
+      <c r="AK27">
         <v>1.85</v>
       </c>
-      <c r="AC27">
-        <v>3.3</v>
-      </c>
-      <c r="AD27">
-        <v>1.29</v>
-      </c>
-      <c r="AE27">
-        <v>1.08</v>
-      </c>
-      <c r="AF27">
-        <v>1.75</v>
-      </c>
-      <c r="AG27">
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>1</v>
+      </c>
+      <c r="AN27">
         <v>2</v>
       </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>1.33</v>
-      </c>
-      <c r="AK27">
-        <v>1.4</v>
-      </c>
-      <c r="AL27">
-        <v>0</v>
-      </c>
-      <c r="AM27">
-        <v>-1</v>
-      </c>
-      <c r="AN27">
-        <v>-1</v>
-      </c>
       <c r="AO27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP27">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR27">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
@@ -4841,19 +4841,19 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G28">
         <v>0</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -4865,115 +4865,115 @@
         <v>0</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N28">
-        <v>1.93</v>
+        <v>2.7</v>
       </c>
       <c r="O28">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="P28">
-        <v>4</v>
+        <v>2.55</v>
       </c>
       <c r="Q28">
-        <v>2.38</v>
+        <v>3.61</v>
       </c>
       <c r="R28">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="S28">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T28">
-        <v>2.53</v>
+        <v>2.88</v>
       </c>
       <c r="U28">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="V28">
+        <v>1.36</v>
+      </c>
+      <c r="W28">
+        <v>1.04</v>
+      </c>
+      <c r="X28">
+        <v>1.01</v>
+      </c>
+      <c r="Y28">
+        <v>1.32</v>
+      </c>
+      <c r="Z28">
+        <v>3.4</v>
+      </c>
+      <c r="AA28">
+        <v>1.98</v>
+      </c>
+      <c r="AB28">
+        <v>1.87</v>
+      </c>
+      <c r="AC28">
+        <v>3.64</v>
+      </c>
+      <c r="AD28">
+        <v>1.25</v>
+      </c>
+      <c r="AE28">
+        <v>1.1</v>
+      </c>
+      <c r="AF28">
+        <v>1.7</v>
+      </c>
+      <c r="AG28">
+        <v>2.05</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>["65", "67"]</t>
+        </is>
+      </c>
+      <c r="AJ28">
+        <v>1.32</v>
+      </c>
+      <c r="AK28">
+        <v>1.4</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>1</v>
+      </c>
+      <c r="AN28">
+        <v>6</v>
+      </c>
+      <c r="AO28">
+        <v>11</v>
+      </c>
+      <c r="AP28">
+        <v>8</v>
+      </c>
+      <c r="AQ28">
+        <v>1.15</v>
+      </c>
+      <c r="AR28">
         <v>1.28</v>
       </c>
-      <c r="W28">
-        <v>1.06</v>
-      </c>
-      <c r="X28">
-        <v>1.05</v>
-      </c>
-      <c r="Y28">
-        <v>1.36</v>
-      </c>
-      <c r="Z28">
-        <v>2.72</v>
-      </c>
-      <c r="AA28">
-        <v>2.32</v>
-      </c>
-      <c r="AB28">
-        <v>1.66</v>
-      </c>
-      <c r="AC28">
-        <v>4.39</v>
-      </c>
-      <c r="AD28">
-        <v>1.17</v>
-      </c>
-      <c r="AE28">
-        <v>1.02</v>
-      </c>
-      <c r="AF28">
-        <v>1.98</v>
-      </c>
-      <c r="AG28">
-        <v>1.74</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28">
-        <v>1.28</v>
-      </c>
-      <c r="AK28">
-        <v>1.85</v>
-      </c>
-      <c r="AL28">
-        <v>0</v>
-      </c>
-      <c r="AM28">
-        <v>-1</v>
-      </c>
-      <c r="AN28">
-        <v>-1</v>
-      </c>
-      <c r="AO28">
-        <v>-1</v>
-      </c>
-      <c r="AP28">
-        <v>-1</v>
-      </c>
-      <c r="AQ28">
-        <v>0</v>
-      </c>
-      <c r="AR28">
-        <v>0</v>
-      </c>
       <c r="AS28">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT28">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
@@ -5004,139 +5004,139 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I29">
         <v>0</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N29">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="O29">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="P29">
-        <v>2.55</v>
+        <v>4.65</v>
       </c>
       <c r="Q29">
-        <v>3.51</v>
+        <v>2.31</v>
       </c>
       <c r="R29">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S29">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T29">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U29">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="V29">
         <v>1.36</v>
       </c>
       <c r="W29">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X29">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y29">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z29">
         <v>3.4</v>
       </c>
       <c r="AA29">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="AB29">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AC29">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AD29">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AE29">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF29">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AG29">
+        <v>1.77</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>["58"]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>["23", "70", "90+8"]</t>
+        </is>
+      </c>
+      <c r="AJ29">
+        <v>1.22</v>
+      </c>
+      <c r="AK29">
         <v>2.05</v>
       </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ29">
-        <v>1.32</v>
-      </c>
-      <c r="AK29">
-        <v>1.4</v>
-      </c>
       <c r="AL29">
         <v>0</v>
       </c>
       <c r="AM29">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN29">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP29">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ29">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR29">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="AS29">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="AT29">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
@@ -5167,139 +5167,139 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I30">
         <v>0</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30">
         <v>0</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N30">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="O30">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="P30">
-        <v>4.6</v>
+        <v>2.35</v>
       </c>
       <c r="Q30">
-        <v>2.31</v>
+        <v>3.4</v>
       </c>
       <c r="R30">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S30">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T30">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="U30">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="V30">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W30">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X30">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z30">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="AA30">
-        <v>1.99</v>
+        <v>1.89</v>
       </c>
       <c r="AB30">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC30">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="AD30">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE30">
         <v>1.08</v>
       </c>
       <c r="AF30">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG30">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["61"]</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["17", "40"]</t>
         </is>
       </c>
       <c r="AJ30">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK30">
-        <v>2.05</v>
+        <v>1.4</v>
       </c>
       <c r="AL30">
         <v>0</v>
       </c>
       <c r="AM30">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO30">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP30">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ30">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AR30">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AS30">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AT30">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>0</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -5354,69 +5354,69 @@
         <v>0</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N31">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="O31">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="P31">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="Q31">
-        <v>4.4</v>
+        <v>4.95</v>
       </c>
       <c r="R31">
-        <v>2.41</v>
+        <v>2.56</v>
       </c>
       <c r="S31">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="T31">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U31">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="V31">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="W31">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X31">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z31">
-        <v>5.97</v>
+        <v>6.73</v>
       </c>
       <c r="AA31">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="AB31">
-        <v>2.75</v>
+        <v>3.03</v>
       </c>
       <c r="AC31">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="AD31">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="AE31">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AF31">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG31">
         <v>2.55</v>
@@ -5428,41 +5428,41 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["54"]</t>
         </is>
       </c>
       <c r="AJ31">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK31">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AL31">
         <v>0</v>
       </c>
       <c r="AM31">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO31">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP31">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ31">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR31">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AS31">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT31">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>0</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -5517,11 +5517,11 @@
         <v>0</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N32">
@@ -5543,7 +5543,7 @@
         <v>1.29</v>
       </c>
       <c r="T32">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="U32">
         <v>2.38</v>
@@ -5561,13 +5561,13 @@
         <v>1.17</v>
       </c>
       <c r="Z32">
-        <v>3.95</v>
+        <v>3.98</v>
       </c>
       <c r="AA32">
         <v>1.6</v>
       </c>
       <c r="AB32">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC32">
         <v>2.7</v>
@@ -5579,7 +5579,7 @@
         <v>1.13</v>
       </c>
       <c r="AF32">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AG32">
         <v>2.15</v>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["63"]</t>
         </is>
       </c>
       <c r="AJ32">
@@ -5604,28 +5604,28 @@
         <v>0</v>
       </c>
       <c r="AM32">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP32">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ32">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AR32">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AS32">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT32">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
@@ -5665,36 +5665,36 @@
         </is>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N33">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="O33">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P33">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="Q33">
         <v>2.64</v>
@@ -5706,10 +5706,10 @@
         <v>1.34</v>
       </c>
       <c r="T33">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="U33">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="V33">
         <v>1.36</v>
@@ -5724,16 +5724,16 @@
         <v>1.28</v>
       </c>
       <c r="Z33">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="AA33">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB33">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC33">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AD33">
         <v>1.27</v>
@@ -5749,12 +5749,12 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["12", "45+2", "90+4"]</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["6", "58"]</t>
         </is>
       </c>
       <c r="AJ33">
@@ -5767,28 +5767,28 @@
         <v>0</v>
       </c>
       <c r="AM33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN33">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO33">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ33">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AR33">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AS33">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AT33">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
@@ -5828,10 +5828,10 @@
         </is>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -5840,14 +5840,14 @@
         <v>0</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N34">
@@ -5860,7 +5860,7 @@
         <v>2.73</v>
       </c>
       <c r="Q34">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="R34">
         <v>2.3</v>
@@ -5881,25 +5881,25 @@
         <v>1.08</v>
       </c>
       <c r="X34">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z34">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AA34">
         <v>1.68</v>
       </c>
       <c r="AB34">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC34">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="AD34">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AE34">
         <v>1.2</v>
@@ -5912,12 +5912,12 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["54"]</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["87"]</t>
         </is>
       </c>
       <c r="AJ34">
@@ -5930,28 +5930,28 @@
         <v>0</v>
       </c>
       <c r="AM34">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN34">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP34">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ34">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="AR34">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AS34">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AT34">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         <v>0</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -6006,21 +6006,21 @@
         <v>0</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N35">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="O35">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P35">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="Q35">
         <v>2.76</v>
@@ -6032,13 +6032,13 @@
         <v>1.34</v>
       </c>
       <c r="T35">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="U35">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="V35">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W35">
         <v>1.06</v>
@@ -6047,19 +6047,19 @@
         <v>1.05</v>
       </c>
       <c r="Y35">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z35">
-        <v>3.58</v>
+        <v>3.72</v>
       </c>
       <c r="AA35">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AB35">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AC35">
-        <v>2.83</v>
+        <v>2.74</v>
       </c>
       <c r="AD35">
         <v>1.4</v>
@@ -6068,7 +6068,7 @@
         <v>1.13</v>
       </c>
       <c r="AF35">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG35">
         <v>2.15</v>
@@ -6080,7 +6080,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["52"]</t>
         </is>
       </c>
       <c r="AJ35">
@@ -6093,28 +6093,28 @@
         <v>0</v>
       </c>
       <c r="AM35">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN35">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO35">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AP35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ35">
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="AR35">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="AS35">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AT35">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
@@ -6145,19 +6145,19 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -6173,111 +6173,111 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N36">
-        <v>2.6</v>
+        <v>1.74</v>
       </c>
       <c r="O36">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P36">
-        <v>2.4</v>
+        <v>4.1</v>
       </c>
       <c r="Q36">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="R36">
         <v>2.3</v>
       </c>
       <c r="S36">
+        <v>1.29</v>
+      </c>
+      <c r="T36">
+        <v>3.4</v>
+      </c>
+      <c r="U36">
+        <v>2.38</v>
+      </c>
+      <c r="V36">
+        <v>1.5</v>
+      </c>
+      <c r="W36">
+        <v>1.09</v>
+      </c>
+      <c r="X36">
+        <v>1.01</v>
+      </c>
+      <c r="Y36">
         <v>1.2</v>
       </c>
-      <c r="T36">
-        <v>3.35</v>
-      </c>
-      <c r="U36">
-        <v>2.25</v>
-      </c>
-      <c r="V36">
+      <c r="Z36">
+        <v>4.33</v>
+      </c>
+      <c r="AA36">
         <v>1.61</v>
       </c>
-      <c r="W36">
-        <v>1.13</v>
-      </c>
-      <c r="X36">
+      <c r="AB36">
+        <v>2.15</v>
+      </c>
+      <c r="AC36">
+        <v>2.6</v>
+      </c>
+      <c r="AD36">
+        <v>1.44</v>
+      </c>
+      <c r="AE36">
+        <v>1.14</v>
+      </c>
+      <c r="AF36">
+        <v>1.57</v>
+      </c>
+      <c r="AG36">
+        <v>2.17</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>["-1"]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>["-1", "-1", "-1", "-1", "-1", "-1", "-1"]</t>
+        </is>
+      </c>
+      <c r="AJ36">
+        <v>1.18</v>
+      </c>
+      <c r="AK36">
+        <v>2</v>
+      </c>
+      <c r="AL36">
+        <v>0</v>
+      </c>
+      <c r="AM36">
+        <v>3</v>
+      </c>
+      <c r="AN36">
+        <v>13</v>
+      </c>
+      <c r="AO36">
+        <v>10</v>
+      </c>
+      <c r="AP36">
+        <v>24</v>
+      </c>
+      <c r="AQ36">
         <v>1.03</v>
       </c>
-      <c r="Y36">
-        <v>1.11</v>
-      </c>
-      <c r="Z36">
-        <v>4.8</v>
-      </c>
-      <c r="AA36">
-        <v>1.49</v>
-      </c>
-      <c r="AB36">
-        <v>2.3</v>
-      </c>
-      <c r="AC36">
-        <v>2.3</v>
-      </c>
-      <c r="AD36">
-        <v>1.57</v>
-      </c>
-      <c r="AE36">
-        <v>1.18</v>
-      </c>
-      <c r="AF36">
-        <v>1.44</v>
-      </c>
-      <c r="AG36">
-        <v>2.5</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ36">
-        <v>1.48</v>
-      </c>
-      <c r="AK36">
-        <v>1.44</v>
-      </c>
-      <c r="AL36">
-        <v>0</v>
-      </c>
-      <c r="AM36">
-        <v>-1</v>
-      </c>
-      <c r="AN36">
-        <v>-1</v>
-      </c>
-      <c r="AO36">
-        <v>-1</v>
-      </c>
-      <c r="AP36">
-        <v>-1</v>
-      </c>
-      <c r="AQ36">
-        <v>0</v>
-      </c>
       <c r="AR36">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AS36">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AT36">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
@@ -6308,139 +6308,139 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N37">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="O37">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P37">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="Q37">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="R37">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="S37">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T37">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U37">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="V37">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W37">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X37">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y37">
         <v>1.2</v>
       </c>
       <c r="Z37">
-        <v>4.33</v>
+        <v>4.52</v>
       </c>
       <c r="AA37">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="AB37">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC37">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AD37">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE37">
         <v>1.13</v>
       </c>
       <c r="AF37">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AG37">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10", "29", "45+2", "89"]</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["23", "34", "90+2"]</t>
         </is>
       </c>
       <c r="AJ37">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK37">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AL37">
         <v>0</v>
       </c>
       <c r="AM37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO37">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP37">
-        <v>-1</v>
+        <v>26</v>
       </c>
       <c r="AQ37">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AR37">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AS37">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AT37">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
@@ -6471,139 +6471,139 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38">
         <v>0</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N38">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="O38">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P38">
+        <v>2.26</v>
+      </c>
+      <c r="Q38">
         <v>3</v>
       </c>
-      <c r="Q38">
-        <v>2.74</v>
-      </c>
       <c r="R38">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S38">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T38">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="U38">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="V38">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="W38">
+        <v>1.13</v>
+      </c>
+      <c r="X38">
+        <v>1.03</v>
+      </c>
+      <c r="Y38">
         <v>1.11</v>
       </c>
-      <c r="X38">
-        <v>1</v>
-      </c>
-      <c r="Y38">
+      <c r="Z38">
+        <v>4.8</v>
+      </c>
+      <c r="AA38">
+        <v>1.48</v>
+      </c>
+      <c r="AB38">
+        <v>2.3</v>
+      </c>
+      <c r="AC38">
+        <v>2.3</v>
+      </c>
+      <c r="AD38">
+        <v>1.57</v>
+      </c>
+      <c r="AE38">
         <v>1.18</v>
       </c>
-      <c r="Z38">
-        <v>4.33</v>
-      </c>
-      <c r="AA38">
-        <v>1.57</v>
-      </c>
-      <c r="AB38">
-        <v>2.38</v>
-      </c>
-      <c r="AC38">
-        <v>2.55</v>
-      </c>
-      <c r="AD38">
-        <v>1.52</v>
-      </c>
-      <c r="AE38">
-        <v>1.16</v>
-      </c>
       <c r="AF38">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="AG38">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["35", "78"]</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["80"]</t>
         </is>
       </c>
       <c r="AJ38">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="AK38">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AL38">
         <v>0</v>
       </c>
       <c r="AM38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO38">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AP38">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ38">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AR38">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AS38">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT38">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
@@ -6634,51 +6634,51 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I39">
         <v>0</v>
       </c>
       <c r="J39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L39">
         <v>0</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N39">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="O39">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="P39">
-        <v>5.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q39">
-        <v>2.1</v>
+        <v>2.62</v>
       </c>
       <c r="R39">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="S39">
         <v>1.25</v>
@@ -6687,86 +6687,86 @@
         <v>3.6</v>
       </c>
       <c r="U39">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="V39">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W39">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X39">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y39">
         <v>1.2</v>
       </c>
       <c r="Z39">
-        <v>4.52</v>
+        <v>4.33</v>
       </c>
       <c r="AA39">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AB39">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AC39">
-        <v>2.67</v>
+        <v>2.55</v>
       </c>
       <c r="AD39">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="AE39">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF39">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AG39">
-        <v>2.08</v>
+        <v>2.55</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["76", "86"]</t>
         </is>
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["8", "42"]</t>
         </is>
       </c>
       <c r="AJ39">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AK39">
-        <v>2.11</v>
+        <v>1.68</v>
       </c>
       <c r="AL39">
         <v>0</v>
       </c>
       <c r="AM39">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO39">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP39">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ39">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR39">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS39">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT39">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
@@ -6806,10 +6806,10 @@
         </is>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -6818,14 +6818,14 @@
         <v>0</v>
       </c>
       <c r="K40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N40">
@@ -6847,40 +6847,40 @@
         <v>1.36</v>
       </c>
       <c r="T40">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="U40">
-        <v>3.04</v>
+        <v>3.11</v>
       </c>
       <c r="V40">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W40">
         <v>1.02</v>
       </c>
       <c r="X40">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y40">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="Z40">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="AA40">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AB40">
         <v>1.62</v>
       </c>
       <c r="AC40">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AD40">
         <v>1.25</v>
       </c>
       <c r="AE40">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF40">
         <v>1.87</v>
@@ -6890,46 +6890,46 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["51", "90+2"]</t>
         </is>
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["64"]</t>
         </is>
       </c>
       <c r="AJ40">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AK40">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AL40">
         <v>0</v>
       </c>
       <c r="AM40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN40">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP40">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ40">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AR40">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="AS40">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="AT40">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
@@ -6969,39 +6969,39 @@
         </is>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41">
         <v>0</v>
       </c>
       <c r="K41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N41">
-        <v>3.2</v>
+        <v>2.79</v>
       </c>
       <c r="O41">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P41">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q41">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R41">
         <v>2.05</v>
@@ -7013,31 +7013,31 @@
         <v>2.7</v>
       </c>
       <c r="U41">
-        <v>3.08</v>
+        <v>2.94</v>
       </c>
       <c r="V41">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W41">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X41">
         <v>1.06</v>
       </c>
       <c r="Y41">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z41">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AA41">
         <v>2.1</v>
       </c>
       <c r="AB41">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="AC41">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AD41">
         <v>1.22</v>
@@ -7046,19 +7046,19 @@
         <v>1.06</v>
       </c>
       <c r="AF41">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AG41">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["18", "63"]</t>
         </is>
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["52"]</t>
         </is>
       </c>
       <c r="AJ41">
@@ -7071,28 +7071,28 @@
         <v>0</v>
       </c>
       <c r="AM41">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN41">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ41">
-        <v>0</v>
+        <v>0.74</v>
       </c>
       <c r="AR41">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AS41">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT41">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
@@ -7132,16 +7132,16 @@
         </is>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42">
         <v>0</v>
@@ -7151,111 +7151,111 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N42">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="O42">
         <v>3.1</v>
       </c>
       <c r="P42">
+        <v>1.7</v>
+      </c>
+      <c r="Q42">
+        <v>4.75</v>
+      </c>
+      <c r="R42">
         <v>2</v>
-      </c>
-      <c r="Q42">
-        <v>4.2</v>
-      </c>
-      <c r="R42">
-        <v>2.05</v>
       </c>
       <c r="S42">
         <v>1.4</v>
       </c>
       <c r="T42">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="U42">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="V42">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="W42">
+        <v>1.06</v>
+      </c>
+      <c r="X42">
         <v>1.05</v>
       </c>
-      <c r="X42">
-        <v>1.06</v>
-      </c>
       <c r="Y42">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z42">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="AA42">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AB42">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AC42">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AD42">
+        <v>1.2</v>
+      </c>
+      <c r="AE42">
+        <v>1.04</v>
+      </c>
+      <c r="AF42">
+        <v>1.95</v>
+      </c>
+      <c r="AG42">
+        <v>1.75</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>["45+4"]</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>["45+1"]</t>
+        </is>
+      </c>
+      <c r="AJ42">
+        <v>1.24</v>
+      </c>
+      <c r="AK42">
         <v>1.17</v>
       </c>
-      <c r="AE42">
-        <v>1.03</v>
-      </c>
-      <c r="AF42">
-        <v>1.91</v>
-      </c>
-      <c r="AG42">
-        <v>1.83</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ42">
-        <v>1.33</v>
-      </c>
-      <c r="AK42">
-        <v>1.25</v>
-      </c>
       <c r="AL42">
         <v>0</v>
       </c>
       <c r="AM42">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP42">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AQ42">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="AR42">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AS42">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AT42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
@@ -7295,72 +7295,72 @@
         </is>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43">
         <v>0</v>
       </c>
       <c r="K43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N43">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="O43">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P43">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="Q43">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="R43">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S43">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T43">
-        <v>2.93</v>
+        <v>3.1</v>
       </c>
       <c r="U43">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="V43">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W43">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X43">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y43">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z43">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="AA43">
         <v>1.72</v>
       </c>
       <c r="AB43">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AC43">
         <v>2.8</v>
@@ -7372,53 +7372,53 @@
         <v>1.13</v>
       </c>
       <c r="AF43">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AG43">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["14", "65", "77"]</t>
         </is>
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+3", "90+4"]</t>
         </is>
       </c>
       <c r="AJ43">
         <v>1.16</v>
       </c>
       <c r="AK43">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AL43">
         <v>0</v>
       </c>
       <c r="AM43">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP43">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ43">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="AR43">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AS43">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AT43">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
@@ -7458,13 +7458,13 @@
         </is>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44">
         <v>0</v>
       </c>
       <c r="I44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44">
         <v>0</v>
@@ -7477,20 +7477,20 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N44">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="O44">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="P44">
-        <v>3.85</v>
+        <v>5.25</v>
       </c>
       <c r="Q44">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="R44">
         <v>2.5</v>
@@ -7499,50 +7499,50 @@
         <v>1.22</v>
       </c>
       <c r="T44">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="U44">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="V44">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W44">
         <v>1.13</v>
       </c>
       <c r="X44">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z44">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AA44">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AB44">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AC44">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AD44">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AE44">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AF44">
         <v>1.53</v>
       </c>
       <c r="AG44">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["15"]</t>
         </is>
       </c>
       <c r="AI44" t="inlineStr">
@@ -7554,34 +7554,34 @@
         <v>1.2</v>
       </c>
       <c r="AK44">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AL44">
         <v>0</v>
       </c>
       <c r="AM44">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN44">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO44">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP44">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ44">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR44">
-        <v>0</v>
+        <v>0.59</v>
       </c>
       <c r="AS44">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT44">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
@@ -7640,23 +7640,23 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N45">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="O45">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="P45">
         <v>4</v>
       </c>
       <c r="Q45">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="R45">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="S45">
         <v>1.22</v>
@@ -7665,43 +7665,43 @@
         <v>3.9</v>
       </c>
       <c r="U45">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="V45">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="W45">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="X45">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y45">
         <v>1.11</v>
       </c>
       <c r="Z45">
-        <v>5.75</v>
+        <v>6.63</v>
       </c>
       <c r="AA45">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AB45">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="AC45">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AD45">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="AE45">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AF45">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AG45">
-        <v>2.53</v>
+        <v>2.77</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>1.22</v>
       </c>
       <c r="AK45">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7784,7 +7784,7 @@
         </is>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46">
         <v>0</v>
@@ -7796,33 +7796,33 @@
         <v>0</v>
       </c>
       <c r="K46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46">
         <v>0</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N46">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="O46">
-        <v>3.8</v>
+        <v>3.48</v>
       </c>
       <c r="P46">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Q46">
         <v>3.5</v>
       </c>
       <c r="R46">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="S46">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="T46">
         <v>4</v>
@@ -7834,19 +7834,19 @@
         <v>1.79</v>
       </c>
       <c r="W46">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X46">
         <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z46">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA46">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AB46">
         <v>3.25</v>
@@ -7855,20 +7855,20 @@
         <v>1.91</v>
       </c>
       <c r="AD46">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AE46">
         <v>1.35</v>
       </c>
       <c r="AF46">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AG46">
-        <v>2.98</v>
+        <v>3.04</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["48"]</t>
         </is>
       </c>
       <c r="AI46" t="inlineStr">
@@ -7886,28 +7886,28 @@
         <v>0</v>
       </c>
       <c r="AM46">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN46">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO46">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP46">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ46">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AR46">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AS46">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AT46">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
@@ -7947,30 +7947,30 @@
         </is>
       </c>
       <c r="G47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N47">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="O47">
         <v>3.6</v>
@@ -7979,16 +7979,16 @@
         <v>2</v>
       </c>
       <c r="Q47">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="R47">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="S47">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="T47">
-        <v>4.15</v>
+        <v>3.84</v>
       </c>
       <c r="U47">
         <v>2</v>
@@ -8021,7 +8021,7 @@
         <v>1.85</v>
       </c>
       <c r="AE47">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AF47">
         <v>1.36</v>
@@ -8031,12 +8031,12 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["1", "49"]</t>
         </is>
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["42", "71", "78"]</t>
         </is>
       </c>
       <c r="AJ47">
@@ -8049,28 +8049,28 @@
         <v>0</v>
       </c>
       <c r="AM47">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN47">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO47">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AP47">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ47">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="AR47">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="AS47">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT47">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
@@ -8110,16 +8110,16 @@
         </is>
       </c>
       <c r="G48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K48">
         <v>0</v>
@@ -8129,26 +8129,26 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N48">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="O48">
-        <v>3.8</v>
+        <v>4.15</v>
       </c>
       <c r="P48">
         <v>4.33</v>
       </c>
       <c r="Q48">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R48">
         <v>2.45</v>
       </c>
       <c r="S48">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T48">
         <v>3.6</v>
@@ -8163,25 +8163,25 @@
         <v>1.11</v>
       </c>
       <c r="X48">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z48">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="AA48">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AB48">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AC48">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="AD48">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AE48">
         <v>1.18</v>
@@ -8190,50 +8190,50 @@
         <v>1.57</v>
       </c>
       <c r="AG48">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["16", "43"]</t>
         </is>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["21", "45+3"]</t>
         </is>
       </c>
       <c r="AJ48">
         <v>1.15</v>
       </c>
       <c r="AK48">
+        <v>1.95</v>
+      </c>
+      <c r="AL48">
+        <v>0</v>
+      </c>
+      <c r="AM48">
         <v>2</v>
       </c>
-      <c r="AL48">
-        <v>0</v>
-      </c>
-      <c r="AM48">
-        <v>-1</v>
-      </c>
       <c r="AN48">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO48">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AP48">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ48">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="AR48">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="AS48">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT48">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
@@ -8264,139 +8264,139 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="G49">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H49">
         <v>0</v>
       </c>
       <c r="I49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49">
         <v>0</v>
       </c>
       <c r="K49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L49">
         <v>0</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N49">
-        <v>2.22</v>
+        <v>1.43</v>
       </c>
       <c r="O49">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="P49">
-        <v>2.61</v>
+        <v>5</v>
       </c>
       <c r="Q49">
-        <v>3.12</v>
+        <v>1.9</v>
       </c>
       <c r="R49">
-        <v>2.33</v>
+        <v>2.47</v>
       </c>
       <c r="S49">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T49">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="U49">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="V49">
-        <v>1.38</v>
+        <v>1.64</v>
       </c>
       <c r="W49">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X49">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="Z49">
-        <v>4.05</v>
+        <v>5.05</v>
       </c>
       <c r="AA49">
-        <v>1.75</v>
+        <v>1.42</v>
       </c>
       <c r="AB49">
-        <v>1.95</v>
+        <v>2.49</v>
       </c>
       <c r="AC49">
-        <v>2.91</v>
+        <v>2.15</v>
       </c>
       <c r="AD49">
-        <v>1.35</v>
+        <v>1.62</v>
       </c>
       <c r="AE49">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AF49">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AG49">
         <v>2.21</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
+          <t>["8", "64", "84"]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ49">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK49">
-        <v>1.5</v>
+        <v>2.53</v>
       </c>
       <c r="AL49">
         <v>0</v>
       </c>
       <c r="AM49">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN49">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO49">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP49">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ49">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR49">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="AS49">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AT49">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
@@ -8427,139 +8427,139 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H50">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I50">
         <v>0</v>
       </c>
       <c r="J50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L50">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N50">
-        <v>1.48</v>
+        <v>2.3</v>
       </c>
       <c r="O50">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="P50">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="Q50">
-        <v>1.9</v>
+        <v>2.63</v>
       </c>
       <c r="R50">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="S50">
+        <v>1.25</v>
+      </c>
+      <c r="T50">
+        <v>3.5</v>
+      </c>
+      <c r="U50">
+        <v>1.92</v>
+      </c>
+      <c r="V50">
+        <v>1.47</v>
+      </c>
+      <c r="W50">
+        <v>1.09</v>
+      </c>
+      <c r="X50">
+        <v>1.01</v>
+      </c>
+      <c r="Y50">
+        <v>1.16</v>
+      </c>
+      <c r="Z50">
+        <v>5.27</v>
+      </c>
+      <c r="AA50">
+        <v>1.55</v>
+      </c>
+      <c r="AB50">
+        <v>2.4</v>
+      </c>
+      <c r="AC50">
+        <v>2.3</v>
+      </c>
+      <c r="AD50">
+        <v>1.51</v>
+      </c>
+      <c r="AE50">
+        <v>1.23</v>
+      </c>
+      <c r="AF50">
+        <v>1.43</v>
+      </c>
+      <c r="AG50">
+        <v>2.51</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>["53", "82"]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>["28", "38", "58", "66", "74"]</t>
+        </is>
+      </c>
+      <c r="AJ50">
         <v>1.22</v>
       </c>
-      <c r="T50">
-        <v>3.75</v>
-      </c>
-      <c r="U50">
-        <v>2.05</v>
-      </c>
-      <c r="V50">
-        <v>1.65</v>
-      </c>
-      <c r="W50">
-        <v>1.14</v>
-      </c>
-      <c r="X50">
-        <v>1.02</v>
-      </c>
-      <c r="Y50">
+      <c r="AK50">
+        <v>1.6</v>
+      </c>
+      <c r="AL50">
+        <v>0</v>
+      </c>
+      <c r="AM50">
+        <v>3</v>
+      </c>
+      <c r="AN50">
+        <v>4</v>
+      </c>
+      <c r="AO50">
+        <v>8</v>
+      </c>
+      <c r="AP50">
+        <v>4</v>
+      </c>
+      <c r="AQ50">
         <v>1.17</v>
       </c>
-      <c r="Z50">
-        <v>5.1</v>
-      </c>
-      <c r="AA50">
-        <v>1.41</v>
-      </c>
-      <c r="AB50">
-        <v>2.52</v>
-      </c>
-      <c r="AC50">
-        <v>2.15</v>
-      </c>
-      <c r="AD50">
-        <v>1.62</v>
-      </c>
-      <c r="AE50">
-        <v>1.28</v>
-      </c>
-      <c r="AF50">
-        <v>1.57</v>
-      </c>
-      <c r="AG50">
-        <v>2.27</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ50">
-        <v>1.14</v>
-      </c>
-      <c r="AK50">
-        <v>2.36</v>
-      </c>
-      <c r="AL50">
-        <v>0</v>
-      </c>
-      <c r="AM50">
-        <v>-1</v>
-      </c>
-      <c r="AN50">
-        <v>-1</v>
-      </c>
-      <c r="AO50">
-        <v>-1</v>
-      </c>
-      <c r="AP50">
-        <v>-1</v>
-      </c>
-      <c r="AQ50">
-        <v>0</v>
-      </c>
       <c r="AR50">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="AS50">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AT50">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
@@ -8590,139 +8590,139 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H51">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51">
         <v>0</v>
       </c>
       <c r="L51">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N51">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="O51">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P51">
+        <v>2.5</v>
+      </c>
+      <c r="Q51">
+        <v>3.11</v>
+      </c>
+      <c r="R51">
+        <v>2.33</v>
+      </c>
+      <c r="S51">
+        <v>1.3</v>
+      </c>
+      <c r="T51">
+        <v>3.2</v>
+      </c>
+      <c r="U51">
+        <v>2.11</v>
+      </c>
+      <c r="V51">
+        <v>1.38</v>
+      </c>
+      <c r="W51">
+        <v>1.11</v>
+      </c>
+      <c r="X51">
+        <v>1</v>
+      </c>
+      <c r="Y51">
+        <v>1.23</v>
+      </c>
+      <c r="Z51">
+        <v>3.9</v>
+      </c>
+      <c r="AA51">
+        <v>1.75</v>
+      </c>
+      <c r="AB51">
+        <v>1.95</v>
+      </c>
+      <c r="AC51">
         <v>2.7</v>
       </c>
-      <c r="Q51">
-        <v>2.63</v>
-      </c>
-      <c r="R51">
-        <v>2.4</v>
-      </c>
-      <c r="S51">
-        <v>1.27</v>
-      </c>
-      <c r="T51">
-        <v>3.5</v>
-      </c>
-      <c r="U51">
-        <v>1.96</v>
-      </c>
-      <c r="V51">
-        <v>1.45</v>
-      </c>
-      <c r="W51">
-        <v>1.08</v>
-      </c>
-      <c r="X51">
-        <v>1.01</v>
-      </c>
-      <c r="Y51">
-        <v>1.13</v>
-      </c>
-      <c r="Z51">
-        <v>5</v>
-      </c>
-      <c r="AA51">
-        <v>1.52</v>
-      </c>
-      <c r="AB51">
-        <v>2.25</v>
-      </c>
-      <c r="AC51">
-        <v>2.4</v>
-      </c>
       <c r="AD51">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AE51">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="AF51">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AG51">
-        <v>2.45</v>
+        <v>2.23</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["37"]</t>
         </is>
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["26", "77", "90+2"]</t>
         </is>
       </c>
       <c r="AJ51">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK51">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AL51">
         <v>0</v>
       </c>
       <c r="AM51">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN51">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO51">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP51">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ51">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR51">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AS51">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AT51">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
@@ -8762,36 +8762,36 @@
         </is>
       </c>
       <c r="G52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I52">
         <v>0</v>
       </c>
       <c r="J52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N52">
-        <v>5.85</v>
+        <v>5.35</v>
       </c>
       <c r="O52">
-        <v>4.85</v>
+        <v>4.33</v>
       </c>
       <c r="P52">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="Q52">
         <v>5</v>
@@ -8821,19 +8821,19 @@
         <v>1.08</v>
       </c>
       <c r="Z52">
-        <v>6.5</v>
+        <v>6.15</v>
       </c>
       <c r="AA52">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AB52">
         <v>3.05</v>
       </c>
       <c r="AC52">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AD52">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AE52">
         <v>1.35</v>
@@ -8846,46 +8846,46 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["87"]</t>
         </is>
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["19", "76"]</t>
         </is>
       </c>
       <c r="AJ52">
         <v>2.62</v>
       </c>
       <c r="AK52">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AL52">
         <v>0</v>
       </c>
       <c r="AM52">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN52">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO52">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP52">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ52">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR52">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AS52">
-        <v>0<